--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,65 +461,70 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Radiación solar [W/m2] - promedio</t>
+          <t>Radiación solar [W/m2] 1 - promedio</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Radiación solar [W/m2] 2 - promedio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>DPV [kPa] - promedio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>DPV [kPa] - mín</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Humedad relativa HC [%] - promedio</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Humedad relativa HC [%] - máx</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Humedad relativa HC [%] - mín</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Precipitación [mm] - sum</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Panel solar [mV] - última</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Batería [mV] - última</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>DeltaT [°C] - promedio</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>DeltaT [°C] - máx</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DeltaT [°C] - mín</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Duración del sol [mín] - tiempo</t>
         </is>
@@ -528,236 +533,239 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.92</v>
+        <v>16.49</v>
       </c>
       <c r="C2" t="n">
-        <v>17.22</v>
+        <v>16.79</v>
       </c>
       <c r="D2" t="n">
-        <v>16.72</v>
+        <v>16.31</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F2" t="n">
-        <v>13.8</v>
+        <v>14.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.31</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>83.48999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="K2" t="n">
-        <v>85.67</v>
+        <v>89.09</v>
       </c>
       <c r="L2" t="n">
-        <v>80.43000000000001</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>87.73</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6465</v>
+        <v>5349</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>6445</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.37</v>
+        <v>16.27</v>
       </c>
       <c r="C3" t="n">
-        <v>17.64</v>
+        <v>16.31</v>
       </c>
       <c r="D3" t="n">
-        <v>17.15</v>
+        <v>16.24</v>
       </c>
       <c r="E3" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F3" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.36</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="J3" t="n">
-        <v>81.5</v>
+        <v>0.15</v>
       </c>
       <c r="K3" t="n">
-        <v>83.2</v>
+        <v>90.12</v>
       </c>
       <c r="L3" t="n">
-        <v>79.69</v>
+        <v>91.63</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>88.84</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6471</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>6422</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.37</v>
+        <v>16.37</v>
       </c>
       <c r="C4" t="n">
-        <v>17.71</v>
+        <v>16.42</v>
       </c>
       <c r="D4" t="n">
-        <v>17.16</v>
+        <v>16.3</v>
       </c>
       <c r="E4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F4" t="n">
         <v>14.4</v>
       </c>
-      <c r="F4" t="n">
-        <v>14</v>
-      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.33</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>83.11</v>
+        <v>0.18</v>
       </c>
       <c r="K4" t="n">
-        <v>85.31</v>
+        <v>88.97</v>
       </c>
       <c r="L4" t="n">
-        <v>78.94</v>
+        <v>90.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6474</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>6414</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.78</v>
+        <v>16.35</v>
       </c>
       <c r="C5" t="n">
-        <v>18.2</v>
+        <v>16.36</v>
       </c>
       <c r="D5" t="n">
-        <v>17.44</v>
+        <v>16.35</v>
       </c>
       <c r="E5" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="F5" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.38</v>
+        <v>2592</v>
       </c>
       <c r="I5" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="J5" t="n">
-        <v>81.01000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="K5" t="n">
-        <v>82.84999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="L5" t="n">
-        <v>78.13</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>84.31</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6494</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>6425</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -766,2629 +774,2739 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.91</v>
+        <v>16.33</v>
       </c>
       <c r="C6" t="n">
-        <v>19.32</v>
+        <v>16.56</v>
       </c>
       <c r="D6" t="n">
-        <v>18.33</v>
+        <v>15.86</v>
       </c>
       <c r="E6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="F6" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.59</v>
+        <v>2522</v>
       </c>
       <c r="I6" t="n">
-        <v>0.49</v>
+        <v>0.19</v>
       </c>
       <c r="J6" t="n">
-        <v>72.89</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>76.66</v>
+        <v>89.8</v>
       </c>
       <c r="L6" t="n">
-        <v>67.31</v>
+        <v>99.73</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>85.27</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6496</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>6422</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.65</v>
+        <v>16.27</v>
       </c>
       <c r="C7" t="n">
-        <v>19.86</v>
+        <v>16.37</v>
       </c>
       <c r="D7" t="n">
-        <v>19.37</v>
+        <v>16.2</v>
       </c>
       <c r="E7" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="F7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.65</v>
+        <v>0.17</v>
       </c>
       <c r="J7" t="n">
-        <v>69.28</v>
+        <v>0.15</v>
       </c>
       <c r="K7" t="n">
-        <v>71.03</v>
+        <v>90.44</v>
       </c>
       <c r="L7" t="n">
-        <v>67.26000000000001</v>
+        <v>91.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6511</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>6417</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.34</v>
+        <v>16.26</v>
       </c>
       <c r="C8" t="n">
-        <v>19.5</v>
+        <v>16.49</v>
       </c>
       <c r="D8" t="n">
-        <v>19.25</v>
+        <v>16.14</v>
       </c>
       <c r="E8" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="F8" t="n">
-        <v>13.4</v>
+        <v>14.6</v>
       </c>
       <c r="G8" t="n">
-        <v>67</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.68</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.67</v>
+        <v>0.17</v>
       </c>
       <c r="J8" t="n">
-        <v>69.37</v>
+        <v>0.15</v>
       </c>
       <c r="K8" t="n">
-        <v>70.14</v>
+        <v>90.33</v>
       </c>
       <c r="L8" t="n">
-        <v>68.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6536</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>6425</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.29</v>
+        <v>16.61</v>
       </c>
       <c r="C9" t="n">
-        <v>19.86</v>
+        <v>16.82</v>
       </c>
       <c r="D9" t="n">
-        <v>19.1</v>
+        <v>16.45</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="F9" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.66</v>
+        <v>0.23</v>
       </c>
       <c r="J9" t="n">
-        <v>68.94</v>
+        <v>0.19</v>
       </c>
       <c r="K9" t="n">
-        <v>69.94</v>
+        <v>87.3</v>
       </c>
       <c r="L9" t="n">
-        <v>66.66</v>
+        <v>89.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>86.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4462</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6539</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>6434</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.82</v>
+        <v>16.92</v>
       </c>
       <c r="C10" t="n">
-        <v>21.19</v>
+        <v>17.22</v>
       </c>
       <c r="D10" t="n">
-        <v>19.8</v>
+        <v>16.72</v>
       </c>
       <c r="E10" t="n">
-        <v>12.3</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>11.7</v>
+        <v>13.8</v>
       </c>
       <c r="G10" t="n">
-        <v>215</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.02</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="J10" t="n">
-        <v>58.55</v>
+        <v>0.27</v>
       </c>
       <c r="K10" t="n">
-        <v>67.09</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>55.27</v>
+        <v>85.67</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6579</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>6465</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>60</v>
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.17</v>
+        <v>17.37</v>
       </c>
       <c r="C11" t="n">
-        <v>21.41</v>
+        <v>17.64</v>
       </c>
       <c r="D11" t="n">
-        <v>20.87</v>
+        <v>17.15</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3</v>
+        <v>14.1</v>
       </c>
       <c r="F11" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="G11" t="n">
-        <v>419</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.06</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.99</v>
+        <v>0.36</v>
       </c>
       <c r="J11" t="n">
-        <v>57.42</v>
+        <v>0.33</v>
       </c>
       <c r="K11" t="n">
-        <v>60.15</v>
+        <v>81.5</v>
       </c>
       <c r="L11" t="n">
-        <v>55.34</v>
+        <v>83.2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>79.69</v>
       </c>
       <c r="N11" t="n">
-        <v>6777</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6613</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>6471</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>60</v>
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21.2</v>
+        <v>17.37</v>
       </c>
       <c r="C12" t="n">
-        <v>21.55</v>
+        <v>17.71</v>
       </c>
       <c r="D12" t="n">
-        <v>20.85</v>
+        <v>17.16</v>
       </c>
       <c r="E12" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="F12" t="n">
-        <v>12.1</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>629</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.04</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="J12" t="n">
-        <v>58.56</v>
+        <v>0.28</v>
       </c>
       <c r="K12" t="n">
-        <v>61.5</v>
+        <v>83.11</v>
       </c>
       <c r="L12" t="n">
-        <v>56.2</v>
+        <v>85.31</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>78.94</v>
       </c>
       <c r="N12" t="n">
-        <v>6849</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6647</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>6474</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>60</v>
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.75</v>
+        <v>17.78</v>
       </c>
       <c r="C13" t="n">
-        <v>21.44</v>
+        <v>18.2</v>
       </c>
       <c r="D13" t="n">
-        <v>20.1</v>
+        <v>17.44</v>
       </c>
       <c r="E13" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="F13" t="n">
-        <v>12.1</v>
+        <v>14.3</v>
       </c>
       <c r="G13" t="n">
-        <v>612</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.98</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.38</v>
       </c>
       <c r="J13" t="n">
-        <v>59.8</v>
+        <v>0.34</v>
       </c>
       <c r="K13" t="n">
-        <v>61.83</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>58.57</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="N13" t="n">
-        <v>6901</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6676</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>6494</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>60</v>
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20.11</v>
+        <v>18.91</v>
       </c>
       <c r="C14" t="n">
-        <v>21.09</v>
+        <v>19.32</v>
       </c>
       <c r="D14" t="n">
-        <v>19.18</v>
+        <v>18.33</v>
       </c>
       <c r="E14" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="F14" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="G14" t="n">
-        <v>471</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.85</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="J14" t="n">
-        <v>63.63</v>
+        <v>0.49</v>
       </c>
       <c r="K14" t="n">
-        <v>67.22</v>
+        <v>72.89</v>
       </c>
       <c r="L14" t="n">
-        <v>59.39</v>
+        <v>76.66</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>67.31</v>
       </c>
       <c r="N14" t="n">
-        <v>6810</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6613</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>6496</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
         <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.28</v>
+        <v>19.65</v>
       </c>
       <c r="C15" t="n">
-        <v>19.69</v>
+        <v>19.86</v>
       </c>
       <c r="D15" t="n">
-        <v>18.97</v>
+        <v>19.37</v>
       </c>
       <c r="E15" t="n">
-        <v>12.9</v>
+        <v>13.8</v>
       </c>
       <c r="F15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="G15" t="n">
-        <v>300</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.73</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.65</v>
       </c>
-      <c r="J15" t="n">
-        <v>66.97</v>
-      </c>
       <c r="K15" t="n">
-        <v>70.23999999999999</v>
+        <v>69.28</v>
       </c>
       <c r="L15" t="n">
-        <v>65.22</v>
+        <v>71.03</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>6681</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6565</v>
+        <v>2267</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>6511</v>
       </c>
       <c r="Q15" t="n">
         <v>4</v>
       </c>
       <c r="R15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="S15" t="n">
-        <v>60</v>
+      <c r="T15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.64</v>
+        <v>19.34</v>
       </c>
       <c r="C16" t="n">
-        <v>20.12</v>
+        <v>19.5</v>
       </c>
       <c r="D16" t="n">
-        <v>17.71</v>
+        <v>19.25</v>
       </c>
       <c r="E16" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="F16" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="G16" t="n">
-        <v>347</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.61</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="J16" t="n">
-        <v>71.42</v>
+        <v>0.67</v>
       </c>
       <c r="K16" t="n">
-        <v>76.48</v>
+        <v>69.37</v>
       </c>
       <c r="L16" t="n">
-        <v>66.62</v>
+        <v>70.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>68.55</v>
       </c>
       <c r="N16" t="n">
-        <v>6739</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6565</v>
+        <v>4721</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>6536</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="S16" t="n">
-        <v>60</v>
+      <c r="T16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.37</v>
+        <v>19.29</v>
       </c>
       <c r="C17" t="n">
-        <v>18.2</v>
+        <v>19.86</v>
       </c>
       <c r="D17" t="n">
-        <v>16.67</v>
+        <v>19.1</v>
       </c>
       <c r="E17" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="F17" t="n">
         <v>13.3</v>
       </c>
       <c r="G17" t="n">
-        <v>167</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>79.89</v>
+        <v>0.66</v>
       </c>
       <c r="K17" t="n">
-        <v>86.01000000000001</v>
+        <v>68.94</v>
       </c>
       <c r="L17" t="n">
-        <v>75.15000000000001</v>
+        <v>69.94</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>66.66</v>
       </c>
       <c r="N17" t="n">
-        <v>6499</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6494</v>
+        <v>4462</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>6539</v>
       </c>
       <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>40</v>
+      <c r="T17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.89</v>
+        <v>20.82</v>
       </c>
       <c r="C18" t="n">
-        <v>16.51</v>
+        <v>21.19</v>
       </c>
       <c r="D18" t="n">
-        <v>15.53</v>
+        <v>19.8</v>
       </c>
       <c r="E18" t="n">
-        <v>14.5</v>
+        <v>12.3</v>
       </c>
       <c r="F18" t="n">
-        <v>14.3</v>
+        <v>11.7</v>
       </c>
       <c r="G18" t="n">
-        <v>40</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.14</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>1.02</v>
       </c>
       <c r="J18" t="n">
-        <v>91.95</v>
+        <v>0.75</v>
       </c>
       <c r="K18" t="n">
-        <v>93.86</v>
+        <v>58.55</v>
       </c>
       <c r="L18" t="n">
-        <v>87.84999999999999</v>
+        <v>67.09</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>55.27</v>
       </c>
       <c r="N18" t="n">
-        <v>4793</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6442</v>
+        <v>6250</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>6579</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.63</v>
+        <v>21.17</v>
       </c>
       <c r="C19" t="n">
-        <v>15.72</v>
+        <v>21.41</v>
       </c>
       <c r="D19" t="n">
-        <v>15.55</v>
+        <v>20.87</v>
       </c>
       <c r="E19" t="n">
-        <v>14.3</v>
+        <v>12.3</v>
       </c>
       <c r="F19" t="n">
-        <v>14.2</v>
+        <v>11.8</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.13</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.11</v>
+        <v>1.06</v>
       </c>
       <c r="J19" t="n">
-        <v>92.23</v>
+        <v>0.99</v>
       </c>
       <c r="K19" t="n">
-        <v>93.61</v>
+        <v>57.42</v>
       </c>
       <c r="L19" t="n">
-        <v>90.98</v>
+        <v>60.15</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>55.34</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6417</v>
+        <v>6777</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>6613</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.65</v>
+        <v>21.2</v>
       </c>
       <c r="C20" t="n">
-        <v>15.76</v>
+        <v>21.55</v>
       </c>
       <c r="D20" t="n">
-        <v>15.53</v>
+        <v>20.85</v>
       </c>
       <c r="E20" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="F20" t="n">
-        <v>14.5</v>
+        <v>12.1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.11</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.1</v>
+        <v>1.04</v>
       </c>
       <c r="J20" t="n">
-        <v>93.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>93.83</v>
+        <v>58.56</v>
       </c>
       <c r="L20" t="n">
-        <v>92.88</v>
+        <v>61.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>56.2</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6405</v>
+        <v>6849</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>6647</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.63</v>
+        <v>20.75</v>
       </c>
       <c r="C21" t="n">
-        <v>15.74</v>
+        <v>21.44</v>
       </c>
       <c r="D21" t="n">
-        <v>15.57</v>
+        <v>20.1</v>
       </c>
       <c r="E21" t="n">
-        <v>14.7</v>
+        <v>12.6</v>
       </c>
       <c r="F21" t="n">
-        <v>14.6</v>
+        <v>12.1</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.08</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="J21" t="n">
-        <v>94.87</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="n">
-        <v>95.69</v>
+        <v>59.8</v>
       </c>
       <c r="L21" t="n">
-        <v>93.40000000000001</v>
+        <v>61.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>58.57</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6414</v>
+        <v>6901</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6676</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15.74</v>
+        <v>20.11</v>
       </c>
       <c r="C22" t="n">
-        <v>15.95</v>
+        <v>21.09</v>
       </c>
       <c r="D22" t="n">
-        <v>15.62</v>
+        <v>19.18</v>
       </c>
       <c r="E22" t="n">
-        <v>14.9</v>
+        <v>12.9</v>
       </c>
       <c r="F22" t="n">
-        <v>14.9</v>
+        <v>12.5</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.08</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.06</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="n">
-        <v>95.13</v>
+        <v>0.72</v>
       </c>
       <c r="K22" t="n">
-        <v>96.19</v>
+        <v>63.63</v>
       </c>
       <c r="L22" t="n">
-        <v>94.28</v>
+        <v>67.22</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>59.39</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6422</v>
+        <v>6810</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6613</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.02</v>
+        <v>19.28</v>
       </c>
       <c r="C23" t="n">
-        <v>16.13</v>
+        <v>19.69</v>
       </c>
       <c r="D23" t="n">
-        <v>15.96</v>
+        <v>18.97</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>12.9</v>
       </c>
       <c r="F23" t="n">
-        <v>14.9</v>
+        <v>12.5</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.1</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.09</v>
+        <v>0.73</v>
       </c>
       <c r="J23" t="n">
-        <v>94.3</v>
+        <v>0.65</v>
       </c>
       <c r="K23" t="n">
-        <v>94.76000000000001</v>
+        <v>66.97</v>
       </c>
       <c r="L23" t="n">
-        <v>93.61</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>65.22</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6414</v>
+        <v>6681</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>6565</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.24</v>
+        <v>18.64</v>
       </c>
       <c r="C24" t="n">
-        <v>16.32</v>
+        <v>20.12</v>
       </c>
       <c r="D24" t="n">
-        <v>16.16</v>
+        <v>17.71</v>
       </c>
       <c r="E24" t="n">
-        <v>15.1</v>
+        <v>13.3</v>
       </c>
       <c r="F24" t="n">
-        <v>15.1</v>
+        <v>12.9</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.11</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.1</v>
+        <v>0.61</v>
       </c>
       <c r="J24" t="n">
-        <v>93.55</v>
+        <v>0.48</v>
       </c>
       <c r="K24" t="n">
-        <v>94.40000000000001</v>
+        <v>71.42</v>
       </c>
       <c r="L24" t="n">
-        <v>92.81</v>
+        <v>76.48</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>66.62</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6417</v>
+        <v>6739</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>6565</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.57</v>
+        <v>17.37</v>
       </c>
       <c r="C25" t="n">
-        <v>16.97</v>
+        <v>18.2</v>
       </c>
       <c r="D25" t="n">
-        <v>16.32</v>
+        <v>16.67</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="F25" t="n">
-        <v>14.7</v>
+        <v>13.3</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.16</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
-        <v>90.97</v>
+        <v>0.26</v>
       </c>
       <c r="K25" t="n">
-        <v>93.34999999999999</v>
+        <v>79.89</v>
       </c>
       <c r="L25" t="n">
-        <v>87.03</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6422</v>
+        <v>6499</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>6494</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.39</v>
+        <v>15.89</v>
       </c>
       <c r="C26" t="n">
-        <v>17.59</v>
+        <v>16.51</v>
       </c>
       <c r="D26" t="n">
-        <v>17.17</v>
+        <v>15.53</v>
       </c>
       <c r="E26" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="F26" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.4</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="J26" t="n">
-        <v>79.91</v>
+        <v>0.1</v>
       </c>
       <c r="K26" t="n">
-        <v>84</v>
+        <v>91.95</v>
       </c>
       <c r="L26" t="n">
-        <v>77.81999999999999</v>
+        <v>93.86</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6417</v>
+        <v>4793</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>6442</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.82</v>
+        <v>15.63</v>
       </c>
       <c r="C27" t="n">
-        <v>17.99</v>
+        <v>15.72</v>
       </c>
       <c r="D27" t="n">
-        <v>17.64</v>
+        <v>15.55</v>
       </c>
       <c r="E27" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="F27" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="J27" t="n">
-        <v>77.5</v>
+        <v>0.11</v>
       </c>
       <c r="K27" t="n">
-        <v>79.29000000000001</v>
+        <v>92.23</v>
       </c>
       <c r="L27" t="n">
-        <v>76.37</v>
+        <v>93.61</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>90.98</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6425</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>6417</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.13</v>
+        <v>15.65</v>
       </c>
       <c r="C28" t="n">
-        <v>18.3</v>
+        <v>15.76</v>
       </c>
       <c r="D28" t="n">
-        <v>17.82</v>
+        <v>15.53</v>
       </c>
       <c r="E28" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="F28" t="n">
-        <v>13.4</v>
+        <v>14.5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.48</v>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.36</v>
+        <v>0.11</v>
       </c>
       <c r="J28" t="n">
-        <v>76.5</v>
+        <v>0.1</v>
       </c>
       <c r="K28" t="n">
-        <v>81.88</v>
+        <v>93.44</v>
       </c>
       <c r="L28" t="n">
-        <v>74.38</v>
+        <v>93.83</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>92.88</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6428</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>6405</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.85</v>
+        <v>15.63</v>
       </c>
       <c r="C29" t="n">
-        <v>18.1</v>
+        <v>15.74</v>
       </c>
       <c r="D29" t="n">
-        <v>17.67</v>
+        <v>15.57</v>
       </c>
       <c r="E29" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="F29" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="n">
-        <v>0.38</v>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="J29" t="n">
-        <v>80.95</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>82.98</v>
+        <v>94.87</v>
       </c>
       <c r="L29" t="n">
-        <v>77.86</v>
+        <v>95.69</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6434</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>6414</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18.69</v>
+        <v>15.74</v>
       </c>
       <c r="C30" t="n">
-        <v>19.09</v>
+        <v>15.95</v>
       </c>
       <c r="D30" t="n">
-        <v>18.24</v>
+        <v>15.62</v>
       </c>
       <c r="E30" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>14.9</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="J30" t="n">
-        <v>71.91</v>
+        <v>0.06</v>
       </c>
       <c r="K30" t="n">
-        <v>75.81999999999999</v>
+        <v>95.13</v>
       </c>
       <c r="L30" t="n">
-        <v>68.15000000000001</v>
+        <v>96.19</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>94.28</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6440</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>6422</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.36</v>
+        <v>16.02</v>
       </c>
       <c r="C31" t="n">
-        <v>19.58</v>
+        <v>16.13</v>
       </c>
       <c r="D31" t="n">
-        <v>19.06</v>
+        <v>15.96</v>
       </c>
       <c r="E31" t="n">
-        <v>12.8</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>12.5</v>
+        <v>14.9</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.67</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
-        <v>66.34999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="K31" t="n">
-        <v>69.37</v>
+        <v>94.3</v>
       </c>
       <c r="L31" t="n">
-        <v>63.92</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>93.61</v>
       </c>
       <c r="N31" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6465</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>6414</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19.82</v>
+        <v>16.24</v>
       </c>
       <c r="C32" t="n">
-        <v>20.22</v>
+        <v>16.32</v>
       </c>
       <c r="D32" t="n">
-        <v>19.58</v>
+        <v>16.16</v>
       </c>
       <c r="E32" t="n">
-        <v>12.9</v>
+        <v>15.1</v>
       </c>
       <c r="F32" t="n">
-        <v>12.6</v>
+        <v>15.1</v>
       </c>
       <c r="G32" t="n">
-        <v>114</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.76</v>
+        <v>0.11</v>
       </c>
       <c r="J32" t="n">
-        <v>64.69</v>
+        <v>0.1</v>
       </c>
       <c r="K32" t="n">
-        <v>67.25</v>
+        <v>93.55</v>
       </c>
       <c r="L32" t="n">
-        <v>63.16</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>92.81</v>
       </c>
       <c r="N32" t="n">
-        <v>3944</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6511</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>6417</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>19.77</v>
+        <v>16.57</v>
       </c>
       <c r="C33" t="n">
-        <v>20.09</v>
+        <v>16.97</v>
       </c>
       <c r="D33" t="n">
-        <v>19.54</v>
+        <v>16.32</v>
       </c>
       <c r="E33" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>12.2</v>
+        <v>14.7</v>
       </c>
       <c r="G33" t="n">
-        <v>158</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.77</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.71</v>
+        <v>0.16</v>
       </c>
       <c r="J33" t="n">
-        <v>66.33</v>
+        <v>0.12</v>
       </c>
       <c r="K33" t="n">
-        <v>68.87</v>
+        <v>90.97</v>
       </c>
       <c r="L33" t="n">
-        <v>61.21</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>87.03</v>
       </c>
       <c r="N33" t="n">
-        <v>6671</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6539</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>6422</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.58</v>
+        <v>17.39</v>
       </c>
       <c r="C34" t="n">
-        <v>19.95</v>
+        <v>17.59</v>
       </c>
       <c r="D34" t="n">
-        <v>19.38</v>
+        <v>17.17</v>
       </c>
       <c r="E34" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="F34" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="G34" t="n">
-        <v>138</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
-        <v>65.27</v>
+        <v>0.31</v>
       </c>
       <c r="K34" t="n">
-        <v>67.09999999999999</v>
+        <v>79.91</v>
       </c>
       <c r="L34" t="n">
-        <v>61.34</v>
+        <v>84</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>6389</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6534</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>6417</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>35</v>
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.96</v>
+        <v>17.82</v>
       </c>
       <c r="C35" t="n">
-        <v>20.7</v>
+        <v>17.99</v>
       </c>
       <c r="D35" t="n">
-        <v>19.58</v>
+        <v>17.64</v>
       </c>
       <c r="E35" t="n">
-        <v>12.6</v>
+        <v>13.7</v>
       </c>
       <c r="F35" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="G35" t="n">
-        <v>171</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.86</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
       <c r="J35" t="n">
-        <v>62.94</v>
+        <v>0.42</v>
       </c>
       <c r="K35" t="n">
-        <v>66.14</v>
+        <v>77.5</v>
       </c>
       <c r="L35" t="n">
-        <v>60.5</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>76.37</v>
       </c>
       <c r="N35" t="n">
-        <v>4869</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6534</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>6425</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
-        <v>35</v>
+        <v>2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14 13:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.73</v>
+        <v>18.13</v>
       </c>
       <c r="C36" t="n">
-        <v>20.67</v>
+        <v>18.3</v>
       </c>
       <c r="D36" t="n">
-        <v>18.8</v>
+        <v>17.82</v>
       </c>
       <c r="E36" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="F36" t="n">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="G36" t="n">
-        <v>327</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.73</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="J36" t="n">
-        <v>68.13</v>
+        <v>0.36</v>
       </c>
       <c r="K36" t="n">
-        <v>72.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="L36" t="n">
-        <v>62.94</v>
+        <v>81.88</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>74.38</v>
       </c>
       <c r="N36" t="n">
-        <v>6834</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6628</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>6428</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
         <v>3</v>
       </c>
       <c r="S36" t="n">
-        <v>60</v>
+        <v>2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="C37" t="n">
-        <v>19.06</v>
+        <v>18.1</v>
       </c>
       <c r="D37" t="n">
-        <v>17.92</v>
+        <v>17.67</v>
       </c>
       <c r="E37" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="F37" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="G37" t="n">
-        <v>187</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.51</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="J37" t="n">
-        <v>75.56999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="K37" t="n">
-        <v>79.63</v>
+        <v>80.95</v>
       </c>
       <c r="L37" t="n">
-        <v>70.59999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>77.86</v>
       </c>
       <c r="N37" t="n">
-        <v>6657</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6505</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3</v>
+        <v>6434</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
         <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.86</v>
+        <v>18.69</v>
       </c>
       <c r="C38" t="n">
-        <v>18.57</v>
+        <v>19.09</v>
       </c>
       <c r="D38" t="n">
-        <v>17.34</v>
+        <v>18.24</v>
       </c>
       <c r="E38" t="n">
-        <v>14.3</v>
+        <v>13.4</v>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38" t="n">
-        <v>200</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
-        <v>80.04000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="K38" t="n">
-        <v>83.84999999999999</v>
+        <v>71.91</v>
       </c>
       <c r="L38" t="n">
-        <v>75.48999999999999</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>5507</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6536</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>6440</v>
       </c>
       <c r="Q38" t="n">
         <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.19</v>
+        <v>19.36</v>
       </c>
       <c r="C39" t="n">
-        <v>17.65</v>
+        <v>19.58</v>
       </c>
       <c r="D39" t="n">
-        <v>16.8</v>
+        <v>19.06</v>
       </c>
       <c r="E39" t="n">
-        <v>14.7</v>
+        <v>12.8</v>
       </c>
       <c r="F39" t="n">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="G39" t="n">
-        <v>193</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.28</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.21</v>
+        <v>0.75</v>
       </c>
       <c r="J39" t="n">
-        <v>85.59999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="K39" t="n">
-        <v>88.92</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>81.26000000000001</v>
+        <v>69.37</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>63.92</v>
       </c>
       <c r="N39" t="n">
-        <v>5914</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6534</v>
+        <v>1620</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>6465</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S39" t="n">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14 09:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15.97</v>
+        <v>19.82</v>
       </c>
       <c r="C40" t="n">
-        <v>16.92</v>
+        <v>20.22</v>
       </c>
       <c r="D40" t="n">
-        <v>15.43</v>
+        <v>19.58</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>12.9</v>
       </c>
       <c r="F40" t="n">
-        <v>14.8</v>
+        <v>12.6</v>
       </c>
       <c r="G40" t="n">
-        <v>160</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.1</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>94.48999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="K40" t="n">
-        <v>98.25</v>
+        <v>64.69</v>
       </c>
       <c r="L40" t="n">
-        <v>88.31</v>
+        <v>67.25</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>63.16</v>
       </c>
       <c r="N40" t="n">
-        <v>6686</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6528</v>
+        <v>3944</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>6511</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.32</v>
+        <v>19.77</v>
       </c>
       <c r="C41" t="n">
-        <v>15.42</v>
+        <v>20.09</v>
       </c>
       <c r="D41" t="n">
-        <v>15.15</v>
+        <v>19.54</v>
       </c>
       <c r="E41" t="n">
-        <v>15.1</v>
+        <v>13.2</v>
       </c>
       <c r="F41" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="G41" t="n">
-        <v>71</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.01</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="J41" t="n">
-        <v>98.81</v>
+        <v>0.71</v>
       </c>
       <c r="K41" t="n">
-        <v>100</v>
+        <v>66.33</v>
       </c>
       <c r="L41" t="n">
-        <v>97.27</v>
+        <v>68.87</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>61.21</v>
       </c>
       <c r="N41" t="n">
-        <v>5147</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6465</v>
+        <v>6671</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>6539</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 07:00:00</t>
+          <t>2026-10-14 15:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>14.76</v>
+        <v>19.58</v>
       </c>
       <c r="C42" t="n">
-        <v>15.04</v>
+        <v>19.95</v>
       </c>
       <c r="D42" t="n">
-        <v>14.58</v>
+        <v>19.38</v>
       </c>
       <c r="E42" t="n">
-        <v>14.7</v>
+        <v>12.8</v>
       </c>
       <c r="F42" t="n">
-        <v>14.5</v>
+        <v>12.2</v>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="J42" t="n">
-        <v>99.98</v>
+        <v>0.74</v>
       </c>
       <c r="K42" t="n">
-        <v>100</v>
+        <v>65.27</v>
       </c>
       <c r="L42" t="n">
-        <v>99.84999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>61.34</v>
       </c>
       <c r="N42" t="n">
-        <v>3891</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6451</v>
+        <v>6389</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>6534</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 06:00:00</t>
+          <t>2026-10-14 14:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14.58</v>
+        <v>19.96</v>
       </c>
       <c r="C43" t="n">
-        <v>14.65</v>
+        <v>20.7</v>
       </c>
       <c r="D43" t="n">
-        <v>14.54</v>
+        <v>19.58</v>
       </c>
       <c r="E43" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="F43" t="n">
-        <v>14.5</v>
+        <v>12.4</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="J43" t="n">
-        <v>99.98</v>
+        <v>0.77</v>
       </c>
       <c r="K43" t="n">
-        <v>99.98999999999999</v>
+        <v>62.94</v>
       </c>
       <c r="L43" t="n">
-        <v>99.98</v>
+        <v>66.14</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6420</v>
+        <v>4869</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6534</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 05:00:00</t>
+          <t>2026-10-14 13:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14.76</v>
+        <v>19.73</v>
       </c>
       <c r="C44" t="n">
-        <v>14.84</v>
+        <v>20.67</v>
       </c>
       <c r="D44" t="n">
-        <v>14.68</v>
+        <v>18.8</v>
       </c>
       <c r="E44" t="n">
-        <v>14.7</v>
+        <v>13.6</v>
       </c>
       <c r="F44" t="n">
-        <v>14.6</v>
+        <v>12.8</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="J44" t="n">
-        <v>99.98</v>
+        <v>0.6</v>
       </c>
       <c r="K44" t="n">
-        <v>99.98999999999999</v>
+        <v>68.13</v>
       </c>
       <c r="L44" t="n">
-        <v>99.97</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2</v>
+        <v>62.94</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6425</v>
+        <v>6834</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>6628</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 04:00:00</t>
+          <t>2026-10-14 12:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.32</v>
+        <v>18.44</v>
       </c>
       <c r="C45" t="n">
-        <v>15.83</v>
+        <v>19.06</v>
       </c>
       <c r="D45" t="n">
-        <v>14.69</v>
+        <v>17.92</v>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F45" t="n">
-        <v>14.6</v>
+        <v>13.5</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.02</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="J45" t="n">
-        <v>98.59</v>
+        <v>0.42</v>
       </c>
       <c r="K45" t="n">
-        <v>99.98999999999999</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>95.95999999999999</v>
+        <v>79.63</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6431</v>
+        <v>6657</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>6505</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="T45" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 03:00:00</t>
+          <t>2026-10-14 11:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.86</v>
+        <v>17.86</v>
       </c>
       <c r="C46" t="n">
-        <v>16</v>
+        <v>18.57</v>
       </c>
       <c r="D46" t="n">
-        <v>15.64</v>
+        <v>17.34</v>
       </c>
       <c r="E46" t="n">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.06</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
-        <v>96.20999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="K46" t="n">
-        <v>98.48</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>94.84999999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6431</v>
+        <v>5507</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>6536</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 02:00:00</t>
+          <t>2026-10-14 10:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.18</v>
+        <v>17.19</v>
       </c>
       <c r="C47" t="n">
-        <v>16.35</v>
+        <v>17.65</v>
       </c>
       <c r="D47" t="n">
-        <v>15.72</v>
+        <v>16.8</v>
       </c>
       <c r="E47" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.1</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.03</v>
+        <v>0.28</v>
       </c>
       <c r="J47" t="n">
-        <v>94.09</v>
+        <v>0.21</v>
       </c>
       <c r="K47" t="n">
-        <v>98.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>92.19</v>
+        <v>88.92</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6440</v>
+        <v>5914</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>6534</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:00</t>
+          <t>2026-10-14 09:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16.18</v>
+        <v>15.97</v>
       </c>
       <c r="C48" t="n">
-        <v>16.32</v>
+        <v>16.92</v>
       </c>
       <c r="D48" t="n">
-        <v>16.08</v>
+        <v>15.43</v>
       </c>
       <c r="E48" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>160</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K48" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="L48" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="M48" t="n">
+        <v>88.31</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>6686</v>
+      </c>
+      <c r="P48" t="n">
+        <v>6528</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-14 08:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="C49" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="E49" t="n">
         <v>15.1</v>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J48" t="n">
-        <v>94.79000000000001</v>
-      </c>
-      <c r="K48" t="n">
-        <v>96.01000000000001</v>
-      </c>
-      <c r="L48" t="n">
-        <v>92.84</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>6445</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
+      <c r="F49" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>71</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="L49" t="n">
+        <v>100</v>
+      </c>
+      <c r="M49" t="n">
+        <v>97.27</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>5147</v>
+      </c>
+      <c r="P49" t="n">
+        <v>6465</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
         <v>0</v>
       </c>
     </row>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,365 +533,361 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.49</v>
+        <v>19.3</v>
       </c>
       <c r="C2" t="n">
-        <v>16.79</v>
+        <v>19.63</v>
       </c>
       <c r="D2" t="n">
-        <v>16.31</v>
+        <v>19.11</v>
       </c>
       <c r="E2" t="n">
-        <v>14.6</v>
+        <v>13.1</v>
       </c>
       <c r="F2" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="J2" t="n">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="K2" t="n">
-        <v>89.09</v>
+        <v>67.81</v>
       </c>
       <c r="L2" t="n">
-        <v>91.65000000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>87.73</v>
+        <v>66.75</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>5349</v>
+        <v>6595</v>
       </c>
       <c r="P2" t="n">
-        <v>6445</v>
+        <v>6425</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.27</v>
+        <v>18.92</v>
       </c>
       <c r="C3" t="n">
-        <v>16.31</v>
+        <v>19.22</v>
       </c>
       <c r="D3" t="n">
-        <v>16.24</v>
+        <v>18.64</v>
       </c>
       <c r="E3" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="F3" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="J3" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="K3" t="n">
-        <v>90.12</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>91.63</v>
+        <v>73.28</v>
       </c>
       <c r="M3" t="n">
-        <v>88.84</v>
+        <v>69.45</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="P3" t="n">
-        <v>6422</v>
+        <v>6508</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.37</v>
+        <v>18.78</v>
       </c>
       <c r="C4" t="n">
-        <v>16.42</v>
+        <v>18.89</v>
       </c>
       <c r="D4" t="n">
-        <v>16.3</v>
+        <v>18.67</v>
       </c>
       <c r="E4" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="F4" t="n">
-        <v>14.4</v>
+        <v>12.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="J4" t="n">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="K4" t="n">
-        <v>88.97</v>
+        <v>70.87</v>
       </c>
       <c r="L4" t="n">
-        <v>90.09</v>
+        <v>73.17</v>
       </c>
       <c r="M4" t="n">
-        <v>88.26000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5929</v>
       </c>
       <c r="P4" t="n">
-        <v>6414</v>
+        <v>6494</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.35</v>
+        <v>18.59</v>
       </c>
       <c r="C5" t="n">
-        <v>16.36</v>
+        <v>19.26</v>
       </c>
       <c r="D5" t="n">
-        <v>16.35</v>
+        <v>18.18</v>
       </c>
       <c r="E5" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="F5" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2592</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="K5" t="n">
-        <v>84.98</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>85.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M5" t="n">
-        <v>84.31</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="P5" t="n">
-        <v>6425</v>
+        <v>6494</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.33</v>
+        <v>17.89</v>
       </c>
       <c r="C6" t="n">
-        <v>16.56</v>
+        <v>18.29</v>
       </c>
       <c r="D6" t="n">
-        <v>15.86</v>
+        <v>17.02</v>
       </c>
       <c r="E6" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2522</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="K6" t="n">
-        <v>89.8</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>99.73</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>85.27</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P6" t="n">
-        <v>6422</v>
+        <v>6488</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.27</v>
+        <v>16.49</v>
       </c>
       <c r="C7" t="n">
-        <v>16.37</v>
+        <v>16.79</v>
       </c>
       <c r="D7" t="n">
-        <v>16.2</v>
+        <v>16.31</v>
       </c>
       <c r="E7" t="n">
         <v>14.6</v>
       </c>
       <c r="F7" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
         <v>0.15</v>
       </c>
       <c r="K7" t="n">
-        <v>90.44</v>
+        <v>89.09</v>
       </c>
       <c r="L7" t="n">
-        <v>91.61</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>89.09999999999999</v>
+        <v>87.73</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P7" t="n">
-        <v>6417</v>
+        <v>6445</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -909,42 +905,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="C8" t="n">
-        <v>16.49</v>
+        <v>16.31</v>
       </c>
       <c r="D8" t="n">
-        <v>16.14</v>
+        <v>16.24</v>
       </c>
       <c r="E8" t="n">
         <v>14.6</v>
       </c>
       <c r="F8" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="J8" t="n">
         <v>0.15</v>
       </c>
       <c r="K8" t="n">
-        <v>90.33</v>
+        <v>90.12</v>
       </c>
       <c r="L8" t="n">
-        <v>91.40000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="M8" t="n">
-        <v>89.20999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -953,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -971,42 +967,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.61</v>
+        <v>16.37</v>
       </c>
       <c r="C9" t="n">
-        <v>16.82</v>
+        <v>16.42</v>
       </c>
       <c r="D9" t="n">
-        <v>16.45</v>
+        <v>16.3</v>
       </c>
       <c r="E9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F9" t="n">
         <v>14.4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14.3</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="K9" t="n">
-        <v>87.3</v>
+        <v>88.97</v>
       </c>
       <c r="L9" t="n">
-        <v>89.45</v>
+        <v>90.09</v>
       </c>
       <c r="M9" t="n">
-        <v>86.06</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1015,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6434</v>
+        <v>6414</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1033,42 +1029,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.92</v>
+        <v>16.35</v>
       </c>
       <c r="C10" t="n">
-        <v>17.22</v>
+        <v>16.36</v>
       </c>
       <c r="D10" t="n">
-        <v>16.72</v>
+        <v>16.35</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="F10" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>2592</v>
+      </c>
       <c r="I10" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="J10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="K10" t="n">
-        <v>83.48999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="L10" t="n">
-        <v>85.67</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>80.43000000000001</v>
+        <v>84.31</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1077,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q10" t="n">
         <v>2</v>
@@ -1086,7 +1084,7 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1095,42 +1093,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.37</v>
+        <v>16.33</v>
       </c>
       <c r="C11" t="n">
-        <v>17.64</v>
+        <v>16.56</v>
       </c>
       <c r="D11" t="n">
-        <v>17.15</v>
+        <v>15.86</v>
       </c>
       <c r="E11" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F11" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>2522</v>
+      </c>
       <c r="I11" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
       </c>
       <c r="J11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>81.5</v>
+        <v>89.8</v>
       </c>
       <c r="L11" t="n">
-        <v>83.2</v>
+        <v>99.73</v>
       </c>
       <c r="M11" t="n">
-        <v>79.69</v>
+        <v>85.27</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1139,16 +1139,16 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>6471</v>
+        <v>6422</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1157,42 +1157,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.37</v>
+        <v>16.27</v>
       </c>
       <c r="C12" t="n">
-        <v>17.71</v>
+        <v>16.37</v>
       </c>
       <c r="D12" t="n">
-        <v>17.16</v>
+        <v>16.2</v>
       </c>
       <c r="E12" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="J12" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="K12" t="n">
-        <v>83.11</v>
+        <v>90.44</v>
       </c>
       <c r="L12" t="n">
-        <v>85.31</v>
+        <v>91.61</v>
       </c>
       <c r="M12" t="n">
-        <v>78.94</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1201,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6474</v>
+        <v>6417</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1219,42 +1219,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.78</v>
+        <v>16.26</v>
       </c>
       <c r="C13" t="n">
-        <v>18.2</v>
+        <v>16.49</v>
       </c>
       <c r="D13" t="n">
-        <v>17.44</v>
+        <v>16.14</v>
       </c>
       <c r="E13" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F13" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.34</v>
+        <v>0.15</v>
       </c>
       <c r="K13" t="n">
-        <v>81.01000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="L13" t="n">
-        <v>82.84999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>78.13</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1263,16 +1263,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6494</v>
+        <v>6425</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1281,42 +1281,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.91</v>
+        <v>16.61</v>
       </c>
       <c r="C14" t="n">
-        <v>19.32</v>
+        <v>16.82</v>
       </c>
       <c r="D14" t="n">
-        <v>18.33</v>
+        <v>16.45</v>
       </c>
       <c r="E14" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="F14" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.59</v>
+        <v>0.23</v>
       </c>
       <c r="J14" t="n">
-        <v>0.49</v>
+        <v>0.19</v>
       </c>
       <c r="K14" t="n">
-        <v>72.89</v>
+        <v>87.3</v>
       </c>
       <c r="L14" t="n">
-        <v>76.66</v>
+        <v>89.45</v>
       </c>
       <c r="M14" t="n">
-        <v>67.31</v>
+        <v>86.06</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1325,16 +1325,16 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6496</v>
+        <v>6434</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1343,60 +1343,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.65</v>
+        <v>16.92</v>
       </c>
       <c r="C15" t="n">
-        <v>19.86</v>
+        <v>17.22</v>
       </c>
       <c r="D15" t="n">
-        <v>19.37</v>
+        <v>16.72</v>
       </c>
       <c r="E15" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" t="n">
         <v>13.8</v>
       </c>
-      <c r="F15" t="n">
-        <v>13.5</v>
-      </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
       <c r="J15" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
       <c r="K15" t="n">
-        <v>69.28</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>71.03</v>
+        <v>85.67</v>
       </c>
       <c r="M15" t="n">
-        <v>67.26000000000001</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6511</v>
+        <v>6465</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1405,60 +1405,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19.34</v>
+        <v>17.37</v>
       </c>
       <c r="C16" t="n">
-        <v>19.5</v>
+        <v>17.64</v>
       </c>
       <c r="D16" t="n">
-        <v>19.25</v>
+        <v>17.15</v>
       </c>
       <c r="E16" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="F16" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="G16" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="J16" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="K16" t="n">
-        <v>69.37</v>
+        <v>81.5</v>
       </c>
       <c r="L16" t="n">
-        <v>70.14</v>
+        <v>83.2</v>
       </c>
       <c r="M16" t="n">
-        <v>68.55</v>
+        <v>79.69</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6536</v>
+        <v>6471</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1467,432 +1467,432 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.29</v>
+        <v>17.37</v>
       </c>
       <c r="C17" t="n">
-        <v>19.86</v>
+        <v>17.71</v>
       </c>
       <c r="D17" t="n">
-        <v>19.1</v>
+        <v>17.16</v>
       </c>
       <c r="E17" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="F17" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="J17" t="n">
-        <v>0.66</v>
+        <v>0.28</v>
       </c>
       <c r="K17" t="n">
-        <v>68.94</v>
+        <v>83.11</v>
       </c>
       <c r="L17" t="n">
-        <v>69.94</v>
+        <v>85.31</v>
       </c>
       <c r="M17" t="n">
-        <v>66.66</v>
+        <v>78.94</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4462</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6539</v>
+        <v>6474</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.82</v>
+        <v>17.78</v>
       </c>
       <c r="C18" t="n">
-        <v>21.19</v>
+        <v>18.2</v>
       </c>
       <c r="D18" t="n">
-        <v>19.8</v>
+        <v>17.44</v>
       </c>
       <c r="E18" t="n">
-        <v>12.3</v>
+        <v>14.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.7</v>
+        <v>14.3</v>
       </c>
       <c r="G18" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>1.02</v>
+        <v>0.38</v>
       </c>
       <c r="J18" t="n">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
       <c r="K18" t="n">
-        <v>58.55</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>67.09</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>55.27</v>
+        <v>78.13</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6579</v>
+        <v>6494</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21.17</v>
+        <v>18.91</v>
       </c>
       <c r="C19" t="n">
-        <v>21.41</v>
+        <v>19.32</v>
       </c>
       <c r="D19" t="n">
-        <v>20.87</v>
+        <v>18.33</v>
       </c>
       <c r="E19" t="n">
-        <v>12.3</v>
+        <v>13.9</v>
       </c>
       <c r="F19" t="n">
-        <v>11.8</v>
+        <v>13.1</v>
       </c>
       <c r="G19" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>1.06</v>
+        <v>0.59</v>
       </c>
       <c r="J19" t="n">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="K19" t="n">
-        <v>57.42</v>
+        <v>72.89</v>
       </c>
       <c r="L19" t="n">
-        <v>60.15</v>
+        <v>76.66</v>
       </c>
       <c r="M19" t="n">
-        <v>55.34</v>
+        <v>67.31</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6777</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6613</v>
+        <v>6496</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.2</v>
+        <v>19.65</v>
       </c>
       <c r="C20" t="n">
-        <v>21.55</v>
+        <v>19.86</v>
       </c>
       <c r="D20" t="n">
-        <v>20.85</v>
+        <v>19.37</v>
       </c>
       <c r="E20" t="n">
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
       <c r="F20" t="n">
-        <v>12.1</v>
+        <v>13.5</v>
       </c>
       <c r="G20" t="n">
-        <v>629</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>1.04</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="K20" t="n">
-        <v>58.56</v>
+        <v>69.28</v>
       </c>
       <c r="L20" t="n">
-        <v>61.5</v>
+        <v>71.03</v>
       </c>
       <c r="M20" t="n">
-        <v>56.2</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6849</v>
+        <v>2267</v>
       </c>
       <c r="P20" t="n">
-        <v>6647</v>
+        <v>6511</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.75</v>
+        <v>19.34</v>
       </c>
       <c r="C21" t="n">
-        <v>21.44</v>
+        <v>19.5</v>
       </c>
       <c r="D21" t="n">
-        <v>20.1</v>
+        <v>19.25</v>
       </c>
       <c r="E21" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="F21" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
       <c r="G21" t="n">
-        <v>612</v>
+        <v>67</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="K21" t="n">
-        <v>59.8</v>
+        <v>69.37</v>
       </c>
       <c r="L21" t="n">
-        <v>61.83</v>
+        <v>70.14</v>
       </c>
       <c r="M21" t="n">
-        <v>58.57</v>
+        <v>68.55</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6901</v>
+        <v>4721</v>
       </c>
       <c r="P21" t="n">
-        <v>6676</v>
+        <v>6536</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20.11</v>
+        <v>19.29</v>
       </c>
       <c r="C22" t="n">
-        <v>21.09</v>
+        <v>19.86</v>
       </c>
       <c r="D22" t="n">
-        <v>19.18</v>
+        <v>19.1</v>
       </c>
       <c r="E22" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="F22" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="G22" t="n">
-        <v>471</v>
+        <v>68</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="K22" t="n">
-        <v>63.63</v>
+        <v>68.94</v>
       </c>
       <c r="L22" t="n">
-        <v>67.22</v>
+        <v>69.94</v>
       </c>
       <c r="M22" t="n">
-        <v>59.39</v>
+        <v>66.66</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6810</v>
+        <v>4462</v>
       </c>
       <c r="P22" t="n">
-        <v>6613</v>
+        <v>6539</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
         <v>5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.28</v>
+        <v>20.82</v>
       </c>
       <c r="C23" t="n">
-        <v>19.69</v>
+        <v>21.19</v>
       </c>
       <c r="D23" t="n">
-        <v>18.97</v>
+        <v>19.8</v>
       </c>
       <c r="E23" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F23" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
       <c r="G23" t="n">
-        <v>300</v>
+        <v>215</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
       <c r="J23" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="K23" t="n">
-        <v>66.97</v>
+        <v>58.55</v>
       </c>
       <c r="L23" t="n">
-        <v>70.23999999999999</v>
+        <v>67.09</v>
       </c>
       <c r="M23" t="n">
-        <v>65.22</v>
+        <v>55.27</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6681</v>
+        <v>6250</v>
       </c>
       <c r="P23" t="n">
-        <v>6565</v>
+        <v>6579</v>
       </c>
       <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
       </c>
       <c r="T23" t="n">
         <v>60</v>
@@ -1901,60 +1901,60 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18.64</v>
+        <v>21.17</v>
       </c>
       <c r="C24" t="n">
-        <v>20.12</v>
+        <v>21.41</v>
       </c>
       <c r="D24" t="n">
-        <v>17.71</v>
+        <v>20.87</v>
       </c>
       <c r="E24" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="F24" t="n">
-        <v>12.9</v>
+        <v>11.8</v>
       </c>
       <c r="G24" t="n">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.61</v>
+        <v>1.06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="K24" t="n">
-        <v>71.42</v>
+        <v>57.42</v>
       </c>
       <c r="L24" t="n">
-        <v>76.48</v>
+        <v>60.15</v>
       </c>
       <c r="M24" t="n">
-        <v>66.62</v>
+        <v>55.34</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6739</v>
+        <v>6777</v>
       </c>
       <c r="P24" t="n">
-        <v>6565</v>
+        <v>6613</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
         <v>60</v>
@@ -1963,423 +1963,423 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.37</v>
+        <v>21.2</v>
       </c>
       <c r="C25" t="n">
-        <v>18.2</v>
+        <v>21.55</v>
       </c>
       <c r="D25" t="n">
-        <v>16.67</v>
+        <v>20.85</v>
       </c>
       <c r="E25" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="F25" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="G25" t="n">
-        <v>167</v>
+        <v>629</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>1.04</v>
       </c>
       <c r="J25" t="n">
-        <v>0.26</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>79.89</v>
+        <v>58.56</v>
       </c>
       <c r="L25" t="n">
-        <v>86.01000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="M25" t="n">
-        <v>75.15000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6499</v>
+        <v>6849</v>
       </c>
       <c r="P25" t="n">
-        <v>6494</v>
+        <v>6647</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15.89</v>
+        <v>20.75</v>
       </c>
       <c r="C26" t="n">
-        <v>16.51</v>
+        <v>21.44</v>
       </c>
       <c r="D26" t="n">
-        <v>15.53</v>
+        <v>20.1</v>
       </c>
       <c r="E26" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="F26" t="n">
-        <v>14.3</v>
+        <v>12.1</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>612</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.14</v>
+        <v>0.98</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>91.95</v>
+        <v>59.8</v>
       </c>
       <c r="L26" t="n">
-        <v>93.86</v>
+        <v>61.83</v>
       </c>
       <c r="M26" t="n">
-        <v>87.84999999999999</v>
+        <v>58.57</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4793</v>
+        <v>6901</v>
       </c>
       <c r="P26" t="n">
-        <v>6442</v>
+        <v>6676</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.63</v>
+        <v>20.11</v>
       </c>
       <c r="C27" t="n">
-        <v>15.72</v>
+        <v>21.09</v>
       </c>
       <c r="D27" t="n">
-        <v>15.55</v>
+        <v>19.18</v>
       </c>
       <c r="E27" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="F27" t="n">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.13</v>
+        <v>0.85</v>
       </c>
       <c r="J27" t="n">
-        <v>0.11</v>
+        <v>0.72</v>
       </c>
       <c r="K27" t="n">
-        <v>92.23</v>
+        <v>63.63</v>
       </c>
       <c r="L27" t="n">
-        <v>93.61</v>
+        <v>67.22</v>
       </c>
       <c r="M27" t="n">
-        <v>90.98</v>
+        <v>59.39</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>6810</v>
       </c>
       <c r="P27" t="n">
-        <v>6417</v>
+        <v>6613</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15.65</v>
+        <v>19.28</v>
       </c>
       <c r="C28" t="n">
-        <v>15.76</v>
+        <v>19.69</v>
       </c>
       <c r="D28" t="n">
-        <v>15.53</v>
+        <v>18.97</v>
       </c>
       <c r="E28" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="F28" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.11</v>
+        <v>0.73</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="K28" t="n">
-        <v>93.44</v>
+        <v>66.97</v>
       </c>
       <c r="L28" t="n">
-        <v>93.83</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>92.88</v>
+        <v>65.22</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>6681</v>
       </c>
       <c r="P28" t="n">
-        <v>6405</v>
+        <v>6565</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15.63</v>
+        <v>18.64</v>
       </c>
       <c r="C29" t="n">
-        <v>15.74</v>
+        <v>20.12</v>
       </c>
       <c r="D29" t="n">
-        <v>15.57</v>
+        <v>17.71</v>
       </c>
       <c r="E29" t="n">
-        <v>14.7</v>
+        <v>13.3</v>
       </c>
       <c r="F29" t="n">
-        <v>14.6</v>
+        <v>12.9</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.08</v>
+        <v>0.61</v>
       </c>
       <c r="J29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="K29" t="n">
-        <v>94.87</v>
+        <v>71.42</v>
       </c>
       <c r="L29" t="n">
-        <v>95.69</v>
+        <v>76.48</v>
       </c>
       <c r="M29" t="n">
-        <v>93.40000000000001</v>
+        <v>66.62</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>6739</v>
       </c>
       <c r="P29" t="n">
-        <v>6414</v>
+        <v>6565</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15.74</v>
+        <v>17.37</v>
       </c>
       <c r="C30" t="n">
-        <v>15.95</v>
+        <v>18.2</v>
       </c>
       <c r="D30" t="n">
-        <v>15.62</v>
+        <v>16.67</v>
       </c>
       <c r="E30" t="n">
-        <v>14.9</v>
+        <v>13.8</v>
       </c>
       <c r="F30" t="n">
-        <v>14.9</v>
+        <v>13.3</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="K30" t="n">
-        <v>95.13</v>
+        <v>79.89</v>
       </c>
       <c r="L30" t="n">
-        <v>96.19</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>94.28</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>6499</v>
       </c>
       <c r="P30" t="n">
-        <v>6422</v>
+        <v>6494</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.02</v>
+        <v>15.89</v>
       </c>
       <c r="C31" t="n">
-        <v>16.13</v>
+        <v>16.51</v>
       </c>
       <c r="D31" t="n">
-        <v>15.96</v>
+        <v>15.53</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="F31" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J31" t="n">
         <v>0.1</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K31" t="n">
-        <v>94.3</v>
+        <v>91.95</v>
       </c>
       <c r="L31" t="n">
-        <v>94.76000000000001</v>
+        <v>93.86</v>
       </c>
       <c r="M31" t="n">
-        <v>93.61</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4793</v>
       </c>
       <c r="P31" t="n">
-        <v>6414</v>
+        <v>6442</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -2397,42 +2397,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.24</v>
+        <v>15.63</v>
       </c>
       <c r="C32" t="n">
-        <v>16.32</v>
+        <v>15.72</v>
       </c>
       <c r="D32" t="n">
-        <v>16.16</v>
+        <v>15.55</v>
       </c>
       <c r="E32" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="F32" t="n">
-        <v>15.1</v>
+        <v>14.2</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J32" t="n">
         <v>0.11</v>
       </c>
-      <c r="J32" t="n">
-        <v>0.1</v>
-      </c>
       <c r="K32" t="n">
-        <v>93.55</v>
+        <v>92.23</v>
       </c>
       <c r="L32" t="n">
-        <v>94.40000000000001</v>
+        <v>93.61</v>
       </c>
       <c r="M32" t="n">
-        <v>92.81</v>
+        <v>90.98</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2459,42 +2459,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.57</v>
+        <v>15.65</v>
       </c>
       <c r="C33" t="n">
-        <v>16.97</v>
+        <v>15.76</v>
       </c>
       <c r="D33" t="n">
-        <v>16.32</v>
+        <v>15.53</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="F33" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="J33" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K33" t="n">
-        <v>90.97</v>
+        <v>93.44</v>
       </c>
       <c r="L33" t="n">
-        <v>93.34999999999999</v>
+        <v>93.83</v>
       </c>
       <c r="M33" t="n">
-        <v>87.03</v>
+        <v>92.88</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6422</v>
+        <v>6405</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
@@ -2521,42 +2521,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.39</v>
+        <v>15.63</v>
       </c>
       <c r="C34" t="n">
-        <v>17.59</v>
+        <v>15.74</v>
       </c>
       <c r="D34" t="n">
-        <v>17.17</v>
+        <v>15.57</v>
       </c>
       <c r="E34" t="n">
-        <v>13.8</v>
+        <v>14.7</v>
       </c>
       <c r="F34" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="J34" t="n">
-        <v>0.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>79.91</v>
+        <v>94.87</v>
       </c>
       <c r="L34" t="n">
-        <v>84</v>
+        <v>95.69</v>
       </c>
       <c r="M34" t="n">
-        <v>77.81999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2565,16 +2565,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -2583,42 +2583,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.82</v>
+        <v>15.74</v>
       </c>
       <c r="C35" t="n">
-        <v>17.99</v>
+        <v>15.95</v>
       </c>
       <c r="D35" t="n">
-        <v>17.64</v>
+        <v>15.62</v>
       </c>
       <c r="E35" t="n">
-        <v>13.7</v>
+        <v>14.9</v>
       </c>
       <c r="F35" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="J35" t="n">
-        <v>0.42</v>
+        <v>0.06</v>
       </c>
       <c r="K35" t="n">
-        <v>77.5</v>
+        <v>95.13</v>
       </c>
       <c r="L35" t="n">
-        <v>79.29000000000001</v>
+        <v>96.19</v>
       </c>
       <c r="M35" t="n">
-        <v>76.37</v>
+        <v>94.28</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2627,16 +2627,16 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -2645,42 +2645,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18.13</v>
+        <v>16.02</v>
       </c>
       <c r="C36" t="n">
-        <v>18.3</v>
+        <v>16.13</v>
       </c>
       <c r="D36" t="n">
-        <v>17.82</v>
+        <v>15.96</v>
       </c>
       <c r="E36" t="n">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.48</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.36</v>
+        <v>0.09</v>
       </c>
       <c r="K36" t="n">
-        <v>76.5</v>
+        <v>94.3</v>
       </c>
       <c r="L36" t="n">
-        <v>81.88</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>74.38</v>
+        <v>93.61</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2689,16 +2689,16 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>6428</v>
+        <v>6414</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -2707,42 +2707,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.85</v>
+        <v>16.24</v>
       </c>
       <c r="C37" t="n">
-        <v>18.1</v>
+        <v>16.32</v>
       </c>
       <c r="D37" t="n">
-        <v>17.67</v>
+        <v>16.16</v>
       </c>
       <c r="E37" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="F37" t="n">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.38</v>
+        <v>0.11</v>
       </c>
       <c r="J37" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="K37" t="n">
-        <v>80.95</v>
+        <v>93.55</v>
       </c>
       <c r="L37" t="n">
-        <v>82.98</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>77.86</v>
+        <v>92.81</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2751,16 +2751,16 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>6434</v>
+        <v>6417</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -2769,42 +2769,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.69</v>
+        <v>16.57</v>
       </c>
       <c r="C38" t="n">
-        <v>19.09</v>
+        <v>16.97</v>
       </c>
       <c r="D38" t="n">
-        <v>18.24</v>
+        <v>16.32</v>
       </c>
       <c r="E38" t="n">
-        <v>13.4</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>13</v>
+        <v>14.7</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="K38" t="n">
-        <v>71.91</v>
+        <v>90.97</v>
       </c>
       <c r="L38" t="n">
-        <v>75.81999999999999</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>68.15000000000001</v>
+        <v>87.03</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -2813,16 +2813,16 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6440</v>
+        <v>6422</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -2831,60 +2831,60 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.36</v>
+        <v>17.39</v>
       </c>
       <c r="C39" t="n">
-        <v>19.58</v>
+        <v>17.59</v>
       </c>
       <c r="D39" t="n">
-        <v>19.06</v>
+        <v>17.17</v>
       </c>
       <c r="E39" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="F39" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="G39" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
-        <v>0.67</v>
+        <v>0.31</v>
       </c>
       <c r="K39" t="n">
-        <v>66.34999999999999</v>
+        <v>79.91</v>
       </c>
       <c r="L39" t="n">
-        <v>69.37</v>
+        <v>84</v>
       </c>
       <c r="M39" t="n">
-        <v>63.92</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6465</v>
+        <v>6417</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -2893,299 +2893,299 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.82</v>
+        <v>17.82</v>
       </c>
       <c r="C40" t="n">
-        <v>20.22</v>
+        <v>17.99</v>
       </c>
       <c r="D40" t="n">
-        <v>19.58</v>
+        <v>17.64</v>
       </c>
       <c r="E40" t="n">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="F40" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="G40" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="J40" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="K40" t="n">
-        <v>64.69</v>
+        <v>77.5</v>
       </c>
       <c r="L40" t="n">
-        <v>67.25</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>63.16</v>
+        <v>76.37</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3944</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6511</v>
+        <v>6425</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T40" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.77</v>
+        <v>18.13</v>
       </c>
       <c r="C41" t="n">
-        <v>20.09</v>
+        <v>18.3</v>
       </c>
       <c r="D41" t="n">
-        <v>19.54</v>
+        <v>17.82</v>
       </c>
       <c r="E41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="F41" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="G41" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.77</v>
+        <v>0.48</v>
       </c>
       <c r="J41" t="n">
-        <v>0.71</v>
+        <v>0.36</v>
       </c>
       <c r="K41" t="n">
-        <v>66.33</v>
+        <v>76.5</v>
       </c>
       <c r="L41" t="n">
-        <v>68.87</v>
+        <v>81.88</v>
       </c>
       <c r="M41" t="n">
-        <v>61.21</v>
+        <v>74.38</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6671</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6539</v>
+        <v>6428</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.58</v>
+        <v>17.85</v>
       </c>
       <c r="C42" t="n">
-        <v>19.95</v>
+        <v>18.1</v>
       </c>
       <c r="D42" t="n">
-        <v>19.38</v>
+        <v>17.67</v>
       </c>
       <c r="E42" t="n">
-        <v>12.8</v>
+        <v>14.4</v>
       </c>
       <c r="F42" t="n">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
       <c r="G42" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="J42" t="n">
-        <v>0.74</v>
+        <v>0.34</v>
       </c>
       <c r="K42" t="n">
-        <v>65.27</v>
+        <v>80.95</v>
       </c>
       <c r="L42" t="n">
-        <v>67.09999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="M42" t="n">
-        <v>61.34</v>
+        <v>77.86</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6389</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6534</v>
+        <v>6434</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.96</v>
+        <v>18.69</v>
       </c>
       <c r="C43" t="n">
-        <v>20.7</v>
+        <v>19.09</v>
       </c>
       <c r="D43" t="n">
-        <v>19.58</v>
+        <v>18.24</v>
       </c>
       <c r="E43" t="n">
-        <v>12.6</v>
+        <v>13.4</v>
       </c>
       <c r="F43" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="K43" t="n">
-        <v>62.94</v>
+        <v>71.91</v>
       </c>
       <c r="L43" t="n">
-        <v>66.14</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>60.5</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4869</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6534</v>
+        <v>6440</v>
       </c>
       <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
         <v>4</v>
       </c>
-      <c r="R43" t="n">
-        <v>5</v>
-      </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 13:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.73</v>
+        <v>19.36</v>
       </c>
       <c r="C44" t="n">
-        <v>20.67</v>
+        <v>19.58</v>
       </c>
       <c r="D44" t="n">
-        <v>18.8</v>
+        <v>19.06</v>
       </c>
       <c r="E44" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="F44" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="G44" t="n">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="K44" t="n">
-        <v>68.13</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>72.90000000000001</v>
+        <v>69.37</v>
       </c>
       <c r="M44" t="n">
-        <v>62.94</v>
+        <v>63.92</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6834</v>
+        <v>1620</v>
       </c>
       <c r="P44" t="n">
-        <v>6628</v>
+        <v>6465</v>
       </c>
       <c r="Q44" t="n">
         <v>4</v>
@@ -3194,131 +3194,131 @@
         <v>4</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18.44</v>
+        <v>19.82</v>
       </c>
       <c r="C45" t="n">
-        <v>19.06</v>
+        <v>20.22</v>
       </c>
       <c r="D45" t="n">
-        <v>17.92</v>
+        <v>19.58</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>12.9</v>
       </c>
       <c r="F45" t="n">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="G45" t="n">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.51</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="K45" t="n">
-        <v>75.56999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="L45" t="n">
-        <v>79.63</v>
+        <v>67.25</v>
       </c>
       <c r="M45" t="n">
-        <v>70.59999999999999</v>
+        <v>63.16</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6657</v>
+        <v>3944</v>
       </c>
       <c r="P45" t="n">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.86</v>
+        <v>19.77</v>
       </c>
       <c r="C46" t="n">
-        <v>18.57</v>
+        <v>20.09</v>
       </c>
       <c r="D46" t="n">
-        <v>17.34</v>
+        <v>19.54</v>
       </c>
       <c r="E46" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="F46" t="n">
-        <v>14</v>
+        <v>12.2</v>
       </c>
       <c r="G46" t="n">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="J46" t="n">
-        <v>0.32</v>
+        <v>0.71</v>
       </c>
       <c r="K46" t="n">
-        <v>80.04000000000001</v>
+        <v>66.33</v>
       </c>
       <c r="L46" t="n">
-        <v>83.84999999999999</v>
+        <v>68.87</v>
       </c>
       <c r="M46" t="n">
-        <v>75.48999999999999</v>
+        <v>61.21</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>5507</v>
+        <v>6671</v>
       </c>
       <c r="P46" t="n">
-        <v>6536</v>
+        <v>6539</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
         <v>50</v>
@@ -3327,187 +3327,187 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00:00</t>
+          <t>2026-10-14 15:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.19</v>
+        <v>19.58</v>
       </c>
       <c r="C47" t="n">
-        <v>17.65</v>
+        <v>19.95</v>
       </c>
       <c r="D47" t="n">
-        <v>16.8</v>
+        <v>19.38</v>
       </c>
       <c r="E47" t="n">
-        <v>14.7</v>
+        <v>12.8</v>
       </c>
       <c r="F47" t="n">
-        <v>14.2</v>
+        <v>12.2</v>
       </c>
       <c r="G47" t="n">
-        <v>193</v>
+        <v>138</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.28</v>
+        <v>0.79</v>
       </c>
       <c r="J47" t="n">
-        <v>0.21</v>
+        <v>0.74</v>
       </c>
       <c r="K47" t="n">
-        <v>85.59999999999999</v>
+        <v>65.27</v>
       </c>
       <c r="L47" t="n">
-        <v>88.92</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>81.26000000000001</v>
+        <v>61.34</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>5914</v>
+        <v>6389</v>
       </c>
       <c r="P47" t="n">
         <v>6534</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 09:00:00</t>
+          <t>2026-10-14 14:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15.97</v>
+        <v>19.96</v>
       </c>
       <c r="C48" t="n">
-        <v>16.92</v>
+        <v>20.7</v>
       </c>
       <c r="D48" t="n">
-        <v>15.43</v>
+        <v>19.58</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>12.6</v>
       </c>
       <c r="F48" t="n">
-        <v>14.8</v>
+        <v>12.4</v>
       </c>
       <c r="G48" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>0.86</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03</v>
+        <v>0.77</v>
       </c>
       <c r="K48" t="n">
-        <v>94.48999999999999</v>
+        <v>62.94</v>
       </c>
       <c r="L48" t="n">
-        <v>98.25</v>
+        <v>66.14</v>
       </c>
       <c r="M48" t="n">
-        <v>88.31</v>
+        <v>60.5</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6686</v>
+        <v>4869</v>
       </c>
       <c r="P48" t="n">
-        <v>6528</v>
+        <v>6534</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00:00</t>
+          <t>2026-10-14 13:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15.32</v>
+        <v>19.73</v>
       </c>
       <c r="C49" t="n">
-        <v>15.42</v>
+        <v>20.67</v>
       </c>
       <c r="D49" t="n">
-        <v>15.15</v>
+        <v>18.8</v>
       </c>
       <c r="E49" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="F49" t="n">
-        <v>14.9</v>
+        <v>12.8</v>
       </c>
       <c r="G49" t="n">
-        <v>71</v>
+        <v>327</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.01</v>
+        <v>0.73</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K49" t="n">
-        <v>98.81</v>
+        <v>68.13</v>
       </c>
       <c r="L49" t="n">
-        <v>100</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>97.27</v>
+        <v>62.94</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>5147</v>
+        <v>6834</v>
       </c>
       <c r="P49" t="n">
-        <v>6465</v>
+        <v>6628</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,60 +533,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.3</v>
+        <v>22.18</v>
       </c>
       <c r="C2" t="n">
-        <v>19.63</v>
+        <v>22.92</v>
       </c>
       <c r="D2" t="n">
-        <v>19.11</v>
+        <v>21.96</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="F2" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="G2" t="n">
-        <v>184</v>
+        <v>567</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.72</v>
+        <v>1.22</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7</v>
+        <v>1.16</v>
       </c>
       <c r="K2" t="n">
-        <v>67.81</v>
+        <v>54.01</v>
       </c>
       <c r="L2" t="n">
-        <v>68.68000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="M2" t="n">
-        <v>66.75</v>
+        <v>51.48</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6595</v>
+        <v>6786</v>
       </c>
       <c r="P2" t="n">
-        <v>6425</v>
+        <v>6593</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
         <v>30</v>
@@ -595,122 +595,122 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.92</v>
+        <v>21.45</v>
       </c>
       <c r="C3" t="n">
-        <v>19.22</v>
+        <v>22.62</v>
       </c>
       <c r="D3" t="n">
-        <v>18.64</v>
+        <v>20.83</v>
       </c>
       <c r="E3" t="n">
-        <v>13.6</v>
+        <v>12.3</v>
       </c>
       <c r="F3" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="G3" t="n">
-        <v>143</v>
+        <v>640</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="K3" t="n">
-        <v>71.48999999999999</v>
+        <v>56.35</v>
       </c>
       <c r="L3" t="n">
-        <v>73.28</v>
+        <v>62.61</v>
       </c>
       <c r="M3" t="n">
-        <v>69.45</v>
+        <v>51.88</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6254</v>
+        <v>6810</v>
       </c>
       <c r="P3" t="n">
-        <v>6508</v>
+        <v>6610</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.78</v>
+        <v>19.67</v>
       </c>
       <c r="C4" t="n">
-        <v>18.89</v>
+        <v>20.85</v>
       </c>
       <c r="D4" t="n">
-        <v>18.67</v>
+        <v>19.11</v>
       </c>
       <c r="E4" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F4" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="G4" t="n">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="J4" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>70.87</v>
+        <v>66.39</v>
       </c>
       <c r="L4" t="n">
-        <v>73.17</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>68.48</v>
+        <v>61.4</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5929</v>
+        <v>6772</v>
       </c>
       <c r="P4" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>60</v>
@@ -719,51 +719,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.59</v>
+        <v>18.92</v>
       </c>
       <c r="C5" t="n">
-        <v>19.26</v>
+        <v>19.22</v>
       </c>
       <c r="D5" t="n">
-        <v>18.18</v>
+        <v>18.64</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="F5" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G5" t="n">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="J5" t="n">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
       <c r="K5" t="n">
-        <v>76.48999999999999</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>80.08</v>
+        <v>73.28</v>
       </c>
       <c r="M5" t="n">
-        <v>71.70999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>5478</v>
+        <v>6254</v>
       </c>
       <c r="P5" t="n">
-        <v>6494</v>
+        <v>6508</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
@@ -772,69 +772,69 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.89</v>
+        <v>18.78</v>
       </c>
       <c r="C6" t="n">
-        <v>18.29</v>
+        <v>18.89</v>
       </c>
       <c r="D6" t="n">
-        <v>17.02</v>
+        <v>18.67</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="F6" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="G6" t="n">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="J6" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="K6" t="n">
-        <v>82.51000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="L6" t="n">
-        <v>87.40000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="M6" t="n">
-        <v>79.09999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6633</v>
+        <v>5929</v>
       </c>
       <c r="P6" t="n">
-        <v>6488</v>
+        <v>6494</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
         <v>60</v>
@@ -843,175 +843,175 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.49</v>
+        <v>18.59</v>
       </c>
       <c r="C7" t="n">
-        <v>16.79</v>
+        <v>19.26</v>
       </c>
       <c r="D7" t="n">
-        <v>16.31</v>
+        <v>18.18</v>
       </c>
       <c r="E7" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F7" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="K7" t="n">
-        <v>89.09</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>91.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M7" t="n">
-        <v>87.73</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5349</v>
+        <v>5478</v>
       </c>
       <c r="P7" t="n">
-        <v>6445</v>
+        <v>6494</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.27</v>
+        <v>17.89</v>
       </c>
       <c r="C8" t="n">
-        <v>16.31</v>
+        <v>18.29</v>
       </c>
       <c r="D8" t="n">
-        <v>16.24</v>
+        <v>17.02</v>
       </c>
       <c r="E8" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F8" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="J8" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="K8" t="n">
-        <v>90.12</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>91.63</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>88.84</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P8" t="n">
-        <v>6422</v>
+        <v>6488</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.37</v>
+        <v>16.49</v>
       </c>
       <c r="C9" t="n">
-        <v>16.42</v>
+        <v>16.79</v>
       </c>
       <c r="D9" t="n">
-        <v>16.3</v>
+        <v>16.31</v>
       </c>
       <c r="E9" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F9" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="K9" t="n">
-        <v>88.97</v>
+        <v>89.09</v>
       </c>
       <c r="L9" t="n">
-        <v>90.09</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>88.26000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P9" t="n">
-        <v>6414</v>
+        <v>6445</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1029,44 +1029,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.35</v>
+        <v>16.27</v>
       </c>
       <c r="C10" t="n">
-        <v>16.36</v>
+        <v>16.31</v>
       </c>
       <c r="D10" t="n">
-        <v>16.35</v>
+        <v>16.24</v>
       </c>
       <c r="E10" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="F10" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
-        <v>2592</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="K10" t="n">
-        <v>84.98</v>
+        <v>90.12</v>
       </c>
       <c r="L10" t="n">
-        <v>85.65000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="M10" t="n">
-        <v>84.31</v>
+        <v>88.84</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1075,13 +1073,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1093,44 +1091,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.33</v>
+        <v>16.37</v>
       </c>
       <c r="C11" t="n">
-        <v>16.56</v>
+        <v>16.42</v>
       </c>
       <c r="D11" t="n">
-        <v>15.86</v>
+        <v>16.3</v>
       </c>
       <c r="E11" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
-        <v>2522</v>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K11" t="n">
-        <v>89.8</v>
+        <v>88.97</v>
       </c>
       <c r="L11" t="n">
-        <v>99.73</v>
+        <v>90.09</v>
       </c>
       <c r="M11" t="n">
-        <v>85.27</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1139,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1157,42 +1153,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.27</v>
+        <v>16.35</v>
       </c>
       <c r="C12" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="D12" t="n">
-        <v>16.2</v>
+        <v>16.35</v>
       </c>
       <c r="E12" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F12" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>2592</v>
+      </c>
       <c r="I12" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="J12" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K12" t="n">
-        <v>90.44</v>
+        <v>84.98</v>
       </c>
       <c r="L12" t="n">
-        <v>91.61</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>89.09999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1201,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1219,42 +1217,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.26</v>
+        <v>16.33</v>
       </c>
       <c r="C13" t="n">
-        <v>16.49</v>
+        <v>16.56</v>
       </c>
       <c r="D13" t="n">
-        <v>16.14</v>
+        <v>15.86</v>
       </c>
       <c r="E13" t="n">
         <v>14.6</v>
       </c>
       <c r="F13" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>2522</v>
+      </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J13" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>90.33</v>
+        <v>89.8</v>
       </c>
       <c r="L13" t="n">
-        <v>91.40000000000001</v>
+        <v>99.73</v>
       </c>
       <c r="M13" t="n">
-        <v>89.20999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1263,16 +1263,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1281,42 +1281,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.61</v>
+        <v>16.27</v>
       </c>
       <c r="C14" t="n">
-        <v>16.82</v>
+        <v>16.37</v>
       </c>
       <c r="D14" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="E14" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F14" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K14" t="n">
-        <v>87.3</v>
+        <v>90.44</v>
       </c>
       <c r="L14" t="n">
-        <v>89.45</v>
+        <v>91.61</v>
       </c>
       <c r="M14" t="n">
-        <v>86.06</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6434</v>
+        <v>6417</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1343,42 +1343,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.92</v>
+        <v>16.26</v>
       </c>
       <c r="C15" t="n">
-        <v>17.22</v>
+        <v>16.49</v>
       </c>
       <c r="D15" t="n">
-        <v>16.72</v>
+        <v>16.14</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F15" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="J15" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="K15" t="n">
-        <v>83.48999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="L15" t="n">
-        <v>85.67</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>80.43000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1387,16 +1387,16 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1405,42 +1405,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.37</v>
+        <v>16.61</v>
       </c>
       <c r="C16" t="n">
-        <v>17.64</v>
+        <v>16.82</v>
       </c>
       <c r="D16" t="n">
-        <v>17.15</v>
+        <v>16.45</v>
       </c>
       <c r="E16" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="F16" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="J16" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="K16" t="n">
-        <v>81.5</v>
+        <v>87.3</v>
       </c>
       <c r="L16" t="n">
-        <v>83.2</v>
+        <v>89.45</v>
       </c>
       <c r="M16" t="n">
-        <v>79.69</v>
+        <v>86.06</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1449,16 +1449,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6471</v>
+        <v>6434</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1467,42 +1467,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.37</v>
+        <v>16.92</v>
       </c>
       <c r="C17" t="n">
-        <v>17.71</v>
+        <v>17.22</v>
       </c>
       <c r="D17" t="n">
-        <v>17.16</v>
+        <v>16.72</v>
       </c>
       <c r="E17" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J17" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="K17" t="n">
-        <v>83.11</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>85.31</v>
+        <v>85.67</v>
       </c>
       <c r="M17" t="n">
-        <v>78.94</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6474</v>
+        <v>6465</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
@@ -1529,42 +1529,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.78</v>
+        <v>17.37</v>
       </c>
       <c r="C18" t="n">
-        <v>18.2</v>
+        <v>17.64</v>
       </c>
       <c r="D18" t="n">
-        <v>17.44</v>
+        <v>17.15</v>
       </c>
       <c r="E18" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="F18" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="J18" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="K18" t="n">
-        <v>81.01000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="L18" t="n">
-        <v>82.84999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="M18" t="n">
-        <v>78.13</v>
+        <v>79.69</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6494</v>
+        <v>6471</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
@@ -1591,42 +1591,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.91</v>
+        <v>17.37</v>
       </c>
       <c r="C19" t="n">
-        <v>19.32</v>
+        <v>17.71</v>
       </c>
       <c r="D19" t="n">
-        <v>18.33</v>
+        <v>17.16</v>
       </c>
       <c r="E19" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="F19" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="J19" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="K19" t="n">
-        <v>72.89</v>
+        <v>83.11</v>
       </c>
       <c r="L19" t="n">
-        <v>76.66</v>
+        <v>85.31</v>
       </c>
       <c r="M19" t="n">
-        <v>67.31</v>
+        <v>78.94</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1635,16 +1635,16 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6496</v>
+        <v>6474</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -1653,60 +1653,60 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.65</v>
+        <v>17.78</v>
       </c>
       <c r="C20" t="n">
-        <v>19.86</v>
+        <v>18.2</v>
       </c>
       <c r="D20" t="n">
-        <v>19.37</v>
+        <v>17.44</v>
       </c>
       <c r="E20" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="F20" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="J20" t="n">
-        <v>0.65</v>
+        <v>0.34</v>
       </c>
       <c r="K20" t="n">
-        <v>69.28</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>71.03</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>67.26000000000001</v>
+        <v>78.13</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6511</v>
+        <v>6494</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -1715,54 +1715,54 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.34</v>
+        <v>18.91</v>
       </c>
       <c r="C21" t="n">
-        <v>19.5</v>
+        <v>19.32</v>
       </c>
       <c r="D21" t="n">
-        <v>19.25</v>
+        <v>18.33</v>
       </c>
       <c r="E21" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="F21" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="G21" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="J21" t="n">
-        <v>0.67</v>
+        <v>0.49</v>
       </c>
       <c r="K21" t="n">
-        <v>69.37</v>
+        <v>72.89</v>
       </c>
       <c r="L21" t="n">
-        <v>70.14</v>
+        <v>76.66</v>
       </c>
       <c r="M21" t="n">
-        <v>68.55</v>
+        <v>67.31</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6536</v>
+        <v>6496</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>4</v>
@@ -1777,51 +1777,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.29</v>
+        <v>19.65</v>
       </c>
       <c r="C22" t="n">
         <v>19.86</v>
       </c>
       <c r="D22" t="n">
-        <v>19.1</v>
+        <v>19.37</v>
       </c>
       <c r="E22" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="F22" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="G22" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="K22" t="n">
-        <v>68.94</v>
+        <v>69.28</v>
       </c>
       <c r="L22" t="n">
-        <v>69.94</v>
+        <v>71.03</v>
       </c>
       <c r="M22" t="n">
-        <v>66.66</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4462</v>
+        <v>2267</v>
       </c>
       <c r="P22" t="n">
-        <v>6539</v>
+        <v>6511</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
@@ -1833,181 +1833,181 @@
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20.82</v>
+        <v>19.34</v>
       </c>
       <c r="C23" t="n">
-        <v>21.19</v>
+        <v>19.5</v>
       </c>
       <c r="D23" t="n">
-        <v>19.8</v>
+        <v>19.25</v>
       </c>
       <c r="E23" t="n">
-        <v>12.3</v>
+        <v>13.5</v>
       </c>
       <c r="F23" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
       <c r="G23" t="n">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="J23" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="K23" t="n">
-        <v>58.55</v>
+        <v>69.37</v>
       </c>
       <c r="L23" t="n">
-        <v>67.09</v>
+        <v>70.14</v>
       </c>
       <c r="M23" t="n">
-        <v>55.27</v>
+        <v>68.55</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6250</v>
+        <v>4721</v>
       </c>
       <c r="P23" t="n">
-        <v>6579</v>
+        <v>6536</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21.17</v>
+        <v>19.29</v>
       </c>
       <c r="C24" t="n">
-        <v>21.41</v>
+        <v>19.86</v>
       </c>
       <c r="D24" t="n">
-        <v>20.87</v>
+        <v>19.1</v>
       </c>
       <c r="E24" t="n">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="F24" t="n">
-        <v>11.8</v>
+        <v>13.3</v>
       </c>
       <c r="G24" t="n">
-        <v>419</v>
+        <v>68</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.99</v>
+        <v>0.66</v>
       </c>
       <c r="K24" t="n">
-        <v>57.42</v>
+        <v>68.94</v>
       </c>
       <c r="L24" t="n">
-        <v>60.15</v>
+        <v>69.94</v>
       </c>
       <c r="M24" t="n">
-        <v>55.34</v>
+        <v>66.66</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6777</v>
+        <v>4462</v>
       </c>
       <c r="P24" t="n">
-        <v>6613</v>
+        <v>6539</v>
       </c>
       <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
         <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21.2</v>
+        <v>20.82</v>
       </c>
       <c r="C25" t="n">
-        <v>21.55</v>
+        <v>21.19</v>
       </c>
       <c r="D25" t="n">
-        <v>20.85</v>
+        <v>19.8</v>
       </c>
       <c r="E25" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F25" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="G25" t="n">
-        <v>629</v>
+        <v>215</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K25" t="n">
-        <v>58.56</v>
+        <v>58.55</v>
       </c>
       <c r="L25" t="n">
-        <v>61.5</v>
+        <v>67.09</v>
       </c>
       <c r="M25" t="n">
-        <v>56.2</v>
+        <v>55.27</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6849</v>
+        <v>6250</v>
       </c>
       <c r="P25" t="n">
-        <v>6647</v>
+        <v>6579</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
@@ -2016,7 +2016,7 @@
         <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
         <v>60</v>
@@ -2025,51 +2025,51 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.75</v>
+        <v>21.17</v>
       </c>
       <c r="C26" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
       <c r="D26" t="n">
-        <v>20.1</v>
+        <v>20.87</v>
       </c>
       <c r="E26" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F26" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="G26" t="n">
-        <v>612</v>
+        <v>419</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="K26" t="n">
-        <v>59.8</v>
+        <v>57.42</v>
       </c>
       <c r="L26" t="n">
-        <v>61.83</v>
+        <v>60.15</v>
       </c>
       <c r="M26" t="n">
-        <v>58.57</v>
+        <v>55.34</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6901</v>
+        <v>6777</v>
       </c>
       <c r="P26" t="n">
-        <v>6676</v>
+        <v>6613</v>
       </c>
       <c r="Q26" t="n">
         <v>5</v>
@@ -2087,60 +2087,60 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.11</v>
+        <v>21.2</v>
       </c>
       <c r="C27" t="n">
-        <v>21.09</v>
+        <v>21.55</v>
       </c>
       <c r="D27" t="n">
-        <v>19.18</v>
+        <v>20.85</v>
       </c>
       <c r="E27" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F27" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G27" t="n">
-        <v>471</v>
+        <v>629</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="J27" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>63.63</v>
+        <v>58.56</v>
       </c>
       <c r="L27" t="n">
-        <v>67.22</v>
+        <v>61.5</v>
       </c>
       <c r="M27" t="n">
-        <v>59.39</v>
+        <v>56.2</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6810</v>
+        <v>6849</v>
       </c>
       <c r="P27" t="n">
-        <v>6613</v>
+        <v>6647</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
         <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
         <v>60</v>
@@ -2149,60 +2149,60 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>20.75</v>
       </c>
       <c r="C28" t="n">
-        <v>19.69</v>
+        <v>21.44</v>
       </c>
       <c r="D28" t="n">
-        <v>18.97</v>
+        <v>20.1</v>
       </c>
       <c r="E28" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F28" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G28" t="n">
-        <v>300</v>
+        <v>612</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="J28" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>66.97</v>
+        <v>59.8</v>
       </c>
       <c r="L28" t="n">
-        <v>70.23999999999999</v>
+        <v>61.83</v>
       </c>
       <c r="M28" t="n">
-        <v>65.22</v>
+        <v>58.57</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6681</v>
+        <v>6901</v>
       </c>
       <c r="P28" t="n">
-        <v>6565</v>
+        <v>6676</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
         <v>60</v>
@@ -2211,60 +2211,60 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18.64</v>
+        <v>20.11</v>
       </c>
       <c r="C29" t="n">
-        <v>20.12</v>
+        <v>21.09</v>
       </c>
       <c r="D29" t="n">
-        <v>17.71</v>
+        <v>19.18</v>
       </c>
       <c r="E29" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="F29" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="G29" t="n">
-        <v>347</v>
+        <v>471</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="J29" t="n">
-        <v>0.48</v>
+        <v>0.72</v>
       </c>
       <c r="K29" t="n">
-        <v>71.42</v>
+        <v>63.63</v>
       </c>
       <c r="L29" t="n">
-        <v>76.48</v>
+        <v>67.22</v>
       </c>
       <c r="M29" t="n">
-        <v>66.62</v>
+        <v>59.39</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6739</v>
+        <v>6810</v>
       </c>
       <c r="P29" t="n">
-        <v>6565</v>
+        <v>6613</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S29" t="n">
         <v>4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
       </c>
       <c r="T29" t="n">
         <v>60</v>
@@ -2273,200 +2273,200 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.37</v>
+        <v>19.28</v>
       </c>
       <c r="C30" t="n">
-        <v>18.2</v>
+        <v>19.69</v>
       </c>
       <c r="D30" t="n">
-        <v>16.67</v>
+        <v>18.97</v>
       </c>
       <c r="E30" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="F30" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="G30" t="n">
-        <v>167</v>
+        <v>300</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="J30" t="n">
-        <v>0.26</v>
+        <v>0.65</v>
       </c>
       <c r="K30" t="n">
-        <v>79.89</v>
+        <v>66.97</v>
       </c>
       <c r="L30" t="n">
-        <v>86.01000000000001</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>75.15000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6499</v>
+        <v>6681</v>
       </c>
       <c r="P30" t="n">
-        <v>6494</v>
+        <v>6565</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
+        <v>4</v>
+      </c>
+      <c r="S30" t="n">
         <v>3</v>
       </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
       <c r="T30" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>15.89</v>
+        <v>18.64</v>
       </c>
       <c r="C31" t="n">
-        <v>16.51</v>
+        <v>20.12</v>
       </c>
       <c r="D31" t="n">
-        <v>15.53</v>
+        <v>17.71</v>
       </c>
       <c r="E31" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="F31" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="G31" t="n">
-        <v>40</v>
+        <v>347</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.14</v>
+        <v>0.61</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="K31" t="n">
-        <v>91.95</v>
+        <v>71.42</v>
       </c>
       <c r="L31" t="n">
-        <v>93.86</v>
+        <v>76.48</v>
       </c>
       <c r="M31" t="n">
-        <v>87.84999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4793</v>
+        <v>6739</v>
       </c>
       <c r="P31" t="n">
-        <v>6442</v>
+        <v>6565</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15.63</v>
+        <v>17.37</v>
       </c>
       <c r="C32" t="n">
-        <v>15.72</v>
+        <v>18.2</v>
       </c>
       <c r="D32" t="n">
-        <v>15.55</v>
+        <v>16.67</v>
       </c>
       <c r="E32" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="F32" t="n">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="K32" t="n">
-        <v>92.23</v>
+        <v>79.89</v>
       </c>
       <c r="L32" t="n">
-        <v>93.61</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>90.98</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>6499</v>
       </c>
       <c r="P32" t="n">
-        <v>6417</v>
+        <v>6494</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15.65</v>
+        <v>15.89</v>
       </c>
       <c r="C33" t="n">
-        <v>15.76</v>
+        <v>16.51</v>
       </c>
       <c r="D33" t="n">
         <v>15.53</v>
@@ -2475,35 +2475,35 @@
         <v>14.5</v>
       </c>
       <c r="F33" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="J33" t="n">
         <v>0.1</v>
       </c>
       <c r="K33" t="n">
-        <v>93.44</v>
+        <v>91.95</v>
       </c>
       <c r="L33" t="n">
-        <v>93.83</v>
+        <v>93.86</v>
       </c>
       <c r="M33" t="n">
-        <v>92.88</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4793</v>
       </c>
       <c r="P33" t="n">
-        <v>6405</v>
+        <v>6442</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
@@ -2521,42 +2521,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>15.63</v>
       </c>
       <c r="C34" t="n">
-        <v>15.74</v>
+        <v>15.72</v>
       </c>
       <c r="D34" t="n">
-        <v>15.57</v>
+        <v>15.55</v>
       </c>
       <c r="E34" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="F34" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="J34" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="K34" t="n">
-        <v>94.87</v>
+        <v>92.23</v>
       </c>
       <c r="L34" t="n">
-        <v>95.69</v>
+        <v>93.61</v>
       </c>
       <c r="M34" t="n">
-        <v>93.40000000000001</v>
+        <v>90.98</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2565,16 +2565,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -2583,42 +2583,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.74</v>
+        <v>15.65</v>
       </c>
       <c r="C35" t="n">
-        <v>15.95</v>
+        <v>15.76</v>
       </c>
       <c r="D35" t="n">
-        <v>15.62</v>
+        <v>15.53</v>
       </c>
       <c r="E35" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="F35" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J35" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="K35" t="n">
-        <v>95.13</v>
+        <v>93.44</v>
       </c>
       <c r="L35" t="n">
-        <v>96.19</v>
+        <v>93.83</v>
       </c>
       <c r="M35" t="n">
-        <v>94.28</v>
+        <v>92.88</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2627,16 +2627,16 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6422</v>
+        <v>6405</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -2645,42 +2645,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.02</v>
+        <v>15.63</v>
       </c>
       <c r="C36" t="n">
-        <v>16.13</v>
+        <v>15.74</v>
       </c>
       <c r="D36" t="n">
-        <v>15.96</v>
+        <v>15.57</v>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F36" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J36" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>94.3</v>
+        <v>94.87</v>
       </c>
       <c r="L36" t="n">
-        <v>94.76000000000001</v>
+        <v>95.69</v>
       </c>
       <c r="M36" t="n">
-        <v>93.61</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>6414</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -2707,42 +2707,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.24</v>
+        <v>15.74</v>
       </c>
       <c r="C37" t="n">
-        <v>16.32</v>
+        <v>15.95</v>
       </c>
       <c r="D37" t="n">
-        <v>16.16</v>
+        <v>15.62</v>
       </c>
       <c r="E37" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="F37" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="K37" t="n">
-        <v>93.55</v>
+        <v>95.13</v>
       </c>
       <c r="L37" t="n">
-        <v>94.40000000000001</v>
+        <v>96.19</v>
       </c>
       <c r="M37" t="n">
-        <v>92.81</v>
+        <v>94.28</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2751,16 +2751,16 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -2769,42 +2769,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.57</v>
+        <v>16.02</v>
       </c>
       <c r="C38" t="n">
-        <v>16.97</v>
+        <v>16.13</v>
       </c>
       <c r="D38" t="n">
-        <v>16.32</v>
+        <v>15.96</v>
       </c>
       <c r="E38" t="n">
         <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="K38" t="n">
-        <v>90.97</v>
+        <v>94.3</v>
       </c>
       <c r="L38" t="n">
-        <v>93.34999999999999</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>87.03</v>
+        <v>93.61</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -2831,42 +2831,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.39</v>
+        <v>16.24</v>
       </c>
       <c r="C39" t="n">
-        <v>17.59</v>
+        <v>16.32</v>
       </c>
       <c r="D39" t="n">
-        <v>17.17</v>
+        <v>16.16</v>
       </c>
       <c r="E39" t="n">
-        <v>13.8</v>
+        <v>15.1</v>
       </c>
       <c r="F39" t="n">
-        <v>13.5</v>
+        <v>15.1</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>0.11</v>
       </c>
       <c r="J39" t="n">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="K39" t="n">
-        <v>79.91</v>
+        <v>93.55</v>
       </c>
       <c r="L39" t="n">
-        <v>84</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>77.81999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>6417</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -2893,42 +2893,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.82</v>
+        <v>16.57</v>
       </c>
       <c r="C40" t="n">
-        <v>17.99</v>
+        <v>16.97</v>
       </c>
       <c r="D40" t="n">
-        <v>17.64</v>
+        <v>16.32</v>
       </c>
       <c r="E40" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.45</v>
+        <v>0.16</v>
       </c>
       <c r="J40" t="n">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="K40" t="n">
-        <v>77.5</v>
+        <v>90.97</v>
       </c>
       <c r="L40" t="n">
-        <v>79.29000000000001</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>76.37</v>
+        <v>87.03</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -2955,42 +2955,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18.13</v>
+        <v>17.39</v>
       </c>
       <c r="C41" t="n">
-        <v>18.3</v>
+        <v>17.59</v>
       </c>
       <c r="D41" t="n">
-        <v>17.82</v>
+        <v>17.17</v>
       </c>
       <c r="E41" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F41" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="K41" t="n">
-        <v>76.5</v>
+        <v>79.91</v>
       </c>
       <c r="L41" t="n">
-        <v>81.88</v>
+        <v>84</v>
       </c>
       <c r="M41" t="n">
-        <v>74.38</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2999,13 +2999,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6428</v>
+        <v>6417</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -3017,42 +3017,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.85</v>
+        <v>17.82</v>
       </c>
       <c r="C42" t="n">
-        <v>18.1</v>
+        <v>17.99</v>
       </c>
       <c r="D42" t="n">
-        <v>17.67</v>
+        <v>17.64</v>
       </c>
       <c r="E42" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="F42" t="n">
-        <v>14.1</v>
+        <v>13.5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="J42" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="K42" t="n">
-        <v>80.95</v>
+        <v>77.5</v>
       </c>
       <c r="L42" t="n">
-        <v>82.98</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>77.86</v>
+        <v>76.37</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3061,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -3079,42 +3079,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.69</v>
+        <v>18.13</v>
       </c>
       <c r="C43" t="n">
-        <v>19.09</v>
+        <v>18.3</v>
       </c>
       <c r="D43" t="n">
-        <v>18.24</v>
+        <v>17.82</v>
       </c>
       <c r="E43" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F43" t="n">
         <v>13.4</v>
-      </c>
-      <c r="F43" t="n">
-        <v>13</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="K43" t="n">
-        <v>71.91</v>
+        <v>76.5</v>
       </c>
       <c r="L43" t="n">
-        <v>75.81999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="M43" t="n">
-        <v>68.15000000000001</v>
+        <v>74.38</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="Q43" t="n">
         <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3141,60 +3141,60 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.36</v>
+        <v>17.85</v>
       </c>
       <c r="C44" t="n">
-        <v>19.58</v>
+        <v>18.1</v>
       </c>
       <c r="D44" t="n">
-        <v>19.06</v>
+        <v>17.67</v>
       </c>
       <c r="E44" t="n">
-        <v>12.8</v>
+        <v>14.4</v>
       </c>
       <c r="F44" t="n">
-        <v>12.5</v>
+        <v>14.1</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="J44" t="n">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
       <c r="K44" t="n">
-        <v>66.34999999999999</v>
+        <v>80.95</v>
       </c>
       <c r="L44" t="n">
-        <v>69.37</v>
+        <v>82.98</v>
       </c>
       <c r="M44" t="n">
-        <v>63.92</v>
+        <v>77.86</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6465</v>
+        <v>6434</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -3203,237 +3203,237 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.82</v>
+        <v>18.69</v>
       </c>
       <c r="C45" t="n">
-        <v>20.22</v>
+        <v>19.09</v>
       </c>
       <c r="D45" t="n">
-        <v>19.58</v>
+        <v>18.24</v>
       </c>
       <c r="E45" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="F45" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="G45" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="K45" t="n">
-        <v>64.69</v>
+        <v>71.91</v>
       </c>
       <c r="L45" t="n">
-        <v>67.25</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>63.16</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3944</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6511</v>
+        <v>6440</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
         <v>4</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.77</v>
+        <v>19.36</v>
       </c>
       <c r="C46" t="n">
-        <v>20.09</v>
+        <v>19.58</v>
       </c>
       <c r="D46" t="n">
-        <v>19.54</v>
+        <v>19.06</v>
       </c>
       <c r="E46" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="F46" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="G46" t="n">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="J46" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="K46" t="n">
-        <v>66.33</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>68.87</v>
+        <v>69.37</v>
       </c>
       <c r="M46" t="n">
-        <v>61.21</v>
+        <v>63.92</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6671</v>
+        <v>1620</v>
       </c>
       <c r="P46" t="n">
-        <v>6539</v>
+        <v>6465</v>
       </c>
       <c r="Q46" t="n">
         <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="C47" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="D47" t="n">
         <v>19.58</v>
       </c>
-      <c r="C47" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="D47" t="n">
-        <v>19.38</v>
-      </c>
       <c r="E47" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F47" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="G47" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="K47" t="n">
-        <v>65.27</v>
+        <v>64.69</v>
       </c>
       <c r="L47" t="n">
-        <v>67.09999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="M47" t="n">
-        <v>61.34</v>
+        <v>63.16</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6389</v>
+        <v>3944</v>
       </c>
       <c r="P47" t="n">
-        <v>6534</v>
+        <v>6511</v>
       </c>
       <c r="Q47" t="n">
         <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.96</v>
+        <v>19.77</v>
       </c>
       <c r="C48" t="n">
-        <v>20.7</v>
+        <v>20.09</v>
       </c>
       <c r="D48" t="n">
-        <v>19.58</v>
+        <v>19.54</v>
       </c>
       <c r="E48" t="n">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
       <c r="F48" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="G48" t="n">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="J48" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="K48" t="n">
-        <v>62.94</v>
+        <v>66.33</v>
       </c>
       <c r="L48" t="n">
-        <v>66.14</v>
+        <v>68.87</v>
       </c>
       <c r="M48" t="n">
-        <v>60.5</v>
+        <v>61.21</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4869</v>
+        <v>6671</v>
       </c>
       <c r="P48" t="n">
-        <v>6534</v>
+        <v>6539</v>
       </c>
       <c r="Q48" t="n">
         <v>4</v>
@@ -3445,69 +3445,69 @@
         <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 13:00:00</t>
+          <t>2026-10-14 15:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.73</v>
+        <v>19.58</v>
       </c>
       <c r="C49" t="n">
-        <v>20.67</v>
+        <v>19.95</v>
       </c>
       <c r="D49" t="n">
-        <v>18.8</v>
+        <v>19.38</v>
       </c>
       <c r="E49" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="F49" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="G49" t="n">
-        <v>327</v>
+        <v>138</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="K49" t="n">
-        <v>68.13</v>
+        <v>65.27</v>
       </c>
       <c r="L49" t="n">
-        <v>72.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>62.94</v>
+        <v>61.34</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6834</v>
+        <v>6389</v>
       </c>
       <c r="P49" t="n">
-        <v>6628</v>
+        <v>6534</v>
       </c>
       <c r="Q49" t="n">
         <v>4</v>
       </c>
       <c r="R49" t="n">
+        <v>5</v>
+      </c>
+      <c r="S49" t="n">
         <v>4</v>
       </c>
-      <c r="S49" t="n">
-        <v>3</v>
-      </c>
       <c r="T49" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,48 +533,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.18</v>
+        <v>22.46</v>
       </c>
       <c r="C2" t="n">
-        <v>22.92</v>
+        <v>23.17</v>
       </c>
       <c r="D2" t="n">
-        <v>21.96</v>
+        <v>21.82</v>
       </c>
       <c r="E2" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="F2" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="G2" t="n">
-        <v>567</v>
+        <v>383</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="J2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="K2" t="n">
-        <v>54.01</v>
+        <v>52.56</v>
       </c>
       <c r="L2" t="n">
-        <v>55.7</v>
+        <v>54.35</v>
       </c>
       <c r="M2" t="n">
-        <v>51.48</v>
+        <v>50.6</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6786</v>
+        <v>6763</v>
       </c>
       <c r="P2" t="n">
         <v>6593</v>
@@ -589,60 +589,60 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.45</v>
+        <v>22.1</v>
       </c>
       <c r="C3" t="n">
-        <v>22.62</v>
+        <v>22.92</v>
       </c>
       <c r="D3" t="n">
-        <v>20.83</v>
+        <v>21.76</v>
       </c>
       <c r="E3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F3" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>640</v>
+        <v>479</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="K3" t="n">
-        <v>56.35</v>
+        <v>53.58</v>
       </c>
       <c r="L3" t="n">
-        <v>62.61</v>
+        <v>55.95</v>
       </c>
       <c r="M3" t="n">
-        <v>51.88</v>
+        <v>51.48</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6810</v>
+        <v>6739</v>
       </c>
       <c r="P3" t="n">
-        <v>6610</v>
+        <v>6582</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
         <v>6</v>
@@ -657,60 +657,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.67</v>
+        <v>21.45</v>
       </c>
       <c r="C4" t="n">
-        <v>20.85</v>
+        <v>22.62</v>
       </c>
       <c r="D4" t="n">
-        <v>19.11</v>
+        <v>20.83</v>
       </c>
       <c r="E4" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="F4" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
       <c r="G4" t="n">
-        <v>279</v>
+        <v>640</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.77</v>
+        <v>1.11</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="K4" t="n">
-        <v>66.39</v>
+        <v>56.35</v>
       </c>
       <c r="L4" t="n">
-        <v>68.68000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="M4" t="n">
-        <v>61.4</v>
+        <v>51.88</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6772</v>
+        <v>6810</v>
       </c>
       <c r="P4" t="n">
-        <v>6571</v>
+        <v>6610</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" t="n">
         <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
       </c>
       <c r="T4" t="n">
         <v>60</v>
@@ -719,172 +719,172 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.92</v>
+        <v>19.67</v>
       </c>
       <c r="C5" t="n">
-        <v>19.22</v>
+        <v>20.85</v>
       </c>
       <c r="D5" t="n">
-        <v>18.64</v>
+        <v>19.11</v>
       </c>
       <c r="E5" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="F5" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="G5" t="n">
-        <v>143</v>
+        <v>279</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="J5" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>71.48999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="L5" t="n">
-        <v>73.28</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>69.45</v>
+        <v>61.4</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6254</v>
+        <v>6772</v>
       </c>
       <c r="P5" t="n">
-        <v>6508</v>
+        <v>6571</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.78</v>
+        <v>18.92</v>
       </c>
       <c r="C6" t="n">
-        <v>18.89</v>
+        <v>19.22</v>
       </c>
       <c r="D6" t="n">
-        <v>18.67</v>
+        <v>18.64</v>
       </c>
       <c r="E6" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="F6" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="G6" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="J6" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="K6" t="n">
-        <v>70.87</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>73.17</v>
+        <v>73.28</v>
       </c>
       <c r="M6" t="n">
-        <v>68.48</v>
+        <v>69.45</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5929</v>
+        <v>6254</v>
       </c>
       <c r="P6" t="n">
-        <v>6494</v>
+        <v>6508</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.59</v>
+        <v>18.78</v>
       </c>
       <c r="C7" t="n">
-        <v>19.26</v>
+        <v>18.89</v>
       </c>
       <c r="D7" t="n">
-        <v>18.18</v>
+        <v>18.67</v>
       </c>
       <c r="E7" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="F7" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="G7" t="n">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41</v>
+        <v>0.57</v>
       </c>
       <c r="K7" t="n">
-        <v>76.48999999999999</v>
+        <v>70.87</v>
       </c>
       <c r="L7" t="n">
-        <v>80.08</v>
+        <v>73.17</v>
       </c>
       <c r="M7" t="n">
-        <v>71.70999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5478</v>
+        <v>5929</v>
       </c>
       <c r="P7" t="n">
         <v>6494</v>
@@ -893,10 +893,10 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
@@ -905,60 +905,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.89</v>
+        <v>18.59</v>
       </c>
       <c r="C8" t="n">
-        <v>18.29</v>
+        <v>19.26</v>
       </c>
       <c r="D8" t="n">
-        <v>17.02</v>
+        <v>18.18</v>
       </c>
       <c r="E8" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="F8" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="G8" t="n">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="K8" t="n">
-        <v>82.51000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>87.40000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M8" t="n">
-        <v>79.09999999999999</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6633</v>
+        <v>5478</v>
       </c>
       <c r="P8" t="n">
-        <v>6488</v>
+        <v>6494</v>
       </c>
       <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
@@ -967,113 +967,113 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.49</v>
+        <v>17.89</v>
       </c>
       <c r="C9" t="n">
-        <v>16.79</v>
+        <v>18.29</v>
       </c>
       <c r="D9" t="n">
-        <v>16.31</v>
+        <v>17.02</v>
       </c>
       <c r="E9" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F9" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J9" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="K9" t="n">
-        <v>89.09</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>91.65000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>87.73</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5349</v>
+        <v>6633</v>
       </c>
       <c r="P9" t="n">
-        <v>6445</v>
+        <v>6488</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.27</v>
+        <v>16.49</v>
       </c>
       <c r="C10" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="D10" t="n">
         <v>16.31</v>
-      </c>
-      <c r="D10" t="n">
-        <v>16.24</v>
       </c>
       <c r="E10" t="n">
         <v>14.6</v>
       </c>
       <c r="F10" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0.15</v>
       </c>
       <c r="K10" t="n">
-        <v>90.12</v>
+        <v>89.09</v>
       </c>
       <c r="L10" t="n">
-        <v>91.63</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>88.84</v>
+        <v>87.73</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P10" t="n">
-        <v>6422</v>
+        <v>6445</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1091,20 +1091,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.37</v>
+        <v>16.27</v>
       </c>
       <c r="C11" t="n">
-        <v>16.42</v>
+        <v>16.31</v>
       </c>
       <c r="D11" t="n">
-        <v>16.3</v>
+        <v>16.24</v>
       </c>
       <c r="E11" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F11" t="n">
         <v>14.4</v>
@@ -1114,19 +1114,19 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J11" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="K11" t="n">
-        <v>88.97</v>
+        <v>90.12</v>
       </c>
       <c r="L11" t="n">
-        <v>90.09</v>
+        <v>91.63</v>
       </c>
       <c r="M11" t="n">
-        <v>88.26000000000001</v>
+        <v>88.84</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1153,44 +1153,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.35</v>
+        <v>16.37</v>
       </c>
       <c r="C12" t="n">
-        <v>16.36</v>
+        <v>16.42</v>
       </c>
       <c r="D12" t="n">
-        <v>16.35</v>
+        <v>16.3</v>
       </c>
       <c r="E12" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="F12" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
-        <v>2592</v>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="K12" t="n">
-        <v>84.98</v>
+        <v>88.97</v>
       </c>
       <c r="L12" t="n">
-        <v>85.65000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="M12" t="n">
-        <v>84.31</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1199,13 +1197,13 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1217,44 +1215,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.33</v>
+        <v>16.35</v>
       </c>
       <c r="C13" t="n">
-        <v>16.56</v>
+        <v>16.36</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86</v>
+        <v>16.35</v>
       </c>
       <c r="E13" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2522</v>
+        <v>2592</v>
       </c>
       <c r="I13" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="K13" t="n">
-        <v>89.8</v>
+        <v>84.98</v>
       </c>
       <c r="L13" t="n">
-        <v>99.73</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>85.27</v>
+        <v>84.31</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1263,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6422</v>
+        <v>6425</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1281,42 +1279,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.27</v>
+        <v>16.33</v>
       </c>
       <c r="C14" t="n">
-        <v>16.37</v>
+        <v>16.56</v>
       </c>
       <c r="D14" t="n">
-        <v>16.2</v>
+        <v>15.86</v>
       </c>
       <c r="E14" t="n">
         <v>14.6</v>
       </c>
       <c r="F14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>2522</v>
+      </c>
       <c r="I14" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J14" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>90.44</v>
+        <v>89.8</v>
       </c>
       <c r="L14" t="n">
-        <v>91.61</v>
+        <v>99.73</v>
       </c>
       <c r="M14" t="n">
-        <v>89.09999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1325,16 +1325,16 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1343,23 +1343,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="C15" t="n">
-        <v>16.49</v>
+        <v>16.37</v>
       </c>
       <c r="D15" t="n">
-        <v>16.14</v>
+        <v>16.2</v>
       </c>
       <c r="E15" t="n">
         <v>14.6</v>
       </c>
       <c r="F15" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>0.15</v>
       </c>
       <c r="K15" t="n">
-        <v>90.33</v>
+        <v>90.44</v>
       </c>
       <c r="L15" t="n">
-        <v>91.40000000000001</v>
+        <v>91.61</v>
       </c>
       <c r="M15" t="n">
-        <v>89.20999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -1405,42 +1405,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.61</v>
+        <v>16.26</v>
       </c>
       <c r="C16" t="n">
-        <v>16.82</v>
+        <v>16.49</v>
       </c>
       <c r="D16" t="n">
-        <v>16.45</v>
+        <v>16.14</v>
       </c>
       <c r="E16" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F16" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="J16" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K16" t="n">
-        <v>87.3</v>
+        <v>90.33</v>
       </c>
       <c r="L16" t="n">
-        <v>89.45</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>86.06</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -1467,42 +1467,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.92</v>
+        <v>16.61</v>
       </c>
       <c r="C17" t="n">
-        <v>17.22</v>
+        <v>16.82</v>
       </c>
       <c r="D17" t="n">
-        <v>16.72</v>
+        <v>16.45</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="F17" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="J17" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="K17" t="n">
-        <v>83.48999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="L17" t="n">
-        <v>85.67</v>
+        <v>89.45</v>
       </c>
       <c r="M17" t="n">
-        <v>80.43000000000001</v>
+        <v>86.06</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1511,16 +1511,16 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6465</v>
+        <v>6434</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1529,42 +1529,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.37</v>
+        <v>16.92</v>
       </c>
       <c r="C18" t="n">
-        <v>17.64</v>
+        <v>17.22</v>
       </c>
       <c r="D18" t="n">
-        <v>17.15</v>
+        <v>16.72</v>
       </c>
       <c r="E18" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="J18" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="K18" t="n">
-        <v>81.5</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>83.2</v>
+        <v>85.67</v>
       </c>
       <c r="M18" t="n">
-        <v>79.69</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6471</v>
+        <v>6465</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
@@ -1591,42 +1591,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>17.37</v>
       </c>
       <c r="C19" t="n">
-        <v>17.71</v>
+        <v>17.64</v>
       </c>
       <c r="D19" t="n">
-        <v>17.16</v>
+        <v>17.15</v>
       </c>
       <c r="E19" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.33</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.28</v>
-      </c>
       <c r="K19" t="n">
-        <v>83.11</v>
+        <v>81.5</v>
       </c>
       <c r="L19" t="n">
-        <v>85.31</v>
+        <v>83.2</v>
       </c>
       <c r="M19" t="n">
-        <v>78.94</v>
+        <v>79.69</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6474</v>
+        <v>6471</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
@@ -1653,42 +1653,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.78</v>
+        <v>17.37</v>
       </c>
       <c r="C20" t="n">
-        <v>18.2</v>
+        <v>17.71</v>
       </c>
       <c r="D20" t="n">
-        <v>17.44</v>
+        <v>17.16</v>
       </c>
       <c r="E20" t="n">
         <v>14.4</v>
       </c>
       <c r="F20" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="J20" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="K20" t="n">
-        <v>81.01000000000001</v>
+        <v>83.11</v>
       </c>
       <c r="L20" t="n">
-        <v>82.84999999999999</v>
+        <v>85.31</v>
       </c>
       <c r="M20" t="n">
-        <v>78.13</v>
+        <v>78.94</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6494</v>
+        <v>6474</v>
       </c>
       <c r="Q20" t="n">
         <v>2</v>
@@ -1715,42 +1715,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.91</v>
+        <v>17.78</v>
       </c>
       <c r="C21" t="n">
-        <v>19.32</v>
+        <v>18.2</v>
       </c>
       <c r="D21" t="n">
-        <v>18.33</v>
+        <v>17.44</v>
       </c>
       <c r="E21" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="F21" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="J21" t="n">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="K21" t="n">
-        <v>72.89</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>76.66</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>67.31</v>
+        <v>78.13</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1759,16 +1759,16 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6496</v>
+        <v>6494</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -1777,54 +1777,54 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.65</v>
+        <v>18.91</v>
       </c>
       <c r="C22" t="n">
-        <v>19.86</v>
+        <v>19.32</v>
       </c>
       <c r="D22" t="n">
-        <v>19.37</v>
+        <v>18.33</v>
       </c>
       <c r="E22" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="F22" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="J22" t="n">
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="K22" t="n">
-        <v>69.28</v>
+        <v>72.89</v>
       </c>
       <c r="L22" t="n">
-        <v>71.03</v>
+        <v>76.66</v>
       </c>
       <c r="M22" t="n">
-        <v>67.26000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6511</v>
+        <v>6496</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
         <v>4</v>
@@ -1839,51 +1839,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.34</v>
+        <v>19.65</v>
       </c>
       <c r="C23" t="n">
-        <v>19.5</v>
+        <v>19.86</v>
       </c>
       <c r="D23" t="n">
-        <v>19.25</v>
+        <v>19.37</v>
       </c>
       <c r="E23" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F23" t="n">
         <v>13.5</v>
       </c>
-      <c r="F23" t="n">
-        <v>13.4</v>
-      </c>
       <c r="G23" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="K23" t="n">
-        <v>69.37</v>
+        <v>69.28</v>
       </c>
       <c r="L23" t="n">
-        <v>70.14</v>
+        <v>71.03</v>
       </c>
       <c r="M23" t="n">
-        <v>68.55</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4721</v>
+        <v>2267</v>
       </c>
       <c r="P23" t="n">
-        <v>6536</v>
+        <v>6511</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
@@ -1901,51 +1901,51 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.29</v>
+        <v>19.34</v>
       </c>
       <c r="C24" t="n">
-        <v>19.86</v>
+        <v>19.5</v>
       </c>
       <c r="D24" t="n">
-        <v>19.1</v>
+        <v>19.25</v>
       </c>
       <c r="E24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F24" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" t="n">
-        <v>13.3</v>
-      </c>
       <c r="G24" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="J24" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="K24" t="n">
-        <v>68.94</v>
+        <v>69.37</v>
       </c>
       <c r="L24" t="n">
-        <v>69.94</v>
+        <v>70.14</v>
       </c>
       <c r="M24" t="n">
-        <v>66.66</v>
+        <v>68.55</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4462</v>
+        <v>4721</v>
       </c>
       <c r="P24" t="n">
-        <v>6539</v>
+        <v>6536</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -1957,119 +1957,119 @@
         <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.82</v>
+        <v>19.29</v>
       </c>
       <c r="C25" t="n">
-        <v>21.19</v>
+        <v>19.86</v>
       </c>
       <c r="D25" t="n">
-        <v>19.8</v>
+        <v>19.1</v>
       </c>
       <c r="E25" t="n">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="F25" t="n">
-        <v>11.7</v>
+        <v>13.3</v>
       </c>
       <c r="G25" t="n">
-        <v>215</v>
+        <v>68</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>1.02</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="K25" t="n">
-        <v>58.55</v>
+        <v>68.94</v>
       </c>
       <c r="L25" t="n">
-        <v>67.09</v>
+        <v>69.94</v>
       </c>
       <c r="M25" t="n">
-        <v>55.27</v>
+        <v>66.66</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6250</v>
+        <v>4462</v>
       </c>
       <c r="P25" t="n">
-        <v>6579</v>
+        <v>6539</v>
       </c>
       <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
         <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21.17</v>
+        <v>20.82</v>
       </c>
       <c r="C26" t="n">
-        <v>21.41</v>
+        <v>21.19</v>
       </c>
       <c r="D26" t="n">
-        <v>20.87</v>
+        <v>19.8</v>
       </c>
       <c r="E26" t="n">
         <v>12.3</v>
       </c>
       <c r="F26" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="G26" t="n">
-        <v>419</v>
+        <v>215</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="J26" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="K26" t="n">
-        <v>57.42</v>
+        <v>58.55</v>
       </c>
       <c r="L26" t="n">
-        <v>60.15</v>
+        <v>67.09</v>
       </c>
       <c r="M26" t="n">
-        <v>55.34</v>
+        <v>55.27</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6777</v>
+        <v>6250</v>
       </c>
       <c r="P26" t="n">
-        <v>6613</v>
+        <v>6579</v>
       </c>
       <c r="Q26" t="n">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         <v>5</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
         <v>60</v>
@@ -2087,51 +2087,51 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.2</v>
+        <v>21.17</v>
       </c>
       <c r="C27" t="n">
-        <v>21.55</v>
+        <v>21.41</v>
       </c>
       <c r="D27" t="n">
-        <v>20.85</v>
+        <v>20.87</v>
       </c>
       <c r="E27" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F27" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="G27" t="n">
-        <v>629</v>
+        <v>419</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="K27" t="n">
-        <v>58.56</v>
+        <v>57.42</v>
       </c>
       <c r="L27" t="n">
-        <v>61.5</v>
+        <v>60.15</v>
       </c>
       <c r="M27" t="n">
-        <v>56.2</v>
+        <v>55.34</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6849</v>
+        <v>6777</v>
       </c>
       <c r="P27" t="n">
-        <v>6647</v>
+        <v>6613</v>
       </c>
       <c r="Q27" t="n">
         <v>5</v>
@@ -2149,17 +2149,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20.75</v>
+        <v>21.2</v>
       </c>
       <c r="C28" t="n">
-        <v>21.44</v>
+        <v>21.55</v>
       </c>
       <c r="D28" t="n">
-        <v>20.1</v>
+        <v>20.85</v>
       </c>
       <c r="E28" t="n">
         <v>12.6</v>
@@ -2168,32 +2168,32 @@
         <v>12.1</v>
       </c>
       <c r="G28" t="n">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>59.8</v>
+        <v>58.56</v>
       </c>
       <c r="L28" t="n">
-        <v>61.83</v>
+        <v>61.5</v>
       </c>
       <c r="M28" t="n">
-        <v>58.57</v>
+        <v>56.2</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6901</v>
+        <v>6849</v>
       </c>
       <c r="P28" t="n">
-        <v>6676</v>
+        <v>6647</v>
       </c>
       <c r="Q28" t="n">
         <v>5</v>
@@ -2211,60 +2211,60 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20.11</v>
+        <v>20.75</v>
       </c>
       <c r="C29" t="n">
-        <v>21.09</v>
+        <v>21.44</v>
       </c>
       <c r="D29" t="n">
-        <v>19.18</v>
+        <v>20.1</v>
       </c>
       <c r="E29" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F29" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G29" t="n">
-        <v>471</v>
+        <v>612</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="J29" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="K29" t="n">
-        <v>63.63</v>
+        <v>59.8</v>
       </c>
       <c r="L29" t="n">
-        <v>67.22</v>
+        <v>61.83</v>
       </c>
       <c r="M29" t="n">
-        <v>59.39</v>
+        <v>58.57</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6810</v>
+        <v>6901</v>
       </c>
       <c r="P29" t="n">
-        <v>6613</v>
+        <v>6676</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
         <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
         <v>60</v>
@@ -2273,17 +2273,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.28</v>
+        <v>20.11</v>
       </c>
       <c r="C30" t="n">
-        <v>19.69</v>
+        <v>21.09</v>
       </c>
       <c r="D30" t="n">
-        <v>18.97</v>
+        <v>19.18</v>
       </c>
       <c r="E30" t="n">
         <v>12.9</v>
@@ -2292,41 +2292,41 @@
         <v>12.5</v>
       </c>
       <c r="G30" t="n">
-        <v>300</v>
+        <v>471</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="K30" t="n">
-        <v>66.97</v>
+        <v>63.63</v>
       </c>
       <c r="L30" t="n">
-        <v>70.23999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="M30" t="n">
-        <v>65.22</v>
+        <v>59.39</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6681</v>
+        <v>6810</v>
       </c>
       <c r="P30" t="n">
-        <v>6565</v>
+        <v>6613</v>
       </c>
       <c r="Q30" t="n">
         <v>4</v>
       </c>
       <c r="R30" t="n">
+        <v>5</v>
+      </c>
+      <c r="S30" t="n">
         <v>4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
       </c>
       <c r="T30" t="n">
         <v>60</v>
@@ -2335,54 +2335,54 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18.64</v>
+        <v>19.28</v>
       </c>
       <c r="C31" t="n">
-        <v>20.12</v>
+        <v>19.69</v>
       </c>
       <c r="D31" t="n">
-        <v>17.71</v>
+        <v>18.97</v>
       </c>
       <c r="E31" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="F31" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="G31" t="n">
-        <v>347</v>
+        <v>300</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="J31" t="n">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="K31" t="n">
-        <v>71.42</v>
+        <v>66.97</v>
       </c>
       <c r="L31" t="n">
-        <v>76.48</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>66.62</v>
+        <v>65.22</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6739</v>
+        <v>6681</v>
       </c>
       <c r="P31" t="n">
         <v>6565</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
         <v>4</v>
@@ -2397,175 +2397,175 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.37</v>
+        <v>18.64</v>
       </c>
       <c r="C32" t="n">
-        <v>18.2</v>
+        <v>20.12</v>
       </c>
       <c r="D32" t="n">
-        <v>16.67</v>
+        <v>17.71</v>
       </c>
       <c r="E32" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="F32" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="G32" t="n">
-        <v>167</v>
+        <v>347</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="J32" t="n">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="K32" t="n">
-        <v>79.89</v>
+        <v>71.42</v>
       </c>
       <c r="L32" t="n">
-        <v>86.01000000000001</v>
+        <v>76.48</v>
       </c>
       <c r="M32" t="n">
-        <v>75.15000000000001</v>
+        <v>66.62</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6499</v>
+        <v>6739</v>
       </c>
       <c r="P32" t="n">
-        <v>6494</v>
+        <v>6565</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
       <c r="T32" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15.89</v>
+        <v>17.37</v>
       </c>
       <c r="C33" t="n">
-        <v>16.51</v>
+        <v>18.2</v>
       </c>
       <c r="D33" t="n">
-        <v>15.53</v>
+        <v>16.67</v>
       </c>
       <c r="E33" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="F33" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="K33" t="n">
-        <v>91.95</v>
+        <v>79.89</v>
       </c>
       <c r="L33" t="n">
-        <v>93.86</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>87.84999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4793</v>
+        <v>6499</v>
       </c>
       <c r="P33" t="n">
-        <v>6442</v>
+        <v>6494</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15.63</v>
+        <v>15.89</v>
       </c>
       <c r="C34" t="n">
-        <v>15.72</v>
+        <v>16.51</v>
       </c>
       <c r="D34" t="n">
-        <v>15.55</v>
+        <v>15.53</v>
       </c>
       <c r="E34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F34" t="n">
         <v>14.3</v>
       </c>
-      <c r="F34" t="n">
-        <v>14.2</v>
-      </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="J34" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K34" t="n">
-        <v>92.23</v>
+        <v>91.95</v>
       </c>
       <c r="L34" t="n">
-        <v>93.61</v>
+        <v>93.86</v>
       </c>
       <c r="M34" t="n">
-        <v>90.98</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4793</v>
       </c>
       <c r="P34" t="n">
-        <v>6417</v>
+        <v>6442</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
@@ -2583,42 +2583,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.65</v>
+        <v>15.63</v>
       </c>
       <c r="C35" t="n">
-        <v>15.76</v>
+        <v>15.72</v>
       </c>
       <c r="D35" t="n">
-        <v>15.53</v>
+        <v>15.55</v>
       </c>
       <c r="E35" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F35" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J35" t="n">
         <v>0.11</v>
       </c>
-      <c r="J35" t="n">
-        <v>0.1</v>
-      </c>
       <c r="K35" t="n">
-        <v>93.44</v>
+        <v>92.23</v>
       </c>
       <c r="L35" t="n">
-        <v>93.83</v>
+        <v>93.61</v>
       </c>
       <c r="M35" t="n">
-        <v>92.88</v>
+        <v>90.98</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6405</v>
+        <v>6417</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
@@ -2645,42 +2645,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.63</v>
+        <v>15.65</v>
       </c>
       <c r="C36" t="n">
-        <v>15.74</v>
+        <v>15.76</v>
       </c>
       <c r="D36" t="n">
-        <v>15.57</v>
+        <v>15.53</v>
       </c>
       <c r="E36" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="F36" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="K36" t="n">
-        <v>94.87</v>
+        <v>93.44</v>
       </c>
       <c r="L36" t="n">
-        <v>95.69</v>
+        <v>93.83</v>
       </c>
       <c r="M36" t="n">
-        <v>93.40000000000001</v>
+        <v>92.88</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2689,16 +2689,16 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>6414</v>
+        <v>6405</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -2707,23 +2707,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="C37" t="n">
         <v>15.74</v>
       </c>
-      <c r="C37" t="n">
-        <v>15.95</v>
-      </c>
       <c r="D37" t="n">
-        <v>15.62</v>
+        <v>15.57</v>
       </c>
       <c r="E37" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F37" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2733,16 +2733,16 @@
         <v>0.08</v>
       </c>
       <c r="J37" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>95.13</v>
+        <v>94.87</v>
       </c>
       <c r="L37" t="n">
-        <v>96.19</v>
+        <v>95.69</v>
       </c>
       <c r="M37" t="n">
-        <v>94.28</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -2769,20 +2769,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.02</v>
+        <v>15.74</v>
       </c>
       <c r="C38" t="n">
-        <v>16.13</v>
+        <v>15.95</v>
       </c>
       <c r="D38" t="n">
-        <v>15.96</v>
+        <v>15.62</v>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F38" t="n">
         <v>14.9</v>
@@ -2792,19 +2792,19 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J38" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="K38" t="n">
-        <v>94.3</v>
+        <v>95.13</v>
       </c>
       <c r="L38" t="n">
-        <v>94.76000000000001</v>
+        <v>96.19</v>
       </c>
       <c r="M38" t="n">
-        <v>93.61</v>
+        <v>94.28</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -2813,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -2831,42 +2831,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.24</v>
+        <v>16.02</v>
       </c>
       <c r="C39" t="n">
-        <v>16.32</v>
+        <v>16.13</v>
       </c>
       <c r="D39" t="n">
-        <v>16.16</v>
+        <v>15.96</v>
       </c>
       <c r="E39" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K39" t="n">
-        <v>93.55</v>
+        <v>94.3</v>
       </c>
       <c r="L39" t="n">
-        <v>94.40000000000001</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>92.81</v>
+        <v>93.61</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -2884,7 +2884,7 @@
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -2893,42 +2893,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.57</v>
+        <v>16.24</v>
       </c>
       <c r="C40" t="n">
-        <v>16.97</v>
+        <v>16.32</v>
       </c>
       <c r="D40" t="n">
-        <v>16.32</v>
+        <v>16.16</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="F40" t="n">
-        <v>14.7</v>
+        <v>15.1</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="J40" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K40" t="n">
-        <v>90.97</v>
+        <v>93.55</v>
       </c>
       <c r="L40" t="n">
-        <v>93.34999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>87.03</v>
+        <v>92.81</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6422</v>
+        <v>6417</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
@@ -2955,42 +2955,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.39</v>
+        <v>16.57</v>
       </c>
       <c r="C41" t="n">
-        <v>17.59</v>
+        <v>16.97</v>
       </c>
       <c r="D41" t="n">
-        <v>17.17</v>
+        <v>16.32</v>
       </c>
       <c r="E41" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="J41" t="n">
-        <v>0.31</v>
+        <v>0.12</v>
       </c>
       <c r="K41" t="n">
-        <v>79.91</v>
+        <v>90.97</v>
       </c>
       <c r="L41" t="n">
-        <v>84</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>77.81999999999999</v>
+        <v>87.03</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2999,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3017,20 +3017,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.82</v>
+        <v>17.39</v>
       </c>
       <c r="C42" t="n">
-        <v>17.99</v>
+        <v>17.59</v>
       </c>
       <c r="D42" t="n">
-        <v>17.64</v>
+        <v>17.17</v>
       </c>
       <c r="E42" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F42" t="n">
         <v>13.5</v>
@@ -3040,19 +3040,19 @@
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="K42" t="n">
-        <v>77.5</v>
+        <v>79.91</v>
       </c>
       <c r="L42" t="n">
-        <v>79.29000000000001</v>
+        <v>84</v>
       </c>
       <c r="M42" t="n">
-        <v>76.37</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3061,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -3079,42 +3079,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.13</v>
+        <v>17.82</v>
       </c>
       <c r="C43" t="n">
-        <v>18.3</v>
+        <v>17.99</v>
       </c>
       <c r="D43" t="n">
-        <v>17.82</v>
+        <v>17.64</v>
       </c>
       <c r="E43" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="F43" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="J43" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="K43" t="n">
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
       <c r="L43" t="n">
-        <v>81.88</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>74.38</v>
+        <v>76.37</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3123,10 +3123,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
         <v>3</v>
@@ -3141,42 +3141,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.85</v>
+        <v>18.13</v>
       </c>
       <c r="C44" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="D44" t="n">
-        <v>17.67</v>
+        <v>17.82</v>
       </c>
       <c r="E44" t="n">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
       <c r="F44" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="J44" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="K44" t="n">
-        <v>80.95</v>
+        <v>76.5</v>
       </c>
       <c r="L44" t="n">
-        <v>82.98</v>
+        <v>81.88</v>
       </c>
       <c r="M44" t="n">
-        <v>77.86</v>
+        <v>74.38</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3185,13 +3185,13 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6434</v>
+        <v>6428</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -3203,42 +3203,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18.69</v>
+        <v>17.85</v>
       </c>
       <c r="C45" t="n">
-        <v>19.09</v>
+        <v>18.1</v>
       </c>
       <c r="D45" t="n">
-        <v>18.24</v>
+        <v>17.67</v>
       </c>
       <c r="E45" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="F45" t="n">
-        <v>13</v>
+        <v>14.1</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="J45" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="K45" t="n">
-        <v>71.91</v>
+        <v>80.95</v>
       </c>
       <c r="L45" t="n">
-        <v>75.81999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="M45" t="n">
-        <v>68.15000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3247,16 +3247,16 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -3265,60 +3265,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 19:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.36</v>
+        <v>18.69</v>
       </c>
       <c r="C46" t="n">
-        <v>19.58</v>
+        <v>19.09</v>
       </c>
       <c r="D46" t="n">
-        <v>19.06</v>
+        <v>18.24</v>
       </c>
       <c r="E46" t="n">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="F46" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G46" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="K46" t="n">
-        <v>66.34999999999999</v>
+        <v>71.91</v>
       </c>
       <c r="L46" t="n">
-        <v>69.37</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>63.92</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6465</v>
+        <v>6440</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
         <v>4</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -3327,51 +3327,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.82</v>
+        <v>19.36</v>
       </c>
       <c r="C47" t="n">
-        <v>20.22</v>
+        <v>19.58</v>
       </c>
       <c r="D47" t="n">
-        <v>19.58</v>
+        <v>19.06</v>
       </c>
       <c r="E47" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F47" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="G47" t="n">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="J47" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="K47" t="n">
-        <v>64.69</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>67.25</v>
+        <v>69.37</v>
       </c>
       <c r="M47" t="n">
-        <v>63.16</v>
+        <v>63.92</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3944</v>
+        <v>1620</v>
       </c>
       <c r="P47" t="n">
-        <v>6511</v>
+        <v>6465</v>
       </c>
       <c r="Q47" t="n">
         <v>4</v>
@@ -3383,119 +3383,119 @@
         <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.77</v>
+        <v>19.82</v>
       </c>
       <c r="C48" t="n">
-        <v>20.09</v>
+        <v>20.22</v>
       </c>
       <c r="D48" t="n">
-        <v>19.54</v>
+        <v>19.58</v>
       </c>
       <c r="E48" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="F48" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="G48" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="K48" t="n">
-        <v>66.33</v>
+        <v>64.69</v>
       </c>
       <c r="L48" t="n">
-        <v>68.87</v>
+        <v>67.25</v>
       </c>
       <c r="M48" t="n">
-        <v>61.21</v>
+        <v>63.16</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6671</v>
+        <v>3944</v>
       </c>
       <c r="P48" t="n">
-        <v>6539</v>
+        <v>6511</v>
       </c>
       <c r="Q48" t="n">
         <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.58</v>
+        <v>19.77</v>
       </c>
       <c r="C49" t="n">
-        <v>19.95</v>
+        <v>20.09</v>
       </c>
       <c r="D49" t="n">
-        <v>19.38</v>
+        <v>19.54</v>
       </c>
       <c r="E49" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="F49" t="n">
         <v>12.2</v>
       </c>
       <c r="G49" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="J49" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="K49" t="n">
-        <v>65.27</v>
+        <v>66.33</v>
       </c>
       <c r="L49" t="n">
-        <v>67.09999999999999</v>
+        <v>68.87</v>
       </c>
       <c r="M49" t="n">
-        <v>61.34</v>
+        <v>61.21</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6389</v>
+        <v>6671</v>
       </c>
       <c r="P49" t="n">
-        <v>6534</v>
+        <v>6539</v>
       </c>
       <c r="Q49" t="n">
         <v>4</v>
@@ -3507,7 +3507,7 @@
         <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,246 +533,246 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.46</v>
+        <v>20.57</v>
       </c>
       <c r="C2" t="n">
-        <v>23.17</v>
+        <v>20.67</v>
       </c>
       <c r="D2" t="n">
-        <v>21.82</v>
+        <v>20.48</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="F2" t="n">
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
       <c r="G2" t="n">
-        <v>383</v>
+        <v>24</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1.29</v>
+        <v>0.86</v>
       </c>
       <c r="J2" t="n">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="K2" t="n">
-        <v>52.56</v>
+        <v>64.16</v>
       </c>
       <c r="L2" t="n">
-        <v>54.35</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>50.6</v>
+        <v>63.43</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6763</v>
+        <v>2008</v>
       </c>
       <c r="P2" t="n">
-        <v>6593</v>
+        <v>6511</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.1</v>
+        <v>21.22</v>
       </c>
       <c r="C3" t="n">
-        <v>22.92</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="n">
-        <v>21.76</v>
+        <v>20.76</v>
       </c>
       <c r="E3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>479</v>
+        <v>73</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1.23</v>
+        <v>0.99</v>
       </c>
       <c r="J3" t="n">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="K3" t="n">
-        <v>53.58</v>
+        <v>60.52</v>
       </c>
       <c r="L3" t="n">
-        <v>55.95</v>
+        <v>62.17</v>
       </c>
       <c r="M3" t="n">
-        <v>51.48</v>
+        <v>58.42</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6739</v>
+        <v>2990</v>
       </c>
       <c r="P3" t="n">
-        <v>6582</v>
+        <v>6516</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.45</v>
+        <v>21.62</v>
       </c>
       <c r="C4" t="n">
-        <v>22.62</v>
+        <v>21.84</v>
       </c>
       <c r="D4" t="n">
-        <v>20.83</v>
+        <v>21.44</v>
       </c>
       <c r="E4" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="G4" t="n">
-        <v>640</v>
+        <v>137</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>56.35</v>
+        <v>58.13</v>
       </c>
       <c r="L4" t="n">
-        <v>62.61</v>
+        <v>60.32</v>
       </c>
       <c r="M4" t="n">
-        <v>51.88</v>
+        <v>56.76</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6810</v>
+        <v>5684</v>
       </c>
       <c r="P4" t="n">
-        <v>6610</v>
+        <v>6548</v>
       </c>
       <c r="Q4" t="n">
         <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.67</v>
+        <v>21.96</v>
       </c>
       <c r="C5" t="n">
-        <v>20.85</v>
+        <v>22.41</v>
       </c>
       <c r="D5" t="n">
-        <v>19.11</v>
+        <v>21.77</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="F5" t="n">
-        <v>12.9</v>
+        <v>12.2</v>
       </c>
       <c r="G5" t="n">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="K5" t="n">
-        <v>66.39</v>
+        <v>55.95</v>
       </c>
       <c r="L5" t="n">
-        <v>68.68000000000001</v>
+        <v>57.92</v>
       </c>
       <c r="M5" t="n">
-        <v>61.4</v>
+        <v>54.15</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6772</v>
+        <v>6619</v>
       </c>
       <c r="P5" t="n">
-        <v>6571</v>
+        <v>6573</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
         <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
@@ -781,122 +781,122 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.92</v>
+        <v>22.46</v>
       </c>
       <c r="C6" t="n">
-        <v>19.22</v>
+        <v>23.17</v>
       </c>
       <c r="D6" t="n">
-        <v>18.64</v>
+        <v>21.82</v>
       </c>
       <c r="E6" t="n">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="F6" t="n">
-        <v>13.2</v>
+        <v>11.6</v>
       </c>
       <c r="G6" t="n">
-        <v>143</v>
+        <v>383</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.62</v>
+        <v>1.29</v>
       </c>
       <c r="J6" t="n">
-        <v>0.58</v>
+        <v>1.21</v>
       </c>
       <c r="K6" t="n">
-        <v>71.48999999999999</v>
+        <v>52.56</v>
       </c>
       <c r="L6" t="n">
-        <v>73.28</v>
+        <v>54.35</v>
       </c>
       <c r="M6" t="n">
-        <v>69.45</v>
+        <v>50.6</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6254</v>
+        <v>6763</v>
       </c>
       <c r="P6" t="n">
-        <v>6508</v>
+        <v>6593</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.78</v>
+        <v>22.1</v>
       </c>
       <c r="C7" t="n">
-        <v>18.89</v>
+        <v>22.92</v>
       </c>
       <c r="D7" t="n">
-        <v>18.67</v>
+        <v>21.76</v>
       </c>
       <c r="E7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F7" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="G7" t="n">
-        <v>134</v>
+        <v>479</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.63</v>
+        <v>1.23</v>
       </c>
       <c r="J7" t="n">
-        <v>0.57</v>
+        <v>1.14</v>
       </c>
       <c r="K7" t="n">
-        <v>70.87</v>
+        <v>53.58</v>
       </c>
       <c r="L7" t="n">
-        <v>73.17</v>
+        <v>55.95</v>
       </c>
       <c r="M7" t="n">
-        <v>68.48</v>
+        <v>51.48</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5929</v>
+        <v>6739</v>
       </c>
       <c r="P7" t="n">
-        <v>6494</v>
+        <v>6582</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
@@ -905,60 +905,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.59</v>
+        <v>21.45</v>
       </c>
       <c r="C8" t="n">
-        <v>19.26</v>
+        <v>22.62</v>
       </c>
       <c r="D8" t="n">
-        <v>18.18</v>
+        <v>20.83</v>
       </c>
       <c r="E8" t="n">
-        <v>14.3</v>
+        <v>12.3</v>
       </c>
       <c r="F8" t="n">
-        <v>13.8</v>
+        <v>11.1</v>
       </c>
       <c r="G8" t="n">
-        <v>205</v>
+        <v>640</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41</v>
+        <v>0.92</v>
       </c>
       <c r="K8" t="n">
-        <v>76.48999999999999</v>
+        <v>56.35</v>
       </c>
       <c r="L8" t="n">
-        <v>80.08</v>
+        <v>62.61</v>
       </c>
       <c r="M8" t="n">
-        <v>71.70999999999999</v>
+        <v>51.88</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5478</v>
+        <v>6810</v>
       </c>
       <c r="P8" t="n">
-        <v>6494</v>
+        <v>6610</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
@@ -967,60 +967,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.89</v>
+        <v>19.67</v>
       </c>
       <c r="C9" t="n">
-        <v>18.29</v>
+        <v>20.85</v>
       </c>
       <c r="D9" t="n">
-        <v>17.02</v>
+        <v>19.11</v>
       </c>
       <c r="E9" t="n">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
       <c r="F9" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="G9" t="n">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.35</v>
+        <v>0.77</v>
       </c>
       <c r="J9" t="n">
-        <v>0.24</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>82.51000000000001</v>
+        <v>66.39</v>
       </c>
       <c r="L9" t="n">
-        <v>87.40000000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>79.09999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6633</v>
+        <v>6772</v>
       </c>
       <c r="P9" t="n">
-        <v>6488</v>
+        <v>6571</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -1029,239 +1029,237 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.49</v>
+        <v>18.92</v>
       </c>
       <c r="C10" t="n">
-        <v>16.79</v>
+        <v>19.22</v>
       </c>
       <c r="D10" t="n">
-        <v>16.31</v>
+        <v>18.64</v>
       </c>
       <c r="E10" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="F10" t="n">
-        <v>14.2</v>
+        <v>13.2</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.62</v>
       </c>
       <c r="J10" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="K10" t="n">
-        <v>89.09</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>91.65000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="M10" t="n">
-        <v>87.73</v>
+        <v>69.45</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5349</v>
+        <v>6254</v>
       </c>
       <c r="P10" t="n">
-        <v>6445</v>
+        <v>6508</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.27</v>
+        <v>18.78</v>
       </c>
       <c r="C11" t="n">
-        <v>16.31</v>
+        <v>18.89</v>
       </c>
       <c r="D11" t="n">
-        <v>16.24</v>
+        <v>18.67</v>
       </c>
       <c r="E11" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="F11" t="n">
-        <v>14.4</v>
+        <v>12.8</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.18</v>
+        <v>0.63</v>
       </c>
       <c r="J11" t="n">
-        <v>0.15</v>
+        <v>0.57</v>
       </c>
       <c r="K11" t="n">
-        <v>90.12</v>
+        <v>70.87</v>
       </c>
       <c r="L11" t="n">
-        <v>91.63</v>
+        <v>73.17</v>
       </c>
       <c r="M11" t="n">
-        <v>88.84</v>
+        <v>68.48</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5929</v>
       </c>
       <c r="P11" t="n">
-        <v>6422</v>
+        <v>6494</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.37</v>
+        <v>18.59</v>
       </c>
       <c r="C12" t="n">
-        <v>16.42</v>
+        <v>19.26</v>
       </c>
       <c r="D12" t="n">
-        <v>16.3</v>
+        <v>18.18</v>
       </c>
       <c r="E12" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F12" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="K12" t="n">
-        <v>88.97</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>90.09</v>
+        <v>80.08</v>
       </c>
       <c r="M12" t="n">
-        <v>88.26000000000001</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="P12" t="n">
-        <v>6414</v>
+        <v>6494</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.35</v>
+        <v>17.89</v>
       </c>
       <c r="C13" t="n">
-        <v>16.36</v>
+        <v>18.29</v>
       </c>
       <c r="D13" t="n">
-        <v>16.35</v>
+        <v>17.02</v>
       </c>
       <c r="E13" t="n">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="F13" t="n">
-        <v>13.6</v>
+        <v>14.3</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2592</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="J13" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="K13" t="n">
-        <v>84.98</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>85.65000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>84.31</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P13" t="n">
-        <v>6425</v>
+        <v>6488</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -1273,68 +1271,66 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.33</v>
+        <v>16.49</v>
       </c>
       <c r="C14" t="n">
-        <v>16.56</v>
+        <v>16.79</v>
       </c>
       <c r="D14" t="n">
-        <v>15.86</v>
+        <v>16.31</v>
       </c>
       <c r="E14" t="n">
         <v>14.6</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2522</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K14" t="n">
-        <v>89.8</v>
+        <v>89.09</v>
       </c>
       <c r="L14" t="n">
-        <v>99.73</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>85.27</v>
+        <v>87.73</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P14" t="n">
-        <v>6422</v>
+        <v>6445</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1343,42 +1339,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>16.27</v>
       </c>
       <c r="C15" t="n">
-        <v>16.37</v>
+        <v>16.31</v>
       </c>
       <c r="D15" t="n">
-        <v>16.2</v>
+        <v>16.24</v>
       </c>
       <c r="E15" t="n">
         <v>14.6</v>
       </c>
       <c r="F15" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="J15" t="n">
         <v>0.15</v>
       </c>
       <c r="K15" t="n">
-        <v>90.44</v>
+        <v>90.12</v>
       </c>
       <c r="L15" t="n">
-        <v>91.61</v>
+        <v>91.63</v>
       </c>
       <c r="M15" t="n">
-        <v>89.09999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1387,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -1405,42 +1401,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.26</v>
+        <v>16.37</v>
       </c>
       <c r="C16" t="n">
-        <v>16.49</v>
+        <v>16.42</v>
       </c>
       <c r="D16" t="n">
-        <v>16.14</v>
+        <v>16.3</v>
       </c>
       <c r="E16" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F16" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="K16" t="n">
-        <v>90.33</v>
+        <v>88.97</v>
       </c>
       <c r="L16" t="n">
-        <v>91.40000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="M16" t="n">
-        <v>89.20999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1449,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -1467,42 +1463,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.61</v>
+        <v>16.35</v>
       </c>
       <c r="C17" t="n">
-        <v>16.82</v>
+        <v>16.36</v>
       </c>
       <c r="D17" t="n">
-        <v>16.45</v>
+        <v>16.35</v>
       </c>
       <c r="E17" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="F17" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>2592</v>
+      </c>
       <c r="I17" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="J17" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="K17" t="n">
-        <v>87.3</v>
+        <v>84.98</v>
       </c>
       <c r="L17" t="n">
-        <v>89.45</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>86.06</v>
+        <v>84.31</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1511,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -1529,42 +1527,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.92</v>
+        <v>16.33</v>
       </c>
       <c r="C18" t="n">
-        <v>17.22</v>
+        <v>16.56</v>
       </c>
       <c r="D18" t="n">
-        <v>16.72</v>
+        <v>15.86</v>
       </c>
       <c r="E18" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F18" t="n">
         <v>14</v>
       </c>
-      <c r="F18" t="n">
-        <v>13.8</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>2522</v>
+      </c>
       <c r="I18" t="n">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="J18" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>83.48999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="L18" t="n">
-        <v>85.67</v>
+        <v>99.73</v>
       </c>
       <c r="M18" t="n">
-        <v>80.43000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1573,16 +1573,16 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6465</v>
+        <v>6422</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -1591,42 +1591,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.37</v>
+        <v>16.27</v>
       </c>
       <c r="C19" t="n">
-        <v>17.64</v>
+        <v>16.37</v>
       </c>
       <c r="D19" t="n">
-        <v>17.15</v>
+        <v>16.2</v>
       </c>
       <c r="E19" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F19" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="J19" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="K19" t="n">
-        <v>81.5</v>
+        <v>90.44</v>
       </c>
       <c r="L19" t="n">
-        <v>83.2</v>
+        <v>91.61</v>
       </c>
       <c r="M19" t="n">
-        <v>79.69</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1635,16 +1635,16 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6471</v>
+        <v>6417</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -1653,42 +1653,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.37</v>
+        <v>16.26</v>
       </c>
       <c r="C20" t="n">
-        <v>17.71</v>
+        <v>16.49</v>
       </c>
       <c r="D20" t="n">
-        <v>17.16</v>
+        <v>16.14</v>
       </c>
       <c r="E20" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="J20" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="K20" t="n">
-        <v>83.11</v>
+        <v>90.33</v>
       </c>
       <c r="L20" t="n">
-        <v>85.31</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>78.94</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1697,16 +1697,16 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6474</v>
+        <v>6425</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -1715,17 +1715,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.78</v>
+        <v>16.61</v>
       </c>
       <c r="C21" t="n">
-        <v>18.2</v>
+        <v>16.82</v>
       </c>
       <c r="D21" t="n">
-        <v>17.44</v>
+        <v>16.45</v>
       </c>
       <c r="E21" t="n">
         <v>14.4</v>
@@ -1738,19 +1738,19 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="J21" t="n">
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="K21" t="n">
-        <v>81.01000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="L21" t="n">
-        <v>82.84999999999999</v>
+        <v>89.45</v>
       </c>
       <c r="M21" t="n">
-        <v>78.13</v>
+        <v>86.06</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1759,16 +1759,16 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6494</v>
+        <v>6434</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -1777,42 +1777,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18.91</v>
+        <v>16.92</v>
       </c>
       <c r="C22" t="n">
-        <v>19.32</v>
+        <v>17.22</v>
       </c>
       <c r="D22" t="n">
-        <v>18.33</v>
+        <v>16.72</v>
       </c>
       <c r="E22" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="J22" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
       <c r="K22" t="n">
-        <v>72.89</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>76.66</v>
+        <v>85.67</v>
       </c>
       <c r="M22" t="n">
-        <v>67.31</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1821,16 +1821,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6496</v>
+        <v>6465</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -1839,60 +1839,60 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.65</v>
+        <v>17.37</v>
       </c>
       <c r="C23" t="n">
-        <v>19.86</v>
+        <v>17.64</v>
       </c>
       <c r="D23" t="n">
-        <v>19.37</v>
+        <v>17.15</v>
       </c>
       <c r="E23" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="F23" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="J23" t="n">
-        <v>0.65</v>
+        <v>0.33</v>
       </c>
       <c r="K23" t="n">
-        <v>69.28</v>
+        <v>81.5</v>
       </c>
       <c r="L23" t="n">
-        <v>71.03</v>
+        <v>83.2</v>
       </c>
       <c r="M23" t="n">
-        <v>67.26000000000001</v>
+        <v>79.69</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6511</v>
+        <v>6471</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -1901,60 +1901,60 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.34</v>
+        <v>17.37</v>
       </c>
       <c r="C24" t="n">
-        <v>19.5</v>
+        <v>17.71</v>
       </c>
       <c r="D24" t="n">
-        <v>19.25</v>
+        <v>17.16</v>
       </c>
       <c r="E24" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="F24" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.68</v>
+        <v>0.33</v>
       </c>
       <c r="J24" t="n">
-        <v>0.67</v>
+        <v>0.28</v>
       </c>
       <c r="K24" t="n">
-        <v>69.37</v>
+        <v>83.11</v>
       </c>
       <c r="L24" t="n">
-        <v>70.14</v>
+        <v>85.31</v>
       </c>
       <c r="M24" t="n">
-        <v>68.55</v>
+        <v>78.94</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6536</v>
+        <v>6474</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -1963,364 +1963,364 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.29</v>
+        <v>17.78</v>
       </c>
       <c r="C25" t="n">
-        <v>19.86</v>
+        <v>18.2</v>
       </c>
       <c r="D25" t="n">
-        <v>19.1</v>
+        <v>17.44</v>
       </c>
       <c r="E25" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="F25" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="G25" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="J25" t="n">
-        <v>0.66</v>
+        <v>0.34</v>
       </c>
       <c r="K25" t="n">
-        <v>68.94</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>69.94</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>66.66</v>
+        <v>78.13</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4462</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6539</v>
+        <v>6494</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.82</v>
+        <v>18.91</v>
       </c>
       <c r="C26" t="n">
-        <v>21.19</v>
+        <v>19.32</v>
       </c>
       <c r="D26" t="n">
-        <v>19.8</v>
+        <v>18.33</v>
       </c>
       <c r="E26" t="n">
-        <v>12.3</v>
+        <v>13.9</v>
       </c>
       <c r="F26" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="G26" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>1.02</v>
+        <v>0.59</v>
       </c>
       <c r="J26" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="K26" t="n">
-        <v>58.55</v>
+        <v>72.89</v>
       </c>
       <c r="L26" t="n">
-        <v>67.09</v>
+        <v>76.66</v>
       </c>
       <c r="M26" t="n">
-        <v>55.27</v>
+        <v>67.31</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6579</v>
+        <v>6496</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.17</v>
+        <v>19.65</v>
       </c>
       <c r="C27" t="n">
-        <v>21.41</v>
+        <v>19.86</v>
       </c>
       <c r="D27" t="n">
-        <v>20.87</v>
+        <v>19.37</v>
       </c>
       <c r="E27" t="n">
-        <v>12.3</v>
+        <v>13.8</v>
       </c>
       <c r="F27" t="n">
-        <v>11.8</v>
+        <v>13.5</v>
       </c>
       <c r="G27" t="n">
-        <v>419</v>
+        <v>55</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="K27" t="n">
-        <v>57.42</v>
+        <v>69.28</v>
       </c>
       <c r="L27" t="n">
-        <v>60.15</v>
+        <v>71.03</v>
       </c>
       <c r="M27" t="n">
-        <v>55.34</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6777</v>
+        <v>2267</v>
       </c>
       <c r="P27" t="n">
-        <v>6613</v>
+        <v>6511</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21.2</v>
+        <v>19.34</v>
       </c>
       <c r="C28" t="n">
-        <v>21.55</v>
+        <v>19.5</v>
       </c>
       <c r="D28" t="n">
-        <v>20.85</v>
+        <v>19.25</v>
       </c>
       <c r="E28" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="F28" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
       <c r="G28" t="n">
-        <v>629</v>
+        <v>67</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>1.04</v>
+        <v>0.68</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="K28" t="n">
-        <v>58.56</v>
+        <v>69.37</v>
       </c>
       <c r="L28" t="n">
-        <v>61.5</v>
+        <v>70.14</v>
       </c>
       <c r="M28" t="n">
-        <v>56.2</v>
+        <v>68.55</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6849</v>
+        <v>4721</v>
       </c>
       <c r="P28" t="n">
-        <v>6647</v>
+        <v>6536</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20.75</v>
+        <v>19.29</v>
       </c>
       <c r="C29" t="n">
-        <v>21.44</v>
+        <v>19.86</v>
       </c>
       <c r="D29" t="n">
-        <v>20.1</v>
+        <v>19.1</v>
       </c>
       <c r="E29" t="n">
-        <v>12.6</v>
+        <v>13.4</v>
       </c>
       <c r="F29" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="G29" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="K29" t="n">
-        <v>59.8</v>
+        <v>68.94</v>
       </c>
       <c r="L29" t="n">
-        <v>61.83</v>
+        <v>69.94</v>
       </c>
       <c r="M29" t="n">
-        <v>58.57</v>
+        <v>66.66</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6901</v>
+        <v>4462</v>
       </c>
       <c r="P29" t="n">
-        <v>6676</v>
+        <v>6539</v>
       </c>
       <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
         <v>5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20.11</v>
+        <v>20.82</v>
       </c>
       <c r="C30" t="n">
-        <v>21.09</v>
+        <v>21.19</v>
       </c>
       <c r="D30" t="n">
-        <v>19.18</v>
+        <v>19.8</v>
       </c>
       <c r="E30" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F30" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
       <c r="G30" t="n">
-        <v>471</v>
+        <v>215</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="J30" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="K30" t="n">
-        <v>63.63</v>
+        <v>58.55</v>
       </c>
       <c r="L30" t="n">
-        <v>67.22</v>
+        <v>67.09</v>
       </c>
       <c r="M30" t="n">
-        <v>59.39</v>
+        <v>55.27</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6810</v>
+        <v>6250</v>
       </c>
       <c r="P30" t="n">
-        <v>6613</v>
+        <v>6579</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
         <v>5</v>
@@ -2335,60 +2335,60 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>21.17</v>
       </c>
       <c r="C31" t="n">
-        <v>19.69</v>
+        <v>21.41</v>
       </c>
       <c r="D31" t="n">
-        <v>18.97</v>
+        <v>20.87</v>
       </c>
       <c r="E31" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G31" t="n">
-        <v>300</v>
+        <v>419</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="J31" t="n">
-        <v>0.65</v>
+        <v>0.99</v>
       </c>
       <c r="K31" t="n">
-        <v>66.97</v>
+        <v>57.42</v>
       </c>
       <c r="L31" t="n">
-        <v>70.23999999999999</v>
+        <v>60.15</v>
       </c>
       <c r="M31" t="n">
-        <v>65.22</v>
+        <v>55.34</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6681</v>
+        <v>6777</v>
       </c>
       <c r="P31" t="n">
-        <v>6565</v>
+        <v>6613</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
         <v>60</v>
@@ -2397,60 +2397,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18.64</v>
+        <v>21.2</v>
       </c>
       <c r="C32" t="n">
-        <v>20.12</v>
+        <v>21.55</v>
       </c>
       <c r="D32" t="n">
-        <v>17.71</v>
+        <v>20.85</v>
       </c>
       <c r="E32" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="F32" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="G32" t="n">
-        <v>347</v>
+        <v>629</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.61</v>
+        <v>1.04</v>
       </c>
       <c r="J32" t="n">
-        <v>0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>71.42</v>
+        <v>58.56</v>
       </c>
       <c r="L32" t="n">
-        <v>76.48</v>
+        <v>61.5</v>
       </c>
       <c r="M32" t="n">
-        <v>66.62</v>
+        <v>56.2</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6739</v>
+        <v>6849</v>
       </c>
       <c r="P32" t="n">
-        <v>6565</v>
+        <v>6647</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="n">
         <v>60</v>
@@ -2459,370 +2459,370 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.37</v>
+        <v>20.75</v>
       </c>
       <c r="C33" t="n">
-        <v>18.2</v>
+        <v>21.44</v>
       </c>
       <c r="D33" t="n">
-        <v>16.67</v>
+        <v>20.1</v>
       </c>
       <c r="E33" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="F33" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="G33" t="n">
-        <v>167</v>
+        <v>612</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="J33" t="n">
-        <v>0.26</v>
+        <v>0.9</v>
       </c>
       <c r="K33" t="n">
-        <v>79.89</v>
+        <v>59.8</v>
       </c>
       <c r="L33" t="n">
-        <v>86.01000000000001</v>
+        <v>61.83</v>
       </c>
       <c r="M33" t="n">
-        <v>75.15000000000001</v>
+        <v>58.57</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6499</v>
+        <v>6901</v>
       </c>
       <c r="P33" t="n">
-        <v>6494</v>
+        <v>6676</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15.89</v>
+        <v>20.11</v>
       </c>
       <c r="C34" t="n">
-        <v>16.51</v>
+        <v>21.09</v>
       </c>
       <c r="D34" t="n">
-        <v>15.53</v>
+        <v>19.18</v>
       </c>
       <c r="E34" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="F34" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>471</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.14</v>
+        <v>0.85</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1</v>
+        <v>0.72</v>
       </c>
       <c r="K34" t="n">
-        <v>91.95</v>
+        <v>63.63</v>
       </c>
       <c r="L34" t="n">
-        <v>93.86</v>
+        <v>67.22</v>
       </c>
       <c r="M34" t="n">
-        <v>87.84999999999999</v>
+        <v>59.39</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4793</v>
+        <v>6810</v>
       </c>
       <c r="P34" t="n">
-        <v>6442</v>
+        <v>6613</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.63</v>
+        <v>19.28</v>
       </c>
       <c r="C35" t="n">
-        <v>15.72</v>
+        <v>19.69</v>
       </c>
       <c r="D35" t="n">
-        <v>15.55</v>
+        <v>18.97</v>
       </c>
       <c r="E35" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="F35" t="n">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.13</v>
+        <v>0.73</v>
       </c>
       <c r="J35" t="n">
-        <v>0.11</v>
+        <v>0.65</v>
       </c>
       <c r="K35" t="n">
-        <v>92.23</v>
+        <v>66.97</v>
       </c>
       <c r="L35" t="n">
-        <v>93.61</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>90.98</v>
+        <v>65.22</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>6681</v>
       </c>
       <c r="P35" t="n">
-        <v>6417</v>
+        <v>6565</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.65</v>
+        <v>18.64</v>
       </c>
       <c r="C36" t="n">
-        <v>15.76</v>
+        <v>20.12</v>
       </c>
       <c r="D36" t="n">
-        <v>15.53</v>
+        <v>17.71</v>
       </c>
       <c r="E36" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="F36" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.11</v>
+        <v>0.61</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="K36" t="n">
-        <v>93.44</v>
+        <v>71.42</v>
       </c>
       <c r="L36" t="n">
-        <v>93.83</v>
+        <v>76.48</v>
       </c>
       <c r="M36" t="n">
-        <v>92.88</v>
+        <v>66.62</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>6739</v>
       </c>
       <c r="P36" t="n">
-        <v>6405</v>
+        <v>6565</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.63</v>
+        <v>17.37</v>
       </c>
       <c r="C37" t="n">
-        <v>15.74</v>
+        <v>18.2</v>
       </c>
       <c r="D37" t="n">
-        <v>15.57</v>
+        <v>16.67</v>
       </c>
       <c r="E37" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
       <c r="F37" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="K37" t="n">
-        <v>94.87</v>
+        <v>79.89</v>
       </c>
       <c r="L37" t="n">
-        <v>95.69</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>93.40000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>6499</v>
       </c>
       <c r="P37" t="n">
-        <v>6414</v>
+        <v>6494</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>15.74</v>
+        <v>15.89</v>
       </c>
       <c r="C38" t="n">
-        <v>15.95</v>
+        <v>16.51</v>
       </c>
       <c r="D38" t="n">
-        <v>15.62</v>
+        <v>15.53</v>
       </c>
       <c r="E38" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="F38" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="J38" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="K38" t="n">
-        <v>95.13</v>
+        <v>91.95</v>
       </c>
       <c r="L38" t="n">
-        <v>96.19</v>
+        <v>93.86</v>
       </c>
       <c r="M38" t="n">
-        <v>94.28</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4793</v>
       </c>
       <c r="P38" t="n">
-        <v>6422</v>
+        <v>6442</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -2831,42 +2831,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.02</v>
+        <v>15.63</v>
       </c>
       <c r="C39" t="n">
-        <v>16.13</v>
+        <v>15.72</v>
       </c>
       <c r="D39" t="n">
-        <v>15.96</v>
+        <v>15.55</v>
       </c>
       <c r="E39" t="n">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="F39" t="n">
-        <v>14.9</v>
+        <v>14.2</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="J39" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="K39" t="n">
-        <v>94.3</v>
+        <v>92.23</v>
       </c>
       <c r="L39" t="n">
-        <v>94.76000000000001</v>
+        <v>93.61</v>
       </c>
       <c r="M39" t="n">
-        <v>93.61</v>
+        <v>90.98</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -2884,7 +2884,7 @@
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -2893,23 +2893,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.24</v>
+        <v>15.65</v>
       </c>
       <c r="C40" t="n">
-        <v>16.32</v>
+        <v>15.76</v>
       </c>
       <c r="D40" t="n">
-        <v>16.16</v>
+        <v>15.53</v>
       </c>
       <c r="E40" t="n">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="F40" t="n">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2922,13 +2922,13 @@
         <v>0.1</v>
       </c>
       <c r="K40" t="n">
-        <v>93.55</v>
+        <v>93.44</v>
       </c>
       <c r="L40" t="n">
-        <v>94.40000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="M40" t="n">
-        <v>92.81</v>
+        <v>92.88</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6417</v>
+        <v>6405</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
@@ -2955,42 +2955,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.57</v>
+        <v>15.63</v>
       </c>
       <c r="C41" t="n">
-        <v>16.97</v>
+        <v>15.74</v>
       </c>
       <c r="D41" t="n">
-        <v>16.32</v>
+        <v>15.57</v>
       </c>
       <c r="E41" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F41" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="J41" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>90.97</v>
+        <v>94.87</v>
       </c>
       <c r="L41" t="n">
-        <v>93.34999999999999</v>
+        <v>95.69</v>
       </c>
       <c r="M41" t="n">
-        <v>87.03</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2999,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3017,42 +3017,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.39</v>
+        <v>15.74</v>
       </c>
       <c r="C42" t="n">
-        <v>17.59</v>
+        <v>15.95</v>
       </c>
       <c r="D42" t="n">
-        <v>17.17</v>
+        <v>15.62</v>
       </c>
       <c r="E42" t="n">
-        <v>13.8</v>
+        <v>14.9</v>
       </c>
       <c r="F42" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="J42" t="n">
-        <v>0.31</v>
+        <v>0.06</v>
       </c>
       <c r="K42" t="n">
-        <v>79.91</v>
+        <v>95.13</v>
       </c>
       <c r="L42" t="n">
-        <v>84</v>
+        <v>96.19</v>
       </c>
       <c r="M42" t="n">
-        <v>77.81999999999999</v>
+        <v>94.28</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3061,16 +3061,16 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -3079,42 +3079,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.82</v>
+        <v>16.02</v>
       </c>
       <c r="C43" t="n">
-        <v>17.99</v>
+        <v>16.13</v>
       </c>
       <c r="D43" t="n">
-        <v>17.64</v>
+        <v>15.96</v>
       </c>
       <c r="E43" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="J43" t="n">
-        <v>0.42</v>
+        <v>0.09</v>
       </c>
       <c r="K43" t="n">
-        <v>77.5</v>
+        <v>94.3</v>
       </c>
       <c r="L43" t="n">
-        <v>79.29000000000001</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>76.37</v>
+        <v>93.61</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3141,42 +3141,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.13</v>
+        <v>16.24</v>
       </c>
       <c r="C44" t="n">
-        <v>18.3</v>
+        <v>16.32</v>
       </c>
       <c r="D44" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="E44" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="F44" t="n">
-        <v>13.4</v>
+        <v>15.1</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.48</v>
+        <v>0.11</v>
       </c>
       <c r="J44" t="n">
-        <v>0.36</v>
+        <v>0.1</v>
       </c>
       <c r="K44" t="n">
-        <v>76.5</v>
+        <v>93.55</v>
       </c>
       <c r="L44" t="n">
-        <v>81.88</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>74.38</v>
+        <v>92.81</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3185,16 +3185,16 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6428</v>
+        <v>6417</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -3203,42 +3203,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.85</v>
+        <v>16.57</v>
       </c>
       <c r="C45" t="n">
-        <v>18.1</v>
+        <v>16.97</v>
       </c>
       <c r="D45" t="n">
-        <v>17.67</v>
+        <v>16.32</v>
       </c>
       <c r="E45" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>14.1</v>
+        <v>14.7</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="J45" t="n">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="K45" t="n">
-        <v>80.95</v>
+        <v>90.97</v>
       </c>
       <c r="L45" t="n">
-        <v>82.98</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>77.86</v>
+        <v>87.03</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3247,16 +3247,16 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6434</v>
+        <v>6422</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -3265,42 +3265,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 19:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18.69</v>
+        <v>17.39</v>
       </c>
       <c r="C46" t="n">
-        <v>19.09</v>
+        <v>17.59</v>
       </c>
       <c r="D46" t="n">
-        <v>18.24</v>
+        <v>17.17</v>
       </c>
       <c r="E46" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="K46" t="n">
-        <v>71.91</v>
+        <v>79.91</v>
       </c>
       <c r="L46" t="n">
-        <v>75.81999999999999</v>
+        <v>84</v>
       </c>
       <c r="M46" t="n">
-        <v>68.15000000000001</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3309,16 +3309,16 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6440</v>
+        <v>6417</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -3327,60 +3327,60 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.36</v>
+        <v>17.82</v>
       </c>
       <c r="C47" t="n">
-        <v>19.58</v>
+        <v>17.99</v>
       </c>
       <c r="D47" t="n">
-        <v>19.06</v>
+        <v>17.64</v>
       </c>
       <c r="E47" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="F47" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="G47" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="J47" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="K47" t="n">
-        <v>66.34999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="L47" t="n">
-        <v>69.37</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>63.92</v>
+        <v>76.37</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -3389,125 +3389,125 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.82</v>
+        <v>18.13</v>
       </c>
       <c r="C48" t="n">
-        <v>20.22</v>
+        <v>18.3</v>
       </c>
       <c r="D48" t="n">
-        <v>19.58</v>
+        <v>17.82</v>
       </c>
       <c r="E48" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="F48" t="n">
-        <v>12.6</v>
+        <v>13.4</v>
       </c>
       <c r="G48" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="J48" t="n">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="K48" t="n">
-        <v>64.69</v>
+        <v>76.5</v>
       </c>
       <c r="L48" t="n">
-        <v>67.25</v>
+        <v>81.88</v>
       </c>
       <c r="M48" t="n">
-        <v>63.16</v>
+        <v>74.38</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3944</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6511</v>
+        <v>6428</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.77</v>
+        <v>17.85</v>
       </c>
       <c r="C49" t="n">
-        <v>20.09</v>
+        <v>18.1</v>
       </c>
       <c r="D49" t="n">
-        <v>19.54</v>
+        <v>17.67</v>
       </c>
       <c r="E49" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
       <c r="F49" t="n">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
       <c r="G49" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.77</v>
+        <v>0.38</v>
       </c>
       <c r="J49" t="n">
-        <v>0.71</v>
+        <v>0.34</v>
       </c>
       <c r="K49" t="n">
-        <v>66.33</v>
+        <v>80.95</v>
       </c>
       <c r="L49" t="n">
-        <v>68.87</v>
+        <v>82.98</v>
       </c>
       <c r="M49" t="n">
-        <v>61.21</v>
+        <v>77.86</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6671</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6539</v>
+        <v>6434</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T49" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,60 +533,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.57</v>
+        <v>18.42</v>
       </c>
       <c r="C2" t="n">
-        <v>20.67</v>
+        <v>18.45</v>
       </c>
       <c r="D2" t="n">
-        <v>20.48</v>
+        <v>18.39</v>
       </c>
       <c r="E2" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="F2" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.86</v>
+        <v>0.41</v>
       </c>
       <c r="J2" t="n">
-        <v>0.83</v>
+        <v>0.41</v>
       </c>
       <c r="K2" t="n">
-        <v>64.16</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>65.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>63.43</v>
+        <v>79.83</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2008</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6511</v>
+        <v>6479</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -595,299 +595,299 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.22</v>
+        <v>18.81</v>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>19.07</v>
       </c>
       <c r="D3" t="n">
-        <v>20.76</v>
+        <v>18.51</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.99</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="K3" t="n">
-        <v>60.52</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>62.17</v>
+        <v>79.87</v>
       </c>
       <c r="M3" t="n">
-        <v>58.42</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6516</v>
+        <v>6482</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.62</v>
+        <v>19.81</v>
       </c>
       <c r="C4" t="n">
-        <v>21.84</v>
+        <v>20.67</v>
       </c>
       <c r="D4" t="n">
-        <v>21.44</v>
+        <v>18.96</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7</v>
+        <v>13.4</v>
       </c>
       <c r="G4" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>0.54</v>
       </c>
       <c r="K4" t="n">
-        <v>58.13</v>
+        <v>69.16</v>
       </c>
       <c r="L4" t="n">
-        <v>60.32</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>56.76</v>
+        <v>63.43</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>6548</v>
+        <v>6496</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.96</v>
+        <v>21.22</v>
       </c>
       <c r="C5" t="n">
-        <v>22.41</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="n">
-        <v>21.77</v>
+        <v>20.76</v>
       </c>
       <c r="E5" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="F5" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="K5" t="n">
-        <v>55.95</v>
+        <v>60.52</v>
       </c>
       <c r="L5" t="n">
-        <v>57.92</v>
+        <v>62.17</v>
       </c>
       <c r="M5" t="n">
-        <v>54.15</v>
+        <v>58.42</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6619</v>
+        <v>2990</v>
       </c>
       <c r="P5" t="n">
-        <v>6573</v>
+        <v>6516</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.46</v>
+        <v>21.62</v>
       </c>
       <c r="C6" t="n">
-        <v>23.17</v>
+        <v>21.84</v>
       </c>
       <c r="D6" t="n">
-        <v>21.82</v>
+        <v>21.44</v>
       </c>
       <c r="E6" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G6" t="n">
-        <v>383</v>
+        <v>137</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>52.56</v>
+        <v>58.13</v>
       </c>
       <c r="L6" t="n">
-        <v>54.35</v>
+        <v>60.32</v>
       </c>
       <c r="M6" t="n">
-        <v>50.6</v>
+        <v>56.76</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6763</v>
+        <v>5684</v>
       </c>
       <c r="P6" t="n">
-        <v>6593</v>
+        <v>6548</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.1</v>
+        <v>21.96</v>
       </c>
       <c r="C7" t="n">
-        <v>22.92</v>
+        <v>22.41</v>
       </c>
       <c r="D7" t="n">
-        <v>21.76</v>
+        <v>21.77</v>
       </c>
       <c r="E7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F7" t="n">
         <v>12.2</v>
       </c>
-      <c r="F7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G7" t="n">
-        <v>479</v>
+        <v>205</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="J7" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="K7" t="n">
-        <v>53.58</v>
+        <v>55.95</v>
       </c>
       <c r="L7" t="n">
-        <v>55.95</v>
+        <v>57.92</v>
       </c>
       <c r="M7" t="n">
-        <v>51.48</v>
+        <v>54.15</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6739</v>
+        <v>6619</v>
       </c>
       <c r="P7" t="n">
-        <v>6582</v>
+        <v>6573</v>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
@@ -905,60 +905,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.45</v>
+        <v>22.46</v>
       </c>
       <c r="C8" t="n">
-        <v>22.62</v>
+        <v>23.17</v>
       </c>
       <c r="D8" t="n">
-        <v>20.83</v>
+        <v>21.82</v>
       </c>
       <c r="E8" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F8" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G8" t="n">
-        <v>640</v>
+        <v>383</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="J8" t="n">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="K8" t="n">
-        <v>56.35</v>
+        <v>52.56</v>
       </c>
       <c r="L8" t="n">
-        <v>62.61</v>
+        <v>54.35</v>
       </c>
       <c r="M8" t="n">
-        <v>51.88</v>
+        <v>50.6</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6810</v>
+        <v>6763</v>
       </c>
       <c r="P8" t="n">
-        <v>6610</v>
+        <v>6593</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
         <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
@@ -967,60 +967,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.67</v>
+        <v>22.1</v>
       </c>
       <c r="C9" t="n">
-        <v>20.85</v>
+        <v>22.92</v>
       </c>
       <c r="D9" t="n">
-        <v>19.11</v>
+        <v>21.76</v>
       </c>
       <c r="E9" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F9" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>279</v>
+        <v>479</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.77</v>
+        <v>1.23</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="K9" t="n">
-        <v>66.39</v>
+        <v>53.58</v>
       </c>
       <c r="L9" t="n">
-        <v>68.68000000000001</v>
+        <v>55.95</v>
       </c>
       <c r="M9" t="n">
-        <v>61.4</v>
+        <v>51.48</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6772</v>
+        <v>6739</v>
       </c>
       <c r="P9" t="n">
-        <v>6571</v>
+        <v>6582</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
         <v>5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -1029,122 +1029,122 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18.92</v>
+        <v>21.45</v>
       </c>
       <c r="C10" t="n">
-        <v>19.22</v>
+        <v>22.62</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64</v>
+        <v>20.83</v>
       </c>
       <c r="E10" t="n">
-        <v>13.6</v>
+        <v>12.3</v>
       </c>
       <c r="F10" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="G10" t="n">
-        <v>143</v>
+        <v>640</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="K10" t="n">
-        <v>71.48999999999999</v>
+        <v>56.35</v>
       </c>
       <c r="L10" t="n">
-        <v>73.28</v>
+        <v>62.61</v>
       </c>
       <c r="M10" t="n">
-        <v>69.45</v>
+        <v>51.88</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6254</v>
+        <v>6810</v>
       </c>
       <c r="P10" t="n">
-        <v>6508</v>
+        <v>6610</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18.78</v>
+        <v>19.67</v>
       </c>
       <c r="C11" t="n">
-        <v>18.89</v>
+        <v>20.85</v>
       </c>
       <c r="D11" t="n">
-        <v>18.67</v>
+        <v>19.11</v>
       </c>
       <c r="E11" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F11" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="G11" t="n">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="J11" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>70.87</v>
+        <v>66.39</v>
       </c>
       <c r="L11" t="n">
-        <v>73.17</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>68.48</v>
+        <v>61.4</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5929</v>
+        <v>6772</v>
       </c>
       <c r="P11" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
         <v>4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>60</v>
@@ -1153,51 +1153,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.59</v>
+        <v>18.92</v>
       </c>
       <c r="C12" t="n">
-        <v>19.26</v>
+        <v>19.22</v>
       </c>
       <c r="D12" t="n">
-        <v>18.18</v>
+        <v>18.64</v>
       </c>
       <c r="E12" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="F12" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G12" t="n">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="J12" t="n">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
       <c r="K12" t="n">
-        <v>76.48999999999999</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>80.08</v>
+        <v>73.28</v>
       </c>
       <c r="M12" t="n">
-        <v>71.70999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5478</v>
+        <v>6254</v>
       </c>
       <c r="P12" t="n">
-        <v>6494</v>
+        <v>6508</v>
       </c>
       <c r="Q12" t="n">
         <v>3</v>
@@ -1206,69 +1206,69 @@
         <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.89</v>
+        <v>18.78</v>
       </c>
       <c r="C13" t="n">
-        <v>18.29</v>
+        <v>18.89</v>
       </c>
       <c r="D13" t="n">
-        <v>17.02</v>
+        <v>18.67</v>
       </c>
       <c r="E13" t="n">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="F13" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="G13" t="n">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="J13" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="K13" t="n">
-        <v>82.51000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="L13" t="n">
-        <v>87.40000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="M13" t="n">
-        <v>79.09999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6633</v>
+        <v>5929</v>
       </c>
       <c r="P13" t="n">
-        <v>6488</v>
+        <v>6494</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
@@ -1277,175 +1277,175 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.49</v>
+        <v>18.59</v>
       </c>
       <c r="C14" t="n">
-        <v>16.79</v>
+        <v>19.26</v>
       </c>
       <c r="D14" t="n">
-        <v>16.31</v>
+        <v>18.18</v>
       </c>
       <c r="E14" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F14" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="G14" t="n">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="K14" t="n">
-        <v>89.09</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>91.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M14" t="n">
-        <v>87.73</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5349</v>
+        <v>5478</v>
       </c>
       <c r="P14" t="n">
-        <v>6445</v>
+        <v>6494</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.27</v>
+        <v>17.89</v>
       </c>
       <c r="C15" t="n">
-        <v>16.31</v>
+        <v>18.29</v>
       </c>
       <c r="D15" t="n">
-        <v>16.24</v>
+        <v>17.02</v>
       </c>
       <c r="E15" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F15" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="J15" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="K15" t="n">
-        <v>90.12</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>91.63</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>88.84</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P15" t="n">
-        <v>6422</v>
+        <v>6488</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.37</v>
+        <v>16.49</v>
       </c>
       <c r="C16" t="n">
-        <v>16.42</v>
+        <v>16.79</v>
       </c>
       <c r="D16" t="n">
-        <v>16.3</v>
+        <v>16.31</v>
       </c>
       <c r="E16" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F16" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>0.2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="K16" t="n">
-        <v>88.97</v>
+        <v>89.09</v>
       </c>
       <c r="L16" t="n">
-        <v>90.09</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>88.26000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P16" t="n">
-        <v>6414</v>
+        <v>6445</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -1463,44 +1463,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.35</v>
+        <v>16.27</v>
       </c>
       <c r="C17" t="n">
-        <v>16.36</v>
+        <v>16.31</v>
       </c>
       <c r="D17" t="n">
-        <v>16.35</v>
+        <v>16.24</v>
       </c>
       <c r="E17" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="F17" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="n">
-        <v>2592</v>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="J17" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="K17" t="n">
-        <v>84.98</v>
+        <v>90.12</v>
       </c>
       <c r="L17" t="n">
-        <v>85.65000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="M17" t="n">
-        <v>84.31</v>
+        <v>88.84</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1509,13 +1507,13 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -1527,44 +1525,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.33</v>
+        <v>16.37</v>
       </c>
       <c r="C18" t="n">
-        <v>16.56</v>
+        <v>16.42</v>
       </c>
       <c r="D18" t="n">
-        <v>15.86</v>
+        <v>16.3</v>
       </c>
       <c r="E18" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="n">
-        <v>2522</v>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K18" t="n">
-        <v>89.8</v>
+        <v>88.97</v>
       </c>
       <c r="L18" t="n">
-        <v>99.73</v>
+        <v>90.09</v>
       </c>
       <c r="M18" t="n">
-        <v>85.27</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1573,16 +1569,16 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -1591,42 +1587,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.27</v>
+        <v>16.35</v>
       </c>
       <c r="C19" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="D19" t="n">
-        <v>16.2</v>
+        <v>16.35</v>
       </c>
       <c r="E19" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F19" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>2592</v>
+      </c>
       <c r="I19" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="J19" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K19" t="n">
-        <v>90.44</v>
+        <v>84.98</v>
       </c>
       <c r="L19" t="n">
-        <v>91.61</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>89.09999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1635,13 +1633,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -1653,42 +1651,44 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.26</v>
+        <v>16.33</v>
       </c>
       <c r="C20" t="n">
-        <v>16.49</v>
+        <v>16.56</v>
       </c>
       <c r="D20" t="n">
-        <v>16.14</v>
+        <v>15.86</v>
       </c>
       <c r="E20" t="n">
         <v>14.6</v>
       </c>
       <c r="F20" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>2522</v>
+      </c>
       <c r="I20" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J20" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>90.33</v>
+        <v>89.8</v>
       </c>
       <c r="L20" t="n">
-        <v>91.40000000000001</v>
+        <v>99.73</v>
       </c>
       <c r="M20" t="n">
-        <v>89.20999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1697,16 +1697,16 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -1715,42 +1715,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.61</v>
+        <v>16.27</v>
       </c>
       <c r="C21" t="n">
-        <v>16.82</v>
+        <v>16.37</v>
       </c>
       <c r="D21" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="E21" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F21" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="J21" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K21" t="n">
-        <v>87.3</v>
+        <v>90.44</v>
       </c>
       <c r="L21" t="n">
-        <v>89.45</v>
+        <v>91.61</v>
       </c>
       <c r="M21" t="n">
-        <v>86.06</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6434</v>
+        <v>6417</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
@@ -1777,42 +1777,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.92</v>
+        <v>16.26</v>
       </c>
       <c r="C22" t="n">
-        <v>17.22</v>
+        <v>16.49</v>
       </c>
       <c r="D22" t="n">
-        <v>16.72</v>
+        <v>16.14</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F22" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="J22" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="K22" t="n">
-        <v>83.48999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="L22" t="n">
-        <v>85.67</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>80.43000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1821,16 +1821,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -1839,42 +1839,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.37</v>
+        <v>16.61</v>
       </c>
       <c r="C23" t="n">
-        <v>17.64</v>
+        <v>16.82</v>
       </c>
       <c r="D23" t="n">
-        <v>17.15</v>
+        <v>16.45</v>
       </c>
       <c r="E23" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="F23" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="J23" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="K23" t="n">
-        <v>81.5</v>
+        <v>87.3</v>
       </c>
       <c r="L23" t="n">
-        <v>83.2</v>
+        <v>89.45</v>
       </c>
       <c r="M23" t="n">
-        <v>79.69</v>
+        <v>86.06</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1883,16 +1883,16 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6471</v>
+        <v>6434</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -1901,42 +1901,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.37</v>
+        <v>16.92</v>
       </c>
       <c r="C24" t="n">
-        <v>17.71</v>
+        <v>17.22</v>
       </c>
       <c r="D24" t="n">
-        <v>17.16</v>
+        <v>16.72</v>
       </c>
       <c r="E24" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J24" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="K24" t="n">
-        <v>83.11</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>85.31</v>
+        <v>85.67</v>
       </c>
       <c r="M24" t="n">
-        <v>78.94</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6474</v>
+        <v>6465</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -1963,42 +1963,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.78</v>
+        <v>17.37</v>
       </c>
       <c r="C25" t="n">
-        <v>18.2</v>
+        <v>17.64</v>
       </c>
       <c r="D25" t="n">
-        <v>17.44</v>
+        <v>17.15</v>
       </c>
       <c r="E25" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="F25" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="J25" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="K25" t="n">
-        <v>81.01000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="L25" t="n">
-        <v>82.84999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="M25" t="n">
-        <v>78.13</v>
+        <v>79.69</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6494</v>
+        <v>6471</v>
       </c>
       <c r="Q25" t="n">
         <v>2</v>
@@ -2025,42 +2025,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.91</v>
+        <v>17.37</v>
       </c>
       <c r="C26" t="n">
-        <v>19.32</v>
+        <v>17.71</v>
       </c>
       <c r="D26" t="n">
-        <v>18.33</v>
+        <v>17.16</v>
       </c>
       <c r="E26" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="F26" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="J26" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="K26" t="n">
-        <v>72.89</v>
+        <v>83.11</v>
       </c>
       <c r="L26" t="n">
-        <v>76.66</v>
+        <v>85.31</v>
       </c>
       <c r="M26" t="n">
-        <v>67.31</v>
+        <v>78.94</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2069,16 +2069,16 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6496</v>
+        <v>6474</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2087,60 +2087,60 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.65</v>
+        <v>17.78</v>
       </c>
       <c r="C27" t="n">
-        <v>19.86</v>
+        <v>18.2</v>
       </c>
       <c r="D27" t="n">
-        <v>19.37</v>
+        <v>17.44</v>
       </c>
       <c r="E27" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="F27" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="G27" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="J27" t="n">
-        <v>0.65</v>
+        <v>0.34</v>
       </c>
       <c r="K27" t="n">
-        <v>69.28</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>71.03</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>67.26000000000001</v>
+        <v>78.13</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6511</v>
+        <v>6494</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2149,54 +2149,54 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.34</v>
+        <v>18.91</v>
       </c>
       <c r="C28" t="n">
-        <v>19.5</v>
+        <v>19.32</v>
       </c>
       <c r="D28" t="n">
-        <v>19.25</v>
+        <v>18.33</v>
       </c>
       <c r="E28" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="F28" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="G28" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="J28" t="n">
-        <v>0.67</v>
+        <v>0.49</v>
       </c>
       <c r="K28" t="n">
-        <v>69.37</v>
+        <v>72.89</v>
       </c>
       <c r="L28" t="n">
-        <v>70.14</v>
+        <v>76.66</v>
       </c>
       <c r="M28" t="n">
-        <v>68.55</v>
+        <v>67.31</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6536</v>
+        <v>6496</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
         <v>4</v>
@@ -2211,51 +2211,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.29</v>
+        <v>19.65</v>
       </c>
       <c r="C29" t="n">
         <v>19.86</v>
       </c>
       <c r="D29" t="n">
-        <v>19.1</v>
+        <v>19.37</v>
       </c>
       <c r="E29" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="F29" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="G29" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="K29" t="n">
-        <v>68.94</v>
+        <v>69.28</v>
       </c>
       <c r="L29" t="n">
-        <v>69.94</v>
+        <v>71.03</v>
       </c>
       <c r="M29" t="n">
-        <v>66.66</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4462</v>
+        <v>2267</v>
       </c>
       <c r="P29" t="n">
-        <v>6539</v>
+        <v>6511</v>
       </c>
       <c r="Q29" t="n">
         <v>4</v>
@@ -2267,181 +2267,181 @@
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20.82</v>
+        <v>19.34</v>
       </c>
       <c r="C30" t="n">
-        <v>21.19</v>
+        <v>19.5</v>
       </c>
       <c r="D30" t="n">
-        <v>19.8</v>
+        <v>19.25</v>
       </c>
       <c r="E30" t="n">
-        <v>12.3</v>
+        <v>13.5</v>
       </c>
       <c r="F30" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
       <c r="G30" t="n">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="J30" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="K30" t="n">
-        <v>58.55</v>
+        <v>69.37</v>
       </c>
       <c r="L30" t="n">
-        <v>67.09</v>
+        <v>70.14</v>
       </c>
       <c r="M30" t="n">
-        <v>55.27</v>
+        <v>68.55</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6250</v>
+        <v>4721</v>
       </c>
       <c r="P30" t="n">
-        <v>6579</v>
+        <v>6536</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.17</v>
+        <v>19.29</v>
       </c>
       <c r="C31" t="n">
-        <v>21.41</v>
+        <v>19.86</v>
       </c>
       <c r="D31" t="n">
-        <v>20.87</v>
+        <v>19.1</v>
       </c>
       <c r="E31" t="n">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="F31" t="n">
-        <v>11.8</v>
+        <v>13.3</v>
       </c>
       <c r="G31" t="n">
-        <v>419</v>
+        <v>68</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.99</v>
+        <v>0.66</v>
       </c>
       <c r="K31" t="n">
-        <v>57.42</v>
+        <v>68.94</v>
       </c>
       <c r="L31" t="n">
-        <v>60.15</v>
+        <v>69.94</v>
       </c>
       <c r="M31" t="n">
-        <v>55.34</v>
+        <v>66.66</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6777</v>
+        <v>4462</v>
       </c>
       <c r="P31" t="n">
-        <v>6613</v>
+        <v>6539</v>
       </c>
       <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="n">
         <v>5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21.2</v>
+        <v>20.82</v>
       </c>
       <c r="C32" t="n">
-        <v>21.55</v>
+        <v>21.19</v>
       </c>
       <c r="D32" t="n">
-        <v>20.85</v>
+        <v>19.8</v>
       </c>
       <c r="E32" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F32" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="G32" t="n">
-        <v>629</v>
+        <v>215</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K32" t="n">
-        <v>58.56</v>
+        <v>58.55</v>
       </c>
       <c r="L32" t="n">
-        <v>61.5</v>
+        <v>67.09</v>
       </c>
       <c r="M32" t="n">
-        <v>56.2</v>
+        <v>55.27</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6849</v>
+        <v>6250</v>
       </c>
       <c r="P32" t="n">
-        <v>6647</v>
+        <v>6579</v>
       </c>
       <c r="Q32" t="n">
         <v>5</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
         <v>60</v>
@@ -2459,51 +2459,51 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.75</v>
+        <v>21.17</v>
       </c>
       <c r="C33" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
       <c r="D33" t="n">
-        <v>20.1</v>
+        <v>20.87</v>
       </c>
       <c r="E33" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F33" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="G33" t="n">
-        <v>612</v>
+        <v>419</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="K33" t="n">
-        <v>59.8</v>
+        <v>57.42</v>
       </c>
       <c r="L33" t="n">
-        <v>61.83</v>
+        <v>60.15</v>
       </c>
       <c r="M33" t="n">
-        <v>58.57</v>
+        <v>55.34</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6901</v>
+        <v>6777</v>
       </c>
       <c r="P33" t="n">
-        <v>6676</v>
+        <v>6613</v>
       </c>
       <c r="Q33" t="n">
         <v>5</v>
@@ -2521,60 +2521,60 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20.11</v>
+        <v>21.2</v>
       </c>
       <c r="C34" t="n">
-        <v>21.09</v>
+        <v>21.55</v>
       </c>
       <c r="D34" t="n">
-        <v>19.18</v>
+        <v>20.85</v>
       </c>
       <c r="E34" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F34" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G34" t="n">
-        <v>471</v>
+        <v>629</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="J34" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>63.63</v>
+        <v>58.56</v>
       </c>
       <c r="L34" t="n">
-        <v>67.22</v>
+        <v>61.5</v>
       </c>
       <c r="M34" t="n">
-        <v>59.39</v>
+        <v>56.2</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6810</v>
+        <v>6849</v>
       </c>
       <c r="P34" t="n">
-        <v>6613</v>
+        <v>6647</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
         <v>5</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
         <v>60</v>
@@ -2583,60 +2583,60 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.28</v>
+        <v>20.75</v>
       </c>
       <c r="C35" t="n">
-        <v>19.69</v>
+        <v>21.44</v>
       </c>
       <c r="D35" t="n">
-        <v>18.97</v>
+        <v>20.1</v>
       </c>
       <c r="E35" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F35" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G35" t="n">
-        <v>300</v>
+        <v>612</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="J35" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="K35" t="n">
-        <v>66.97</v>
+        <v>59.8</v>
       </c>
       <c r="L35" t="n">
-        <v>70.23999999999999</v>
+        <v>61.83</v>
       </c>
       <c r="M35" t="n">
-        <v>65.22</v>
+        <v>58.57</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6681</v>
+        <v>6901</v>
       </c>
       <c r="P35" t="n">
-        <v>6565</v>
+        <v>6676</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
         <v>60</v>
@@ -2645,60 +2645,60 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18.64</v>
+        <v>20.11</v>
       </c>
       <c r="C36" t="n">
-        <v>20.12</v>
+        <v>21.09</v>
       </c>
       <c r="D36" t="n">
-        <v>17.71</v>
+        <v>19.18</v>
       </c>
       <c r="E36" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="F36" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="G36" t="n">
-        <v>347</v>
+        <v>471</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="J36" t="n">
-        <v>0.48</v>
+        <v>0.72</v>
       </c>
       <c r="K36" t="n">
-        <v>71.42</v>
+        <v>63.63</v>
       </c>
       <c r="L36" t="n">
-        <v>76.48</v>
+        <v>67.22</v>
       </c>
       <c r="M36" t="n">
-        <v>66.62</v>
+        <v>59.39</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6739</v>
+        <v>6810</v>
       </c>
       <c r="P36" t="n">
-        <v>6565</v>
+        <v>6613</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
+        <v>5</v>
+      </c>
+      <c r="S36" t="n">
         <v>4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
       </c>
       <c r="T36" t="n">
         <v>60</v>
@@ -2707,200 +2707,200 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.37</v>
+        <v>19.28</v>
       </c>
       <c r="C37" t="n">
-        <v>18.2</v>
+        <v>19.69</v>
       </c>
       <c r="D37" t="n">
-        <v>16.67</v>
+        <v>18.97</v>
       </c>
       <c r="E37" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="F37" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="G37" t="n">
-        <v>167</v>
+        <v>300</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="J37" t="n">
-        <v>0.26</v>
+        <v>0.65</v>
       </c>
       <c r="K37" t="n">
-        <v>79.89</v>
+        <v>66.97</v>
       </c>
       <c r="L37" t="n">
-        <v>86.01000000000001</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>75.15000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6499</v>
+        <v>6681</v>
       </c>
       <c r="P37" t="n">
-        <v>6494</v>
+        <v>6565</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
       <c r="T37" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>15.89</v>
+        <v>18.64</v>
       </c>
       <c r="C38" t="n">
-        <v>16.51</v>
+        <v>20.12</v>
       </c>
       <c r="D38" t="n">
-        <v>15.53</v>
+        <v>17.71</v>
       </c>
       <c r="E38" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="F38" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="G38" t="n">
-        <v>40</v>
+        <v>347</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.14</v>
+        <v>0.61</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="K38" t="n">
-        <v>91.95</v>
+        <v>71.42</v>
       </c>
       <c r="L38" t="n">
-        <v>93.86</v>
+        <v>76.48</v>
       </c>
       <c r="M38" t="n">
-        <v>87.84999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4793</v>
+        <v>6739</v>
       </c>
       <c r="P38" t="n">
-        <v>6442</v>
+        <v>6565</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15.63</v>
+        <v>17.37</v>
       </c>
       <c r="C39" t="n">
-        <v>15.72</v>
+        <v>18.2</v>
       </c>
       <c r="D39" t="n">
-        <v>15.55</v>
+        <v>16.67</v>
       </c>
       <c r="E39" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="F39" t="n">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="K39" t="n">
-        <v>92.23</v>
+        <v>79.89</v>
       </c>
       <c r="L39" t="n">
-        <v>93.61</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>90.98</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>6499</v>
       </c>
       <c r="P39" t="n">
-        <v>6417</v>
+        <v>6494</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15.65</v>
+        <v>15.89</v>
       </c>
       <c r="C40" t="n">
-        <v>15.76</v>
+        <v>16.51</v>
       </c>
       <c r="D40" t="n">
         <v>15.53</v>
@@ -2909,35 +2909,35 @@
         <v>14.5</v>
       </c>
       <c r="F40" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="J40" t="n">
         <v>0.1</v>
       </c>
       <c r="K40" t="n">
-        <v>93.44</v>
+        <v>91.95</v>
       </c>
       <c r="L40" t="n">
-        <v>93.83</v>
+        <v>93.86</v>
       </c>
       <c r="M40" t="n">
-        <v>92.88</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4793</v>
       </c>
       <c r="P40" t="n">
-        <v>6405</v>
+        <v>6442</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
@@ -2955,42 +2955,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>15.63</v>
       </c>
       <c r="C41" t="n">
-        <v>15.74</v>
+        <v>15.72</v>
       </c>
       <c r="D41" t="n">
-        <v>15.57</v>
+        <v>15.55</v>
       </c>
       <c r="E41" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="F41" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="J41" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="K41" t="n">
-        <v>94.87</v>
+        <v>92.23</v>
       </c>
       <c r="L41" t="n">
-        <v>95.69</v>
+        <v>93.61</v>
       </c>
       <c r="M41" t="n">
-        <v>93.40000000000001</v>
+        <v>90.98</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2999,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3017,42 +3017,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.74</v>
+        <v>15.65</v>
       </c>
       <c r="C42" t="n">
-        <v>15.95</v>
+        <v>15.76</v>
       </c>
       <c r="D42" t="n">
-        <v>15.62</v>
+        <v>15.53</v>
       </c>
       <c r="E42" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="F42" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J42" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="K42" t="n">
-        <v>95.13</v>
+        <v>93.44</v>
       </c>
       <c r="L42" t="n">
-        <v>96.19</v>
+        <v>93.83</v>
       </c>
       <c r="M42" t="n">
-        <v>94.28</v>
+        <v>92.88</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3061,16 +3061,16 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6422</v>
+        <v>6405</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -3079,42 +3079,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.02</v>
+        <v>15.63</v>
       </c>
       <c r="C43" t="n">
-        <v>16.13</v>
+        <v>15.74</v>
       </c>
       <c r="D43" t="n">
-        <v>15.96</v>
+        <v>15.57</v>
       </c>
       <c r="E43" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F43" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J43" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>94.3</v>
+        <v>94.87</v>
       </c>
       <c r="L43" t="n">
-        <v>94.76000000000001</v>
+        <v>95.69</v>
       </c>
       <c r="M43" t="n">
-        <v>93.61</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>6414</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -3141,42 +3141,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.24</v>
+        <v>15.74</v>
       </c>
       <c r="C44" t="n">
-        <v>16.32</v>
+        <v>15.95</v>
       </c>
       <c r="D44" t="n">
-        <v>16.16</v>
+        <v>15.62</v>
       </c>
       <c r="E44" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="F44" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="K44" t="n">
-        <v>93.55</v>
+        <v>95.13</v>
       </c>
       <c r="L44" t="n">
-        <v>94.40000000000001</v>
+        <v>96.19</v>
       </c>
       <c r="M44" t="n">
-        <v>92.81</v>
+        <v>94.28</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3185,16 +3185,16 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -3203,42 +3203,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.57</v>
+        <v>16.02</v>
       </c>
       <c r="C45" t="n">
-        <v>16.97</v>
+        <v>16.13</v>
       </c>
       <c r="D45" t="n">
-        <v>16.32</v>
+        <v>15.96</v>
       </c>
       <c r="E45" t="n">
         <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="K45" t="n">
-        <v>90.97</v>
+        <v>94.3</v>
       </c>
       <c r="L45" t="n">
-        <v>93.34999999999999</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>87.03</v>
+        <v>93.61</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -3256,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -3265,42 +3265,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.39</v>
+        <v>16.24</v>
       </c>
       <c r="C46" t="n">
-        <v>17.59</v>
+        <v>16.32</v>
       </c>
       <c r="D46" t="n">
-        <v>17.17</v>
+        <v>16.16</v>
       </c>
       <c r="E46" t="n">
-        <v>13.8</v>
+        <v>15.1</v>
       </c>
       <c r="F46" t="n">
-        <v>13.5</v>
+        <v>15.1</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.11</v>
       </c>
       <c r="J46" t="n">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="K46" t="n">
-        <v>79.91</v>
+        <v>93.55</v>
       </c>
       <c r="L46" t="n">
-        <v>84</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>77.81999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>6417</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -3327,42 +3327,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.82</v>
+        <v>16.57</v>
       </c>
       <c r="C47" t="n">
-        <v>17.99</v>
+        <v>16.97</v>
       </c>
       <c r="D47" t="n">
-        <v>17.64</v>
+        <v>16.32</v>
       </c>
       <c r="E47" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.45</v>
+        <v>0.16</v>
       </c>
       <c r="J47" t="n">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="K47" t="n">
-        <v>77.5</v>
+        <v>90.97</v>
       </c>
       <c r="L47" t="n">
-        <v>79.29000000000001</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>76.37</v>
+        <v>87.03</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3371,16 +3371,16 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -3389,42 +3389,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.13</v>
+        <v>17.39</v>
       </c>
       <c r="C48" t="n">
-        <v>18.3</v>
+        <v>17.59</v>
       </c>
       <c r="D48" t="n">
-        <v>17.82</v>
+        <v>17.17</v>
       </c>
       <c r="E48" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F48" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="K48" t="n">
-        <v>76.5</v>
+        <v>79.91</v>
       </c>
       <c r="L48" t="n">
-        <v>81.88</v>
+        <v>84</v>
       </c>
       <c r="M48" t="n">
-        <v>74.38</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3433,13 +3433,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6428</v>
+        <v>6417</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -3451,42 +3451,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.85</v>
+        <v>17.82</v>
       </c>
       <c r="C49" t="n">
-        <v>18.1</v>
+        <v>17.99</v>
       </c>
       <c r="D49" t="n">
-        <v>17.67</v>
+        <v>17.64</v>
       </c>
       <c r="E49" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="F49" t="n">
-        <v>14.1</v>
+        <v>13.5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="J49" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="K49" t="n">
-        <v>80.95</v>
+        <v>77.5</v>
       </c>
       <c r="L49" t="n">
-        <v>82.98</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>77.86</v>
+        <v>76.37</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3495,13 +3495,13 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S49" t="n">
         <v>2</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,42 +533,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.42</v>
+        <v>17.92</v>
       </c>
       <c r="C2" t="n">
-        <v>18.45</v>
+        <v>18.06</v>
       </c>
       <c r="D2" t="n">
-        <v>18.39</v>
+        <v>17.79</v>
       </c>
       <c r="E2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
         <v>14.9</v>
-      </c>
-      <c r="F2" t="n">
-        <v>14.8</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="K2" t="n">
-        <v>80.23999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="L2" t="n">
-        <v>80.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="M2" t="n">
-        <v>79.83</v>
+        <v>81.95</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6479</v>
+        <v>6462</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
@@ -595,42 +595,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.81</v>
+        <v>18.36</v>
       </c>
       <c r="C3" t="n">
-        <v>19.07</v>
+        <v>18.45</v>
       </c>
       <c r="D3" t="n">
-        <v>18.51</v>
+        <v>18.19</v>
       </c>
       <c r="E3" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="F3" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="K3" t="n">
-        <v>76.59999999999999</v>
+        <v>80.73</v>
       </c>
       <c r="L3" t="n">
-        <v>79.87</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>74.01000000000001</v>
+        <v>79.83</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -639,13 +639,13 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6482</v>
+        <v>6471</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -657,42 +657,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.81</v>
+        <v>18.81</v>
       </c>
       <c r="C4" t="n">
-        <v>20.67</v>
+        <v>19.07</v>
       </c>
       <c r="D4" t="n">
-        <v>18.96</v>
+        <v>18.51</v>
       </c>
       <c r="E4" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="F4" t="n">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="K4" t="n">
-        <v>69.16</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>75.04000000000001</v>
+        <v>79.87</v>
       </c>
       <c r="M4" t="n">
-        <v>63.43</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>6496</v>
+        <v>6482</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -719,113 +719,113 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.22</v>
+        <v>19.81</v>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>20.67</v>
       </c>
       <c r="D5" t="n">
-        <v>20.76</v>
+        <v>18.96</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="G5" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
       <c r="J5" t="n">
-        <v>0.93</v>
+        <v>0.54</v>
       </c>
       <c r="K5" t="n">
-        <v>60.52</v>
+        <v>69.16</v>
       </c>
       <c r="L5" t="n">
-        <v>62.17</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>58.42</v>
+        <v>63.43</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6516</v>
+        <v>6496</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.62</v>
+        <v>21.22</v>
       </c>
       <c r="C6" t="n">
-        <v>21.84</v>
+        <v>21.6</v>
       </c>
       <c r="D6" t="n">
-        <v>21.44</v>
+        <v>20.76</v>
       </c>
       <c r="E6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F6" t="n">
         <v>13</v>
       </c>
-      <c r="F6" t="n">
-        <v>12.7</v>
-      </c>
       <c r="G6" t="n">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>0.93</v>
       </c>
       <c r="K6" t="n">
-        <v>58.13</v>
+        <v>60.52</v>
       </c>
       <c r="L6" t="n">
-        <v>60.32</v>
+        <v>62.17</v>
       </c>
       <c r="M6" t="n">
-        <v>56.76</v>
+        <v>58.42</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5684</v>
+        <v>2990</v>
       </c>
       <c r="P6" t="n">
-        <v>6548</v>
+        <v>6516</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
@@ -837,119 +837,119 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.96</v>
+        <v>21.62</v>
       </c>
       <c r="C7" t="n">
-        <v>22.41</v>
+        <v>21.84</v>
       </c>
       <c r="D7" t="n">
-        <v>21.77</v>
+        <v>21.44</v>
       </c>
       <c r="E7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" t="n">
         <v>12.7</v>
       </c>
-      <c r="F7" t="n">
-        <v>12.2</v>
-      </c>
       <c r="G7" t="n">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>55.95</v>
+        <v>58.13</v>
       </c>
       <c r="L7" t="n">
-        <v>57.92</v>
+        <v>60.32</v>
       </c>
       <c r="M7" t="n">
-        <v>54.15</v>
+        <v>56.76</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6619</v>
+        <v>5684</v>
       </c>
       <c r="P7" t="n">
-        <v>6573</v>
+        <v>6548</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.46</v>
+        <v>21.96</v>
       </c>
       <c r="C8" t="n">
-        <v>23.17</v>
+        <v>22.41</v>
       </c>
       <c r="D8" t="n">
-        <v>21.82</v>
+        <v>21.77</v>
       </c>
       <c r="E8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F8" t="n">
         <v>12.2</v>
       </c>
-      <c r="F8" t="n">
-        <v>11.6</v>
-      </c>
       <c r="G8" t="n">
-        <v>383</v>
+        <v>205</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="J8" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="K8" t="n">
-        <v>52.56</v>
+        <v>55.95</v>
       </c>
       <c r="L8" t="n">
-        <v>54.35</v>
+        <v>57.92</v>
       </c>
       <c r="M8" t="n">
-        <v>50.6</v>
+        <v>54.15</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6763</v>
+        <v>6619</v>
       </c>
       <c r="P8" t="n">
-        <v>6593</v>
+        <v>6573</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
@@ -958,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
@@ -967,51 +967,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.1</v>
+        <v>22.46</v>
       </c>
       <c r="C9" t="n">
-        <v>22.92</v>
+        <v>23.17</v>
       </c>
       <c r="D9" t="n">
-        <v>21.76</v>
+        <v>21.82</v>
       </c>
       <c r="E9" t="n">
         <v>12.2</v>
       </c>
       <c r="F9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="G9" t="n">
-        <v>479</v>
+        <v>383</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="J9" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="K9" t="n">
-        <v>53.58</v>
+        <v>52.56</v>
       </c>
       <c r="L9" t="n">
-        <v>55.95</v>
+        <v>54.35</v>
       </c>
       <c r="M9" t="n">
-        <v>51.48</v>
+        <v>50.6</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6739</v>
+        <v>6763</v>
       </c>
       <c r="P9" t="n">
-        <v>6582</v>
+        <v>6593</v>
       </c>
       <c r="Q9" t="n">
         <v>6</v>
@@ -1020,7 +1020,7 @@
         <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -1029,54 +1029,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.45</v>
+        <v>22.1</v>
       </c>
       <c r="C10" t="n">
-        <v>22.62</v>
+        <v>22.92</v>
       </c>
       <c r="D10" t="n">
-        <v>20.83</v>
+        <v>21.76</v>
       </c>
       <c r="E10" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F10" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="G10" t="n">
-        <v>640</v>
+        <v>479</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="K10" t="n">
-        <v>56.35</v>
+        <v>53.58</v>
       </c>
       <c r="L10" t="n">
-        <v>62.61</v>
+        <v>55.95</v>
       </c>
       <c r="M10" t="n">
-        <v>51.88</v>
+        <v>51.48</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6810</v>
+        <v>6739</v>
       </c>
       <c r="P10" t="n">
-        <v>6610</v>
+        <v>6582</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
         <v>6</v>
@@ -1091,60 +1091,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.67</v>
+        <v>21.45</v>
       </c>
       <c r="C11" t="n">
-        <v>20.85</v>
+        <v>22.62</v>
       </c>
       <c r="D11" t="n">
-        <v>19.11</v>
+        <v>20.83</v>
       </c>
       <c r="E11" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="F11" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
       <c r="G11" t="n">
-        <v>279</v>
+        <v>640</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.77</v>
+        <v>1.11</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="K11" t="n">
-        <v>66.39</v>
+        <v>56.35</v>
       </c>
       <c r="L11" t="n">
-        <v>68.68000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="M11" t="n">
-        <v>61.4</v>
+        <v>51.88</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6772</v>
+        <v>6810</v>
       </c>
       <c r="P11" t="n">
-        <v>6571</v>
+        <v>6610</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
         <v>5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
       </c>
       <c r="T11" t="n">
         <v>60</v>
@@ -1153,172 +1153,172 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.92</v>
+        <v>19.67</v>
       </c>
       <c r="C12" t="n">
-        <v>19.22</v>
+        <v>20.85</v>
       </c>
       <c r="D12" t="n">
-        <v>18.64</v>
+        <v>19.11</v>
       </c>
       <c r="E12" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="F12" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="G12" t="n">
-        <v>143</v>
+        <v>279</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="J12" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>71.48999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="L12" t="n">
-        <v>73.28</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>69.45</v>
+        <v>61.4</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6254</v>
+        <v>6772</v>
       </c>
       <c r="P12" t="n">
-        <v>6508</v>
+        <v>6571</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18.78</v>
+        <v>18.92</v>
       </c>
       <c r="C13" t="n">
-        <v>18.89</v>
+        <v>19.22</v>
       </c>
       <c r="D13" t="n">
-        <v>18.67</v>
+        <v>18.64</v>
       </c>
       <c r="E13" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="F13" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="G13" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="J13" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="K13" t="n">
-        <v>70.87</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>73.17</v>
+        <v>73.28</v>
       </c>
       <c r="M13" t="n">
-        <v>68.48</v>
+        <v>69.45</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5929</v>
+        <v>6254</v>
       </c>
       <c r="P13" t="n">
-        <v>6494</v>
+        <v>6508</v>
       </c>
       <c r="Q13" t="n">
         <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.59</v>
+        <v>18.78</v>
       </c>
       <c r="C14" t="n">
-        <v>19.26</v>
+        <v>18.89</v>
       </c>
       <c r="D14" t="n">
-        <v>18.18</v>
+        <v>18.67</v>
       </c>
       <c r="E14" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="F14" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="G14" t="n">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="J14" t="n">
-        <v>0.41</v>
+        <v>0.57</v>
       </c>
       <c r="K14" t="n">
-        <v>76.48999999999999</v>
+        <v>70.87</v>
       </c>
       <c r="L14" t="n">
-        <v>80.08</v>
+        <v>73.17</v>
       </c>
       <c r="M14" t="n">
-        <v>71.70999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5478</v>
+        <v>5929</v>
       </c>
       <c r="P14" t="n">
         <v>6494</v>
@@ -1327,10 +1327,10 @@
         <v>3</v>
       </c>
       <c r="R14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
       </c>
       <c r="T14" t="n">
         <v>60</v>
@@ -1339,60 +1339,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.89</v>
+        <v>18.59</v>
       </c>
       <c r="C15" t="n">
-        <v>18.29</v>
+        <v>19.26</v>
       </c>
       <c r="D15" t="n">
-        <v>17.02</v>
+        <v>18.18</v>
       </c>
       <c r="E15" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="F15" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="G15" t="n">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="K15" t="n">
-        <v>82.51000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>87.40000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M15" t="n">
-        <v>79.09999999999999</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6633</v>
+        <v>5478</v>
       </c>
       <c r="P15" t="n">
-        <v>6488</v>
+        <v>6494</v>
       </c>
       <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>60</v>
@@ -1401,113 +1401,113 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.49</v>
+        <v>17.89</v>
       </c>
       <c r="C16" t="n">
-        <v>16.79</v>
+        <v>18.29</v>
       </c>
       <c r="D16" t="n">
-        <v>16.31</v>
+        <v>17.02</v>
       </c>
       <c r="E16" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F16" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J16" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="K16" t="n">
-        <v>89.09</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>91.65000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>87.73</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5349</v>
+        <v>6633</v>
       </c>
       <c r="P16" t="n">
-        <v>6445</v>
+        <v>6488</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.27</v>
+        <v>16.49</v>
       </c>
       <c r="C17" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="D17" t="n">
         <v>16.31</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16.24</v>
       </c>
       <c r="E17" t="n">
         <v>14.6</v>
       </c>
       <c r="F17" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
         <v>0.15</v>
       </c>
       <c r="K17" t="n">
-        <v>90.12</v>
+        <v>89.09</v>
       </c>
       <c r="L17" t="n">
-        <v>91.63</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>88.84</v>
+        <v>87.73</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P17" t="n">
-        <v>6422</v>
+        <v>6445</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -1525,20 +1525,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.37</v>
+        <v>16.27</v>
       </c>
       <c r="C18" t="n">
-        <v>16.42</v>
+        <v>16.31</v>
       </c>
       <c r="D18" t="n">
-        <v>16.3</v>
+        <v>16.24</v>
       </c>
       <c r="E18" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F18" t="n">
         <v>14.4</v>
@@ -1548,19 +1548,19 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J18" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="K18" t="n">
-        <v>88.97</v>
+        <v>90.12</v>
       </c>
       <c r="L18" t="n">
-        <v>90.09</v>
+        <v>91.63</v>
       </c>
       <c r="M18" t="n">
-        <v>88.26000000000001</v>
+        <v>88.84</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -1587,44 +1587,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.35</v>
+        <v>16.37</v>
       </c>
       <c r="C19" t="n">
-        <v>16.36</v>
+        <v>16.42</v>
       </c>
       <c r="D19" t="n">
-        <v>16.35</v>
+        <v>16.3</v>
       </c>
       <c r="E19" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="F19" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="n">
-        <v>2592</v>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="K19" t="n">
-        <v>84.98</v>
+        <v>88.97</v>
       </c>
       <c r="L19" t="n">
-        <v>85.65000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="M19" t="n">
-        <v>84.31</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1633,13 +1631,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -1651,44 +1649,44 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.33</v>
+        <v>16.35</v>
       </c>
       <c r="C20" t="n">
-        <v>16.56</v>
+        <v>16.36</v>
       </c>
       <c r="D20" t="n">
-        <v>15.86</v>
+        <v>16.35</v>
       </c>
       <c r="E20" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2522</v>
+        <v>2592</v>
       </c>
       <c r="I20" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="K20" t="n">
-        <v>89.8</v>
+        <v>84.98</v>
       </c>
       <c r="L20" t="n">
-        <v>99.73</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>85.27</v>
+        <v>84.31</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1697,16 +1695,16 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6422</v>
+        <v>6425</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -1715,42 +1713,44 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.27</v>
+        <v>16.33</v>
       </c>
       <c r="C21" t="n">
-        <v>16.37</v>
+        <v>16.56</v>
       </c>
       <c r="D21" t="n">
-        <v>16.2</v>
+        <v>15.86</v>
       </c>
       <c r="E21" t="n">
         <v>14.6</v>
       </c>
       <c r="F21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>2522</v>
+      </c>
       <c r="I21" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J21" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>90.44</v>
+        <v>89.8</v>
       </c>
       <c r="L21" t="n">
-        <v>91.61</v>
+        <v>99.73</v>
       </c>
       <c r="M21" t="n">
-        <v>89.09999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1759,16 +1759,16 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -1777,23 +1777,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="C22" t="n">
-        <v>16.49</v>
+        <v>16.37</v>
       </c>
       <c r="D22" t="n">
-        <v>16.14</v>
+        <v>16.2</v>
       </c>
       <c r="E22" t="n">
         <v>14.6</v>
       </c>
       <c r="F22" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1806,13 +1806,13 @@
         <v>0.15</v>
       </c>
       <c r="K22" t="n">
-        <v>90.33</v>
+        <v>90.44</v>
       </c>
       <c r="L22" t="n">
-        <v>91.40000000000001</v>
+        <v>91.61</v>
       </c>
       <c r="M22" t="n">
-        <v>89.20999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
@@ -1839,42 +1839,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.61</v>
+        <v>16.26</v>
       </c>
       <c r="C23" t="n">
-        <v>16.82</v>
+        <v>16.49</v>
       </c>
       <c r="D23" t="n">
-        <v>16.45</v>
+        <v>16.14</v>
       </c>
       <c r="E23" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F23" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="J23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K23" t="n">
-        <v>87.3</v>
+        <v>90.33</v>
       </c>
       <c r="L23" t="n">
-        <v>89.45</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>86.06</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -1901,42 +1901,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.92</v>
+        <v>16.61</v>
       </c>
       <c r="C24" t="n">
-        <v>17.22</v>
+        <v>16.82</v>
       </c>
       <c r="D24" t="n">
-        <v>16.72</v>
+        <v>16.45</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="F24" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="J24" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="K24" t="n">
-        <v>83.48999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="L24" t="n">
-        <v>85.67</v>
+        <v>89.45</v>
       </c>
       <c r="M24" t="n">
-        <v>80.43000000000001</v>
+        <v>86.06</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1945,16 +1945,16 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6465</v>
+        <v>6434</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -1963,42 +1963,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.37</v>
+        <v>16.92</v>
       </c>
       <c r="C25" t="n">
-        <v>17.64</v>
+        <v>17.22</v>
       </c>
       <c r="D25" t="n">
-        <v>17.15</v>
+        <v>16.72</v>
       </c>
       <c r="E25" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="J25" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="K25" t="n">
-        <v>81.5</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>83.2</v>
+        <v>85.67</v>
       </c>
       <c r="M25" t="n">
-        <v>79.69</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6471</v>
+        <v>6465</v>
       </c>
       <c r="Q25" t="n">
         <v>2</v>
@@ -2025,42 +2025,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>17.37</v>
       </c>
       <c r="C26" t="n">
-        <v>17.71</v>
+        <v>17.64</v>
       </c>
       <c r="D26" t="n">
-        <v>17.16</v>
+        <v>17.15</v>
       </c>
       <c r="E26" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J26" t="n">
         <v>0.33</v>
       </c>
-      <c r="J26" t="n">
-        <v>0.28</v>
-      </c>
       <c r="K26" t="n">
-        <v>83.11</v>
+        <v>81.5</v>
       </c>
       <c r="L26" t="n">
-        <v>85.31</v>
+        <v>83.2</v>
       </c>
       <c r="M26" t="n">
-        <v>78.94</v>
+        <v>79.69</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6474</v>
+        <v>6471</v>
       </c>
       <c r="Q26" t="n">
         <v>2</v>
@@ -2087,42 +2087,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.78</v>
+        <v>17.37</v>
       </c>
       <c r="C27" t="n">
-        <v>18.2</v>
+        <v>17.71</v>
       </c>
       <c r="D27" t="n">
-        <v>17.44</v>
+        <v>17.16</v>
       </c>
       <c r="E27" t="n">
         <v>14.4</v>
       </c>
       <c r="F27" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="J27" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="K27" t="n">
-        <v>81.01000000000001</v>
+        <v>83.11</v>
       </c>
       <c r="L27" t="n">
-        <v>82.84999999999999</v>
+        <v>85.31</v>
       </c>
       <c r="M27" t="n">
-        <v>78.13</v>
+        <v>78.94</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6494</v>
+        <v>6474</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
@@ -2149,42 +2149,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.91</v>
+        <v>17.78</v>
       </c>
       <c r="C28" t="n">
-        <v>19.32</v>
+        <v>18.2</v>
       </c>
       <c r="D28" t="n">
-        <v>18.33</v>
+        <v>17.44</v>
       </c>
       <c r="E28" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="F28" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="J28" t="n">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="K28" t="n">
-        <v>72.89</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>76.66</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>67.31</v>
+        <v>78.13</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2193,16 +2193,16 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6496</v>
+        <v>6494</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2211,54 +2211,54 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.65</v>
+        <v>18.91</v>
       </c>
       <c r="C29" t="n">
-        <v>19.86</v>
+        <v>19.32</v>
       </c>
       <c r="D29" t="n">
-        <v>19.37</v>
+        <v>18.33</v>
       </c>
       <c r="E29" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="F29" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="G29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="J29" t="n">
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="K29" t="n">
-        <v>69.28</v>
+        <v>72.89</v>
       </c>
       <c r="L29" t="n">
-        <v>71.03</v>
+        <v>76.66</v>
       </c>
       <c r="M29" t="n">
-        <v>67.26000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>6511</v>
+        <v>6496</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
         <v>4</v>
@@ -2273,51 +2273,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.34</v>
+        <v>19.65</v>
       </c>
       <c r="C30" t="n">
-        <v>19.5</v>
+        <v>19.86</v>
       </c>
       <c r="D30" t="n">
-        <v>19.25</v>
+        <v>19.37</v>
       </c>
       <c r="E30" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F30" t="n">
         <v>13.5</v>
       </c>
-      <c r="F30" t="n">
-        <v>13.4</v>
-      </c>
       <c r="G30" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="K30" t="n">
-        <v>69.37</v>
+        <v>69.28</v>
       </c>
       <c r="L30" t="n">
-        <v>70.14</v>
+        <v>71.03</v>
       </c>
       <c r="M30" t="n">
-        <v>68.55</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4721</v>
+        <v>2267</v>
       </c>
       <c r="P30" t="n">
-        <v>6536</v>
+        <v>6511</v>
       </c>
       <c r="Q30" t="n">
         <v>4</v>
@@ -2335,51 +2335,51 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.29</v>
+        <v>19.34</v>
       </c>
       <c r="C31" t="n">
-        <v>19.86</v>
+        <v>19.5</v>
       </c>
       <c r="D31" t="n">
-        <v>19.1</v>
+        <v>19.25</v>
       </c>
       <c r="E31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F31" t="n">
         <v>13.4</v>
       </c>
-      <c r="F31" t="n">
-        <v>13.3</v>
-      </c>
       <c r="G31" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="J31" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="K31" t="n">
-        <v>68.94</v>
+        <v>69.37</v>
       </c>
       <c r="L31" t="n">
-        <v>69.94</v>
+        <v>70.14</v>
       </c>
       <c r="M31" t="n">
-        <v>66.66</v>
+        <v>68.55</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4462</v>
+        <v>4721</v>
       </c>
       <c r="P31" t="n">
-        <v>6539</v>
+        <v>6536</v>
       </c>
       <c r="Q31" t="n">
         <v>4</v>
@@ -2391,119 +2391,119 @@
         <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20.82</v>
+        <v>19.29</v>
       </c>
       <c r="C32" t="n">
-        <v>21.19</v>
+        <v>19.86</v>
       </c>
       <c r="D32" t="n">
-        <v>19.8</v>
+        <v>19.1</v>
       </c>
       <c r="E32" t="n">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="F32" t="n">
-        <v>11.7</v>
+        <v>13.3</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>68</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>1.02</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="K32" t="n">
-        <v>58.55</v>
+        <v>68.94</v>
       </c>
       <c r="L32" t="n">
-        <v>67.09</v>
+        <v>69.94</v>
       </c>
       <c r="M32" t="n">
-        <v>55.27</v>
+        <v>66.66</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6250</v>
+        <v>4462</v>
       </c>
       <c r="P32" t="n">
-        <v>6579</v>
+        <v>6539</v>
       </c>
       <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
         <v>5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.17</v>
+        <v>20.82</v>
       </c>
       <c r="C33" t="n">
-        <v>21.41</v>
+        <v>21.19</v>
       </c>
       <c r="D33" t="n">
-        <v>20.87</v>
+        <v>19.8</v>
       </c>
       <c r="E33" t="n">
         <v>12.3</v>
       </c>
       <c r="F33" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="G33" t="n">
-        <v>419</v>
+        <v>215</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="J33" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="K33" t="n">
-        <v>57.42</v>
+        <v>58.55</v>
       </c>
       <c r="L33" t="n">
-        <v>60.15</v>
+        <v>67.09</v>
       </c>
       <c r="M33" t="n">
-        <v>55.34</v>
+        <v>55.27</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6777</v>
+        <v>6250</v>
       </c>
       <c r="P33" t="n">
-        <v>6613</v>
+        <v>6579</v>
       </c>
       <c r="Q33" t="n">
         <v>5</v>
@@ -2512,7 +2512,7 @@
         <v>5</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
         <v>60</v>
@@ -2521,51 +2521,51 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.2</v>
+        <v>21.17</v>
       </c>
       <c r="C34" t="n">
-        <v>21.55</v>
+        <v>21.41</v>
       </c>
       <c r="D34" t="n">
-        <v>20.85</v>
+        <v>20.87</v>
       </c>
       <c r="E34" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F34" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="G34" t="n">
-        <v>629</v>
+        <v>419</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="K34" t="n">
-        <v>58.56</v>
+        <v>57.42</v>
       </c>
       <c r="L34" t="n">
-        <v>61.5</v>
+        <v>60.15</v>
       </c>
       <c r="M34" t="n">
-        <v>56.2</v>
+        <v>55.34</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6849</v>
+        <v>6777</v>
       </c>
       <c r="P34" t="n">
-        <v>6647</v>
+        <v>6613</v>
       </c>
       <c r="Q34" t="n">
         <v>5</v>
@@ -2583,17 +2583,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>20.75</v>
+        <v>21.2</v>
       </c>
       <c r="C35" t="n">
-        <v>21.44</v>
+        <v>21.55</v>
       </c>
       <c r="D35" t="n">
-        <v>20.1</v>
+        <v>20.85</v>
       </c>
       <c r="E35" t="n">
         <v>12.6</v>
@@ -2602,32 +2602,32 @@
         <v>12.1</v>
       </c>
       <c r="G35" t="n">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>59.8</v>
+        <v>58.56</v>
       </c>
       <c r="L35" t="n">
-        <v>61.83</v>
+        <v>61.5</v>
       </c>
       <c r="M35" t="n">
-        <v>58.57</v>
+        <v>56.2</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6901</v>
+        <v>6849</v>
       </c>
       <c r="P35" t="n">
-        <v>6676</v>
+        <v>6647</v>
       </c>
       <c r="Q35" t="n">
         <v>5</v>
@@ -2645,60 +2645,60 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20.11</v>
+        <v>20.75</v>
       </c>
       <c r="C36" t="n">
-        <v>21.09</v>
+        <v>21.44</v>
       </c>
       <c r="D36" t="n">
-        <v>19.18</v>
+        <v>20.1</v>
       </c>
       <c r="E36" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F36" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G36" t="n">
-        <v>471</v>
+        <v>612</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="J36" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="K36" t="n">
-        <v>63.63</v>
+        <v>59.8</v>
       </c>
       <c r="L36" t="n">
-        <v>67.22</v>
+        <v>61.83</v>
       </c>
       <c r="M36" t="n">
-        <v>59.39</v>
+        <v>58.57</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6810</v>
+        <v>6901</v>
       </c>
       <c r="P36" t="n">
-        <v>6613</v>
+        <v>6676</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
         <v>5</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
         <v>60</v>
@@ -2707,17 +2707,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>20.11</v>
       </c>
       <c r="C37" t="n">
-        <v>19.69</v>
+        <v>21.09</v>
       </c>
       <c r="D37" t="n">
-        <v>18.97</v>
+        <v>19.18</v>
       </c>
       <c r="E37" t="n">
         <v>12.9</v>
@@ -2726,41 +2726,41 @@
         <v>12.5</v>
       </c>
       <c r="G37" t="n">
-        <v>300</v>
+        <v>471</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="J37" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="K37" t="n">
-        <v>66.97</v>
+        <v>63.63</v>
       </c>
       <c r="L37" t="n">
-        <v>70.23999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="M37" t="n">
-        <v>65.22</v>
+        <v>59.39</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6681</v>
+        <v>6810</v>
       </c>
       <c r="P37" t="n">
-        <v>6565</v>
+        <v>6613</v>
       </c>
       <c r="Q37" t="n">
         <v>4</v>
       </c>
       <c r="R37" t="n">
+        <v>5</v>
+      </c>
+      <c r="S37" t="n">
         <v>4</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
       </c>
       <c r="T37" t="n">
         <v>60</v>
@@ -2769,54 +2769,54 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.64</v>
+        <v>19.28</v>
       </c>
       <c r="C38" t="n">
-        <v>20.12</v>
+        <v>19.69</v>
       </c>
       <c r="D38" t="n">
-        <v>17.71</v>
+        <v>18.97</v>
       </c>
       <c r="E38" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="F38" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="G38" t="n">
-        <v>347</v>
+        <v>300</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="J38" t="n">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="K38" t="n">
-        <v>71.42</v>
+        <v>66.97</v>
       </c>
       <c r="L38" t="n">
-        <v>76.48</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>66.62</v>
+        <v>65.22</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6739</v>
+        <v>6681</v>
       </c>
       <c r="P38" t="n">
         <v>6565</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
         <v>4</v>
@@ -2831,175 +2831,175 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.37</v>
+        <v>18.64</v>
       </c>
       <c r="C39" t="n">
-        <v>18.2</v>
+        <v>20.12</v>
       </c>
       <c r="D39" t="n">
-        <v>16.67</v>
+        <v>17.71</v>
       </c>
       <c r="E39" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="F39" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="G39" t="n">
-        <v>167</v>
+        <v>347</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="J39" t="n">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="K39" t="n">
-        <v>79.89</v>
+        <v>71.42</v>
       </c>
       <c r="L39" t="n">
-        <v>86.01000000000001</v>
+        <v>76.48</v>
       </c>
       <c r="M39" t="n">
-        <v>75.15000000000001</v>
+        <v>66.62</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6499</v>
+        <v>6739</v>
       </c>
       <c r="P39" t="n">
-        <v>6494</v>
+        <v>6565</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" t="n">
         <v>3</v>
       </c>
-      <c r="S39" t="n">
-        <v>1</v>
-      </c>
       <c r="T39" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15.89</v>
+        <v>17.37</v>
       </c>
       <c r="C40" t="n">
-        <v>16.51</v>
+        <v>18.2</v>
       </c>
       <c r="D40" t="n">
-        <v>15.53</v>
+        <v>16.67</v>
       </c>
       <c r="E40" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="F40" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="K40" t="n">
-        <v>91.95</v>
+        <v>79.89</v>
       </c>
       <c r="L40" t="n">
-        <v>93.86</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>87.84999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4793</v>
+        <v>6499</v>
       </c>
       <c r="P40" t="n">
-        <v>6442</v>
+        <v>6494</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.63</v>
+        <v>15.89</v>
       </c>
       <c r="C41" t="n">
-        <v>15.72</v>
+        <v>16.51</v>
       </c>
       <c r="D41" t="n">
-        <v>15.55</v>
+        <v>15.53</v>
       </c>
       <c r="E41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F41" t="n">
         <v>14.3</v>
       </c>
-      <c r="F41" t="n">
-        <v>14.2</v>
-      </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="J41" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K41" t="n">
-        <v>92.23</v>
+        <v>91.95</v>
       </c>
       <c r="L41" t="n">
-        <v>93.61</v>
+        <v>93.86</v>
       </c>
       <c r="M41" t="n">
-        <v>90.98</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4793</v>
       </c>
       <c r="P41" t="n">
-        <v>6417</v>
+        <v>6442</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
@@ -3017,42 +3017,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.65</v>
+        <v>15.63</v>
       </c>
       <c r="C42" t="n">
-        <v>15.76</v>
+        <v>15.72</v>
       </c>
       <c r="D42" t="n">
-        <v>15.53</v>
+        <v>15.55</v>
       </c>
       <c r="E42" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F42" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J42" t="n">
         <v>0.11</v>
       </c>
-      <c r="J42" t="n">
-        <v>0.1</v>
-      </c>
       <c r="K42" t="n">
-        <v>93.44</v>
+        <v>92.23</v>
       </c>
       <c r="L42" t="n">
-        <v>93.83</v>
+        <v>93.61</v>
       </c>
       <c r="M42" t="n">
-        <v>92.88</v>
+        <v>90.98</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6405</v>
+        <v>6417</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -3079,42 +3079,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.63</v>
+        <v>15.65</v>
       </c>
       <c r="C43" t="n">
-        <v>15.74</v>
+        <v>15.76</v>
       </c>
       <c r="D43" t="n">
-        <v>15.57</v>
+        <v>15.53</v>
       </c>
       <c r="E43" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="F43" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J43" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="K43" t="n">
-        <v>94.87</v>
+        <v>93.44</v>
       </c>
       <c r="L43" t="n">
-        <v>95.69</v>
+        <v>93.83</v>
       </c>
       <c r="M43" t="n">
-        <v>93.40000000000001</v>
+        <v>92.88</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6414</v>
+        <v>6405</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3141,23 +3141,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="C44" t="n">
         <v>15.74</v>
       </c>
-      <c r="C44" t="n">
-        <v>15.95</v>
-      </c>
       <c r="D44" t="n">
-        <v>15.62</v>
+        <v>15.57</v>
       </c>
       <c r="E44" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F44" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3167,16 +3167,16 @@
         <v>0.08</v>
       </c>
       <c r="J44" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>95.13</v>
+        <v>94.87</v>
       </c>
       <c r="L44" t="n">
-        <v>96.19</v>
+        <v>95.69</v>
       </c>
       <c r="M44" t="n">
-        <v>94.28</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3203,20 +3203,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.02</v>
+        <v>15.74</v>
       </c>
       <c r="C45" t="n">
-        <v>16.13</v>
+        <v>15.95</v>
       </c>
       <c r="D45" t="n">
-        <v>15.96</v>
+        <v>15.62</v>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F45" t="n">
         <v>14.9</v>
@@ -3226,19 +3226,19 @@
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J45" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="K45" t="n">
-        <v>94.3</v>
+        <v>95.13</v>
       </c>
       <c r="L45" t="n">
-        <v>94.76000000000001</v>
+        <v>96.19</v>
       </c>
       <c r="M45" t="n">
-        <v>93.61</v>
+        <v>94.28</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3247,10 +3247,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -3265,42 +3265,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.24</v>
+        <v>16.02</v>
       </c>
       <c r="C46" t="n">
-        <v>16.32</v>
+        <v>16.13</v>
       </c>
       <c r="D46" t="n">
-        <v>16.16</v>
+        <v>15.96</v>
       </c>
       <c r="E46" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K46" t="n">
-        <v>93.55</v>
+        <v>94.3</v>
       </c>
       <c r="L46" t="n">
-        <v>94.40000000000001</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>92.81</v>
+        <v>93.61</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
@@ -3318,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -3327,42 +3327,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 01:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.57</v>
+        <v>16.24</v>
       </c>
       <c r="C47" t="n">
-        <v>16.97</v>
+        <v>16.32</v>
       </c>
       <c r="D47" t="n">
-        <v>16.32</v>
+        <v>16.16</v>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="F47" t="n">
-        <v>14.7</v>
+        <v>15.1</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="J47" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K47" t="n">
-        <v>90.97</v>
+        <v>93.55</v>
       </c>
       <c r="L47" t="n">
-        <v>93.34999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>87.03</v>
+        <v>92.81</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6422</v>
+        <v>6417</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
@@ -3389,42 +3389,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.39</v>
+        <v>16.57</v>
       </c>
       <c r="C48" t="n">
-        <v>17.59</v>
+        <v>16.97</v>
       </c>
       <c r="D48" t="n">
-        <v>17.17</v>
+        <v>16.32</v>
       </c>
       <c r="E48" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="J48" t="n">
-        <v>0.31</v>
+        <v>0.12</v>
       </c>
       <c r="K48" t="n">
-        <v>79.91</v>
+        <v>90.97</v>
       </c>
       <c r="L48" t="n">
-        <v>84</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>77.81999999999999</v>
+        <v>87.03</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -3451,20 +3451,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-14 23:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.82</v>
+        <v>17.39</v>
       </c>
       <c r="C49" t="n">
-        <v>17.99</v>
+        <v>17.59</v>
       </c>
       <c r="D49" t="n">
-        <v>17.64</v>
+        <v>17.17</v>
       </c>
       <c r="E49" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F49" t="n">
         <v>13.5</v>
@@ -3474,19 +3474,19 @@
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="K49" t="n">
-        <v>77.5</v>
+        <v>79.91</v>
       </c>
       <c r="L49" t="n">
-        <v>79.29000000000001</v>
+        <v>84</v>
       </c>
       <c r="M49" t="n">
-        <v>76.37</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3495,13 +3495,13 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
         <v>2</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,17 +533,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.92</v>
+        <v>17.22</v>
       </c>
       <c r="C2" t="n">
-        <v>18.06</v>
+        <v>17.34</v>
       </c>
       <c r="D2" t="n">
-        <v>17.79</v>
+        <v>17.11</v>
       </c>
       <c r="E2" t="n">
         <v>15</v>
@@ -556,19 +556,19 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="K2" t="n">
-        <v>83.5</v>
+        <v>87.37</v>
       </c>
       <c r="L2" t="n">
-        <v>85.2</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>81.95</v>
+        <v>86.23</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -577,16 +577,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -595,42 +595,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.36</v>
+        <v>17.38</v>
       </c>
       <c r="C3" t="n">
-        <v>18.45</v>
+        <v>17.5</v>
       </c>
       <c r="D3" t="n">
-        <v>18.19</v>
+        <v>17.22</v>
       </c>
       <c r="E3" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="F3" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="K3" t="n">
-        <v>80.73</v>
+        <v>87.89</v>
       </c>
       <c r="L3" t="n">
-        <v>81.93000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="M3" t="n">
-        <v>79.83</v>
+        <v>87.03</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -639,16 +639,16 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6471</v>
+        <v>6408</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -657,42 +657,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.81</v>
+        <v>17.51</v>
       </c>
       <c r="C4" t="n">
-        <v>19.07</v>
+        <v>17.64</v>
       </c>
       <c r="D4" t="n">
-        <v>18.51</v>
+        <v>17.34</v>
       </c>
       <c r="E4" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="F4" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="J4" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="K4" t="n">
-        <v>76.59999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="L4" t="n">
-        <v>79.87</v>
+        <v>90.3</v>
       </c>
       <c r="M4" t="n">
-        <v>74.01000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>6482</v>
+        <v>6437</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -719,42 +719,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.81</v>
+        <v>17.73</v>
       </c>
       <c r="C5" t="n">
-        <v>20.67</v>
+        <v>18.06</v>
       </c>
       <c r="D5" t="n">
-        <v>18.96</v>
+        <v>17.42</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="F5" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="J5" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="K5" t="n">
-        <v>69.16</v>
+        <v>85.27</v>
       </c>
       <c r="L5" t="n">
-        <v>75.04000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="M5" t="n">
-        <v>63.43</v>
+        <v>81.95</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -763,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6496</v>
+        <v>6457</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -781,364 +781,364 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.22</v>
+        <v>18.36</v>
       </c>
       <c r="C6" t="n">
-        <v>21.6</v>
+        <v>18.45</v>
       </c>
       <c r="D6" t="n">
-        <v>20.76</v>
+        <v>18.19</v>
       </c>
       <c r="E6" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="G6" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
       <c r="K6" t="n">
-        <v>60.52</v>
+        <v>80.73</v>
       </c>
       <c r="L6" t="n">
-        <v>62.17</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>58.42</v>
+        <v>79.83</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6516</v>
+        <v>6471</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.62</v>
+        <v>18.81</v>
       </c>
       <c r="C7" t="n">
-        <v>21.84</v>
+        <v>19.07</v>
       </c>
       <c r="D7" t="n">
-        <v>21.44</v>
+        <v>18.51</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F7" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="G7" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="K7" t="n">
-        <v>58.13</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>60.32</v>
+        <v>79.87</v>
       </c>
       <c r="M7" t="n">
-        <v>56.76</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6548</v>
+        <v>6482</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.96</v>
+        <v>19.81</v>
       </c>
       <c r="C8" t="n">
-        <v>22.41</v>
+        <v>20.67</v>
       </c>
       <c r="D8" t="n">
-        <v>21.77</v>
+        <v>18.96</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="F8" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="G8" t="n">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1.15</v>
+        <v>0.71</v>
       </c>
       <c r="J8" t="n">
-        <v>1.11</v>
+        <v>0.54</v>
       </c>
       <c r="K8" t="n">
-        <v>55.95</v>
+        <v>69.16</v>
       </c>
       <c r="L8" t="n">
-        <v>57.92</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>54.15</v>
+        <v>63.43</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6573</v>
+        <v>6496</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.46</v>
+        <v>21.22</v>
       </c>
       <c r="C9" t="n">
-        <v>23.17</v>
+        <v>21.6</v>
       </c>
       <c r="D9" t="n">
-        <v>21.82</v>
+        <v>20.76</v>
       </c>
       <c r="E9" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F9" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>383</v>
+        <v>73</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>1.29</v>
+        <v>0.99</v>
       </c>
       <c r="J9" t="n">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="K9" t="n">
-        <v>52.56</v>
+        <v>60.52</v>
       </c>
       <c r="L9" t="n">
-        <v>54.35</v>
+        <v>62.17</v>
       </c>
       <c r="M9" t="n">
-        <v>50.6</v>
+        <v>58.42</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6763</v>
+        <v>2990</v>
       </c>
       <c r="P9" t="n">
-        <v>6593</v>
+        <v>6516</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.1</v>
+        <v>21.62</v>
       </c>
       <c r="C10" t="n">
-        <v>22.92</v>
+        <v>21.84</v>
       </c>
       <c r="D10" t="n">
-        <v>21.76</v>
+        <v>21.44</v>
       </c>
       <c r="E10" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>11.5</v>
+        <v>12.7</v>
       </c>
       <c r="G10" t="n">
-        <v>479</v>
+        <v>137</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="J10" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>53.58</v>
+        <v>58.13</v>
       </c>
       <c r="L10" t="n">
-        <v>55.95</v>
+        <v>60.32</v>
       </c>
       <c r="M10" t="n">
-        <v>51.48</v>
+        <v>56.76</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6739</v>
+        <v>5684</v>
       </c>
       <c r="P10" t="n">
-        <v>6582</v>
+        <v>6548</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.45</v>
+        <v>21.96</v>
       </c>
       <c r="C11" t="n">
-        <v>22.62</v>
+        <v>22.41</v>
       </c>
       <c r="D11" t="n">
-        <v>20.83</v>
+        <v>21.77</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G11" t="n">
-        <v>640</v>
+        <v>205</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.11</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.92</v>
-      </c>
       <c r="K11" t="n">
-        <v>56.35</v>
+        <v>55.95</v>
       </c>
       <c r="L11" t="n">
-        <v>62.61</v>
+        <v>57.92</v>
       </c>
       <c r="M11" t="n">
-        <v>51.88</v>
+        <v>54.15</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6810</v>
+        <v>6619</v>
       </c>
       <c r="P11" t="n">
-        <v>6610</v>
+        <v>6573</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
         <v>6</v>
@@ -1153,60 +1153,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.67</v>
+        <v>22.46</v>
       </c>
       <c r="C12" t="n">
-        <v>20.85</v>
+        <v>23.17</v>
       </c>
       <c r="D12" t="n">
-        <v>19.11</v>
+        <v>21.82</v>
       </c>
       <c r="E12" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F12" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="G12" t="n">
-        <v>279</v>
+        <v>383</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>1.21</v>
       </c>
       <c r="K12" t="n">
-        <v>66.39</v>
+        <v>52.56</v>
       </c>
       <c r="L12" t="n">
-        <v>68.68000000000001</v>
+        <v>54.35</v>
       </c>
       <c r="M12" t="n">
-        <v>61.4</v>
+        <v>50.6</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6772</v>
+        <v>6763</v>
       </c>
       <c r="P12" t="n">
-        <v>6571</v>
+        <v>6593</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
@@ -1215,122 +1215,122 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18.92</v>
+        <v>22.1</v>
       </c>
       <c r="C13" t="n">
-        <v>19.22</v>
+        <v>22.92</v>
       </c>
       <c r="D13" t="n">
-        <v>18.64</v>
+        <v>21.76</v>
       </c>
       <c r="E13" t="n">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="F13" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="G13" t="n">
-        <v>143</v>
+        <v>479</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="J13" t="n">
-        <v>0.58</v>
+        <v>1.14</v>
       </c>
       <c r="K13" t="n">
-        <v>71.48999999999999</v>
+        <v>53.58</v>
       </c>
       <c r="L13" t="n">
-        <v>73.28</v>
+        <v>55.95</v>
       </c>
       <c r="M13" t="n">
-        <v>69.45</v>
+        <v>51.48</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6254</v>
+        <v>6739</v>
       </c>
       <c r="P13" t="n">
-        <v>6508</v>
+        <v>6582</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.78</v>
+        <v>21.45</v>
       </c>
       <c r="C14" t="n">
-        <v>18.89</v>
+        <v>22.62</v>
       </c>
       <c r="D14" t="n">
-        <v>18.67</v>
+        <v>20.83</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="F14" t="n">
-        <v>12.8</v>
+        <v>11.1</v>
       </c>
       <c r="G14" t="n">
-        <v>134</v>
+        <v>640</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.63</v>
+        <v>1.11</v>
       </c>
       <c r="J14" t="n">
-        <v>0.57</v>
+        <v>0.92</v>
       </c>
       <c r="K14" t="n">
-        <v>70.87</v>
+        <v>56.35</v>
       </c>
       <c r="L14" t="n">
-        <v>73.17</v>
+        <v>62.61</v>
       </c>
       <c r="M14" t="n">
-        <v>68.48</v>
+        <v>51.88</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5929</v>
+        <v>6810</v>
       </c>
       <c r="P14" t="n">
-        <v>6494</v>
+        <v>6610</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
         <v>60</v>
@@ -1339,60 +1339,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.59</v>
+        <v>19.67</v>
       </c>
       <c r="C15" t="n">
-        <v>19.26</v>
+        <v>20.85</v>
       </c>
       <c r="D15" t="n">
-        <v>18.18</v>
+        <v>19.11</v>
       </c>
       <c r="E15" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="F15" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="G15" t="n">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="J15" t="n">
-        <v>0.41</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>76.48999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="L15" t="n">
-        <v>80.08</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>71.70999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5478</v>
+        <v>6772</v>
       </c>
       <c r="P15" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
         <v>60</v>
@@ -1401,307 +1401,305 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.89</v>
+        <v>18.92</v>
       </c>
       <c r="C16" t="n">
-        <v>18.29</v>
+        <v>19.22</v>
       </c>
       <c r="D16" t="n">
-        <v>17.02</v>
+        <v>18.64</v>
       </c>
       <c r="E16" t="n">
-        <v>14.8</v>
+        <v>13.6</v>
       </c>
       <c r="F16" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="G16" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="J16" t="n">
-        <v>0.24</v>
+        <v>0.58</v>
       </c>
       <c r="K16" t="n">
-        <v>82.51000000000001</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>87.40000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="M16" t="n">
-        <v>79.09999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6633</v>
+        <v>6254</v>
       </c>
       <c r="P16" t="n">
-        <v>6488</v>
+        <v>6508</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.49</v>
+        <v>18.78</v>
       </c>
       <c r="C17" t="n">
-        <v>16.79</v>
+        <v>18.89</v>
       </c>
       <c r="D17" t="n">
-        <v>16.31</v>
+        <v>18.67</v>
       </c>
       <c r="E17" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="F17" t="n">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="J17" t="n">
-        <v>0.15</v>
+        <v>0.57</v>
       </c>
       <c r="K17" t="n">
-        <v>89.09</v>
+        <v>70.87</v>
       </c>
       <c r="L17" t="n">
-        <v>91.65000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="M17" t="n">
-        <v>87.73</v>
+        <v>68.48</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5349</v>
+        <v>5929</v>
       </c>
       <c r="P17" t="n">
-        <v>6445</v>
+        <v>6494</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.27</v>
+        <v>18.59</v>
       </c>
       <c r="C18" t="n">
-        <v>16.31</v>
+        <v>19.26</v>
       </c>
       <c r="D18" t="n">
-        <v>16.24</v>
+        <v>18.18</v>
       </c>
       <c r="E18" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F18" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="K18" t="n">
-        <v>90.12</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>91.63</v>
+        <v>80.08</v>
       </c>
       <c r="M18" t="n">
-        <v>88.84</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="P18" t="n">
-        <v>6422</v>
+        <v>6494</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.37</v>
+        <v>17.89</v>
       </c>
       <c r="C19" t="n">
-        <v>16.42</v>
+        <v>18.29</v>
       </c>
       <c r="D19" t="n">
-        <v>16.3</v>
+        <v>17.02</v>
       </c>
       <c r="E19" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="F19" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J19" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="K19" t="n">
-        <v>88.97</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>90.09</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>88.26000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P19" t="n">
-        <v>6414</v>
+        <v>6488</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.35</v>
+        <v>16.49</v>
       </c>
       <c r="C20" t="n">
-        <v>16.36</v>
+        <v>16.79</v>
       </c>
       <c r="D20" t="n">
-        <v>16.35</v>
+        <v>16.31</v>
       </c>
       <c r="E20" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="F20" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2592</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="K20" t="n">
-        <v>84.98</v>
+        <v>89.09</v>
       </c>
       <c r="L20" t="n">
-        <v>85.65000000000001</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>84.31</v>
+        <v>87.73</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P20" t="n">
-        <v>6425</v>
+        <v>6445</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -1713,44 +1711,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.33</v>
+        <v>16.27</v>
       </c>
       <c r="C21" t="n">
-        <v>16.56</v>
+        <v>16.31</v>
       </c>
       <c r="D21" t="n">
-        <v>15.86</v>
+        <v>16.24</v>
       </c>
       <c r="E21" t="n">
         <v>14.6</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="n">
-        <v>2522</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K21" t="n">
-        <v>89.8</v>
+        <v>90.12</v>
       </c>
       <c r="L21" t="n">
-        <v>99.73</v>
+        <v>91.63</v>
       </c>
       <c r="M21" t="n">
-        <v>85.27</v>
+        <v>88.84</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1765,10 +1761,10 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -1777,42 +1773,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.27</v>
+        <v>16.37</v>
       </c>
       <c r="C22" t="n">
-        <v>16.37</v>
+        <v>16.42</v>
       </c>
       <c r="D22" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="E22" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="K22" t="n">
-        <v>90.44</v>
+        <v>88.97</v>
       </c>
       <c r="L22" t="n">
-        <v>91.61</v>
+        <v>90.09</v>
       </c>
       <c r="M22" t="n">
-        <v>89.09999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1821,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
@@ -1839,42 +1835,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.26</v>
+        <v>16.35</v>
       </c>
       <c r="C23" t="n">
-        <v>16.49</v>
+        <v>16.36</v>
       </c>
       <c r="D23" t="n">
-        <v>16.14</v>
+        <v>16.35</v>
       </c>
       <c r="E23" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F23" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>2592</v>
+      </c>
       <c r="I23" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="J23" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K23" t="n">
-        <v>90.33</v>
+        <v>84.98</v>
       </c>
       <c r="L23" t="n">
-        <v>91.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>89.20999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1886,10 +1884,10 @@
         <v>6425</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -1901,42 +1899,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.61</v>
+        <v>16.33</v>
       </c>
       <c r="C24" t="n">
-        <v>16.82</v>
+        <v>16.56</v>
       </c>
       <c r="D24" t="n">
-        <v>16.45</v>
+        <v>15.86</v>
       </c>
       <c r="E24" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F24" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>2522</v>
+      </c>
       <c r="I24" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J24" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>87.3</v>
+        <v>89.8</v>
       </c>
       <c r="L24" t="n">
-        <v>89.45</v>
+        <v>99.73</v>
       </c>
       <c r="M24" t="n">
-        <v>86.06</v>
+        <v>85.27</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1945,16 +1945,16 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6434</v>
+        <v>6422</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -1963,42 +1963,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.92</v>
+        <v>16.27</v>
       </c>
       <c r="C25" t="n">
-        <v>17.22</v>
+        <v>16.37</v>
       </c>
       <c r="D25" t="n">
-        <v>16.72</v>
+        <v>16.2</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F25" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="J25" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="K25" t="n">
-        <v>83.48999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="L25" t="n">
-        <v>85.67</v>
+        <v>91.61</v>
       </c>
       <c r="M25" t="n">
-        <v>80.43000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6465</v>
+        <v>6417</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2025,42 +2025,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.37</v>
+        <v>16.26</v>
       </c>
       <c r="C26" t="n">
-        <v>17.64</v>
+        <v>16.49</v>
       </c>
       <c r="D26" t="n">
-        <v>17.15</v>
+        <v>16.14</v>
       </c>
       <c r="E26" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="J26" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="K26" t="n">
-        <v>81.5</v>
+        <v>90.33</v>
       </c>
       <c r="L26" t="n">
-        <v>83.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>79.69</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2069,16 +2069,16 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6471</v>
+        <v>6425</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2087,42 +2087,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.37</v>
+        <v>16.61</v>
       </c>
       <c r="C27" t="n">
-        <v>17.71</v>
+        <v>16.82</v>
       </c>
       <c r="D27" t="n">
-        <v>17.16</v>
+        <v>16.45</v>
       </c>
       <c r="E27" t="n">
         <v>14.4</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="J27" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="K27" t="n">
-        <v>83.11</v>
+        <v>87.3</v>
       </c>
       <c r="L27" t="n">
-        <v>85.31</v>
+        <v>89.45</v>
       </c>
       <c r="M27" t="n">
-        <v>78.94</v>
+        <v>86.06</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2131,16 +2131,16 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6474</v>
+        <v>6434</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2149,42 +2149,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.78</v>
+        <v>16.92</v>
       </c>
       <c r="C28" t="n">
-        <v>18.2</v>
+        <v>17.22</v>
       </c>
       <c r="D28" t="n">
-        <v>17.44</v>
+        <v>16.72</v>
       </c>
       <c r="E28" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="J28" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="K28" t="n">
-        <v>81.01000000000001</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>82.84999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="M28" t="n">
-        <v>78.13</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6494</v>
+        <v>6465</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
@@ -2211,42 +2211,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18.91</v>
+        <v>17.37</v>
       </c>
       <c r="C29" t="n">
-        <v>19.32</v>
+        <v>17.64</v>
       </c>
       <c r="D29" t="n">
-        <v>18.33</v>
+        <v>17.15</v>
       </c>
       <c r="E29" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F29" t="n">
         <v>13.9</v>
-      </c>
-      <c r="F29" t="n">
-        <v>13.1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="J29" t="n">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="K29" t="n">
-        <v>72.89</v>
+        <v>81.5</v>
       </c>
       <c r="L29" t="n">
-        <v>76.66</v>
+        <v>83.2</v>
       </c>
       <c r="M29" t="n">
-        <v>67.31</v>
+        <v>79.69</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2255,16 +2255,16 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>6496</v>
+        <v>6471</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2273,60 +2273,60 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.65</v>
+        <v>17.37</v>
       </c>
       <c r="C30" t="n">
-        <v>19.86</v>
+        <v>17.71</v>
       </c>
       <c r="D30" t="n">
-        <v>19.37</v>
+        <v>17.16</v>
       </c>
       <c r="E30" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="F30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="J30" t="n">
-        <v>0.65</v>
+        <v>0.28</v>
       </c>
       <c r="K30" t="n">
-        <v>69.28</v>
+        <v>83.11</v>
       </c>
       <c r="L30" t="n">
-        <v>71.03</v>
+        <v>85.31</v>
       </c>
       <c r="M30" t="n">
-        <v>67.26000000000001</v>
+        <v>78.94</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>6511</v>
+        <v>6474</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -2335,60 +2335,60 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.34</v>
+        <v>17.78</v>
       </c>
       <c r="C31" t="n">
-        <v>19.5</v>
+        <v>18.2</v>
       </c>
       <c r="D31" t="n">
-        <v>19.25</v>
+        <v>17.44</v>
       </c>
       <c r="E31" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="F31" t="n">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="G31" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="J31" t="n">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
       <c r="K31" t="n">
-        <v>69.37</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>70.14</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>68.55</v>
+        <v>78.13</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6536</v>
+        <v>6494</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -2397,54 +2397,54 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19.29</v>
+        <v>18.91</v>
       </c>
       <c r="C32" t="n">
-        <v>19.86</v>
+        <v>19.32</v>
       </c>
       <c r="D32" t="n">
-        <v>19.1</v>
+        <v>18.33</v>
       </c>
       <c r="E32" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="F32" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="G32" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="J32" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="K32" t="n">
-        <v>68.94</v>
+        <v>72.89</v>
       </c>
       <c r="L32" t="n">
-        <v>69.94</v>
+        <v>76.66</v>
       </c>
       <c r="M32" t="n">
-        <v>66.66</v>
+        <v>67.31</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4462</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>6539</v>
+        <v>6496</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
         <v>4</v>
@@ -2453,243 +2453,243 @@
         <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.82</v>
+        <v>19.65</v>
       </c>
       <c r="C33" t="n">
-        <v>21.19</v>
+        <v>19.86</v>
       </c>
       <c r="D33" t="n">
-        <v>19.8</v>
+        <v>19.37</v>
       </c>
       <c r="E33" t="n">
-        <v>12.3</v>
+        <v>13.8</v>
       </c>
       <c r="F33" t="n">
-        <v>11.7</v>
+        <v>13.5</v>
       </c>
       <c r="G33" t="n">
-        <v>215</v>
+        <v>55</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>1.02</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="K33" t="n">
-        <v>58.55</v>
+        <v>69.28</v>
       </c>
       <c r="L33" t="n">
-        <v>67.09</v>
+        <v>71.03</v>
       </c>
       <c r="M33" t="n">
-        <v>55.27</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6250</v>
+        <v>2267</v>
       </c>
       <c r="P33" t="n">
-        <v>6579</v>
+        <v>6511</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.17</v>
+        <v>19.34</v>
       </c>
       <c r="C34" t="n">
-        <v>21.41</v>
+        <v>19.5</v>
       </c>
       <c r="D34" t="n">
-        <v>20.87</v>
+        <v>19.25</v>
       </c>
       <c r="E34" t="n">
-        <v>12.3</v>
+        <v>13.5</v>
       </c>
       <c r="F34" t="n">
-        <v>11.8</v>
+        <v>13.4</v>
       </c>
       <c r="G34" t="n">
-        <v>419</v>
+        <v>67</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>1.06</v>
+        <v>0.68</v>
       </c>
       <c r="J34" t="n">
-        <v>0.99</v>
+        <v>0.67</v>
       </c>
       <c r="K34" t="n">
-        <v>57.42</v>
+        <v>69.37</v>
       </c>
       <c r="L34" t="n">
-        <v>60.15</v>
+        <v>70.14</v>
       </c>
       <c r="M34" t="n">
-        <v>55.34</v>
+        <v>68.55</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6777</v>
+        <v>4721</v>
       </c>
       <c r="P34" t="n">
-        <v>6613</v>
+        <v>6536</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21.2</v>
+        <v>19.29</v>
       </c>
       <c r="C35" t="n">
-        <v>21.55</v>
+        <v>19.86</v>
       </c>
       <c r="D35" t="n">
-        <v>20.85</v>
+        <v>19.1</v>
       </c>
       <c r="E35" t="n">
-        <v>12.6</v>
+        <v>13.4</v>
       </c>
       <c r="F35" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="G35" t="n">
-        <v>629</v>
+        <v>68</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>1.04</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="K35" t="n">
-        <v>58.56</v>
+        <v>68.94</v>
       </c>
       <c r="L35" t="n">
-        <v>61.5</v>
+        <v>69.94</v>
       </c>
       <c r="M35" t="n">
-        <v>56.2</v>
+        <v>66.66</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6849</v>
+        <v>4462</v>
       </c>
       <c r="P35" t="n">
-        <v>6647</v>
+        <v>6539</v>
       </c>
       <c r="Q35" t="n">
+        <v>4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="n">
         <v>5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>5</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20.75</v>
+        <v>20.82</v>
       </c>
       <c r="C36" t="n">
-        <v>21.44</v>
+        <v>21.19</v>
       </c>
       <c r="D36" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="E36" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F36" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="G36" t="n">
-        <v>612</v>
+        <v>215</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="K36" t="n">
-        <v>59.8</v>
+        <v>58.55</v>
       </c>
       <c r="L36" t="n">
-        <v>61.83</v>
+        <v>67.09</v>
       </c>
       <c r="M36" t="n">
-        <v>58.57</v>
+        <v>55.27</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6901</v>
+        <v>6250</v>
       </c>
       <c r="P36" t="n">
-        <v>6676</v>
+        <v>6579</v>
       </c>
       <c r="Q36" t="n">
         <v>5</v>
@@ -2698,7 +2698,7 @@
         <v>5</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
         <v>60</v>
@@ -2707,60 +2707,60 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.11</v>
+        <v>21.17</v>
       </c>
       <c r="C37" t="n">
-        <v>21.09</v>
+        <v>21.41</v>
       </c>
       <c r="D37" t="n">
-        <v>19.18</v>
+        <v>20.87</v>
       </c>
       <c r="E37" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G37" t="n">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.85</v>
+        <v>1.06</v>
       </c>
       <c r="J37" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="K37" t="n">
-        <v>63.63</v>
+        <v>57.42</v>
       </c>
       <c r="L37" t="n">
-        <v>67.22</v>
+        <v>60.15</v>
       </c>
       <c r="M37" t="n">
-        <v>59.39</v>
+        <v>55.34</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6810</v>
+        <v>6777</v>
       </c>
       <c r="P37" t="n">
         <v>6613</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
         <v>5</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
         <v>60</v>
@@ -2769,60 +2769,60 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.28</v>
+        <v>21.2</v>
       </c>
       <c r="C38" t="n">
-        <v>19.69</v>
+        <v>21.55</v>
       </c>
       <c r="D38" t="n">
-        <v>18.97</v>
+        <v>20.85</v>
       </c>
       <c r="E38" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F38" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G38" t="n">
-        <v>300</v>
+        <v>629</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="J38" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>66.97</v>
+        <v>58.56</v>
       </c>
       <c r="L38" t="n">
-        <v>70.23999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="M38" t="n">
-        <v>65.22</v>
+        <v>56.2</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6681</v>
+        <v>6849</v>
       </c>
       <c r="P38" t="n">
-        <v>6565</v>
+        <v>6647</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
         <v>60</v>
@@ -2831,60 +2831,60 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18.64</v>
+        <v>20.75</v>
       </c>
       <c r="C39" t="n">
-        <v>20.12</v>
+        <v>21.44</v>
       </c>
       <c r="D39" t="n">
-        <v>17.71</v>
+        <v>20.1</v>
       </c>
       <c r="E39" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="F39" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="G39" t="n">
-        <v>347</v>
+        <v>612</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="J39" t="n">
-        <v>0.48</v>
+        <v>0.9</v>
       </c>
       <c r="K39" t="n">
-        <v>71.42</v>
+        <v>59.8</v>
       </c>
       <c r="L39" t="n">
-        <v>76.48</v>
+        <v>61.83</v>
       </c>
       <c r="M39" t="n">
-        <v>66.62</v>
+        <v>58.57</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6739</v>
+        <v>6901</v>
       </c>
       <c r="P39" t="n">
-        <v>6565</v>
+        <v>6676</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="n">
         <v>60</v>
@@ -2893,308 +2893,308 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.37</v>
+        <v>20.11</v>
       </c>
       <c r="C40" t="n">
-        <v>18.2</v>
+        <v>21.09</v>
       </c>
       <c r="D40" t="n">
-        <v>16.67</v>
+        <v>19.18</v>
       </c>
       <c r="E40" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="F40" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="G40" t="n">
-        <v>167</v>
+        <v>471</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="J40" t="n">
-        <v>0.26</v>
+        <v>0.72</v>
       </c>
       <c r="K40" t="n">
-        <v>79.89</v>
+        <v>63.63</v>
       </c>
       <c r="L40" t="n">
-        <v>86.01000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="M40" t="n">
-        <v>75.15000000000001</v>
+        <v>59.39</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6499</v>
+        <v>6810</v>
       </c>
       <c r="P40" t="n">
-        <v>6494</v>
+        <v>6613</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.89</v>
+        <v>19.28</v>
       </c>
       <c r="C41" t="n">
-        <v>16.51</v>
+        <v>19.69</v>
       </c>
       <c r="D41" t="n">
-        <v>15.53</v>
+        <v>18.97</v>
       </c>
       <c r="E41" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="F41" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="G41" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.14</v>
+        <v>0.73</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="K41" t="n">
-        <v>91.95</v>
+        <v>66.97</v>
       </c>
       <c r="L41" t="n">
-        <v>93.86</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>87.84999999999999</v>
+        <v>65.22</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4793</v>
+        <v>6681</v>
       </c>
       <c r="P41" t="n">
-        <v>6442</v>
+        <v>6565</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.63</v>
+        <v>18.64</v>
       </c>
       <c r="C42" t="n">
-        <v>15.72</v>
+        <v>20.12</v>
       </c>
       <c r="D42" t="n">
-        <v>15.55</v>
+        <v>17.71</v>
       </c>
       <c r="E42" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="F42" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.13</v>
+        <v>0.61</v>
       </c>
       <c r="J42" t="n">
-        <v>0.11</v>
+        <v>0.48</v>
       </c>
       <c r="K42" t="n">
-        <v>92.23</v>
+        <v>71.42</v>
       </c>
       <c r="L42" t="n">
-        <v>93.61</v>
+        <v>76.48</v>
       </c>
       <c r="M42" t="n">
-        <v>90.98</v>
+        <v>66.62</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>6739</v>
       </c>
       <c r="P42" t="n">
-        <v>6417</v>
+        <v>6565</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.65</v>
+        <v>17.37</v>
       </c>
       <c r="C43" t="n">
-        <v>15.76</v>
+        <v>18.2</v>
       </c>
       <c r="D43" t="n">
-        <v>15.53</v>
+        <v>16.67</v>
       </c>
       <c r="E43" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="F43" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="K43" t="n">
-        <v>93.44</v>
+        <v>79.89</v>
       </c>
       <c r="L43" t="n">
-        <v>93.83</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>92.88</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>6499</v>
       </c>
       <c r="P43" t="n">
-        <v>6405</v>
+        <v>6494</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15.63</v>
+        <v>15.89</v>
       </c>
       <c r="C44" t="n">
-        <v>15.74</v>
+        <v>16.51</v>
       </c>
       <c r="D44" t="n">
-        <v>15.57</v>
+        <v>15.53</v>
       </c>
       <c r="E44" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="F44" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="J44" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="K44" t="n">
-        <v>94.87</v>
+        <v>91.95</v>
       </c>
       <c r="L44" t="n">
-        <v>95.69</v>
+        <v>93.86</v>
       </c>
       <c r="M44" t="n">
-        <v>93.40000000000001</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4793</v>
       </c>
       <c r="P44" t="n">
-        <v>6414</v>
+        <v>6442</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -3203,42 +3203,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 06:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.74</v>
+        <v>15.63</v>
       </c>
       <c r="C45" t="n">
-        <v>15.95</v>
+        <v>15.72</v>
       </c>
       <c r="D45" t="n">
-        <v>15.62</v>
+        <v>15.55</v>
       </c>
       <c r="E45" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="F45" t="n">
-        <v>14.9</v>
+        <v>14.2</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="J45" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="K45" t="n">
-        <v>95.13</v>
+        <v>92.23</v>
       </c>
       <c r="L45" t="n">
-        <v>96.19</v>
+        <v>93.61</v>
       </c>
       <c r="M45" t="n">
-        <v>94.28</v>
+        <v>90.98</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3247,16 +3247,16 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6422</v>
+        <v>6417</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -3265,42 +3265,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 05:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.02</v>
+        <v>15.65</v>
       </c>
       <c r="C46" t="n">
-        <v>16.13</v>
+        <v>15.76</v>
       </c>
       <c r="D46" t="n">
-        <v>15.96</v>
+        <v>15.53</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="F46" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.1</v>
       </c>
-      <c r="J46" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K46" t="n">
-        <v>94.3</v>
+        <v>93.44</v>
       </c>
       <c r="L46" t="n">
-        <v>94.76000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="M46" t="n">
-        <v>93.61</v>
+        <v>92.88</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6414</v>
+        <v>6405</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
@@ -3318,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -3327,42 +3327,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 01:00:00</t>
+          <t>2026-10-15 04:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.24</v>
+        <v>15.63</v>
       </c>
       <c r="C47" t="n">
-        <v>16.32</v>
+        <v>15.74</v>
       </c>
       <c r="D47" t="n">
-        <v>16.16</v>
+        <v>15.57</v>
       </c>
       <c r="E47" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="F47" t="n">
-        <v>15.1</v>
+        <v>14.6</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>93.55</v>
+        <v>94.87</v>
       </c>
       <c r="L47" t="n">
-        <v>94.40000000000001</v>
+        <v>95.69</v>
       </c>
       <c r="M47" t="n">
-        <v>92.81</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3371,16 +3371,16 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -3389,42 +3389,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-15 03:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16.57</v>
+        <v>15.74</v>
       </c>
       <c r="C48" t="n">
-        <v>16.97</v>
+        <v>15.95</v>
       </c>
       <c r="D48" t="n">
-        <v>16.32</v>
+        <v>15.62</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F48" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="J48" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="K48" t="n">
-        <v>90.97</v>
+        <v>95.13</v>
       </c>
       <c r="L48" t="n">
-        <v>93.34999999999999</v>
+        <v>96.19</v>
       </c>
       <c r="M48" t="n">
-        <v>87.03</v>
+        <v>94.28</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3436,13 +3436,13 @@
         <v>6422</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -3451,42 +3451,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 23:00:00</t>
+          <t>2026-10-15 02:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.39</v>
+        <v>16.02</v>
       </c>
       <c r="C49" t="n">
-        <v>17.59</v>
+        <v>16.13</v>
       </c>
       <c r="D49" t="n">
-        <v>17.17</v>
+        <v>15.96</v>
       </c>
       <c r="E49" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
-        <v>0.31</v>
+        <v>0.09</v>
       </c>
       <c r="K49" t="n">
-        <v>79.91</v>
+        <v>94.3</v>
       </c>
       <c r="L49" t="n">
-        <v>84</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>77.81999999999999</v>
+        <v>93.61</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3495,16 +3495,16 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,20 +533,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.22</v>
+        <v>16.86</v>
       </c>
       <c r="C2" t="n">
-        <v>17.34</v>
+        <v>16.9</v>
       </c>
       <c r="D2" t="n">
-        <v>17.11</v>
+        <v>16.81</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F2" t="n">
         <v>14.9</v>
@@ -556,19 +556,19 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="K2" t="n">
-        <v>87.37</v>
+        <v>88.98</v>
       </c>
       <c r="L2" t="n">
-        <v>88.34999999999999</v>
+        <v>89.56</v>
       </c>
       <c r="M2" t="n">
-        <v>86.23</v>
+        <v>88.14</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -595,42 +595,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.38</v>
+        <v>17.13</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5</v>
+        <v>17.32</v>
       </c>
       <c r="D3" t="n">
-        <v>17.22</v>
+        <v>16.89</v>
       </c>
       <c r="E3" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F3" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="J3" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="K3" t="n">
-        <v>87.89</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>89.09</v>
+        <v>88.63</v>
       </c>
       <c r="M3" t="n">
-        <v>87.03</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -639,13 +639,13 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6408</v>
+        <v>6414</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -657,23 +657,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.51</v>
+        <v>17.01</v>
       </c>
       <c r="C4" t="n">
-        <v>17.64</v>
+        <v>17.08</v>
       </c>
       <c r="D4" t="n">
-        <v>17.34</v>
+        <v>16.93</v>
       </c>
       <c r="E4" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -683,16 +683,16 @@
         <v>0.22</v>
       </c>
       <c r="J4" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="K4" t="n">
-        <v>88.95</v>
+        <v>88.16</v>
       </c>
       <c r="L4" t="n">
-        <v>90.3</v>
+        <v>88.7</v>
       </c>
       <c r="M4" t="n">
-        <v>87.78</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>6437</v>
+        <v>6414</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -719,20 +719,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.73</v>
+        <v>17.07</v>
       </c>
       <c r="C5" t="n">
-        <v>18.06</v>
+        <v>17.29</v>
       </c>
       <c r="D5" t="n">
-        <v>17.42</v>
+        <v>16.93</v>
       </c>
       <c r="E5" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>14.9</v>
@@ -742,19 +742,19 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="J5" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="K5" t="n">
-        <v>85.27</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>88.19</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>81.95</v>
+        <v>85.97</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6457</v>
+        <v>6417</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
@@ -781,42 +781,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.36</v>
+        <v>17.44</v>
       </c>
       <c r="C6" t="n">
-        <v>18.45</v>
+        <v>17.52</v>
       </c>
       <c r="D6" t="n">
-        <v>18.19</v>
+        <v>17.31</v>
       </c>
       <c r="E6" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F6" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="J6" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="K6" t="n">
-        <v>80.73</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>81.93000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="M6" t="n">
-        <v>79.83</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6471</v>
+        <v>6417</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
@@ -843,42 +843,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.81</v>
+        <v>17.22</v>
       </c>
       <c r="C7" t="n">
-        <v>19.07</v>
+        <v>17.34</v>
       </c>
       <c r="D7" t="n">
-        <v>18.51</v>
+        <v>17.11</v>
       </c>
       <c r="E7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="J7" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="K7" t="n">
-        <v>76.59999999999999</v>
+        <v>87.37</v>
       </c>
       <c r="L7" t="n">
-        <v>79.87</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>74.01000000000001</v>
+        <v>86.23</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6482</v>
+        <v>6425</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -905,42 +905,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.81</v>
+        <v>17.38</v>
       </c>
       <c r="C8" t="n">
-        <v>20.67</v>
+        <v>17.5</v>
       </c>
       <c r="D8" t="n">
-        <v>18.96</v>
+        <v>17.22</v>
       </c>
       <c r="E8" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="F8" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.71</v>
+        <v>0.23</v>
       </c>
       <c r="J8" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="K8" t="n">
-        <v>69.16</v>
+        <v>87.89</v>
       </c>
       <c r="L8" t="n">
-        <v>75.04000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="M8" t="n">
-        <v>63.43</v>
+        <v>87.03</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -949,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6496</v>
+        <v>6408</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -967,556 +967,556 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.22</v>
+        <v>17.51</v>
       </c>
       <c r="C9" t="n">
-        <v>21.6</v>
+        <v>17.64</v>
       </c>
       <c r="D9" t="n">
-        <v>20.76</v>
+        <v>17.34</v>
       </c>
       <c r="E9" t="n">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="G9" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.99</v>
+        <v>0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>0.93</v>
+        <v>0.19</v>
       </c>
       <c r="K9" t="n">
-        <v>60.52</v>
+        <v>88.95</v>
       </c>
       <c r="L9" t="n">
-        <v>62.17</v>
+        <v>90.3</v>
       </c>
       <c r="M9" t="n">
-        <v>58.42</v>
+        <v>87.78</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6516</v>
+        <v>6437</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.62</v>
+        <v>17.73</v>
       </c>
       <c r="C10" t="n">
-        <v>21.84</v>
+        <v>18.06</v>
       </c>
       <c r="D10" t="n">
-        <v>21.44</v>
+        <v>17.42</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="F10" t="n">
-        <v>12.7</v>
+        <v>14.9</v>
       </c>
       <c r="G10" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1.07</v>
+        <v>0.29</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>0.23</v>
       </c>
       <c r="K10" t="n">
-        <v>58.13</v>
+        <v>85.27</v>
       </c>
       <c r="L10" t="n">
-        <v>60.32</v>
+        <v>88.19</v>
       </c>
       <c r="M10" t="n">
-        <v>56.76</v>
+        <v>81.95</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6548</v>
+        <v>6457</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.96</v>
+        <v>18.36</v>
       </c>
       <c r="C11" t="n">
-        <v>22.41</v>
+        <v>18.45</v>
       </c>
       <c r="D11" t="n">
-        <v>21.77</v>
+        <v>18.19</v>
       </c>
       <c r="E11" t="n">
-        <v>12.7</v>
+        <v>14.9</v>
       </c>
       <c r="F11" t="n">
-        <v>12.2</v>
+        <v>14.8</v>
       </c>
       <c r="G11" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>1.15</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.11</v>
+        <v>0.37</v>
       </c>
       <c r="K11" t="n">
-        <v>55.95</v>
+        <v>80.73</v>
       </c>
       <c r="L11" t="n">
-        <v>57.92</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>54.15</v>
+        <v>79.83</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>6573</v>
+        <v>6471</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22.46</v>
+        <v>18.81</v>
       </c>
       <c r="C12" t="n">
-        <v>23.17</v>
+        <v>19.07</v>
       </c>
       <c r="D12" t="n">
-        <v>21.82</v>
+        <v>18.51</v>
       </c>
       <c r="E12" t="n">
-        <v>12.2</v>
+        <v>14.5</v>
       </c>
       <c r="F12" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="G12" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.21</v>
+        <v>0.42</v>
       </c>
       <c r="K12" t="n">
-        <v>52.56</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>54.35</v>
+        <v>79.87</v>
       </c>
       <c r="M12" t="n">
-        <v>50.6</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6763</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6593</v>
+        <v>6482</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22.1</v>
+        <v>19.81</v>
       </c>
       <c r="C13" t="n">
-        <v>22.92</v>
+        <v>20.67</v>
       </c>
       <c r="D13" t="n">
-        <v>21.76</v>
+        <v>18.96</v>
       </c>
       <c r="E13" t="n">
-        <v>12.2</v>
+        <v>13.9</v>
       </c>
       <c r="F13" t="n">
-        <v>11.5</v>
+        <v>13.4</v>
       </c>
       <c r="G13" t="n">
-        <v>479</v>
+        <v>6</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>1.23</v>
+        <v>0.71</v>
       </c>
       <c r="J13" t="n">
-        <v>1.14</v>
+        <v>0.54</v>
       </c>
       <c r="K13" t="n">
-        <v>53.58</v>
+        <v>69.16</v>
       </c>
       <c r="L13" t="n">
-        <v>55.95</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>51.48</v>
+        <v>63.43</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6739</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6582</v>
+        <v>6496</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.45</v>
+        <v>21.22</v>
       </c>
       <c r="C14" t="n">
-        <v>22.62</v>
+        <v>21.6</v>
       </c>
       <c r="D14" t="n">
-        <v>20.83</v>
+        <v>20.76</v>
       </c>
       <c r="E14" t="n">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="F14" t="n">
-        <v>11.1</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>640</v>
+        <v>73</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="J14" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K14" t="n">
-        <v>56.35</v>
+        <v>60.52</v>
       </c>
       <c r="L14" t="n">
-        <v>62.61</v>
+        <v>62.17</v>
       </c>
       <c r="M14" t="n">
-        <v>51.88</v>
+        <v>58.42</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6810</v>
+        <v>2990</v>
       </c>
       <c r="P14" t="n">
-        <v>6610</v>
+        <v>6516</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.67</v>
+        <v>21.62</v>
       </c>
       <c r="C15" t="n">
-        <v>20.85</v>
+        <v>21.84</v>
       </c>
       <c r="D15" t="n">
-        <v>19.11</v>
+        <v>21.44</v>
       </c>
       <c r="E15" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="G15" t="n">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>66.39</v>
+        <v>58.13</v>
       </c>
       <c r="L15" t="n">
-        <v>68.68000000000001</v>
+        <v>60.32</v>
       </c>
       <c r="M15" t="n">
-        <v>61.4</v>
+        <v>56.76</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6772</v>
+        <v>5684</v>
       </c>
       <c r="P15" t="n">
-        <v>6571</v>
+        <v>6548</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>5</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.92</v>
+        <v>21.96</v>
       </c>
       <c r="C16" t="n">
-        <v>19.22</v>
+        <v>22.41</v>
       </c>
       <c r="D16" t="n">
-        <v>18.64</v>
+        <v>21.77</v>
       </c>
       <c r="E16" t="n">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="F16" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="G16" t="n">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.62</v>
+        <v>1.15</v>
       </c>
       <c r="J16" t="n">
-        <v>0.58</v>
+        <v>1.11</v>
       </c>
       <c r="K16" t="n">
-        <v>71.48999999999999</v>
+        <v>55.95</v>
       </c>
       <c r="L16" t="n">
-        <v>73.28</v>
+        <v>57.92</v>
       </c>
       <c r="M16" t="n">
-        <v>69.45</v>
+        <v>54.15</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6254</v>
+        <v>6619</v>
       </c>
       <c r="P16" t="n">
-        <v>6508</v>
+        <v>6573</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.78</v>
+        <v>22.46</v>
       </c>
       <c r="C17" t="n">
-        <v>18.89</v>
+        <v>23.17</v>
       </c>
       <c r="D17" t="n">
-        <v>18.67</v>
+        <v>21.82</v>
       </c>
       <c r="E17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F17" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="G17" t="n">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.63</v>
+        <v>1.29</v>
       </c>
       <c r="J17" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="K17" t="n">
-        <v>70.87</v>
+        <v>52.56</v>
       </c>
       <c r="L17" t="n">
-        <v>73.17</v>
+        <v>54.35</v>
       </c>
       <c r="M17" t="n">
-        <v>68.48</v>
+        <v>50.6</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5929</v>
+        <v>6763</v>
       </c>
       <c r="P17" t="n">
-        <v>6494</v>
+        <v>6593</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
         <v>60</v>
@@ -1525,60 +1525,60 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.59</v>
+        <v>22.1</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26</v>
+        <v>22.92</v>
       </c>
       <c r="D18" t="n">
-        <v>18.18</v>
+        <v>21.76</v>
       </c>
       <c r="E18" t="n">
-        <v>14.3</v>
+        <v>12.2</v>
       </c>
       <c r="F18" t="n">
-        <v>13.8</v>
+        <v>11.5</v>
       </c>
       <c r="G18" t="n">
-        <v>205</v>
+        <v>479</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.23</v>
       </c>
       <c r="J18" t="n">
-        <v>0.41</v>
+        <v>1.14</v>
       </c>
       <c r="K18" t="n">
-        <v>76.48999999999999</v>
+        <v>53.58</v>
       </c>
       <c r="L18" t="n">
-        <v>80.08</v>
+        <v>55.95</v>
       </c>
       <c r="M18" t="n">
-        <v>71.70999999999999</v>
+        <v>51.48</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>5478</v>
+        <v>6739</v>
       </c>
       <c r="P18" t="n">
-        <v>6494</v>
+        <v>6582</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
         <v>60</v>
@@ -1587,60 +1587,60 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.89</v>
+        <v>21.45</v>
       </c>
       <c r="C19" t="n">
-        <v>18.29</v>
+        <v>22.62</v>
       </c>
       <c r="D19" t="n">
-        <v>17.02</v>
+        <v>20.83</v>
       </c>
       <c r="E19" t="n">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="F19" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="G19" t="n">
-        <v>178</v>
+        <v>640</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.35</v>
+        <v>1.11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
       <c r="K19" t="n">
-        <v>82.51000000000001</v>
+        <v>56.35</v>
       </c>
       <c r="L19" t="n">
-        <v>87.40000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="M19" t="n">
-        <v>79.09999999999999</v>
+        <v>51.88</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6633</v>
+        <v>6810</v>
       </c>
       <c r="P19" t="n">
-        <v>6488</v>
+        <v>6610</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
         <v>60</v>
@@ -1649,365 +1649,361 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.49</v>
+        <v>19.67</v>
       </c>
       <c r="C20" t="n">
-        <v>16.79</v>
+        <v>20.85</v>
       </c>
       <c r="D20" t="n">
-        <v>16.31</v>
+        <v>19.11</v>
       </c>
       <c r="E20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="F20" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="G20" t="n">
-        <v>28</v>
+        <v>279</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>0.77</v>
       </c>
       <c r="J20" t="n">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="K20" t="n">
-        <v>89.09</v>
+        <v>66.39</v>
       </c>
       <c r="L20" t="n">
-        <v>91.65000000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>87.73</v>
+        <v>61.4</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5349</v>
+        <v>6772</v>
       </c>
       <c r="P20" t="n">
-        <v>6445</v>
+        <v>6571</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.27</v>
+        <v>18.92</v>
       </c>
       <c r="C21" t="n">
-        <v>16.31</v>
+        <v>19.22</v>
       </c>
       <c r="D21" t="n">
-        <v>16.24</v>
+        <v>18.64</v>
       </c>
       <c r="E21" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="F21" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="J21" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="K21" t="n">
-        <v>90.12</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>91.63</v>
+        <v>73.28</v>
       </c>
       <c r="M21" t="n">
-        <v>88.84</v>
+        <v>69.45</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="P21" t="n">
-        <v>6422</v>
+        <v>6508</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.37</v>
+        <v>18.78</v>
       </c>
       <c r="C22" t="n">
-        <v>16.42</v>
+        <v>18.89</v>
       </c>
       <c r="D22" t="n">
-        <v>16.3</v>
+        <v>18.67</v>
       </c>
       <c r="E22" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="F22" t="n">
-        <v>14.4</v>
+        <v>12.8</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="J22" t="n">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="K22" t="n">
-        <v>88.97</v>
+        <v>70.87</v>
       </c>
       <c r="L22" t="n">
-        <v>90.09</v>
+        <v>73.17</v>
       </c>
       <c r="M22" t="n">
-        <v>88.26000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5929</v>
       </c>
       <c r="P22" t="n">
-        <v>6414</v>
+        <v>6494</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.35</v>
+        <v>18.59</v>
       </c>
       <c r="C23" t="n">
-        <v>16.36</v>
+        <v>19.26</v>
       </c>
       <c r="D23" t="n">
-        <v>16.35</v>
+        <v>18.18</v>
       </c>
       <c r="E23" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="F23" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2592</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="K23" t="n">
-        <v>84.98</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>85.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M23" t="n">
-        <v>84.31</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="P23" t="n">
-        <v>6425</v>
+        <v>6494</v>
       </c>
       <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="R23" t="n">
-        <v>2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.33</v>
+        <v>17.89</v>
       </c>
       <c r="C24" t="n">
-        <v>16.56</v>
+        <v>18.29</v>
       </c>
       <c r="D24" t="n">
-        <v>15.86</v>
+        <v>17.02</v>
       </c>
       <c r="E24" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2522</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="K24" t="n">
-        <v>89.8</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>99.73</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>85.27</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P24" t="n">
-        <v>6422</v>
+        <v>6488</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
         <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.27</v>
+        <v>16.49</v>
       </c>
       <c r="C25" t="n">
-        <v>16.37</v>
+        <v>16.79</v>
       </c>
       <c r="D25" t="n">
-        <v>16.2</v>
+        <v>16.31</v>
       </c>
       <c r="E25" t="n">
         <v>14.6</v>
       </c>
       <c r="F25" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0.15</v>
       </c>
       <c r="K25" t="n">
-        <v>90.44</v>
+        <v>89.09</v>
       </c>
       <c r="L25" t="n">
-        <v>91.61</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>89.09999999999999</v>
+        <v>87.73</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P25" t="n">
-        <v>6417</v>
+        <v>6445</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
@@ -2025,42 +2021,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="C26" t="n">
-        <v>16.49</v>
+        <v>16.31</v>
       </c>
       <c r="D26" t="n">
-        <v>16.14</v>
+        <v>16.24</v>
       </c>
       <c r="E26" t="n">
         <v>14.6</v>
       </c>
       <c r="F26" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="J26" t="n">
         <v>0.15</v>
       </c>
       <c r="K26" t="n">
-        <v>90.33</v>
+        <v>90.12</v>
       </c>
       <c r="L26" t="n">
-        <v>91.40000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="M26" t="n">
-        <v>89.20999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2069,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
@@ -2087,42 +2083,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.61</v>
+        <v>16.37</v>
       </c>
       <c r="C27" t="n">
-        <v>16.82</v>
+        <v>16.42</v>
       </c>
       <c r="D27" t="n">
-        <v>16.45</v>
+        <v>16.3</v>
       </c>
       <c r="E27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F27" t="n">
         <v>14.4</v>
-      </c>
-      <c r="F27" t="n">
-        <v>14.3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="K27" t="n">
-        <v>87.3</v>
+        <v>88.97</v>
       </c>
       <c r="L27" t="n">
-        <v>89.45</v>
+        <v>90.09</v>
       </c>
       <c r="M27" t="n">
-        <v>86.06</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2131,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6434</v>
+        <v>6414</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
@@ -2149,42 +2145,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.92</v>
+        <v>16.35</v>
       </c>
       <c r="C28" t="n">
-        <v>17.22</v>
+        <v>16.36</v>
       </c>
       <c r="D28" t="n">
-        <v>16.72</v>
+        <v>16.35</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="F28" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>2592</v>
+      </c>
       <c r="I28" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="J28" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="K28" t="n">
-        <v>83.48999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="L28" t="n">
-        <v>85.67</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>80.43000000000001</v>
+        <v>84.31</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2193,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
@@ -2202,7 +2200,7 @@
         <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2211,42 +2209,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.37</v>
+        <v>16.33</v>
       </c>
       <c r="C29" t="n">
-        <v>17.64</v>
+        <v>16.56</v>
       </c>
       <c r="D29" t="n">
-        <v>17.15</v>
+        <v>15.86</v>
       </c>
       <c r="E29" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F29" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>2522</v>
+      </c>
       <c r="I29" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
       </c>
       <c r="J29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>81.5</v>
+        <v>89.8</v>
       </c>
       <c r="L29" t="n">
-        <v>83.2</v>
+        <v>99.73</v>
       </c>
       <c r="M29" t="n">
-        <v>79.69</v>
+        <v>85.27</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2255,16 +2255,16 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>6471</v>
+        <v>6422</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2273,42 +2273,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.37</v>
+        <v>16.27</v>
       </c>
       <c r="C30" t="n">
-        <v>17.71</v>
+        <v>16.37</v>
       </c>
       <c r="D30" t="n">
-        <v>17.16</v>
+        <v>16.2</v>
       </c>
       <c r="E30" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="J30" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="K30" t="n">
-        <v>83.11</v>
+        <v>90.44</v>
       </c>
       <c r="L30" t="n">
-        <v>85.31</v>
+        <v>91.61</v>
       </c>
       <c r="M30" t="n">
-        <v>78.94</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2317,16 +2317,16 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>6474</v>
+        <v>6417</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -2335,42 +2335,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.78</v>
+        <v>16.26</v>
       </c>
       <c r="C31" t="n">
-        <v>18.2</v>
+        <v>16.49</v>
       </c>
       <c r="D31" t="n">
-        <v>17.44</v>
+        <v>16.14</v>
       </c>
       <c r="E31" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F31" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="J31" t="n">
-        <v>0.34</v>
+        <v>0.15</v>
       </c>
       <c r="K31" t="n">
-        <v>81.01000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="L31" t="n">
-        <v>82.84999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>78.13</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6494</v>
+        <v>6425</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -2397,42 +2397,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18.91</v>
+        <v>16.61</v>
       </c>
       <c r="C32" t="n">
-        <v>19.32</v>
+        <v>16.82</v>
       </c>
       <c r="D32" t="n">
-        <v>18.33</v>
+        <v>16.45</v>
       </c>
       <c r="E32" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="F32" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.59</v>
+        <v>0.23</v>
       </c>
       <c r="J32" t="n">
-        <v>0.49</v>
+        <v>0.19</v>
       </c>
       <c r="K32" t="n">
-        <v>72.89</v>
+        <v>87.3</v>
       </c>
       <c r="L32" t="n">
-        <v>76.66</v>
+        <v>89.45</v>
       </c>
       <c r="M32" t="n">
-        <v>67.31</v>
+        <v>86.06</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2441,16 +2441,16 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>6496</v>
+        <v>6434</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -2459,60 +2459,60 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>19.65</v>
+        <v>16.92</v>
       </c>
       <c r="C33" t="n">
-        <v>19.86</v>
+        <v>17.22</v>
       </c>
       <c r="D33" t="n">
-        <v>19.37</v>
+        <v>16.72</v>
       </c>
       <c r="E33" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" t="n">
         <v>13.8</v>
       </c>
-      <c r="F33" t="n">
-        <v>13.5</v>
-      </c>
       <c r="G33" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
       <c r="J33" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
       <c r="K33" t="n">
-        <v>69.28</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>71.03</v>
+        <v>85.67</v>
       </c>
       <c r="M33" t="n">
-        <v>67.26000000000001</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6511</v>
+        <v>6465</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -2521,60 +2521,60 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.34</v>
+        <v>17.37</v>
       </c>
       <c r="C34" t="n">
-        <v>19.5</v>
+        <v>17.64</v>
       </c>
       <c r="D34" t="n">
-        <v>19.25</v>
+        <v>17.15</v>
       </c>
       <c r="E34" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="F34" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="G34" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="J34" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="K34" t="n">
-        <v>69.37</v>
+        <v>81.5</v>
       </c>
       <c r="L34" t="n">
-        <v>70.14</v>
+        <v>83.2</v>
       </c>
       <c r="M34" t="n">
-        <v>68.55</v>
+        <v>79.69</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6536</v>
+        <v>6471</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -2583,432 +2583,432 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.29</v>
+        <v>17.37</v>
       </c>
       <c r="C35" t="n">
-        <v>19.86</v>
+        <v>17.71</v>
       </c>
       <c r="D35" t="n">
-        <v>19.1</v>
+        <v>17.16</v>
       </c>
       <c r="E35" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="F35" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="G35" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="J35" t="n">
-        <v>0.66</v>
+        <v>0.28</v>
       </c>
       <c r="K35" t="n">
-        <v>68.94</v>
+        <v>83.11</v>
       </c>
       <c r="L35" t="n">
-        <v>69.94</v>
+        <v>85.31</v>
       </c>
       <c r="M35" t="n">
-        <v>66.66</v>
+        <v>78.94</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4462</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6539</v>
+        <v>6474</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20.82</v>
+        <v>17.78</v>
       </c>
       <c r="C36" t="n">
-        <v>21.19</v>
+        <v>18.2</v>
       </c>
       <c r="D36" t="n">
-        <v>19.8</v>
+        <v>17.44</v>
       </c>
       <c r="E36" t="n">
-        <v>12.3</v>
+        <v>14.4</v>
       </c>
       <c r="F36" t="n">
-        <v>11.7</v>
+        <v>14.3</v>
       </c>
       <c r="G36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>1.02</v>
+        <v>0.38</v>
       </c>
       <c r="J36" t="n">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
       <c r="K36" t="n">
-        <v>58.55</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>67.09</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>55.27</v>
+        <v>78.13</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>6579</v>
+        <v>6494</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>21.17</v>
+        <v>18.91</v>
       </c>
       <c r="C37" t="n">
-        <v>21.41</v>
+        <v>19.32</v>
       </c>
       <c r="D37" t="n">
-        <v>20.87</v>
+        <v>18.33</v>
       </c>
       <c r="E37" t="n">
-        <v>12.3</v>
+        <v>13.9</v>
       </c>
       <c r="F37" t="n">
-        <v>11.8</v>
+        <v>13.1</v>
       </c>
       <c r="G37" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>1.06</v>
+        <v>0.59</v>
       </c>
       <c r="J37" t="n">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="K37" t="n">
-        <v>57.42</v>
+        <v>72.89</v>
       </c>
       <c r="L37" t="n">
-        <v>60.15</v>
+        <v>76.66</v>
       </c>
       <c r="M37" t="n">
-        <v>55.34</v>
+        <v>67.31</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6777</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>6613</v>
+        <v>6496</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>21.2</v>
+        <v>19.65</v>
       </c>
       <c r="C38" t="n">
-        <v>21.55</v>
+        <v>19.86</v>
       </c>
       <c r="D38" t="n">
-        <v>20.85</v>
+        <v>19.37</v>
       </c>
       <c r="E38" t="n">
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
       <c r="F38" t="n">
-        <v>12.1</v>
+        <v>13.5</v>
       </c>
       <c r="G38" t="n">
-        <v>629</v>
+        <v>55</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>1.04</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="K38" t="n">
-        <v>58.56</v>
+        <v>69.28</v>
       </c>
       <c r="L38" t="n">
-        <v>61.5</v>
+        <v>71.03</v>
       </c>
       <c r="M38" t="n">
-        <v>56.2</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6849</v>
+        <v>2267</v>
       </c>
       <c r="P38" t="n">
-        <v>6647</v>
+        <v>6511</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20.75</v>
+        <v>19.34</v>
       </c>
       <c r="C39" t="n">
-        <v>21.44</v>
+        <v>19.5</v>
       </c>
       <c r="D39" t="n">
-        <v>20.1</v>
+        <v>19.25</v>
       </c>
       <c r="E39" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="F39" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
       <c r="G39" t="n">
-        <v>612</v>
+        <v>67</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="K39" t="n">
-        <v>59.8</v>
+        <v>69.37</v>
       </c>
       <c r="L39" t="n">
-        <v>61.83</v>
+        <v>70.14</v>
       </c>
       <c r="M39" t="n">
-        <v>58.57</v>
+        <v>68.55</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6901</v>
+        <v>4721</v>
       </c>
       <c r="P39" t="n">
-        <v>6676</v>
+        <v>6536</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20.11</v>
+        <v>19.29</v>
       </c>
       <c r="C40" t="n">
-        <v>21.09</v>
+        <v>19.86</v>
       </c>
       <c r="D40" t="n">
-        <v>19.18</v>
+        <v>19.1</v>
       </c>
       <c r="E40" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="F40" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="G40" t="n">
-        <v>471</v>
+        <v>68</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="K40" t="n">
-        <v>63.63</v>
+        <v>68.94</v>
       </c>
       <c r="L40" t="n">
-        <v>67.22</v>
+        <v>69.94</v>
       </c>
       <c r="M40" t="n">
-        <v>59.39</v>
+        <v>66.66</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6810</v>
+        <v>4462</v>
       </c>
       <c r="P40" t="n">
-        <v>6613</v>
+        <v>6539</v>
       </c>
       <c r="Q40" t="n">
         <v>4</v>
       </c>
       <c r="R40" t="n">
+        <v>4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
         <v>5</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.28</v>
+        <v>20.82</v>
       </c>
       <c r="C41" t="n">
-        <v>19.69</v>
+        <v>21.19</v>
       </c>
       <c r="D41" t="n">
-        <v>18.97</v>
+        <v>19.8</v>
       </c>
       <c r="E41" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F41" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
       <c r="G41" t="n">
-        <v>300</v>
+        <v>215</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
       <c r="J41" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="K41" t="n">
-        <v>66.97</v>
+        <v>58.55</v>
       </c>
       <c r="L41" t="n">
-        <v>70.23999999999999</v>
+        <v>67.09</v>
       </c>
       <c r="M41" t="n">
-        <v>65.22</v>
+        <v>55.27</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6681</v>
+        <v>6250</v>
       </c>
       <c r="P41" t="n">
-        <v>6565</v>
+        <v>6579</v>
       </c>
       <c r="Q41" t="n">
+        <v>5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>5</v>
+      </c>
+      <c r="S41" t="n">
         <v>4</v>
-      </c>
-      <c r="R41" t="n">
-        <v>4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
       </c>
       <c r="T41" t="n">
         <v>60</v>
@@ -3017,60 +3017,60 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18.64</v>
+        <v>21.17</v>
       </c>
       <c r="C42" t="n">
-        <v>20.12</v>
+        <v>21.41</v>
       </c>
       <c r="D42" t="n">
-        <v>17.71</v>
+        <v>20.87</v>
       </c>
       <c r="E42" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="F42" t="n">
-        <v>12.9</v>
+        <v>11.8</v>
       </c>
       <c r="G42" t="n">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.61</v>
+        <v>1.06</v>
       </c>
       <c r="J42" t="n">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="K42" t="n">
-        <v>71.42</v>
+        <v>57.42</v>
       </c>
       <c r="L42" t="n">
-        <v>76.48</v>
+        <v>60.15</v>
       </c>
       <c r="M42" t="n">
-        <v>66.62</v>
+        <v>55.34</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6739</v>
+        <v>6777</v>
       </c>
       <c r="P42" t="n">
-        <v>6565</v>
+        <v>6613</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="n">
         <v>60</v>
@@ -3079,423 +3079,423 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.37</v>
+        <v>21.2</v>
       </c>
       <c r="C43" t="n">
-        <v>18.2</v>
+        <v>21.55</v>
       </c>
       <c r="D43" t="n">
-        <v>16.67</v>
+        <v>20.85</v>
       </c>
       <c r="E43" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="F43" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="G43" t="n">
-        <v>167</v>
+        <v>629</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1.04</v>
       </c>
       <c r="J43" t="n">
-        <v>0.26</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>79.89</v>
+        <v>58.56</v>
       </c>
       <c r="L43" t="n">
-        <v>86.01000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="M43" t="n">
-        <v>75.15000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6499</v>
+        <v>6849</v>
       </c>
       <c r="P43" t="n">
-        <v>6494</v>
+        <v>6647</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15.89</v>
+        <v>20.75</v>
       </c>
       <c r="C44" t="n">
-        <v>16.51</v>
+        <v>21.44</v>
       </c>
       <c r="D44" t="n">
-        <v>15.53</v>
+        <v>20.1</v>
       </c>
       <c r="E44" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="F44" t="n">
-        <v>14.3</v>
+        <v>12.1</v>
       </c>
       <c r="G44" t="n">
-        <v>40</v>
+        <v>612</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.14</v>
+        <v>0.98</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="K44" t="n">
-        <v>91.95</v>
+        <v>59.8</v>
       </c>
       <c r="L44" t="n">
-        <v>93.86</v>
+        <v>61.83</v>
       </c>
       <c r="M44" t="n">
-        <v>87.84999999999999</v>
+        <v>58.57</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4793</v>
+        <v>6901</v>
       </c>
       <c r="P44" t="n">
-        <v>6442</v>
+        <v>6676</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 06:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.63</v>
+        <v>20.11</v>
       </c>
       <c r="C45" t="n">
-        <v>15.72</v>
+        <v>21.09</v>
       </c>
       <c r="D45" t="n">
-        <v>15.55</v>
+        <v>19.18</v>
       </c>
       <c r="E45" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="F45" t="n">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.13</v>
+        <v>0.85</v>
       </c>
       <c r="J45" t="n">
-        <v>0.11</v>
+        <v>0.72</v>
       </c>
       <c r="K45" t="n">
-        <v>92.23</v>
+        <v>63.63</v>
       </c>
       <c r="L45" t="n">
-        <v>93.61</v>
+        <v>67.22</v>
       </c>
       <c r="M45" t="n">
-        <v>90.98</v>
+        <v>59.39</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>6810</v>
       </c>
       <c r="P45" t="n">
-        <v>6417</v>
+        <v>6613</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 05:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.65</v>
+        <v>19.28</v>
       </c>
       <c r="C46" t="n">
-        <v>15.76</v>
+        <v>19.69</v>
       </c>
       <c r="D46" t="n">
-        <v>15.53</v>
+        <v>18.97</v>
       </c>
       <c r="E46" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="F46" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.11</v>
+        <v>0.73</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="K46" t="n">
-        <v>93.44</v>
+        <v>66.97</v>
       </c>
       <c r="L46" t="n">
-        <v>93.83</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>92.88</v>
+        <v>65.22</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>6681</v>
       </c>
       <c r="P46" t="n">
-        <v>6405</v>
+        <v>6565</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 04:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>15.63</v>
+        <v>18.64</v>
       </c>
       <c r="C47" t="n">
-        <v>15.74</v>
+        <v>20.12</v>
       </c>
       <c r="D47" t="n">
-        <v>15.57</v>
+        <v>17.71</v>
       </c>
       <c r="E47" t="n">
-        <v>14.7</v>
+        <v>13.3</v>
       </c>
       <c r="F47" t="n">
-        <v>14.6</v>
+        <v>12.9</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.08</v>
+        <v>0.61</v>
       </c>
       <c r="J47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="K47" t="n">
-        <v>94.87</v>
+        <v>71.42</v>
       </c>
       <c r="L47" t="n">
-        <v>95.69</v>
+        <v>76.48</v>
       </c>
       <c r="M47" t="n">
-        <v>93.40000000000001</v>
+        <v>66.62</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>6739</v>
       </c>
       <c r="P47" t="n">
-        <v>6414</v>
+        <v>6565</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 03:00:00</t>
+          <t>2026-10-15 08:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15.74</v>
+        <v>17.37</v>
       </c>
       <c r="C48" t="n">
-        <v>15.95</v>
+        <v>18.2</v>
       </c>
       <c r="D48" t="n">
-        <v>15.62</v>
+        <v>16.67</v>
       </c>
       <c r="E48" t="n">
-        <v>14.9</v>
+        <v>13.8</v>
       </c>
       <c r="F48" t="n">
-        <v>14.9</v>
+        <v>13.3</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="K48" t="n">
-        <v>95.13</v>
+        <v>79.89</v>
       </c>
       <c r="L48" t="n">
-        <v>96.19</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>94.28</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>6499</v>
       </c>
       <c r="P48" t="n">
-        <v>6422</v>
+        <v>6494</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 02:00:00</t>
+          <t>2026-10-15 07:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16.02</v>
+        <v>15.89</v>
       </c>
       <c r="C49" t="n">
-        <v>16.13</v>
+        <v>16.51</v>
       </c>
       <c r="D49" t="n">
-        <v>15.96</v>
+        <v>15.53</v>
       </c>
       <c r="E49" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="F49" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J49" t="n">
         <v>0.1</v>
       </c>
-      <c r="J49" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K49" t="n">
-        <v>94.3</v>
+        <v>91.95</v>
       </c>
       <c r="L49" t="n">
-        <v>94.76000000000001</v>
+        <v>93.86</v>
       </c>
       <c r="M49" t="n">
-        <v>93.61</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4793</v>
       </c>
       <c r="P49" t="n">
-        <v>6414</v>
+        <v>6442</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
@@ -3504,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,181 +533,181 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.86</v>
+        <v>19.77</v>
       </c>
       <c r="C2" t="n">
-        <v>16.9</v>
+        <v>19.89</v>
       </c>
       <c r="D2" t="n">
-        <v>16.81</v>
+        <v>19.53</v>
       </c>
       <c r="E2" t="n">
-        <v>14.9</v>
+        <v>10.9</v>
       </c>
       <c r="F2" t="n">
-        <v>14.9</v>
+        <v>10.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.98</v>
       </c>
       <c r="J2" t="n">
-        <v>0.19</v>
+        <v>0.95</v>
       </c>
       <c r="K2" t="n">
-        <v>88.98</v>
+        <v>57.03</v>
       </c>
       <c r="L2" t="n">
-        <v>89.56</v>
+        <v>57.87</v>
       </c>
       <c r="M2" t="n">
-        <v>88.14</v>
+        <v>55.43</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>6719</v>
       </c>
       <c r="P2" t="n">
-        <v>6414</v>
+        <v>6542</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.13</v>
+        <v>18.89</v>
       </c>
       <c r="C3" t="n">
-        <v>17.32</v>
+        <v>19.62</v>
       </c>
       <c r="D3" t="n">
-        <v>16.89</v>
+        <v>18.08</v>
       </c>
       <c r="E3" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="F3" t="n">
-        <v>14.4</v>
+        <v>10.9</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.27</v>
+        <v>0.66</v>
       </c>
       <c r="J3" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="K3" t="n">
-        <v>85.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="L3" t="n">
-        <v>88.63</v>
+        <v>82.87</v>
       </c>
       <c r="M3" t="n">
-        <v>83.40000000000001</v>
+        <v>57.89</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="P3" t="n">
-        <v>6414</v>
+        <v>6514</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.01</v>
+        <v>17.5</v>
       </c>
       <c r="C4" t="n">
-        <v>17.08</v>
+        <v>17.9</v>
       </c>
       <c r="D4" t="n">
-        <v>16.93</v>
+        <v>17.26</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F4" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="J4" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="K4" t="n">
-        <v>88.16</v>
+        <v>84.14</v>
       </c>
       <c r="L4" t="n">
-        <v>88.7</v>
+        <v>87.05</v>
       </c>
       <c r="M4" t="n">
-        <v>87.34999999999999</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="P4" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -719,51 +719,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.07</v>
+        <v>17.02</v>
       </c>
       <c r="C5" t="n">
-        <v>17.29</v>
+        <v>17.27</v>
       </c>
       <c r="D5" t="n">
-        <v>16.93</v>
+        <v>16.92</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F5" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="K5" t="n">
-        <v>88.06999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="L5" t="n">
-        <v>89.45999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="M5" t="n">
-        <v>85.97</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="P5" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -781,42 +781,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.44</v>
+        <v>16.89</v>
       </c>
       <c r="C6" t="n">
-        <v>17.52</v>
+        <v>17.03</v>
       </c>
       <c r="D6" t="n">
-        <v>17.31</v>
+        <v>16.78</v>
       </c>
       <c r="E6" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="F6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="K6" t="n">
-        <v>84.31999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>85.27</v>
+        <v>90.31</v>
       </c>
       <c r="M6" t="n">
-        <v>82.56999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -828,13 +828,13 @@
         <v>6417</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -843,42 +843,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.22</v>
+        <v>17.13</v>
       </c>
       <c r="C7" t="n">
-        <v>17.34</v>
+        <v>17.32</v>
       </c>
       <c r="D7" t="n">
-        <v>17.11</v>
+        <v>16.89</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F7" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="J7" t="n">
         <v>0.22</v>
       </c>
       <c r="K7" t="n">
-        <v>87.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>88.34999999999999</v>
+        <v>88.63</v>
       </c>
       <c r="M7" t="n">
-        <v>86.23</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -887,13 +887,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -905,42 +905,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.38</v>
+        <v>17.01</v>
       </c>
       <c r="C8" t="n">
-        <v>17.5</v>
+        <v>17.08</v>
       </c>
       <c r="D8" t="n">
-        <v>17.22</v>
+        <v>16.93</v>
       </c>
       <c r="E8" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J8" t="n">
         <v>0.21</v>
       </c>
       <c r="K8" t="n">
-        <v>87.89</v>
+        <v>88.16</v>
       </c>
       <c r="L8" t="n">
-        <v>89.09</v>
+        <v>88.7</v>
       </c>
       <c r="M8" t="n">
-        <v>87.03</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6408</v>
+        <v>6414</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -967,23 +967,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.51</v>
+        <v>17.07</v>
       </c>
       <c r="C9" t="n">
-        <v>17.64</v>
+        <v>17.29</v>
       </c>
       <c r="D9" t="n">
-        <v>17.34</v>
+        <v>16.93</v>
       </c>
       <c r="E9" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -993,16 +993,16 @@
         <v>0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="K9" t="n">
-        <v>88.95</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>90.3</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>87.78</v>
+        <v>85.97</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1011,13 +1011,13 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6437</v>
+        <v>6417</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1029,42 +1029,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.73</v>
+        <v>17.44</v>
       </c>
       <c r="C10" t="n">
-        <v>18.06</v>
+        <v>17.52</v>
       </c>
       <c r="D10" t="n">
-        <v>17.42</v>
+        <v>17.31</v>
       </c>
       <c r="E10" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="F10" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.29</v>
       </c>
-      <c r="J10" t="n">
-        <v>0.23</v>
-      </c>
       <c r="K10" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="L10" t="n">
         <v>85.27</v>
       </c>
-      <c r="L10" t="n">
-        <v>88.19</v>
-      </c>
       <c r="M10" t="n">
-        <v>81.95</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6457</v>
+        <v>6417</v>
       </c>
       <c r="Q10" t="n">
         <v>2</v>
@@ -1082,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1091,42 +1091,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18.36</v>
+        <v>17.22</v>
       </c>
       <c r="C11" t="n">
-        <v>18.45</v>
+        <v>17.34</v>
       </c>
       <c r="D11" t="n">
-        <v>18.19</v>
+        <v>17.11</v>
       </c>
       <c r="E11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" t="n">
         <v>14.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>14.8</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="J11" t="n">
-        <v>0.37</v>
+        <v>0.22</v>
       </c>
       <c r="K11" t="n">
-        <v>80.73</v>
+        <v>87.37</v>
       </c>
       <c r="L11" t="n">
-        <v>81.93000000000001</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>79.83</v>
+        <v>86.23</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>6471</v>
+        <v>6425</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1153,42 +1153,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.81</v>
+        <v>17.38</v>
       </c>
       <c r="C12" t="n">
-        <v>19.07</v>
+        <v>17.5</v>
       </c>
       <c r="D12" t="n">
-        <v>18.51</v>
+        <v>17.22</v>
       </c>
       <c r="E12" t="n">
-        <v>14.5</v>
+        <v>15.3</v>
       </c>
       <c r="F12" t="n">
-        <v>14.3</v>
+        <v>15.2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="J12" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="K12" t="n">
-        <v>76.59999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="L12" t="n">
-        <v>79.87</v>
+        <v>89.09</v>
       </c>
       <c r="M12" t="n">
-        <v>74.01000000000001</v>
+        <v>87.03</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1197,16 +1197,16 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6482</v>
+        <v>6408</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1215,42 +1215,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.81</v>
+        <v>17.51</v>
       </c>
       <c r="C13" t="n">
-        <v>20.67</v>
+        <v>17.64</v>
       </c>
       <c r="D13" t="n">
-        <v>18.96</v>
+        <v>17.34</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9</v>
+        <v>15.6</v>
       </c>
       <c r="F13" t="n">
-        <v>13.4</v>
+        <v>15.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.71</v>
+        <v>0.22</v>
       </c>
       <c r="J13" t="n">
-        <v>0.54</v>
+        <v>0.19</v>
       </c>
       <c r="K13" t="n">
-        <v>69.16</v>
+        <v>88.95</v>
       </c>
       <c r="L13" t="n">
-        <v>75.04000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="M13" t="n">
-        <v>63.43</v>
+        <v>87.78</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1259,16 +1259,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6496</v>
+        <v>6437</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1277,432 +1277,432 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.22</v>
+        <v>17.73</v>
       </c>
       <c r="C14" t="n">
-        <v>21.6</v>
+        <v>18.06</v>
       </c>
       <c r="D14" t="n">
-        <v>20.76</v>
+        <v>17.42</v>
       </c>
       <c r="E14" t="n">
-        <v>13.2</v>
+        <v>15.1</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>14.9</v>
       </c>
       <c r="G14" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.99</v>
+        <v>0.29</v>
       </c>
       <c r="J14" t="n">
-        <v>0.93</v>
+        <v>0.23</v>
       </c>
       <c r="K14" t="n">
-        <v>60.52</v>
+        <v>85.27</v>
       </c>
       <c r="L14" t="n">
-        <v>62.17</v>
+        <v>88.19</v>
       </c>
       <c r="M14" t="n">
-        <v>58.42</v>
+        <v>81.95</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6516</v>
+        <v>6457</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.62</v>
+        <v>18.36</v>
       </c>
       <c r="C15" t="n">
-        <v>21.84</v>
+        <v>18.45</v>
       </c>
       <c r="D15" t="n">
-        <v>21.44</v>
+        <v>18.19</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>14.9</v>
       </c>
       <c r="F15" t="n">
-        <v>12.7</v>
+        <v>14.8</v>
       </c>
       <c r="G15" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>1.07</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>0.37</v>
       </c>
       <c r="K15" t="n">
-        <v>58.13</v>
+        <v>80.73</v>
       </c>
       <c r="L15" t="n">
-        <v>60.32</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>56.76</v>
+        <v>79.83</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6548</v>
+        <v>6471</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21.96</v>
+        <v>18.81</v>
       </c>
       <c r="C16" t="n">
-        <v>22.41</v>
+        <v>19.07</v>
       </c>
       <c r="D16" t="n">
-        <v>21.77</v>
+        <v>18.51</v>
       </c>
       <c r="E16" t="n">
-        <v>12.7</v>
+        <v>14.5</v>
       </c>
       <c r="F16" t="n">
-        <v>12.2</v>
+        <v>14.3</v>
       </c>
       <c r="G16" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.11</v>
+        <v>0.42</v>
       </c>
       <c r="K16" t="n">
-        <v>55.95</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>57.92</v>
+        <v>79.87</v>
       </c>
       <c r="M16" t="n">
-        <v>54.15</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6573</v>
+        <v>6482</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.46</v>
+        <v>19.81</v>
       </c>
       <c r="C17" t="n">
-        <v>23.17</v>
+        <v>20.67</v>
       </c>
       <c r="D17" t="n">
-        <v>21.82</v>
+        <v>18.96</v>
       </c>
       <c r="E17" t="n">
-        <v>12.2</v>
+        <v>13.9</v>
       </c>
       <c r="F17" t="n">
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
       <c r="G17" t="n">
-        <v>383</v>
+        <v>6</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>1.29</v>
+        <v>0.71</v>
       </c>
       <c r="J17" t="n">
-        <v>1.21</v>
+        <v>0.54</v>
       </c>
       <c r="K17" t="n">
-        <v>52.56</v>
+        <v>69.16</v>
       </c>
       <c r="L17" t="n">
-        <v>54.35</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>50.6</v>
+        <v>63.43</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6763</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6593</v>
+        <v>6496</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22.1</v>
+        <v>21.22</v>
       </c>
       <c r="C18" t="n">
-        <v>22.92</v>
+        <v>21.6</v>
       </c>
       <c r="D18" t="n">
-        <v>21.76</v>
+        <v>20.76</v>
       </c>
       <c r="E18" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>479</v>
+        <v>73</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>1.23</v>
+        <v>0.99</v>
       </c>
       <c r="J18" t="n">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="K18" t="n">
-        <v>53.58</v>
+        <v>60.52</v>
       </c>
       <c r="L18" t="n">
-        <v>55.95</v>
+        <v>62.17</v>
       </c>
       <c r="M18" t="n">
-        <v>51.48</v>
+        <v>58.42</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6739</v>
+        <v>2990</v>
       </c>
       <c r="P18" t="n">
-        <v>6582</v>
+        <v>6516</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21.45</v>
+        <v>21.62</v>
       </c>
       <c r="C19" t="n">
-        <v>22.62</v>
+        <v>21.84</v>
       </c>
       <c r="D19" t="n">
-        <v>20.83</v>
+        <v>21.44</v>
       </c>
       <c r="E19" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="G19" t="n">
-        <v>640</v>
+        <v>137</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="J19" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
-        <v>56.35</v>
+        <v>58.13</v>
       </c>
       <c r="L19" t="n">
-        <v>62.61</v>
+        <v>60.32</v>
       </c>
       <c r="M19" t="n">
-        <v>51.88</v>
+        <v>56.76</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6810</v>
+        <v>5684</v>
       </c>
       <c r="P19" t="n">
-        <v>6610</v>
+        <v>6548</v>
       </c>
       <c r="Q19" t="n">
         <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.67</v>
+        <v>21.96</v>
       </c>
       <c r="C20" t="n">
-        <v>20.85</v>
+        <v>22.41</v>
       </c>
       <c r="D20" t="n">
-        <v>19.11</v>
+        <v>21.77</v>
       </c>
       <c r="E20" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="F20" t="n">
-        <v>12.9</v>
+        <v>12.2</v>
       </c>
       <c r="G20" t="n">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="K20" t="n">
-        <v>66.39</v>
+        <v>55.95</v>
       </c>
       <c r="L20" t="n">
-        <v>68.68000000000001</v>
+        <v>57.92</v>
       </c>
       <c r="M20" t="n">
-        <v>61.4</v>
+        <v>54.15</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6772</v>
+        <v>6619</v>
       </c>
       <c r="P20" t="n">
-        <v>6571</v>
+        <v>6573</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
+        <v>6</v>
+      </c>
+      <c r="S20" t="n">
         <v>5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4</v>
       </c>
       <c r="T20" t="n">
         <v>60</v>
@@ -1711,122 +1711,122 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.92</v>
+        <v>22.46</v>
       </c>
       <c r="C21" t="n">
-        <v>19.22</v>
+        <v>23.17</v>
       </c>
       <c r="D21" t="n">
-        <v>18.64</v>
+        <v>21.82</v>
       </c>
       <c r="E21" t="n">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="F21" t="n">
-        <v>13.2</v>
+        <v>11.6</v>
       </c>
       <c r="G21" t="n">
-        <v>143</v>
+        <v>383</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.62</v>
+        <v>1.29</v>
       </c>
       <c r="J21" t="n">
-        <v>0.58</v>
+        <v>1.21</v>
       </c>
       <c r="K21" t="n">
-        <v>71.48999999999999</v>
+        <v>52.56</v>
       </c>
       <c r="L21" t="n">
-        <v>73.28</v>
+        <v>54.35</v>
       </c>
       <c r="M21" t="n">
-        <v>69.45</v>
+        <v>50.6</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6254</v>
+        <v>6763</v>
       </c>
       <c r="P21" t="n">
-        <v>6508</v>
+        <v>6593</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18.78</v>
+        <v>22.1</v>
       </c>
       <c r="C22" t="n">
-        <v>18.89</v>
+        <v>22.92</v>
       </c>
       <c r="D22" t="n">
-        <v>18.67</v>
+        <v>21.76</v>
       </c>
       <c r="E22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F22" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="G22" t="n">
-        <v>134</v>
+        <v>479</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.63</v>
+        <v>1.23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.57</v>
+        <v>1.14</v>
       </c>
       <c r="K22" t="n">
-        <v>70.87</v>
+        <v>53.58</v>
       </c>
       <c r="L22" t="n">
-        <v>73.17</v>
+        <v>55.95</v>
       </c>
       <c r="M22" t="n">
-        <v>68.48</v>
+        <v>51.48</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5929</v>
+        <v>6739</v>
       </c>
       <c r="P22" t="n">
-        <v>6494</v>
+        <v>6582</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
         <v>60</v>
@@ -1835,60 +1835,60 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18.59</v>
+        <v>21.45</v>
       </c>
       <c r="C23" t="n">
-        <v>19.26</v>
+        <v>22.62</v>
       </c>
       <c r="D23" t="n">
-        <v>18.18</v>
+        <v>20.83</v>
       </c>
       <c r="E23" t="n">
-        <v>14.3</v>
+        <v>12.3</v>
       </c>
       <c r="F23" t="n">
-        <v>13.8</v>
+        <v>11.1</v>
       </c>
       <c r="G23" t="n">
-        <v>205</v>
+        <v>640</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="J23" t="n">
-        <v>0.41</v>
+        <v>0.92</v>
       </c>
       <c r="K23" t="n">
-        <v>76.48999999999999</v>
+        <v>56.35</v>
       </c>
       <c r="L23" t="n">
-        <v>80.08</v>
+        <v>62.61</v>
       </c>
       <c r="M23" t="n">
-        <v>71.70999999999999</v>
+        <v>51.88</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>5478</v>
+        <v>6810</v>
       </c>
       <c r="P23" t="n">
-        <v>6494</v>
+        <v>6610</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
         <v>60</v>
@@ -1897,60 +1897,60 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.89</v>
+        <v>19.67</v>
       </c>
       <c r="C24" t="n">
-        <v>18.29</v>
+        <v>20.85</v>
       </c>
       <c r="D24" t="n">
-        <v>17.02</v>
+        <v>19.11</v>
       </c>
       <c r="E24" t="n">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
       <c r="F24" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="G24" t="n">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.35</v>
+        <v>0.77</v>
       </c>
       <c r="J24" t="n">
-        <v>0.24</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
-        <v>82.51000000000001</v>
+        <v>66.39</v>
       </c>
       <c r="L24" t="n">
-        <v>87.40000000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>79.09999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6633</v>
+        <v>6772</v>
       </c>
       <c r="P24" t="n">
-        <v>6488</v>
+        <v>6571</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
         <v>60</v>
@@ -1959,239 +1959,237 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.49</v>
+        <v>18.92</v>
       </c>
       <c r="C25" t="n">
-        <v>16.79</v>
+        <v>19.22</v>
       </c>
       <c r="D25" t="n">
-        <v>16.31</v>
+        <v>18.64</v>
       </c>
       <c r="E25" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="F25" t="n">
-        <v>14.2</v>
+        <v>13.2</v>
       </c>
       <c r="G25" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>0.62</v>
       </c>
       <c r="J25" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="K25" t="n">
-        <v>89.09</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>91.65000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="M25" t="n">
-        <v>87.73</v>
+        <v>69.45</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>5349</v>
+        <v>6254</v>
       </c>
       <c r="P25" t="n">
-        <v>6445</v>
+        <v>6508</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.27</v>
+        <v>18.78</v>
       </c>
       <c r="C26" t="n">
-        <v>16.31</v>
+        <v>18.89</v>
       </c>
       <c r="D26" t="n">
-        <v>16.24</v>
+        <v>18.67</v>
       </c>
       <c r="E26" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="F26" t="n">
-        <v>14.4</v>
+        <v>12.8</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.18</v>
+        <v>0.63</v>
       </c>
       <c r="J26" t="n">
-        <v>0.15</v>
+        <v>0.57</v>
       </c>
       <c r="K26" t="n">
-        <v>90.12</v>
+        <v>70.87</v>
       </c>
       <c r="L26" t="n">
-        <v>91.63</v>
+        <v>73.17</v>
       </c>
       <c r="M26" t="n">
-        <v>88.84</v>
+        <v>68.48</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5929</v>
       </c>
       <c r="P26" t="n">
-        <v>6422</v>
+        <v>6494</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.37</v>
+        <v>18.59</v>
       </c>
       <c r="C27" t="n">
-        <v>16.42</v>
+        <v>19.26</v>
       </c>
       <c r="D27" t="n">
-        <v>16.3</v>
+        <v>18.18</v>
       </c>
       <c r="E27" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F27" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="K27" t="n">
-        <v>88.97</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>90.09</v>
+        <v>80.08</v>
       </c>
       <c r="M27" t="n">
-        <v>88.26000000000001</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="P27" t="n">
-        <v>6414</v>
+        <v>6494</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.35</v>
+        <v>17.89</v>
       </c>
       <c r="C28" t="n">
-        <v>16.36</v>
+        <v>18.29</v>
       </c>
       <c r="D28" t="n">
-        <v>16.35</v>
+        <v>17.02</v>
       </c>
       <c r="E28" t="n">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="F28" t="n">
-        <v>13.6</v>
+        <v>14.3</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2592</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="J28" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="K28" t="n">
-        <v>84.98</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>85.65000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>84.31</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P28" t="n">
-        <v>6425</v>
+        <v>6488</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
@@ -2203,68 +2201,66 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16.33</v>
+        <v>16.49</v>
       </c>
       <c r="C29" t="n">
-        <v>16.56</v>
+        <v>16.79</v>
       </c>
       <c r="D29" t="n">
-        <v>15.86</v>
+        <v>16.31</v>
       </c>
       <c r="E29" t="n">
         <v>14.6</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2522</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K29" t="n">
-        <v>89.8</v>
+        <v>89.09</v>
       </c>
       <c r="L29" t="n">
-        <v>99.73</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>85.27</v>
+        <v>87.73</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P29" t="n">
-        <v>6422</v>
+        <v>6445</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2273,42 +2269,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>16.27</v>
       </c>
       <c r="C30" t="n">
-        <v>16.37</v>
+        <v>16.31</v>
       </c>
       <c r="D30" t="n">
-        <v>16.2</v>
+        <v>16.24</v>
       </c>
       <c r="E30" t="n">
         <v>14.6</v>
       </c>
       <c r="F30" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="J30" t="n">
         <v>0.15</v>
       </c>
       <c r="K30" t="n">
-        <v>90.44</v>
+        <v>90.12</v>
       </c>
       <c r="L30" t="n">
-        <v>91.61</v>
+        <v>91.63</v>
       </c>
       <c r="M30" t="n">
-        <v>89.09999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2317,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -2335,42 +2331,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.26</v>
+        <v>16.37</v>
       </c>
       <c r="C31" t="n">
-        <v>16.49</v>
+        <v>16.42</v>
       </c>
       <c r="D31" t="n">
-        <v>16.14</v>
+        <v>16.3</v>
       </c>
       <c r="E31" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F31" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="K31" t="n">
-        <v>90.33</v>
+        <v>88.97</v>
       </c>
       <c r="L31" t="n">
-        <v>91.40000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="M31" t="n">
-        <v>89.20999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2379,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
@@ -2397,42 +2393,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.61</v>
+        <v>16.35</v>
       </c>
       <c r="C32" t="n">
-        <v>16.82</v>
+        <v>16.36</v>
       </c>
       <c r="D32" t="n">
-        <v>16.45</v>
+        <v>16.35</v>
       </c>
       <c r="E32" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="F32" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>2592</v>
+      </c>
       <c r="I32" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="J32" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="K32" t="n">
-        <v>87.3</v>
+        <v>84.98</v>
       </c>
       <c r="L32" t="n">
-        <v>89.45</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>86.06</v>
+        <v>84.31</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2441,13 +2439,13 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -2459,42 +2457,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.92</v>
+        <v>16.33</v>
       </c>
       <c r="C33" t="n">
-        <v>17.22</v>
+        <v>16.56</v>
       </c>
       <c r="D33" t="n">
-        <v>16.72</v>
+        <v>15.86</v>
       </c>
       <c r="E33" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F33" t="n">
         <v>14</v>
       </c>
-      <c r="F33" t="n">
-        <v>13.8</v>
-      </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>2522</v>
+      </c>
       <c r="I33" t="n">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="J33" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>83.48999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="L33" t="n">
-        <v>85.67</v>
+        <v>99.73</v>
       </c>
       <c r="M33" t="n">
-        <v>80.43000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2503,16 +2503,16 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6465</v>
+        <v>6422</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>2</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -2521,42 +2521,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.37</v>
+        <v>16.27</v>
       </c>
       <c r="C34" t="n">
-        <v>17.64</v>
+        <v>16.37</v>
       </c>
       <c r="D34" t="n">
-        <v>17.15</v>
+        <v>16.2</v>
       </c>
       <c r="E34" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F34" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="J34" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="K34" t="n">
-        <v>81.5</v>
+        <v>90.44</v>
       </c>
       <c r="L34" t="n">
-        <v>83.2</v>
+        <v>91.61</v>
       </c>
       <c r="M34" t="n">
-        <v>79.69</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2565,16 +2565,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6471</v>
+        <v>6417</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -2583,42 +2583,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.37</v>
+        <v>16.26</v>
       </c>
       <c r="C35" t="n">
-        <v>17.71</v>
+        <v>16.49</v>
       </c>
       <c r="D35" t="n">
-        <v>17.16</v>
+        <v>16.14</v>
       </c>
       <c r="E35" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F35" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="J35" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="K35" t="n">
-        <v>83.11</v>
+        <v>90.33</v>
       </c>
       <c r="L35" t="n">
-        <v>85.31</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>78.94</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2627,16 +2627,16 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6474</v>
+        <v>6425</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -2645,17 +2645,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.78</v>
+        <v>16.61</v>
       </c>
       <c r="C36" t="n">
-        <v>18.2</v>
+        <v>16.82</v>
       </c>
       <c r="D36" t="n">
-        <v>17.44</v>
+        <v>16.45</v>
       </c>
       <c r="E36" t="n">
         <v>14.4</v>
@@ -2668,19 +2668,19 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="J36" t="n">
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="K36" t="n">
-        <v>81.01000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="L36" t="n">
-        <v>82.84999999999999</v>
+        <v>89.45</v>
       </c>
       <c r="M36" t="n">
-        <v>78.13</v>
+        <v>86.06</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2689,16 +2689,16 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>6494</v>
+        <v>6434</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -2707,42 +2707,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.91</v>
+        <v>16.92</v>
       </c>
       <c r="C37" t="n">
-        <v>19.32</v>
+        <v>17.22</v>
       </c>
       <c r="D37" t="n">
-        <v>18.33</v>
+        <v>16.72</v>
       </c>
       <c r="E37" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="F37" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="J37" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
       <c r="K37" t="n">
-        <v>72.89</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>76.66</v>
+        <v>85.67</v>
       </c>
       <c r="M37" t="n">
-        <v>67.31</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2751,16 +2751,16 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>6496</v>
+        <v>6465</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -2769,60 +2769,60 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.65</v>
+        <v>17.37</v>
       </c>
       <c r="C38" t="n">
-        <v>19.86</v>
+        <v>17.64</v>
       </c>
       <c r="D38" t="n">
-        <v>19.37</v>
+        <v>17.15</v>
       </c>
       <c r="E38" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="F38" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="G38" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="J38" t="n">
-        <v>0.65</v>
+        <v>0.33</v>
       </c>
       <c r="K38" t="n">
-        <v>69.28</v>
+        <v>81.5</v>
       </c>
       <c r="L38" t="n">
-        <v>71.03</v>
+        <v>83.2</v>
       </c>
       <c r="M38" t="n">
-        <v>67.26000000000001</v>
+        <v>79.69</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6511</v>
+        <v>6471</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -2831,60 +2831,60 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.34</v>
+        <v>17.37</v>
       </c>
       <c r="C39" t="n">
-        <v>19.5</v>
+        <v>17.71</v>
       </c>
       <c r="D39" t="n">
-        <v>19.25</v>
+        <v>17.16</v>
       </c>
       <c r="E39" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="F39" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="G39" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.68</v>
+        <v>0.33</v>
       </c>
       <c r="J39" t="n">
-        <v>0.67</v>
+        <v>0.28</v>
       </c>
       <c r="K39" t="n">
-        <v>69.37</v>
+        <v>83.11</v>
       </c>
       <c r="L39" t="n">
-        <v>70.14</v>
+        <v>85.31</v>
       </c>
       <c r="M39" t="n">
-        <v>68.55</v>
+        <v>78.94</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6536</v>
+        <v>6474</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -2893,364 +2893,364 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.29</v>
+        <v>17.78</v>
       </c>
       <c r="C40" t="n">
-        <v>19.86</v>
+        <v>18.2</v>
       </c>
       <c r="D40" t="n">
-        <v>19.1</v>
+        <v>17.44</v>
       </c>
       <c r="E40" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="F40" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="G40" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="J40" t="n">
-        <v>0.66</v>
+        <v>0.34</v>
       </c>
       <c r="K40" t="n">
-        <v>68.94</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>69.94</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>66.66</v>
+        <v>78.13</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4462</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6539</v>
+        <v>6494</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20.82</v>
+        <v>18.91</v>
       </c>
       <c r="C41" t="n">
-        <v>21.19</v>
+        <v>19.32</v>
       </c>
       <c r="D41" t="n">
-        <v>19.8</v>
+        <v>18.33</v>
       </c>
       <c r="E41" t="n">
-        <v>12.3</v>
+        <v>13.9</v>
       </c>
       <c r="F41" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="G41" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>1.02</v>
+        <v>0.59</v>
       </c>
       <c r="J41" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="K41" t="n">
-        <v>58.55</v>
+        <v>72.89</v>
       </c>
       <c r="L41" t="n">
-        <v>67.09</v>
+        <v>76.66</v>
       </c>
       <c r="M41" t="n">
-        <v>55.27</v>
+        <v>67.31</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6579</v>
+        <v>6496</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21.17</v>
+        <v>19.65</v>
       </c>
       <c r="C42" t="n">
-        <v>21.41</v>
+        <v>19.86</v>
       </c>
       <c r="D42" t="n">
-        <v>20.87</v>
+        <v>19.37</v>
       </c>
       <c r="E42" t="n">
-        <v>12.3</v>
+        <v>13.8</v>
       </c>
       <c r="F42" t="n">
-        <v>11.8</v>
+        <v>13.5</v>
       </c>
       <c r="G42" t="n">
-        <v>419</v>
+        <v>55</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="K42" t="n">
-        <v>57.42</v>
+        <v>69.28</v>
       </c>
       <c r="L42" t="n">
-        <v>60.15</v>
+        <v>71.03</v>
       </c>
       <c r="M42" t="n">
-        <v>55.34</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6777</v>
+        <v>2267</v>
       </c>
       <c r="P42" t="n">
-        <v>6613</v>
+        <v>6511</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21.2</v>
+        <v>19.34</v>
       </c>
       <c r="C43" t="n">
-        <v>21.55</v>
+        <v>19.5</v>
       </c>
       <c r="D43" t="n">
-        <v>20.85</v>
+        <v>19.25</v>
       </c>
       <c r="E43" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="F43" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
       <c r="G43" t="n">
-        <v>629</v>
+        <v>67</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>1.04</v>
+        <v>0.68</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="K43" t="n">
-        <v>58.56</v>
+        <v>69.37</v>
       </c>
       <c r="L43" t="n">
-        <v>61.5</v>
+        <v>70.14</v>
       </c>
       <c r="M43" t="n">
-        <v>56.2</v>
+        <v>68.55</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6849</v>
+        <v>4721</v>
       </c>
       <c r="P43" t="n">
-        <v>6647</v>
+        <v>6536</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.75</v>
+        <v>19.29</v>
       </c>
       <c r="C44" t="n">
-        <v>21.44</v>
+        <v>19.86</v>
       </c>
       <c r="D44" t="n">
-        <v>20.1</v>
+        <v>19.1</v>
       </c>
       <c r="E44" t="n">
-        <v>12.6</v>
+        <v>13.4</v>
       </c>
       <c r="F44" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="G44" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="K44" t="n">
-        <v>59.8</v>
+        <v>68.94</v>
       </c>
       <c r="L44" t="n">
-        <v>61.83</v>
+        <v>69.94</v>
       </c>
       <c r="M44" t="n">
-        <v>58.57</v>
+        <v>66.66</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6901</v>
+        <v>4462</v>
       </c>
       <c r="P44" t="n">
-        <v>6676</v>
+        <v>6539</v>
       </c>
       <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>4</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
         <v>5</v>
-      </c>
-      <c r="R44" t="n">
-        <v>5</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>20.11</v>
+        <v>20.82</v>
       </c>
       <c r="C45" t="n">
-        <v>21.09</v>
+        <v>21.19</v>
       </c>
       <c r="D45" t="n">
-        <v>19.18</v>
+        <v>19.8</v>
       </c>
       <c r="E45" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F45" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
       <c r="G45" t="n">
-        <v>471</v>
+        <v>215</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="J45" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="K45" t="n">
-        <v>63.63</v>
+        <v>58.55</v>
       </c>
       <c r="L45" t="n">
-        <v>67.22</v>
+        <v>67.09</v>
       </c>
       <c r="M45" t="n">
-        <v>59.39</v>
+        <v>55.27</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6810</v>
+        <v>6250</v>
       </c>
       <c r="P45" t="n">
-        <v>6613</v>
+        <v>6579</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R45" t="n">
         <v>5</v>
@@ -3265,60 +3265,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.28</v>
+        <v>21.17</v>
       </c>
       <c r="C46" t="n">
-        <v>19.69</v>
+        <v>21.41</v>
       </c>
       <c r="D46" t="n">
-        <v>18.97</v>
+        <v>20.87</v>
       </c>
       <c r="E46" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G46" t="n">
-        <v>300</v>
+        <v>419</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="J46" t="n">
-        <v>0.65</v>
+        <v>0.99</v>
       </c>
       <c r="K46" t="n">
-        <v>66.97</v>
+        <v>57.42</v>
       </c>
       <c r="L46" t="n">
-        <v>70.23999999999999</v>
+        <v>60.15</v>
       </c>
       <c r="M46" t="n">
-        <v>65.22</v>
+        <v>55.34</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6681</v>
+        <v>6777</v>
       </c>
       <c r="P46" t="n">
-        <v>6565</v>
+        <v>6613</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="n">
         <v>60</v>
@@ -3327,60 +3327,60 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18.64</v>
+        <v>21.2</v>
       </c>
       <c r="C47" t="n">
-        <v>20.12</v>
+        <v>21.55</v>
       </c>
       <c r="D47" t="n">
-        <v>17.71</v>
+        <v>20.85</v>
       </c>
       <c r="E47" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="F47" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="G47" t="n">
-        <v>347</v>
+        <v>629</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.61</v>
+        <v>1.04</v>
       </c>
       <c r="J47" t="n">
-        <v>0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>71.42</v>
+        <v>58.56</v>
       </c>
       <c r="L47" t="n">
-        <v>76.48</v>
+        <v>61.5</v>
       </c>
       <c r="M47" t="n">
-        <v>66.62</v>
+        <v>56.2</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6739</v>
+        <v>6849</v>
       </c>
       <c r="P47" t="n">
-        <v>6565</v>
+        <v>6647</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="n">
         <v>60</v>
@@ -3389,125 +3389,125 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.37</v>
+        <v>20.75</v>
       </c>
       <c r="C48" t="n">
-        <v>18.2</v>
+        <v>21.44</v>
       </c>
       <c r="D48" t="n">
-        <v>16.67</v>
+        <v>20.1</v>
       </c>
       <c r="E48" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="F48" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="G48" t="n">
-        <v>167</v>
+        <v>612</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="J48" t="n">
-        <v>0.26</v>
+        <v>0.9</v>
       </c>
       <c r="K48" t="n">
-        <v>79.89</v>
+        <v>59.8</v>
       </c>
       <c r="L48" t="n">
-        <v>86.01000000000001</v>
+        <v>61.83</v>
       </c>
       <c r="M48" t="n">
-        <v>75.15000000000001</v>
+        <v>58.57</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6499</v>
+        <v>6901</v>
       </c>
       <c r="P48" t="n">
-        <v>6494</v>
+        <v>6676</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T48" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 07:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15.89</v>
+        <v>20.11</v>
       </c>
       <c r="C49" t="n">
-        <v>16.51</v>
+        <v>21.09</v>
       </c>
       <c r="D49" t="n">
-        <v>15.53</v>
+        <v>19.18</v>
       </c>
       <c r="E49" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="F49" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="G49" t="n">
-        <v>40</v>
+        <v>471</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.14</v>
+        <v>0.85</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1</v>
+        <v>0.72</v>
       </c>
       <c r="K49" t="n">
-        <v>91.95</v>
+        <v>63.63</v>
       </c>
       <c r="L49" t="n">
-        <v>93.86</v>
+        <v>67.22</v>
       </c>
       <c r="M49" t="n">
-        <v>87.84999999999999</v>
+        <v>59.39</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4793</v>
+        <v>6810</v>
       </c>
       <c r="P49" t="n">
-        <v>6442</v>
+        <v>6613</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,364 +533,364 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.77</v>
+        <v>22.51</v>
       </c>
       <c r="C2" t="n">
-        <v>19.89</v>
+        <v>22.96</v>
       </c>
       <c r="D2" t="n">
-        <v>19.53</v>
+        <v>22.11</v>
       </c>
       <c r="E2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F2" t="n">
         <v>10.9</v>
       </c>
-      <c r="F2" t="n">
-        <v>10.7</v>
-      </c>
       <c r="G2" t="n">
-        <v>358</v>
+        <v>404</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.98</v>
+        <v>1.38</v>
       </c>
       <c r="J2" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="K2" t="n">
-        <v>57.03</v>
+        <v>49.12</v>
       </c>
       <c r="L2" t="n">
-        <v>57.87</v>
+        <v>51.28</v>
       </c>
       <c r="M2" t="n">
-        <v>55.43</v>
+        <v>47.37</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6719</v>
+        <v>6753</v>
       </c>
       <c r="P2" t="n">
-        <v>6542</v>
+        <v>6573</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.89</v>
+        <v>22.01</v>
       </c>
       <c r="C3" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D3" t="n">
-        <v>18.08</v>
+        <v>21.62</v>
       </c>
       <c r="E3" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G3" t="n">
-        <v>212</v>
+        <v>452</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="J3" t="n">
-        <v>0.35</v>
+        <v>1.27</v>
       </c>
       <c r="K3" t="n">
-        <v>69.7</v>
+        <v>49.71</v>
       </c>
       <c r="L3" t="n">
-        <v>82.87</v>
+        <v>51.65</v>
       </c>
       <c r="M3" t="n">
-        <v>57.89</v>
+        <v>46.69</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6691</v>
+        <v>6767</v>
       </c>
       <c r="P3" t="n">
-        <v>6514</v>
+        <v>6576</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.5</v>
+        <v>21.59</v>
       </c>
       <c r="C4" t="n">
-        <v>17.9</v>
+        <v>22.58</v>
       </c>
       <c r="D4" t="n">
-        <v>17.26</v>
+        <v>20.76</v>
       </c>
       <c r="E4" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="F4" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="G4" t="n">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.31</v>
+        <v>1.24</v>
       </c>
       <c r="J4" t="n">
-        <v>0.25</v>
+        <v>1.07</v>
       </c>
       <c r="K4" t="n">
-        <v>84.14</v>
+        <v>51.87</v>
       </c>
       <c r="L4" t="n">
-        <v>87.05</v>
+        <v>56.03</v>
       </c>
       <c r="M4" t="n">
-        <v>79.48999999999999</v>
+        <v>45.92</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3786</v>
+        <v>6796</v>
       </c>
       <c r="P4" t="n">
-        <v>6422</v>
+        <v>6599</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.02</v>
+        <v>20.19</v>
       </c>
       <c r="C5" t="n">
-        <v>17.27</v>
+        <v>20.64</v>
       </c>
       <c r="D5" t="n">
-        <v>16.92</v>
+        <v>19.53</v>
       </c>
       <c r="E5" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F5" t="n">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.25</v>
+        <v>1.05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.21</v>
+        <v>0.95</v>
       </c>
       <c r="K5" t="n">
-        <v>86.8</v>
+        <v>55.29</v>
       </c>
       <c r="L5" t="n">
-        <v>88.91</v>
+        <v>57.87</v>
       </c>
       <c r="M5" t="n">
-        <v>81.98999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1246</v>
+        <v>6767</v>
       </c>
       <c r="P5" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.89</v>
+        <v>18.89</v>
       </c>
       <c r="C6" t="n">
-        <v>17.03</v>
+        <v>19.62</v>
       </c>
       <c r="D6" t="n">
-        <v>16.78</v>
+        <v>18.08</v>
       </c>
       <c r="E6" t="n">
-        <v>14.9</v>
+        <v>13.1</v>
       </c>
       <c r="F6" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="J6" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="K6" t="n">
-        <v>88.48999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="L6" t="n">
-        <v>90.31</v>
+        <v>82.87</v>
       </c>
       <c r="M6" t="n">
-        <v>85.76000000000001</v>
+        <v>57.89</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="P6" t="n">
-        <v>6417</v>
+        <v>6514</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
         <v>2</v>
       </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.13</v>
+        <v>17.5</v>
       </c>
       <c r="C7" t="n">
-        <v>17.32</v>
+        <v>17.9</v>
       </c>
       <c r="D7" t="n">
-        <v>16.89</v>
+        <v>17.26</v>
       </c>
       <c r="E7" t="n">
         <v>14.7</v>
       </c>
       <c r="F7" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="J7" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="K7" t="n">
-        <v>85.90000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="L7" t="n">
-        <v>88.63</v>
+        <v>87.05</v>
       </c>
       <c r="M7" t="n">
-        <v>83.40000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="P7" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>2</v>
@@ -905,48 +905,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.01</v>
+        <v>17.02</v>
       </c>
       <c r="C8" t="n">
-        <v>17.08</v>
+        <v>17.27</v>
       </c>
       <c r="D8" t="n">
-        <v>16.93</v>
+        <v>16.92</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F8" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J8" t="n">
         <v>0.21</v>
       </c>
       <c r="K8" t="n">
-        <v>88.16</v>
+        <v>86.8</v>
       </c>
       <c r="L8" t="n">
-        <v>88.7</v>
+        <v>88.91</v>
       </c>
       <c r="M8" t="n">
-        <v>87.34999999999999</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="P8" t="n">
         <v>6414</v>
@@ -955,7 +955,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -967,42 +967,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.07</v>
+        <v>16.89</v>
       </c>
       <c r="C9" t="n">
-        <v>17.29</v>
+        <v>17.03</v>
       </c>
       <c r="D9" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F9" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K9" t="n">
-        <v>88.06999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>89.45999999999999</v>
+        <v>90.31</v>
       </c>
       <c r="M9" t="n">
-        <v>85.97</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1029,42 +1029,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.44</v>
+        <v>17.13</v>
       </c>
       <c r="C10" t="n">
-        <v>17.52</v>
+        <v>17.32</v>
       </c>
       <c r="D10" t="n">
-        <v>17.31</v>
+        <v>16.89</v>
       </c>
       <c r="E10" t="n">
         <v>14.7</v>
       </c>
       <c r="F10" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="J10" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="K10" t="n">
-        <v>84.31999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>85.27</v>
+        <v>88.63</v>
       </c>
       <c r="M10" t="n">
-        <v>82.56999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1073,16 +1073,16 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1091,42 +1091,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.22</v>
+        <v>17.01</v>
       </c>
       <c r="C11" t="n">
-        <v>17.34</v>
+        <v>17.08</v>
       </c>
       <c r="D11" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E11" t="n">
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="J11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="K11" t="n">
-        <v>87.37</v>
+        <v>88.16</v>
       </c>
       <c r="L11" t="n">
-        <v>88.34999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="M11" t="n">
-        <v>86.23</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1153,42 +1153,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.38</v>
+        <v>17.07</v>
       </c>
       <c r="C12" t="n">
-        <v>17.5</v>
+        <v>17.29</v>
       </c>
       <c r="D12" t="n">
-        <v>17.22</v>
+        <v>16.93</v>
       </c>
       <c r="E12" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="K12" t="n">
-        <v>87.89</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>89.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>87.03</v>
+        <v>85.97</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1197,13 +1197,13 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1215,42 +1215,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.51</v>
+        <v>17.44</v>
       </c>
       <c r="C13" t="n">
-        <v>17.64</v>
+        <v>17.52</v>
       </c>
       <c r="D13" t="n">
-        <v>17.34</v>
+        <v>17.31</v>
       </c>
       <c r="E13" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="F13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="J13" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="K13" t="n">
-        <v>88.95</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>90.3</v>
+        <v>85.27</v>
       </c>
       <c r="M13" t="n">
-        <v>87.78</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1259,16 +1259,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6437</v>
+        <v>6417</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1277,20 +1277,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.73</v>
+        <v>17.22</v>
       </c>
       <c r="C14" t="n">
-        <v>18.06</v>
+        <v>17.34</v>
       </c>
       <c r="D14" t="n">
-        <v>17.42</v>
+        <v>17.11</v>
       </c>
       <c r="E14" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>14.9</v>
@@ -1300,19 +1300,19 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="J14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="K14" t="n">
-        <v>85.27</v>
+        <v>87.37</v>
       </c>
       <c r="L14" t="n">
-        <v>88.19</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>81.95</v>
+        <v>86.23</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1321,13 +1321,13 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1339,42 +1339,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.36</v>
+        <v>17.38</v>
       </c>
       <c r="C15" t="n">
-        <v>18.45</v>
+        <v>17.5</v>
       </c>
       <c r="D15" t="n">
-        <v>18.19</v>
+        <v>17.22</v>
       </c>
       <c r="E15" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="F15" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="J15" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="K15" t="n">
-        <v>80.73</v>
+        <v>87.89</v>
       </c>
       <c r="L15" t="n">
-        <v>81.93000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="M15" t="n">
-        <v>79.83</v>
+        <v>87.03</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1383,16 +1383,16 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6471</v>
+        <v>6408</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.81</v>
+        <v>17.51</v>
       </c>
       <c r="C16" t="n">
-        <v>19.07</v>
+        <v>17.64</v>
       </c>
       <c r="D16" t="n">
-        <v>18.51</v>
+        <v>17.34</v>
       </c>
       <c r="E16" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="F16" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="K16" t="n">
-        <v>76.59999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="L16" t="n">
-        <v>79.87</v>
+        <v>90.3</v>
       </c>
       <c r="M16" t="n">
-        <v>74.01000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1445,16 +1445,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6482</v>
+        <v>6437</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1463,42 +1463,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.81</v>
+        <v>17.73</v>
       </c>
       <c r="C17" t="n">
-        <v>20.67</v>
+        <v>18.06</v>
       </c>
       <c r="D17" t="n">
-        <v>18.96</v>
+        <v>17.42</v>
       </c>
       <c r="E17" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="F17" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="J17" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="K17" t="n">
-        <v>69.16</v>
+        <v>85.27</v>
       </c>
       <c r="L17" t="n">
-        <v>75.04000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="M17" t="n">
-        <v>63.43</v>
+        <v>81.95</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1507,16 +1507,16 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6496</v>
+        <v>6457</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1525,364 +1525,364 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.22</v>
+        <v>18.36</v>
       </c>
       <c r="C18" t="n">
-        <v>21.6</v>
+        <v>18.45</v>
       </c>
       <c r="D18" t="n">
-        <v>20.76</v>
+        <v>18.19</v>
       </c>
       <c r="E18" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="G18" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
       <c r="K18" t="n">
-        <v>60.52</v>
+        <v>80.73</v>
       </c>
       <c r="L18" t="n">
-        <v>62.17</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>58.42</v>
+        <v>79.83</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6516</v>
+        <v>6471</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21.62</v>
+        <v>18.81</v>
       </c>
       <c r="C19" t="n">
-        <v>21.84</v>
+        <v>19.07</v>
       </c>
       <c r="D19" t="n">
-        <v>21.44</v>
+        <v>18.51</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F19" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="G19" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="K19" t="n">
-        <v>58.13</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>60.32</v>
+        <v>79.87</v>
       </c>
       <c r="M19" t="n">
-        <v>56.76</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6548</v>
+        <v>6482</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.96</v>
+        <v>19.81</v>
       </c>
       <c r="C20" t="n">
-        <v>22.41</v>
+        <v>20.67</v>
       </c>
       <c r="D20" t="n">
-        <v>21.77</v>
+        <v>18.96</v>
       </c>
       <c r="E20" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="F20" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="G20" t="n">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>1.15</v>
+        <v>0.71</v>
       </c>
       <c r="J20" t="n">
-        <v>1.11</v>
+        <v>0.54</v>
       </c>
       <c r="K20" t="n">
-        <v>55.95</v>
+        <v>69.16</v>
       </c>
       <c r="L20" t="n">
-        <v>57.92</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>54.15</v>
+        <v>63.43</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6573</v>
+        <v>6496</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.46</v>
+        <v>21.22</v>
       </c>
       <c r="C21" t="n">
-        <v>23.17</v>
+        <v>21.6</v>
       </c>
       <c r="D21" t="n">
-        <v>21.82</v>
+        <v>20.76</v>
       </c>
       <c r="E21" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F21" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>383</v>
+        <v>73</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>1.29</v>
+        <v>0.99</v>
       </c>
       <c r="J21" t="n">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="K21" t="n">
-        <v>52.56</v>
+        <v>60.52</v>
       </c>
       <c r="L21" t="n">
-        <v>54.35</v>
+        <v>62.17</v>
       </c>
       <c r="M21" t="n">
-        <v>50.6</v>
+        <v>58.42</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6763</v>
+        <v>2990</v>
       </c>
       <c r="P21" t="n">
-        <v>6593</v>
+        <v>6516</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.1</v>
+        <v>21.62</v>
       </c>
       <c r="C22" t="n">
-        <v>22.92</v>
+        <v>21.84</v>
       </c>
       <c r="D22" t="n">
-        <v>21.76</v>
+        <v>21.44</v>
       </c>
       <c r="E22" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>11.5</v>
+        <v>12.7</v>
       </c>
       <c r="G22" t="n">
-        <v>479</v>
+        <v>137</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="J22" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="K22" t="n">
-        <v>53.58</v>
+        <v>58.13</v>
       </c>
       <c r="L22" t="n">
-        <v>55.95</v>
+        <v>60.32</v>
       </c>
       <c r="M22" t="n">
-        <v>51.48</v>
+        <v>56.76</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6739</v>
+        <v>5684</v>
       </c>
       <c r="P22" t="n">
-        <v>6582</v>
+        <v>6548</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.45</v>
+        <v>21.96</v>
       </c>
       <c r="C23" t="n">
-        <v>22.62</v>
+        <v>22.41</v>
       </c>
       <c r="D23" t="n">
-        <v>20.83</v>
+        <v>21.77</v>
       </c>
       <c r="E23" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G23" t="n">
-        <v>640</v>
+        <v>205</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J23" t="n">
         <v>1.11</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.92</v>
-      </c>
       <c r="K23" t="n">
-        <v>56.35</v>
+        <v>55.95</v>
       </c>
       <c r="L23" t="n">
-        <v>62.61</v>
+        <v>57.92</v>
       </c>
       <c r="M23" t="n">
-        <v>51.88</v>
+        <v>54.15</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6810</v>
+        <v>6619</v>
       </c>
       <c r="P23" t="n">
-        <v>6610</v>
+        <v>6573</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
         <v>6</v>
@@ -1897,60 +1897,60 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.67</v>
+        <v>22.46</v>
       </c>
       <c r="C24" t="n">
-        <v>20.85</v>
+        <v>23.17</v>
       </c>
       <c r="D24" t="n">
-        <v>19.11</v>
+        <v>21.82</v>
       </c>
       <c r="E24" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F24" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="G24" t="n">
-        <v>279</v>
+        <v>383</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>1.21</v>
       </c>
       <c r="K24" t="n">
-        <v>66.39</v>
+        <v>52.56</v>
       </c>
       <c r="L24" t="n">
-        <v>68.68000000000001</v>
+        <v>54.35</v>
       </c>
       <c r="M24" t="n">
-        <v>61.4</v>
+        <v>50.6</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6772</v>
+        <v>6763</v>
       </c>
       <c r="P24" t="n">
-        <v>6571</v>
+        <v>6593</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T24" t="n">
         <v>60</v>
@@ -1959,122 +1959,122 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18.92</v>
+        <v>22.1</v>
       </c>
       <c r="C25" t="n">
-        <v>19.22</v>
+        <v>22.92</v>
       </c>
       <c r="D25" t="n">
-        <v>18.64</v>
+        <v>21.76</v>
       </c>
       <c r="E25" t="n">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="F25" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="G25" t="n">
-        <v>143</v>
+        <v>479</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="J25" t="n">
-        <v>0.58</v>
+        <v>1.14</v>
       </c>
       <c r="K25" t="n">
-        <v>71.48999999999999</v>
+        <v>53.58</v>
       </c>
       <c r="L25" t="n">
-        <v>73.28</v>
+        <v>55.95</v>
       </c>
       <c r="M25" t="n">
-        <v>69.45</v>
+        <v>51.48</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6254</v>
+        <v>6739</v>
       </c>
       <c r="P25" t="n">
-        <v>6508</v>
+        <v>6582</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.78</v>
+        <v>21.45</v>
       </c>
       <c r="C26" t="n">
-        <v>18.89</v>
+        <v>22.62</v>
       </c>
       <c r="D26" t="n">
-        <v>18.67</v>
+        <v>20.83</v>
       </c>
       <c r="E26" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="F26" t="n">
-        <v>12.8</v>
+        <v>11.1</v>
       </c>
       <c r="G26" t="n">
-        <v>134</v>
+        <v>640</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.63</v>
+        <v>1.11</v>
       </c>
       <c r="J26" t="n">
-        <v>0.57</v>
+        <v>0.92</v>
       </c>
       <c r="K26" t="n">
-        <v>70.87</v>
+        <v>56.35</v>
       </c>
       <c r="L26" t="n">
-        <v>73.17</v>
+        <v>62.61</v>
       </c>
       <c r="M26" t="n">
-        <v>68.48</v>
+        <v>51.88</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>5929</v>
+        <v>6810</v>
       </c>
       <c r="P26" t="n">
-        <v>6494</v>
+        <v>6610</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
         <v>60</v>
@@ -2083,60 +2083,60 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18.59</v>
+        <v>19.67</v>
       </c>
       <c r="C27" t="n">
-        <v>19.26</v>
+        <v>20.85</v>
       </c>
       <c r="D27" t="n">
-        <v>18.18</v>
+        <v>19.11</v>
       </c>
       <c r="E27" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="F27" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="G27" t="n">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="J27" t="n">
-        <v>0.41</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>76.48999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="L27" t="n">
-        <v>80.08</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>71.70999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5478</v>
+        <v>6772</v>
       </c>
       <c r="P27" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
         <v>60</v>
@@ -2145,307 +2145,305 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.89</v>
+        <v>18.92</v>
       </c>
       <c r="C28" t="n">
-        <v>18.29</v>
+        <v>19.22</v>
       </c>
       <c r="D28" t="n">
-        <v>17.02</v>
+        <v>18.64</v>
       </c>
       <c r="E28" t="n">
-        <v>14.8</v>
+        <v>13.6</v>
       </c>
       <c r="F28" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="G28" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="J28" t="n">
-        <v>0.24</v>
+        <v>0.58</v>
       </c>
       <c r="K28" t="n">
-        <v>82.51000000000001</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>87.40000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="M28" t="n">
-        <v>79.09999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6633</v>
+        <v>6254</v>
       </c>
       <c r="P28" t="n">
-        <v>6488</v>
+        <v>6508</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16.49</v>
+        <v>18.78</v>
       </c>
       <c r="C29" t="n">
-        <v>16.79</v>
+        <v>18.89</v>
       </c>
       <c r="D29" t="n">
-        <v>16.31</v>
+        <v>18.67</v>
       </c>
       <c r="E29" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="F29" t="n">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="G29" t="n">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="J29" t="n">
-        <v>0.15</v>
+        <v>0.57</v>
       </c>
       <c r="K29" t="n">
-        <v>89.09</v>
+        <v>70.87</v>
       </c>
       <c r="L29" t="n">
-        <v>91.65000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="M29" t="n">
-        <v>87.73</v>
+        <v>68.48</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>5349</v>
+        <v>5929</v>
       </c>
       <c r="P29" t="n">
-        <v>6445</v>
+        <v>6494</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>16.27</v>
+        <v>18.59</v>
       </c>
       <c r="C30" t="n">
-        <v>16.31</v>
+        <v>19.26</v>
       </c>
       <c r="D30" t="n">
-        <v>16.24</v>
+        <v>18.18</v>
       </c>
       <c r="E30" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F30" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="K30" t="n">
-        <v>90.12</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>91.63</v>
+        <v>80.08</v>
       </c>
       <c r="M30" t="n">
-        <v>88.84</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="P30" t="n">
-        <v>6422</v>
+        <v>6494</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.37</v>
+        <v>17.89</v>
       </c>
       <c r="C31" t="n">
-        <v>16.42</v>
+        <v>18.29</v>
       </c>
       <c r="D31" t="n">
-        <v>16.3</v>
+        <v>17.02</v>
       </c>
       <c r="E31" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="F31" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J31" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="K31" t="n">
-        <v>88.97</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>90.09</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>88.26000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P31" t="n">
-        <v>6414</v>
+        <v>6488</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.35</v>
+        <v>16.49</v>
       </c>
       <c r="C32" t="n">
-        <v>16.36</v>
+        <v>16.79</v>
       </c>
       <c r="D32" t="n">
-        <v>16.35</v>
+        <v>16.31</v>
       </c>
       <c r="E32" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="F32" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2592</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="K32" t="n">
-        <v>84.98</v>
+        <v>89.09</v>
       </c>
       <c r="L32" t="n">
-        <v>85.65000000000001</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>84.31</v>
+        <v>87.73</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P32" t="n">
-        <v>6425</v>
+        <v>6445</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -2457,44 +2455,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.33</v>
+        <v>16.27</v>
       </c>
       <c r="C33" t="n">
-        <v>16.56</v>
+        <v>16.31</v>
       </c>
       <c r="D33" t="n">
-        <v>15.86</v>
+        <v>16.24</v>
       </c>
       <c r="E33" t="n">
         <v>14.6</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="n">
-        <v>2522</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K33" t="n">
-        <v>89.8</v>
+        <v>90.12</v>
       </c>
       <c r="L33" t="n">
-        <v>99.73</v>
+        <v>91.63</v>
       </c>
       <c r="M33" t="n">
-        <v>85.27</v>
+        <v>88.84</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2509,10 +2505,10 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -2521,42 +2517,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.27</v>
+        <v>16.37</v>
       </c>
       <c r="C34" t="n">
-        <v>16.37</v>
+        <v>16.42</v>
       </c>
       <c r="D34" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="E34" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F34" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="K34" t="n">
-        <v>90.44</v>
+        <v>88.97</v>
       </c>
       <c r="L34" t="n">
-        <v>91.61</v>
+        <v>90.09</v>
       </c>
       <c r="M34" t="n">
-        <v>89.09999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2565,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
@@ -2583,42 +2579,44 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.26</v>
+        <v>16.35</v>
       </c>
       <c r="C35" t="n">
-        <v>16.49</v>
+        <v>16.36</v>
       </c>
       <c r="D35" t="n">
-        <v>16.14</v>
+        <v>16.35</v>
       </c>
       <c r="E35" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F35" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>2592</v>
+      </c>
       <c r="I35" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="J35" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K35" t="n">
-        <v>90.33</v>
+        <v>84.98</v>
       </c>
       <c r="L35" t="n">
-        <v>91.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>89.20999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2630,10 +2628,10 @@
         <v>6425</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -2645,42 +2643,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.61</v>
+        <v>16.33</v>
       </c>
       <c r="C36" t="n">
-        <v>16.82</v>
+        <v>16.56</v>
       </c>
       <c r="D36" t="n">
-        <v>16.45</v>
+        <v>15.86</v>
       </c>
       <c r="E36" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F36" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>2522</v>
+      </c>
       <c r="I36" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J36" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>87.3</v>
+        <v>89.8</v>
       </c>
       <c r="L36" t="n">
-        <v>89.45</v>
+        <v>99.73</v>
       </c>
       <c r="M36" t="n">
-        <v>86.06</v>
+        <v>85.27</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2689,16 +2689,16 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>6434</v>
+        <v>6422</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -2707,42 +2707,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.92</v>
+        <v>16.27</v>
       </c>
       <c r="C37" t="n">
-        <v>17.22</v>
+        <v>16.37</v>
       </c>
       <c r="D37" t="n">
-        <v>16.72</v>
+        <v>16.2</v>
       </c>
       <c r="E37" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F37" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="J37" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="K37" t="n">
-        <v>83.48999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="L37" t="n">
-        <v>85.67</v>
+        <v>91.61</v>
       </c>
       <c r="M37" t="n">
-        <v>80.43000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2751,16 +2751,16 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>6465</v>
+        <v>6417</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -2769,42 +2769,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.37</v>
+        <v>16.26</v>
       </c>
       <c r="C38" t="n">
-        <v>17.64</v>
+        <v>16.49</v>
       </c>
       <c r="D38" t="n">
-        <v>17.15</v>
+        <v>16.14</v>
       </c>
       <c r="E38" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="J38" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="K38" t="n">
-        <v>81.5</v>
+        <v>90.33</v>
       </c>
       <c r="L38" t="n">
-        <v>83.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>79.69</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -2813,16 +2813,16 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6471</v>
+        <v>6425</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -2831,42 +2831,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.37</v>
+        <v>16.61</v>
       </c>
       <c r="C39" t="n">
-        <v>17.71</v>
+        <v>16.82</v>
       </c>
       <c r="D39" t="n">
-        <v>17.16</v>
+        <v>16.45</v>
       </c>
       <c r="E39" t="n">
         <v>14.4</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="J39" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="K39" t="n">
-        <v>83.11</v>
+        <v>87.3</v>
       </c>
       <c r="L39" t="n">
-        <v>85.31</v>
+        <v>89.45</v>
       </c>
       <c r="M39" t="n">
-        <v>78.94</v>
+        <v>86.06</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6474</v>
+        <v>6434</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -2893,42 +2893,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.78</v>
+        <v>16.92</v>
       </c>
       <c r="C40" t="n">
-        <v>18.2</v>
+        <v>17.22</v>
       </c>
       <c r="D40" t="n">
-        <v>17.44</v>
+        <v>16.72</v>
       </c>
       <c r="E40" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="F40" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="J40" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="K40" t="n">
-        <v>81.01000000000001</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>82.84999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="M40" t="n">
-        <v>78.13</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6494</v>
+        <v>6465</v>
       </c>
       <c r="Q40" t="n">
         <v>2</v>
@@ -2955,42 +2955,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18.91</v>
+        <v>17.37</v>
       </c>
       <c r="C41" t="n">
-        <v>19.32</v>
+        <v>17.64</v>
       </c>
       <c r="D41" t="n">
-        <v>18.33</v>
+        <v>17.15</v>
       </c>
       <c r="E41" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F41" t="n">
         <v>13.9</v>
-      </c>
-      <c r="F41" t="n">
-        <v>13.1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="J41" t="n">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="K41" t="n">
-        <v>72.89</v>
+        <v>81.5</v>
       </c>
       <c r="L41" t="n">
-        <v>76.66</v>
+        <v>83.2</v>
       </c>
       <c r="M41" t="n">
-        <v>67.31</v>
+        <v>79.69</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2999,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6496</v>
+        <v>6471</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3017,60 +3017,60 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.65</v>
+        <v>17.37</v>
       </c>
       <c r="C42" t="n">
-        <v>19.86</v>
+        <v>17.71</v>
       </c>
       <c r="D42" t="n">
-        <v>19.37</v>
+        <v>17.16</v>
       </c>
       <c r="E42" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="F42" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G42" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="J42" t="n">
-        <v>0.65</v>
+        <v>0.28</v>
       </c>
       <c r="K42" t="n">
-        <v>69.28</v>
+        <v>83.11</v>
       </c>
       <c r="L42" t="n">
-        <v>71.03</v>
+        <v>85.31</v>
       </c>
       <c r="M42" t="n">
-        <v>67.26000000000001</v>
+        <v>78.94</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6511</v>
+        <v>6474</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -3079,60 +3079,60 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.34</v>
+        <v>17.78</v>
       </c>
       <c r="C43" t="n">
-        <v>19.5</v>
+        <v>18.2</v>
       </c>
       <c r="D43" t="n">
-        <v>19.25</v>
+        <v>17.44</v>
       </c>
       <c r="E43" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="F43" t="n">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="G43" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="J43" t="n">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
       <c r="K43" t="n">
-        <v>69.37</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>70.14</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>68.55</v>
+        <v>78.13</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6536</v>
+        <v>6494</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3141,54 +3141,54 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.29</v>
+        <v>18.91</v>
       </c>
       <c r="C44" t="n">
-        <v>19.86</v>
+        <v>19.32</v>
       </c>
       <c r="D44" t="n">
-        <v>19.1</v>
+        <v>18.33</v>
       </c>
       <c r="E44" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="F44" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="G44" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="J44" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="K44" t="n">
-        <v>68.94</v>
+        <v>72.89</v>
       </c>
       <c r="L44" t="n">
-        <v>69.94</v>
+        <v>76.66</v>
       </c>
       <c r="M44" t="n">
-        <v>66.66</v>
+        <v>67.31</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4462</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6539</v>
+        <v>6496</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
         <v>4</v>
@@ -3197,243 +3197,243 @@
         <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>20.82</v>
+        <v>19.65</v>
       </c>
       <c r="C45" t="n">
-        <v>21.19</v>
+        <v>19.86</v>
       </c>
       <c r="D45" t="n">
-        <v>19.8</v>
+        <v>19.37</v>
       </c>
       <c r="E45" t="n">
-        <v>12.3</v>
+        <v>13.8</v>
       </c>
       <c r="F45" t="n">
-        <v>11.7</v>
+        <v>13.5</v>
       </c>
       <c r="G45" t="n">
-        <v>215</v>
+        <v>55</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>1.02</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="K45" t="n">
-        <v>58.55</v>
+        <v>69.28</v>
       </c>
       <c r="L45" t="n">
-        <v>67.09</v>
+        <v>71.03</v>
       </c>
       <c r="M45" t="n">
-        <v>55.27</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6250</v>
+        <v>2267</v>
       </c>
       <c r="P45" t="n">
-        <v>6579</v>
+        <v>6511</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>21.17</v>
+        <v>19.34</v>
       </c>
       <c r="C46" t="n">
-        <v>21.41</v>
+        <v>19.5</v>
       </c>
       <c r="D46" t="n">
-        <v>20.87</v>
+        <v>19.25</v>
       </c>
       <c r="E46" t="n">
-        <v>12.3</v>
+        <v>13.5</v>
       </c>
       <c r="F46" t="n">
-        <v>11.8</v>
+        <v>13.4</v>
       </c>
       <c r="G46" t="n">
-        <v>419</v>
+        <v>67</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>1.06</v>
+        <v>0.68</v>
       </c>
       <c r="J46" t="n">
-        <v>0.99</v>
+        <v>0.67</v>
       </c>
       <c r="K46" t="n">
-        <v>57.42</v>
+        <v>69.37</v>
       </c>
       <c r="L46" t="n">
-        <v>60.15</v>
+        <v>70.14</v>
       </c>
       <c r="M46" t="n">
-        <v>55.34</v>
+        <v>68.55</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6777</v>
+        <v>4721</v>
       </c>
       <c r="P46" t="n">
-        <v>6613</v>
+        <v>6536</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.2</v>
+        <v>19.29</v>
       </c>
       <c r="C47" t="n">
-        <v>21.55</v>
+        <v>19.86</v>
       </c>
       <c r="D47" t="n">
-        <v>20.85</v>
+        <v>19.1</v>
       </c>
       <c r="E47" t="n">
-        <v>12.6</v>
+        <v>13.4</v>
       </c>
       <c r="F47" t="n">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="G47" t="n">
-        <v>629</v>
+        <v>68</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>1.04</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="K47" t="n">
-        <v>58.56</v>
+        <v>68.94</v>
       </c>
       <c r="L47" t="n">
-        <v>61.5</v>
+        <v>69.94</v>
       </c>
       <c r="M47" t="n">
-        <v>56.2</v>
+        <v>66.66</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6849</v>
+        <v>4462</v>
       </c>
       <c r="P47" t="n">
-        <v>6647</v>
+        <v>6539</v>
       </c>
       <c r="Q47" t="n">
+        <v>4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
         <v>5</v>
-      </c>
-      <c r="R47" t="n">
-        <v>5</v>
-      </c>
-      <c r="S47" t="n">
-        <v>5</v>
-      </c>
-      <c r="T47" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.75</v>
+        <v>20.82</v>
       </c>
       <c r="C48" t="n">
-        <v>21.44</v>
+        <v>21.19</v>
       </c>
       <c r="D48" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="E48" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F48" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="G48" t="n">
-        <v>612</v>
+        <v>215</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="K48" t="n">
-        <v>59.8</v>
+        <v>58.55</v>
       </c>
       <c r="L48" t="n">
-        <v>61.83</v>
+        <v>67.09</v>
       </c>
       <c r="M48" t="n">
-        <v>58.57</v>
+        <v>55.27</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6901</v>
+        <v>6250</v>
       </c>
       <c r="P48" t="n">
-        <v>6676</v>
+        <v>6579</v>
       </c>
       <c r="Q48" t="n">
         <v>5</v>
@@ -3442,7 +3442,7 @@
         <v>5</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
         <v>60</v>
@@ -3451,60 +3451,60 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.11</v>
+        <v>21.17</v>
       </c>
       <c r="C49" t="n">
-        <v>21.09</v>
+        <v>21.41</v>
       </c>
       <c r="D49" t="n">
-        <v>19.18</v>
+        <v>20.87</v>
       </c>
       <c r="E49" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="F49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="G49" t="n">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.85</v>
+        <v>1.06</v>
       </c>
       <c r="J49" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="K49" t="n">
-        <v>63.63</v>
+        <v>57.42</v>
       </c>
       <c r="L49" t="n">
-        <v>67.22</v>
+        <v>60.15</v>
       </c>
       <c r="M49" t="n">
-        <v>59.39</v>
+        <v>55.34</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6810</v>
+        <v>6777</v>
       </c>
       <c r="P49" t="n">
         <v>6613</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
         <v>5</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="n">
         <v>60</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,54 +533,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.51</v>
+        <v>22.02</v>
       </c>
       <c r="C2" t="n">
-        <v>22.96</v>
+        <v>22.16</v>
       </c>
       <c r="D2" t="n">
-        <v>22.11</v>
+        <v>21.88</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="F2" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="G2" t="n">
-        <v>404</v>
+        <v>111</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="J2" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="K2" t="n">
-        <v>49.12</v>
+        <v>50.18</v>
       </c>
       <c r="L2" t="n">
-        <v>51.28</v>
+        <v>52.66</v>
       </c>
       <c r="M2" t="n">
-        <v>47.37</v>
+        <v>47.74</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6753</v>
+        <v>4352</v>
       </c>
       <c r="P2" t="n">
-        <v>6573</v>
+        <v>6511</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
         <v>7</v>
@@ -589,57 +589,57 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.01</v>
+        <v>22.31</v>
       </c>
       <c r="C3" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D3" t="n">
-        <v>21.62</v>
+        <v>22.04</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F3" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="G3" t="n">
-        <v>452</v>
+        <v>198</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="J3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="K3" t="n">
-        <v>49.71</v>
+        <v>50.19</v>
       </c>
       <c r="L3" t="n">
-        <v>51.65</v>
+        <v>51.75</v>
       </c>
       <c r="M3" t="n">
-        <v>46.69</v>
+        <v>47.76</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6767</v>
+        <v>5406</v>
       </c>
       <c r="P3" t="n">
-        <v>6576</v>
+        <v>6539</v>
       </c>
       <c r="Q3" t="n">
         <v>6</v>
@@ -651,66 +651,66 @@
         <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.59</v>
+        <v>22.68</v>
       </c>
       <c r="C4" t="n">
-        <v>22.58</v>
+        <v>23.1</v>
       </c>
       <c r="D4" t="n">
-        <v>20.76</v>
+        <v>22.11</v>
       </c>
       <c r="E4" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F4" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G4" t="n">
-        <v>564</v>
+        <v>384</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="K4" t="n">
-        <v>51.87</v>
+        <v>48.82</v>
       </c>
       <c r="L4" t="n">
-        <v>56.03</v>
+        <v>51.28</v>
       </c>
       <c r="M4" t="n">
-        <v>45.92</v>
+        <v>47.13</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6796</v>
+        <v>6743</v>
       </c>
       <c r="P4" t="n">
-        <v>6599</v>
+        <v>6573</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
         <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
         <v>60</v>
@@ -719,42 +719,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.19</v>
+        <v>22.01</v>
       </c>
       <c r="C5" t="n">
-        <v>20.64</v>
+        <v>22.58</v>
       </c>
       <c r="D5" t="n">
-        <v>19.53</v>
+        <v>21.62</v>
       </c>
       <c r="E5" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>10.6</v>
       </c>
       <c r="G5" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="J5" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="K5" t="n">
-        <v>55.29</v>
+        <v>49.71</v>
       </c>
       <c r="L5" t="n">
-        <v>57.87</v>
+        <v>51.65</v>
       </c>
       <c r="M5" t="n">
-        <v>52.99</v>
+        <v>46.69</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -766,13 +766,13 @@
         <v>6576</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
+        <v>7</v>
+      </c>
+      <c r="S5" t="n">
         <v>6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
@@ -781,240 +781,240 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.89</v>
+        <v>21.59</v>
       </c>
       <c r="C6" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D6" t="n">
-        <v>18.08</v>
+        <v>20.76</v>
       </c>
       <c r="E6" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="F6" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="G6" t="n">
-        <v>212</v>
+        <v>564</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.66</v>
+        <v>1.24</v>
       </c>
       <c r="J6" t="n">
-        <v>0.35</v>
+        <v>1.07</v>
       </c>
       <c r="K6" t="n">
-        <v>69.7</v>
+        <v>51.87</v>
       </c>
       <c r="L6" t="n">
-        <v>82.87</v>
+        <v>56.03</v>
       </c>
       <c r="M6" t="n">
-        <v>57.89</v>
+        <v>45.92</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6691</v>
+        <v>6796</v>
       </c>
       <c r="P6" t="n">
-        <v>6514</v>
+        <v>6599</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" t="n">
         <v>5</v>
       </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.5</v>
+        <v>20.19</v>
       </c>
       <c r="C7" t="n">
-        <v>17.9</v>
+        <v>20.64</v>
       </c>
       <c r="D7" t="n">
-        <v>17.26</v>
+        <v>19.53</v>
       </c>
       <c r="E7" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F7" t="n">
-        <v>14.3</v>
+        <v>10.6</v>
       </c>
       <c r="G7" t="n">
-        <v>43</v>
+        <v>426</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.31</v>
+        <v>1.05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="K7" t="n">
-        <v>84.14</v>
+        <v>55.29</v>
       </c>
       <c r="L7" t="n">
-        <v>87.05</v>
+        <v>57.87</v>
       </c>
       <c r="M7" t="n">
-        <v>79.48999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3786</v>
+        <v>6767</v>
       </c>
       <c r="P7" t="n">
-        <v>6422</v>
+        <v>6576</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.02</v>
+        <v>18.89</v>
       </c>
       <c r="C8" t="n">
-        <v>17.27</v>
+        <v>19.62</v>
       </c>
       <c r="D8" t="n">
-        <v>16.92</v>
+        <v>18.08</v>
       </c>
       <c r="E8" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="F8" t="n">
-        <v>14.1</v>
+        <v>10.9</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="J8" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="K8" t="n">
-        <v>86.8</v>
+        <v>69.7</v>
       </c>
       <c r="L8" t="n">
-        <v>88.91</v>
+        <v>82.87</v>
       </c>
       <c r="M8" t="n">
-        <v>81.98999999999999</v>
+        <v>57.89</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1246</v>
+        <v>6691</v>
       </c>
       <c r="P8" t="n">
-        <v>6414</v>
+        <v>6514</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.89</v>
+        <v>17.5</v>
       </c>
       <c r="C9" t="n">
-        <v>17.03</v>
+        <v>17.9</v>
       </c>
       <c r="D9" t="n">
-        <v>16.78</v>
+        <v>17.26</v>
       </c>
       <c r="E9" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F9" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="J9" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="K9" t="n">
-        <v>88.48999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="L9" t="n">
-        <v>90.31</v>
+        <v>87.05</v>
       </c>
       <c r="M9" t="n">
-        <v>85.76000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="P9" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>2</v>
@@ -1029,48 +1029,48 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.13</v>
+        <v>17.02</v>
       </c>
       <c r="C10" t="n">
-        <v>17.32</v>
+        <v>17.27</v>
       </c>
       <c r="D10" t="n">
-        <v>16.89</v>
+        <v>16.92</v>
       </c>
       <c r="E10" t="n">
         <v>14.7</v>
       </c>
       <c r="F10" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="K10" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="L10" t="n">
-        <v>88.63</v>
+        <v>88.91</v>
       </c>
       <c r="M10" t="n">
-        <v>83.40000000000001</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="P10" t="n">
         <v>6414</v>
@@ -1091,42 +1091,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.01</v>
+        <v>16.89</v>
       </c>
       <c r="C11" t="n">
-        <v>17.08</v>
+        <v>17.03</v>
       </c>
       <c r="D11" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F11" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J11" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="K11" t="n">
-        <v>88.16</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>88.7</v>
+        <v>90.31</v>
       </c>
       <c r="M11" t="n">
-        <v>87.34999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1153,42 +1153,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.07</v>
+        <v>17.13</v>
       </c>
       <c r="C12" t="n">
-        <v>17.29</v>
+        <v>17.32</v>
       </c>
       <c r="D12" t="n">
-        <v>16.93</v>
+        <v>16.89</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F12" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.22</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.2</v>
-      </c>
       <c r="K12" t="n">
-        <v>88.06999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>89.45999999999999</v>
+        <v>88.63</v>
       </c>
       <c r="M12" t="n">
-        <v>85.97</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1215,42 +1215,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.44</v>
+        <v>17.01</v>
       </c>
       <c r="C13" t="n">
-        <v>17.52</v>
+        <v>17.08</v>
       </c>
       <c r="D13" t="n">
-        <v>17.31</v>
+        <v>16.93</v>
       </c>
       <c r="E13" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="J13" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="K13" t="n">
-        <v>84.31999999999999</v>
+        <v>88.16</v>
       </c>
       <c r="L13" t="n">
-        <v>85.27</v>
+        <v>88.7</v>
       </c>
       <c r="M13" t="n">
-        <v>82.56999999999999</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1259,16 +1259,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1277,17 +1277,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.22</v>
+        <v>17.07</v>
       </c>
       <c r="C14" t="n">
-        <v>17.34</v>
+        <v>17.29</v>
       </c>
       <c r="D14" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E14" t="n">
         <v>15</v>
@@ -1300,19 +1300,19 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="J14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="K14" t="n">
-        <v>87.37</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>88.34999999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>86.23</v>
+        <v>85.97</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1321,13 +1321,13 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1339,42 +1339,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5</v>
+        <v>17.52</v>
       </c>
       <c r="D15" t="n">
-        <v>17.22</v>
+        <v>17.31</v>
       </c>
       <c r="E15" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F15" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="J15" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="K15" t="n">
-        <v>87.89</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>89.09</v>
+        <v>85.27</v>
       </c>
       <c r="M15" t="n">
-        <v>87.03</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1383,16 +1383,16 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.51</v>
+        <v>17.22</v>
       </c>
       <c r="C16" t="n">
-        <v>17.64</v>
+        <v>17.34</v>
       </c>
       <c r="D16" t="n">
-        <v>17.34</v>
+        <v>17.11</v>
       </c>
       <c r="E16" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.22</v>
       </c>
-      <c r="J16" t="n">
-        <v>0.19</v>
-      </c>
       <c r="K16" t="n">
-        <v>88.95</v>
+        <v>87.37</v>
       </c>
       <c r="L16" t="n">
-        <v>90.3</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>87.78</v>
+        <v>86.23</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -1463,42 +1463,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.73</v>
+        <v>17.38</v>
       </c>
       <c r="C17" t="n">
-        <v>18.06</v>
+        <v>17.5</v>
       </c>
       <c r="D17" t="n">
-        <v>17.42</v>
+        <v>17.22</v>
       </c>
       <c r="E17" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="F17" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="J17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="K17" t="n">
-        <v>85.27</v>
+        <v>87.89</v>
       </c>
       <c r="L17" t="n">
-        <v>88.19</v>
+        <v>89.09</v>
       </c>
       <c r="M17" t="n">
-        <v>81.95</v>
+        <v>87.03</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1507,13 +1507,13 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6457</v>
+        <v>6408</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -1525,42 +1525,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.36</v>
+        <v>17.51</v>
       </c>
       <c r="C18" t="n">
-        <v>18.45</v>
+        <v>17.64</v>
       </c>
       <c r="D18" t="n">
-        <v>18.19</v>
+        <v>17.34</v>
       </c>
       <c r="E18" t="n">
-        <v>14.9</v>
+        <v>15.6</v>
       </c>
       <c r="F18" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="J18" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="K18" t="n">
-        <v>80.73</v>
+        <v>88.95</v>
       </c>
       <c r="L18" t="n">
-        <v>81.93000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="M18" t="n">
-        <v>79.83</v>
+        <v>87.78</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1569,16 +1569,16 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6471</v>
+        <v>6437</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -1587,42 +1587,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.81</v>
+        <v>17.73</v>
       </c>
       <c r="C19" t="n">
-        <v>19.07</v>
+        <v>18.06</v>
       </c>
       <c r="D19" t="n">
-        <v>18.51</v>
+        <v>17.42</v>
       </c>
       <c r="E19" t="n">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="F19" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="J19" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="K19" t="n">
-        <v>76.59999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="L19" t="n">
-        <v>79.87</v>
+        <v>88.19</v>
       </c>
       <c r="M19" t="n">
-        <v>74.01000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6482</v>
+        <v>6457</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -1649,42 +1649,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.81</v>
+        <v>18.36</v>
       </c>
       <c r="C20" t="n">
-        <v>20.67</v>
+        <v>18.45</v>
       </c>
       <c r="D20" t="n">
-        <v>18.96</v>
+        <v>18.19</v>
       </c>
       <c r="E20" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="F20" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="K20" t="n">
-        <v>69.16</v>
+        <v>80.73</v>
       </c>
       <c r="L20" t="n">
-        <v>75.04000000000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>63.43</v>
+        <v>79.83</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6496</v>
+        <v>6471</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -1711,299 +1711,299 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.22</v>
+        <v>18.81</v>
       </c>
       <c r="C21" t="n">
-        <v>21.6</v>
+        <v>19.07</v>
       </c>
       <c r="D21" t="n">
-        <v>20.76</v>
+        <v>18.51</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="G21" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.99</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="K21" t="n">
-        <v>60.52</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>62.17</v>
+        <v>79.87</v>
       </c>
       <c r="M21" t="n">
-        <v>58.42</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6516</v>
+        <v>6482</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.62</v>
+        <v>19.81</v>
       </c>
       <c r="C22" t="n">
-        <v>21.84</v>
+        <v>20.67</v>
       </c>
       <c r="D22" t="n">
-        <v>21.44</v>
+        <v>18.96</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="F22" t="n">
-        <v>12.7</v>
+        <v>13.4</v>
       </c>
       <c r="G22" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>0.54</v>
       </c>
       <c r="K22" t="n">
-        <v>58.13</v>
+        <v>69.16</v>
       </c>
       <c r="L22" t="n">
-        <v>60.32</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>56.76</v>
+        <v>63.43</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6548</v>
+        <v>6496</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.96</v>
+        <v>21.22</v>
       </c>
       <c r="C23" t="n">
-        <v>22.41</v>
+        <v>21.6</v>
       </c>
       <c r="D23" t="n">
-        <v>21.77</v>
+        <v>20.76</v>
       </c>
       <c r="E23" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="F23" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="J23" t="n">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="K23" t="n">
-        <v>55.95</v>
+        <v>60.52</v>
       </c>
       <c r="L23" t="n">
-        <v>57.92</v>
+        <v>62.17</v>
       </c>
       <c r="M23" t="n">
-        <v>54.15</v>
+        <v>58.42</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6619</v>
+        <v>2990</v>
       </c>
       <c r="P23" t="n">
-        <v>6573</v>
+        <v>6516</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.46</v>
+        <v>21.62</v>
       </c>
       <c r="C24" t="n">
-        <v>23.17</v>
+        <v>21.84</v>
       </c>
       <c r="D24" t="n">
-        <v>21.82</v>
+        <v>21.44</v>
       </c>
       <c r="E24" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G24" t="n">
-        <v>383</v>
+        <v>137</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="J24" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>52.56</v>
+        <v>58.13</v>
       </c>
       <c r="L24" t="n">
-        <v>54.35</v>
+        <v>60.32</v>
       </c>
       <c r="M24" t="n">
-        <v>50.6</v>
+        <v>56.76</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6763</v>
+        <v>5684</v>
       </c>
       <c r="P24" t="n">
-        <v>6593</v>
+        <v>6548</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.1</v>
+        <v>21.96</v>
       </c>
       <c r="C25" t="n">
-        <v>22.92</v>
+        <v>22.41</v>
       </c>
       <c r="D25" t="n">
-        <v>21.76</v>
+        <v>21.77</v>
       </c>
       <c r="E25" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F25" t="n">
         <v>12.2</v>
       </c>
-      <c r="F25" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G25" t="n">
-        <v>479</v>
+        <v>205</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="J25" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="K25" t="n">
-        <v>53.58</v>
+        <v>55.95</v>
       </c>
       <c r="L25" t="n">
-        <v>55.95</v>
+        <v>57.92</v>
       </c>
       <c r="M25" t="n">
-        <v>51.48</v>
+        <v>54.15</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6739</v>
+        <v>6619</v>
       </c>
       <c r="P25" t="n">
-        <v>6582</v>
+        <v>6573</v>
       </c>
       <c r="Q25" t="n">
         <v>6</v>
@@ -2021,60 +2021,60 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21.45</v>
+        <v>22.46</v>
       </c>
       <c r="C26" t="n">
-        <v>22.62</v>
+        <v>23.17</v>
       </c>
       <c r="D26" t="n">
-        <v>20.83</v>
+        <v>21.82</v>
       </c>
       <c r="E26" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F26" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G26" t="n">
-        <v>640</v>
+        <v>383</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="J26" t="n">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="K26" t="n">
-        <v>56.35</v>
+        <v>52.56</v>
       </c>
       <c r="L26" t="n">
-        <v>62.61</v>
+        <v>54.35</v>
       </c>
       <c r="M26" t="n">
-        <v>51.88</v>
+        <v>50.6</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6810</v>
+        <v>6763</v>
       </c>
       <c r="P26" t="n">
-        <v>6610</v>
+        <v>6593</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
         <v>6</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
         <v>60</v>
@@ -2083,60 +2083,60 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.67</v>
+        <v>22.1</v>
       </c>
       <c r="C27" t="n">
-        <v>20.85</v>
+        <v>22.92</v>
       </c>
       <c r="D27" t="n">
-        <v>19.11</v>
+        <v>21.76</v>
       </c>
       <c r="E27" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F27" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="G27" t="n">
-        <v>279</v>
+        <v>479</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.77</v>
+        <v>1.23</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="K27" t="n">
-        <v>66.39</v>
+        <v>53.58</v>
       </c>
       <c r="L27" t="n">
-        <v>68.68000000000001</v>
+        <v>55.95</v>
       </c>
       <c r="M27" t="n">
-        <v>61.4</v>
+        <v>51.48</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6772</v>
+        <v>6739</v>
       </c>
       <c r="P27" t="n">
-        <v>6571</v>
+        <v>6582</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
+        <v>6</v>
+      </c>
+      <c r="S27" t="n">
         <v>5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4</v>
       </c>
       <c r="T27" t="n">
         <v>60</v>
@@ -2145,122 +2145,122 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.92</v>
+        <v>21.45</v>
       </c>
       <c r="C28" t="n">
-        <v>19.22</v>
+        <v>22.62</v>
       </c>
       <c r="D28" t="n">
-        <v>18.64</v>
+        <v>20.83</v>
       </c>
       <c r="E28" t="n">
-        <v>13.6</v>
+        <v>12.3</v>
       </c>
       <c r="F28" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="G28" t="n">
-        <v>143</v>
+        <v>640</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="J28" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="K28" t="n">
-        <v>71.48999999999999</v>
+        <v>56.35</v>
       </c>
       <c r="L28" t="n">
-        <v>73.28</v>
+        <v>62.61</v>
       </c>
       <c r="M28" t="n">
-        <v>69.45</v>
+        <v>51.88</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6254</v>
+        <v>6810</v>
       </c>
       <c r="P28" t="n">
-        <v>6508</v>
+        <v>6610</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18.78</v>
+        <v>19.67</v>
       </c>
       <c r="C29" t="n">
-        <v>18.89</v>
+        <v>20.85</v>
       </c>
       <c r="D29" t="n">
-        <v>18.67</v>
+        <v>19.11</v>
       </c>
       <c r="E29" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F29" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="G29" t="n">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="J29" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>70.87</v>
+        <v>66.39</v>
       </c>
       <c r="L29" t="n">
-        <v>73.17</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>68.48</v>
+        <v>61.4</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>5929</v>
+        <v>6772</v>
       </c>
       <c r="P29" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S29" t="n">
         <v>4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
       </c>
       <c r="T29" t="n">
         <v>60</v>
@@ -2269,51 +2269,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18.59</v>
+        <v>18.92</v>
       </c>
       <c r="C30" t="n">
-        <v>19.26</v>
+        <v>19.22</v>
       </c>
       <c r="D30" t="n">
-        <v>18.18</v>
+        <v>18.64</v>
       </c>
       <c r="E30" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="F30" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G30" t="n">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="J30" t="n">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
       <c r="K30" t="n">
-        <v>76.48999999999999</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>80.08</v>
+        <v>73.28</v>
       </c>
       <c r="M30" t="n">
-        <v>71.70999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>5478</v>
+        <v>6254</v>
       </c>
       <c r="P30" t="n">
-        <v>6494</v>
+        <v>6508</v>
       </c>
       <c r="Q30" t="n">
         <v>3</v>
@@ -2322,69 +2322,69 @@
         <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.89</v>
+        <v>18.78</v>
       </c>
       <c r="C31" t="n">
-        <v>18.29</v>
+        <v>18.89</v>
       </c>
       <c r="D31" t="n">
-        <v>17.02</v>
+        <v>18.67</v>
       </c>
       <c r="E31" t="n">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="F31" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="G31" t="n">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="J31" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="K31" t="n">
-        <v>82.51000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="L31" t="n">
-        <v>87.40000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="M31" t="n">
-        <v>79.09999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6633</v>
+        <v>5929</v>
       </c>
       <c r="P31" t="n">
-        <v>6488</v>
+        <v>6494</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
         <v>60</v>
@@ -2393,175 +2393,175 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.49</v>
+        <v>18.59</v>
       </c>
       <c r="C32" t="n">
-        <v>16.79</v>
+        <v>19.26</v>
       </c>
       <c r="D32" t="n">
-        <v>16.31</v>
+        <v>18.18</v>
       </c>
       <c r="E32" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F32" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="G32" t="n">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="K32" t="n">
-        <v>89.09</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>91.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M32" t="n">
-        <v>87.73</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>5349</v>
+        <v>5478</v>
       </c>
       <c r="P32" t="n">
-        <v>6445</v>
+        <v>6494</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.27</v>
+        <v>17.89</v>
       </c>
       <c r="C33" t="n">
-        <v>16.31</v>
+        <v>18.29</v>
       </c>
       <c r="D33" t="n">
-        <v>16.24</v>
+        <v>17.02</v>
       </c>
       <c r="E33" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F33" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="J33" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="K33" t="n">
-        <v>90.12</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>91.63</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>88.84</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P33" t="n">
-        <v>6422</v>
+        <v>6488</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.37</v>
+        <v>16.49</v>
       </c>
       <c r="C34" t="n">
-        <v>16.42</v>
+        <v>16.79</v>
       </c>
       <c r="D34" t="n">
-        <v>16.3</v>
+        <v>16.31</v>
       </c>
       <c r="E34" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F34" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>0.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="K34" t="n">
-        <v>88.97</v>
+        <v>89.09</v>
       </c>
       <c r="L34" t="n">
-        <v>90.09</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>88.26000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P34" t="n">
-        <v>6414</v>
+        <v>6445</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
@@ -2579,44 +2579,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.35</v>
+        <v>16.27</v>
       </c>
       <c r="C35" t="n">
-        <v>16.36</v>
+        <v>16.31</v>
       </c>
       <c r="D35" t="n">
-        <v>16.35</v>
+        <v>16.24</v>
       </c>
       <c r="E35" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="F35" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="n">
-        <v>2592</v>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="J35" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="K35" t="n">
-        <v>84.98</v>
+        <v>90.12</v>
       </c>
       <c r="L35" t="n">
-        <v>85.65000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="M35" t="n">
-        <v>84.31</v>
+        <v>88.84</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2625,13 +2623,13 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -2643,44 +2641,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.33</v>
+        <v>16.37</v>
       </c>
       <c r="C36" t="n">
-        <v>16.56</v>
+        <v>16.42</v>
       </c>
       <c r="D36" t="n">
-        <v>15.86</v>
+        <v>16.3</v>
       </c>
       <c r="E36" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F36" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="n">
-        <v>2522</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K36" t="n">
-        <v>89.8</v>
+        <v>88.97</v>
       </c>
       <c r="L36" t="n">
-        <v>99.73</v>
+        <v>90.09</v>
       </c>
       <c r="M36" t="n">
-        <v>85.27</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2689,16 +2685,16 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -2707,42 +2703,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.27</v>
+        <v>16.35</v>
       </c>
       <c r="C37" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="D37" t="n">
-        <v>16.2</v>
+        <v>16.35</v>
       </c>
       <c r="E37" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F37" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>2592</v>
+      </c>
       <c r="I37" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="J37" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K37" t="n">
-        <v>90.44</v>
+        <v>84.98</v>
       </c>
       <c r="L37" t="n">
-        <v>91.61</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>89.09999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2751,13 +2749,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -2769,42 +2767,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.26</v>
+        <v>16.33</v>
       </c>
       <c r="C38" t="n">
-        <v>16.49</v>
+        <v>16.56</v>
       </c>
       <c r="D38" t="n">
-        <v>16.14</v>
+        <v>15.86</v>
       </c>
       <c r="E38" t="n">
         <v>14.6</v>
       </c>
       <c r="F38" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>2522</v>
+      </c>
       <c r="I38" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J38" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>90.33</v>
+        <v>89.8</v>
       </c>
       <c r="L38" t="n">
-        <v>91.40000000000001</v>
+        <v>99.73</v>
       </c>
       <c r="M38" t="n">
-        <v>89.20999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -2813,16 +2813,16 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -2831,42 +2831,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.61</v>
+        <v>16.27</v>
       </c>
       <c r="C39" t="n">
-        <v>16.82</v>
+        <v>16.37</v>
       </c>
       <c r="D39" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="E39" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F39" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="J39" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K39" t="n">
-        <v>87.3</v>
+        <v>90.44</v>
       </c>
       <c r="L39" t="n">
-        <v>89.45</v>
+        <v>91.61</v>
       </c>
       <c r="M39" t="n">
-        <v>86.06</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6434</v>
+        <v>6417</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -2893,42 +2893,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.92</v>
+        <v>16.26</v>
       </c>
       <c r="C40" t="n">
-        <v>17.22</v>
+        <v>16.49</v>
       </c>
       <c r="D40" t="n">
-        <v>16.72</v>
+        <v>16.14</v>
       </c>
       <c r="E40" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F40" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="J40" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="K40" t="n">
-        <v>83.48999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="L40" t="n">
-        <v>85.67</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>80.43000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -2955,42 +2955,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.37</v>
+        <v>16.61</v>
       </c>
       <c r="C41" t="n">
-        <v>17.64</v>
+        <v>16.82</v>
       </c>
       <c r="D41" t="n">
-        <v>17.15</v>
+        <v>16.45</v>
       </c>
       <c r="E41" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="F41" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="J41" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="K41" t="n">
-        <v>81.5</v>
+        <v>87.3</v>
       </c>
       <c r="L41" t="n">
-        <v>83.2</v>
+        <v>89.45</v>
       </c>
       <c r="M41" t="n">
-        <v>79.69</v>
+        <v>86.06</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2999,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6471</v>
+        <v>6434</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3017,42 +3017,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.37</v>
+        <v>16.92</v>
       </c>
       <c r="C42" t="n">
-        <v>17.71</v>
+        <v>17.22</v>
       </c>
       <c r="D42" t="n">
-        <v>17.16</v>
+        <v>16.72</v>
       </c>
       <c r="E42" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J42" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="K42" t="n">
-        <v>83.11</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>85.31</v>
+        <v>85.67</v>
       </c>
       <c r="M42" t="n">
-        <v>78.94</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6474</v>
+        <v>6465</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
@@ -3079,42 +3079,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.78</v>
+        <v>17.37</v>
       </c>
       <c r="C43" t="n">
-        <v>18.2</v>
+        <v>17.64</v>
       </c>
       <c r="D43" t="n">
-        <v>17.44</v>
+        <v>17.15</v>
       </c>
       <c r="E43" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="F43" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="J43" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="K43" t="n">
-        <v>81.01000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="L43" t="n">
-        <v>82.84999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="M43" t="n">
-        <v>78.13</v>
+        <v>79.69</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6494</v>
+        <v>6471</v>
       </c>
       <c r="Q43" t="n">
         <v>2</v>
@@ -3141,42 +3141,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.91</v>
+        <v>17.37</v>
       </c>
       <c r="C44" t="n">
-        <v>19.32</v>
+        <v>17.71</v>
       </c>
       <c r="D44" t="n">
-        <v>18.33</v>
+        <v>17.16</v>
       </c>
       <c r="E44" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="F44" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="J44" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="K44" t="n">
-        <v>72.89</v>
+        <v>83.11</v>
       </c>
       <c r="L44" t="n">
-        <v>76.66</v>
+        <v>85.31</v>
       </c>
       <c r="M44" t="n">
-        <v>67.31</v>
+        <v>78.94</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3185,16 +3185,16 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6496</v>
+        <v>6474</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -3203,60 +3203,60 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.65</v>
+        <v>17.78</v>
       </c>
       <c r="C45" t="n">
-        <v>19.86</v>
+        <v>18.2</v>
       </c>
       <c r="D45" t="n">
-        <v>19.37</v>
+        <v>17.44</v>
       </c>
       <c r="E45" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="F45" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="G45" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="J45" t="n">
-        <v>0.65</v>
+        <v>0.34</v>
       </c>
       <c r="K45" t="n">
-        <v>69.28</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>71.03</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>67.26000000000001</v>
+        <v>78.13</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6511</v>
+        <v>6494</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -3265,54 +3265,54 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.34</v>
+        <v>18.91</v>
       </c>
       <c r="C46" t="n">
-        <v>19.5</v>
+        <v>19.32</v>
       </c>
       <c r="D46" t="n">
-        <v>19.25</v>
+        <v>18.33</v>
       </c>
       <c r="E46" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="F46" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="G46" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="J46" t="n">
-        <v>0.67</v>
+        <v>0.49</v>
       </c>
       <c r="K46" t="n">
-        <v>69.37</v>
+        <v>72.89</v>
       </c>
       <c r="L46" t="n">
-        <v>70.14</v>
+        <v>76.66</v>
       </c>
       <c r="M46" t="n">
-        <v>68.55</v>
+        <v>67.31</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6536</v>
+        <v>6496</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
         <v>4</v>
@@ -3327,51 +3327,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.29</v>
+        <v>19.65</v>
       </c>
       <c r="C47" t="n">
         <v>19.86</v>
       </c>
       <c r="D47" t="n">
-        <v>19.1</v>
+        <v>19.37</v>
       </c>
       <c r="E47" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="F47" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="G47" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="K47" t="n">
-        <v>68.94</v>
+        <v>69.28</v>
       </c>
       <c r="L47" t="n">
-        <v>69.94</v>
+        <v>71.03</v>
       </c>
       <c r="M47" t="n">
-        <v>66.66</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4462</v>
+        <v>2267</v>
       </c>
       <c r="P47" t="n">
-        <v>6539</v>
+        <v>6511</v>
       </c>
       <c r="Q47" t="n">
         <v>4</v>
@@ -3383,131 +3383,131 @@
         <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 17:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.82</v>
+        <v>19.34</v>
       </c>
       <c r="C48" t="n">
-        <v>21.19</v>
+        <v>19.5</v>
       </c>
       <c r="D48" t="n">
-        <v>19.8</v>
+        <v>19.25</v>
       </c>
       <c r="E48" t="n">
-        <v>12.3</v>
+        <v>13.5</v>
       </c>
       <c r="F48" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
       <c r="G48" t="n">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="J48" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="K48" t="n">
-        <v>58.55</v>
+        <v>69.37</v>
       </c>
       <c r="L48" t="n">
-        <v>67.09</v>
+        <v>70.14</v>
       </c>
       <c r="M48" t="n">
-        <v>55.27</v>
+        <v>68.55</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6250</v>
+        <v>4721</v>
       </c>
       <c r="P48" t="n">
-        <v>6579</v>
+        <v>6536</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>21.17</v>
+        <v>19.29</v>
       </c>
       <c r="C49" t="n">
-        <v>21.41</v>
+        <v>19.86</v>
       </c>
       <c r="D49" t="n">
-        <v>20.87</v>
+        <v>19.1</v>
       </c>
       <c r="E49" t="n">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="F49" t="n">
-        <v>11.8</v>
+        <v>13.3</v>
       </c>
       <c r="G49" t="n">
-        <v>419</v>
+        <v>68</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>0.99</v>
+        <v>0.66</v>
       </c>
       <c r="K49" t="n">
-        <v>57.42</v>
+        <v>68.94</v>
       </c>
       <c r="L49" t="n">
-        <v>60.15</v>
+        <v>69.94</v>
       </c>
       <c r="M49" t="n">
-        <v>55.34</v>
+        <v>66.66</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6777</v>
+        <v>4462</v>
       </c>
       <c r="P49" t="n">
-        <v>6613</v>
+        <v>6539</v>
       </c>
       <c r="Q49" t="n">
+        <v>4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
         <v>5</v>
-      </c>
-      <c r="R49" t="n">
-        <v>5</v>
-      </c>
-      <c r="S49" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" t="n">
-        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,237 +533,237 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.02</v>
+        <v>18.02</v>
       </c>
       <c r="C2" t="n">
-        <v>22.16</v>
+        <v>18.12</v>
       </c>
       <c r="D2" t="n">
-        <v>21.88</v>
+        <v>17.84</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="G2" t="n">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1.31</v>
+        <v>0.36</v>
       </c>
       <c r="J2" t="n">
-        <v>1.24</v>
+        <v>0.31</v>
       </c>
       <c r="K2" t="n">
-        <v>50.18</v>
+        <v>82.62</v>
       </c>
       <c r="L2" t="n">
-        <v>52.66</v>
+        <v>84.8</v>
       </c>
       <c r="M2" t="n">
-        <v>47.74</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4352</v>
+        <v>1869</v>
       </c>
       <c r="P2" t="n">
-        <v>6511</v>
+        <v>6474</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.31</v>
+        <v>19.95</v>
       </c>
       <c r="C3" t="n">
-        <v>22.81</v>
+        <v>21.08</v>
       </c>
       <c r="D3" t="n">
-        <v>22.04</v>
+        <v>18.04</v>
       </c>
       <c r="E3" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="F3" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="G3" t="n">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
       <c r="J3" t="n">
-        <v>1.28</v>
+        <v>0.41</v>
       </c>
       <c r="K3" t="n">
-        <v>50.19</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>51.75</v>
+        <v>79.75</v>
       </c>
       <c r="M3" t="n">
-        <v>47.76</v>
+        <v>55.98</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5406</v>
+        <v>1926</v>
       </c>
       <c r="P3" t="n">
-        <v>6539</v>
+        <v>6474</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.68</v>
+        <v>21.54</v>
       </c>
       <c r="C4" t="n">
-        <v>23.1</v>
+        <v>21.83</v>
       </c>
       <c r="D4" t="n">
-        <v>22.11</v>
+        <v>21.18</v>
       </c>
       <c r="E4" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F4" t="n">
         <v>10.7</v>
       </c>
       <c r="G4" t="n">
-        <v>384</v>
+        <v>44</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="J4" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="K4" t="n">
-        <v>48.82</v>
+        <v>53.45</v>
       </c>
       <c r="L4" t="n">
-        <v>51.28</v>
+        <v>58.22</v>
       </c>
       <c r="M4" t="n">
-        <v>47.13</v>
+        <v>49.34</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6743</v>
+        <v>2410</v>
       </c>
       <c r="P4" t="n">
-        <v>6573</v>
+        <v>6485</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.01</v>
+        <v>22.02</v>
       </c>
       <c r="C5" t="n">
-        <v>22.58</v>
+        <v>22.16</v>
       </c>
       <c r="D5" t="n">
-        <v>21.62</v>
+        <v>21.88</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="G5" t="n">
-        <v>452</v>
+        <v>111</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="J5" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="K5" t="n">
-        <v>49.71</v>
+        <v>50.18</v>
       </c>
       <c r="L5" t="n">
-        <v>51.65</v>
+        <v>52.66</v>
       </c>
       <c r="M5" t="n">
-        <v>46.69</v>
+        <v>47.74</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6767</v>
+        <v>4352</v>
       </c>
       <c r="P5" t="n">
-        <v>6576</v>
+        <v>6511</v>
       </c>
       <c r="Q5" t="n">
         <v>6</v>
@@ -775,57 +775,57 @@
         <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.59</v>
+        <v>22.31</v>
       </c>
       <c r="C6" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D6" t="n">
-        <v>20.76</v>
+        <v>22.04</v>
       </c>
       <c r="E6" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="F6" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="G6" t="n">
-        <v>564</v>
+        <v>198</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="K6" t="n">
-        <v>51.87</v>
+        <v>50.19</v>
       </c>
       <c r="L6" t="n">
-        <v>56.03</v>
+        <v>51.75</v>
       </c>
       <c r="M6" t="n">
-        <v>45.92</v>
+        <v>47.76</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6796</v>
+        <v>5406</v>
       </c>
       <c r="P6" t="n">
-        <v>6599</v>
+        <v>6539</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -834,69 +834,69 @@
         <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.19</v>
+        <v>22.68</v>
       </c>
       <c r="C7" t="n">
-        <v>20.64</v>
+        <v>23.1</v>
       </c>
       <c r="D7" t="n">
-        <v>19.53</v>
+        <v>22.11</v>
       </c>
       <c r="E7" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F7" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="G7" t="n">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="K7" t="n">
-        <v>55.29</v>
+        <v>48.82</v>
       </c>
       <c r="L7" t="n">
-        <v>57.87</v>
+        <v>51.28</v>
       </c>
       <c r="M7" t="n">
-        <v>52.99</v>
+        <v>47.13</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6767</v>
+        <v>6743</v>
       </c>
       <c r="P7" t="n">
-        <v>6576</v>
+        <v>6573</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S7" t="n">
         <v>6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
@@ -905,302 +905,302 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.89</v>
+        <v>22.01</v>
       </c>
       <c r="C8" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D8" t="n">
-        <v>18.08</v>
+        <v>21.62</v>
       </c>
       <c r="E8" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G8" t="n">
-        <v>212</v>
+        <v>452</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="J8" t="n">
-        <v>0.35</v>
+        <v>1.27</v>
       </c>
       <c r="K8" t="n">
-        <v>69.7</v>
+        <v>49.71</v>
       </c>
       <c r="L8" t="n">
-        <v>82.87</v>
+        <v>51.65</v>
       </c>
       <c r="M8" t="n">
-        <v>57.89</v>
+        <v>46.69</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6691</v>
+        <v>6767</v>
       </c>
       <c r="P8" t="n">
-        <v>6514</v>
+        <v>6576</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.5</v>
+        <v>21.59</v>
       </c>
       <c r="C9" t="n">
-        <v>17.9</v>
+        <v>22.58</v>
       </c>
       <c r="D9" t="n">
-        <v>17.26</v>
+        <v>20.76</v>
       </c>
       <c r="E9" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="F9" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.31</v>
+        <v>1.24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.25</v>
+        <v>1.07</v>
       </c>
       <c r="K9" t="n">
-        <v>84.14</v>
+        <v>51.87</v>
       </c>
       <c r="L9" t="n">
-        <v>87.05</v>
+        <v>56.03</v>
       </c>
       <c r="M9" t="n">
-        <v>79.48999999999999</v>
+        <v>45.92</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3786</v>
+        <v>6796</v>
       </c>
       <c r="P9" t="n">
-        <v>6422</v>
+        <v>6599</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.02</v>
+        <v>20.19</v>
       </c>
       <c r="C10" t="n">
-        <v>17.27</v>
+        <v>20.64</v>
       </c>
       <c r="D10" t="n">
-        <v>16.92</v>
+        <v>19.53</v>
       </c>
       <c r="E10" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F10" t="n">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.25</v>
+        <v>1.05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.21</v>
+        <v>0.95</v>
       </c>
       <c r="K10" t="n">
-        <v>86.8</v>
+        <v>55.29</v>
       </c>
       <c r="L10" t="n">
-        <v>88.91</v>
+        <v>57.87</v>
       </c>
       <c r="M10" t="n">
-        <v>81.98999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1246</v>
+        <v>6767</v>
       </c>
       <c r="P10" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.89</v>
+        <v>18.89</v>
       </c>
       <c r="C11" t="n">
-        <v>17.03</v>
+        <v>19.62</v>
       </c>
       <c r="D11" t="n">
-        <v>16.78</v>
+        <v>18.08</v>
       </c>
       <c r="E11" t="n">
-        <v>14.9</v>
+        <v>13.1</v>
       </c>
       <c r="F11" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="J11" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="K11" t="n">
-        <v>88.48999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="L11" t="n">
-        <v>90.31</v>
+        <v>82.87</v>
       </c>
       <c r="M11" t="n">
-        <v>85.76000000000001</v>
+        <v>57.89</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="P11" t="n">
-        <v>6417</v>
+        <v>6514</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.13</v>
+        <v>17.5</v>
       </c>
       <c r="C12" t="n">
-        <v>17.32</v>
+        <v>17.9</v>
       </c>
       <c r="D12" t="n">
-        <v>16.89</v>
+        <v>17.26</v>
       </c>
       <c r="E12" t="n">
         <v>14.7</v>
       </c>
       <c r="F12" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="J12" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="K12" t="n">
-        <v>85.90000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="L12" t="n">
-        <v>88.63</v>
+        <v>87.05</v>
       </c>
       <c r="M12" t="n">
-        <v>83.40000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="P12" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>2</v>
@@ -1215,48 +1215,48 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.01</v>
+        <v>17.02</v>
       </c>
       <c r="C13" t="n">
-        <v>17.08</v>
+        <v>17.27</v>
       </c>
       <c r="D13" t="n">
-        <v>16.93</v>
+        <v>16.92</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F13" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J13" t="n">
         <v>0.21</v>
       </c>
       <c r="K13" t="n">
-        <v>88.16</v>
+        <v>86.8</v>
       </c>
       <c r="L13" t="n">
-        <v>88.7</v>
+        <v>88.91</v>
       </c>
       <c r="M13" t="n">
-        <v>87.34999999999999</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="P13" t="n">
         <v>6414</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1277,42 +1277,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.07</v>
+        <v>16.89</v>
       </c>
       <c r="C14" t="n">
-        <v>17.29</v>
+        <v>17.03</v>
       </c>
       <c r="D14" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F14" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K14" t="n">
-        <v>88.06999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>89.45999999999999</v>
+        <v>90.31</v>
       </c>
       <c r="M14" t="n">
-        <v>85.97</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1339,42 +1339,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.44</v>
+        <v>17.13</v>
       </c>
       <c r="C15" t="n">
-        <v>17.52</v>
+        <v>17.32</v>
       </c>
       <c r="D15" t="n">
-        <v>17.31</v>
+        <v>16.89</v>
       </c>
       <c r="E15" t="n">
         <v>14.7</v>
       </c>
       <c r="F15" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="J15" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="K15" t="n">
-        <v>84.31999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>85.27</v>
+        <v>88.63</v>
       </c>
       <c r="M15" t="n">
-        <v>82.56999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1383,16 +1383,16 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1401,42 +1401,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.22</v>
+        <v>17.01</v>
       </c>
       <c r="C16" t="n">
-        <v>17.34</v>
+        <v>17.08</v>
       </c>
       <c r="D16" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="J16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="K16" t="n">
-        <v>87.37</v>
+        <v>88.16</v>
       </c>
       <c r="L16" t="n">
-        <v>88.34999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="M16" t="n">
-        <v>86.23</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -1463,42 +1463,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.38</v>
+        <v>17.07</v>
       </c>
       <c r="C17" t="n">
-        <v>17.5</v>
+        <v>17.29</v>
       </c>
       <c r="D17" t="n">
-        <v>17.22</v>
+        <v>16.93</v>
       </c>
       <c r="E17" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="K17" t="n">
-        <v>87.89</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>89.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>87.03</v>
+        <v>85.97</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1507,13 +1507,13 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -1525,42 +1525,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.51</v>
+        <v>17.44</v>
       </c>
       <c r="C18" t="n">
-        <v>17.64</v>
+        <v>17.52</v>
       </c>
       <c r="D18" t="n">
-        <v>17.34</v>
+        <v>17.31</v>
       </c>
       <c r="E18" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="F18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="J18" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="K18" t="n">
-        <v>88.95</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>90.3</v>
+        <v>85.27</v>
       </c>
       <c r="M18" t="n">
-        <v>87.78</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1569,16 +1569,16 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6437</v>
+        <v>6417</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -1587,20 +1587,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.73</v>
+        <v>17.22</v>
       </c>
       <c r="C19" t="n">
-        <v>18.06</v>
+        <v>17.34</v>
       </c>
       <c r="D19" t="n">
-        <v>17.42</v>
+        <v>17.11</v>
       </c>
       <c r="E19" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
         <v>14.9</v>
@@ -1610,19 +1610,19 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="J19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="K19" t="n">
-        <v>85.27</v>
+        <v>87.37</v>
       </c>
       <c r="L19" t="n">
-        <v>88.19</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>81.95</v>
+        <v>86.23</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1631,13 +1631,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -1649,42 +1649,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18.36</v>
+        <v>17.38</v>
       </c>
       <c r="C20" t="n">
-        <v>18.45</v>
+        <v>17.5</v>
       </c>
       <c r="D20" t="n">
-        <v>18.19</v>
+        <v>17.22</v>
       </c>
       <c r="E20" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="F20" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="K20" t="n">
-        <v>80.73</v>
+        <v>87.89</v>
       </c>
       <c r="L20" t="n">
-        <v>81.93000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="M20" t="n">
-        <v>79.83</v>
+        <v>87.03</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6471</v>
+        <v>6408</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -1711,42 +1711,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.81</v>
+        <v>17.51</v>
       </c>
       <c r="C21" t="n">
-        <v>19.07</v>
+        <v>17.64</v>
       </c>
       <c r="D21" t="n">
-        <v>18.51</v>
+        <v>17.34</v>
       </c>
       <c r="E21" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="F21" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="K21" t="n">
-        <v>76.59999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="L21" t="n">
-        <v>79.87</v>
+        <v>90.3</v>
       </c>
       <c r="M21" t="n">
-        <v>74.01000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1755,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6482</v>
+        <v>6437</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -1773,42 +1773,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.81</v>
+        <v>17.73</v>
       </c>
       <c r="C22" t="n">
-        <v>20.67</v>
+        <v>18.06</v>
       </c>
       <c r="D22" t="n">
-        <v>18.96</v>
+        <v>17.42</v>
       </c>
       <c r="E22" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="F22" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="J22" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="K22" t="n">
-        <v>69.16</v>
+        <v>85.27</v>
       </c>
       <c r="L22" t="n">
-        <v>75.04000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="M22" t="n">
-        <v>63.43</v>
+        <v>81.95</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1817,16 +1817,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6496</v>
+        <v>6457</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -1835,364 +1835,364 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.22</v>
+        <v>18.36</v>
       </c>
       <c r="C23" t="n">
-        <v>21.6</v>
+        <v>18.45</v>
       </c>
       <c r="D23" t="n">
-        <v>20.76</v>
+        <v>18.19</v>
       </c>
       <c r="E23" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="G23" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
       <c r="K23" t="n">
-        <v>60.52</v>
+        <v>80.73</v>
       </c>
       <c r="L23" t="n">
-        <v>62.17</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>58.42</v>
+        <v>79.83</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6516</v>
+        <v>6471</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21.62</v>
+        <v>18.81</v>
       </c>
       <c r="C24" t="n">
-        <v>21.84</v>
+        <v>19.07</v>
       </c>
       <c r="D24" t="n">
-        <v>21.44</v>
+        <v>18.51</v>
       </c>
       <c r="E24" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F24" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="G24" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="K24" t="n">
-        <v>58.13</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>60.32</v>
+        <v>79.87</v>
       </c>
       <c r="M24" t="n">
-        <v>56.76</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6548</v>
+        <v>6482</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21.96</v>
+        <v>19.81</v>
       </c>
       <c r="C25" t="n">
-        <v>22.41</v>
+        <v>20.67</v>
       </c>
       <c r="D25" t="n">
-        <v>21.77</v>
+        <v>18.96</v>
       </c>
       <c r="E25" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="F25" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="G25" t="n">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>1.15</v>
+        <v>0.71</v>
       </c>
       <c r="J25" t="n">
-        <v>1.11</v>
+        <v>0.54</v>
       </c>
       <c r="K25" t="n">
-        <v>55.95</v>
+        <v>69.16</v>
       </c>
       <c r="L25" t="n">
-        <v>57.92</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>54.15</v>
+        <v>63.43</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6573</v>
+        <v>6496</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.46</v>
+        <v>21.22</v>
       </c>
       <c r="C26" t="n">
-        <v>23.17</v>
+        <v>21.6</v>
       </c>
       <c r="D26" t="n">
-        <v>21.82</v>
+        <v>20.76</v>
       </c>
       <c r="E26" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F26" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>383</v>
+        <v>73</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>1.29</v>
+        <v>0.99</v>
       </c>
       <c r="J26" t="n">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="K26" t="n">
-        <v>52.56</v>
+        <v>60.52</v>
       </c>
       <c r="L26" t="n">
-        <v>54.35</v>
+        <v>62.17</v>
       </c>
       <c r="M26" t="n">
-        <v>50.6</v>
+        <v>58.42</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6763</v>
+        <v>2990</v>
       </c>
       <c r="P26" t="n">
-        <v>6593</v>
+        <v>6516</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22.1</v>
+        <v>21.62</v>
       </c>
       <c r="C27" t="n">
-        <v>22.92</v>
+        <v>21.84</v>
       </c>
       <c r="D27" t="n">
-        <v>21.76</v>
+        <v>21.44</v>
       </c>
       <c r="E27" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>11.5</v>
+        <v>12.7</v>
       </c>
       <c r="G27" t="n">
-        <v>479</v>
+        <v>137</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="J27" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="K27" t="n">
-        <v>53.58</v>
+        <v>58.13</v>
       </c>
       <c r="L27" t="n">
-        <v>55.95</v>
+        <v>60.32</v>
       </c>
       <c r="M27" t="n">
-        <v>51.48</v>
+        <v>56.76</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6739</v>
+        <v>5684</v>
       </c>
       <c r="P27" t="n">
-        <v>6582</v>
+        <v>6548</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21.45</v>
+        <v>21.96</v>
       </c>
       <c r="C28" t="n">
-        <v>22.62</v>
+        <v>22.41</v>
       </c>
       <c r="D28" t="n">
-        <v>20.83</v>
+        <v>21.77</v>
       </c>
       <c r="E28" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F28" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G28" t="n">
-        <v>640</v>
+        <v>205</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J28" t="n">
         <v>1.11</v>
       </c>
-      <c r="J28" t="n">
-        <v>0.92</v>
-      </c>
       <c r="K28" t="n">
-        <v>56.35</v>
+        <v>55.95</v>
       </c>
       <c r="L28" t="n">
-        <v>62.61</v>
+        <v>57.92</v>
       </c>
       <c r="M28" t="n">
-        <v>51.88</v>
+        <v>54.15</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6810</v>
+        <v>6619</v>
       </c>
       <c r="P28" t="n">
-        <v>6610</v>
+        <v>6573</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
         <v>6</v>
@@ -2207,60 +2207,60 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.67</v>
+        <v>22.46</v>
       </c>
       <c r="C29" t="n">
-        <v>20.85</v>
+        <v>23.17</v>
       </c>
       <c r="D29" t="n">
-        <v>19.11</v>
+        <v>21.82</v>
       </c>
       <c r="E29" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F29" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="G29" t="n">
-        <v>279</v>
+        <v>383</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>1.21</v>
       </c>
       <c r="K29" t="n">
-        <v>66.39</v>
+        <v>52.56</v>
       </c>
       <c r="L29" t="n">
-        <v>68.68000000000001</v>
+        <v>54.35</v>
       </c>
       <c r="M29" t="n">
-        <v>61.4</v>
+        <v>50.6</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6772</v>
+        <v>6763</v>
       </c>
       <c r="P29" t="n">
-        <v>6571</v>
+        <v>6593</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T29" t="n">
         <v>60</v>
@@ -2269,122 +2269,122 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18.92</v>
+        <v>22.1</v>
       </c>
       <c r="C30" t="n">
-        <v>19.22</v>
+        <v>22.92</v>
       </c>
       <c r="D30" t="n">
-        <v>18.64</v>
+        <v>21.76</v>
       </c>
       <c r="E30" t="n">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="F30" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="G30" t="n">
-        <v>143</v>
+        <v>479</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="J30" t="n">
-        <v>0.58</v>
+        <v>1.14</v>
       </c>
       <c r="K30" t="n">
-        <v>71.48999999999999</v>
+        <v>53.58</v>
       </c>
       <c r="L30" t="n">
-        <v>73.28</v>
+        <v>55.95</v>
       </c>
       <c r="M30" t="n">
-        <v>69.45</v>
+        <v>51.48</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6254</v>
+        <v>6739</v>
       </c>
       <c r="P30" t="n">
-        <v>6508</v>
+        <v>6582</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18.78</v>
+        <v>21.45</v>
       </c>
       <c r="C31" t="n">
-        <v>18.89</v>
+        <v>22.62</v>
       </c>
       <c r="D31" t="n">
-        <v>18.67</v>
+        <v>20.83</v>
       </c>
       <c r="E31" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="F31" t="n">
-        <v>12.8</v>
+        <v>11.1</v>
       </c>
       <c r="G31" t="n">
-        <v>134</v>
+        <v>640</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.63</v>
+        <v>1.11</v>
       </c>
       <c r="J31" t="n">
-        <v>0.57</v>
+        <v>0.92</v>
       </c>
       <c r="K31" t="n">
-        <v>70.87</v>
+        <v>56.35</v>
       </c>
       <c r="L31" t="n">
-        <v>73.17</v>
+        <v>62.61</v>
       </c>
       <c r="M31" t="n">
-        <v>68.48</v>
+        <v>51.88</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>5929</v>
+        <v>6810</v>
       </c>
       <c r="P31" t="n">
-        <v>6494</v>
+        <v>6610</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
         <v>60</v>
@@ -2393,60 +2393,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18.59</v>
+        <v>19.67</v>
       </c>
       <c r="C32" t="n">
-        <v>19.26</v>
+        <v>20.85</v>
       </c>
       <c r="D32" t="n">
-        <v>18.18</v>
+        <v>19.11</v>
       </c>
       <c r="E32" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="F32" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="G32" t="n">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="J32" t="n">
-        <v>0.41</v>
+        <v>0.7</v>
       </c>
       <c r="K32" t="n">
-        <v>76.48999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="L32" t="n">
-        <v>80.08</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>71.70999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>5478</v>
+        <v>6772</v>
       </c>
       <c r="P32" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
         <v>60</v>
@@ -2455,307 +2455,305 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.89</v>
+        <v>18.92</v>
       </c>
       <c r="C33" t="n">
-        <v>18.29</v>
+        <v>19.22</v>
       </c>
       <c r="D33" t="n">
-        <v>17.02</v>
+        <v>18.64</v>
       </c>
       <c r="E33" t="n">
-        <v>14.8</v>
+        <v>13.6</v>
       </c>
       <c r="F33" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="G33" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="J33" t="n">
-        <v>0.24</v>
+        <v>0.58</v>
       </c>
       <c r="K33" t="n">
-        <v>82.51000000000001</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>87.40000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="M33" t="n">
-        <v>79.09999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6633</v>
+        <v>6254</v>
       </c>
       <c r="P33" t="n">
-        <v>6488</v>
+        <v>6508</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.49</v>
+        <v>18.78</v>
       </c>
       <c r="C34" t="n">
-        <v>16.79</v>
+        <v>18.89</v>
       </c>
       <c r="D34" t="n">
-        <v>16.31</v>
+        <v>18.67</v>
       </c>
       <c r="E34" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="F34" t="n">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="G34" t="n">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="J34" t="n">
-        <v>0.15</v>
+        <v>0.57</v>
       </c>
       <c r="K34" t="n">
-        <v>89.09</v>
+        <v>70.87</v>
       </c>
       <c r="L34" t="n">
-        <v>91.65000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="M34" t="n">
-        <v>87.73</v>
+        <v>68.48</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>5349</v>
+        <v>5929</v>
       </c>
       <c r="P34" t="n">
-        <v>6445</v>
+        <v>6494</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.27</v>
+        <v>18.59</v>
       </c>
       <c r="C35" t="n">
-        <v>16.31</v>
+        <v>19.26</v>
       </c>
       <c r="D35" t="n">
-        <v>16.24</v>
+        <v>18.18</v>
       </c>
       <c r="E35" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F35" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="K35" t="n">
-        <v>90.12</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>91.63</v>
+        <v>80.08</v>
       </c>
       <c r="M35" t="n">
-        <v>88.84</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="P35" t="n">
-        <v>6422</v>
+        <v>6494</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.37</v>
+        <v>17.89</v>
       </c>
       <c r="C36" t="n">
-        <v>16.42</v>
+        <v>18.29</v>
       </c>
       <c r="D36" t="n">
-        <v>16.3</v>
+        <v>17.02</v>
       </c>
       <c r="E36" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="F36" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J36" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="K36" t="n">
-        <v>88.97</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>90.09</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>88.26000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P36" t="n">
-        <v>6414</v>
+        <v>6488</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.35</v>
+        <v>16.49</v>
       </c>
       <c r="C37" t="n">
-        <v>16.36</v>
+        <v>16.79</v>
       </c>
       <c r="D37" t="n">
-        <v>16.35</v>
+        <v>16.31</v>
       </c>
       <c r="E37" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="F37" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>2592</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="J37" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="K37" t="n">
-        <v>84.98</v>
+        <v>89.09</v>
       </c>
       <c r="L37" t="n">
-        <v>85.65000000000001</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>84.31</v>
+        <v>87.73</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P37" t="n">
-        <v>6425</v>
+        <v>6445</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -2767,44 +2765,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.33</v>
+        <v>16.27</v>
       </c>
       <c r="C38" t="n">
-        <v>16.56</v>
+        <v>16.31</v>
       </c>
       <c r="D38" t="n">
-        <v>15.86</v>
+        <v>16.24</v>
       </c>
       <c r="E38" t="n">
         <v>14.6</v>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="n">
-        <v>2522</v>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K38" t="n">
-        <v>89.8</v>
+        <v>90.12</v>
       </c>
       <c r="L38" t="n">
-        <v>99.73</v>
+        <v>91.63</v>
       </c>
       <c r="M38" t="n">
-        <v>85.27</v>
+        <v>88.84</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -2819,10 +2815,10 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -2831,42 +2827,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.27</v>
+        <v>16.37</v>
       </c>
       <c r="C39" t="n">
-        <v>16.37</v>
+        <v>16.42</v>
       </c>
       <c r="D39" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="E39" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F39" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="K39" t="n">
-        <v>90.44</v>
+        <v>88.97</v>
       </c>
       <c r="L39" t="n">
-        <v>91.61</v>
+        <v>90.09</v>
       </c>
       <c r="M39" t="n">
-        <v>89.09999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2875,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -2893,42 +2889,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.26</v>
+        <v>16.35</v>
       </c>
       <c r="C40" t="n">
-        <v>16.49</v>
+        <v>16.36</v>
       </c>
       <c r="D40" t="n">
-        <v>16.14</v>
+        <v>16.35</v>
       </c>
       <c r="E40" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F40" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>2592</v>
+      </c>
       <c r="I40" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="J40" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K40" t="n">
-        <v>90.33</v>
+        <v>84.98</v>
       </c>
       <c r="L40" t="n">
-        <v>91.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>89.20999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2940,10 +2938,10 @@
         <v>6425</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -2955,42 +2953,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.61</v>
+        <v>16.33</v>
       </c>
       <c r="C41" t="n">
-        <v>16.82</v>
+        <v>16.56</v>
       </c>
       <c r="D41" t="n">
-        <v>16.45</v>
+        <v>15.86</v>
       </c>
       <c r="E41" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F41" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>2522</v>
+      </c>
       <c r="I41" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J41" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>87.3</v>
+        <v>89.8</v>
       </c>
       <c r="L41" t="n">
-        <v>89.45</v>
+        <v>99.73</v>
       </c>
       <c r="M41" t="n">
-        <v>86.06</v>
+        <v>85.27</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2999,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6434</v>
+        <v>6422</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3017,42 +3017,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16.92</v>
+        <v>16.27</v>
       </c>
       <c r="C42" t="n">
-        <v>17.22</v>
+        <v>16.37</v>
       </c>
       <c r="D42" t="n">
-        <v>16.72</v>
+        <v>16.2</v>
       </c>
       <c r="E42" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F42" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="J42" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="K42" t="n">
-        <v>83.48999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="L42" t="n">
-        <v>85.67</v>
+        <v>91.61</v>
       </c>
       <c r="M42" t="n">
-        <v>80.43000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3061,16 +3061,16 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6465</v>
+        <v>6417</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -3079,42 +3079,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.37</v>
+        <v>16.26</v>
       </c>
       <c r="C43" t="n">
-        <v>17.64</v>
+        <v>16.49</v>
       </c>
       <c r="D43" t="n">
-        <v>17.15</v>
+        <v>16.14</v>
       </c>
       <c r="E43" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F43" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="J43" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="K43" t="n">
-        <v>81.5</v>
+        <v>90.33</v>
       </c>
       <c r="L43" t="n">
-        <v>83.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>79.69</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6471</v>
+        <v>6425</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3141,42 +3141,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.37</v>
+        <v>16.61</v>
       </c>
       <c r="C44" t="n">
-        <v>17.71</v>
+        <v>16.82</v>
       </c>
       <c r="D44" t="n">
-        <v>17.16</v>
+        <v>16.45</v>
       </c>
       <c r="E44" t="n">
         <v>14.4</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="J44" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="K44" t="n">
-        <v>83.11</v>
+        <v>87.3</v>
       </c>
       <c r="L44" t="n">
-        <v>85.31</v>
+        <v>89.45</v>
       </c>
       <c r="M44" t="n">
-        <v>78.94</v>
+        <v>86.06</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3185,16 +3185,16 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6474</v>
+        <v>6434</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -3203,42 +3203,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.78</v>
+        <v>16.92</v>
       </c>
       <c r="C45" t="n">
-        <v>18.2</v>
+        <v>17.22</v>
       </c>
       <c r="D45" t="n">
-        <v>17.44</v>
+        <v>16.72</v>
       </c>
       <c r="E45" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="F45" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="J45" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="K45" t="n">
-        <v>81.01000000000001</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>82.84999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="M45" t="n">
-        <v>78.13</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6494</v>
+        <v>6465</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
@@ -3265,42 +3265,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18.91</v>
+        <v>17.37</v>
       </c>
       <c r="C46" t="n">
-        <v>19.32</v>
+        <v>17.64</v>
       </c>
       <c r="D46" t="n">
-        <v>18.33</v>
+        <v>17.15</v>
       </c>
       <c r="E46" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F46" t="n">
         <v>13.9</v>
-      </c>
-      <c r="F46" t="n">
-        <v>13.1</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="J46" t="n">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="K46" t="n">
-        <v>72.89</v>
+        <v>81.5</v>
       </c>
       <c r="L46" t="n">
-        <v>76.66</v>
+        <v>83.2</v>
       </c>
       <c r="M46" t="n">
-        <v>67.31</v>
+        <v>79.69</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3309,16 +3309,16 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6496</v>
+        <v>6471</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -3327,60 +3327,60 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.65</v>
+        <v>17.37</v>
       </c>
       <c r="C47" t="n">
-        <v>19.86</v>
+        <v>17.71</v>
       </c>
       <c r="D47" t="n">
-        <v>19.37</v>
+        <v>17.16</v>
       </c>
       <c r="E47" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="F47" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G47" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="J47" t="n">
-        <v>0.65</v>
+        <v>0.28</v>
       </c>
       <c r="K47" t="n">
-        <v>69.28</v>
+        <v>83.11</v>
       </c>
       <c r="L47" t="n">
-        <v>71.03</v>
+        <v>85.31</v>
       </c>
       <c r="M47" t="n">
-        <v>67.26000000000001</v>
+        <v>78.94</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2267</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6511</v>
+        <v>6474</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -3389,60 +3389,60 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00:00</t>
+          <t>2026-10-15 20:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.34</v>
+        <v>17.78</v>
       </c>
       <c r="C48" t="n">
-        <v>19.5</v>
+        <v>18.2</v>
       </c>
       <c r="D48" t="n">
-        <v>19.25</v>
+        <v>17.44</v>
       </c>
       <c r="E48" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="F48" t="n">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="G48" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="J48" t="n">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
       <c r="K48" t="n">
-        <v>69.37</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>70.14</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>68.55</v>
+        <v>78.13</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4721</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6536</v>
+        <v>6494</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -3451,54 +3451,54 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 19:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19.29</v>
+        <v>18.91</v>
       </c>
       <c r="C49" t="n">
-        <v>19.86</v>
+        <v>19.32</v>
       </c>
       <c r="D49" t="n">
-        <v>19.1</v>
+        <v>18.33</v>
       </c>
       <c r="E49" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="F49" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="G49" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="J49" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="K49" t="n">
-        <v>68.94</v>
+        <v>72.89</v>
       </c>
       <c r="L49" t="n">
-        <v>69.94</v>
+        <v>76.66</v>
       </c>
       <c r="M49" t="n">
-        <v>66.66</v>
+        <v>67.31</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4462</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6539</v>
+        <v>6496</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
         <v>4</v>
@@ -3507,7 +3507,7 @@
         <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,60 +533,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.02</v>
+        <v>16.61</v>
       </c>
       <c r="C2" t="n">
-        <v>18.12</v>
+        <v>16.65</v>
       </c>
       <c r="D2" t="n">
-        <v>17.84</v>
+        <v>16.59</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="F2" t="n">
-        <v>14.6</v>
+        <v>15.8</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.36</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.31</v>
+        <v>0.06</v>
       </c>
       <c r="K2" t="n">
-        <v>82.62</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>84.8</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>80.54000000000001</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1869</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6474</v>
+        <v>6434</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -595,60 +595,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.95</v>
+        <v>16.91</v>
       </c>
       <c r="C3" t="n">
-        <v>21.08</v>
+        <v>17.19</v>
       </c>
       <c r="D3" t="n">
-        <v>18.04</v>
+        <v>16.69</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9</v>
+        <v>15.9</v>
       </c>
       <c r="F3" t="n">
-        <v>11.6</v>
+        <v>15.6</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.82</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.41</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>64.73999999999999</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>79.75</v>
+        <v>96.09</v>
       </c>
       <c r="M3" t="n">
-        <v>55.98</v>
+        <v>90.87</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6474</v>
+        <v>6442</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -657,60 +657,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.54</v>
+        <v>17.68</v>
       </c>
       <c r="C4" t="n">
-        <v>21.83</v>
+        <v>18.12</v>
       </c>
       <c r="D4" t="n">
-        <v>21.18</v>
+        <v>17.08</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6</v>
+        <v>15.3</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7</v>
+        <v>14.6</v>
       </c>
       <c r="G4" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1.19</v>
+        <v>0.27</v>
       </c>
       <c r="J4" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="K4" t="n">
-        <v>53.45</v>
+        <v>86.59</v>
       </c>
       <c r="L4" t="n">
-        <v>58.22</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>49.34</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2410</v>
+        <v>685</v>
       </c>
       <c r="P4" t="n">
-        <v>6485</v>
+        <v>6451</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -719,178 +719,178 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.02</v>
+        <v>19.95</v>
       </c>
       <c r="C5" t="n">
-        <v>22.16</v>
+        <v>21.08</v>
       </c>
       <c r="D5" t="n">
-        <v>21.88</v>
+        <v>18.04</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="F5" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="G5" t="n">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="J5" t="n">
-        <v>1.24</v>
+        <v>0.41</v>
       </c>
       <c r="K5" t="n">
-        <v>50.18</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>52.66</v>
+        <v>79.75</v>
       </c>
       <c r="M5" t="n">
-        <v>47.74</v>
+        <v>55.98</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4352</v>
+        <v>1926</v>
       </c>
       <c r="P5" t="n">
-        <v>6511</v>
+        <v>6474</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.31</v>
+        <v>21.54</v>
       </c>
       <c r="C6" t="n">
-        <v>22.81</v>
+        <v>21.83</v>
       </c>
       <c r="D6" t="n">
-        <v>22.04</v>
+        <v>21.18</v>
       </c>
       <c r="E6" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F6" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="G6" t="n">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="J6" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="K6" t="n">
-        <v>50.19</v>
+        <v>53.45</v>
       </c>
       <c r="L6" t="n">
-        <v>51.75</v>
+        <v>58.22</v>
       </c>
       <c r="M6" t="n">
-        <v>47.76</v>
+        <v>49.34</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5406</v>
+        <v>2410</v>
       </c>
       <c r="P6" t="n">
-        <v>6539</v>
+        <v>6485</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.68</v>
+        <v>22.02</v>
       </c>
       <c r="C7" t="n">
-        <v>23.1</v>
+        <v>22.16</v>
       </c>
       <c r="D7" t="n">
-        <v>22.11</v>
+        <v>21.88</v>
       </c>
       <c r="E7" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="F7" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G7" t="n">
-        <v>384</v>
+        <v>111</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="J7" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="K7" t="n">
-        <v>48.82</v>
+        <v>50.18</v>
       </c>
       <c r="L7" t="n">
-        <v>51.28</v>
+        <v>52.66</v>
       </c>
       <c r="M7" t="n">
-        <v>47.13</v>
+        <v>47.74</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6743</v>
+        <v>4352</v>
       </c>
       <c r="P7" t="n">
-        <v>6573</v>
+        <v>6511</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
         <v>7</v>
@@ -899,57 +899,57 @@
         <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.01</v>
+        <v>22.31</v>
       </c>
       <c r="C8" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D8" t="n">
-        <v>21.62</v>
+        <v>22.04</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F8" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="G8" t="n">
-        <v>452</v>
+        <v>198</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="J8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="K8" t="n">
-        <v>49.71</v>
+        <v>50.19</v>
       </c>
       <c r="L8" t="n">
-        <v>51.65</v>
+        <v>51.75</v>
       </c>
       <c r="M8" t="n">
-        <v>46.69</v>
+        <v>47.76</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6767</v>
+        <v>5406</v>
       </c>
       <c r="P8" t="n">
-        <v>6576</v>
+        <v>6539</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
@@ -961,66 +961,66 @@
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.59</v>
+        <v>22.68</v>
       </c>
       <c r="C9" t="n">
-        <v>22.58</v>
+        <v>23.1</v>
       </c>
       <c r="D9" t="n">
-        <v>20.76</v>
+        <v>22.11</v>
       </c>
       <c r="E9" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F9" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G9" t="n">
-        <v>564</v>
+        <v>384</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="K9" t="n">
-        <v>51.87</v>
+        <v>48.82</v>
       </c>
       <c r="L9" t="n">
-        <v>56.03</v>
+        <v>51.28</v>
       </c>
       <c r="M9" t="n">
-        <v>45.92</v>
+        <v>47.13</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6796</v>
+        <v>6743</v>
       </c>
       <c r="P9" t="n">
-        <v>6599</v>
+        <v>6573</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
         <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -1029,42 +1029,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.19</v>
+        <v>22.01</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64</v>
+        <v>22.58</v>
       </c>
       <c r="D10" t="n">
-        <v>19.53</v>
+        <v>21.62</v>
       </c>
       <c r="E10" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
         <v>10.6</v>
       </c>
       <c r="G10" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="J10" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="K10" t="n">
-        <v>55.29</v>
+        <v>49.71</v>
       </c>
       <c r="L10" t="n">
-        <v>57.87</v>
+        <v>51.65</v>
       </c>
       <c r="M10" t="n">
-        <v>52.99</v>
+        <v>46.69</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1076,13 +1076,13 @@
         <v>6576</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" t="n">
         <v>6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
       </c>
       <c r="T10" t="n">
         <v>60</v>
@@ -1091,240 +1091,240 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18.89</v>
+        <v>21.59</v>
       </c>
       <c r="C11" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D11" t="n">
-        <v>18.08</v>
+        <v>20.76</v>
       </c>
       <c r="E11" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="F11" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="G11" t="n">
-        <v>212</v>
+        <v>564</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.66</v>
+        <v>1.24</v>
       </c>
       <c r="J11" t="n">
-        <v>0.35</v>
+        <v>1.07</v>
       </c>
       <c r="K11" t="n">
-        <v>69.7</v>
+        <v>51.87</v>
       </c>
       <c r="L11" t="n">
-        <v>82.87</v>
+        <v>56.03</v>
       </c>
       <c r="M11" t="n">
-        <v>57.89</v>
+        <v>45.92</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6691</v>
+        <v>6796</v>
       </c>
       <c r="P11" t="n">
-        <v>6514</v>
+        <v>6599</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.5</v>
+        <v>20.19</v>
       </c>
       <c r="C12" t="n">
-        <v>17.9</v>
+        <v>20.64</v>
       </c>
       <c r="D12" t="n">
-        <v>17.26</v>
+        <v>19.53</v>
       </c>
       <c r="E12" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F12" t="n">
-        <v>14.3</v>
+        <v>10.6</v>
       </c>
       <c r="G12" t="n">
-        <v>43</v>
+        <v>426</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.31</v>
+        <v>1.05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="K12" t="n">
-        <v>84.14</v>
+        <v>55.29</v>
       </c>
       <c r="L12" t="n">
-        <v>87.05</v>
+        <v>57.87</v>
       </c>
       <c r="M12" t="n">
-        <v>79.48999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3786</v>
+        <v>6767</v>
       </c>
       <c r="P12" t="n">
-        <v>6422</v>
+        <v>6576</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.02</v>
+        <v>18.89</v>
       </c>
       <c r="C13" t="n">
-        <v>17.27</v>
+        <v>19.62</v>
       </c>
       <c r="D13" t="n">
-        <v>16.92</v>
+        <v>18.08</v>
       </c>
       <c r="E13" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="F13" t="n">
-        <v>14.1</v>
+        <v>10.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="J13" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="K13" t="n">
-        <v>86.8</v>
+        <v>69.7</v>
       </c>
       <c r="L13" t="n">
-        <v>88.91</v>
+        <v>82.87</v>
       </c>
       <c r="M13" t="n">
-        <v>81.98999999999999</v>
+        <v>57.89</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1246</v>
+        <v>6691</v>
       </c>
       <c r="P13" t="n">
-        <v>6414</v>
+        <v>6514</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.89</v>
+        <v>17.5</v>
       </c>
       <c r="C14" t="n">
-        <v>17.03</v>
+        <v>17.9</v>
       </c>
       <c r="D14" t="n">
-        <v>16.78</v>
+        <v>17.26</v>
       </c>
       <c r="E14" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F14" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="J14" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="K14" t="n">
-        <v>88.48999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="L14" t="n">
-        <v>90.31</v>
+        <v>87.05</v>
       </c>
       <c r="M14" t="n">
-        <v>85.76000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="P14" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>2</v>
@@ -1339,48 +1339,48 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.13</v>
+        <v>17.02</v>
       </c>
       <c r="C15" t="n">
-        <v>17.32</v>
+        <v>17.27</v>
       </c>
       <c r="D15" t="n">
-        <v>16.89</v>
+        <v>16.92</v>
       </c>
       <c r="E15" t="n">
         <v>14.7</v>
       </c>
       <c r="F15" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="K15" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="L15" t="n">
-        <v>88.63</v>
+        <v>88.91</v>
       </c>
       <c r="M15" t="n">
-        <v>83.40000000000001</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="P15" t="n">
         <v>6414</v>
@@ -1401,42 +1401,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.01</v>
+        <v>16.89</v>
       </c>
       <c r="C16" t="n">
-        <v>17.08</v>
+        <v>17.03</v>
       </c>
       <c r="D16" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F16" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J16" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="K16" t="n">
-        <v>88.16</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>88.7</v>
+        <v>90.31</v>
       </c>
       <c r="M16" t="n">
-        <v>87.34999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1445,13 +1445,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -1463,42 +1463,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.07</v>
+        <v>17.13</v>
       </c>
       <c r="C17" t="n">
-        <v>17.29</v>
+        <v>17.32</v>
       </c>
       <c r="D17" t="n">
-        <v>16.93</v>
+        <v>16.89</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F17" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.22</v>
       </c>
-      <c r="J17" t="n">
-        <v>0.2</v>
-      </c>
       <c r="K17" t="n">
-        <v>88.06999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>89.45999999999999</v>
+        <v>88.63</v>
       </c>
       <c r="M17" t="n">
-        <v>85.97</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -1525,42 +1525,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.44</v>
+        <v>17.01</v>
       </c>
       <c r="C18" t="n">
-        <v>17.52</v>
+        <v>17.08</v>
       </c>
       <c r="D18" t="n">
-        <v>17.31</v>
+        <v>16.93</v>
       </c>
       <c r="E18" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="J18" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="K18" t="n">
-        <v>84.31999999999999</v>
+        <v>88.16</v>
       </c>
       <c r="L18" t="n">
-        <v>85.27</v>
+        <v>88.7</v>
       </c>
       <c r="M18" t="n">
-        <v>82.56999999999999</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1569,16 +1569,16 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -1587,17 +1587,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.22</v>
+        <v>17.07</v>
       </c>
       <c r="C19" t="n">
-        <v>17.34</v>
+        <v>17.29</v>
       </c>
       <c r="D19" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E19" t="n">
         <v>15</v>
@@ -1610,19 +1610,19 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="J19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="K19" t="n">
-        <v>87.37</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>88.34999999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>86.23</v>
+        <v>85.97</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1631,13 +1631,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -1649,42 +1649,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="C20" t="n">
-        <v>17.5</v>
+        <v>17.52</v>
       </c>
       <c r="D20" t="n">
-        <v>17.22</v>
+        <v>17.31</v>
       </c>
       <c r="E20" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F20" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="J20" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="K20" t="n">
-        <v>87.89</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>89.09</v>
+        <v>85.27</v>
       </c>
       <c r="M20" t="n">
-        <v>87.03</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -1711,42 +1711,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.51</v>
+        <v>17.22</v>
       </c>
       <c r="C21" t="n">
-        <v>17.64</v>
+        <v>17.34</v>
       </c>
       <c r="D21" t="n">
-        <v>17.34</v>
+        <v>17.11</v>
       </c>
       <c r="E21" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.22</v>
       </c>
-      <c r="J21" t="n">
-        <v>0.19</v>
-      </c>
       <c r="K21" t="n">
-        <v>88.95</v>
+        <v>87.37</v>
       </c>
       <c r="L21" t="n">
-        <v>90.3</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>87.78</v>
+        <v>86.23</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1755,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
@@ -1773,42 +1773,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.73</v>
+        <v>17.38</v>
       </c>
       <c r="C22" t="n">
-        <v>18.06</v>
+        <v>17.5</v>
       </c>
       <c r="D22" t="n">
-        <v>17.42</v>
+        <v>17.22</v>
       </c>
       <c r="E22" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="F22" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="J22" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="K22" t="n">
-        <v>85.27</v>
+        <v>87.89</v>
       </c>
       <c r="L22" t="n">
-        <v>88.19</v>
+        <v>89.09</v>
       </c>
       <c r="M22" t="n">
-        <v>81.95</v>
+        <v>87.03</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1817,13 +1817,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6457</v>
+        <v>6408</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -1835,42 +1835,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18.36</v>
+        <v>17.51</v>
       </c>
       <c r="C23" t="n">
-        <v>18.45</v>
+        <v>17.64</v>
       </c>
       <c r="D23" t="n">
-        <v>18.19</v>
+        <v>17.34</v>
       </c>
       <c r="E23" t="n">
-        <v>14.9</v>
+        <v>15.6</v>
       </c>
       <c r="F23" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="J23" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="K23" t="n">
-        <v>80.73</v>
+        <v>88.95</v>
       </c>
       <c r="L23" t="n">
-        <v>81.93000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="M23" t="n">
-        <v>79.83</v>
+        <v>87.78</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1879,16 +1879,16 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6471</v>
+        <v>6437</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -1897,42 +1897,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18.81</v>
+        <v>17.73</v>
       </c>
       <c r="C24" t="n">
-        <v>19.07</v>
+        <v>18.06</v>
       </c>
       <c r="D24" t="n">
-        <v>18.51</v>
+        <v>17.42</v>
       </c>
       <c r="E24" t="n">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="F24" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="K24" t="n">
-        <v>76.59999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="L24" t="n">
-        <v>79.87</v>
+        <v>88.19</v>
       </c>
       <c r="M24" t="n">
-        <v>74.01000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1941,16 +1941,16 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6482</v>
+        <v>6457</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -1959,42 +1959,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.81</v>
+        <v>18.36</v>
       </c>
       <c r="C25" t="n">
-        <v>20.67</v>
+        <v>18.45</v>
       </c>
       <c r="D25" t="n">
-        <v>18.96</v>
+        <v>18.19</v>
       </c>
       <c r="E25" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="F25" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="K25" t="n">
-        <v>69.16</v>
+        <v>80.73</v>
       </c>
       <c r="L25" t="n">
-        <v>75.04000000000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>63.43</v>
+        <v>79.83</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2003,16 +2003,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6496</v>
+        <v>6471</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2021,299 +2021,299 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21.22</v>
+        <v>18.81</v>
       </c>
       <c r="C26" t="n">
-        <v>21.6</v>
+        <v>19.07</v>
       </c>
       <c r="D26" t="n">
-        <v>20.76</v>
+        <v>18.51</v>
       </c>
       <c r="E26" t="n">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="G26" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.99</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="K26" t="n">
-        <v>60.52</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>62.17</v>
+        <v>79.87</v>
       </c>
       <c r="M26" t="n">
-        <v>58.42</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6516</v>
+        <v>6482</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.62</v>
+        <v>19.81</v>
       </c>
       <c r="C27" t="n">
-        <v>21.84</v>
+        <v>20.67</v>
       </c>
       <c r="D27" t="n">
-        <v>21.44</v>
+        <v>18.96</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="F27" t="n">
-        <v>12.7</v>
+        <v>13.4</v>
       </c>
       <c r="G27" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>0.54</v>
       </c>
       <c r="K27" t="n">
-        <v>58.13</v>
+        <v>69.16</v>
       </c>
       <c r="L27" t="n">
-        <v>60.32</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>56.76</v>
+        <v>63.43</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6548</v>
+        <v>6496</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21.96</v>
+        <v>21.22</v>
       </c>
       <c r="C28" t="n">
-        <v>22.41</v>
+        <v>21.6</v>
       </c>
       <c r="D28" t="n">
-        <v>21.77</v>
+        <v>20.76</v>
       </c>
       <c r="E28" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="F28" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="J28" t="n">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="K28" t="n">
-        <v>55.95</v>
+        <v>60.52</v>
       </c>
       <c r="L28" t="n">
-        <v>57.92</v>
+        <v>62.17</v>
       </c>
       <c r="M28" t="n">
-        <v>54.15</v>
+        <v>58.42</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6619</v>
+        <v>2990</v>
       </c>
       <c r="P28" t="n">
-        <v>6573</v>
+        <v>6516</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22.46</v>
+        <v>21.62</v>
       </c>
       <c r="C29" t="n">
-        <v>23.17</v>
+        <v>21.84</v>
       </c>
       <c r="D29" t="n">
-        <v>21.82</v>
+        <v>21.44</v>
       </c>
       <c r="E29" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G29" t="n">
-        <v>383</v>
+        <v>137</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="J29" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>52.56</v>
+        <v>58.13</v>
       </c>
       <c r="L29" t="n">
-        <v>54.35</v>
+        <v>60.32</v>
       </c>
       <c r="M29" t="n">
-        <v>50.6</v>
+        <v>56.76</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6763</v>
+        <v>5684</v>
       </c>
       <c r="P29" t="n">
-        <v>6593</v>
+        <v>6548</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.1</v>
+        <v>21.96</v>
       </c>
       <c r="C30" t="n">
-        <v>22.92</v>
+        <v>22.41</v>
       </c>
       <c r="D30" t="n">
-        <v>21.76</v>
+        <v>21.77</v>
       </c>
       <c r="E30" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F30" t="n">
         <v>12.2</v>
       </c>
-      <c r="F30" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G30" t="n">
-        <v>479</v>
+        <v>205</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="J30" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="K30" t="n">
-        <v>53.58</v>
+        <v>55.95</v>
       </c>
       <c r="L30" t="n">
-        <v>55.95</v>
+        <v>57.92</v>
       </c>
       <c r="M30" t="n">
-        <v>51.48</v>
+        <v>54.15</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6739</v>
+        <v>6619</v>
       </c>
       <c r="P30" t="n">
-        <v>6582</v>
+        <v>6573</v>
       </c>
       <c r="Q30" t="n">
         <v>6</v>
@@ -2331,60 +2331,60 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.45</v>
+        <v>22.46</v>
       </c>
       <c r="C31" t="n">
-        <v>22.62</v>
+        <v>23.17</v>
       </c>
       <c r="D31" t="n">
-        <v>20.83</v>
+        <v>21.82</v>
       </c>
       <c r="E31" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F31" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G31" t="n">
-        <v>640</v>
+        <v>383</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="J31" t="n">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="K31" t="n">
-        <v>56.35</v>
+        <v>52.56</v>
       </c>
       <c r="L31" t="n">
-        <v>62.61</v>
+        <v>54.35</v>
       </c>
       <c r="M31" t="n">
-        <v>51.88</v>
+        <v>50.6</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6810</v>
+        <v>6763</v>
       </c>
       <c r="P31" t="n">
-        <v>6610</v>
+        <v>6593</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
         <v>6</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="n">
         <v>60</v>
@@ -2393,60 +2393,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19.67</v>
+        <v>22.1</v>
       </c>
       <c r="C32" t="n">
-        <v>20.85</v>
+        <v>22.92</v>
       </c>
       <c r="D32" t="n">
-        <v>19.11</v>
+        <v>21.76</v>
       </c>
       <c r="E32" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F32" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="G32" t="n">
-        <v>279</v>
+        <v>479</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.77</v>
+        <v>1.23</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="K32" t="n">
-        <v>66.39</v>
+        <v>53.58</v>
       </c>
       <c r="L32" t="n">
-        <v>68.68000000000001</v>
+        <v>55.95</v>
       </c>
       <c r="M32" t="n">
-        <v>61.4</v>
+        <v>51.48</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6772</v>
+        <v>6739</v>
       </c>
       <c r="P32" t="n">
-        <v>6571</v>
+        <v>6582</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R32" t="n">
+        <v>6</v>
+      </c>
+      <c r="S32" t="n">
         <v>5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
       </c>
       <c r="T32" t="n">
         <v>60</v>
@@ -2455,122 +2455,122 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18.92</v>
+        <v>21.45</v>
       </c>
       <c r="C33" t="n">
-        <v>19.22</v>
+        <v>22.62</v>
       </c>
       <c r="D33" t="n">
-        <v>18.64</v>
+        <v>20.83</v>
       </c>
       <c r="E33" t="n">
-        <v>13.6</v>
+        <v>12.3</v>
       </c>
       <c r="F33" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="G33" t="n">
-        <v>143</v>
+        <v>640</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="J33" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="K33" t="n">
-        <v>71.48999999999999</v>
+        <v>56.35</v>
       </c>
       <c r="L33" t="n">
-        <v>73.28</v>
+        <v>62.61</v>
       </c>
       <c r="M33" t="n">
-        <v>69.45</v>
+        <v>51.88</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6254</v>
+        <v>6810</v>
       </c>
       <c r="P33" t="n">
-        <v>6508</v>
+        <v>6610</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18.78</v>
+        <v>19.67</v>
       </c>
       <c r="C34" t="n">
-        <v>18.89</v>
+        <v>20.85</v>
       </c>
       <c r="D34" t="n">
-        <v>18.67</v>
+        <v>19.11</v>
       </c>
       <c r="E34" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F34" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="G34" t="n">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="J34" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="K34" t="n">
-        <v>70.87</v>
+        <v>66.39</v>
       </c>
       <c r="L34" t="n">
-        <v>73.17</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>68.48</v>
+        <v>61.4</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>5929</v>
+        <v>6772</v>
       </c>
       <c r="P34" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
         <v>4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3</v>
       </c>
       <c r="T34" t="n">
         <v>60</v>
@@ -2579,51 +2579,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>18.59</v>
+        <v>18.92</v>
       </c>
       <c r="C35" t="n">
-        <v>19.26</v>
+        <v>19.22</v>
       </c>
       <c r="D35" t="n">
-        <v>18.18</v>
+        <v>18.64</v>
       </c>
       <c r="E35" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="F35" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G35" t="n">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="J35" t="n">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
       <c r="K35" t="n">
-        <v>76.48999999999999</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>80.08</v>
+        <v>73.28</v>
       </c>
       <c r="M35" t="n">
-        <v>71.70999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>5478</v>
+        <v>6254</v>
       </c>
       <c r="P35" t="n">
-        <v>6494</v>
+        <v>6508</v>
       </c>
       <c r="Q35" t="n">
         <v>3</v>
@@ -2632,69 +2632,69 @@
         <v>3</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.89</v>
+        <v>18.78</v>
       </c>
       <c r="C36" t="n">
-        <v>18.29</v>
+        <v>18.89</v>
       </c>
       <c r="D36" t="n">
-        <v>17.02</v>
+        <v>18.67</v>
       </c>
       <c r="E36" t="n">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="F36" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="G36" t="n">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="J36" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="K36" t="n">
-        <v>82.51000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="L36" t="n">
-        <v>87.40000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="M36" t="n">
-        <v>79.09999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6633</v>
+        <v>5929</v>
       </c>
       <c r="P36" t="n">
-        <v>6488</v>
+        <v>6494</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
         <v>60</v>
@@ -2703,175 +2703,175 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.49</v>
+        <v>18.59</v>
       </c>
       <c r="C37" t="n">
-        <v>16.79</v>
+        <v>19.26</v>
       </c>
       <c r="D37" t="n">
-        <v>16.31</v>
+        <v>18.18</v>
       </c>
       <c r="E37" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F37" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="G37" t="n">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="K37" t="n">
-        <v>89.09</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>91.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M37" t="n">
-        <v>87.73</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>5349</v>
+        <v>5478</v>
       </c>
       <c r="P37" t="n">
-        <v>6445</v>
+        <v>6494</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.27</v>
+        <v>17.89</v>
       </c>
       <c r="C38" t="n">
-        <v>16.31</v>
+        <v>18.29</v>
       </c>
       <c r="D38" t="n">
-        <v>16.24</v>
+        <v>17.02</v>
       </c>
       <c r="E38" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F38" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="J38" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="K38" t="n">
-        <v>90.12</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>91.63</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>88.84</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P38" t="n">
-        <v>6422</v>
+        <v>6488</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.37</v>
+        <v>16.49</v>
       </c>
       <c r="C39" t="n">
-        <v>16.42</v>
+        <v>16.79</v>
       </c>
       <c r="D39" t="n">
-        <v>16.3</v>
+        <v>16.31</v>
       </c>
       <c r="E39" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F39" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>0.2</v>
       </c>
       <c r="J39" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="K39" t="n">
-        <v>88.97</v>
+        <v>89.09</v>
       </c>
       <c r="L39" t="n">
-        <v>90.09</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>88.26000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P39" t="n">
-        <v>6414</v>
+        <v>6445</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -2889,44 +2889,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.35</v>
+        <v>16.27</v>
       </c>
       <c r="C40" t="n">
-        <v>16.36</v>
+        <v>16.31</v>
       </c>
       <c r="D40" t="n">
-        <v>16.35</v>
+        <v>16.24</v>
       </c>
       <c r="E40" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="F40" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="n">
-        <v>2592</v>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="J40" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="K40" t="n">
-        <v>84.98</v>
+        <v>90.12</v>
       </c>
       <c r="L40" t="n">
-        <v>85.65000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="M40" t="n">
-        <v>84.31</v>
+        <v>88.84</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2935,13 +2933,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -2953,44 +2951,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.33</v>
+        <v>16.37</v>
       </c>
       <c r="C41" t="n">
-        <v>16.56</v>
+        <v>16.42</v>
       </c>
       <c r="D41" t="n">
-        <v>15.86</v>
+        <v>16.3</v>
       </c>
       <c r="E41" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="n">
-        <v>2522</v>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K41" t="n">
-        <v>89.8</v>
+        <v>88.97</v>
       </c>
       <c r="L41" t="n">
-        <v>99.73</v>
+        <v>90.09</v>
       </c>
       <c r="M41" t="n">
-        <v>85.27</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2999,16 +2995,16 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3017,42 +3013,44 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16.27</v>
+        <v>16.35</v>
       </c>
       <c r="C42" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="D42" t="n">
-        <v>16.2</v>
+        <v>16.35</v>
       </c>
       <c r="E42" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F42" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>2592</v>
+      </c>
       <c r="I42" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="J42" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K42" t="n">
-        <v>90.44</v>
+        <v>84.98</v>
       </c>
       <c r="L42" t="n">
-        <v>91.61</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>89.09999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3061,13 +3059,13 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -3079,42 +3077,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.26</v>
+        <v>16.33</v>
       </c>
       <c r="C43" t="n">
-        <v>16.49</v>
+        <v>16.56</v>
       </c>
       <c r="D43" t="n">
-        <v>16.14</v>
+        <v>15.86</v>
       </c>
       <c r="E43" t="n">
         <v>14.6</v>
       </c>
       <c r="F43" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>2522</v>
+      </c>
       <c r="I43" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J43" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>90.33</v>
+        <v>89.8</v>
       </c>
       <c r="L43" t="n">
-        <v>91.40000000000001</v>
+        <v>99.73</v>
       </c>
       <c r="M43" t="n">
-        <v>89.20999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3141,42 +3141,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.61</v>
+        <v>16.27</v>
       </c>
       <c r="C44" t="n">
-        <v>16.82</v>
+        <v>16.37</v>
       </c>
       <c r="D44" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="E44" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F44" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="J44" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K44" t="n">
-        <v>87.3</v>
+        <v>90.44</v>
       </c>
       <c r="L44" t="n">
-        <v>89.45</v>
+        <v>91.61</v>
       </c>
       <c r="M44" t="n">
-        <v>86.06</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6434</v>
+        <v>6417</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
@@ -3203,42 +3203,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.92</v>
+        <v>16.26</v>
       </c>
       <c r="C45" t="n">
-        <v>17.22</v>
+        <v>16.49</v>
       </c>
       <c r="D45" t="n">
-        <v>16.72</v>
+        <v>16.14</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F45" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="J45" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="K45" t="n">
-        <v>83.48999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="L45" t="n">
-        <v>85.67</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>80.43000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3247,16 +3247,16 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -3265,42 +3265,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.37</v>
+        <v>16.61</v>
       </c>
       <c r="C46" t="n">
-        <v>17.64</v>
+        <v>16.82</v>
       </c>
       <c r="D46" t="n">
-        <v>17.15</v>
+        <v>16.45</v>
       </c>
       <c r="E46" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="F46" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="J46" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="K46" t="n">
-        <v>81.5</v>
+        <v>87.3</v>
       </c>
       <c r="L46" t="n">
-        <v>83.2</v>
+        <v>89.45</v>
       </c>
       <c r="M46" t="n">
-        <v>79.69</v>
+        <v>86.06</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3309,16 +3309,16 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6471</v>
+        <v>6434</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -3327,42 +3327,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.37</v>
+        <v>16.92</v>
       </c>
       <c r="C47" t="n">
-        <v>17.71</v>
+        <v>17.22</v>
       </c>
       <c r="D47" t="n">
-        <v>17.16</v>
+        <v>16.72</v>
       </c>
       <c r="E47" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J47" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="K47" t="n">
-        <v>83.11</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>85.31</v>
+        <v>85.67</v>
       </c>
       <c r="M47" t="n">
-        <v>78.94</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6474</v>
+        <v>6465</v>
       </c>
       <c r="Q47" t="n">
         <v>2</v>
@@ -3389,42 +3389,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:00</t>
+          <t>2026-10-15 22:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.78</v>
+        <v>17.37</v>
       </c>
       <c r="C48" t="n">
-        <v>18.2</v>
+        <v>17.64</v>
       </c>
       <c r="D48" t="n">
-        <v>17.44</v>
+        <v>17.15</v>
       </c>
       <c r="E48" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="F48" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="J48" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="K48" t="n">
-        <v>81.01000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="L48" t="n">
-        <v>82.84999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="M48" t="n">
-        <v>78.13</v>
+        <v>79.69</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6494</v>
+        <v>6471</v>
       </c>
       <c r="Q48" t="n">
         <v>2</v>
@@ -3451,42 +3451,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 19:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18.91</v>
+        <v>17.37</v>
       </c>
       <c r="C49" t="n">
-        <v>19.32</v>
+        <v>17.71</v>
       </c>
       <c r="D49" t="n">
-        <v>18.33</v>
+        <v>17.16</v>
       </c>
       <c r="E49" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="F49" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="J49" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="K49" t="n">
-        <v>72.89</v>
+        <v>83.11</v>
       </c>
       <c r="L49" t="n">
-        <v>76.66</v>
+        <v>85.31</v>
       </c>
       <c r="M49" t="n">
-        <v>67.31</v>
+        <v>78.94</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3495,16 +3495,16 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6496</v>
+        <v>6474</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,42 +533,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.61</v>
+        <v>16.81</v>
       </c>
       <c r="C2" t="n">
-        <v>16.65</v>
+        <v>16.91</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59</v>
+        <v>16.66</v>
       </c>
       <c r="E2" t="n">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="F2" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="K2" t="n">
-        <v>95.79000000000001</v>
+        <v>90.84</v>
       </c>
       <c r="L2" t="n">
-        <v>96.45999999999999</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>95.43000000000001</v>
+        <v>89.92</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -577,16 +577,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6434</v>
+        <v>6414</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -595,42 +595,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.91</v>
+        <v>16.79</v>
       </c>
       <c r="C3" t="n">
-        <v>17.19</v>
+        <v>16.87</v>
       </c>
       <c r="D3" t="n">
-        <v>16.69</v>
+        <v>16.65</v>
       </c>
       <c r="E3" t="n">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="F3" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="K3" t="n">
-        <v>94.18000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>96.09</v>
+        <v>93.45</v>
       </c>
       <c r="M3" t="n">
-        <v>90.87</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6442</v>
+        <v>6420</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -648,7 +648,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -657,60 +657,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.68</v>
+        <v>16.6</v>
       </c>
       <c r="C4" t="n">
-        <v>18.12</v>
+        <v>16.66</v>
       </c>
       <c r="D4" t="n">
-        <v>17.08</v>
+        <v>16.52</v>
       </c>
       <c r="E4" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="F4" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="K4" t="n">
-        <v>86.59</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>93.40000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>80.54000000000001</v>
+        <v>93.84</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>6451</v>
+        <v>6425</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -719,60 +719,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.95</v>
+        <v>16.91</v>
       </c>
       <c r="C5" t="n">
-        <v>21.08</v>
+        <v>17.19</v>
       </c>
       <c r="D5" t="n">
-        <v>18.04</v>
+        <v>16.69</v>
       </c>
       <c r="E5" t="n">
-        <v>12.9</v>
+        <v>15.9</v>
       </c>
       <c r="F5" t="n">
-        <v>11.6</v>
+        <v>15.6</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.82</v>
+        <v>0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.41</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>64.73999999999999</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>79.75</v>
+        <v>96.09</v>
       </c>
       <c r="M5" t="n">
-        <v>55.98</v>
+        <v>90.87</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6474</v>
+        <v>6442</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -781,60 +781,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.54</v>
+        <v>17.68</v>
       </c>
       <c r="C6" t="n">
-        <v>21.83</v>
+        <v>18.12</v>
       </c>
       <c r="D6" t="n">
-        <v>21.18</v>
+        <v>17.08</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6</v>
+        <v>15.3</v>
       </c>
       <c r="F6" t="n">
-        <v>10.7</v>
+        <v>14.6</v>
       </c>
       <c r="G6" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1.19</v>
+        <v>0.27</v>
       </c>
       <c r="J6" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="K6" t="n">
-        <v>53.45</v>
+        <v>86.59</v>
       </c>
       <c r="L6" t="n">
-        <v>58.22</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>49.34</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2410</v>
+        <v>685</v>
       </c>
       <c r="P6" t="n">
-        <v>6485</v>
+        <v>6451</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -843,178 +843,178 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.02</v>
+        <v>19.95</v>
       </c>
       <c r="C7" t="n">
-        <v>22.16</v>
+        <v>21.08</v>
       </c>
       <c r="D7" t="n">
-        <v>21.88</v>
+        <v>18.04</v>
       </c>
       <c r="E7" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="F7" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="G7" t="n">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="J7" t="n">
-        <v>1.24</v>
+        <v>0.41</v>
       </c>
       <c r="K7" t="n">
-        <v>50.18</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>52.66</v>
+        <v>79.75</v>
       </c>
       <c r="M7" t="n">
-        <v>47.74</v>
+        <v>55.98</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4352</v>
+        <v>1926</v>
       </c>
       <c r="P7" t="n">
-        <v>6511</v>
+        <v>6474</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.31</v>
+        <v>21.54</v>
       </c>
       <c r="C8" t="n">
-        <v>22.81</v>
+        <v>21.83</v>
       </c>
       <c r="D8" t="n">
-        <v>22.04</v>
+        <v>21.18</v>
       </c>
       <c r="E8" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F8" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="G8" t="n">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="J8" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="K8" t="n">
-        <v>50.19</v>
+        <v>53.45</v>
       </c>
       <c r="L8" t="n">
-        <v>51.75</v>
+        <v>58.22</v>
       </c>
       <c r="M8" t="n">
-        <v>47.76</v>
+        <v>49.34</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5406</v>
+        <v>2410</v>
       </c>
       <c r="P8" t="n">
-        <v>6539</v>
+        <v>6485</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.68</v>
+        <v>22.02</v>
       </c>
       <c r="C9" t="n">
-        <v>23.1</v>
+        <v>22.16</v>
       </c>
       <c r="D9" t="n">
-        <v>22.11</v>
+        <v>21.88</v>
       </c>
       <c r="E9" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="F9" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G9" t="n">
-        <v>384</v>
+        <v>111</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="J9" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="K9" t="n">
-        <v>48.82</v>
+        <v>50.18</v>
       </c>
       <c r="L9" t="n">
-        <v>51.28</v>
+        <v>52.66</v>
       </c>
       <c r="M9" t="n">
-        <v>47.13</v>
+        <v>47.74</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6743</v>
+        <v>4352</v>
       </c>
       <c r="P9" t="n">
-        <v>6573</v>
+        <v>6511</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
         <v>7</v>
@@ -1023,57 +1023,57 @@
         <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.01</v>
+        <v>22.31</v>
       </c>
       <c r="C10" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D10" t="n">
-        <v>21.62</v>
+        <v>22.04</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F10" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="G10" t="n">
-        <v>452</v>
+        <v>198</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="J10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="K10" t="n">
-        <v>49.71</v>
+        <v>50.19</v>
       </c>
       <c r="L10" t="n">
-        <v>51.65</v>
+        <v>51.75</v>
       </c>
       <c r="M10" t="n">
-        <v>46.69</v>
+        <v>47.76</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6767</v>
+        <v>5406</v>
       </c>
       <c r="P10" t="n">
-        <v>6576</v>
+        <v>6539</v>
       </c>
       <c r="Q10" t="n">
         <v>6</v>
@@ -1085,66 +1085,66 @@
         <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.59</v>
+        <v>22.68</v>
       </c>
       <c r="C11" t="n">
-        <v>22.58</v>
+        <v>23.1</v>
       </c>
       <c r="D11" t="n">
-        <v>20.76</v>
+        <v>22.11</v>
       </c>
       <c r="E11" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F11" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G11" t="n">
-        <v>564</v>
+        <v>384</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="K11" t="n">
-        <v>51.87</v>
+        <v>48.82</v>
       </c>
       <c r="L11" t="n">
-        <v>56.03</v>
+        <v>51.28</v>
       </c>
       <c r="M11" t="n">
-        <v>45.92</v>
+        <v>47.13</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6796</v>
+        <v>6743</v>
       </c>
       <c r="P11" t="n">
-        <v>6599</v>
+        <v>6573</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
         <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
         <v>60</v>
@@ -1153,42 +1153,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.19</v>
+        <v>22.01</v>
       </c>
       <c r="C12" t="n">
-        <v>20.64</v>
+        <v>22.58</v>
       </c>
       <c r="D12" t="n">
-        <v>19.53</v>
+        <v>21.62</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
         <v>10.6</v>
       </c>
       <c r="G12" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="J12" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="K12" t="n">
-        <v>55.29</v>
+        <v>49.71</v>
       </c>
       <c r="L12" t="n">
-        <v>57.87</v>
+        <v>51.65</v>
       </c>
       <c r="M12" t="n">
-        <v>52.99</v>
+        <v>46.69</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1200,13 +1200,13 @@
         <v>6576</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" t="n">
         <v>6</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
@@ -1215,240 +1215,240 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18.89</v>
+        <v>21.59</v>
       </c>
       <c r="C13" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D13" t="n">
-        <v>18.08</v>
+        <v>20.76</v>
       </c>
       <c r="E13" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="F13" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="G13" t="n">
-        <v>212</v>
+        <v>564</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.66</v>
+        <v>1.24</v>
       </c>
       <c r="J13" t="n">
-        <v>0.35</v>
+        <v>1.07</v>
       </c>
       <c r="K13" t="n">
-        <v>69.7</v>
+        <v>51.87</v>
       </c>
       <c r="L13" t="n">
-        <v>82.87</v>
+        <v>56.03</v>
       </c>
       <c r="M13" t="n">
-        <v>57.89</v>
+        <v>45.92</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6691</v>
+        <v>6796</v>
       </c>
       <c r="P13" t="n">
-        <v>6514</v>
+        <v>6599</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.5</v>
+        <v>20.19</v>
       </c>
       <c r="C14" t="n">
-        <v>17.9</v>
+        <v>20.64</v>
       </c>
       <c r="D14" t="n">
-        <v>17.26</v>
+        <v>19.53</v>
       </c>
       <c r="E14" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F14" t="n">
-        <v>14.3</v>
+        <v>10.6</v>
       </c>
       <c r="G14" t="n">
-        <v>43</v>
+        <v>426</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.31</v>
+        <v>1.05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="K14" t="n">
-        <v>84.14</v>
+        <v>55.29</v>
       </c>
       <c r="L14" t="n">
-        <v>87.05</v>
+        <v>57.87</v>
       </c>
       <c r="M14" t="n">
-        <v>79.48999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3786</v>
+        <v>6767</v>
       </c>
       <c r="P14" t="n">
-        <v>6422</v>
+        <v>6576</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.02</v>
+        <v>18.89</v>
       </c>
       <c r="C15" t="n">
-        <v>17.27</v>
+        <v>19.62</v>
       </c>
       <c r="D15" t="n">
-        <v>16.92</v>
+        <v>18.08</v>
       </c>
       <c r="E15" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="F15" t="n">
-        <v>14.1</v>
+        <v>10.9</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="J15" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="K15" t="n">
-        <v>86.8</v>
+        <v>69.7</v>
       </c>
       <c r="L15" t="n">
-        <v>88.91</v>
+        <v>82.87</v>
       </c>
       <c r="M15" t="n">
-        <v>81.98999999999999</v>
+        <v>57.89</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1246</v>
+        <v>6691</v>
       </c>
       <c r="P15" t="n">
-        <v>6414</v>
+        <v>6514</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.89</v>
+        <v>17.5</v>
       </c>
       <c r="C16" t="n">
-        <v>17.03</v>
+        <v>17.9</v>
       </c>
       <c r="D16" t="n">
-        <v>16.78</v>
+        <v>17.26</v>
       </c>
       <c r="E16" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F16" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="J16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="K16" t="n">
-        <v>88.48999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="L16" t="n">
-        <v>90.31</v>
+        <v>87.05</v>
       </c>
       <c r="M16" t="n">
-        <v>85.76000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="P16" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>2</v>
@@ -1463,48 +1463,48 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.13</v>
+        <v>17.02</v>
       </c>
       <c r="C17" t="n">
-        <v>17.32</v>
+        <v>17.27</v>
       </c>
       <c r="D17" t="n">
-        <v>16.89</v>
+        <v>16.92</v>
       </c>
       <c r="E17" t="n">
         <v>14.7</v>
       </c>
       <c r="F17" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="K17" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="L17" t="n">
-        <v>88.63</v>
+        <v>88.91</v>
       </c>
       <c r="M17" t="n">
-        <v>83.40000000000001</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="P17" t="n">
         <v>6414</v>
@@ -1525,42 +1525,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.01</v>
+        <v>16.89</v>
       </c>
       <c r="C18" t="n">
-        <v>17.08</v>
+        <v>17.03</v>
       </c>
       <c r="D18" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F18" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J18" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="K18" t="n">
-        <v>88.16</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>88.7</v>
+        <v>90.31</v>
       </c>
       <c r="M18" t="n">
-        <v>87.34999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1569,13 +1569,13 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -1587,42 +1587,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.07</v>
+        <v>17.13</v>
       </c>
       <c r="C19" t="n">
-        <v>17.29</v>
+        <v>17.32</v>
       </c>
       <c r="D19" t="n">
-        <v>16.93</v>
+        <v>16.89</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F19" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.22</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.2</v>
-      </c>
       <c r="K19" t="n">
-        <v>88.06999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>89.45999999999999</v>
+        <v>88.63</v>
       </c>
       <c r="M19" t="n">
-        <v>85.97</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1649,42 +1649,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.44</v>
+        <v>17.01</v>
       </c>
       <c r="C20" t="n">
-        <v>17.52</v>
+        <v>17.08</v>
       </c>
       <c r="D20" t="n">
-        <v>17.31</v>
+        <v>16.93</v>
       </c>
       <c r="E20" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="J20" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="K20" t="n">
-        <v>84.31999999999999</v>
+        <v>88.16</v>
       </c>
       <c r="L20" t="n">
-        <v>85.27</v>
+        <v>88.7</v>
       </c>
       <c r="M20" t="n">
-        <v>82.56999999999999</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -1711,17 +1711,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.22</v>
+        <v>17.07</v>
       </c>
       <c r="C21" t="n">
-        <v>17.34</v>
+        <v>17.29</v>
       </c>
       <c r="D21" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E21" t="n">
         <v>15</v>
@@ -1734,19 +1734,19 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="J21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="K21" t="n">
-        <v>87.37</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>88.34999999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>86.23</v>
+        <v>85.97</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1755,13 +1755,13 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -1773,42 +1773,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="C22" t="n">
-        <v>17.5</v>
+        <v>17.52</v>
       </c>
       <c r="D22" t="n">
-        <v>17.22</v>
+        <v>17.31</v>
       </c>
       <c r="E22" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F22" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="J22" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="K22" t="n">
-        <v>87.89</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>89.09</v>
+        <v>85.27</v>
       </c>
       <c r="M22" t="n">
-        <v>87.03</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1817,16 +1817,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -1835,42 +1835,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.51</v>
+        <v>17.22</v>
       </c>
       <c r="C23" t="n">
-        <v>17.64</v>
+        <v>17.34</v>
       </c>
       <c r="D23" t="n">
-        <v>17.34</v>
+        <v>17.11</v>
       </c>
       <c r="E23" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J23" t="n">
         <v>0.22</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.19</v>
-      </c>
       <c r="K23" t="n">
-        <v>88.95</v>
+        <v>87.37</v>
       </c>
       <c r="L23" t="n">
-        <v>90.3</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>87.78</v>
+        <v>86.23</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -1897,42 +1897,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.73</v>
+        <v>17.38</v>
       </c>
       <c r="C24" t="n">
-        <v>18.06</v>
+        <v>17.5</v>
       </c>
       <c r="D24" t="n">
-        <v>17.42</v>
+        <v>17.22</v>
       </c>
       <c r="E24" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="F24" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="J24" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="K24" t="n">
-        <v>85.27</v>
+        <v>87.89</v>
       </c>
       <c r="L24" t="n">
-        <v>88.19</v>
+        <v>89.09</v>
       </c>
       <c r="M24" t="n">
-        <v>81.95</v>
+        <v>87.03</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1941,13 +1941,13 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6457</v>
+        <v>6408</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -1959,42 +1959,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18.36</v>
+        <v>17.51</v>
       </c>
       <c r="C25" t="n">
-        <v>18.45</v>
+        <v>17.64</v>
       </c>
       <c r="D25" t="n">
-        <v>18.19</v>
+        <v>17.34</v>
       </c>
       <c r="E25" t="n">
-        <v>14.9</v>
+        <v>15.6</v>
       </c>
       <c r="F25" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="J25" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="K25" t="n">
-        <v>80.73</v>
+        <v>88.95</v>
       </c>
       <c r="L25" t="n">
-        <v>81.93000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="M25" t="n">
-        <v>79.83</v>
+        <v>87.78</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2003,16 +2003,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6471</v>
+        <v>6437</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2021,42 +2021,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.81</v>
+        <v>17.73</v>
       </c>
       <c r="C26" t="n">
-        <v>19.07</v>
+        <v>18.06</v>
       </c>
       <c r="D26" t="n">
-        <v>18.51</v>
+        <v>17.42</v>
       </c>
       <c r="E26" t="n">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="F26" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="J26" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="K26" t="n">
-        <v>76.59999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="L26" t="n">
-        <v>79.87</v>
+        <v>88.19</v>
       </c>
       <c r="M26" t="n">
-        <v>74.01000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2065,16 +2065,16 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6482</v>
+        <v>6457</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2083,42 +2083,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.81</v>
+        <v>18.36</v>
       </c>
       <c r="C27" t="n">
-        <v>20.67</v>
+        <v>18.45</v>
       </c>
       <c r="D27" t="n">
-        <v>18.96</v>
+        <v>18.19</v>
       </c>
       <c r="E27" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="F27" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="K27" t="n">
-        <v>69.16</v>
+        <v>80.73</v>
       </c>
       <c r="L27" t="n">
-        <v>75.04000000000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>63.43</v>
+        <v>79.83</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6496</v>
+        <v>6471</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2145,299 +2145,299 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21.22</v>
+        <v>18.81</v>
       </c>
       <c r="C28" t="n">
-        <v>21.6</v>
+        <v>19.07</v>
       </c>
       <c r="D28" t="n">
-        <v>20.76</v>
+        <v>18.51</v>
       </c>
       <c r="E28" t="n">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="G28" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.99</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="K28" t="n">
-        <v>60.52</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>62.17</v>
+        <v>79.87</v>
       </c>
       <c r="M28" t="n">
-        <v>58.42</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6516</v>
+        <v>6482</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.62</v>
+        <v>19.81</v>
       </c>
       <c r="C29" t="n">
-        <v>21.84</v>
+        <v>20.67</v>
       </c>
       <c r="D29" t="n">
-        <v>21.44</v>
+        <v>18.96</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="F29" t="n">
-        <v>12.7</v>
+        <v>13.4</v>
       </c>
       <c r="G29" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>0.54</v>
       </c>
       <c r="K29" t="n">
-        <v>58.13</v>
+        <v>69.16</v>
       </c>
       <c r="L29" t="n">
-        <v>60.32</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>56.76</v>
+        <v>63.43</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>6548</v>
+        <v>6496</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.96</v>
+        <v>21.22</v>
       </c>
       <c r="C30" t="n">
-        <v>22.41</v>
+        <v>21.6</v>
       </c>
       <c r="D30" t="n">
-        <v>21.77</v>
+        <v>20.76</v>
       </c>
       <c r="E30" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="F30" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="J30" t="n">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="K30" t="n">
-        <v>55.95</v>
+        <v>60.52</v>
       </c>
       <c r="L30" t="n">
-        <v>57.92</v>
+        <v>62.17</v>
       </c>
       <c r="M30" t="n">
-        <v>54.15</v>
+        <v>58.42</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6619</v>
+        <v>2990</v>
       </c>
       <c r="P30" t="n">
-        <v>6573</v>
+        <v>6516</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.46</v>
+        <v>21.62</v>
       </c>
       <c r="C31" t="n">
-        <v>23.17</v>
+        <v>21.84</v>
       </c>
       <c r="D31" t="n">
-        <v>21.82</v>
+        <v>21.44</v>
       </c>
       <c r="E31" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G31" t="n">
-        <v>383</v>
+        <v>137</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="J31" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="K31" t="n">
-        <v>52.56</v>
+        <v>58.13</v>
       </c>
       <c r="L31" t="n">
-        <v>54.35</v>
+        <v>60.32</v>
       </c>
       <c r="M31" t="n">
-        <v>50.6</v>
+        <v>56.76</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6763</v>
+        <v>5684</v>
       </c>
       <c r="P31" t="n">
-        <v>6593</v>
+        <v>6548</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.1</v>
+        <v>21.96</v>
       </c>
       <c r="C32" t="n">
-        <v>22.92</v>
+        <v>22.41</v>
       </c>
       <c r="D32" t="n">
-        <v>21.76</v>
+        <v>21.77</v>
       </c>
       <c r="E32" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F32" t="n">
         <v>12.2</v>
       </c>
-      <c r="F32" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G32" t="n">
-        <v>479</v>
+        <v>205</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="J32" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="K32" t="n">
-        <v>53.58</v>
+        <v>55.95</v>
       </c>
       <c r="L32" t="n">
-        <v>55.95</v>
+        <v>57.92</v>
       </c>
       <c r="M32" t="n">
-        <v>51.48</v>
+        <v>54.15</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6739</v>
+        <v>6619</v>
       </c>
       <c r="P32" t="n">
-        <v>6582</v>
+        <v>6573</v>
       </c>
       <c r="Q32" t="n">
         <v>6</v>
@@ -2455,60 +2455,60 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.45</v>
+        <v>22.46</v>
       </c>
       <c r="C33" t="n">
-        <v>22.62</v>
+        <v>23.17</v>
       </c>
       <c r="D33" t="n">
-        <v>20.83</v>
+        <v>21.82</v>
       </c>
       <c r="E33" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F33" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="G33" t="n">
-        <v>640</v>
+        <v>383</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="J33" t="n">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="K33" t="n">
-        <v>56.35</v>
+        <v>52.56</v>
       </c>
       <c r="L33" t="n">
-        <v>62.61</v>
+        <v>54.35</v>
       </c>
       <c r="M33" t="n">
-        <v>51.88</v>
+        <v>50.6</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6810</v>
+        <v>6763</v>
       </c>
       <c r="P33" t="n">
-        <v>6610</v>
+        <v>6593</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
         <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33" t="n">
         <v>60</v>
@@ -2517,60 +2517,60 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.67</v>
+        <v>22.1</v>
       </c>
       <c r="C34" t="n">
-        <v>20.85</v>
+        <v>22.92</v>
       </c>
       <c r="D34" t="n">
-        <v>19.11</v>
+        <v>21.76</v>
       </c>
       <c r="E34" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F34" t="n">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="G34" t="n">
-        <v>279</v>
+        <v>479</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.77</v>
+        <v>1.23</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="K34" t="n">
-        <v>66.39</v>
+        <v>53.58</v>
       </c>
       <c r="L34" t="n">
-        <v>68.68000000000001</v>
+        <v>55.95</v>
       </c>
       <c r="M34" t="n">
-        <v>61.4</v>
+        <v>51.48</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6772</v>
+        <v>6739</v>
       </c>
       <c r="P34" t="n">
-        <v>6571</v>
+        <v>6582</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
+        <v>6</v>
+      </c>
+      <c r="S34" t="n">
         <v>5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
       </c>
       <c r="T34" t="n">
         <v>60</v>
@@ -2579,122 +2579,122 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>18.92</v>
+        <v>21.45</v>
       </c>
       <c r="C35" t="n">
-        <v>19.22</v>
+        <v>22.62</v>
       </c>
       <c r="D35" t="n">
-        <v>18.64</v>
+        <v>20.83</v>
       </c>
       <c r="E35" t="n">
-        <v>13.6</v>
+        <v>12.3</v>
       </c>
       <c r="F35" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="G35" t="n">
-        <v>143</v>
+        <v>640</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="J35" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="K35" t="n">
-        <v>71.48999999999999</v>
+        <v>56.35</v>
       </c>
       <c r="L35" t="n">
-        <v>73.28</v>
+        <v>62.61</v>
       </c>
       <c r="M35" t="n">
-        <v>69.45</v>
+        <v>51.88</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6254</v>
+        <v>6810</v>
       </c>
       <c r="P35" t="n">
-        <v>6508</v>
+        <v>6610</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18.78</v>
+        <v>19.67</v>
       </c>
       <c r="C36" t="n">
-        <v>18.89</v>
+        <v>20.85</v>
       </c>
       <c r="D36" t="n">
-        <v>18.67</v>
+        <v>19.11</v>
       </c>
       <c r="E36" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F36" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="G36" t="n">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="J36" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="K36" t="n">
-        <v>70.87</v>
+        <v>66.39</v>
       </c>
       <c r="L36" t="n">
-        <v>73.17</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>68.48</v>
+        <v>61.4</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>5929</v>
+        <v>6772</v>
       </c>
       <c r="P36" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
+        <v>5</v>
+      </c>
+      <c r="S36" t="n">
         <v>4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
       </c>
       <c r="T36" t="n">
         <v>60</v>
@@ -2703,51 +2703,51 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.59</v>
+        <v>18.92</v>
       </c>
       <c r="C37" t="n">
-        <v>19.26</v>
+        <v>19.22</v>
       </c>
       <c r="D37" t="n">
-        <v>18.18</v>
+        <v>18.64</v>
       </c>
       <c r="E37" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="F37" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G37" t="n">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="J37" t="n">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
       <c r="K37" t="n">
-        <v>76.48999999999999</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>80.08</v>
+        <v>73.28</v>
       </c>
       <c r="M37" t="n">
-        <v>71.70999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>5478</v>
+        <v>6254</v>
       </c>
       <c r="P37" t="n">
-        <v>6494</v>
+        <v>6508</v>
       </c>
       <c r="Q37" t="n">
         <v>3</v>
@@ -2756,69 +2756,69 @@
         <v>3</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.89</v>
+        <v>18.78</v>
       </c>
       <c r="C38" t="n">
-        <v>18.29</v>
+        <v>18.89</v>
       </c>
       <c r="D38" t="n">
-        <v>17.02</v>
+        <v>18.67</v>
       </c>
       <c r="E38" t="n">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="F38" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="G38" t="n">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="J38" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="K38" t="n">
-        <v>82.51000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="L38" t="n">
-        <v>87.40000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="M38" t="n">
-        <v>79.09999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6633</v>
+        <v>5929</v>
       </c>
       <c r="P38" t="n">
-        <v>6488</v>
+        <v>6494</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
         <v>60</v>
@@ -2827,175 +2827,175 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.49</v>
+        <v>18.59</v>
       </c>
       <c r="C39" t="n">
-        <v>16.79</v>
+        <v>19.26</v>
       </c>
       <c r="D39" t="n">
-        <v>16.31</v>
+        <v>18.18</v>
       </c>
       <c r="E39" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F39" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="G39" t="n">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="K39" t="n">
-        <v>89.09</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>91.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M39" t="n">
-        <v>87.73</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>5349</v>
+        <v>5478</v>
       </c>
       <c r="P39" t="n">
-        <v>6445</v>
+        <v>6494</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.27</v>
+        <v>17.89</v>
       </c>
       <c r="C40" t="n">
-        <v>16.31</v>
+        <v>18.29</v>
       </c>
       <c r="D40" t="n">
-        <v>16.24</v>
+        <v>17.02</v>
       </c>
       <c r="E40" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F40" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="J40" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="K40" t="n">
-        <v>90.12</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>91.63</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>88.84</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P40" t="n">
-        <v>6422</v>
+        <v>6488</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.37</v>
+        <v>16.49</v>
       </c>
       <c r="C41" t="n">
-        <v>16.42</v>
+        <v>16.79</v>
       </c>
       <c r="D41" t="n">
-        <v>16.3</v>
+        <v>16.31</v>
       </c>
       <c r="E41" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F41" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>0.2</v>
       </c>
       <c r="J41" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="K41" t="n">
-        <v>88.97</v>
+        <v>89.09</v>
       </c>
       <c r="L41" t="n">
-        <v>90.09</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>88.26000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P41" t="n">
-        <v>6414</v>
+        <v>6445</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
@@ -3013,44 +3013,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16.35</v>
+        <v>16.27</v>
       </c>
       <c r="C42" t="n">
-        <v>16.36</v>
+        <v>16.31</v>
       </c>
       <c r="D42" t="n">
-        <v>16.35</v>
+        <v>16.24</v>
       </c>
       <c r="E42" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="F42" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="n">
-        <v>2592</v>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="J42" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="K42" t="n">
-        <v>84.98</v>
+        <v>90.12</v>
       </c>
       <c r="L42" t="n">
-        <v>85.65000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="M42" t="n">
-        <v>84.31</v>
+        <v>88.84</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3059,13 +3057,13 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -3077,44 +3075,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.33</v>
+        <v>16.37</v>
       </c>
       <c r="C43" t="n">
-        <v>16.56</v>
+        <v>16.42</v>
       </c>
       <c r="D43" t="n">
-        <v>15.86</v>
+        <v>16.3</v>
       </c>
       <c r="E43" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F43" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="n">
-        <v>2522</v>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K43" t="n">
-        <v>89.8</v>
+        <v>88.97</v>
       </c>
       <c r="L43" t="n">
-        <v>99.73</v>
+        <v>90.09</v>
       </c>
       <c r="M43" t="n">
-        <v>85.27</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3123,16 +3119,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6422</v>
+        <v>6414</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3141,42 +3137,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.27</v>
+        <v>16.35</v>
       </c>
       <c r="C44" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="D44" t="n">
-        <v>16.2</v>
+        <v>16.35</v>
       </c>
       <c r="E44" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="F44" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>2592</v>
+      </c>
       <c r="I44" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="J44" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="K44" t="n">
-        <v>90.44</v>
+        <v>84.98</v>
       </c>
       <c r="L44" t="n">
-        <v>91.61</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>89.09999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3185,13 +3183,13 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -3203,42 +3201,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 03:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.26</v>
+        <v>16.33</v>
       </c>
       <c r="C45" t="n">
-        <v>16.49</v>
+        <v>16.56</v>
       </c>
       <c r="D45" t="n">
-        <v>16.14</v>
+        <v>15.86</v>
       </c>
       <c r="E45" t="n">
         <v>14.6</v>
       </c>
       <c r="F45" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>2522</v>
+      </c>
       <c r="I45" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J45" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>90.33</v>
+        <v>89.8</v>
       </c>
       <c r="L45" t="n">
-        <v>91.40000000000001</v>
+        <v>99.73</v>
       </c>
       <c r="M45" t="n">
-        <v>89.20999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3247,16 +3247,16 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -3265,42 +3265,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 02:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.61</v>
+        <v>16.27</v>
       </c>
       <c r="C46" t="n">
-        <v>16.82</v>
+        <v>16.37</v>
       </c>
       <c r="D46" t="n">
-        <v>16.45</v>
+        <v>16.2</v>
       </c>
       <c r="E46" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F46" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="J46" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K46" t="n">
-        <v>87.3</v>
+        <v>90.44</v>
       </c>
       <c r="L46" t="n">
-        <v>89.45</v>
+        <v>91.61</v>
       </c>
       <c r="M46" t="n">
-        <v>86.06</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6434</v>
+        <v>6417</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
@@ -3327,42 +3327,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 01:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.92</v>
+        <v>16.26</v>
       </c>
       <c r="C47" t="n">
-        <v>17.22</v>
+        <v>16.49</v>
       </c>
       <c r="D47" t="n">
-        <v>16.72</v>
+        <v>16.14</v>
       </c>
       <c r="E47" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="F47" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="J47" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="K47" t="n">
-        <v>83.48999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="L47" t="n">
-        <v>85.67</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>80.43000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3371,16 +3371,16 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -3389,42 +3389,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.37</v>
+        <v>16.61</v>
       </c>
       <c r="C48" t="n">
-        <v>17.64</v>
+        <v>16.82</v>
       </c>
       <c r="D48" t="n">
-        <v>17.15</v>
+        <v>16.45</v>
       </c>
       <c r="E48" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="F48" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="J48" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="K48" t="n">
-        <v>81.5</v>
+        <v>87.3</v>
       </c>
       <c r="L48" t="n">
-        <v>83.2</v>
+        <v>89.45</v>
       </c>
       <c r="M48" t="n">
-        <v>79.69</v>
+        <v>86.06</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6471</v>
+        <v>6434</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -3451,42 +3451,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.37</v>
+        <v>16.92</v>
       </c>
       <c r="C49" t="n">
-        <v>17.71</v>
+        <v>17.22</v>
       </c>
       <c r="D49" t="n">
-        <v>17.16</v>
+        <v>16.72</v>
       </c>
       <c r="E49" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J49" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="K49" t="n">
-        <v>83.11</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>85.31</v>
+        <v>85.67</v>
       </c>
       <c r="M49" t="n">
-        <v>78.94</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6474</v>
+        <v>6465</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -533,42 +533,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.81</v>
+        <v>15.92</v>
       </c>
       <c r="C2" t="n">
-        <v>16.91</v>
+        <v>16.08</v>
       </c>
       <c r="D2" t="n">
-        <v>16.66</v>
+        <v>15.71</v>
       </c>
       <c r="E2" t="n">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="F2" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="J2" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="K2" t="n">
-        <v>90.84</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>91.98999999999999</v>
+        <v>89.39</v>
       </c>
       <c r="M2" t="n">
-        <v>89.92</v>
+        <v>86.37</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6414</v>
+        <v>6408</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -595,42 +595,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.79</v>
+        <v>16.22</v>
       </c>
       <c r="C3" t="n">
-        <v>16.87</v>
+        <v>16.35</v>
       </c>
       <c r="D3" t="n">
-        <v>16.65</v>
+        <v>16.12</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5</v>
+        <v>13.7</v>
       </c>
       <c r="F3" t="n">
-        <v>15.3</v>
+        <v>13.4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="J3" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="K3" t="n">
-        <v>92.09999999999999</v>
+        <v>85.42</v>
       </c>
       <c r="L3" t="n">
-        <v>93.45</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>90.81999999999999</v>
+        <v>83.22</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -639,13 +639,13 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6420</v>
+        <v>6405</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -657,42 +657,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.6</v>
+        <v>16.39</v>
       </c>
       <c r="C4" t="n">
-        <v>16.66</v>
+        <v>16.55</v>
       </c>
       <c r="D4" t="n">
-        <v>16.52</v>
+        <v>16.22</v>
       </c>
       <c r="E4" t="n">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="F4" t="n">
-        <v>15.6</v>
+        <v>13.8</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="K4" t="n">
-        <v>95.29000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>96.45999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="M4" t="n">
-        <v>93.84</v>
+        <v>84.14</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -719,42 +719,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.91</v>
+        <v>16.68</v>
       </c>
       <c r="C5" t="n">
-        <v>17.19</v>
+        <v>16.76</v>
       </c>
       <c r="D5" t="n">
-        <v>16.69</v>
+        <v>16.63</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="F5" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="K5" t="n">
-        <v>94.18000000000001</v>
+        <v>84.16</v>
       </c>
       <c r="L5" t="n">
-        <v>96.09</v>
+        <v>86.08</v>
       </c>
       <c r="M5" t="n">
-        <v>90.87</v>
+        <v>81.98</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -763,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6442</v>
+        <v>6411</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -781,57 +781,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.68</v>
+        <v>16.64</v>
       </c>
       <c r="C6" t="n">
-        <v>18.12</v>
+        <v>16.72</v>
       </c>
       <c r="D6" t="n">
-        <v>17.08</v>
+        <v>16.62</v>
       </c>
       <c r="E6" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="F6" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="J6" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="K6" t="n">
-        <v>86.59</v>
+        <v>89.45</v>
       </c>
       <c r="L6" t="n">
-        <v>93.40000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>80.54000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6451</v>
+        <v>6411</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -843,60 +843,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.95</v>
+        <v>16.73</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08</v>
+        <v>16.91</v>
       </c>
       <c r="D7" t="n">
-        <v>18.04</v>
+        <v>16.64</v>
       </c>
       <c r="E7" t="n">
-        <v>12.9</v>
+        <v>15.2</v>
       </c>
       <c r="F7" t="n">
-        <v>11.6</v>
+        <v>15.1</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.82</v>
+        <v>0.16</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="K7" t="n">
-        <v>64.73999999999999</v>
+        <v>91.16</v>
       </c>
       <c r="L7" t="n">
-        <v>79.75</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>55.98</v>
+        <v>89.92</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6474</v>
+        <v>6417</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -905,60 +905,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.54</v>
+        <v>16.79</v>
       </c>
       <c r="C8" t="n">
-        <v>21.83</v>
+        <v>16.87</v>
       </c>
       <c r="D8" t="n">
-        <v>21.18</v>
+        <v>16.65</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6</v>
+        <v>15.5</v>
       </c>
       <c r="F8" t="n">
-        <v>10.7</v>
+        <v>15.3</v>
       </c>
       <c r="G8" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1.19</v>
+        <v>0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="K8" t="n">
-        <v>53.45</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>58.22</v>
+        <v>93.45</v>
       </c>
       <c r="M8" t="n">
-        <v>49.34</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6485</v>
+        <v>6420</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -967,798 +967,798 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.02</v>
+        <v>16.6</v>
       </c>
       <c r="C9" t="n">
-        <v>22.16</v>
+        <v>16.66</v>
       </c>
       <c r="D9" t="n">
-        <v>21.88</v>
+        <v>16.52</v>
       </c>
       <c r="E9" t="n">
-        <v>11.1</v>
+        <v>15.8</v>
       </c>
       <c r="F9" t="n">
-        <v>10.4</v>
+        <v>15.6</v>
       </c>
       <c r="G9" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>1.31</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.24</v>
+        <v>0.06</v>
       </c>
       <c r="K9" t="n">
-        <v>50.18</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>52.66</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>47.74</v>
+        <v>93.84</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4352</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6511</v>
+        <v>6425</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.31</v>
+        <v>16.91</v>
       </c>
       <c r="C10" t="n">
-        <v>22.81</v>
+        <v>17.19</v>
       </c>
       <c r="D10" t="n">
-        <v>22.04</v>
+        <v>16.69</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
       <c r="F10" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="G10" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1.34</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>50.19</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>51.75</v>
+        <v>96.09</v>
       </c>
       <c r="M10" t="n">
-        <v>47.76</v>
+        <v>90.87</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5406</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6539</v>
+        <v>6442</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.68</v>
+        <v>17.68</v>
       </c>
       <c r="C11" t="n">
-        <v>23.1</v>
+        <v>18.12</v>
       </c>
       <c r="D11" t="n">
-        <v>22.11</v>
+        <v>17.08</v>
       </c>
       <c r="E11" t="n">
-        <v>11.3</v>
+        <v>15.3</v>
       </c>
       <c r="F11" t="n">
-        <v>10.7</v>
+        <v>14.6</v>
       </c>
       <c r="G11" t="n">
-        <v>384</v>
+        <v>7</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>0.27</v>
       </c>
       <c r="J11" t="n">
-        <v>1.32</v>
+        <v>0.12</v>
       </c>
       <c r="K11" t="n">
-        <v>48.82</v>
+        <v>86.59</v>
       </c>
       <c r="L11" t="n">
-        <v>51.28</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>47.13</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6743</v>
+        <v>685</v>
       </c>
       <c r="P11" t="n">
-        <v>6573</v>
+        <v>6451</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22.01</v>
+        <v>19.95</v>
       </c>
       <c r="C12" t="n">
-        <v>22.58</v>
+        <v>21.08</v>
       </c>
       <c r="D12" t="n">
-        <v>21.62</v>
+        <v>18.04</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="F12" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="G12" t="n">
-        <v>452</v>
+        <v>18</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>1.33</v>
+        <v>0.82</v>
       </c>
       <c r="J12" t="n">
-        <v>1.27</v>
+        <v>0.41</v>
       </c>
       <c r="K12" t="n">
-        <v>49.71</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>51.65</v>
+        <v>79.75</v>
       </c>
       <c r="M12" t="n">
-        <v>46.69</v>
+        <v>55.98</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6767</v>
+        <v>1926</v>
       </c>
       <c r="P12" t="n">
-        <v>6576</v>
+        <v>6474</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.59</v>
+        <v>21.54</v>
       </c>
       <c r="C13" t="n">
-        <v>22.58</v>
+        <v>21.83</v>
       </c>
       <c r="D13" t="n">
-        <v>20.76</v>
+        <v>21.18</v>
       </c>
       <c r="E13" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="F13" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G13" t="n">
-        <v>564</v>
+        <v>44</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="J13" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="K13" t="n">
-        <v>51.87</v>
+        <v>53.45</v>
       </c>
       <c r="L13" t="n">
-        <v>56.03</v>
+        <v>58.22</v>
       </c>
       <c r="M13" t="n">
-        <v>45.92</v>
+        <v>49.34</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6796</v>
+        <v>2410</v>
       </c>
       <c r="P13" t="n">
-        <v>6599</v>
+        <v>6485</v>
       </c>
       <c r="Q13" t="n">
         <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20.19</v>
+        <v>22.02</v>
       </c>
       <c r="C14" t="n">
-        <v>20.64</v>
+        <v>22.16</v>
       </c>
       <c r="D14" t="n">
-        <v>19.53</v>
+        <v>21.88</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="F14" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="G14" t="n">
-        <v>426</v>
+        <v>111</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="J14" t="n">
-        <v>0.95</v>
+        <v>1.24</v>
       </c>
       <c r="K14" t="n">
-        <v>55.29</v>
+        <v>50.18</v>
       </c>
       <c r="L14" t="n">
-        <v>57.87</v>
+        <v>52.66</v>
       </c>
       <c r="M14" t="n">
-        <v>52.99</v>
+        <v>47.74</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6767</v>
+        <v>4352</v>
       </c>
       <c r="P14" t="n">
-        <v>6576</v>
+        <v>6511</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
+        <v>7</v>
+      </c>
+      <c r="S14" t="n">
         <v>6</v>
       </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.89</v>
+        <v>22.31</v>
       </c>
       <c r="C15" t="n">
-        <v>19.62</v>
+        <v>22.81</v>
       </c>
       <c r="D15" t="n">
-        <v>18.08</v>
+        <v>22.04</v>
       </c>
       <c r="E15" t="n">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="F15" t="n">
         <v>10.9</v>
       </c>
       <c r="G15" t="n">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.66</v>
+        <v>1.34</v>
       </c>
       <c r="J15" t="n">
-        <v>0.35</v>
+        <v>1.28</v>
       </c>
       <c r="K15" t="n">
-        <v>69.7</v>
+        <v>50.19</v>
       </c>
       <c r="L15" t="n">
-        <v>82.87</v>
+        <v>51.75</v>
       </c>
       <c r="M15" t="n">
-        <v>57.89</v>
+        <v>47.76</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6691</v>
+        <v>5406</v>
       </c>
       <c r="P15" t="n">
-        <v>6514</v>
+        <v>6539</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.5</v>
+        <v>22.68</v>
       </c>
       <c r="C16" t="n">
-        <v>17.9</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="n">
-        <v>17.26</v>
+        <v>22.11</v>
       </c>
       <c r="E16" t="n">
-        <v>14.7</v>
+        <v>11.3</v>
       </c>
       <c r="F16" t="n">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="G16" t="n">
-        <v>43</v>
+        <v>384</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.31</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.25</v>
+        <v>1.32</v>
       </c>
       <c r="K16" t="n">
-        <v>84.14</v>
+        <v>48.82</v>
       </c>
       <c r="L16" t="n">
-        <v>87.05</v>
+        <v>51.28</v>
       </c>
       <c r="M16" t="n">
-        <v>79.48999999999999</v>
+        <v>47.13</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3786</v>
+        <v>6743</v>
       </c>
       <c r="P16" t="n">
-        <v>6422</v>
+        <v>6573</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.02</v>
+        <v>22.01</v>
       </c>
       <c r="C17" t="n">
-        <v>17.27</v>
+        <v>22.58</v>
       </c>
       <c r="D17" t="n">
-        <v>16.92</v>
+        <v>21.62</v>
       </c>
       <c r="E17" t="n">
-        <v>14.7</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.25</v>
+        <v>1.33</v>
       </c>
       <c r="J17" t="n">
-        <v>0.21</v>
+        <v>1.27</v>
       </c>
       <c r="K17" t="n">
-        <v>86.8</v>
+        <v>49.71</v>
       </c>
       <c r="L17" t="n">
-        <v>88.91</v>
+        <v>51.65</v>
       </c>
       <c r="M17" t="n">
-        <v>81.98999999999999</v>
+        <v>46.69</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1246</v>
+        <v>6767</v>
       </c>
       <c r="P17" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.89</v>
+        <v>21.59</v>
       </c>
       <c r="C18" t="n">
-        <v>17.03</v>
+        <v>22.58</v>
       </c>
       <c r="D18" t="n">
-        <v>16.78</v>
+        <v>20.76</v>
       </c>
       <c r="E18" t="n">
-        <v>14.9</v>
+        <v>11.2</v>
       </c>
       <c r="F18" t="n">
-        <v>14.6</v>
+        <v>10.3</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.21</v>
+        <v>1.24</v>
       </c>
       <c r="J18" t="n">
-        <v>0.18</v>
+        <v>1.07</v>
       </c>
       <c r="K18" t="n">
-        <v>88.48999999999999</v>
+        <v>51.87</v>
       </c>
       <c r="L18" t="n">
-        <v>90.31</v>
+        <v>56.03</v>
       </c>
       <c r="M18" t="n">
-        <v>85.76000000000001</v>
+        <v>45.92</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>6796</v>
       </c>
       <c r="P18" t="n">
-        <v>6417</v>
+        <v>6599</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.13</v>
+        <v>20.19</v>
       </c>
       <c r="C19" t="n">
-        <v>17.32</v>
+        <v>20.64</v>
       </c>
       <c r="D19" t="n">
-        <v>16.89</v>
+        <v>19.53</v>
       </c>
       <c r="E19" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F19" t="n">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.27</v>
+        <v>1.05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.22</v>
+        <v>0.95</v>
       </c>
       <c r="K19" t="n">
-        <v>85.90000000000001</v>
+        <v>55.29</v>
       </c>
       <c r="L19" t="n">
-        <v>88.63</v>
+        <v>57.87</v>
       </c>
       <c r="M19" t="n">
-        <v>83.40000000000001</v>
+        <v>52.99</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>6767</v>
       </c>
       <c r="P19" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.01</v>
+        <v>18.89</v>
       </c>
       <c r="C20" t="n">
-        <v>17.08</v>
+        <v>19.62</v>
       </c>
       <c r="D20" t="n">
-        <v>16.93</v>
+        <v>18.08</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>13.1</v>
       </c>
       <c r="F20" t="n">
-        <v>14.8</v>
+        <v>10.9</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.22</v>
+        <v>0.66</v>
       </c>
       <c r="J20" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="K20" t="n">
-        <v>88.16</v>
+        <v>69.7</v>
       </c>
       <c r="L20" t="n">
-        <v>88.7</v>
+        <v>82.87</v>
       </c>
       <c r="M20" t="n">
-        <v>87.34999999999999</v>
+        <v>57.89</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="P20" t="n">
-        <v>6414</v>
+        <v>6514</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.07</v>
+        <v>17.5</v>
       </c>
       <c r="C21" t="n">
-        <v>17.29</v>
+        <v>17.9</v>
       </c>
       <c r="D21" t="n">
-        <v>16.93</v>
+        <v>17.26</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F21" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="K21" t="n">
-        <v>88.06999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="L21" t="n">
-        <v>89.45999999999999</v>
+        <v>87.05</v>
       </c>
       <c r="M21" t="n">
-        <v>85.97</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="P21" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
         <v>2</v>
@@ -1773,60 +1773,60 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.44</v>
+        <v>17.02</v>
       </c>
       <c r="C22" t="n">
-        <v>17.52</v>
+        <v>17.27</v>
       </c>
       <c r="D22" t="n">
-        <v>17.31</v>
+        <v>16.92</v>
       </c>
       <c r="E22" t="n">
         <v>14.7</v>
       </c>
       <c r="F22" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="J22" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="K22" t="n">
-        <v>84.31999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="L22" t="n">
-        <v>85.27</v>
+        <v>88.91</v>
       </c>
       <c r="M22" t="n">
-        <v>82.56999999999999</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="P22" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -1835,42 +1835,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.22</v>
+        <v>16.89</v>
       </c>
       <c r="C23" t="n">
-        <v>17.34</v>
+        <v>17.03</v>
       </c>
       <c r="D23" t="n">
-        <v>17.11</v>
+        <v>16.78</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F23" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="J23" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="K23" t="n">
-        <v>87.37</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>88.34999999999999</v>
+        <v>90.31</v>
       </c>
       <c r="M23" t="n">
-        <v>86.23</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1879,13 +1879,13 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -1897,42 +1897,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.38</v>
+        <v>17.13</v>
       </c>
       <c r="C24" t="n">
-        <v>17.5</v>
+        <v>17.32</v>
       </c>
       <c r="D24" t="n">
-        <v>17.22</v>
+        <v>16.89</v>
       </c>
       <c r="E24" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F24" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="J24" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="K24" t="n">
-        <v>87.89</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>89.09</v>
+        <v>88.63</v>
       </c>
       <c r="M24" t="n">
-        <v>87.03</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1941,13 +1941,13 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6408</v>
+        <v>6414</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -1959,23 +1959,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.51</v>
+        <v>17.01</v>
       </c>
       <c r="C25" t="n">
-        <v>17.64</v>
+        <v>17.08</v>
       </c>
       <c r="D25" t="n">
-        <v>17.34</v>
+        <v>16.93</v>
       </c>
       <c r="E25" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1985,16 +1985,16 @@
         <v>0.22</v>
       </c>
       <c r="J25" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="K25" t="n">
-        <v>88.95</v>
+        <v>88.16</v>
       </c>
       <c r="L25" t="n">
-        <v>90.3</v>
+        <v>88.7</v>
       </c>
       <c r="M25" t="n">
-        <v>87.78</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6437</v>
+        <v>6414</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
@@ -2021,20 +2021,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.73</v>
+        <v>17.07</v>
       </c>
       <c r="C26" t="n">
-        <v>18.06</v>
+        <v>17.29</v>
       </c>
       <c r="D26" t="n">
-        <v>17.42</v>
+        <v>16.93</v>
       </c>
       <c r="E26" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
         <v>14.9</v>
@@ -2044,19 +2044,19 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="K26" t="n">
-        <v>85.27</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>88.19</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>81.95</v>
+        <v>85.97</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2065,10 +2065,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>6457</v>
+        <v>6417</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>2</v>
@@ -2083,42 +2083,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18.36</v>
+        <v>17.44</v>
       </c>
       <c r="C27" t="n">
-        <v>18.45</v>
+        <v>17.52</v>
       </c>
       <c r="D27" t="n">
-        <v>18.19</v>
+        <v>17.31</v>
       </c>
       <c r="E27" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F27" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="J27" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="K27" t="n">
-        <v>80.73</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>81.93000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="M27" t="n">
-        <v>79.83</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6471</v>
+        <v>6417</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
@@ -2145,42 +2145,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.81</v>
+        <v>17.22</v>
       </c>
       <c r="C28" t="n">
-        <v>19.07</v>
+        <v>17.34</v>
       </c>
       <c r="D28" t="n">
-        <v>18.51</v>
+        <v>17.11</v>
       </c>
       <c r="E28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="J28" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="K28" t="n">
-        <v>76.59999999999999</v>
+        <v>87.37</v>
       </c>
       <c r="L28" t="n">
-        <v>79.87</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>74.01000000000001</v>
+        <v>86.23</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2189,16 +2189,16 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6482</v>
+        <v>6425</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2207,42 +2207,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.81</v>
+        <v>17.38</v>
       </c>
       <c r="C29" t="n">
-        <v>20.67</v>
+        <v>17.5</v>
       </c>
       <c r="D29" t="n">
-        <v>18.96</v>
+        <v>17.22</v>
       </c>
       <c r="E29" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="F29" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.71</v>
+        <v>0.23</v>
       </c>
       <c r="J29" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="K29" t="n">
-        <v>69.16</v>
+        <v>87.89</v>
       </c>
       <c r="L29" t="n">
-        <v>75.04000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="M29" t="n">
-        <v>63.43</v>
+        <v>87.03</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>6496</v>
+        <v>6408</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2269,556 +2269,556 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.22</v>
+        <v>17.51</v>
       </c>
       <c r="C30" t="n">
-        <v>21.6</v>
+        <v>17.64</v>
       </c>
       <c r="D30" t="n">
-        <v>20.76</v>
+        <v>17.34</v>
       </c>
       <c r="E30" t="n">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="G30" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.99</v>
+        <v>0.22</v>
       </c>
       <c r="J30" t="n">
-        <v>0.93</v>
+        <v>0.19</v>
       </c>
       <c r="K30" t="n">
-        <v>60.52</v>
+        <v>88.95</v>
       </c>
       <c r="L30" t="n">
-        <v>62.17</v>
+        <v>90.3</v>
       </c>
       <c r="M30" t="n">
-        <v>58.42</v>
+        <v>87.78</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>6516</v>
+        <v>6437</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.62</v>
+        <v>17.73</v>
       </c>
       <c r="C31" t="n">
-        <v>21.84</v>
+        <v>18.06</v>
       </c>
       <c r="D31" t="n">
-        <v>21.44</v>
+        <v>17.42</v>
       </c>
       <c r="E31" t="n">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="F31" t="n">
-        <v>12.7</v>
+        <v>14.9</v>
       </c>
       <c r="G31" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>1.07</v>
+        <v>0.29</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>0.23</v>
       </c>
       <c r="K31" t="n">
-        <v>58.13</v>
+        <v>85.27</v>
       </c>
       <c r="L31" t="n">
-        <v>60.32</v>
+        <v>88.19</v>
       </c>
       <c r="M31" t="n">
-        <v>56.76</v>
+        <v>81.95</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6548</v>
+        <v>6457</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21.96</v>
+        <v>18.36</v>
       </c>
       <c r="C32" t="n">
-        <v>22.41</v>
+        <v>18.45</v>
       </c>
       <c r="D32" t="n">
-        <v>21.77</v>
+        <v>18.19</v>
       </c>
       <c r="E32" t="n">
-        <v>12.7</v>
+        <v>14.9</v>
       </c>
       <c r="F32" t="n">
-        <v>12.2</v>
+        <v>14.8</v>
       </c>
       <c r="G32" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>1.15</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
-        <v>1.11</v>
+        <v>0.37</v>
       </c>
       <c r="K32" t="n">
-        <v>55.95</v>
+        <v>80.73</v>
       </c>
       <c r="L32" t="n">
-        <v>57.92</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>54.15</v>
+        <v>79.83</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>6573</v>
+        <v>6471</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.46</v>
+        <v>18.81</v>
       </c>
       <c r="C33" t="n">
-        <v>23.17</v>
+        <v>19.07</v>
       </c>
       <c r="D33" t="n">
-        <v>21.82</v>
+        <v>18.51</v>
       </c>
       <c r="E33" t="n">
-        <v>12.2</v>
+        <v>14.5</v>
       </c>
       <c r="F33" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="G33" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
-        <v>1.21</v>
+        <v>0.42</v>
       </c>
       <c r="K33" t="n">
-        <v>52.56</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>54.35</v>
+        <v>79.87</v>
       </c>
       <c r="M33" t="n">
-        <v>50.6</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6763</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6593</v>
+        <v>6482</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.1</v>
+        <v>19.81</v>
       </c>
       <c r="C34" t="n">
-        <v>22.92</v>
+        <v>20.67</v>
       </c>
       <c r="D34" t="n">
-        <v>21.76</v>
+        <v>18.96</v>
       </c>
       <c r="E34" t="n">
-        <v>12.2</v>
+        <v>13.9</v>
       </c>
       <c r="F34" t="n">
-        <v>11.5</v>
+        <v>13.4</v>
       </c>
       <c r="G34" t="n">
-        <v>479</v>
+        <v>6</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>1.23</v>
+        <v>0.71</v>
       </c>
       <c r="J34" t="n">
-        <v>1.14</v>
+        <v>0.54</v>
       </c>
       <c r="K34" t="n">
-        <v>53.58</v>
+        <v>69.16</v>
       </c>
       <c r="L34" t="n">
-        <v>55.95</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>51.48</v>
+        <v>63.43</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6739</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6582</v>
+        <v>6496</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21.45</v>
+        <v>21.22</v>
       </c>
       <c r="C35" t="n">
-        <v>22.62</v>
+        <v>21.6</v>
       </c>
       <c r="D35" t="n">
-        <v>20.83</v>
+        <v>20.76</v>
       </c>
       <c r="E35" t="n">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="F35" t="n">
-        <v>11.1</v>
+        <v>13</v>
       </c>
       <c r="G35" t="n">
-        <v>640</v>
+        <v>73</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="J35" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K35" t="n">
-        <v>56.35</v>
+        <v>60.52</v>
       </c>
       <c r="L35" t="n">
-        <v>62.61</v>
+        <v>62.17</v>
       </c>
       <c r="M35" t="n">
-        <v>51.88</v>
+        <v>58.42</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6810</v>
+        <v>2990</v>
       </c>
       <c r="P35" t="n">
-        <v>6610</v>
+        <v>6516</v>
       </c>
       <c r="Q35" t="n">
         <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.67</v>
+        <v>21.62</v>
       </c>
       <c r="C36" t="n">
-        <v>20.85</v>
+        <v>21.84</v>
       </c>
       <c r="D36" t="n">
-        <v>19.11</v>
+        <v>21.44</v>
       </c>
       <c r="E36" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="G36" t="n">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7</v>
+        <v>1.02</v>
       </c>
       <c r="K36" t="n">
-        <v>66.39</v>
+        <v>58.13</v>
       </c>
       <c r="L36" t="n">
-        <v>68.68000000000001</v>
+        <v>60.32</v>
       </c>
       <c r="M36" t="n">
-        <v>61.4</v>
+        <v>56.76</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6772</v>
+        <v>5684</v>
       </c>
       <c r="P36" t="n">
-        <v>6571</v>
+        <v>6548</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
         <v>5</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.92</v>
+        <v>21.96</v>
       </c>
       <c r="C37" t="n">
-        <v>19.22</v>
+        <v>22.41</v>
       </c>
       <c r="D37" t="n">
-        <v>18.64</v>
+        <v>21.77</v>
       </c>
       <c r="E37" t="n">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="F37" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="G37" t="n">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.62</v>
+        <v>1.15</v>
       </c>
       <c r="J37" t="n">
-        <v>0.58</v>
+        <v>1.11</v>
       </c>
       <c r="K37" t="n">
-        <v>71.48999999999999</v>
+        <v>55.95</v>
       </c>
       <c r="L37" t="n">
-        <v>73.28</v>
+        <v>57.92</v>
       </c>
       <c r="M37" t="n">
-        <v>69.45</v>
+        <v>54.15</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6254</v>
+        <v>6619</v>
       </c>
       <c r="P37" t="n">
-        <v>6508</v>
+        <v>6573</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.78</v>
+        <v>22.46</v>
       </c>
       <c r="C38" t="n">
-        <v>18.89</v>
+        <v>23.17</v>
       </c>
       <c r="D38" t="n">
-        <v>18.67</v>
+        <v>21.82</v>
       </c>
       <c r="E38" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F38" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="G38" t="n">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.63</v>
+        <v>1.29</v>
       </c>
       <c r="J38" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="K38" t="n">
-        <v>70.87</v>
+        <v>52.56</v>
       </c>
       <c r="L38" t="n">
-        <v>73.17</v>
+        <v>54.35</v>
       </c>
       <c r="M38" t="n">
-        <v>68.48</v>
+        <v>50.6</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>5929</v>
+        <v>6763</v>
       </c>
       <c r="P38" t="n">
-        <v>6494</v>
+        <v>6593</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T38" t="n">
         <v>60</v>
@@ -2827,60 +2827,60 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18.59</v>
+        <v>22.1</v>
       </c>
       <c r="C39" t="n">
-        <v>19.26</v>
+        <v>22.92</v>
       </c>
       <c r="D39" t="n">
-        <v>18.18</v>
+        <v>21.76</v>
       </c>
       <c r="E39" t="n">
-        <v>14.3</v>
+        <v>12.2</v>
       </c>
       <c r="F39" t="n">
-        <v>13.8</v>
+        <v>11.5</v>
       </c>
       <c r="G39" t="n">
-        <v>205</v>
+        <v>479</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.23</v>
       </c>
       <c r="J39" t="n">
-        <v>0.41</v>
+        <v>1.14</v>
       </c>
       <c r="K39" t="n">
-        <v>76.48999999999999</v>
+        <v>53.58</v>
       </c>
       <c r="L39" t="n">
-        <v>80.08</v>
+        <v>55.95</v>
       </c>
       <c r="M39" t="n">
-        <v>71.70999999999999</v>
+        <v>51.48</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>5478</v>
+        <v>6739</v>
       </c>
       <c r="P39" t="n">
-        <v>6494</v>
+        <v>6582</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" t="n">
         <v>60</v>
@@ -2889,60 +2889,60 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.89</v>
+        <v>21.45</v>
       </c>
       <c r="C40" t="n">
-        <v>18.29</v>
+        <v>22.62</v>
       </c>
       <c r="D40" t="n">
-        <v>17.02</v>
+        <v>20.83</v>
       </c>
       <c r="E40" t="n">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="F40" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="G40" t="n">
-        <v>178</v>
+        <v>640</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.35</v>
+        <v>1.11</v>
       </c>
       <c r="J40" t="n">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
       <c r="K40" t="n">
-        <v>82.51000000000001</v>
+        <v>56.35</v>
       </c>
       <c r="L40" t="n">
-        <v>87.40000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="M40" t="n">
-        <v>79.09999999999999</v>
+        <v>51.88</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6633</v>
+        <v>6810</v>
       </c>
       <c r="P40" t="n">
-        <v>6488</v>
+        <v>6610</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T40" t="n">
         <v>60</v>
@@ -2951,365 +2951,361 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.49</v>
+        <v>19.67</v>
       </c>
       <c r="C41" t="n">
-        <v>16.79</v>
+        <v>20.85</v>
       </c>
       <c r="D41" t="n">
-        <v>16.31</v>
+        <v>19.11</v>
       </c>
       <c r="E41" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="F41" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="G41" t="n">
-        <v>28</v>
+        <v>279</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>0.77</v>
       </c>
       <c r="J41" t="n">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="K41" t="n">
-        <v>89.09</v>
+        <v>66.39</v>
       </c>
       <c r="L41" t="n">
-        <v>91.65000000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>87.73</v>
+        <v>61.4</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>5349</v>
+        <v>6772</v>
       </c>
       <c r="P41" t="n">
-        <v>6445</v>
+        <v>6571</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16.27</v>
+        <v>18.92</v>
       </c>
       <c r="C42" t="n">
-        <v>16.31</v>
+        <v>19.22</v>
       </c>
       <c r="D42" t="n">
-        <v>16.24</v>
+        <v>18.64</v>
       </c>
       <c r="E42" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="F42" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="J42" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="K42" t="n">
-        <v>90.12</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>91.63</v>
+        <v>73.28</v>
       </c>
       <c r="M42" t="n">
-        <v>88.84</v>
+        <v>69.45</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="P42" t="n">
-        <v>6422</v>
+        <v>6508</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.37</v>
+        <v>18.78</v>
       </c>
       <c r="C43" t="n">
-        <v>16.42</v>
+        <v>18.89</v>
       </c>
       <c r="D43" t="n">
-        <v>16.3</v>
+        <v>18.67</v>
       </c>
       <c r="E43" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="F43" t="n">
-        <v>14.4</v>
+        <v>12.8</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="J43" t="n">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="K43" t="n">
-        <v>88.97</v>
+        <v>70.87</v>
       </c>
       <c r="L43" t="n">
-        <v>90.09</v>
+        <v>73.17</v>
       </c>
       <c r="M43" t="n">
-        <v>88.26000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>5929</v>
       </c>
       <c r="P43" t="n">
-        <v>6414</v>
+        <v>6494</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.35</v>
+        <v>18.59</v>
       </c>
       <c r="C44" t="n">
-        <v>16.36</v>
+        <v>19.26</v>
       </c>
       <c r="D44" t="n">
-        <v>16.35</v>
+        <v>18.18</v>
       </c>
       <c r="E44" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="F44" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2592</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="K44" t="n">
-        <v>84.98</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>85.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="M44" t="n">
-        <v>84.31</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="P44" t="n">
-        <v>6425</v>
+        <v>6494</v>
       </c>
       <c r="Q44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3</v>
+      </c>
+      <c r="S44" t="n">
         <v>2</v>
       </c>
-      <c r="R44" t="n">
-        <v>2</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1</v>
-      </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 03:00:00</t>
+          <t>2026-10-16 08:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.33</v>
+        <v>17.89</v>
       </c>
       <c r="C45" t="n">
-        <v>16.56</v>
+        <v>18.29</v>
       </c>
       <c r="D45" t="n">
-        <v>15.86</v>
+        <v>17.02</v>
       </c>
       <c r="E45" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="F45" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2522</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="K45" t="n">
-        <v>89.8</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>99.73</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>85.27</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>6633</v>
       </c>
       <c r="P45" t="n">
-        <v>6422</v>
+        <v>6488</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
         <v>2</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 02:00:00</t>
+          <t>2026-10-16 07:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.27</v>
+        <v>16.49</v>
       </c>
       <c r="C46" t="n">
-        <v>16.37</v>
+        <v>16.79</v>
       </c>
       <c r="D46" t="n">
-        <v>16.2</v>
+        <v>16.31</v>
       </c>
       <c r="E46" t="n">
         <v>14.6</v>
       </c>
       <c r="F46" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0.15</v>
       </c>
       <c r="K46" t="n">
-        <v>90.44</v>
+        <v>89.09</v>
       </c>
       <c r="L46" t="n">
-        <v>91.61</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>89.09999999999999</v>
+        <v>87.73</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="P46" t="n">
-        <v>6417</v>
+        <v>6445</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
@@ -3327,42 +3323,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 01:00:00</t>
+          <t>2026-10-16 06:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="C47" t="n">
-        <v>16.49</v>
+        <v>16.31</v>
       </c>
       <c r="D47" t="n">
-        <v>16.14</v>
+        <v>16.24</v>
       </c>
       <c r="E47" t="n">
         <v>14.6</v>
       </c>
       <c r="F47" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="J47" t="n">
         <v>0.15</v>
       </c>
       <c r="K47" t="n">
-        <v>90.33</v>
+        <v>90.12</v>
       </c>
       <c r="L47" t="n">
-        <v>91.40000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="M47" t="n">
-        <v>89.20999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3371,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
@@ -3389,42 +3385,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-16 05:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16.61</v>
+        <v>16.37</v>
       </c>
       <c r="C48" t="n">
-        <v>16.82</v>
+        <v>16.42</v>
       </c>
       <c r="D48" t="n">
-        <v>16.45</v>
+        <v>16.3</v>
       </c>
       <c r="E48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F48" t="n">
         <v>14.4</v>
-      </c>
-      <c r="F48" t="n">
-        <v>14.3</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="K48" t="n">
-        <v>87.3</v>
+        <v>88.97</v>
       </c>
       <c r="L48" t="n">
-        <v>89.45</v>
+        <v>90.09</v>
       </c>
       <c r="M48" t="n">
-        <v>86.06</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3433,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6434</v>
+        <v>6414</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
@@ -3451,42 +3447,44 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-16 04:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16.92</v>
+        <v>16.35</v>
       </c>
       <c r="C49" t="n">
-        <v>17.22</v>
+        <v>16.36</v>
       </c>
       <c r="D49" t="n">
-        <v>16.72</v>
+        <v>16.35</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="F49" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>2592</v>
+      </c>
       <c r="I49" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="J49" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="K49" t="n">
-        <v>83.48999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="L49" t="n">
-        <v>85.67</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>80.43000000000001</v>
+        <v>84.31</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3495,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6465</v>
+        <v>6425</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
@@ -3504,7 +3502,7 @@
         <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,70 +461,65 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Radiación solar [W/m2] 1 - promedio</t>
+          <t>Radiación solar [W/m2] - promedio</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Radiación solar [W/m2] 2 - promedio</t>
+          <t>DPV [kPa] - promedio</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>DPV [kPa] - promedio</t>
+          <t>DPV [kPa] - mín</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>DPV [kPa] - mín</t>
+          <t>Humedad relativa HC [%] - promedio</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Humedad relativa HC [%] - promedio</t>
+          <t>Humedad relativa HC [%] - máx</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Humedad relativa HC [%] - máx</t>
+          <t>Humedad relativa HC [%] - mín</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Humedad relativa HC [%] - mín</t>
+          <t>Precipitación [mm] - sum</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Precipitación [mm] - sum</t>
+          <t>Panel solar [mV] - última</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Panel solar [mV] - última</t>
+          <t>Batería [mV] - última</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Batería [mV] - última</t>
+          <t>DeltaT [°C] - promedio</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>DeltaT [°C] - promedio</t>
+          <t>DeltaT [°C] - máx</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>DeltaT [°C] - máx</t>
+          <t>DeltaT [°C] - mín</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>DeltaT [°C] - mín</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Duración del sol [mín] - tiempo</t>
         </is>
@@ -533,113 +528,114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.92</v>
+        <v>14.36</v>
       </c>
       <c r="C2" t="n">
-        <v>16.08</v>
+        <v>14.4</v>
       </c>
       <c r="D2" t="n">
-        <v>15.71</v>
+        <v>14.32</v>
       </c>
       <c r="E2" t="n">
-        <v>13.8</v>
+        <v>10.7</v>
       </c>
       <c r="F2" t="n">
-        <v>13.7</v>
+        <v>10.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.33</v>
+      </c>
       <c r="I2" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="J2" t="n">
-        <v>0.19</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>87.56999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>89.39</v>
+        <v>77.13</v>
       </c>
       <c r="M2" t="n">
-        <v>86.37</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>6437</v>
       </c>
       <c r="P2" t="n">
-        <v>6408</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.22</v>
+        <v>14.56</v>
       </c>
       <c r="C3" t="n">
-        <v>16.35</v>
+        <v>14.75</v>
       </c>
       <c r="D3" t="n">
-        <v>16.12</v>
+        <v>14.34</v>
       </c>
       <c r="E3" t="n">
-        <v>13.7</v>
+        <v>10.8</v>
       </c>
       <c r="F3" t="n">
-        <v>13.4</v>
+        <v>10.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.36</v>
+      </c>
       <c r="I3" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="J3" t="n">
-        <v>0.23</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>85.42</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>87.15000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>83.22</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>6420</v>
       </c>
       <c r="P3" t="n">
-        <v>6405</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
@@ -648,246 +644,242 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.39</v>
+        <v>14.79</v>
       </c>
       <c r="C4" t="n">
-        <v>16.55</v>
+        <v>14.98</v>
       </c>
       <c r="D4" t="n">
-        <v>16.22</v>
+        <v>14.63</v>
       </c>
       <c r="E4" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
       <c r="F4" t="n">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.38</v>
+      </c>
       <c r="I4" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="J4" t="n">
-        <v>0.23</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>85.56999999999999</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>87.13</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>84.14</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>6411</v>
       </c>
       <c r="P4" t="n">
-        <v>6417</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.68</v>
+        <v>15.24</v>
       </c>
       <c r="C5" t="n">
-        <v>16.76</v>
+        <v>15.48</v>
       </c>
       <c r="D5" t="n">
-        <v>16.63</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9</v>
+        <v>10.7</v>
       </c>
       <c r="F5" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0.43</v>
+      </c>
       <c r="I5" t="n">
-        <v>0.29</v>
+        <v>0.42</v>
       </c>
       <c r="J5" t="n">
-        <v>0.26</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>84.16</v>
+        <v>75.5</v>
       </c>
       <c r="L5" t="n">
-        <v>86.08</v>
+        <v>73.42</v>
       </c>
       <c r="M5" t="n">
-        <v>81.98</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6411</v>
       </c>
       <c r="P5" t="n">
-        <v>6411</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.64</v>
+        <v>15.62</v>
       </c>
       <c r="C6" t="n">
-        <v>16.72</v>
+        <v>15.76</v>
       </c>
       <c r="D6" t="n">
-        <v>16.62</v>
+        <v>15.46</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="F6" t="n">
-        <v>14.3</v>
+        <v>10.8</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0.32</v>
+      </c>
       <c r="I6" t="n">
         <v>0.19</v>
       </c>
       <c r="J6" t="n">
-        <v>0.15</v>
+        <v>81.47</v>
       </c>
       <c r="K6" t="n">
-        <v>89.45</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>91.73999999999999</v>
+        <v>74.23</v>
       </c>
       <c r="M6" t="n">
-        <v>85.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6402</v>
       </c>
       <c r="P6" t="n">
-        <v>6411</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.73</v>
+        <v>15.86</v>
       </c>
       <c r="C7" t="n">
-        <v>16.91</v>
+        <v>16.08</v>
       </c>
       <c r="D7" t="n">
-        <v>16.64</v>
+        <v>15.66</v>
       </c>
       <c r="E7" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="F7" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.21</v>
+      </c>
       <c r="I7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>0.15</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>91.16</v>
+        <v>89.39</v>
       </c>
       <c r="L7" t="n">
-        <v>91.98999999999999</v>
+        <v>86.37</v>
       </c>
       <c r="M7" t="n">
-        <v>89.92</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6411</v>
       </c>
       <c r="P7" t="n">
-        <v>6417</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -896,1424 +888,1401 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.79</v>
+        <v>16.22</v>
       </c>
       <c r="C8" t="n">
-        <v>16.87</v>
+        <v>16.35</v>
       </c>
       <c r="D8" t="n">
-        <v>16.65</v>
+        <v>16.12</v>
       </c>
       <c r="E8" t="n">
-        <v>15.5</v>
+        <v>13.7</v>
       </c>
       <c r="F8" t="n">
-        <v>15.3</v>
+        <v>13.4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.26</v>
+      </c>
       <c r="I8" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="J8" t="n">
-        <v>0.12</v>
+        <v>85.42</v>
       </c>
       <c r="K8" t="n">
-        <v>92.09999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>93.45</v>
+        <v>83.22</v>
       </c>
       <c r="M8" t="n">
-        <v>90.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>6405</v>
       </c>
       <c r="P8" t="n">
-        <v>6420</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.6</v>
+        <v>16.39</v>
       </c>
       <c r="C9" t="n">
-        <v>16.66</v>
+        <v>16.55</v>
       </c>
       <c r="D9" t="n">
-        <v>16.52</v>
+        <v>16.22</v>
       </c>
       <c r="E9" t="n">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="F9" t="n">
-        <v>15.6</v>
+        <v>13.8</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.26</v>
+      </c>
       <c r="I9" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>95.29000000000001</v>
+        <v>87.13</v>
       </c>
       <c r="L9" t="n">
-        <v>96.45999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="M9" t="n">
-        <v>93.84</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>6417</v>
       </c>
       <c r="P9" t="n">
-        <v>6425</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.91</v>
+        <v>16.68</v>
       </c>
       <c r="C10" t="n">
-        <v>17.19</v>
+        <v>16.76</v>
       </c>
       <c r="D10" t="n">
-        <v>16.69</v>
+        <v>16.63</v>
       </c>
       <c r="E10" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="F10" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.29</v>
+      </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="J10" t="n">
-        <v>0.07000000000000001</v>
+        <v>84.16</v>
       </c>
       <c r="K10" t="n">
-        <v>94.18000000000001</v>
+        <v>86.08</v>
       </c>
       <c r="L10" t="n">
-        <v>96.09</v>
+        <v>81.98</v>
       </c>
       <c r="M10" t="n">
-        <v>90.87</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6411</v>
       </c>
       <c r="P10" t="n">
-        <v>6442</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.68</v>
+        <v>16.64</v>
       </c>
       <c r="C11" t="n">
-        <v>18.12</v>
+        <v>16.72</v>
       </c>
       <c r="D11" t="n">
-        <v>17.08</v>
+        <v>16.62</v>
       </c>
       <c r="E11" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="F11" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.19</v>
+      </c>
       <c r="I11" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="J11" t="n">
-        <v>0.12</v>
+        <v>89.45</v>
       </c>
       <c r="K11" t="n">
-        <v>86.59</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>93.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="M11" t="n">
-        <v>80.54000000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>685</v>
+        <v>6411</v>
       </c>
       <c r="P11" t="n">
-        <v>6451</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.95</v>
+        <v>16.73</v>
       </c>
       <c r="C12" t="n">
-        <v>21.08</v>
+        <v>16.91</v>
       </c>
       <c r="D12" t="n">
-        <v>18.04</v>
+        <v>16.64</v>
       </c>
       <c r="E12" t="n">
-        <v>12.9</v>
+        <v>15.2</v>
       </c>
       <c r="F12" t="n">
-        <v>11.6</v>
+        <v>15.1</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.16</v>
+      </c>
       <c r="I12" t="n">
-        <v>0.82</v>
+        <v>0.15</v>
       </c>
       <c r="J12" t="n">
-        <v>0.41</v>
+        <v>91.16</v>
       </c>
       <c r="K12" t="n">
-        <v>64.73999999999999</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>79.75</v>
+        <v>89.92</v>
       </c>
       <c r="M12" t="n">
-        <v>55.98</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1926</v>
+        <v>6417</v>
       </c>
       <c r="P12" t="n">
-        <v>6474</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.54</v>
+        <v>16.79</v>
       </c>
       <c r="C13" t="n">
-        <v>21.83</v>
+        <v>16.87</v>
       </c>
       <c r="D13" t="n">
-        <v>21.18</v>
+        <v>16.65</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6</v>
+        <v>15.5</v>
       </c>
       <c r="F13" t="n">
-        <v>10.7</v>
+        <v>15.3</v>
       </c>
       <c r="G13" t="n">
-        <v>44</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.14</v>
+      </c>
       <c r="I13" t="n">
-        <v>1.19</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>1.05</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>53.45</v>
+        <v>93.45</v>
       </c>
       <c r="L13" t="n">
-        <v>58.22</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>49.34</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2410</v>
+        <v>6420</v>
       </c>
       <c r="P13" t="n">
-        <v>6485</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22.02</v>
+        <v>16.6</v>
       </c>
       <c r="C14" t="n">
-        <v>22.16</v>
+        <v>16.66</v>
       </c>
       <c r="D14" t="n">
-        <v>21.88</v>
+        <v>16.52</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1</v>
+        <v>15.8</v>
       </c>
       <c r="F14" t="n">
-        <v>10.4</v>
+        <v>15.6</v>
       </c>
       <c r="G14" t="n">
-        <v>111</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.08</v>
+      </c>
       <c r="I14" t="n">
-        <v>1.31</v>
+        <v>0.06</v>
       </c>
       <c r="J14" t="n">
-        <v>1.24</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>50.18</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>52.66</v>
+        <v>93.84</v>
       </c>
       <c r="M14" t="n">
-        <v>47.74</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4352</v>
+        <v>6425</v>
       </c>
       <c r="P14" t="n">
-        <v>6511</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.31</v>
+        <v>16.91</v>
       </c>
       <c r="C15" t="n">
-        <v>22.81</v>
+        <v>17.19</v>
       </c>
       <c r="D15" t="n">
-        <v>22.04</v>
+        <v>16.69</v>
       </c>
       <c r="E15" t="n">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
       <c r="F15" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="G15" t="n">
-        <v>198</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1</v>
+      </c>
       <c r="I15" t="n">
-        <v>1.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.28</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>50.19</v>
+        <v>96.09</v>
       </c>
       <c r="L15" t="n">
-        <v>51.75</v>
+        <v>90.87</v>
       </c>
       <c r="M15" t="n">
-        <v>47.76</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5406</v>
+        <v>6442</v>
       </c>
       <c r="P15" t="n">
-        <v>6539</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.68</v>
+        <v>17.68</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>18.12</v>
       </c>
       <c r="D16" t="n">
-        <v>22.11</v>
+        <v>17.08</v>
       </c>
       <c r="E16" t="n">
-        <v>11.3</v>
+        <v>15.3</v>
       </c>
       <c r="F16" t="n">
-        <v>10.7</v>
+        <v>14.6</v>
       </c>
       <c r="G16" t="n">
-        <v>384</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.27</v>
+      </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>0.12</v>
       </c>
       <c r="J16" t="n">
-        <v>1.32</v>
+        <v>86.59</v>
       </c>
       <c r="K16" t="n">
-        <v>48.82</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>51.28</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>47.13</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="O16" t="n">
-        <v>6743</v>
+        <v>6451</v>
       </c>
       <c r="P16" t="n">
-        <v>6573</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.01</v>
+        <v>19.95</v>
       </c>
       <c r="C17" t="n">
-        <v>22.58</v>
+        <v>21.08</v>
       </c>
       <c r="D17" t="n">
-        <v>21.62</v>
+        <v>18.04</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="F17" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="G17" t="n">
-        <v>452</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.82</v>
+      </c>
       <c r="I17" t="n">
-        <v>1.33</v>
+        <v>0.41</v>
       </c>
       <c r="J17" t="n">
-        <v>1.27</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>49.71</v>
+        <v>79.75</v>
       </c>
       <c r="L17" t="n">
-        <v>51.65</v>
+        <v>55.98</v>
       </c>
       <c r="M17" t="n">
-        <v>46.69</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1926</v>
       </c>
       <c r="O17" t="n">
-        <v>6767</v>
+        <v>6474</v>
       </c>
       <c r="P17" t="n">
-        <v>6576</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.59</v>
+        <v>21.54</v>
       </c>
       <c r="C18" t="n">
-        <v>22.58</v>
+        <v>21.83</v>
       </c>
       <c r="D18" t="n">
-        <v>20.76</v>
+        <v>21.18</v>
       </c>
       <c r="E18" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="F18" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G18" t="n">
-        <v>564</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.19</v>
+      </c>
       <c r="I18" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="J18" t="n">
-        <v>1.07</v>
+        <v>53.45</v>
       </c>
       <c r="K18" t="n">
-        <v>51.87</v>
+        <v>58.22</v>
       </c>
       <c r="L18" t="n">
-        <v>56.03</v>
+        <v>49.34</v>
       </c>
       <c r="M18" t="n">
-        <v>45.92</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2410</v>
       </c>
       <c r="O18" t="n">
-        <v>6796</v>
+        <v>6485</v>
       </c>
       <c r="P18" t="n">
-        <v>6599</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
         <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.19</v>
+        <v>22.02</v>
       </c>
       <c r="C19" t="n">
-        <v>20.64</v>
+        <v>22.16</v>
       </c>
       <c r="D19" t="n">
-        <v>19.53</v>
+        <v>21.88</v>
       </c>
       <c r="E19" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="F19" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="G19" t="n">
-        <v>426</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>111</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.31</v>
+      </c>
       <c r="I19" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="J19" t="n">
-        <v>0.95</v>
+        <v>50.18</v>
       </c>
       <c r="K19" t="n">
-        <v>55.29</v>
+        <v>52.66</v>
       </c>
       <c r="L19" t="n">
-        <v>57.87</v>
+        <v>47.74</v>
       </c>
       <c r="M19" t="n">
-        <v>52.99</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4352</v>
       </c>
       <c r="O19" t="n">
-        <v>6767</v>
+        <v>6511</v>
       </c>
       <c r="P19" t="n">
-        <v>6576</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
         <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18.89</v>
+        <v>22.31</v>
       </c>
       <c r="C20" t="n">
-        <v>19.62</v>
+        <v>22.81</v>
       </c>
       <c r="D20" t="n">
-        <v>18.08</v>
+        <v>22.04</v>
       </c>
       <c r="E20" t="n">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="n">
         <v>10.9</v>
       </c>
       <c r="G20" t="n">
-        <v>212</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>198</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.34</v>
+      </c>
       <c r="I20" t="n">
-        <v>0.66</v>
+        <v>1.28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.35</v>
+        <v>50.19</v>
       </c>
       <c r="K20" t="n">
-        <v>69.7</v>
+        <v>51.75</v>
       </c>
       <c r="L20" t="n">
-        <v>82.87</v>
+        <v>47.76</v>
       </c>
       <c r="M20" t="n">
-        <v>57.89</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5406</v>
       </c>
       <c r="O20" t="n">
-        <v>6691</v>
+        <v>6539</v>
       </c>
       <c r="P20" t="n">
-        <v>6514</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.5</v>
+        <v>22.68</v>
       </c>
       <c r="C21" t="n">
-        <v>17.9</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="n">
-        <v>17.26</v>
+        <v>22.11</v>
       </c>
       <c r="E21" t="n">
-        <v>14.7</v>
+        <v>11.3</v>
       </c>
       <c r="F21" t="n">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="G21" t="n">
-        <v>43</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>384</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.4</v>
+      </c>
       <c r="I21" t="n">
-        <v>0.31</v>
+        <v>1.32</v>
       </c>
       <c r="J21" t="n">
-        <v>0.25</v>
+        <v>48.82</v>
       </c>
       <c r="K21" t="n">
-        <v>84.14</v>
+        <v>51.28</v>
       </c>
       <c r="L21" t="n">
-        <v>87.05</v>
+        <v>47.13</v>
       </c>
       <c r="M21" t="n">
-        <v>79.48999999999999</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6743</v>
       </c>
       <c r="O21" t="n">
-        <v>3786</v>
+        <v>6573</v>
       </c>
       <c r="P21" t="n">
-        <v>6422</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.02</v>
+        <v>22.01</v>
       </c>
       <c r="C22" t="n">
-        <v>17.27</v>
+        <v>22.58</v>
       </c>
       <c r="D22" t="n">
-        <v>16.92</v>
+        <v>21.62</v>
       </c>
       <c r="E22" t="n">
-        <v>14.7</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>452</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.33</v>
+      </c>
       <c r="I22" t="n">
-        <v>0.25</v>
+        <v>1.27</v>
       </c>
       <c r="J22" t="n">
-        <v>0.21</v>
+        <v>49.71</v>
       </c>
       <c r="K22" t="n">
-        <v>86.8</v>
+        <v>51.65</v>
       </c>
       <c r="L22" t="n">
-        <v>88.91</v>
+        <v>46.69</v>
       </c>
       <c r="M22" t="n">
-        <v>81.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6767</v>
       </c>
       <c r="O22" t="n">
-        <v>1246</v>
+        <v>6576</v>
       </c>
       <c r="P22" t="n">
-        <v>6414</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.89</v>
+        <v>21.59</v>
       </c>
       <c r="C23" t="n">
-        <v>17.03</v>
+        <v>22.58</v>
       </c>
       <c r="D23" t="n">
-        <v>16.78</v>
+        <v>20.76</v>
       </c>
       <c r="E23" t="n">
-        <v>14.9</v>
+        <v>11.2</v>
       </c>
       <c r="F23" t="n">
-        <v>14.6</v>
+        <v>10.3</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>564</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.24</v>
+      </c>
       <c r="I23" t="n">
-        <v>0.21</v>
+        <v>1.07</v>
       </c>
       <c r="J23" t="n">
-        <v>0.18</v>
+        <v>51.87</v>
       </c>
       <c r="K23" t="n">
-        <v>88.48999999999999</v>
+        <v>56.03</v>
       </c>
       <c r="L23" t="n">
-        <v>90.31</v>
+        <v>45.92</v>
       </c>
       <c r="M23" t="n">
-        <v>85.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>6796</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>6599</v>
       </c>
       <c r="P23" t="n">
-        <v>6417</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.13</v>
+        <v>20.19</v>
       </c>
       <c r="C24" t="n">
-        <v>17.32</v>
+        <v>20.64</v>
       </c>
       <c r="D24" t="n">
-        <v>16.89</v>
+        <v>19.53</v>
       </c>
       <c r="E24" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F24" t="n">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>426</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.05</v>
+      </c>
       <c r="I24" t="n">
-        <v>0.27</v>
+        <v>0.95</v>
       </c>
       <c r="J24" t="n">
-        <v>0.22</v>
+        <v>55.29</v>
       </c>
       <c r="K24" t="n">
-        <v>85.90000000000001</v>
+        <v>57.87</v>
       </c>
       <c r="L24" t="n">
-        <v>88.63</v>
+        <v>52.99</v>
       </c>
       <c r="M24" t="n">
-        <v>83.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6767</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="P24" t="n">
-        <v>6414</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.01</v>
+        <v>18.89</v>
       </c>
       <c r="C25" t="n">
-        <v>17.08</v>
+        <v>19.62</v>
       </c>
       <c r="D25" t="n">
-        <v>16.93</v>
+        <v>18.08</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>13.1</v>
       </c>
       <c r="F25" t="n">
-        <v>14.8</v>
+        <v>10.9</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>212</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.66</v>
+      </c>
       <c r="I25" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="J25" t="n">
-        <v>0.21</v>
+        <v>69.7</v>
       </c>
       <c r="K25" t="n">
-        <v>88.16</v>
+        <v>82.87</v>
       </c>
       <c r="L25" t="n">
-        <v>88.7</v>
+        <v>57.89</v>
       </c>
       <c r="M25" t="n">
-        <v>87.34999999999999</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>6514</v>
       </c>
       <c r="P25" t="n">
-        <v>6414</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.07</v>
+        <v>17.5</v>
       </c>
       <c r="C26" t="n">
-        <v>17.29</v>
+        <v>17.9</v>
       </c>
       <c r="D26" t="n">
-        <v>16.93</v>
+        <v>17.26</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F26" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.31</v>
+      </c>
       <c r="I26" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2</v>
+        <v>84.14</v>
       </c>
       <c r="K26" t="n">
-        <v>88.06999999999999</v>
+        <v>87.05</v>
       </c>
       <c r="L26" t="n">
-        <v>89.45999999999999</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>85.97</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>6422</v>
       </c>
       <c r="P26" t="n">
-        <v>6417</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.44</v>
+        <v>17.02</v>
       </c>
       <c r="C27" t="n">
-        <v>17.52</v>
+        <v>17.27</v>
       </c>
       <c r="D27" t="n">
-        <v>17.31</v>
+        <v>16.92</v>
       </c>
       <c r="E27" t="n">
         <v>14.7</v>
       </c>
       <c r="F27" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0.25</v>
+      </c>
       <c r="I27" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="J27" t="n">
-        <v>0.29</v>
+        <v>86.8</v>
       </c>
       <c r="K27" t="n">
-        <v>84.31999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="L27" t="n">
-        <v>85.27</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>82.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>6414</v>
       </c>
       <c r="P27" t="n">
-        <v>6417</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.22</v>
+        <v>16.89</v>
       </c>
       <c r="C28" t="n">
-        <v>17.34</v>
+        <v>17.03</v>
       </c>
       <c r="D28" t="n">
-        <v>17.11</v>
+        <v>16.78</v>
       </c>
       <c r="E28" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F28" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0.21</v>
+      </c>
       <c r="I28" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="J28" t="n">
-        <v>0.22</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>87.37</v>
+        <v>90.31</v>
       </c>
       <c r="L28" t="n">
-        <v>88.34999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>86.23</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>6417</v>
       </c>
       <c r="P28" t="n">
-        <v>6425</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.38</v>
+        <v>17.13</v>
       </c>
       <c r="C29" t="n">
-        <v>17.5</v>
+        <v>17.32</v>
       </c>
       <c r="D29" t="n">
-        <v>17.22</v>
+        <v>16.89</v>
       </c>
       <c r="E29" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F29" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0.27</v>
+      </c>
       <c r="I29" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J29" t="n">
-        <v>0.21</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>87.89</v>
+        <v>88.63</v>
       </c>
       <c r="L29" t="n">
-        <v>89.09</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>87.03</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>6414</v>
       </c>
       <c r="P29" t="n">
-        <v>6408</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.51</v>
+        <v>17.01</v>
       </c>
       <c r="C30" t="n">
-        <v>17.64</v>
+        <v>17.08</v>
       </c>
       <c r="D30" t="n">
-        <v>17.34</v>
+        <v>16.93</v>
       </c>
       <c r="E30" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0.22</v>
+      </c>
       <c r="I30" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J30" t="n">
-        <v>0.19</v>
+        <v>88.16</v>
       </c>
       <c r="K30" t="n">
-        <v>88.95</v>
+        <v>88.7</v>
       </c>
       <c r="L30" t="n">
-        <v>90.3</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>87.78</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>6414</v>
       </c>
       <c r="P30" t="n">
-        <v>6437</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -2322,29 +2291,26 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.73</v>
+        <v>17.07</v>
       </c>
       <c r="C31" t="n">
-        <v>18.06</v>
+        <v>17.29</v>
       </c>
       <c r="D31" t="n">
-        <v>17.42</v>
+        <v>16.93</v>
       </c>
       <c r="E31" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>14.9</v>
@@ -2352,92 +2318,93 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0.22</v>
+      </c>
       <c r="I31" t="n">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
-        <v>0.23</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>85.27</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>88.19</v>
+        <v>85.97</v>
       </c>
       <c r="M31" t="n">
-        <v>81.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>6417</v>
       </c>
       <c r="P31" t="n">
-        <v>6457</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18.36</v>
+        <v>17.44</v>
       </c>
       <c r="C32" t="n">
-        <v>18.45</v>
+        <v>17.52</v>
       </c>
       <c r="D32" t="n">
-        <v>18.19</v>
+        <v>17.31</v>
       </c>
       <c r="E32" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F32" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0.31</v>
+      </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="J32" t="n">
-        <v>0.37</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>80.73</v>
+        <v>85.27</v>
       </c>
       <c r="L32" t="n">
-        <v>81.93000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>79.83</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>6417</v>
       </c>
       <c r="P32" t="n">
-        <v>6471</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -2446,1066 +2413,1044 @@
         <v>2</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18.81</v>
+        <v>17.22</v>
       </c>
       <c r="C33" t="n">
-        <v>19.07</v>
+        <v>17.34</v>
       </c>
       <c r="D33" t="n">
-        <v>18.51</v>
+        <v>17.11</v>
       </c>
       <c r="E33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>0.24</v>
+      </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="J33" t="n">
-        <v>0.42</v>
+        <v>87.37</v>
       </c>
       <c r="K33" t="n">
-        <v>76.59999999999999</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>79.87</v>
+        <v>86.23</v>
       </c>
       <c r="M33" t="n">
-        <v>74.01000000000001</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6425</v>
       </c>
       <c r="P33" t="n">
-        <v>6482</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.81</v>
+        <v>17.38</v>
       </c>
       <c r="C34" t="n">
-        <v>20.67</v>
+        <v>17.5</v>
       </c>
       <c r="D34" t="n">
-        <v>18.96</v>
+        <v>17.22</v>
       </c>
       <c r="E34" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="F34" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.23</v>
+      </c>
       <c r="I34" t="n">
-        <v>0.71</v>
+        <v>0.21</v>
       </c>
       <c r="J34" t="n">
-        <v>0.54</v>
+        <v>87.89</v>
       </c>
       <c r="K34" t="n">
-        <v>69.16</v>
+        <v>89.09</v>
       </c>
       <c r="L34" t="n">
-        <v>75.04000000000001</v>
+        <v>87.03</v>
       </c>
       <c r="M34" t="n">
-        <v>63.43</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>6408</v>
       </c>
       <c r="P34" t="n">
-        <v>6496</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21.22</v>
+        <v>17.51</v>
       </c>
       <c r="C35" t="n">
-        <v>21.6</v>
+        <v>17.64</v>
       </c>
       <c r="D35" t="n">
-        <v>20.76</v>
+        <v>17.34</v>
       </c>
       <c r="E35" t="n">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="G35" t="n">
-        <v>73</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.22</v>
+      </c>
       <c r="I35" t="n">
-        <v>0.99</v>
+        <v>0.19</v>
       </c>
       <c r="J35" t="n">
-        <v>0.93</v>
+        <v>88.95</v>
       </c>
       <c r="K35" t="n">
-        <v>60.52</v>
+        <v>90.3</v>
       </c>
       <c r="L35" t="n">
-        <v>62.17</v>
+        <v>87.78</v>
       </c>
       <c r="M35" t="n">
-        <v>58.42</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2990</v>
+        <v>6437</v>
       </c>
       <c r="P35" t="n">
-        <v>6516</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.62</v>
+        <v>17.73</v>
       </c>
       <c r="C36" t="n">
-        <v>21.84</v>
+        <v>18.06</v>
       </c>
       <c r="D36" t="n">
-        <v>21.44</v>
+        <v>17.42</v>
       </c>
       <c r="E36" t="n">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="F36" t="n">
-        <v>12.7</v>
+        <v>14.9</v>
       </c>
       <c r="G36" t="n">
-        <v>137</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.29</v>
+      </c>
       <c r="I36" t="n">
-        <v>1.07</v>
+        <v>0.23</v>
       </c>
       <c r="J36" t="n">
-        <v>1.02</v>
+        <v>85.27</v>
       </c>
       <c r="K36" t="n">
-        <v>58.13</v>
+        <v>88.19</v>
       </c>
       <c r="L36" t="n">
-        <v>60.32</v>
+        <v>81.95</v>
       </c>
       <c r="M36" t="n">
-        <v>56.76</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>5684</v>
+        <v>6457</v>
       </c>
       <c r="P36" t="n">
-        <v>6548</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>21.96</v>
+        <v>18.36</v>
       </c>
       <c r="C37" t="n">
-        <v>22.41</v>
+        <v>18.45</v>
       </c>
       <c r="D37" t="n">
-        <v>21.77</v>
+        <v>18.19</v>
       </c>
       <c r="E37" t="n">
-        <v>12.7</v>
+        <v>14.9</v>
       </c>
       <c r="F37" t="n">
-        <v>12.2</v>
+        <v>14.8</v>
       </c>
       <c r="G37" t="n">
-        <v>205</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4</v>
+      </c>
       <c r="I37" t="n">
-        <v>1.15</v>
+        <v>0.37</v>
       </c>
       <c r="J37" t="n">
-        <v>1.11</v>
+        <v>80.73</v>
       </c>
       <c r="K37" t="n">
-        <v>55.95</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>57.92</v>
+        <v>79.83</v>
       </c>
       <c r="M37" t="n">
-        <v>54.15</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6619</v>
+        <v>6471</v>
       </c>
       <c r="P37" t="n">
-        <v>6573</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>22.46</v>
+        <v>18.81</v>
       </c>
       <c r="C38" t="n">
-        <v>23.17</v>
+        <v>19.07</v>
       </c>
       <c r="D38" t="n">
-        <v>21.82</v>
+        <v>18.51</v>
       </c>
       <c r="E38" t="n">
-        <v>12.2</v>
+        <v>14.5</v>
       </c>
       <c r="F38" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="G38" t="n">
-        <v>383</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I38" t="n">
-        <v>1.29</v>
+        <v>0.42</v>
       </c>
       <c r="J38" t="n">
-        <v>1.21</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>52.56</v>
+        <v>79.87</v>
       </c>
       <c r="L38" t="n">
-        <v>54.35</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>50.6</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6763</v>
+        <v>6482</v>
       </c>
       <c r="P38" t="n">
-        <v>6593</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
-      </c>
-      <c r="T38" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22.1</v>
+        <v>19.81</v>
       </c>
       <c r="C39" t="n">
-        <v>22.92</v>
+        <v>20.67</v>
       </c>
       <c r="D39" t="n">
-        <v>21.76</v>
+        <v>18.96</v>
       </c>
       <c r="E39" t="n">
-        <v>12.2</v>
+        <v>13.9</v>
       </c>
       <c r="F39" t="n">
-        <v>11.5</v>
+        <v>13.4</v>
       </c>
       <c r="G39" t="n">
-        <v>479</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.71</v>
+      </c>
       <c r="I39" t="n">
-        <v>1.23</v>
+        <v>0.54</v>
       </c>
       <c r="J39" t="n">
-        <v>1.14</v>
+        <v>69.16</v>
       </c>
       <c r="K39" t="n">
-        <v>53.58</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>55.95</v>
+        <v>63.43</v>
       </c>
       <c r="M39" t="n">
-        <v>51.48</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6739</v>
+        <v>6496</v>
       </c>
       <c r="P39" t="n">
-        <v>6582</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>21.45</v>
+        <v>21.22</v>
       </c>
       <c r="C40" t="n">
-        <v>22.62</v>
+        <v>21.6</v>
       </c>
       <c r="D40" t="n">
-        <v>20.83</v>
+        <v>20.76</v>
       </c>
       <c r="E40" t="n">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="F40" t="n">
-        <v>11.1</v>
+        <v>13</v>
       </c>
       <c r="G40" t="n">
-        <v>640</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.99</v>
+      </c>
       <c r="I40" t="n">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="J40" t="n">
-        <v>0.92</v>
+        <v>60.52</v>
       </c>
       <c r="K40" t="n">
-        <v>56.35</v>
+        <v>62.17</v>
       </c>
       <c r="L40" t="n">
-        <v>62.61</v>
+        <v>58.42</v>
       </c>
       <c r="M40" t="n">
-        <v>51.88</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2990</v>
       </c>
       <c r="O40" t="n">
-        <v>6810</v>
+        <v>6516</v>
       </c>
       <c r="P40" t="n">
-        <v>6610</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="n">
         <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
       </c>
-      <c r="T40" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.67</v>
+        <v>21.62</v>
       </c>
       <c r="C41" t="n">
-        <v>20.85</v>
+        <v>21.84</v>
       </c>
       <c r="D41" t="n">
-        <v>19.11</v>
+        <v>21.44</v>
       </c>
       <c r="E41" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="G41" t="n">
-        <v>279</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.07</v>
+      </c>
       <c r="I41" t="n">
-        <v>0.77</v>
+        <v>1.02</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7</v>
+        <v>58.13</v>
       </c>
       <c r="K41" t="n">
-        <v>66.39</v>
+        <v>60.32</v>
       </c>
       <c r="L41" t="n">
-        <v>68.68000000000001</v>
+        <v>56.76</v>
       </c>
       <c r="M41" t="n">
-        <v>61.4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5684</v>
       </c>
       <c r="O41" t="n">
-        <v>6772</v>
+        <v>6548</v>
       </c>
       <c r="P41" t="n">
-        <v>6571</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
         <v>5</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18.92</v>
+        <v>21.96</v>
       </c>
       <c r="C42" t="n">
-        <v>19.22</v>
+        <v>22.41</v>
       </c>
       <c r="D42" t="n">
-        <v>18.64</v>
+        <v>21.77</v>
       </c>
       <c r="E42" t="n">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="F42" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="G42" t="n">
-        <v>143</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.15</v>
+      </c>
       <c r="I42" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="J42" t="n">
-        <v>0.58</v>
+        <v>55.95</v>
       </c>
       <c r="K42" t="n">
-        <v>71.48999999999999</v>
+        <v>57.92</v>
       </c>
       <c r="L42" t="n">
-        <v>73.28</v>
+        <v>54.15</v>
       </c>
       <c r="M42" t="n">
-        <v>69.45</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6619</v>
       </c>
       <c r="O42" t="n">
-        <v>6254</v>
+        <v>6573</v>
       </c>
       <c r="P42" t="n">
-        <v>6508</v>
+        <v>6</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.78</v>
+        <v>22.46</v>
       </c>
       <c r="C43" t="n">
-        <v>18.89</v>
+        <v>23.17</v>
       </c>
       <c r="D43" t="n">
-        <v>18.67</v>
+        <v>21.82</v>
       </c>
       <c r="E43" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="F43" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="G43" t="n">
-        <v>134</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>383</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.29</v>
+      </c>
       <c r="I43" t="n">
-        <v>0.63</v>
+        <v>1.21</v>
       </c>
       <c r="J43" t="n">
-        <v>0.57</v>
+        <v>52.56</v>
       </c>
       <c r="K43" t="n">
-        <v>70.87</v>
+        <v>54.35</v>
       </c>
       <c r="L43" t="n">
-        <v>73.17</v>
+        <v>50.6</v>
       </c>
       <c r="M43" t="n">
-        <v>68.48</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>6763</v>
       </c>
       <c r="O43" t="n">
-        <v>5929</v>
+        <v>6593</v>
       </c>
       <c r="P43" t="n">
-        <v>6494</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
-      </c>
-      <c r="T43" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.59</v>
+        <v>22.1</v>
       </c>
       <c r="C44" t="n">
-        <v>19.26</v>
+        <v>22.92</v>
       </c>
       <c r="D44" t="n">
-        <v>18.18</v>
+        <v>21.76</v>
       </c>
       <c r="E44" t="n">
-        <v>14.3</v>
+        <v>12.2</v>
       </c>
       <c r="F44" t="n">
-        <v>13.8</v>
+        <v>11.5</v>
       </c>
       <c r="G44" t="n">
-        <v>205</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>479</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.23</v>
+      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="J44" t="n">
-        <v>0.41</v>
+        <v>53.58</v>
       </c>
       <c r="K44" t="n">
-        <v>76.48999999999999</v>
+        <v>55.95</v>
       </c>
       <c r="L44" t="n">
-        <v>80.08</v>
+        <v>51.48</v>
       </c>
       <c r="M44" t="n">
-        <v>71.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>6739</v>
       </c>
       <c r="O44" t="n">
-        <v>5478</v>
+        <v>6582</v>
       </c>
       <c r="P44" t="n">
-        <v>6494</v>
+        <v>6</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
-      </c>
-      <c r="T44" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.89</v>
+        <v>21.45</v>
       </c>
       <c r="C45" t="n">
-        <v>18.29</v>
+        <v>22.62</v>
       </c>
       <c r="D45" t="n">
-        <v>17.02</v>
+        <v>20.83</v>
       </c>
       <c r="E45" t="n">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="F45" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="G45" t="n">
-        <v>178</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>640</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.11</v>
+      </c>
       <c r="I45" t="n">
-        <v>0.35</v>
+        <v>0.92</v>
       </c>
       <c r="J45" t="n">
-        <v>0.24</v>
+        <v>56.35</v>
       </c>
       <c r="K45" t="n">
-        <v>82.51000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="L45" t="n">
-        <v>87.40000000000001</v>
+        <v>51.88</v>
       </c>
       <c r="M45" t="n">
-        <v>79.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>6810</v>
       </c>
       <c r="O45" t="n">
-        <v>6633</v>
+        <v>6610</v>
       </c>
       <c r="P45" t="n">
-        <v>6488</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 07:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.49</v>
+        <v>19.67</v>
       </c>
       <c r="C46" t="n">
-        <v>16.79</v>
+        <v>20.85</v>
       </c>
       <c r="D46" t="n">
-        <v>16.31</v>
+        <v>19.11</v>
       </c>
       <c r="E46" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="F46" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="G46" t="n">
-        <v>28</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>279</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.77</v>
+      </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
-        <v>0.15</v>
+        <v>66.39</v>
       </c>
       <c r="K46" t="n">
-        <v>89.09</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>91.65000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="M46" t="n">
-        <v>87.73</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6772</v>
       </c>
       <c r="O46" t="n">
-        <v>5349</v>
+        <v>6571</v>
       </c>
       <c r="P46" t="n">
-        <v>6445</v>
+        <v>4</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 06:00:00</t>
+          <t>2026-10-16 11:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.27</v>
+        <v>18.92</v>
       </c>
       <c r="C47" t="n">
-        <v>16.31</v>
+        <v>19.22</v>
       </c>
       <c r="D47" t="n">
-        <v>16.24</v>
+        <v>18.64</v>
       </c>
       <c r="E47" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="F47" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>143</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.62</v>
+      </c>
       <c r="I47" t="n">
-        <v>0.18</v>
+        <v>0.58</v>
       </c>
       <c r="J47" t="n">
-        <v>0.15</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>90.12</v>
+        <v>73.28</v>
       </c>
       <c r="L47" t="n">
-        <v>91.63</v>
+        <v>69.45</v>
       </c>
       <c r="M47" t="n">
-        <v>88.84</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>6508</v>
       </c>
       <c r="P47" t="n">
-        <v>6422</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 05:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16.37</v>
+        <v>18.78</v>
       </c>
       <c r="C48" t="n">
-        <v>16.42</v>
+        <v>18.89</v>
       </c>
       <c r="D48" t="n">
-        <v>16.3</v>
+        <v>18.67</v>
       </c>
       <c r="E48" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="F48" t="n">
-        <v>14.4</v>
+        <v>12.8</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.63</v>
+      </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>0.57</v>
       </c>
       <c r="J48" t="n">
-        <v>0.18</v>
+        <v>70.87</v>
       </c>
       <c r="K48" t="n">
-        <v>88.97</v>
+        <v>73.17</v>
       </c>
       <c r="L48" t="n">
-        <v>90.09</v>
+        <v>68.48</v>
       </c>
       <c r="M48" t="n">
-        <v>88.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>5929</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>6494</v>
       </c>
       <c r="P48" t="n">
-        <v>6414</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 04:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16.35</v>
+        <v>18.59</v>
       </c>
       <c r="C49" t="n">
-        <v>16.36</v>
+        <v>19.26</v>
       </c>
       <c r="D49" t="n">
-        <v>16.35</v>
+        <v>18.18</v>
       </c>
       <c r="E49" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="F49" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H49" t="n">
-        <v>2592</v>
+        <v>0.5</v>
       </c>
       <c r="I49" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="J49" t="n">
-        <v>0.26</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>84.98</v>
+        <v>80.08</v>
       </c>
       <c r="L49" t="n">
-        <v>85.65000000000001</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>84.31</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5478</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>6494</v>
       </c>
       <c r="P49" t="n">
-        <v>6425</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
         <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,111 +528,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.36</v>
+        <v>15.36</v>
       </c>
       <c r="C2" t="n">
-        <v>14.4</v>
+        <v>15.86</v>
       </c>
       <c r="D2" t="n">
-        <v>14.32</v>
+        <v>15.05</v>
       </c>
       <c r="E2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F2" t="n">
         <v>10.7</v>
       </c>
-      <c r="F2" t="n">
-        <v>10.3</v>
-      </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="H2" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="I2" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="J2" t="n">
-        <v>79.29000000000001</v>
+        <v>76.31</v>
       </c>
       <c r="K2" t="n">
-        <v>80.34999999999999</v>
+        <v>78.77</v>
       </c>
       <c r="L2" t="n">
-        <v>77.13</v>
+        <v>71.61</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3728</v>
+        <v>6686</v>
       </c>
       <c r="O2" t="n">
-        <v>6437</v>
+        <v>6534</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.56</v>
+        <v>15.04</v>
       </c>
       <c r="C3" t="n">
-        <v>14.75</v>
+        <v>15.26</v>
       </c>
       <c r="D3" t="n">
-        <v>14.34</v>
+        <v>14.82</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F3" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I3" t="n">
         <v>0.33</v>
       </c>
       <c r="J3" t="n">
-        <v>78.20999999999999</v>
+        <v>77.86</v>
       </c>
       <c r="K3" t="n">
-        <v>80.09999999999999</v>
+        <v>80.23</v>
       </c>
       <c r="L3" t="n">
-        <v>75.43000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2449</v>
+        <v>5708</v>
       </c>
       <c r="O3" t="n">
-        <v>6420</v>
+        <v>6494</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -644,126 +644,126 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="C4" t="n">
         <v>14.79</v>
       </c>
-      <c r="C4" t="n">
-        <v>14.98</v>
-      </c>
       <c r="D4" t="n">
-        <v>14.63</v>
+        <v>14.22</v>
       </c>
       <c r="E4" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F4" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I4" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="J4" t="n">
-        <v>77.20999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="K4" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="L4" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="L4" t="n">
-        <v>74.54000000000001</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O4" t="n">
-        <v>6411</v>
+        <v>6491</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.24</v>
+        <v>14.34</v>
       </c>
       <c r="C5" t="n">
-        <v>15.48</v>
+        <v>14.4</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="E5" t="n">
         <v>10.7</v>
       </c>
       <c r="F5" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="J5" t="n">
-        <v>74.68000000000001</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>75.5</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>73.42</v>
+        <v>77.13</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O5" t="n">
-        <v>6411</v>
+        <v>6425</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -772,59 +772,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.62</v>
+        <v>14.56</v>
       </c>
       <c r="C6" t="n">
-        <v>15.76</v>
+        <v>14.75</v>
       </c>
       <c r="D6" t="n">
-        <v>15.46</v>
+        <v>14.34</v>
       </c>
       <c r="E6" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="F6" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I6" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J6" t="n">
-        <v>81.47</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>89.01000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>74.23</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O6" t="n">
-        <v>6402</v>
+        <v>6420</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -833,41 +833,41 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.86</v>
+        <v>14.79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.08</v>
+        <v>14.98</v>
       </c>
       <c r="D7" t="n">
-        <v>15.66</v>
+        <v>14.63</v>
       </c>
       <c r="E7" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="n">
-        <v>13.7</v>
+        <v>10.4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="I7" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>87.95999999999999</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>89.39</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>86.37</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -879,13 +879,13 @@
         <v>6411</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -894,41 +894,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.22</v>
+        <v>15.24</v>
       </c>
       <c r="C8" t="n">
-        <v>16.35</v>
+        <v>15.48</v>
       </c>
       <c r="D8" t="n">
-        <v>16.12</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="F8" t="n">
-        <v>13.4</v>
+        <v>10.4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="I8" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="J8" t="n">
-        <v>85.42</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>87.15000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="L8" t="n">
-        <v>83.22</v>
+        <v>73.42</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6405</v>
+        <v>6411</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -955,41 +955,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.39</v>
+        <v>15.62</v>
       </c>
       <c r="C9" t="n">
-        <v>16.55</v>
+        <v>15.76</v>
       </c>
       <c r="D9" t="n">
-        <v>16.22</v>
+        <v>15.46</v>
       </c>
       <c r="E9" t="n">
-        <v>13.9</v>
+        <v>12.3</v>
       </c>
       <c r="F9" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J9" t="n">
-        <v>85.56999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="K9" t="n">
-        <v>87.13</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>84.14</v>
+        <v>74.23</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6417</v>
+        <v>6402</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1016,41 +1016,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.68</v>
+        <v>15.86</v>
       </c>
       <c r="C10" t="n">
-        <v>16.76</v>
+        <v>16.08</v>
       </c>
       <c r="D10" t="n">
-        <v>16.63</v>
+        <v>15.66</v>
       </c>
       <c r="E10" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="I10" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="J10" t="n">
-        <v>84.16</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>86.08</v>
+        <v>89.39</v>
       </c>
       <c r="L10" t="n">
-        <v>81.98</v>
+        <v>86.37</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1062,10 +1062,10 @@
         <v>6411</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1077,41 +1077,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.64</v>
+        <v>16.22</v>
       </c>
       <c r="C11" t="n">
-        <v>16.72</v>
+        <v>16.35</v>
       </c>
       <c r="D11" t="n">
-        <v>16.62</v>
+        <v>16.12</v>
       </c>
       <c r="E11" t="n">
-        <v>14.8</v>
+        <v>13.7</v>
       </c>
       <c r="F11" t="n">
-        <v>14.3</v>
+        <v>13.4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="I11" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J11" t="n">
-        <v>89.45</v>
+        <v>85.42</v>
       </c>
       <c r="K11" t="n">
-        <v>91.73999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>85.8</v>
+        <v>83.22</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1138,41 +1138,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.73</v>
+        <v>16.39</v>
       </c>
       <c r="C12" t="n">
-        <v>16.91</v>
+        <v>16.55</v>
       </c>
       <c r="D12" t="n">
-        <v>16.64</v>
+        <v>16.22</v>
       </c>
       <c r="E12" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="F12" t="n">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J12" t="n">
-        <v>91.16</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>91.98999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="L12" t="n">
-        <v>89.92</v>
+        <v>84.14</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1199,41 +1199,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.79</v>
+        <v>16.68</v>
       </c>
       <c r="C13" t="n">
-        <v>16.87</v>
+        <v>16.76</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65</v>
+        <v>16.63</v>
       </c>
       <c r="E13" t="n">
-        <v>15.5</v>
+        <v>13.9</v>
       </c>
       <c r="F13" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J13" t="n">
-        <v>92.09999999999999</v>
+        <v>84.16</v>
       </c>
       <c r="K13" t="n">
-        <v>93.45</v>
+        <v>86.08</v>
       </c>
       <c r="L13" t="n">
-        <v>90.81999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1242,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1260,41 +1260,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.6</v>
+        <v>16.64</v>
       </c>
       <c r="C14" t="n">
-        <v>16.66</v>
+        <v>16.72</v>
       </c>
       <c r="D14" t="n">
-        <v>16.52</v>
+        <v>16.62</v>
       </c>
       <c r="E14" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="F14" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J14" t="n">
-        <v>95.29000000000001</v>
+        <v>89.45</v>
       </c>
       <c r="K14" t="n">
-        <v>96.45999999999999</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>93.84</v>
+        <v>85.8</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1303,16 +1303,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6425</v>
+        <v>6411</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1321,41 +1321,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="C15" t="n">
         <v>16.91</v>
       </c>
-      <c r="C15" t="n">
-        <v>17.19</v>
-      </c>
       <c r="D15" t="n">
-        <v>16.69</v>
+        <v>16.64</v>
       </c>
       <c r="E15" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="F15" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="J15" t="n">
-        <v>94.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="K15" t="n">
-        <v>96.09</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>90.87</v>
+        <v>89.92</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6442</v>
+        <v>6417</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1373,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1382,56 +1382,56 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.68</v>
+        <v>16.79</v>
       </c>
       <c r="C16" t="n">
-        <v>18.12</v>
+        <v>16.87</v>
       </c>
       <c r="D16" t="n">
-        <v>17.08</v>
+        <v>16.65</v>
       </c>
       <c r="E16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F16" t="n">
         <v>15.3</v>
       </c>
-      <c r="F16" t="n">
-        <v>14.6</v>
-      </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="I16" t="n">
         <v>0.12</v>
       </c>
       <c r="J16" t="n">
-        <v>86.59</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>93.40000000000001</v>
+        <v>93.45</v>
       </c>
       <c r="L16" t="n">
-        <v>80.54000000000001</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6451</v>
+        <v>6420</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1443,59 +1443,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.95</v>
+        <v>16.6</v>
       </c>
       <c r="C17" t="n">
-        <v>21.08</v>
+        <v>16.66</v>
       </c>
       <c r="D17" t="n">
-        <v>18.04</v>
+        <v>16.52</v>
       </c>
       <c r="E17" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="F17" t="n">
-        <v>11.6</v>
+        <v>15.6</v>
       </c>
       <c r="G17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.82</v>
+        <v>0.08</v>
       </c>
       <c r="I17" t="n">
-        <v>0.41</v>
+        <v>0.06</v>
       </c>
       <c r="J17" t="n">
-        <v>64.73999999999999</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>79.75</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>55.98</v>
+        <v>93.84</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6474</v>
+        <v>6425</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1504,59 +1504,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.54</v>
+        <v>16.91</v>
       </c>
       <c r="C18" t="n">
-        <v>21.83</v>
+        <v>17.19</v>
       </c>
       <c r="D18" t="n">
-        <v>21.18</v>
+        <v>16.69</v>
       </c>
       <c r="E18" t="n">
-        <v>11.6</v>
+        <v>15.9</v>
       </c>
       <c r="F18" t="n">
-        <v>10.7</v>
+        <v>15.6</v>
       </c>
       <c r="G18" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.19</v>
+        <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>53.45</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>58.22</v>
+        <v>96.09</v>
       </c>
       <c r="L18" t="n">
-        <v>49.34</v>
+        <v>90.87</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6485</v>
+        <v>6442</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1565,233 +1565,233 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.02</v>
+        <v>17.68</v>
       </c>
       <c r="C19" t="n">
-        <v>22.16</v>
+        <v>18.12</v>
       </c>
       <c r="D19" t="n">
-        <v>21.88</v>
+        <v>17.08</v>
       </c>
       <c r="E19" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="F19" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="G19" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>1.31</v>
+        <v>0.27</v>
       </c>
       <c r="I19" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>50.18</v>
+        <v>86.59</v>
       </c>
       <c r="K19" t="n">
-        <v>52.66</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>47.74</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4352</v>
+        <v>685</v>
       </c>
       <c r="O19" t="n">
-        <v>6511</v>
+        <v>6451</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.31</v>
+        <v>19.95</v>
       </c>
       <c r="C20" t="n">
-        <v>22.81</v>
+        <v>21.08</v>
       </c>
       <c r="D20" t="n">
-        <v>22.04</v>
+        <v>18.04</v>
       </c>
       <c r="E20" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="F20" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="G20" t="n">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
       <c r="I20" t="n">
-        <v>1.28</v>
+        <v>0.41</v>
       </c>
       <c r="J20" t="n">
-        <v>50.19</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>51.75</v>
+        <v>79.75</v>
       </c>
       <c r="L20" t="n">
-        <v>47.76</v>
+        <v>55.98</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5406</v>
+        <v>1926</v>
       </c>
       <c r="O20" t="n">
-        <v>6539</v>
+        <v>6474</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.68</v>
+        <v>21.54</v>
       </c>
       <c r="C21" t="n">
-        <v>23.1</v>
+        <v>21.83</v>
       </c>
       <c r="D21" t="n">
-        <v>22.11</v>
+        <v>21.18</v>
       </c>
       <c r="E21" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F21" t="n">
         <v>10.7</v>
       </c>
       <c r="G21" t="n">
-        <v>384</v>
+        <v>44</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="I21" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="J21" t="n">
-        <v>48.82</v>
+        <v>53.45</v>
       </c>
       <c r="K21" t="n">
-        <v>51.28</v>
+        <v>58.22</v>
       </c>
       <c r="L21" t="n">
-        <v>47.13</v>
+        <v>49.34</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6743</v>
+        <v>2410</v>
       </c>
       <c r="O21" t="n">
-        <v>6573</v>
+        <v>6485</v>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.01</v>
+        <v>22.02</v>
       </c>
       <c r="C22" t="n">
-        <v>22.58</v>
+        <v>22.16</v>
       </c>
       <c r="D22" t="n">
-        <v>21.62</v>
+        <v>21.88</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F22" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="G22" t="n">
-        <v>452</v>
+        <v>111</v>
       </c>
       <c r="H22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="I22" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="J22" t="n">
-        <v>49.71</v>
+        <v>50.18</v>
       </c>
       <c r="K22" t="n">
-        <v>51.65</v>
+        <v>52.66</v>
       </c>
       <c r="L22" t="n">
-        <v>46.69</v>
+        <v>47.74</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6767</v>
+        <v>4352</v>
       </c>
       <c r="O22" t="n">
-        <v>6576</v>
+        <v>6511</v>
       </c>
       <c r="P22" t="n">
         <v>6</v>
@@ -1803,56 +1803,56 @@
         <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.59</v>
+        <v>22.31</v>
       </c>
       <c r="C23" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D23" t="n">
-        <v>20.76</v>
+        <v>22.04</v>
       </c>
       <c r="E23" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="F23" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="G23" t="n">
-        <v>564</v>
+        <v>198</v>
       </c>
       <c r="H23" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="J23" t="n">
-        <v>51.87</v>
+        <v>50.19</v>
       </c>
       <c r="K23" t="n">
-        <v>56.03</v>
+        <v>51.75</v>
       </c>
       <c r="L23" t="n">
-        <v>45.92</v>
+        <v>47.76</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6796</v>
+        <v>5406</v>
       </c>
       <c r="O23" t="n">
-        <v>6599</v>
+        <v>6539</v>
       </c>
       <c r="P23" t="n">
         <v>6</v>
@@ -1861,68 +1861,68 @@
         <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20.19</v>
+        <v>22.68</v>
       </c>
       <c r="C24" t="n">
-        <v>20.64</v>
+        <v>23.1</v>
       </c>
       <c r="D24" t="n">
-        <v>19.53</v>
+        <v>22.11</v>
       </c>
       <c r="E24" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F24" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="G24" t="n">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="H24" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="I24" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="J24" t="n">
-        <v>55.29</v>
+        <v>48.82</v>
       </c>
       <c r="K24" t="n">
-        <v>57.87</v>
+        <v>51.28</v>
       </c>
       <c r="L24" t="n">
-        <v>52.99</v>
+        <v>47.13</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6767</v>
+        <v>6743</v>
       </c>
       <c r="O24" t="n">
-        <v>6576</v>
+        <v>6573</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q24" t="n">
+        <v>7</v>
+      </c>
+      <c r="R24" t="n">
         <v>6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>5</v>
       </c>
       <c r="S24" t="n">
         <v>60</v>
@@ -1931,297 +1931,297 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18.89</v>
+        <v>22.01</v>
       </c>
       <c r="C25" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D25" t="n">
-        <v>18.08</v>
+        <v>21.62</v>
       </c>
       <c r="E25" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G25" t="n">
-        <v>212</v>
+        <v>452</v>
       </c>
       <c r="H25" t="n">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="I25" t="n">
-        <v>0.35</v>
+        <v>1.27</v>
       </c>
       <c r="J25" t="n">
-        <v>69.7</v>
+        <v>49.71</v>
       </c>
       <c r="K25" t="n">
-        <v>82.87</v>
+        <v>51.65</v>
       </c>
       <c r="L25" t="n">
-        <v>57.89</v>
+        <v>46.69</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6691</v>
+        <v>6767</v>
       </c>
       <c r="O25" t="n">
-        <v>6514</v>
+        <v>6576</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.5</v>
+        <v>21.59</v>
       </c>
       <c r="C26" t="n">
-        <v>17.9</v>
+        <v>22.58</v>
       </c>
       <c r="D26" t="n">
-        <v>17.26</v>
+        <v>20.76</v>
       </c>
       <c r="E26" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="F26" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="G26" t="n">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31</v>
+        <v>1.24</v>
       </c>
       <c r="I26" t="n">
-        <v>0.25</v>
+        <v>1.07</v>
       </c>
       <c r="J26" t="n">
-        <v>84.14</v>
+        <v>51.87</v>
       </c>
       <c r="K26" t="n">
-        <v>87.05</v>
+        <v>56.03</v>
       </c>
       <c r="L26" t="n">
-        <v>79.48999999999999</v>
+        <v>45.92</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3786</v>
+        <v>6796</v>
       </c>
       <c r="O26" t="n">
-        <v>6422</v>
+        <v>6599</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.02</v>
+        <v>20.19</v>
       </c>
       <c r="C27" t="n">
-        <v>17.27</v>
+        <v>20.64</v>
       </c>
       <c r="D27" t="n">
-        <v>16.92</v>
+        <v>19.53</v>
       </c>
       <c r="E27" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F27" t="n">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H27" t="n">
-        <v>0.25</v>
+        <v>1.05</v>
       </c>
       <c r="I27" t="n">
-        <v>0.21</v>
+        <v>0.95</v>
       </c>
       <c r="J27" t="n">
-        <v>86.8</v>
+        <v>55.29</v>
       </c>
       <c r="K27" t="n">
-        <v>88.91</v>
+        <v>57.87</v>
       </c>
       <c r="L27" t="n">
-        <v>81.98999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1246</v>
+        <v>6767</v>
       </c>
       <c r="O27" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.89</v>
+        <v>18.89</v>
       </c>
       <c r="C28" t="n">
-        <v>17.03</v>
+        <v>19.62</v>
       </c>
       <c r="D28" t="n">
-        <v>16.78</v>
+        <v>18.08</v>
       </c>
       <c r="E28" t="n">
-        <v>14.9</v>
+        <v>13.1</v>
       </c>
       <c r="F28" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H28" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="I28" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="J28" t="n">
-        <v>88.48999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K28" t="n">
-        <v>90.31</v>
+        <v>82.87</v>
       </c>
       <c r="L28" t="n">
-        <v>85.76000000000001</v>
+        <v>57.89</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="O28" t="n">
-        <v>6417</v>
+        <v>6514</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.13</v>
+        <v>17.5</v>
       </c>
       <c r="C29" t="n">
-        <v>17.32</v>
+        <v>17.9</v>
       </c>
       <c r="D29" t="n">
-        <v>16.89</v>
+        <v>17.26</v>
       </c>
       <c r="E29" t="n">
         <v>14.7</v>
       </c>
       <c r="F29" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H29" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="I29" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J29" t="n">
-        <v>85.90000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="K29" t="n">
-        <v>88.63</v>
+        <v>87.05</v>
       </c>
       <c r="L29" t="n">
-        <v>83.40000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="O29" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
         <v>2</v>
@@ -2236,47 +2236,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.01</v>
+        <v>17.02</v>
       </c>
       <c r="C30" t="n">
-        <v>17.08</v>
+        <v>17.27</v>
       </c>
       <c r="D30" t="n">
-        <v>16.93</v>
+        <v>16.92</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F30" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="I30" t="n">
         <v>0.21</v>
       </c>
       <c r="J30" t="n">
-        <v>88.16</v>
+        <v>86.8</v>
       </c>
       <c r="K30" t="n">
-        <v>88.7</v>
+        <v>88.91</v>
       </c>
       <c r="L30" t="n">
-        <v>87.34999999999999</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="O30" t="n">
         <v>6414</v>
@@ -2285,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -2297,41 +2297,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.07</v>
+        <v>16.89</v>
       </c>
       <c r="C31" t="n">
-        <v>17.29</v>
+        <v>17.03</v>
       </c>
       <c r="D31" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F31" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J31" t="n">
-        <v>88.06999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>89.45999999999999</v>
+        <v>90.31</v>
       </c>
       <c r="L31" t="n">
-        <v>85.97</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2358,41 +2358,41 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.44</v>
+        <v>17.13</v>
       </c>
       <c r="C32" t="n">
-        <v>17.52</v>
+        <v>17.32</v>
       </c>
       <c r="D32" t="n">
-        <v>17.31</v>
+        <v>16.89</v>
       </c>
       <c r="E32" t="n">
         <v>14.7</v>
       </c>
       <c r="F32" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="J32" t="n">
-        <v>84.31999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>85.27</v>
+        <v>88.63</v>
       </c>
       <c r="L32" t="n">
-        <v>82.56999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2401,16 +2401,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2419,41 +2419,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.22</v>
+        <v>17.01</v>
       </c>
       <c r="C33" t="n">
-        <v>17.34</v>
+        <v>17.08</v>
       </c>
       <c r="D33" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E33" t="n">
         <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J33" t="n">
-        <v>87.37</v>
+        <v>88.16</v>
       </c>
       <c r="K33" t="n">
-        <v>88.34999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="L33" t="n">
-        <v>86.23</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2480,41 +2480,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.38</v>
+        <v>17.07</v>
       </c>
       <c r="C34" t="n">
-        <v>17.5</v>
+        <v>17.29</v>
       </c>
       <c r="D34" t="n">
-        <v>17.22</v>
+        <v>16.93</v>
       </c>
       <c r="E34" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
-        <v>87.89</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>89.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>87.03</v>
+        <v>85.97</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2523,13 +2523,13 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
@@ -2541,41 +2541,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.51</v>
+        <v>17.44</v>
       </c>
       <c r="C35" t="n">
-        <v>17.64</v>
+        <v>17.52</v>
       </c>
       <c r="D35" t="n">
-        <v>17.34</v>
+        <v>17.31</v>
       </c>
       <c r="E35" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="F35" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="I35" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="J35" t="n">
-        <v>88.95</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>90.3</v>
+        <v>85.27</v>
       </c>
       <c r="L35" t="n">
-        <v>87.78</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2584,16 +2584,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6437</v>
+        <v>6417</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -2602,20 +2602,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.73</v>
+        <v>17.22</v>
       </c>
       <c r="C36" t="n">
-        <v>18.06</v>
+        <v>17.34</v>
       </c>
       <c r="D36" t="n">
-        <v>17.42</v>
+        <v>17.11</v>
       </c>
       <c r="E36" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
         <v>14.9</v>
@@ -2624,19 +2624,19 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I36" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J36" t="n">
-        <v>85.27</v>
+        <v>87.37</v>
       </c>
       <c r="K36" t="n">
-        <v>88.19</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>81.95</v>
+        <v>86.23</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2645,13 +2645,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -2663,41 +2663,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18.36</v>
+        <v>17.38</v>
       </c>
       <c r="C37" t="n">
-        <v>18.45</v>
+        <v>17.5</v>
       </c>
       <c r="D37" t="n">
-        <v>18.19</v>
+        <v>17.22</v>
       </c>
       <c r="E37" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="F37" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="I37" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="J37" t="n">
-        <v>80.73</v>
+        <v>87.89</v>
       </c>
       <c r="K37" t="n">
-        <v>81.93000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="L37" t="n">
-        <v>79.83</v>
+        <v>87.03</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2706,16 +2706,16 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6471</v>
+        <v>6408</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -2724,41 +2724,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.81</v>
+        <v>17.51</v>
       </c>
       <c r="C38" t="n">
-        <v>19.07</v>
+        <v>17.64</v>
       </c>
       <c r="D38" t="n">
-        <v>18.51</v>
+        <v>17.34</v>
       </c>
       <c r="E38" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="F38" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="I38" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="J38" t="n">
-        <v>76.59999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="K38" t="n">
-        <v>79.87</v>
+        <v>90.3</v>
       </c>
       <c r="L38" t="n">
-        <v>74.01000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2767,16 +2767,16 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6482</v>
+        <v>6437</v>
       </c>
       <c r="P38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -2785,41 +2785,41 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.81</v>
+        <v>17.73</v>
       </c>
       <c r="C39" t="n">
-        <v>20.67</v>
+        <v>18.06</v>
       </c>
       <c r="D39" t="n">
-        <v>18.96</v>
+        <v>17.42</v>
       </c>
       <c r="E39" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="F39" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="J39" t="n">
-        <v>69.16</v>
+        <v>85.27</v>
       </c>
       <c r="K39" t="n">
-        <v>75.04000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="L39" t="n">
-        <v>63.43</v>
+        <v>81.95</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6496</v>
+        <v>6457</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -2846,358 +2846,358 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>21.22</v>
+        <v>18.36</v>
       </c>
       <c r="C40" t="n">
-        <v>21.6</v>
+        <v>18.45</v>
       </c>
       <c r="D40" t="n">
-        <v>20.76</v>
+        <v>18.19</v>
       </c>
       <c r="E40" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="F40" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="G40" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="I40" t="n">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
       <c r="J40" t="n">
-        <v>60.52</v>
+        <v>80.73</v>
       </c>
       <c r="K40" t="n">
-        <v>62.17</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>58.42</v>
+        <v>79.83</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6516</v>
+        <v>6471</v>
       </c>
       <c r="P40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>21.62</v>
+        <v>18.81</v>
       </c>
       <c r="C41" t="n">
-        <v>21.84</v>
+        <v>19.07</v>
       </c>
       <c r="D41" t="n">
-        <v>21.44</v>
+        <v>18.51</v>
       </c>
       <c r="E41" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F41" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="G41" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="I41" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="J41" t="n">
-        <v>58.13</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>60.32</v>
+        <v>79.87</v>
       </c>
       <c r="L41" t="n">
-        <v>56.76</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6548</v>
+        <v>6482</v>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21.96</v>
+        <v>19.81</v>
       </c>
       <c r="C42" t="n">
-        <v>22.41</v>
+        <v>20.67</v>
       </c>
       <c r="D42" t="n">
-        <v>21.77</v>
+        <v>18.96</v>
       </c>
       <c r="E42" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="F42" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="G42" t="n">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>1.15</v>
+        <v>0.71</v>
       </c>
       <c r="I42" t="n">
-        <v>1.11</v>
+        <v>0.54</v>
       </c>
       <c r="J42" t="n">
-        <v>55.95</v>
+        <v>69.16</v>
       </c>
       <c r="K42" t="n">
-        <v>57.92</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>54.15</v>
+        <v>63.43</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6573</v>
+        <v>6496</v>
       </c>
       <c r="P42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.46</v>
+        <v>21.22</v>
       </c>
       <c r="C43" t="n">
-        <v>23.17</v>
+        <v>21.6</v>
       </c>
       <c r="D43" t="n">
-        <v>21.82</v>
+        <v>20.76</v>
       </c>
       <c r="E43" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F43" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
-        <v>383</v>
+        <v>73</v>
       </c>
       <c r="H43" t="n">
-        <v>1.29</v>
+        <v>0.99</v>
       </c>
       <c r="I43" t="n">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="J43" t="n">
-        <v>52.56</v>
+        <v>60.52</v>
       </c>
       <c r="K43" t="n">
-        <v>54.35</v>
+        <v>62.17</v>
       </c>
       <c r="L43" t="n">
-        <v>50.6</v>
+        <v>58.42</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>6763</v>
+        <v>2990</v>
       </c>
       <c r="O43" t="n">
-        <v>6593</v>
+        <v>6516</v>
       </c>
       <c r="P43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S43" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22.1</v>
+        <v>21.62</v>
       </c>
       <c r="C44" t="n">
-        <v>22.92</v>
+        <v>21.84</v>
       </c>
       <c r="D44" t="n">
-        <v>21.76</v>
+        <v>21.44</v>
       </c>
       <c r="E44" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F44" t="n">
-        <v>11.5</v>
+        <v>12.7</v>
       </c>
       <c r="G44" t="n">
-        <v>479</v>
+        <v>137</v>
       </c>
       <c r="H44" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="I44" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="J44" t="n">
-        <v>53.58</v>
+        <v>58.13</v>
       </c>
       <c r="K44" t="n">
-        <v>55.95</v>
+        <v>60.32</v>
       </c>
       <c r="L44" t="n">
-        <v>51.48</v>
+        <v>56.76</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>6739</v>
+        <v>5684</v>
       </c>
       <c r="O44" t="n">
-        <v>6582</v>
+        <v>6548</v>
       </c>
       <c r="P44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
         <v>5</v>
       </c>
       <c r="S44" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21.45</v>
+        <v>21.96</v>
       </c>
       <c r="C45" t="n">
-        <v>22.62</v>
+        <v>22.41</v>
       </c>
       <c r="D45" t="n">
-        <v>20.83</v>
+        <v>21.77</v>
       </c>
       <c r="E45" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F45" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G45" t="n">
-        <v>640</v>
+        <v>205</v>
       </c>
       <c r="H45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I45" t="n">
         <v>1.11</v>
       </c>
-      <c r="I45" t="n">
-        <v>0.92</v>
-      </c>
       <c r="J45" t="n">
-        <v>56.35</v>
+        <v>55.95</v>
       </c>
       <c r="K45" t="n">
-        <v>62.61</v>
+        <v>57.92</v>
       </c>
       <c r="L45" t="n">
-        <v>51.88</v>
+        <v>54.15</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6810</v>
+        <v>6619</v>
       </c>
       <c r="O45" t="n">
-        <v>6610</v>
+        <v>6573</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q45" t="n">
         <v>6</v>
@@ -3212,59 +3212,59 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.67</v>
+        <v>22.46</v>
       </c>
       <c r="C46" t="n">
-        <v>20.85</v>
+        <v>23.17</v>
       </c>
       <c r="D46" t="n">
-        <v>19.11</v>
+        <v>21.82</v>
       </c>
       <c r="E46" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F46" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="G46" t="n">
-        <v>279</v>
+        <v>383</v>
       </c>
       <c r="H46" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1.21</v>
       </c>
       <c r="J46" t="n">
-        <v>66.39</v>
+        <v>52.56</v>
       </c>
       <c r="K46" t="n">
-        <v>68.68000000000001</v>
+        <v>54.35</v>
       </c>
       <c r="L46" t="n">
-        <v>61.4</v>
+        <v>50.6</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6772</v>
+        <v>6763</v>
       </c>
       <c r="O46" t="n">
-        <v>6571</v>
+        <v>6593</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S46" t="n">
         <v>60</v>
@@ -3273,120 +3273,120 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18.92</v>
+        <v>22.1</v>
       </c>
       <c r="C47" t="n">
-        <v>19.22</v>
+        <v>22.92</v>
       </c>
       <c r="D47" t="n">
-        <v>18.64</v>
+        <v>21.76</v>
       </c>
       <c r="E47" t="n">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="F47" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>143</v>
+        <v>479</v>
       </c>
       <c r="H47" t="n">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.58</v>
+        <v>1.14</v>
       </c>
       <c r="J47" t="n">
-        <v>71.48999999999999</v>
+        <v>53.58</v>
       </c>
       <c r="K47" t="n">
-        <v>73.28</v>
+        <v>55.95</v>
       </c>
       <c r="L47" t="n">
-        <v>69.45</v>
+        <v>51.48</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>6254</v>
+        <v>6739</v>
       </c>
       <c r="O47" t="n">
-        <v>6508</v>
+        <v>6582</v>
       </c>
       <c r="P47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S47" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.78</v>
+        <v>21.45</v>
       </c>
       <c r="C48" t="n">
-        <v>18.89</v>
+        <v>22.62</v>
       </c>
       <c r="D48" t="n">
-        <v>18.67</v>
+        <v>20.83</v>
       </c>
       <c r="E48" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="F48" t="n">
-        <v>12.8</v>
+        <v>11.1</v>
       </c>
       <c r="G48" t="n">
-        <v>134</v>
+        <v>640</v>
       </c>
       <c r="H48" t="n">
-        <v>0.63</v>
+        <v>1.11</v>
       </c>
       <c r="I48" t="n">
-        <v>0.57</v>
+        <v>0.92</v>
       </c>
       <c r="J48" t="n">
-        <v>70.87</v>
+        <v>56.35</v>
       </c>
       <c r="K48" t="n">
-        <v>73.17</v>
+        <v>62.61</v>
       </c>
       <c r="L48" t="n">
-        <v>68.48</v>
+        <v>51.88</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>5929</v>
+        <v>6810</v>
       </c>
       <c r="O48" t="n">
-        <v>6494</v>
+        <v>6610</v>
       </c>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S48" t="n">
         <v>60</v>
@@ -3395,59 +3395,59 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18.59</v>
+        <v>19.67</v>
       </c>
       <c r="C49" t="n">
-        <v>19.26</v>
+        <v>20.85</v>
       </c>
       <c r="D49" t="n">
-        <v>18.18</v>
+        <v>19.11</v>
       </c>
       <c r="E49" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="F49" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="G49" t="n">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="I49" t="n">
-        <v>0.41</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
-        <v>76.48999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="K49" t="n">
-        <v>80.08</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>71.70999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>5478</v>
+        <v>6772</v>
       </c>
       <c r="O49" t="n">
-        <v>6494</v>
+        <v>6571</v>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S49" t="n">
         <v>60</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,294 +528,294 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.36</v>
+        <v>17.45</v>
       </c>
       <c r="C2" t="n">
-        <v>15.86</v>
+        <v>17.76</v>
       </c>
       <c r="D2" t="n">
-        <v>15.05</v>
+        <v>17.19</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="F2" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G2" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H2" t="n">
-        <v>0.41</v>
+        <v>0.68</v>
       </c>
       <c r="I2" t="n">
-        <v>0.36</v>
+        <v>0.62</v>
       </c>
       <c r="J2" t="n">
-        <v>76.31</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>78.77</v>
+        <v>68.27</v>
       </c>
       <c r="L2" t="n">
-        <v>71.61</v>
+        <v>62.48</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6686</v>
+        <v>6561</v>
       </c>
       <c r="O2" t="n">
-        <v>6534</v>
+        <v>6539</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
       </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
       <c r="S2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.04</v>
+        <v>17.1</v>
       </c>
       <c r="C3" t="n">
-        <v>15.26</v>
+        <v>17.35</v>
       </c>
       <c r="D3" t="n">
-        <v>14.82</v>
+        <v>16.86</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="G3" t="n">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="H3" t="n">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="I3" t="n">
-        <v>0.33</v>
+        <v>0.61</v>
       </c>
       <c r="J3" t="n">
-        <v>77.86</v>
+        <v>67.38</v>
       </c>
       <c r="K3" t="n">
-        <v>80.23</v>
+        <v>67.78</v>
       </c>
       <c r="L3" t="n">
-        <v>75.81</v>
+        <v>66.55</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5708</v>
+        <v>6671</v>
       </c>
       <c r="O3" t="n">
-        <v>6494</v>
+        <v>6536</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.47</v>
+        <v>16.52</v>
       </c>
       <c r="C4" t="n">
-        <v>14.79</v>
+        <v>17.36</v>
       </c>
       <c r="D4" t="n">
-        <v>14.22</v>
+        <v>16.01</v>
       </c>
       <c r="E4" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F4" t="n">
         <v>10.7</v>
       </c>
       <c r="G4" t="n">
-        <v>131</v>
+        <v>301</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
-        <v>80.75</v>
+        <v>69.84</v>
       </c>
       <c r="K4" t="n">
-        <v>82.34</v>
+        <v>72.16</v>
       </c>
       <c r="L4" t="n">
-        <v>79.73999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6254</v>
+        <v>6681</v>
       </c>
       <c r="O4" t="n">
-        <v>6491</v>
+        <v>6525</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.34</v>
+        <v>15.55</v>
       </c>
       <c r="C5" t="n">
-        <v>14.4</v>
+        <v>16.32</v>
       </c>
       <c r="D5" t="n">
-        <v>14.25</v>
+        <v>15.05</v>
       </c>
       <c r="E5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F5" t="n">
         <v>10.7</v>
       </c>
-      <c r="F5" t="n">
-        <v>10.3</v>
-      </c>
       <c r="G5" t="n">
-        <v>38</v>
+        <v>231</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I5" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="J5" t="n">
-        <v>79.29000000000001</v>
+        <v>75.25</v>
       </c>
       <c r="K5" t="n">
-        <v>80.34999999999999</v>
+        <v>78.77</v>
       </c>
       <c r="L5" t="n">
-        <v>77.13</v>
+        <v>71.11</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3949</v>
+        <v>6729</v>
       </c>
       <c r="O5" t="n">
-        <v>6425</v>
+        <v>6556</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.56</v>
+        <v>15.04</v>
       </c>
       <c r="C6" t="n">
-        <v>14.75</v>
+        <v>15.26</v>
       </c>
       <c r="D6" t="n">
-        <v>14.34</v>
+        <v>14.82</v>
       </c>
       <c r="E6" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F6" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="H6" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I6" t="n">
         <v>0.33</v>
       </c>
       <c r="J6" t="n">
-        <v>78.20999999999999</v>
+        <v>77.86</v>
       </c>
       <c r="K6" t="n">
-        <v>80.09999999999999</v>
+        <v>80.23</v>
       </c>
       <c r="L6" t="n">
-        <v>75.43000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2449</v>
+        <v>5708</v>
       </c>
       <c r="O6" t="n">
-        <v>6420</v>
+        <v>6494</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -827,126 +827,126 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="C7" t="n">
         <v>14.79</v>
       </c>
-      <c r="C7" t="n">
-        <v>14.98</v>
-      </c>
       <c r="D7" t="n">
-        <v>14.63</v>
+        <v>14.22</v>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F7" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H7" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="J7" t="n">
-        <v>77.20999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="K7" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="L7" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="L7" t="n">
-        <v>74.54000000000001</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O7" t="n">
-        <v>6411</v>
+        <v>6491</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.24</v>
+        <v>14.34</v>
       </c>
       <c r="C8" t="n">
-        <v>15.48</v>
+        <v>14.4</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="E8" t="n">
         <v>10.7</v>
       </c>
       <c r="F8" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="I8" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="J8" t="n">
-        <v>74.68000000000001</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>75.5</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>73.42</v>
+        <v>77.13</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O8" t="n">
-        <v>6411</v>
+        <v>6425</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -955,59 +955,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.62</v>
+        <v>14.56</v>
       </c>
       <c r="C9" t="n">
-        <v>15.76</v>
+        <v>14.75</v>
       </c>
       <c r="D9" t="n">
-        <v>15.46</v>
+        <v>14.34</v>
       </c>
       <c r="E9" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I9" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J9" t="n">
-        <v>81.47</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>89.01000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>74.23</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O9" t="n">
-        <v>6402</v>
+        <v>6420</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1016,41 +1016,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.86</v>
+        <v>14.79</v>
       </c>
       <c r="C10" t="n">
-        <v>16.08</v>
+        <v>14.98</v>
       </c>
       <c r="D10" t="n">
-        <v>15.66</v>
+        <v>14.63</v>
       </c>
       <c r="E10" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="n">
-        <v>13.7</v>
+        <v>10.4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="I10" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J10" t="n">
-        <v>87.95999999999999</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>89.39</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>86.37</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>6411</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1077,41 +1077,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.22</v>
+        <v>15.24</v>
       </c>
       <c r="C11" t="n">
-        <v>16.35</v>
+        <v>15.48</v>
       </c>
       <c r="D11" t="n">
-        <v>16.12</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="F11" t="n">
-        <v>13.4</v>
+        <v>10.4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="I11" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="J11" t="n">
-        <v>85.42</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>87.15000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="L11" t="n">
-        <v>83.22</v>
+        <v>73.42</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6405</v>
+        <v>6411</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1138,41 +1138,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.39</v>
+        <v>15.62</v>
       </c>
       <c r="C12" t="n">
-        <v>16.55</v>
+        <v>15.76</v>
       </c>
       <c r="D12" t="n">
-        <v>16.22</v>
+        <v>15.46</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9</v>
+        <v>12.3</v>
       </c>
       <c r="F12" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J12" t="n">
-        <v>85.56999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="K12" t="n">
-        <v>87.13</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>84.14</v>
+        <v>74.23</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1181,13 +1181,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6417</v>
+        <v>6402</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1199,41 +1199,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.68</v>
+        <v>15.86</v>
       </c>
       <c r="C13" t="n">
-        <v>16.76</v>
+        <v>16.08</v>
       </c>
       <c r="D13" t="n">
-        <v>16.63</v>
+        <v>15.66</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F13" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="I13" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="J13" t="n">
-        <v>84.16</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>86.08</v>
+        <v>89.39</v>
       </c>
       <c r="L13" t="n">
-        <v>81.98</v>
+        <v>86.37</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1245,10 +1245,10 @@
         <v>6411</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1260,41 +1260,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.64</v>
+        <v>16.22</v>
       </c>
       <c r="C14" t="n">
-        <v>16.72</v>
+        <v>16.35</v>
       </c>
       <c r="D14" t="n">
-        <v>16.62</v>
+        <v>16.12</v>
       </c>
       <c r="E14" t="n">
-        <v>14.8</v>
+        <v>13.7</v>
       </c>
       <c r="F14" t="n">
-        <v>14.3</v>
+        <v>13.4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="I14" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J14" t="n">
-        <v>89.45</v>
+        <v>85.42</v>
       </c>
       <c r="K14" t="n">
-        <v>91.73999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>85.8</v>
+        <v>83.22</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1303,13 +1303,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1321,41 +1321,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.73</v>
+        <v>16.39</v>
       </c>
       <c r="C15" t="n">
-        <v>16.91</v>
+        <v>16.55</v>
       </c>
       <c r="D15" t="n">
-        <v>16.64</v>
+        <v>16.22</v>
       </c>
       <c r="E15" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="F15" t="n">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I15" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J15" t="n">
-        <v>91.16</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>91.98999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="L15" t="n">
-        <v>89.92</v>
+        <v>84.14</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1370,7 +1370,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1382,41 +1382,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.79</v>
+        <v>16.68</v>
       </c>
       <c r="C16" t="n">
-        <v>16.87</v>
+        <v>16.76</v>
       </c>
       <c r="D16" t="n">
-        <v>16.65</v>
+        <v>16.63</v>
       </c>
       <c r="E16" t="n">
-        <v>15.5</v>
+        <v>13.9</v>
       </c>
       <c r="F16" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="I16" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J16" t="n">
-        <v>92.09999999999999</v>
+        <v>84.16</v>
       </c>
       <c r="K16" t="n">
-        <v>93.45</v>
+        <v>86.08</v>
       </c>
       <c r="L16" t="n">
-        <v>90.81999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1443,41 +1443,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.6</v>
+        <v>16.64</v>
       </c>
       <c r="C17" t="n">
-        <v>16.66</v>
+        <v>16.72</v>
       </c>
       <c r="D17" t="n">
-        <v>16.52</v>
+        <v>16.62</v>
       </c>
       <c r="E17" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="F17" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J17" t="n">
-        <v>95.29000000000001</v>
+        <v>89.45</v>
       </c>
       <c r="K17" t="n">
-        <v>96.45999999999999</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>93.84</v>
+        <v>85.8</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1486,16 +1486,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6425</v>
+        <v>6411</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1504,41 +1504,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="C18" t="n">
         <v>16.91</v>
       </c>
-      <c r="C18" t="n">
-        <v>17.19</v>
-      </c>
       <c r="D18" t="n">
-        <v>16.69</v>
+        <v>16.64</v>
       </c>
       <c r="E18" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="F18" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="J18" t="n">
-        <v>94.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="K18" t="n">
-        <v>96.09</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>90.87</v>
+        <v>89.92</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6442</v>
+        <v>6417</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1565,56 +1565,56 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.68</v>
+        <v>16.79</v>
       </c>
       <c r="C19" t="n">
-        <v>18.12</v>
+        <v>16.87</v>
       </c>
       <c r="D19" t="n">
-        <v>17.08</v>
+        <v>16.65</v>
       </c>
       <c r="E19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F19" t="n">
         <v>15.3</v>
       </c>
-      <c r="F19" t="n">
-        <v>14.6</v>
-      </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="I19" t="n">
         <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>86.59</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>93.40000000000001</v>
+        <v>93.45</v>
       </c>
       <c r="L19" t="n">
-        <v>80.54000000000001</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6451</v>
+        <v>6420</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -1626,59 +1626,59 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.95</v>
+        <v>16.6</v>
       </c>
       <c r="C20" t="n">
-        <v>21.08</v>
+        <v>16.66</v>
       </c>
       <c r="D20" t="n">
-        <v>18.04</v>
+        <v>16.52</v>
       </c>
       <c r="E20" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="F20" t="n">
-        <v>11.6</v>
+        <v>15.6</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.82</v>
+        <v>0.08</v>
       </c>
       <c r="I20" t="n">
-        <v>0.41</v>
+        <v>0.06</v>
       </c>
       <c r="J20" t="n">
-        <v>64.73999999999999</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>79.75</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>55.98</v>
+        <v>93.84</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6474</v>
+        <v>6425</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1687,59 +1687,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.54</v>
+        <v>16.91</v>
       </c>
       <c r="C21" t="n">
-        <v>21.83</v>
+        <v>17.19</v>
       </c>
       <c r="D21" t="n">
-        <v>21.18</v>
+        <v>16.69</v>
       </c>
       <c r="E21" t="n">
-        <v>11.6</v>
+        <v>15.9</v>
       </c>
       <c r="F21" t="n">
-        <v>10.7</v>
+        <v>15.6</v>
       </c>
       <c r="G21" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.19</v>
+        <v>0.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>53.45</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>58.22</v>
+        <v>96.09</v>
       </c>
       <c r="L21" t="n">
-        <v>49.34</v>
+        <v>90.87</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6485</v>
+        <v>6442</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1748,233 +1748,233 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.02</v>
+        <v>17.68</v>
       </c>
       <c r="C22" t="n">
-        <v>22.16</v>
+        <v>18.12</v>
       </c>
       <c r="D22" t="n">
-        <v>21.88</v>
+        <v>17.08</v>
       </c>
       <c r="E22" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="F22" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="G22" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>1.31</v>
+        <v>0.27</v>
       </c>
       <c r="I22" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="J22" t="n">
-        <v>50.18</v>
+        <v>86.59</v>
       </c>
       <c r="K22" t="n">
-        <v>52.66</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>47.74</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4352</v>
+        <v>685</v>
       </c>
       <c r="O22" t="n">
-        <v>6511</v>
+        <v>6451</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22.31</v>
+        <v>19.95</v>
       </c>
       <c r="C23" t="n">
-        <v>22.81</v>
+        <v>21.08</v>
       </c>
       <c r="D23" t="n">
-        <v>22.04</v>
+        <v>18.04</v>
       </c>
       <c r="E23" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="F23" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="G23" t="n">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="H23" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
       <c r="I23" t="n">
-        <v>1.28</v>
+        <v>0.41</v>
       </c>
       <c r="J23" t="n">
-        <v>50.19</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>51.75</v>
+        <v>79.75</v>
       </c>
       <c r="L23" t="n">
-        <v>47.76</v>
+        <v>55.98</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5406</v>
+        <v>1926</v>
       </c>
       <c r="O23" t="n">
-        <v>6539</v>
+        <v>6474</v>
       </c>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.68</v>
+        <v>21.54</v>
       </c>
       <c r="C24" t="n">
-        <v>23.1</v>
+        <v>21.83</v>
       </c>
       <c r="D24" t="n">
-        <v>22.11</v>
+        <v>21.18</v>
       </c>
       <c r="E24" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F24" t="n">
         <v>10.7</v>
       </c>
       <c r="G24" t="n">
-        <v>384</v>
+        <v>44</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="I24" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="J24" t="n">
-        <v>48.82</v>
+        <v>53.45</v>
       </c>
       <c r="K24" t="n">
-        <v>51.28</v>
+        <v>58.22</v>
       </c>
       <c r="L24" t="n">
-        <v>47.13</v>
+        <v>49.34</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6743</v>
+        <v>2410</v>
       </c>
       <c r="O24" t="n">
-        <v>6573</v>
+        <v>6485</v>
       </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.01</v>
+        <v>22.02</v>
       </c>
       <c r="C25" t="n">
-        <v>22.58</v>
+        <v>22.16</v>
       </c>
       <c r="D25" t="n">
-        <v>21.62</v>
+        <v>21.88</v>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F25" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="G25" t="n">
-        <v>452</v>
+        <v>111</v>
       </c>
       <c r="H25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="I25" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="J25" t="n">
-        <v>49.71</v>
+        <v>50.18</v>
       </c>
       <c r="K25" t="n">
-        <v>51.65</v>
+        <v>52.66</v>
       </c>
       <c r="L25" t="n">
-        <v>46.69</v>
+        <v>47.74</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6767</v>
+        <v>4352</v>
       </c>
       <c r="O25" t="n">
-        <v>6576</v>
+        <v>6511</v>
       </c>
       <c r="P25" t="n">
         <v>6</v>
@@ -1986,56 +1986,56 @@
         <v>6</v>
       </c>
       <c r="S25" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21.59</v>
+        <v>22.31</v>
       </c>
       <c r="C26" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D26" t="n">
-        <v>20.76</v>
+        <v>22.04</v>
       </c>
       <c r="E26" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="F26" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="G26" t="n">
-        <v>564</v>
+        <v>198</v>
       </c>
       <c r="H26" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="I26" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="J26" t="n">
-        <v>51.87</v>
+        <v>50.19</v>
       </c>
       <c r="K26" t="n">
-        <v>56.03</v>
+        <v>51.75</v>
       </c>
       <c r="L26" t="n">
-        <v>45.92</v>
+        <v>47.76</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6796</v>
+        <v>5406</v>
       </c>
       <c r="O26" t="n">
-        <v>6599</v>
+        <v>6539</v>
       </c>
       <c r="P26" t="n">
         <v>6</v>
@@ -2044,68 +2044,68 @@
         <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.19</v>
+        <v>22.68</v>
       </c>
       <c r="C27" t="n">
-        <v>20.64</v>
+        <v>23.1</v>
       </c>
       <c r="D27" t="n">
-        <v>19.53</v>
+        <v>22.11</v>
       </c>
       <c r="E27" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F27" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="G27" t="n">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="H27" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="J27" t="n">
-        <v>55.29</v>
+        <v>48.82</v>
       </c>
       <c r="K27" t="n">
-        <v>57.87</v>
+        <v>51.28</v>
       </c>
       <c r="L27" t="n">
-        <v>52.99</v>
+        <v>47.13</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6767</v>
+        <v>6743</v>
       </c>
       <c r="O27" t="n">
-        <v>6576</v>
+        <v>6573</v>
       </c>
       <c r="P27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
+        <v>7</v>
+      </c>
+      <c r="R27" t="n">
         <v>6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>5</v>
       </c>
       <c r="S27" t="n">
         <v>60</v>
@@ -2114,297 +2114,297 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.89</v>
+        <v>22.01</v>
       </c>
       <c r="C28" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D28" t="n">
-        <v>18.08</v>
+        <v>21.62</v>
       </c>
       <c r="E28" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G28" t="n">
-        <v>212</v>
+        <v>452</v>
       </c>
       <c r="H28" t="n">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.35</v>
+        <v>1.27</v>
       </c>
       <c r="J28" t="n">
-        <v>69.7</v>
+        <v>49.71</v>
       </c>
       <c r="K28" t="n">
-        <v>82.87</v>
+        <v>51.65</v>
       </c>
       <c r="L28" t="n">
-        <v>57.89</v>
+        <v>46.69</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6691</v>
+        <v>6767</v>
       </c>
       <c r="O28" t="n">
-        <v>6514</v>
+        <v>6576</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.5</v>
+        <v>21.59</v>
       </c>
       <c r="C29" t="n">
-        <v>17.9</v>
+        <v>22.58</v>
       </c>
       <c r="D29" t="n">
-        <v>17.26</v>
+        <v>20.76</v>
       </c>
       <c r="E29" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="F29" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="G29" t="n">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31</v>
+        <v>1.24</v>
       </c>
       <c r="I29" t="n">
-        <v>0.25</v>
+        <v>1.07</v>
       </c>
       <c r="J29" t="n">
-        <v>84.14</v>
+        <v>51.87</v>
       </c>
       <c r="K29" t="n">
-        <v>87.05</v>
+        <v>56.03</v>
       </c>
       <c r="L29" t="n">
-        <v>79.48999999999999</v>
+        <v>45.92</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3786</v>
+        <v>6796</v>
       </c>
       <c r="O29" t="n">
-        <v>6422</v>
+        <v>6599</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.02</v>
+        <v>20.19</v>
       </c>
       <c r="C30" t="n">
-        <v>17.27</v>
+        <v>20.64</v>
       </c>
       <c r="D30" t="n">
-        <v>16.92</v>
+        <v>19.53</v>
       </c>
       <c r="E30" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F30" t="n">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H30" t="n">
-        <v>0.25</v>
+        <v>1.05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.21</v>
+        <v>0.95</v>
       </c>
       <c r="J30" t="n">
-        <v>86.8</v>
+        <v>55.29</v>
       </c>
       <c r="K30" t="n">
-        <v>88.91</v>
+        <v>57.87</v>
       </c>
       <c r="L30" t="n">
-        <v>81.98999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1246</v>
+        <v>6767</v>
       </c>
       <c r="O30" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.89</v>
+        <v>18.89</v>
       </c>
       <c r="C31" t="n">
-        <v>17.03</v>
+        <v>19.62</v>
       </c>
       <c r="D31" t="n">
-        <v>16.78</v>
+        <v>18.08</v>
       </c>
       <c r="E31" t="n">
-        <v>14.9</v>
+        <v>13.1</v>
       </c>
       <c r="F31" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H31" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="J31" t="n">
-        <v>88.48999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K31" t="n">
-        <v>90.31</v>
+        <v>82.87</v>
       </c>
       <c r="L31" t="n">
-        <v>85.76000000000001</v>
+        <v>57.89</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="O31" t="n">
-        <v>6417</v>
+        <v>6514</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.13</v>
+        <v>17.5</v>
       </c>
       <c r="C32" t="n">
-        <v>17.32</v>
+        <v>17.9</v>
       </c>
       <c r="D32" t="n">
-        <v>16.89</v>
+        <v>17.26</v>
       </c>
       <c r="E32" t="n">
         <v>14.7</v>
       </c>
       <c r="F32" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H32" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="I32" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J32" t="n">
-        <v>85.90000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="K32" t="n">
-        <v>88.63</v>
+        <v>87.05</v>
       </c>
       <c r="L32" t="n">
-        <v>83.40000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="O32" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -2419,47 +2419,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.01</v>
+        <v>17.02</v>
       </c>
       <c r="C33" t="n">
-        <v>17.08</v>
+        <v>17.27</v>
       </c>
       <c r="D33" t="n">
-        <v>16.93</v>
+        <v>16.92</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F33" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="I33" t="n">
         <v>0.21</v>
       </c>
       <c r="J33" t="n">
-        <v>88.16</v>
+        <v>86.8</v>
       </c>
       <c r="K33" t="n">
-        <v>88.7</v>
+        <v>88.91</v>
       </c>
       <c r="L33" t="n">
-        <v>87.34999999999999</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="O33" t="n">
         <v>6414</v>
@@ -2468,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -2480,41 +2480,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.07</v>
+        <v>16.89</v>
       </c>
       <c r="C34" t="n">
-        <v>17.29</v>
+        <v>17.03</v>
       </c>
       <c r="D34" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E34" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F34" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J34" t="n">
-        <v>88.06999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>89.45999999999999</v>
+        <v>90.31</v>
       </c>
       <c r="L34" t="n">
-        <v>85.97</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2541,41 +2541,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.44</v>
+        <v>17.13</v>
       </c>
       <c r="C35" t="n">
-        <v>17.52</v>
+        <v>17.32</v>
       </c>
       <c r="D35" t="n">
-        <v>17.31</v>
+        <v>16.89</v>
       </c>
       <c r="E35" t="n">
         <v>14.7</v>
       </c>
       <c r="F35" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="I35" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="J35" t="n">
-        <v>84.31999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>85.27</v>
+        <v>88.63</v>
       </c>
       <c r="L35" t="n">
-        <v>82.56999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2584,16 +2584,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
         <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -2602,41 +2602,41 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.22</v>
+        <v>17.01</v>
       </c>
       <c r="C36" t="n">
-        <v>17.34</v>
+        <v>17.08</v>
       </c>
       <c r="D36" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E36" t="n">
         <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="I36" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J36" t="n">
-        <v>87.37</v>
+        <v>88.16</v>
       </c>
       <c r="K36" t="n">
-        <v>88.34999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="L36" t="n">
-        <v>86.23</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -2663,41 +2663,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.38</v>
+        <v>17.07</v>
       </c>
       <c r="C37" t="n">
-        <v>17.5</v>
+        <v>17.29</v>
       </c>
       <c r="D37" t="n">
-        <v>17.22</v>
+        <v>16.93</v>
       </c>
       <c r="E37" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I37" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J37" t="n">
-        <v>87.89</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>89.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>87.03</v>
+        <v>85.97</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2706,13 +2706,13 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -2724,41 +2724,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.51</v>
+        <v>17.44</v>
       </c>
       <c r="C38" t="n">
-        <v>17.64</v>
+        <v>17.52</v>
       </c>
       <c r="D38" t="n">
-        <v>17.34</v>
+        <v>17.31</v>
       </c>
       <c r="E38" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="F38" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="J38" t="n">
-        <v>88.95</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>90.3</v>
+        <v>85.27</v>
       </c>
       <c r="L38" t="n">
-        <v>87.78</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2767,16 +2767,16 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6437</v>
+        <v>6417</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -2785,20 +2785,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.73</v>
+        <v>17.22</v>
       </c>
       <c r="C39" t="n">
-        <v>18.06</v>
+        <v>17.34</v>
       </c>
       <c r="D39" t="n">
-        <v>17.42</v>
+        <v>17.11</v>
       </c>
       <c r="E39" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
         <v>14.9</v>
@@ -2807,19 +2807,19 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I39" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J39" t="n">
-        <v>85.27</v>
+        <v>87.37</v>
       </c>
       <c r="K39" t="n">
-        <v>88.19</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>81.95</v>
+        <v>86.23</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2828,13 +2828,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -2846,41 +2846,41 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18.36</v>
+        <v>17.38</v>
       </c>
       <c r="C40" t="n">
-        <v>18.45</v>
+        <v>17.5</v>
       </c>
       <c r="D40" t="n">
-        <v>18.19</v>
+        <v>17.22</v>
       </c>
       <c r="E40" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="F40" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="I40" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="J40" t="n">
-        <v>80.73</v>
+        <v>87.89</v>
       </c>
       <c r="K40" t="n">
-        <v>81.93000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="L40" t="n">
-        <v>79.83</v>
+        <v>87.03</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2889,16 +2889,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6471</v>
+        <v>6408</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -2907,41 +2907,41 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18.81</v>
+        <v>17.51</v>
       </c>
       <c r="C41" t="n">
-        <v>19.07</v>
+        <v>17.64</v>
       </c>
       <c r="D41" t="n">
-        <v>18.51</v>
+        <v>17.34</v>
       </c>
       <c r="E41" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="F41" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="I41" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="J41" t="n">
-        <v>76.59999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="K41" t="n">
-        <v>79.87</v>
+        <v>90.3</v>
       </c>
       <c r="L41" t="n">
-        <v>74.01000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2950,16 +2950,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6482</v>
+        <v>6437</v>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -2968,41 +2968,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.81</v>
+        <v>17.73</v>
       </c>
       <c r="C42" t="n">
-        <v>20.67</v>
+        <v>18.06</v>
       </c>
       <c r="D42" t="n">
-        <v>18.96</v>
+        <v>17.42</v>
       </c>
       <c r="E42" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="F42" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="J42" t="n">
-        <v>69.16</v>
+        <v>85.27</v>
       </c>
       <c r="K42" t="n">
-        <v>75.04000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="L42" t="n">
-        <v>63.43</v>
+        <v>81.95</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3011,16 +3011,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6496</v>
+        <v>6457</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3029,358 +3029,358 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21.22</v>
+        <v>18.36</v>
       </c>
       <c r="C43" t="n">
-        <v>21.6</v>
+        <v>18.45</v>
       </c>
       <c r="D43" t="n">
-        <v>20.76</v>
+        <v>18.19</v>
       </c>
       <c r="E43" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="F43" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="G43" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
       <c r="J43" t="n">
-        <v>60.52</v>
+        <v>80.73</v>
       </c>
       <c r="K43" t="n">
-        <v>62.17</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>58.42</v>
+        <v>79.83</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6516</v>
+        <v>6471</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21.62</v>
+        <v>18.81</v>
       </c>
       <c r="C44" t="n">
-        <v>21.84</v>
+        <v>19.07</v>
       </c>
       <c r="D44" t="n">
-        <v>21.44</v>
+        <v>18.51</v>
       </c>
       <c r="E44" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F44" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="G44" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="J44" t="n">
-        <v>58.13</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>60.32</v>
+        <v>79.87</v>
       </c>
       <c r="L44" t="n">
-        <v>56.76</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6548</v>
+        <v>6482</v>
       </c>
       <c r="P44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21.96</v>
+        <v>19.81</v>
       </c>
       <c r="C45" t="n">
-        <v>22.41</v>
+        <v>20.67</v>
       </c>
       <c r="D45" t="n">
-        <v>21.77</v>
+        <v>18.96</v>
       </c>
       <c r="E45" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="F45" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="G45" t="n">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="H45" t="n">
-        <v>1.15</v>
+        <v>0.71</v>
       </c>
       <c r="I45" t="n">
-        <v>1.11</v>
+        <v>0.54</v>
       </c>
       <c r="J45" t="n">
-        <v>55.95</v>
+        <v>69.16</v>
       </c>
       <c r="K45" t="n">
-        <v>57.92</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>54.15</v>
+        <v>63.43</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6573</v>
+        <v>6496</v>
       </c>
       <c r="P45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S45" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22.46</v>
+        <v>21.22</v>
       </c>
       <c r="C46" t="n">
-        <v>23.17</v>
+        <v>21.6</v>
       </c>
       <c r="D46" t="n">
-        <v>21.82</v>
+        <v>20.76</v>
       </c>
       <c r="E46" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F46" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="G46" t="n">
-        <v>383</v>
+        <v>73</v>
       </c>
       <c r="H46" t="n">
-        <v>1.29</v>
+        <v>0.99</v>
       </c>
       <c r="I46" t="n">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="J46" t="n">
-        <v>52.56</v>
+        <v>60.52</v>
       </c>
       <c r="K46" t="n">
-        <v>54.35</v>
+        <v>62.17</v>
       </c>
       <c r="L46" t="n">
-        <v>50.6</v>
+        <v>58.42</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6763</v>
+        <v>2990</v>
       </c>
       <c r="O46" t="n">
-        <v>6593</v>
+        <v>6516</v>
       </c>
       <c r="P46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S46" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22.1</v>
+        <v>21.62</v>
       </c>
       <c r="C47" t="n">
-        <v>22.92</v>
+        <v>21.84</v>
       </c>
       <c r="D47" t="n">
-        <v>21.76</v>
+        <v>21.44</v>
       </c>
       <c r="E47" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="F47" t="n">
-        <v>11.5</v>
+        <v>12.7</v>
       </c>
       <c r="G47" t="n">
-        <v>479</v>
+        <v>137</v>
       </c>
       <c r="H47" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="I47" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="J47" t="n">
-        <v>53.58</v>
+        <v>58.13</v>
       </c>
       <c r="K47" t="n">
-        <v>55.95</v>
+        <v>60.32</v>
       </c>
       <c r="L47" t="n">
-        <v>51.48</v>
+        <v>56.76</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>6739</v>
+        <v>5684</v>
       </c>
       <c r="O47" t="n">
-        <v>6582</v>
+        <v>6548</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
         <v>5</v>
       </c>
       <c r="S47" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.45</v>
+        <v>21.96</v>
       </c>
       <c r="C48" t="n">
-        <v>22.62</v>
+        <v>22.41</v>
       </c>
       <c r="D48" t="n">
-        <v>20.83</v>
+        <v>21.77</v>
       </c>
       <c r="E48" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F48" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="G48" t="n">
-        <v>640</v>
+        <v>205</v>
       </c>
       <c r="H48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I48" t="n">
         <v>1.11</v>
       </c>
-      <c r="I48" t="n">
-        <v>0.92</v>
-      </c>
       <c r="J48" t="n">
-        <v>56.35</v>
+        <v>55.95</v>
       </c>
       <c r="K48" t="n">
-        <v>62.61</v>
+        <v>57.92</v>
       </c>
       <c r="L48" t="n">
-        <v>51.88</v>
+        <v>54.15</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6810</v>
+        <v>6619</v>
       </c>
       <c r="O48" t="n">
-        <v>6610</v>
+        <v>6573</v>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q48" t="n">
         <v>6</v>
@@ -3389,67 +3389,6 @@
         <v>5</v>
       </c>
       <c r="S48" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-10-16 12:00:00</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="C49" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="D49" t="n">
-        <v>19.11</v>
-      </c>
-      <c r="E49" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F49" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G49" t="n">
-        <v>279</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J49" t="n">
-        <v>66.39</v>
-      </c>
-      <c r="K49" t="n">
-        <v>68.68000000000001</v>
-      </c>
-      <c r="L49" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>6772</v>
-      </c>
-      <c r="O49" t="n">
-        <v>6571</v>
-      </c>
-      <c r="P49" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>5</v>
-      </c>
-      <c r="R49" t="n">
-        <v>4</v>
-      </c>
-      <c r="S49" t="n">
         <v>60</v>
       </c>
     </row>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,111 +528,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.45</v>
+        <v>17.37</v>
       </c>
       <c r="C2" t="n">
-        <v>17.76</v>
+        <v>17.55</v>
       </c>
       <c r="D2" t="n">
-        <v>17.19</v>
+        <v>17.24</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="F2" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="G2" t="n">
-        <v>210</v>
+        <v>64</v>
       </c>
       <c r="H2" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="I2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>65.79000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K2" t="n">
-        <v>68.27</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>62.48</v>
+        <v>68.52</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6561</v>
+        <v>3570</v>
       </c>
       <c r="O2" t="n">
-        <v>6539</v>
+        <v>6462</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.1</v>
+        <v>17.83</v>
       </c>
       <c r="C3" t="n">
-        <v>17.35</v>
+        <v>18.09</v>
       </c>
       <c r="D3" t="n">
-        <v>16.86</v>
+        <v>17.42</v>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F3" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="G3" t="n">
-        <v>246</v>
+        <v>125</v>
       </c>
       <c r="H3" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="J3" t="n">
-        <v>67.38</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>67.78</v>
+        <v>69.8</v>
       </c>
       <c r="L3" t="n">
-        <v>66.55</v>
+        <v>62.77</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6671</v>
+        <v>4749</v>
       </c>
       <c r="O3" t="n">
-        <v>6536</v>
+        <v>6491</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -644,126 +644,126 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.52</v>
+        <v>17.68</v>
       </c>
       <c r="C4" t="n">
-        <v>17.36</v>
+        <v>17.86</v>
       </c>
       <c r="D4" t="n">
-        <v>16.01</v>
+        <v>17.49</v>
       </c>
       <c r="E4" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G4" t="n">
-        <v>301</v>
+        <v>148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="J4" t="n">
-        <v>69.84</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>72.16</v>
+        <v>67.11</v>
       </c>
       <c r="L4" t="n">
-        <v>66.34999999999999</v>
+        <v>63.11</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6681</v>
+        <v>5962</v>
       </c>
       <c r="O4" t="n">
-        <v>6525</v>
+        <v>6502</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
         <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.55</v>
+        <v>17.45</v>
       </c>
       <c r="C5" t="n">
-        <v>16.32</v>
+        <v>17.76</v>
       </c>
       <c r="D5" t="n">
-        <v>15.05</v>
+        <v>17.19</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F5" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G5" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="H5" t="n">
-        <v>0.43</v>
+        <v>0.68</v>
       </c>
       <c r="I5" t="n">
-        <v>0.36</v>
+        <v>0.62</v>
       </c>
       <c r="J5" t="n">
-        <v>75.25</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>78.77</v>
+        <v>68.27</v>
       </c>
       <c r="L5" t="n">
-        <v>71.11</v>
+        <v>62.48</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6729</v>
+        <v>6561</v>
       </c>
       <c r="O5" t="n">
-        <v>6556</v>
+        <v>6539</v>
       </c>
       <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
         <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>60</v>
@@ -772,233 +772,233 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.04</v>
+        <v>17.1</v>
       </c>
       <c r="C6" t="n">
-        <v>15.26</v>
+        <v>17.35</v>
       </c>
       <c r="D6" t="n">
-        <v>14.82</v>
+        <v>16.86</v>
       </c>
       <c r="E6" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="G6" t="n">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="H6" t="n">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="I6" t="n">
-        <v>0.33</v>
+        <v>0.61</v>
       </c>
       <c r="J6" t="n">
-        <v>77.86</v>
+        <v>67.38</v>
       </c>
       <c r="K6" t="n">
-        <v>80.23</v>
+        <v>67.78</v>
       </c>
       <c r="L6" t="n">
-        <v>75.81</v>
+        <v>66.55</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5708</v>
+        <v>6671</v>
       </c>
       <c r="O6" t="n">
-        <v>6494</v>
+        <v>6536</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.47</v>
+        <v>16.52</v>
       </c>
       <c r="C7" t="n">
-        <v>14.79</v>
+        <v>17.36</v>
       </c>
       <c r="D7" t="n">
-        <v>14.22</v>
+        <v>16.01</v>
       </c>
       <c r="E7" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F7" t="n">
         <v>10.7</v>
       </c>
       <c r="G7" t="n">
-        <v>131</v>
+        <v>301</v>
       </c>
       <c r="H7" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>80.75</v>
+        <v>69.84</v>
       </c>
       <c r="K7" t="n">
-        <v>82.34</v>
+        <v>72.16</v>
       </c>
       <c r="L7" t="n">
-        <v>79.73999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6254</v>
+        <v>6681</v>
       </c>
       <c r="O7" t="n">
-        <v>6491</v>
+        <v>6525</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.34</v>
+        <v>15.55</v>
       </c>
       <c r="C8" t="n">
-        <v>14.4</v>
+        <v>16.32</v>
       </c>
       <c r="D8" t="n">
-        <v>14.25</v>
+        <v>15.05</v>
       </c>
       <c r="E8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F8" t="n">
-        <v>10.3</v>
-      </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>231</v>
       </c>
       <c r="H8" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I8" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="J8" t="n">
-        <v>79.29000000000001</v>
+        <v>75.25</v>
       </c>
       <c r="K8" t="n">
-        <v>80.34999999999999</v>
+        <v>78.77</v>
       </c>
       <c r="L8" t="n">
-        <v>77.13</v>
+        <v>71.11</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3949</v>
+        <v>6729</v>
       </c>
       <c r="O8" t="n">
-        <v>6425</v>
+        <v>6556</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.56</v>
+        <v>15.04</v>
       </c>
       <c r="C9" t="n">
-        <v>14.75</v>
+        <v>15.26</v>
       </c>
       <c r="D9" t="n">
-        <v>14.34</v>
+        <v>14.82</v>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F9" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="H9" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I9" t="n">
         <v>0.33</v>
       </c>
       <c r="J9" t="n">
-        <v>78.20999999999999</v>
+        <v>77.86</v>
       </c>
       <c r="K9" t="n">
-        <v>80.09999999999999</v>
+        <v>80.23</v>
       </c>
       <c r="L9" t="n">
-        <v>75.43000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2449</v>
+        <v>5708</v>
       </c>
       <c r="O9" t="n">
-        <v>6420</v>
+        <v>6494</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -1010,126 +1010,126 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="C10" t="n">
         <v>14.79</v>
       </c>
-      <c r="C10" t="n">
-        <v>14.98</v>
-      </c>
       <c r="D10" t="n">
-        <v>14.63</v>
+        <v>14.22</v>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F10" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H10" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="J10" t="n">
-        <v>77.20999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="K10" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="L10" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="L10" t="n">
-        <v>74.54000000000001</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O10" t="n">
-        <v>6411</v>
+        <v>6491</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.24</v>
+        <v>14.34</v>
       </c>
       <c r="C11" t="n">
-        <v>15.48</v>
+        <v>14.4</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="E11" t="n">
         <v>10.7</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H11" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="I11" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="J11" t="n">
-        <v>74.68000000000001</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>75.5</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>73.42</v>
+        <v>77.13</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O11" t="n">
-        <v>6411</v>
+        <v>6425</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1138,59 +1138,59 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.62</v>
+        <v>14.56</v>
       </c>
       <c r="C12" t="n">
-        <v>15.76</v>
+        <v>14.75</v>
       </c>
       <c r="D12" t="n">
-        <v>15.46</v>
+        <v>14.34</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="F12" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J12" t="n">
-        <v>81.47</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>89.01000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>74.23</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O12" t="n">
-        <v>6402</v>
+        <v>6420</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1199,41 +1199,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.86</v>
+        <v>14.79</v>
       </c>
       <c r="C13" t="n">
-        <v>16.08</v>
+        <v>14.98</v>
       </c>
       <c r="D13" t="n">
-        <v>15.66</v>
+        <v>14.63</v>
       </c>
       <c r="E13" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="F13" t="n">
-        <v>13.7</v>
+        <v>10.4</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="I13" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J13" t="n">
-        <v>87.95999999999999</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>89.39</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>86.37</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1245,13 +1245,13 @@
         <v>6411</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1260,41 +1260,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.22</v>
+        <v>15.24</v>
       </c>
       <c r="C14" t="n">
-        <v>16.35</v>
+        <v>15.48</v>
       </c>
       <c r="D14" t="n">
-        <v>16.12</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="F14" t="n">
-        <v>13.4</v>
+        <v>10.4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="I14" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="J14" t="n">
-        <v>85.42</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>87.15000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="L14" t="n">
-        <v>83.22</v>
+        <v>73.42</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1303,16 +1303,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6405</v>
+        <v>6411</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1321,41 +1321,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.39</v>
+        <v>15.62</v>
       </c>
       <c r="C15" t="n">
-        <v>16.55</v>
+        <v>15.76</v>
       </c>
       <c r="D15" t="n">
-        <v>16.22</v>
+        <v>15.46</v>
       </c>
       <c r="E15" t="n">
-        <v>13.9</v>
+        <v>12.3</v>
       </c>
       <c r="F15" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I15" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J15" t="n">
-        <v>85.56999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="K15" t="n">
-        <v>87.13</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>84.14</v>
+        <v>74.23</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1364,13 +1364,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6417</v>
+        <v>6402</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1382,41 +1382,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.68</v>
+        <v>15.86</v>
       </c>
       <c r="C16" t="n">
-        <v>16.76</v>
+        <v>16.08</v>
       </c>
       <c r="D16" t="n">
-        <v>16.63</v>
+        <v>15.66</v>
       </c>
       <c r="E16" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="I16" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="J16" t="n">
-        <v>84.16</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>86.08</v>
+        <v>89.39</v>
       </c>
       <c r="L16" t="n">
-        <v>81.98</v>
+        <v>86.37</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1428,10 +1428,10 @@
         <v>6411</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1443,41 +1443,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.64</v>
+        <v>16.22</v>
       </c>
       <c r="C17" t="n">
-        <v>16.72</v>
+        <v>16.35</v>
       </c>
       <c r="D17" t="n">
-        <v>16.62</v>
+        <v>16.12</v>
       </c>
       <c r="E17" t="n">
-        <v>14.8</v>
+        <v>13.7</v>
       </c>
       <c r="F17" t="n">
-        <v>14.3</v>
+        <v>13.4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J17" t="n">
-        <v>89.45</v>
+        <v>85.42</v>
       </c>
       <c r="K17" t="n">
-        <v>91.73999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>85.8</v>
+        <v>83.22</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1486,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -1504,41 +1504,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.73</v>
+        <v>16.39</v>
       </c>
       <c r="C18" t="n">
-        <v>16.91</v>
+        <v>16.55</v>
       </c>
       <c r="D18" t="n">
-        <v>16.64</v>
+        <v>16.22</v>
       </c>
       <c r="E18" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="F18" t="n">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J18" t="n">
-        <v>91.16</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>91.98999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="L18" t="n">
-        <v>89.92</v>
+        <v>84.14</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -1565,41 +1565,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.79</v>
+        <v>16.68</v>
       </c>
       <c r="C19" t="n">
-        <v>16.87</v>
+        <v>16.76</v>
       </c>
       <c r="D19" t="n">
-        <v>16.65</v>
+        <v>16.63</v>
       </c>
       <c r="E19" t="n">
-        <v>15.5</v>
+        <v>13.9</v>
       </c>
       <c r="F19" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J19" t="n">
-        <v>92.09999999999999</v>
+        <v>84.16</v>
       </c>
       <c r="K19" t="n">
-        <v>93.45</v>
+        <v>86.08</v>
       </c>
       <c r="L19" t="n">
-        <v>90.81999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1608,13 +1608,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -1626,41 +1626,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.6</v>
+        <v>16.64</v>
       </c>
       <c r="C20" t="n">
-        <v>16.66</v>
+        <v>16.72</v>
       </c>
       <c r="D20" t="n">
-        <v>16.52</v>
+        <v>16.62</v>
       </c>
       <c r="E20" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="F20" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J20" t="n">
-        <v>95.29000000000001</v>
+        <v>89.45</v>
       </c>
       <c r="K20" t="n">
-        <v>96.45999999999999</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>93.84</v>
+        <v>85.8</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1669,16 +1669,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6425</v>
+        <v>6411</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1687,41 +1687,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="C21" t="n">
         <v>16.91</v>
       </c>
-      <c r="C21" t="n">
-        <v>17.19</v>
-      </c>
       <c r="D21" t="n">
-        <v>16.69</v>
+        <v>16.64</v>
       </c>
       <c r="E21" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="F21" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="J21" t="n">
-        <v>94.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="K21" t="n">
-        <v>96.09</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>90.87</v>
+        <v>89.92</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6442</v>
+        <v>6417</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1748,56 +1748,56 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.68</v>
+        <v>16.79</v>
       </c>
       <c r="C22" t="n">
-        <v>18.12</v>
+        <v>16.87</v>
       </c>
       <c r="D22" t="n">
-        <v>17.08</v>
+        <v>16.65</v>
       </c>
       <c r="E22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F22" t="n">
         <v>15.3</v>
       </c>
-      <c r="F22" t="n">
-        <v>14.6</v>
-      </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="I22" t="n">
         <v>0.12</v>
       </c>
       <c r="J22" t="n">
-        <v>86.59</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>93.40000000000001</v>
+        <v>93.45</v>
       </c>
       <c r="L22" t="n">
-        <v>80.54000000000001</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6451</v>
+        <v>6420</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -1809,59 +1809,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.95</v>
+        <v>16.6</v>
       </c>
       <c r="C23" t="n">
-        <v>21.08</v>
+        <v>16.66</v>
       </c>
       <c r="D23" t="n">
-        <v>18.04</v>
+        <v>16.52</v>
       </c>
       <c r="E23" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="F23" t="n">
-        <v>11.6</v>
+        <v>15.6</v>
       </c>
       <c r="G23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.82</v>
+        <v>0.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.41</v>
+        <v>0.06</v>
       </c>
       <c r="J23" t="n">
-        <v>64.73999999999999</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>79.75</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>55.98</v>
+        <v>93.84</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6474</v>
+        <v>6425</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -1870,59 +1870,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21.54</v>
+        <v>16.91</v>
       </c>
       <c r="C24" t="n">
-        <v>21.83</v>
+        <v>17.19</v>
       </c>
       <c r="D24" t="n">
-        <v>21.18</v>
+        <v>16.69</v>
       </c>
       <c r="E24" t="n">
-        <v>11.6</v>
+        <v>15.9</v>
       </c>
       <c r="F24" t="n">
-        <v>10.7</v>
+        <v>15.6</v>
       </c>
       <c r="G24" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.19</v>
+        <v>0.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>53.45</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>58.22</v>
+        <v>96.09</v>
       </c>
       <c r="L24" t="n">
-        <v>49.34</v>
+        <v>90.87</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6485</v>
+        <v>6442</v>
       </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -1931,233 +1931,233 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.02</v>
+        <v>17.68</v>
       </c>
       <c r="C25" t="n">
-        <v>22.16</v>
+        <v>18.12</v>
       </c>
       <c r="D25" t="n">
-        <v>21.88</v>
+        <v>17.08</v>
       </c>
       <c r="E25" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="F25" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="G25" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>1.31</v>
+        <v>0.27</v>
       </c>
       <c r="I25" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="J25" t="n">
-        <v>50.18</v>
+        <v>86.59</v>
       </c>
       <c r="K25" t="n">
-        <v>52.66</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>47.74</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4352</v>
+        <v>685</v>
       </c>
       <c r="O25" t="n">
-        <v>6511</v>
+        <v>6451</v>
       </c>
       <c r="P25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.31</v>
+        <v>19.95</v>
       </c>
       <c r="C26" t="n">
-        <v>22.81</v>
+        <v>21.08</v>
       </c>
       <c r="D26" t="n">
-        <v>22.04</v>
+        <v>18.04</v>
       </c>
       <c r="E26" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="F26" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="G26" t="n">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="H26" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>1.28</v>
+        <v>0.41</v>
       </c>
       <c r="J26" t="n">
-        <v>50.19</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>51.75</v>
+        <v>79.75</v>
       </c>
       <c r="L26" t="n">
-        <v>47.76</v>
+        <v>55.98</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5406</v>
+        <v>1926</v>
       </c>
       <c r="O26" t="n">
-        <v>6539</v>
+        <v>6474</v>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22.68</v>
+        <v>21.54</v>
       </c>
       <c r="C27" t="n">
-        <v>23.1</v>
+        <v>21.83</v>
       </c>
       <c r="D27" t="n">
-        <v>22.11</v>
+        <v>21.18</v>
       </c>
       <c r="E27" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F27" t="n">
         <v>10.7</v>
       </c>
       <c r="G27" t="n">
-        <v>384</v>
+        <v>44</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="I27" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="J27" t="n">
-        <v>48.82</v>
+        <v>53.45</v>
       </c>
       <c r="K27" t="n">
-        <v>51.28</v>
+        <v>58.22</v>
       </c>
       <c r="L27" t="n">
-        <v>47.13</v>
+        <v>49.34</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6743</v>
+        <v>2410</v>
       </c>
       <c r="O27" t="n">
-        <v>6573</v>
+        <v>6485</v>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.01</v>
+        <v>22.02</v>
       </c>
       <c r="C28" t="n">
-        <v>22.58</v>
+        <v>22.16</v>
       </c>
       <c r="D28" t="n">
-        <v>21.62</v>
+        <v>21.88</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F28" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="G28" t="n">
-        <v>452</v>
+        <v>111</v>
       </c>
       <c r="H28" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="J28" t="n">
-        <v>49.71</v>
+        <v>50.18</v>
       </c>
       <c r="K28" t="n">
-        <v>51.65</v>
+        <v>52.66</v>
       </c>
       <c r="L28" t="n">
-        <v>46.69</v>
+        <v>47.74</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6767</v>
+        <v>4352</v>
       </c>
       <c r="O28" t="n">
-        <v>6576</v>
+        <v>6511</v>
       </c>
       <c r="P28" t="n">
         <v>6</v>
@@ -2169,56 +2169,56 @@
         <v>6</v>
       </c>
       <c r="S28" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.59</v>
+        <v>22.31</v>
       </c>
       <c r="C29" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D29" t="n">
-        <v>20.76</v>
+        <v>22.04</v>
       </c>
       <c r="E29" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="F29" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="G29" t="n">
-        <v>564</v>
+        <v>198</v>
       </c>
       <c r="H29" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="I29" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="J29" t="n">
-        <v>51.87</v>
+        <v>50.19</v>
       </c>
       <c r="K29" t="n">
-        <v>56.03</v>
+        <v>51.75</v>
       </c>
       <c r="L29" t="n">
-        <v>45.92</v>
+        <v>47.76</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6796</v>
+        <v>5406</v>
       </c>
       <c r="O29" t="n">
-        <v>6599</v>
+        <v>6539</v>
       </c>
       <c r="P29" t="n">
         <v>6</v>
@@ -2227,68 +2227,68 @@
         <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20.19</v>
+        <v>22.68</v>
       </c>
       <c r="C30" t="n">
-        <v>20.64</v>
+        <v>23.1</v>
       </c>
       <c r="D30" t="n">
-        <v>19.53</v>
+        <v>22.11</v>
       </c>
       <c r="E30" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F30" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="G30" t="n">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="H30" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="I30" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="J30" t="n">
-        <v>55.29</v>
+        <v>48.82</v>
       </c>
       <c r="K30" t="n">
-        <v>57.87</v>
+        <v>51.28</v>
       </c>
       <c r="L30" t="n">
-        <v>52.99</v>
+        <v>47.13</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6767</v>
+        <v>6743</v>
       </c>
       <c r="O30" t="n">
-        <v>6576</v>
+        <v>6573</v>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
+        <v>7</v>
+      </c>
+      <c r="R30" t="n">
         <v>6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>5</v>
       </c>
       <c r="S30" t="n">
         <v>60</v>
@@ -2297,297 +2297,297 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18.89</v>
+        <v>22.01</v>
       </c>
       <c r="C31" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D31" t="n">
-        <v>18.08</v>
+        <v>21.62</v>
       </c>
       <c r="E31" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G31" t="n">
-        <v>212</v>
+        <v>452</v>
       </c>
       <c r="H31" t="n">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="I31" t="n">
-        <v>0.35</v>
+        <v>1.27</v>
       </c>
       <c r="J31" t="n">
-        <v>69.7</v>
+        <v>49.71</v>
       </c>
       <c r="K31" t="n">
-        <v>82.87</v>
+        <v>51.65</v>
       </c>
       <c r="L31" t="n">
-        <v>57.89</v>
+        <v>46.69</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6691</v>
+        <v>6767</v>
       </c>
       <c r="O31" t="n">
-        <v>6514</v>
+        <v>6576</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.5</v>
+        <v>21.59</v>
       </c>
       <c r="C32" t="n">
-        <v>17.9</v>
+        <v>22.58</v>
       </c>
       <c r="D32" t="n">
-        <v>17.26</v>
+        <v>20.76</v>
       </c>
       <c r="E32" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="F32" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="G32" t="n">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="H32" t="n">
-        <v>0.31</v>
+        <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.25</v>
+        <v>1.07</v>
       </c>
       <c r="J32" t="n">
-        <v>84.14</v>
+        <v>51.87</v>
       </c>
       <c r="K32" t="n">
-        <v>87.05</v>
+        <v>56.03</v>
       </c>
       <c r="L32" t="n">
-        <v>79.48999999999999</v>
+        <v>45.92</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3786</v>
+        <v>6796</v>
       </c>
       <c r="O32" t="n">
-        <v>6422</v>
+        <v>6599</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.02</v>
+        <v>20.19</v>
       </c>
       <c r="C33" t="n">
-        <v>17.27</v>
+        <v>20.64</v>
       </c>
       <c r="D33" t="n">
-        <v>16.92</v>
+        <v>19.53</v>
       </c>
       <c r="E33" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F33" t="n">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H33" t="n">
-        <v>0.25</v>
+        <v>1.05</v>
       </c>
       <c r="I33" t="n">
-        <v>0.21</v>
+        <v>0.95</v>
       </c>
       <c r="J33" t="n">
-        <v>86.8</v>
+        <v>55.29</v>
       </c>
       <c r="K33" t="n">
-        <v>88.91</v>
+        <v>57.87</v>
       </c>
       <c r="L33" t="n">
-        <v>81.98999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1246</v>
+        <v>6767</v>
       </c>
       <c r="O33" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.89</v>
+        <v>18.89</v>
       </c>
       <c r="C34" t="n">
-        <v>17.03</v>
+        <v>19.62</v>
       </c>
       <c r="D34" t="n">
-        <v>16.78</v>
+        <v>18.08</v>
       </c>
       <c r="E34" t="n">
-        <v>14.9</v>
+        <v>13.1</v>
       </c>
       <c r="F34" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H34" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="I34" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="J34" t="n">
-        <v>88.48999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K34" t="n">
-        <v>90.31</v>
+        <v>82.87</v>
       </c>
       <c r="L34" t="n">
-        <v>85.76000000000001</v>
+        <v>57.89</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="O34" t="n">
-        <v>6417</v>
+        <v>6514</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.13</v>
+        <v>17.5</v>
       </c>
       <c r="C35" t="n">
-        <v>17.32</v>
+        <v>17.9</v>
       </c>
       <c r="D35" t="n">
-        <v>16.89</v>
+        <v>17.26</v>
       </c>
       <c r="E35" t="n">
         <v>14.7</v>
       </c>
       <c r="F35" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H35" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="I35" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J35" t="n">
-        <v>85.90000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="K35" t="n">
-        <v>88.63</v>
+        <v>87.05</v>
       </c>
       <c r="L35" t="n">
-        <v>83.40000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="O35" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
         <v>2</v>
@@ -2602,47 +2602,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.01</v>
+        <v>17.02</v>
       </c>
       <c r="C36" t="n">
-        <v>17.08</v>
+        <v>17.27</v>
       </c>
       <c r="D36" t="n">
-        <v>16.93</v>
+        <v>16.92</v>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F36" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="I36" t="n">
         <v>0.21</v>
       </c>
       <c r="J36" t="n">
-        <v>88.16</v>
+        <v>86.8</v>
       </c>
       <c r="K36" t="n">
-        <v>88.7</v>
+        <v>88.91</v>
       </c>
       <c r="L36" t="n">
-        <v>87.34999999999999</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="O36" t="n">
         <v>6414</v>
@@ -2651,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -2663,41 +2663,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.07</v>
+        <v>16.89</v>
       </c>
       <c r="C37" t="n">
-        <v>17.29</v>
+        <v>17.03</v>
       </c>
       <c r="D37" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F37" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J37" t="n">
-        <v>88.06999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>89.45999999999999</v>
+        <v>90.31</v>
       </c>
       <c r="L37" t="n">
-        <v>85.97</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2724,41 +2724,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.44</v>
+        <v>17.13</v>
       </c>
       <c r="C38" t="n">
-        <v>17.52</v>
+        <v>17.32</v>
       </c>
       <c r="D38" t="n">
-        <v>17.31</v>
+        <v>16.89</v>
       </c>
       <c r="E38" t="n">
         <v>14.7</v>
       </c>
       <c r="F38" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="I38" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="J38" t="n">
-        <v>84.31999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>85.27</v>
+        <v>88.63</v>
       </c>
       <c r="L38" t="n">
-        <v>82.56999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2767,16 +2767,16 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -2785,41 +2785,41 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.22</v>
+        <v>17.01</v>
       </c>
       <c r="C39" t="n">
-        <v>17.34</v>
+        <v>17.08</v>
       </c>
       <c r="D39" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E39" t="n">
         <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J39" t="n">
-        <v>87.37</v>
+        <v>88.16</v>
       </c>
       <c r="K39" t="n">
-        <v>88.34999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="L39" t="n">
-        <v>86.23</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6425</v>
+        <v>6414</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -2846,41 +2846,41 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.38</v>
+        <v>17.07</v>
       </c>
       <c r="C40" t="n">
-        <v>17.5</v>
+        <v>17.29</v>
       </c>
       <c r="D40" t="n">
-        <v>17.22</v>
+        <v>16.93</v>
       </c>
       <c r="E40" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I40" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
-        <v>87.89</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>89.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>87.03</v>
+        <v>85.97</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -2907,41 +2907,41 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.51</v>
+        <v>17.44</v>
       </c>
       <c r="C41" t="n">
-        <v>17.64</v>
+        <v>17.52</v>
       </c>
       <c r="D41" t="n">
-        <v>17.34</v>
+        <v>17.31</v>
       </c>
       <c r="E41" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="F41" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="I41" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="J41" t="n">
-        <v>88.95</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>90.3</v>
+        <v>85.27</v>
       </c>
       <c r="L41" t="n">
-        <v>87.78</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2950,16 +2950,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6437</v>
+        <v>6417</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -2968,20 +2968,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.73</v>
+        <v>17.22</v>
       </c>
       <c r="C42" t="n">
-        <v>18.06</v>
+        <v>17.34</v>
       </c>
       <c r="D42" t="n">
-        <v>17.42</v>
+        <v>17.11</v>
       </c>
       <c r="E42" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
         <v>14.9</v>
@@ -2990,19 +2990,19 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J42" t="n">
-        <v>85.27</v>
+        <v>87.37</v>
       </c>
       <c r="K42" t="n">
-        <v>88.19</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>81.95</v>
+        <v>86.23</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3011,13 +3011,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -3029,41 +3029,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.36</v>
+        <v>17.38</v>
       </c>
       <c r="C43" t="n">
-        <v>18.45</v>
+        <v>17.5</v>
       </c>
       <c r="D43" t="n">
-        <v>18.19</v>
+        <v>17.22</v>
       </c>
       <c r="E43" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="F43" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="I43" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="J43" t="n">
-        <v>80.73</v>
+        <v>87.89</v>
       </c>
       <c r="K43" t="n">
-        <v>81.93000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="L43" t="n">
-        <v>79.83</v>
+        <v>87.03</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3072,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6471</v>
+        <v>6408</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3090,41 +3090,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.81</v>
+        <v>17.51</v>
       </c>
       <c r="C44" t="n">
-        <v>19.07</v>
+        <v>17.64</v>
       </c>
       <c r="D44" t="n">
-        <v>18.51</v>
+        <v>17.34</v>
       </c>
       <c r="E44" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="F44" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="I44" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="J44" t="n">
-        <v>76.59999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="K44" t="n">
-        <v>79.87</v>
+        <v>90.3</v>
       </c>
       <c r="L44" t="n">
-        <v>74.01000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3133,16 +3133,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6482</v>
+        <v>6437</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3151,41 +3151,41 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.81</v>
+        <v>17.73</v>
       </c>
       <c r="C45" t="n">
-        <v>20.67</v>
+        <v>18.06</v>
       </c>
       <c r="D45" t="n">
-        <v>18.96</v>
+        <v>17.42</v>
       </c>
       <c r="E45" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="F45" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="I45" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="J45" t="n">
-        <v>69.16</v>
+        <v>85.27</v>
       </c>
       <c r="K45" t="n">
-        <v>75.04000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="L45" t="n">
-        <v>63.43</v>
+        <v>81.95</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3194,16 +3194,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6496</v>
+        <v>6457</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3212,184 +3212,245 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>21.22</v>
+        <v>18.36</v>
       </c>
       <c r="C46" t="n">
-        <v>21.6</v>
+        <v>18.45</v>
       </c>
       <c r="D46" t="n">
-        <v>20.76</v>
+        <v>18.19</v>
       </c>
       <c r="E46" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="F46" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="G46" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="I46" t="n">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
       <c r="J46" t="n">
-        <v>60.52</v>
+        <v>80.73</v>
       </c>
       <c r="K46" t="n">
-        <v>62.17</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>58.42</v>
+        <v>79.83</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6516</v>
+        <v>6471</v>
       </c>
       <c r="P46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 17:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.62</v>
+        <v>18.81</v>
       </c>
       <c r="C47" t="n">
-        <v>21.84</v>
+        <v>19.07</v>
       </c>
       <c r="D47" t="n">
-        <v>21.44</v>
+        <v>18.51</v>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F47" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="G47" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="I47" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="J47" t="n">
-        <v>58.13</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>60.32</v>
+        <v>79.87</v>
       </c>
       <c r="L47" t="n">
-        <v>56.76</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6548</v>
+        <v>6482</v>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 19:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.96</v>
+        <v>19.81</v>
       </c>
       <c r="C48" t="n">
-        <v>22.41</v>
+        <v>20.67</v>
       </c>
       <c r="D48" t="n">
-        <v>21.77</v>
+        <v>18.96</v>
       </c>
       <c r="E48" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="F48" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="G48" t="n">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>1.15</v>
+        <v>0.71</v>
       </c>
       <c r="I48" t="n">
-        <v>1.11</v>
+        <v>0.54</v>
       </c>
       <c r="J48" t="n">
-        <v>55.95</v>
+        <v>69.16</v>
       </c>
       <c r="K48" t="n">
-        <v>57.92</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>54.15</v>
+        <v>63.43</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6619</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6573</v>
+        <v>6496</v>
       </c>
       <c r="P48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="C49" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="E49" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13</v>
+      </c>
+      <c r="G49" t="n">
+        <v>73</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J49" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="K49" t="n">
+        <v>62.17</v>
+      </c>
+      <c r="L49" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2990</v>
+      </c>
+      <c r="O49" t="n">
+        <v>6516</v>
+      </c>
+      <c r="P49" t="n">
         <v>5</v>
       </c>
-      <c r="S48" t="n">
-        <v>60</v>
+      <c r="Q49" t="n">
+        <v>5</v>
+      </c>
+      <c r="R49" t="n">
+        <v>5</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,59 +528,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.37</v>
+        <v>16.22</v>
       </c>
       <c r="C2" t="n">
-        <v>17.55</v>
+        <v>16.42</v>
       </c>
       <c r="D2" t="n">
-        <v>17.24</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8</v>
+        <v>12.8</v>
       </c>
       <c r="F2" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="G2" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.59</v>
+        <v>0.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="J2" t="n">
-        <v>70.2</v>
+        <v>80.67</v>
       </c>
       <c r="K2" t="n">
-        <v>71.43000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="L2" t="n">
-        <v>68.52</v>
+        <v>78.12</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3570</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -589,172 +589,172 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.83</v>
+        <v>16.77</v>
       </c>
       <c r="C3" t="n">
-        <v>18.09</v>
+        <v>17.13</v>
       </c>
       <c r="D3" t="n">
-        <v>17.42</v>
+        <v>16.4</v>
       </c>
       <c r="E3" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="F3" t="n">
-        <v>10.6</v>
+        <v>11.9</v>
       </c>
       <c r="G3" t="n">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="J3" t="n">
-        <v>66.04000000000001</v>
+        <v>75.39</v>
       </c>
       <c r="K3" t="n">
-        <v>69.8</v>
+        <v>78.58</v>
       </c>
       <c r="L3" t="n">
-        <v>62.77</v>
+        <v>72.19</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4749</v>
+        <v>1164</v>
       </c>
       <c r="O3" t="n">
-        <v>6491</v>
+        <v>6431</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.68</v>
+        <v>17.34</v>
       </c>
       <c r="C4" t="n">
-        <v>17.86</v>
+        <v>17.55</v>
       </c>
       <c r="D4" t="n">
-        <v>17.49</v>
+        <v>17.15</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="F4" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="G4" t="n">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="J4" t="n">
-        <v>65.15000000000001</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>67.11</v>
+        <v>72.41</v>
       </c>
       <c r="L4" t="n">
-        <v>63.11</v>
+        <v>68.52</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5962</v>
+        <v>3144</v>
       </c>
       <c r="O4" t="n">
-        <v>6502</v>
+        <v>6459</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.45</v>
+        <v>17.83</v>
       </c>
       <c r="C5" t="n">
-        <v>17.76</v>
+        <v>18.09</v>
       </c>
       <c r="D5" t="n">
-        <v>17.19</v>
+        <v>17.42</v>
       </c>
       <c r="E5" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F5" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="G5" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
-        <v>65.79000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>68.27</v>
+        <v>69.8</v>
       </c>
       <c r="L5" t="n">
-        <v>62.48</v>
+        <v>62.77</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6561</v>
+        <v>4749</v>
       </c>
       <c r="O5" t="n">
-        <v>6539</v>
+        <v>6491</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
@@ -766,56 +766,56 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.1</v>
+        <v>17.68</v>
       </c>
       <c r="C6" t="n">
-        <v>17.35</v>
+        <v>17.86</v>
       </c>
       <c r="D6" t="n">
-        <v>16.86</v>
+        <v>17.49</v>
       </c>
       <c r="E6" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>246</v>
+        <v>148</v>
       </c>
       <c r="H6" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="J6" t="n">
-        <v>67.38</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>67.78</v>
+        <v>67.11</v>
       </c>
       <c r="L6" t="n">
-        <v>66.55</v>
+        <v>63.11</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6671</v>
+        <v>5962</v>
       </c>
       <c r="O6" t="n">
-        <v>6536</v>
+        <v>6502</v>
       </c>
       <c r="P6" t="n">
         <v>4</v>
@@ -824,62 +824,62 @@
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.52</v>
+        <v>17.45</v>
       </c>
       <c r="C7" t="n">
-        <v>17.36</v>
+        <v>17.76</v>
       </c>
       <c r="D7" t="n">
-        <v>16.01</v>
+        <v>17.19</v>
       </c>
       <c r="E7" t="n">
         <v>10.9</v>
       </c>
       <c r="F7" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G7" t="n">
-        <v>301</v>
+        <v>210</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="J7" t="n">
-        <v>69.84</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>72.16</v>
+        <v>68.27</v>
       </c>
       <c r="L7" t="n">
-        <v>66.34999999999999</v>
+        <v>62.48</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6681</v>
+        <v>6561</v>
       </c>
       <c r="O7" t="n">
-        <v>6525</v>
+        <v>6539</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
         <v>4</v>
@@ -894,59 +894,59 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.55</v>
+        <v>17.1</v>
       </c>
       <c r="C8" t="n">
-        <v>16.32</v>
+        <v>17.35</v>
       </c>
       <c r="D8" t="n">
-        <v>15.05</v>
+        <v>16.86</v>
       </c>
       <c r="E8" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F8" t="n">
         <v>10.7</v>
       </c>
       <c r="G8" t="n">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H8" t="n">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="I8" t="n">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
       <c r="J8" t="n">
-        <v>75.25</v>
+        <v>67.38</v>
       </c>
       <c r="K8" t="n">
-        <v>78.77</v>
+        <v>67.78</v>
       </c>
       <c r="L8" t="n">
-        <v>71.11</v>
+        <v>66.55</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6729</v>
+        <v>6671</v>
       </c>
       <c r="O8" t="n">
-        <v>6556</v>
+        <v>6536</v>
       </c>
       <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
         <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>60</v>
@@ -955,78 +955,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.04</v>
+        <v>16.52</v>
       </c>
       <c r="C9" t="n">
-        <v>15.26</v>
+        <v>17.36</v>
       </c>
       <c r="D9" t="n">
-        <v>14.82</v>
+        <v>16.01</v>
       </c>
       <c r="E9" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="G9" t="n">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="H9" t="n">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>77.86</v>
+        <v>69.84</v>
       </c>
       <c r="K9" t="n">
-        <v>80.23</v>
+        <v>72.16</v>
       </c>
       <c r="L9" t="n">
-        <v>75.81</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5708</v>
+        <v>6681</v>
       </c>
       <c r="O9" t="n">
-        <v>6494</v>
+        <v>6525</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.47</v>
+        <v>15.55</v>
       </c>
       <c r="C10" t="n">
-        <v>14.79</v>
+        <v>16.32</v>
       </c>
       <c r="D10" t="n">
-        <v>14.22</v>
+        <v>15.05</v>
       </c>
       <c r="E10" t="n">
         <v>11.1</v>
@@ -1035,92 +1035,92 @@
         <v>10.7</v>
       </c>
       <c r="G10" t="n">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="I10" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="J10" t="n">
-        <v>80.75</v>
+        <v>75.25</v>
       </c>
       <c r="K10" t="n">
-        <v>82.34</v>
+        <v>78.77</v>
       </c>
       <c r="L10" t="n">
-        <v>79.73999999999999</v>
+        <v>71.11</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6254</v>
+        <v>6729</v>
       </c>
       <c r="O10" t="n">
-        <v>6491</v>
+        <v>6556</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.34</v>
+        <v>15.04</v>
       </c>
       <c r="C11" t="n">
-        <v>14.4</v>
+        <v>15.26</v>
       </c>
       <c r="D11" t="n">
-        <v>14.25</v>
+        <v>14.82</v>
       </c>
       <c r="E11" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="F11" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="H11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.33</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.32</v>
-      </c>
       <c r="J11" t="n">
-        <v>79.29000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="K11" t="n">
-        <v>80.34999999999999</v>
+        <v>80.23</v>
       </c>
       <c r="L11" t="n">
-        <v>77.13</v>
+        <v>75.81</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3949</v>
+        <v>5708</v>
       </c>
       <c r="O11" t="n">
-        <v>6425</v>
+        <v>6494</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
@@ -1132,56 +1132,56 @@
         <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.56</v>
+        <v>14.47</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75</v>
+        <v>14.79</v>
       </c>
       <c r="D12" t="n">
-        <v>14.34</v>
+        <v>14.22</v>
       </c>
       <c r="E12" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F12" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="H12" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="I12" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="J12" t="n">
-        <v>78.20999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="K12" t="n">
-        <v>80.09999999999999</v>
+        <v>82.34</v>
       </c>
       <c r="L12" t="n">
-        <v>75.43000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2449</v>
+        <v>6254</v>
       </c>
       <c r="O12" t="n">
-        <v>6420</v>
+        <v>6491</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
@@ -1193,62 +1193,62 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.79</v>
+        <v>14.34</v>
       </c>
       <c r="C13" t="n">
-        <v>14.98</v>
+        <v>14.4</v>
       </c>
       <c r="D13" t="n">
-        <v>14.63</v>
+        <v>14.25</v>
       </c>
       <c r="E13" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F13" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J13" t="n">
-        <v>77.20999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>79.73999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>74.54000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O13" t="n">
-        <v>6411</v>
+        <v>6425</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>2</v>
@@ -1260,59 +1260,59 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.24</v>
+        <v>14.56</v>
       </c>
       <c r="C14" t="n">
-        <v>15.48</v>
+        <v>14.75</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>14.34</v>
       </c>
       <c r="E14" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F14" t="n">
         <v>10.4</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="I14" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="J14" t="n">
-        <v>74.68000000000001</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>75.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>73.42</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O14" t="n">
-        <v>6411</v>
+        <v>6420</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1321,41 +1321,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.62</v>
+        <v>14.79</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76</v>
+        <v>14.98</v>
       </c>
       <c r="D15" t="n">
-        <v>15.46</v>
+        <v>14.63</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="F15" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I15" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J15" t="n">
-        <v>81.47</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>89.01000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>74.23</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6402</v>
+        <v>6411</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -1373,7 +1373,7 @@
         <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1382,41 +1382,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.86</v>
+        <v>15.24</v>
       </c>
       <c r="C16" t="n">
-        <v>16.08</v>
+        <v>15.48</v>
       </c>
       <c r="D16" t="n">
-        <v>15.66</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>13.8</v>
+        <v>10.7</v>
       </c>
       <c r="F16" t="n">
-        <v>13.7</v>
+        <v>10.4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="I16" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="J16" t="n">
-        <v>87.95999999999999</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>89.39</v>
+        <v>75.5</v>
       </c>
       <c r="L16" t="n">
-        <v>86.37</v>
+        <v>73.42</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1428,13 +1428,13 @@
         <v>6411</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1443,41 +1443,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.22</v>
+        <v>15.62</v>
       </c>
       <c r="C17" t="n">
-        <v>16.35</v>
+        <v>15.76</v>
       </c>
       <c r="D17" t="n">
-        <v>16.12</v>
+        <v>15.46</v>
       </c>
       <c r="E17" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="F17" t="n">
-        <v>13.4</v>
+        <v>10.8</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J17" t="n">
-        <v>85.42</v>
+        <v>81.47</v>
       </c>
       <c r="K17" t="n">
-        <v>87.15000000000001</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>83.22</v>
+        <v>74.23</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1486,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6405</v>
+        <v>6402</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -1504,41 +1504,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.39</v>
+        <v>15.86</v>
       </c>
       <c r="C18" t="n">
-        <v>16.55</v>
+        <v>16.08</v>
       </c>
       <c r="D18" t="n">
-        <v>16.22</v>
+        <v>15.66</v>
       </c>
       <c r="E18" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F18" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J18" t="n">
-        <v>85.56999999999999</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>87.13</v>
+        <v>89.39</v>
       </c>
       <c r="L18" t="n">
-        <v>84.14</v>
+        <v>86.37</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1547,13 +1547,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -1565,41 +1565,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.68</v>
+        <v>16.22</v>
       </c>
       <c r="C19" t="n">
-        <v>16.76</v>
+        <v>16.35</v>
       </c>
       <c r="D19" t="n">
-        <v>16.63</v>
+        <v>16.12</v>
       </c>
       <c r="E19" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="F19" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="I19" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="J19" t="n">
-        <v>84.16</v>
+        <v>85.42</v>
       </c>
       <c r="K19" t="n">
-        <v>86.08</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>81.98</v>
+        <v>83.22</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
@@ -1626,41 +1626,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.64</v>
+        <v>16.39</v>
       </c>
       <c r="C20" t="n">
-        <v>16.72</v>
+        <v>16.55</v>
       </c>
       <c r="D20" t="n">
-        <v>16.62</v>
+        <v>16.22</v>
       </c>
       <c r="E20" t="n">
-        <v>14.8</v>
+        <v>13.9</v>
       </c>
       <c r="F20" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J20" t="n">
-        <v>89.45</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>91.73999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="L20" t="n">
-        <v>85.8</v>
+        <v>84.14</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1669,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6411</v>
+        <v>6417</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -1687,41 +1687,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.73</v>
+        <v>16.68</v>
       </c>
       <c r="C21" t="n">
-        <v>16.91</v>
+        <v>16.76</v>
       </c>
       <c r="D21" t="n">
-        <v>16.64</v>
+        <v>16.63</v>
       </c>
       <c r="E21" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="F21" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="I21" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="J21" t="n">
-        <v>91.16</v>
+        <v>84.16</v>
       </c>
       <c r="K21" t="n">
-        <v>91.98999999999999</v>
+        <v>86.08</v>
       </c>
       <c r="L21" t="n">
-        <v>89.92</v>
+        <v>81.98</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -1748,41 +1748,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="C22" t="n">
-        <v>16.87</v>
+        <v>16.72</v>
       </c>
       <c r="D22" t="n">
-        <v>16.65</v>
+        <v>16.62</v>
       </c>
       <c r="E22" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="F22" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="J22" t="n">
-        <v>92.09999999999999</v>
+        <v>89.45</v>
       </c>
       <c r="K22" t="n">
-        <v>93.45</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>90.81999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -1809,41 +1809,41 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.6</v>
+        <v>16.73</v>
       </c>
       <c r="C23" t="n">
-        <v>16.66</v>
+        <v>16.91</v>
       </c>
       <c r="D23" t="n">
-        <v>16.52</v>
+        <v>16.64</v>
       </c>
       <c r="E23" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="F23" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J23" t="n">
-        <v>95.29000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="K23" t="n">
-        <v>96.45999999999999</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>93.84</v>
+        <v>89.92</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1852,16 +1852,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -1870,41 +1870,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.91</v>
+        <v>16.79</v>
       </c>
       <c r="C24" t="n">
-        <v>17.19</v>
+        <v>16.87</v>
       </c>
       <c r="D24" t="n">
-        <v>16.69</v>
+        <v>16.65</v>
       </c>
       <c r="E24" t="n">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="F24" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J24" t="n">
-        <v>94.18000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>96.09</v>
+        <v>93.45</v>
       </c>
       <c r="L24" t="n">
-        <v>90.87</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6442</v>
+        <v>6420</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -1931,59 +1931,59 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.68</v>
+        <v>16.6</v>
       </c>
       <c r="C25" t="n">
-        <v>18.12</v>
+        <v>16.66</v>
       </c>
       <c r="D25" t="n">
-        <v>17.08</v>
+        <v>16.52</v>
       </c>
       <c r="E25" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="F25" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="I25" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="J25" t="n">
-        <v>86.59</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>93.40000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>80.54000000000001</v>
+        <v>93.84</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6451</v>
+        <v>6425</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -1992,59 +1992,59 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.95</v>
+        <v>16.91</v>
       </c>
       <c r="C26" t="n">
-        <v>21.08</v>
+        <v>17.19</v>
       </c>
       <c r="D26" t="n">
-        <v>18.04</v>
+        <v>16.69</v>
       </c>
       <c r="E26" t="n">
-        <v>12.9</v>
+        <v>15.9</v>
       </c>
       <c r="F26" t="n">
-        <v>11.6</v>
+        <v>15.6</v>
       </c>
       <c r="G26" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.82</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>0.41</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>64.73999999999999</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>79.75</v>
+        <v>96.09</v>
       </c>
       <c r="L26" t="n">
-        <v>55.98</v>
+        <v>90.87</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6474</v>
+        <v>6442</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2053,59 +2053,59 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.54</v>
+        <v>17.68</v>
       </c>
       <c r="C27" t="n">
-        <v>21.83</v>
+        <v>18.12</v>
       </c>
       <c r="D27" t="n">
-        <v>21.18</v>
+        <v>17.08</v>
       </c>
       <c r="E27" t="n">
-        <v>11.6</v>
+        <v>15.3</v>
       </c>
       <c r="F27" t="n">
-        <v>10.7</v>
+        <v>14.6</v>
       </c>
       <c r="G27" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>1.19</v>
+        <v>0.27</v>
       </c>
       <c r="I27" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="J27" t="n">
-        <v>53.45</v>
+        <v>86.59</v>
       </c>
       <c r="K27" t="n">
-        <v>58.22</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>49.34</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2410</v>
+        <v>685</v>
       </c>
       <c r="O27" t="n">
-        <v>6485</v>
+        <v>6451</v>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2114,175 +2114,175 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.02</v>
+        <v>19.95</v>
       </c>
       <c r="C28" t="n">
-        <v>22.16</v>
+        <v>21.08</v>
       </c>
       <c r="D28" t="n">
-        <v>21.88</v>
+        <v>18.04</v>
       </c>
       <c r="E28" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="F28" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="G28" t="n">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H28" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>1.24</v>
+        <v>0.41</v>
       </c>
       <c r="J28" t="n">
-        <v>50.18</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>52.66</v>
+        <v>79.75</v>
       </c>
       <c r="L28" t="n">
-        <v>47.74</v>
+        <v>55.98</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4352</v>
+        <v>1926</v>
       </c>
       <c r="O28" t="n">
-        <v>6511</v>
+        <v>6474</v>
       </c>
       <c r="P28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22.31</v>
+        <v>21.54</v>
       </c>
       <c r="C29" t="n">
-        <v>22.81</v>
+        <v>21.83</v>
       </c>
       <c r="D29" t="n">
-        <v>22.04</v>
+        <v>21.18</v>
       </c>
       <c r="E29" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F29" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="G29" t="n">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H29" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="I29" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="J29" t="n">
-        <v>50.19</v>
+        <v>53.45</v>
       </c>
       <c r="K29" t="n">
-        <v>51.75</v>
+        <v>58.22</v>
       </c>
       <c r="L29" t="n">
-        <v>47.76</v>
+        <v>49.34</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5406</v>
+        <v>2410</v>
       </c>
       <c r="O29" t="n">
-        <v>6539</v>
+        <v>6485</v>
       </c>
       <c r="P29" t="n">
         <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.68</v>
+        <v>22.02</v>
       </c>
       <c r="C30" t="n">
-        <v>23.1</v>
+        <v>22.16</v>
       </c>
       <c r="D30" t="n">
-        <v>22.11</v>
+        <v>21.88</v>
       </c>
       <c r="E30" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="F30" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G30" t="n">
-        <v>384</v>
+        <v>111</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="I30" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="J30" t="n">
-        <v>48.82</v>
+        <v>50.18</v>
       </c>
       <c r="K30" t="n">
-        <v>51.28</v>
+        <v>52.66</v>
       </c>
       <c r="L30" t="n">
-        <v>47.13</v>
+        <v>47.74</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6743</v>
+        <v>4352</v>
       </c>
       <c r="O30" t="n">
-        <v>6573</v>
+        <v>6511</v>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
         <v>7</v>
@@ -2291,56 +2291,56 @@
         <v>6</v>
       </c>
       <c r="S30" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.01</v>
+        <v>22.31</v>
       </c>
       <c r="C31" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D31" t="n">
-        <v>21.62</v>
+        <v>22.04</v>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F31" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="G31" t="n">
-        <v>452</v>
+        <v>198</v>
       </c>
       <c r="H31" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I31" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="J31" t="n">
-        <v>49.71</v>
+        <v>50.19</v>
       </c>
       <c r="K31" t="n">
-        <v>51.65</v>
+        <v>51.75</v>
       </c>
       <c r="L31" t="n">
-        <v>46.69</v>
+        <v>47.76</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6767</v>
+        <v>5406</v>
       </c>
       <c r="O31" t="n">
-        <v>6576</v>
+        <v>6539</v>
       </c>
       <c r="P31" t="n">
         <v>6</v>
@@ -2352,65 +2352,65 @@
         <v>6</v>
       </c>
       <c r="S31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21.59</v>
+        <v>22.68</v>
       </c>
       <c r="C32" t="n">
-        <v>22.58</v>
+        <v>23.1</v>
       </c>
       <c r="D32" t="n">
-        <v>20.76</v>
+        <v>22.11</v>
       </c>
       <c r="E32" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F32" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G32" t="n">
-        <v>564</v>
+        <v>384</v>
       </c>
       <c r="H32" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="I32" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="J32" t="n">
-        <v>51.87</v>
+        <v>48.82</v>
       </c>
       <c r="K32" t="n">
-        <v>56.03</v>
+        <v>51.28</v>
       </c>
       <c r="L32" t="n">
-        <v>45.92</v>
+        <v>47.13</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6796</v>
+        <v>6743</v>
       </c>
       <c r="O32" t="n">
-        <v>6599</v>
+        <v>6573</v>
       </c>
       <c r="P32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q32" t="n">
         <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S32" t="n">
         <v>60</v>
@@ -2419,41 +2419,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.19</v>
+        <v>22.01</v>
       </c>
       <c r="C33" t="n">
-        <v>20.64</v>
+        <v>22.58</v>
       </c>
       <c r="D33" t="n">
-        <v>19.53</v>
+        <v>21.62</v>
       </c>
       <c r="E33" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
         <v>10.6</v>
       </c>
       <c r="G33" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="H33" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="J33" t="n">
-        <v>55.29</v>
+        <v>49.71</v>
       </c>
       <c r="K33" t="n">
-        <v>57.87</v>
+        <v>51.65</v>
       </c>
       <c r="L33" t="n">
-        <v>52.99</v>
+        <v>46.69</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2465,13 +2465,13 @@
         <v>6576</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q33" t="n">
+        <v>7</v>
+      </c>
+      <c r="R33" t="n">
         <v>6</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5</v>
       </c>
       <c r="S33" t="n">
         <v>60</v>
@@ -2480,236 +2480,236 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18.89</v>
+        <v>21.59</v>
       </c>
       <c r="C34" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D34" t="n">
-        <v>18.08</v>
+        <v>20.76</v>
       </c>
       <c r="E34" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="F34" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="G34" t="n">
-        <v>212</v>
+        <v>564</v>
       </c>
       <c r="H34" t="n">
-        <v>0.66</v>
+        <v>1.24</v>
       </c>
       <c r="I34" t="n">
-        <v>0.35</v>
+        <v>1.07</v>
       </c>
       <c r="J34" t="n">
-        <v>69.7</v>
+        <v>51.87</v>
       </c>
       <c r="K34" t="n">
-        <v>82.87</v>
+        <v>56.03</v>
       </c>
       <c r="L34" t="n">
-        <v>57.89</v>
+        <v>45.92</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6691</v>
+        <v>6796</v>
       </c>
       <c r="O34" t="n">
-        <v>6514</v>
+        <v>6599</v>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q34" t="n">
+        <v>7</v>
+      </c>
+      <c r="R34" t="n">
         <v>5</v>
       </c>
-      <c r="R34" t="n">
-        <v>2</v>
-      </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.5</v>
+        <v>20.19</v>
       </c>
       <c r="C35" t="n">
-        <v>17.9</v>
+        <v>20.64</v>
       </c>
       <c r="D35" t="n">
-        <v>17.26</v>
+        <v>19.53</v>
       </c>
       <c r="E35" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F35" t="n">
-        <v>14.3</v>
+        <v>10.6</v>
       </c>
       <c r="G35" t="n">
-        <v>43</v>
+        <v>426</v>
       </c>
       <c r="H35" t="n">
-        <v>0.31</v>
+        <v>1.05</v>
       </c>
       <c r="I35" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="J35" t="n">
-        <v>84.14</v>
+        <v>55.29</v>
       </c>
       <c r="K35" t="n">
-        <v>87.05</v>
+        <v>57.87</v>
       </c>
       <c r="L35" t="n">
-        <v>79.48999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3786</v>
+        <v>6767</v>
       </c>
       <c r="O35" t="n">
-        <v>6422</v>
+        <v>6576</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.02</v>
+        <v>18.89</v>
       </c>
       <c r="C36" t="n">
-        <v>17.27</v>
+        <v>19.62</v>
       </c>
       <c r="D36" t="n">
-        <v>16.92</v>
+        <v>18.08</v>
       </c>
       <c r="E36" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="F36" t="n">
-        <v>14.1</v>
+        <v>10.9</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H36" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="I36" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="J36" t="n">
-        <v>86.8</v>
+        <v>69.7</v>
       </c>
       <c r="K36" t="n">
-        <v>88.91</v>
+        <v>82.87</v>
       </c>
       <c r="L36" t="n">
-        <v>81.98999999999999</v>
+        <v>57.89</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1246</v>
+        <v>6691</v>
       </c>
       <c r="O36" t="n">
-        <v>6414</v>
+        <v>6514</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.89</v>
+        <v>17.5</v>
       </c>
       <c r="C37" t="n">
-        <v>17.03</v>
+        <v>17.9</v>
       </c>
       <c r="D37" t="n">
-        <v>16.78</v>
+        <v>17.26</v>
       </c>
       <c r="E37" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F37" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H37" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="I37" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="J37" t="n">
-        <v>88.48999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="K37" t="n">
-        <v>90.31</v>
+        <v>87.05</v>
       </c>
       <c r="L37" t="n">
-        <v>85.76000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="O37" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
         <v>2</v>
@@ -2724,47 +2724,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.13</v>
+        <v>17.02</v>
       </c>
       <c r="C38" t="n">
-        <v>17.32</v>
+        <v>17.27</v>
       </c>
       <c r="D38" t="n">
-        <v>16.89</v>
+        <v>16.92</v>
       </c>
       <c r="E38" t="n">
         <v>14.7</v>
       </c>
       <c r="F38" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="I38" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J38" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="K38" t="n">
-        <v>88.63</v>
+        <v>88.91</v>
       </c>
       <c r="L38" t="n">
-        <v>83.40000000000001</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="O38" t="n">
         <v>6414</v>
@@ -2785,41 +2785,41 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.01</v>
+        <v>16.89</v>
       </c>
       <c r="C39" t="n">
-        <v>17.08</v>
+        <v>17.03</v>
       </c>
       <c r="D39" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E39" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F39" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I39" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="J39" t="n">
-        <v>88.16</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>88.7</v>
+        <v>90.31</v>
       </c>
       <c r="L39" t="n">
-        <v>87.34999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2828,13 +2828,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -2846,41 +2846,41 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.07</v>
+        <v>17.13</v>
       </c>
       <c r="C40" t="n">
-        <v>17.29</v>
+        <v>17.32</v>
       </c>
       <c r="D40" t="n">
-        <v>16.93</v>
+        <v>16.89</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F40" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.22</v>
       </c>
-      <c r="I40" t="n">
-        <v>0.2</v>
-      </c>
       <c r="J40" t="n">
-        <v>88.06999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>89.45999999999999</v>
+        <v>88.63</v>
       </c>
       <c r="L40" t="n">
-        <v>85.97</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -2907,41 +2907,41 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.44</v>
+        <v>17.01</v>
       </c>
       <c r="C41" t="n">
-        <v>17.52</v>
+        <v>17.08</v>
       </c>
       <c r="D41" t="n">
-        <v>17.31</v>
+        <v>16.93</v>
       </c>
       <c r="E41" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="I41" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="J41" t="n">
-        <v>84.31999999999999</v>
+        <v>88.16</v>
       </c>
       <c r="K41" t="n">
-        <v>85.27</v>
+        <v>88.7</v>
       </c>
       <c r="L41" t="n">
-        <v>82.56999999999999</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2950,16 +2950,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -2968,17 +2968,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.22</v>
+        <v>17.07</v>
       </c>
       <c r="C42" t="n">
-        <v>17.34</v>
+        <v>17.29</v>
       </c>
       <c r="D42" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E42" t="n">
         <v>15</v>
@@ -2990,19 +2990,19 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
-        <v>87.37</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>88.34999999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>86.23</v>
+        <v>85.97</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3011,13 +3011,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -3029,41 +3029,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="C43" t="n">
-        <v>17.5</v>
+        <v>17.52</v>
       </c>
       <c r="D43" t="n">
-        <v>17.22</v>
+        <v>17.31</v>
       </c>
       <c r="E43" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F43" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="J43" t="n">
-        <v>87.89</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>89.09</v>
+        <v>85.27</v>
       </c>
       <c r="L43" t="n">
-        <v>87.03</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3072,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3090,41 +3090,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.51</v>
+        <v>17.22</v>
       </c>
       <c r="C44" t="n">
-        <v>17.64</v>
+        <v>17.34</v>
       </c>
       <c r="D44" t="n">
-        <v>17.34</v>
+        <v>17.11</v>
       </c>
       <c r="E44" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I44" t="n">
         <v>0.22</v>
       </c>
-      <c r="I44" t="n">
-        <v>0.19</v>
-      </c>
       <c r="J44" t="n">
-        <v>88.95</v>
+        <v>87.37</v>
       </c>
       <c r="K44" t="n">
-        <v>90.3</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>87.78</v>
+        <v>86.23</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3151,41 +3151,41 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.73</v>
+        <v>17.38</v>
       </c>
       <c r="C45" t="n">
-        <v>18.06</v>
+        <v>17.5</v>
       </c>
       <c r="D45" t="n">
-        <v>17.42</v>
+        <v>17.22</v>
       </c>
       <c r="E45" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="F45" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="I45" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="J45" t="n">
-        <v>85.27</v>
+        <v>87.89</v>
       </c>
       <c r="K45" t="n">
-        <v>88.19</v>
+        <v>89.09</v>
       </c>
       <c r="L45" t="n">
-        <v>81.95</v>
+        <v>87.03</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3194,13 +3194,13 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6457</v>
+        <v>6408</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -3212,41 +3212,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18.36</v>
+        <v>17.51</v>
       </c>
       <c r="C46" t="n">
-        <v>18.45</v>
+        <v>17.64</v>
       </c>
       <c r="D46" t="n">
-        <v>18.19</v>
+        <v>17.34</v>
       </c>
       <c r="E46" t="n">
-        <v>14.9</v>
+        <v>15.6</v>
       </c>
       <c r="F46" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="I46" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="J46" t="n">
-        <v>80.73</v>
+        <v>88.95</v>
       </c>
       <c r="K46" t="n">
-        <v>81.93000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="L46" t="n">
-        <v>79.83</v>
+        <v>87.78</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6471</v>
+        <v>6437</v>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -3273,41 +3273,41 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18.81</v>
+        <v>17.73</v>
       </c>
       <c r="C47" t="n">
-        <v>19.07</v>
+        <v>18.06</v>
       </c>
       <c r="D47" t="n">
-        <v>18.51</v>
+        <v>17.42</v>
       </c>
       <c r="E47" t="n">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="F47" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="J47" t="n">
-        <v>76.59999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="K47" t="n">
-        <v>79.87</v>
+        <v>88.19</v>
       </c>
       <c r="L47" t="n">
-        <v>74.01000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6482</v>
+        <v>6457</v>
       </c>
       <c r="P47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3334,41 +3334,41 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 19:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.81</v>
+        <v>18.36</v>
       </c>
       <c r="C48" t="n">
-        <v>20.67</v>
+        <v>18.45</v>
       </c>
       <c r="D48" t="n">
-        <v>18.96</v>
+        <v>18.19</v>
       </c>
       <c r="E48" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="F48" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="J48" t="n">
-        <v>69.16</v>
+        <v>80.73</v>
       </c>
       <c r="K48" t="n">
-        <v>75.04000000000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>63.43</v>
+        <v>79.83</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3377,16 +3377,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6496</v>
+        <v>6471</v>
       </c>
       <c r="P48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -3395,62 +3395,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>21.22</v>
+        <v>18.81</v>
       </c>
       <c r="C49" t="n">
-        <v>21.6</v>
+        <v>19.07</v>
       </c>
       <c r="D49" t="n">
-        <v>20.76</v>
+        <v>18.51</v>
       </c>
       <c r="E49" t="n">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="G49" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.99</v>
+        <v>0.5</v>
       </c>
       <c r="I49" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="J49" t="n">
-        <v>60.52</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>62.17</v>
+        <v>79.87</v>
       </c>
       <c r="L49" t="n">
-        <v>58.42</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2990</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6516</v>
+        <v>6482</v>
       </c>
       <c r="P49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,41 +528,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.22</v>
+        <v>15.57</v>
       </c>
       <c r="C2" t="n">
-        <v>16.42</v>
+        <v>15.65</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15.47</v>
       </c>
       <c r="E2" t="n">
         <v>12.8</v>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="J2" t="n">
-        <v>80.67</v>
+        <v>83.66</v>
       </c>
       <c r="K2" t="n">
-        <v>83.56</v>
+        <v>84.86</v>
       </c>
       <c r="L2" t="n">
-        <v>78.12</v>
+        <v>82.39</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6425</v>
+        <v>6420</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -589,59 +589,59 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.77</v>
+        <v>15.77</v>
       </c>
       <c r="C3" t="n">
-        <v>17.13</v>
+        <v>15.92</v>
       </c>
       <c r="D3" t="n">
-        <v>16.4</v>
+        <v>15.58</v>
       </c>
       <c r="E3" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="F3" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="J3" t="n">
-        <v>75.39</v>
+        <v>84.48</v>
       </c>
       <c r="K3" t="n">
-        <v>78.58</v>
+        <v>86.84</v>
       </c>
       <c r="L3" t="n">
-        <v>72.19</v>
+        <v>81.94</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6431</v>
+        <v>6417</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -650,59 +650,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.34</v>
+        <v>16.16</v>
       </c>
       <c r="C4" t="n">
-        <v>17.55</v>
+        <v>16.42</v>
       </c>
       <c r="D4" t="n">
-        <v>17.15</v>
+        <v>15.94</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9</v>
+        <v>12.9</v>
       </c>
       <c r="F4" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="I4" t="n">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="J4" t="n">
-        <v>70.43000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>72.41</v>
+        <v>84.55</v>
       </c>
       <c r="L4" t="n">
-        <v>68.52</v>
+        <v>78.12</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3144</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6459</v>
+        <v>6420</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -711,172 +711,172 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.83</v>
+        <v>16.77</v>
       </c>
       <c r="C5" t="n">
-        <v>18.09</v>
+        <v>17.13</v>
       </c>
       <c r="D5" t="n">
-        <v>17.42</v>
+        <v>16.4</v>
       </c>
       <c r="E5" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6</v>
+        <v>11.9</v>
       </c>
       <c r="G5" t="n">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="J5" t="n">
-        <v>66.04000000000001</v>
+        <v>75.39</v>
       </c>
       <c r="K5" t="n">
-        <v>69.8</v>
+        <v>78.58</v>
       </c>
       <c r="L5" t="n">
-        <v>62.77</v>
+        <v>72.19</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4749</v>
+        <v>1164</v>
       </c>
       <c r="O5" t="n">
-        <v>6491</v>
+        <v>6431</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.68</v>
+        <v>17.34</v>
       </c>
       <c r="C6" t="n">
-        <v>17.86</v>
+        <v>17.55</v>
       </c>
       <c r="D6" t="n">
-        <v>17.49</v>
+        <v>17.15</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="G6" t="n">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="J6" t="n">
-        <v>65.15000000000001</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>67.11</v>
+        <v>72.41</v>
       </c>
       <c r="L6" t="n">
-        <v>63.11</v>
+        <v>68.52</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5962</v>
+        <v>3144</v>
       </c>
       <c r="O6" t="n">
-        <v>6502</v>
+        <v>6459</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.45</v>
+        <v>17.83</v>
       </c>
       <c r="C7" t="n">
-        <v>17.76</v>
+        <v>18.09</v>
       </c>
       <c r="D7" t="n">
-        <v>17.19</v>
+        <v>17.42</v>
       </c>
       <c r="E7" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F7" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="G7" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="H7" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
-        <v>65.79000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>68.27</v>
+        <v>69.8</v>
       </c>
       <c r="L7" t="n">
-        <v>62.48</v>
+        <v>62.77</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6561</v>
+        <v>4749</v>
       </c>
       <c r="O7" t="n">
-        <v>6539</v>
+        <v>6491</v>
       </c>
       <c r="P7" t="n">
         <v>4</v>
@@ -888,56 +888,56 @@
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.1</v>
+        <v>17.68</v>
       </c>
       <c r="C8" t="n">
-        <v>17.35</v>
+        <v>17.86</v>
       </c>
       <c r="D8" t="n">
-        <v>16.86</v>
+        <v>17.49</v>
       </c>
       <c r="E8" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>246</v>
+        <v>148</v>
       </c>
       <c r="H8" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="J8" t="n">
-        <v>67.38</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>67.78</v>
+        <v>67.11</v>
       </c>
       <c r="L8" t="n">
-        <v>66.55</v>
+        <v>63.11</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6671</v>
+        <v>5962</v>
       </c>
       <c r="O8" t="n">
-        <v>6536</v>
+        <v>6502</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -946,62 +946,62 @@
         <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.52</v>
+        <v>17.45</v>
       </c>
       <c r="C9" t="n">
-        <v>17.36</v>
+        <v>17.76</v>
       </c>
       <c r="D9" t="n">
-        <v>16.01</v>
+        <v>17.19</v>
       </c>
       <c r="E9" t="n">
         <v>10.9</v>
       </c>
       <c r="F9" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G9" t="n">
-        <v>301</v>
+        <v>210</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="J9" t="n">
-        <v>69.84</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>72.16</v>
+        <v>68.27</v>
       </c>
       <c r="L9" t="n">
-        <v>66.34999999999999</v>
+        <v>62.48</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6681</v>
+        <v>6561</v>
       </c>
       <c r="O9" t="n">
-        <v>6525</v>
+        <v>6539</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>4</v>
@@ -1016,59 +1016,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.55</v>
+        <v>17.1</v>
       </c>
       <c r="C10" t="n">
-        <v>16.32</v>
+        <v>17.35</v>
       </c>
       <c r="D10" t="n">
-        <v>15.05</v>
+        <v>16.86</v>
       </c>
       <c r="E10" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F10" t="n">
         <v>10.7</v>
       </c>
       <c r="G10" t="n">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
       <c r="J10" t="n">
-        <v>75.25</v>
+        <v>67.38</v>
       </c>
       <c r="K10" t="n">
-        <v>78.77</v>
+        <v>67.78</v>
       </c>
       <c r="L10" t="n">
-        <v>71.11</v>
+        <v>66.55</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6729</v>
+        <v>6671</v>
       </c>
       <c r="O10" t="n">
-        <v>6556</v>
+        <v>6536</v>
       </c>
       <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
         <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>60</v>
@@ -1077,78 +1077,78 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.04</v>
+        <v>16.52</v>
       </c>
       <c r="C11" t="n">
-        <v>15.26</v>
+        <v>17.36</v>
       </c>
       <c r="D11" t="n">
-        <v>14.82</v>
+        <v>16.01</v>
       </c>
       <c r="E11" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="G11" t="n">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="H11" t="n">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>77.86</v>
+        <v>69.84</v>
       </c>
       <c r="K11" t="n">
-        <v>80.23</v>
+        <v>72.16</v>
       </c>
       <c r="L11" t="n">
-        <v>75.81</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5708</v>
+        <v>6681</v>
       </c>
       <c r="O11" t="n">
-        <v>6494</v>
+        <v>6525</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.47</v>
+        <v>15.55</v>
       </c>
       <c r="C12" t="n">
-        <v>14.79</v>
+        <v>16.32</v>
       </c>
       <c r="D12" t="n">
-        <v>14.22</v>
+        <v>15.05</v>
       </c>
       <c r="E12" t="n">
         <v>11.1</v>
@@ -1157,92 +1157,92 @@
         <v>10.7</v>
       </c>
       <c r="G12" t="n">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="I12" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="J12" t="n">
-        <v>80.75</v>
+        <v>75.25</v>
       </c>
       <c r="K12" t="n">
-        <v>82.34</v>
+        <v>78.77</v>
       </c>
       <c r="L12" t="n">
-        <v>79.73999999999999</v>
+        <v>71.11</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6254</v>
+        <v>6729</v>
       </c>
       <c r="O12" t="n">
-        <v>6491</v>
+        <v>6556</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.34</v>
+        <v>15.04</v>
       </c>
       <c r="C13" t="n">
-        <v>14.4</v>
+        <v>15.26</v>
       </c>
       <c r="D13" t="n">
-        <v>14.25</v>
+        <v>14.82</v>
       </c>
       <c r="E13" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="F13" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="H13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.33</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.32</v>
-      </c>
       <c r="J13" t="n">
-        <v>79.29000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="K13" t="n">
-        <v>80.34999999999999</v>
+        <v>80.23</v>
       </c>
       <c r="L13" t="n">
-        <v>77.13</v>
+        <v>75.81</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3949</v>
+        <v>5708</v>
       </c>
       <c r="O13" t="n">
-        <v>6425</v>
+        <v>6494</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1254,56 +1254,56 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.56</v>
+        <v>14.47</v>
       </c>
       <c r="C14" t="n">
-        <v>14.75</v>
+        <v>14.79</v>
       </c>
       <c r="D14" t="n">
-        <v>14.34</v>
+        <v>14.22</v>
       </c>
       <c r="E14" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F14" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="J14" t="n">
-        <v>78.20999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="K14" t="n">
-        <v>80.09999999999999</v>
+        <v>82.34</v>
       </c>
       <c r="L14" t="n">
-        <v>75.43000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2449</v>
+        <v>6254</v>
       </c>
       <c r="O14" t="n">
-        <v>6420</v>
+        <v>6491</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -1315,62 +1315,62 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.79</v>
+        <v>14.34</v>
       </c>
       <c r="C15" t="n">
-        <v>14.98</v>
+        <v>14.4</v>
       </c>
       <c r="D15" t="n">
-        <v>14.63</v>
+        <v>14.25</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F15" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="I15" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J15" t="n">
-        <v>77.20999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>79.73999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>74.54000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O15" t="n">
-        <v>6411</v>
+        <v>6425</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -1382,59 +1382,59 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.24</v>
+        <v>14.56</v>
       </c>
       <c r="C16" t="n">
-        <v>15.48</v>
+        <v>14.75</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>14.34</v>
       </c>
       <c r="E16" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F16" t="n">
         <v>10.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="I16" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="J16" t="n">
-        <v>74.68000000000001</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>75.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>73.42</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O16" t="n">
-        <v>6411</v>
+        <v>6420</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1443,41 +1443,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.62</v>
+        <v>14.79</v>
       </c>
       <c r="C17" t="n">
-        <v>15.76</v>
+        <v>14.98</v>
       </c>
       <c r="D17" t="n">
-        <v>15.46</v>
+        <v>14.63</v>
       </c>
       <c r="E17" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="F17" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I17" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J17" t="n">
-        <v>81.47</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>89.01000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>74.23</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6402</v>
+        <v>6411</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -1495,7 +1495,7 @@
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1504,41 +1504,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.86</v>
+        <v>15.24</v>
       </c>
       <c r="C18" t="n">
-        <v>16.08</v>
+        <v>15.48</v>
       </c>
       <c r="D18" t="n">
-        <v>15.66</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>13.8</v>
+        <v>10.7</v>
       </c>
       <c r="F18" t="n">
-        <v>13.7</v>
+        <v>10.4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="I18" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="J18" t="n">
-        <v>87.95999999999999</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>89.39</v>
+        <v>75.5</v>
       </c>
       <c r="L18" t="n">
-        <v>86.37</v>
+        <v>73.42</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1550,13 +1550,13 @@
         <v>6411</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1565,41 +1565,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.22</v>
+        <v>15.62</v>
       </c>
       <c r="C19" t="n">
-        <v>16.35</v>
+        <v>15.76</v>
       </c>
       <c r="D19" t="n">
-        <v>16.12</v>
+        <v>15.46</v>
       </c>
       <c r="E19" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="F19" t="n">
-        <v>13.4</v>
+        <v>10.8</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J19" t="n">
-        <v>85.42</v>
+        <v>81.47</v>
       </c>
       <c r="K19" t="n">
-        <v>87.15000000000001</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>83.22</v>
+        <v>74.23</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1608,13 +1608,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6405</v>
+        <v>6402</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -1626,41 +1626,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.39</v>
+        <v>15.86</v>
       </c>
       <c r="C20" t="n">
-        <v>16.55</v>
+        <v>16.08</v>
       </c>
       <c r="D20" t="n">
-        <v>16.22</v>
+        <v>15.66</v>
       </c>
       <c r="E20" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F20" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="I20" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J20" t="n">
-        <v>85.56999999999999</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>87.13</v>
+        <v>89.39</v>
       </c>
       <c r="L20" t="n">
-        <v>84.14</v>
+        <v>86.37</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1669,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -1687,41 +1687,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.68</v>
+        <v>16.22</v>
       </c>
       <c r="C21" t="n">
-        <v>16.76</v>
+        <v>16.35</v>
       </c>
       <c r="D21" t="n">
-        <v>16.63</v>
+        <v>16.12</v>
       </c>
       <c r="E21" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="F21" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="I21" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="J21" t="n">
-        <v>84.16</v>
+        <v>85.42</v>
       </c>
       <c r="K21" t="n">
-        <v>86.08</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>81.98</v>
+        <v>83.22</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -1748,41 +1748,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.64</v>
+        <v>16.39</v>
       </c>
       <c r="C22" t="n">
-        <v>16.72</v>
+        <v>16.55</v>
       </c>
       <c r="D22" t="n">
-        <v>16.62</v>
+        <v>16.22</v>
       </c>
       <c r="E22" t="n">
-        <v>14.8</v>
+        <v>13.9</v>
       </c>
       <c r="F22" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="I22" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J22" t="n">
-        <v>89.45</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>91.73999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="L22" t="n">
-        <v>85.8</v>
+        <v>84.14</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1791,13 +1791,13 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6411</v>
+        <v>6417</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -1809,41 +1809,41 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.73</v>
+        <v>16.68</v>
       </c>
       <c r="C23" t="n">
-        <v>16.91</v>
+        <v>16.76</v>
       </c>
       <c r="D23" t="n">
-        <v>16.64</v>
+        <v>16.63</v>
       </c>
       <c r="E23" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="F23" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="J23" t="n">
-        <v>91.16</v>
+        <v>84.16</v>
       </c>
       <c r="K23" t="n">
-        <v>91.98999999999999</v>
+        <v>86.08</v>
       </c>
       <c r="L23" t="n">
-        <v>89.92</v>
+        <v>81.98</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -1870,41 +1870,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="C24" t="n">
-        <v>16.87</v>
+        <v>16.72</v>
       </c>
       <c r="D24" t="n">
-        <v>16.65</v>
+        <v>16.62</v>
       </c>
       <c r="E24" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="F24" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="I24" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="J24" t="n">
-        <v>92.09999999999999</v>
+        <v>89.45</v>
       </c>
       <c r="K24" t="n">
-        <v>93.45</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>90.81999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -1931,41 +1931,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.6</v>
+        <v>16.73</v>
       </c>
       <c r="C25" t="n">
-        <v>16.66</v>
+        <v>16.91</v>
       </c>
       <c r="D25" t="n">
-        <v>16.52</v>
+        <v>16.64</v>
       </c>
       <c r="E25" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="F25" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J25" t="n">
-        <v>95.29000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="K25" t="n">
-        <v>96.45999999999999</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>93.84</v>
+        <v>89.92</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1974,16 +1974,16 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -1992,41 +1992,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.91</v>
+        <v>16.79</v>
       </c>
       <c r="C26" t="n">
-        <v>17.19</v>
+        <v>16.87</v>
       </c>
       <c r="D26" t="n">
-        <v>16.69</v>
+        <v>16.65</v>
       </c>
       <c r="E26" t="n">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="F26" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J26" t="n">
-        <v>94.18000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>96.09</v>
+        <v>93.45</v>
       </c>
       <c r="L26" t="n">
-        <v>90.87</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6442</v>
+        <v>6420</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -2044,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2053,59 +2053,59 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.68</v>
+        <v>16.6</v>
       </c>
       <c r="C27" t="n">
-        <v>18.12</v>
+        <v>16.66</v>
       </c>
       <c r="D27" t="n">
-        <v>17.08</v>
+        <v>16.52</v>
       </c>
       <c r="E27" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="F27" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="I27" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="J27" t="n">
-        <v>86.59</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>93.40000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>80.54000000000001</v>
+        <v>93.84</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6451</v>
+        <v>6425</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2114,59 +2114,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.95</v>
+        <v>16.91</v>
       </c>
       <c r="C28" t="n">
-        <v>21.08</v>
+        <v>17.19</v>
       </c>
       <c r="D28" t="n">
-        <v>18.04</v>
+        <v>16.69</v>
       </c>
       <c r="E28" t="n">
-        <v>12.9</v>
+        <v>15.9</v>
       </c>
       <c r="F28" t="n">
-        <v>11.6</v>
+        <v>15.6</v>
       </c>
       <c r="G28" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
+        <v>0.1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.41</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>64.73999999999999</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>79.75</v>
+        <v>96.09</v>
       </c>
       <c r="L28" t="n">
-        <v>55.98</v>
+        <v>90.87</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6474</v>
+        <v>6442</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2175,59 +2175,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.54</v>
+        <v>17.68</v>
       </c>
       <c r="C29" t="n">
-        <v>21.83</v>
+        <v>18.12</v>
       </c>
       <c r="D29" t="n">
-        <v>21.18</v>
+        <v>17.08</v>
       </c>
       <c r="E29" t="n">
-        <v>11.6</v>
+        <v>15.3</v>
       </c>
       <c r="F29" t="n">
-        <v>10.7</v>
+        <v>14.6</v>
       </c>
       <c r="G29" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>1.19</v>
+        <v>0.27</v>
       </c>
       <c r="I29" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="J29" t="n">
-        <v>53.45</v>
+        <v>86.59</v>
       </c>
       <c r="K29" t="n">
-        <v>58.22</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>49.34</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2410</v>
+        <v>685</v>
       </c>
       <c r="O29" t="n">
-        <v>6485</v>
+        <v>6451</v>
       </c>
       <c r="P29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2236,175 +2236,175 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.02</v>
+        <v>19.95</v>
       </c>
       <c r="C30" t="n">
-        <v>22.16</v>
+        <v>21.08</v>
       </c>
       <c r="D30" t="n">
-        <v>21.88</v>
+        <v>18.04</v>
       </c>
       <c r="E30" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="F30" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="G30" t="n">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H30" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="I30" t="n">
-        <v>1.24</v>
+        <v>0.41</v>
       </c>
       <c r="J30" t="n">
-        <v>50.18</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>52.66</v>
+        <v>79.75</v>
       </c>
       <c r="L30" t="n">
-        <v>47.74</v>
+        <v>55.98</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4352</v>
+        <v>1926</v>
       </c>
       <c r="O30" t="n">
-        <v>6511</v>
+        <v>6474</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.31</v>
+        <v>21.54</v>
       </c>
       <c r="C31" t="n">
-        <v>22.81</v>
+        <v>21.83</v>
       </c>
       <c r="D31" t="n">
-        <v>22.04</v>
+        <v>21.18</v>
       </c>
       <c r="E31" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F31" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="G31" t="n">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H31" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="I31" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="J31" t="n">
-        <v>50.19</v>
+        <v>53.45</v>
       </c>
       <c r="K31" t="n">
-        <v>51.75</v>
+        <v>58.22</v>
       </c>
       <c r="L31" t="n">
-        <v>47.76</v>
+        <v>49.34</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5406</v>
+        <v>2410</v>
       </c>
       <c r="O31" t="n">
-        <v>6539</v>
+        <v>6485</v>
       </c>
       <c r="P31" t="n">
         <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S31" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.68</v>
+        <v>22.02</v>
       </c>
       <c r="C32" t="n">
-        <v>23.1</v>
+        <v>22.16</v>
       </c>
       <c r="D32" t="n">
-        <v>22.11</v>
+        <v>21.88</v>
       </c>
       <c r="E32" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="F32" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G32" t="n">
-        <v>384</v>
+        <v>111</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="I32" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="J32" t="n">
-        <v>48.82</v>
+        <v>50.18</v>
       </c>
       <c r="K32" t="n">
-        <v>51.28</v>
+        <v>52.66</v>
       </c>
       <c r="L32" t="n">
-        <v>47.13</v>
+        <v>47.74</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6743</v>
+        <v>4352</v>
       </c>
       <c r="O32" t="n">
-        <v>6573</v>
+        <v>6511</v>
       </c>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q32" t="n">
         <v>7</v>
@@ -2413,56 +2413,56 @@
         <v>6</v>
       </c>
       <c r="S32" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.01</v>
+        <v>22.31</v>
       </c>
       <c r="C33" t="n">
-        <v>22.58</v>
+        <v>22.81</v>
       </c>
       <c r="D33" t="n">
-        <v>21.62</v>
+        <v>22.04</v>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F33" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="G33" t="n">
-        <v>452</v>
+        <v>198</v>
       </c>
       <c r="H33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="J33" t="n">
-        <v>49.71</v>
+        <v>50.19</v>
       </c>
       <c r="K33" t="n">
-        <v>51.65</v>
+        <v>51.75</v>
       </c>
       <c r="L33" t="n">
-        <v>46.69</v>
+        <v>47.76</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6767</v>
+        <v>5406</v>
       </c>
       <c r="O33" t="n">
-        <v>6576</v>
+        <v>6539</v>
       </c>
       <c r="P33" t="n">
         <v>6</v>
@@ -2474,65 +2474,65 @@
         <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.59</v>
+        <v>22.68</v>
       </c>
       <c r="C34" t="n">
-        <v>22.58</v>
+        <v>23.1</v>
       </c>
       <c r="D34" t="n">
-        <v>20.76</v>
+        <v>22.11</v>
       </c>
       <c r="E34" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F34" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G34" t="n">
-        <v>564</v>
+        <v>384</v>
       </c>
       <c r="H34" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="I34" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="J34" t="n">
-        <v>51.87</v>
+        <v>48.82</v>
       </c>
       <c r="K34" t="n">
-        <v>56.03</v>
+        <v>51.28</v>
       </c>
       <c r="L34" t="n">
-        <v>45.92</v>
+        <v>47.13</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6796</v>
+        <v>6743</v>
       </c>
       <c r="O34" t="n">
-        <v>6599</v>
+        <v>6573</v>
       </c>
       <c r="P34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q34" t="n">
         <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S34" t="n">
         <v>60</v>
@@ -2541,41 +2541,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>20.19</v>
+        <v>22.01</v>
       </c>
       <c r="C35" t="n">
-        <v>20.64</v>
+        <v>22.58</v>
       </c>
       <c r="D35" t="n">
-        <v>19.53</v>
+        <v>21.62</v>
       </c>
       <c r="E35" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
         <v>10.6</v>
       </c>
       <c r="G35" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="H35" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="I35" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="J35" t="n">
-        <v>55.29</v>
+        <v>49.71</v>
       </c>
       <c r="K35" t="n">
-        <v>57.87</v>
+        <v>51.65</v>
       </c>
       <c r="L35" t="n">
-        <v>52.99</v>
+        <v>46.69</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2587,13 +2587,13 @@
         <v>6576</v>
       </c>
       <c r="P35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q35" t="n">
+        <v>7</v>
+      </c>
+      <c r="R35" t="n">
         <v>6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>5</v>
       </c>
       <c r="S35" t="n">
         <v>60</v>
@@ -2602,236 +2602,236 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18.89</v>
+        <v>21.59</v>
       </c>
       <c r="C36" t="n">
-        <v>19.62</v>
+        <v>22.58</v>
       </c>
       <c r="D36" t="n">
-        <v>18.08</v>
+        <v>20.76</v>
       </c>
       <c r="E36" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="F36" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="G36" t="n">
-        <v>212</v>
+        <v>564</v>
       </c>
       <c r="H36" t="n">
-        <v>0.66</v>
+        <v>1.24</v>
       </c>
       <c r="I36" t="n">
-        <v>0.35</v>
+        <v>1.07</v>
       </c>
       <c r="J36" t="n">
-        <v>69.7</v>
+        <v>51.87</v>
       </c>
       <c r="K36" t="n">
-        <v>82.87</v>
+        <v>56.03</v>
       </c>
       <c r="L36" t="n">
-        <v>57.89</v>
+        <v>45.92</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6691</v>
+        <v>6796</v>
       </c>
       <c r="O36" t="n">
-        <v>6514</v>
+        <v>6599</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
+        <v>7</v>
+      </c>
+      <c r="R36" t="n">
         <v>5</v>
       </c>
-      <c r="R36" t="n">
-        <v>2</v>
-      </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.5</v>
+        <v>20.19</v>
       </c>
       <c r="C37" t="n">
-        <v>17.9</v>
+        <v>20.64</v>
       </c>
       <c r="D37" t="n">
-        <v>17.26</v>
+        <v>19.53</v>
       </c>
       <c r="E37" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F37" t="n">
-        <v>14.3</v>
+        <v>10.6</v>
       </c>
       <c r="G37" t="n">
-        <v>43</v>
+        <v>426</v>
       </c>
       <c r="H37" t="n">
-        <v>0.31</v>
+        <v>1.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="J37" t="n">
-        <v>84.14</v>
+        <v>55.29</v>
       </c>
       <c r="K37" t="n">
-        <v>87.05</v>
+        <v>57.87</v>
       </c>
       <c r="L37" t="n">
-        <v>79.48999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3786</v>
+        <v>6767</v>
       </c>
       <c r="O37" t="n">
-        <v>6422</v>
+        <v>6576</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.02</v>
+        <v>18.89</v>
       </c>
       <c r="C38" t="n">
-        <v>17.27</v>
+        <v>19.62</v>
       </c>
       <c r="D38" t="n">
-        <v>16.92</v>
+        <v>18.08</v>
       </c>
       <c r="E38" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="F38" t="n">
-        <v>14.1</v>
+        <v>10.9</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H38" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="I38" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="J38" t="n">
-        <v>86.8</v>
+        <v>69.7</v>
       </c>
       <c r="K38" t="n">
-        <v>88.91</v>
+        <v>82.87</v>
       </c>
       <c r="L38" t="n">
-        <v>81.98999999999999</v>
+        <v>57.89</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1246</v>
+        <v>6691</v>
       </c>
       <c r="O38" t="n">
-        <v>6414</v>
+        <v>6514</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.89</v>
+        <v>17.5</v>
       </c>
       <c r="C39" t="n">
-        <v>17.03</v>
+        <v>17.9</v>
       </c>
       <c r="D39" t="n">
-        <v>16.78</v>
+        <v>17.26</v>
       </c>
       <c r="E39" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="F39" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H39" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="I39" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="J39" t="n">
-        <v>88.48999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="K39" t="n">
-        <v>90.31</v>
+        <v>87.05</v>
       </c>
       <c r="L39" t="n">
-        <v>85.76000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="O39" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
         <v>2</v>
@@ -2846,47 +2846,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.13</v>
+        <v>17.02</v>
       </c>
       <c r="C40" t="n">
-        <v>17.32</v>
+        <v>17.27</v>
       </c>
       <c r="D40" t="n">
-        <v>16.89</v>
+        <v>16.92</v>
       </c>
       <c r="E40" t="n">
         <v>14.7</v>
       </c>
       <c r="F40" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="I40" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J40" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="K40" t="n">
-        <v>88.63</v>
+        <v>88.91</v>
       </c>
       <c r="L40" t="n">
-        <v>83.40000000000001</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="O40" t="n">
         <v>6414</v>
@@ -2907,41 +2907,41 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.01</v>
+        <v>16.89</v>
       </c>
       <c r="C41" t="n">
-        <v>17.08</v>
+        <v>17.03</v>
       </c>
       <c r="D41" t="n">
-        <v>16.93</v>
+        <v>16.78</v>
       </c>
       <c r="E41" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F41" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I41" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="J41" t="n">
-        <v>88.16</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>88.7</v>
+        <v>90.31</v>
       </c>
       <c r="L41" t="n">
-        <v>87.34999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2950,13 +2950,13 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -2968,41 +2968,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.07</v>
+        <v>17.13</v>
       </c>
       <c r="C42" t="n">
-        <v>17.29</v>
+        <v>17.32</v>
       </c>
       <c r="D42" t="n">
-        <v>16.93</v>
+        <v>16.89</v>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F42" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I42" t="n">
         <v>0.22</v>
       </c>
-      <c r="I42" t="n">
-        <v>0.2</v>
-      </c>
       <c r="J42" t="n">
-        <v>88.06999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>89.45999999999999</v>
+        <v>88.63</v>
       </c>
       <c r="L42" t="n">
-        <v>85.97</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3029,41 +3029,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.44</v>
+        <v>17.01</v>
       </c>
       <c r="C43" t="n">
-        <v>17.52</v>
+        <v>17.08</v>
       </c>
       <c r="D43" t="n">
-        <v>17.31</v>
+        <v>16.93</v>
       </c>
       <c r="E43" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="I43" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="J43" t="n">
-        <v>84.31999999999999</v>
+        <v>88.16</v>
       </c>
       <c r="K43" t="n">
-        <v>85.27</v>
+        <v>88.7</v>
       </c>
       <c r="L43" t="n">
-        <v>82.56999999999999</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3072,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3090,17 +3090,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.22</v>
+        <v>17.07</v>
       </c>
       <c r="C44" t="n">
-        <v>17.34</v>
+        <v>17.29</v>
       </c>
       <c r="D44" t="n">
-        <v>17.11</v>
+        <v>16.93</v>
       </c>
       <c r="E44" t="n">
         <v>15</v>
@@ -3112,19 +3112,19 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="I44" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
-        <v>87.37</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>88.34999999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>86.23</v>
+        <v>85.97</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3133,13 +3133,13 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -3151,41 +3151,41 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 02:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="C45" t="n">
-        <v>17.5</v>
+        <v>17.52</v>
       </c>
       <c r="D45" t="n">
-        <v>17.22</v>
+        <v>17.31</v>
       </c>
       <c r="E45" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F45" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I45" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="J45" t="n">
-        <v>87.89</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>89.09</v>
+        <v>85.27</v>
       </c>
       <c r="L45" t="n">
-        <v>87.03</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3194,16 +3194,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6408</v>
+        <v>6417</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3212,41 +3212,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.51</v>
+        <v>17.22</v>
       </c>
       <c r="C46" t="n">
-        <v>17.64</v>
+        <v>17.34</v>
       </c>
       <c r="D46" t="n">
-        <v>17.34</v>
+        <v>17.11</v>
       </c>
       <c r="E46" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I46" t="n">
         <v>0.22</v>
       </c>
-      <c r="I46" t="n">
-        <v>0.19</v>
-      </c>
       <c r="J46" t="n">
-        <v>88.95</v>
+        <v>87.37</v>
       </c>
       <c r="K46" t="n">
-        <v>90.3</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>87.78</v>
+        <v>86.23</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3273,41 +3273,41 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.73</v>
+        <v>17.38</v>
       </c>
       <c r="C47" t="n">
-        <v>18.06</v>
+        <v>17.5</v>
       </c>
       <c r="D47" t="n">
-        <v>17.42</v>
+        <v>17.22</v>
       </c>
       <c r="E47" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="F47" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="J47" t="n">
-        <v>85.27</v>
+        <v>87.89</v>
       </c>
       <c r="K47" t="n">
-        <v>88.19</v>
+        <v>89.09</v>
       </c>
       <c r="L47" t="n">
-        <v>81.95</v>
+        <v>87.03</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6457</v>
+        <v>6408</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -3334,41 +3334,41 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.36</v>
+        <v>17.51</v>
       </c>
       <c r="C48" t="n">
-        <v>18.45</v>
+        <v>17.64</v>
       </c>
       <c r="D48" t="n">
-        <v>18.19</v>
+        <v>17.34</v>
       </c>
       <c r="E48" t="n">
-        <v>14.9</v>
+        <v>15.6</v>
       </c>
       <c r="F48" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="J48" t="n">
-        <v>80.73</v>
+        <v>88.95</v>
       </c>
       <c r="K48" t="n">
-        <v>81.93000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="L48" t="n">
-        <v>79.83</v>
+        <v>87.78</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3377,16 +3377,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6471</v>
+        <v>6437</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -3395,41 +3395,41 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18.81</v>
+        <v>17.73</v>
       </c>
       <c r="C49" t="n">
-        <v>19.07</v>
+        <v>18.06</v>
       </c>
       <c r="D49" t="n">
-        <v>18.51</v>
+        <v>17.42</v>
       </c>
       <c r="E49" t="n">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="F49" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="I49" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="J49" t="n">
-        <v>76.59999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="K49" t="n">
-        <v>79.87</v>
+        <v>88.19</v>
       </c>
       <c r="L49" t="n">
-        <v>74.01000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3438,16 +3438,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6482</v>
+        <v>6457</v>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,41 +528,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.57</v>
+        <v>15.3</v>
       </c>
       <c r="C2" t="n">
-        <v>15.65</v>
+        <v>15.38</v>
       </c>
       <c r="D2" t="n">
-        <v>15.47</v>
+        <v>15.22</v>
       </c>
       <c r="E2" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="J2" t="n">
-        <v>83.66</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>84.86</v>
+        <v>89.27</v>
       </c>
       <c r="L2" t="n">
-        <v>82.39</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -571,16 +571,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6420</v>
+        <v>6408</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -589,20 +589,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.77</v>
+        <v>15.65</v>
       </c>
       <c r="C3" t="n">
-        <v>15.92</v>
+        <v>15.83</v>
       </c>
       <c r="D3" t="n">
-        <v>15.58</v>
+        <v>15.43</v>
       </c>
       <c r="E3" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="F3" t="n">
         <v>12.7</v>
@@ -617,13 +617,13 @@
         <v>0.23</v>
       </c>
       <c r="J3" t="n">
-        <v>84.48</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>86.84</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>81.94</v>
+        <v>81.81</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -650,41 +650,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.16</v>
+        <v>15.77</v>
       </c>
       <c r="C4" t="n">
-        <v>16.42</v>
+        <v>16.04</v>
       </c>
       <c r="D4" t="n">
-        <v>15.94</v>
+        <v>15.59</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="I4" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="J4" t="n">
-        <v>81.48999999999999</v>
+        <v>84</v>
       </c>
       <c r="K4" t="n">
-        <v>84.55</v>
+        <v>86.05</v>
       </c>
       <c r="L4" t="n">
-        <v>78.12</v>
+        <v>80.77</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6420</v>
+        <v>6414</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -711,56 +711,56 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.77</v>
+        <v>15.89</v>
       </c>
       <c r="C5" t="n">
-        <v>17.13</v>
+        <v>16.09</v>
       </c>
       <c r="D5" t="n">
-        <v>16.4</v>
+        <v>15.55</v>
       </c>
       <c r="E5" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F5" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
-        <v>75.39</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>78.58</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>72.19</v>
+        <v>80.19</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6431</v>
+        <v>6405</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
@@ -772,59 +772,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.34</v>
+        <v>15.43</v>
       </c>
       <c r="C6" t="n">
-        <v>17.55</v>
+        <v>15.49</v>
       </c>
       <c r="D6" t="n">
-        <v>17.15</v>
+        <v>15.38</v>
       </c>
       <c r="E6" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F6" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.58</v>
+        <v>0.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="J6" t="n">
-        <v>70.43000000000001</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>72.41</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>68.52</v>
+        <v>83.27</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3144</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6459</v>
+        <v>6408</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -833,663 +833,663 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.83</v>
+        <v>15.57</v>
       </c>
       <c r="C7" t="n">
-        <v>18.09</v>
+        <v>15.65</v>
       </c>
       <c r="D7" t="n">
-        <v>17.42</v>
+        <v>15.47</v>
       </c>
       <c r="E7" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F7" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="G7" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="J7" t="n">
-        <v>66.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>69.8</v>
+        <v>84.86</v>
       </c>
       <c r="L7" t="n">
-        <v>62.77</v>
+        <v>82.39</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4749</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6491</v>
+        <v>6411</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.68</v>
+        <v>15.77</v>
       </c>
       <c r="C8" t="n">
-        <v>17.86</v>
+        <v>15.92</v>
       </c>
       <c r="D8" t="n">
-        <v>17.49</v>
+        <v>15.58</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>13.1</v>
       </c>
       <c r="F8" t="n">
-        <v>10.5</v>
+        <v>12.7</v>
       </c>
       <c r="G8" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="I8" t="n">
-        <v>0.66</v>
+        <v>0.23</v>
       </c>
       <c r="J8" t="n">
-        <v>65.15000000000001</v>
+        <v>84.48</v>
       </c>
       <c r="K8" t="n">
-        <v>67.11</v>
+        <v>86.84</v>
       </c>
       <c r="L8" t="n">
-        <v>63.11</v>
+        <v>81.94</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5962</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6502</v>
+        <v>6417</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.45</v>
+        <v>16.16</v>
       </c>
       <c r="C9" t="n">
-        <v>17.76</v>
+        <v>16.42</v>
       </c>
       <c r="D9" t="n">
-        <v>17.19</v>
+        <v>15.94</v>
       </c>
       <c r="E9" t="n">
-        <v>10.9</v>
+        <v>12.9</v>
       </c>
       <c r="F9" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="G9" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.68</v>
+        <v>0.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.62</v>
+        <v>0.27</v>
       </c>
       <c r="J9" t="n">
-        <v>65.79000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>68.27</v>
+        <v>84.55</v>
       </c>
       <c r="L9" t="n">
-        <v>62.48</v>
+        <v>78.12</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6561</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6539</v>
+        <v>6420</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.1</v>
+        <v>16.77</v>
       </c>
       <c r="C10" t="n">
-        <v>17.35</v>
+        <v>17.13</v>
       </c>
       <c r="D10" t="n">
-        <v>16.86</v>
+        <v>16.4</v>
       </c>
       <c r="E10" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="F10" t="n">
-        <v>10.7</v>
+        <v>11.9</v>
       </c>
       <c r="G10" t="n">
-        <v>246</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="I10" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="J10" t="n">
-        <v>67.38</v>
+        <v>75.39</v>
       </c>
       <c r="K10" t="n">
-        <v>67.78</v>
+        <v>78.58</v>
       </c>
       <c r="L10" t="n">
-        <v>66.55</v>
+        <v>72.19</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6671</v>
+        <v>1164</v>
       </c>
       <c r="O10" t="n">
-        <v>6536</v>
+        <v>6431</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.52</v>
+        <v>17.34</v>
       </c>
       <c r="C11" t="n">
-        <v>17.36</v>
+        <v>17.55</v>
       </c>
       <c r="D11" t="n">
-        <v>16.01</v>
+        <v>17.15</v>
       </c>
       <c r="E11" t="n">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="F11" t="n">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="G11" t="n">
-        <v>301</v>
+        <v>58</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="J11" t="n">
-        <v>69.84</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>72.16</v>
+        <v>72.41</v>
       </c>
       <c r="L11" t="n">
-        <v>66.34999999999999</v>
+        <v>68.52</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6681</v>
+        <v>3144</v>
       </c>
       <c r="O11" t="n">
-        <v>6525</v>
+        <v>6459</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
         <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.55</v>
+        <v>17.83</v>
       </c>
       <c r="C12" t="n">
-        <v>16.32</v>
+        <v>18.09</v>
       </c>
       <c r="D12" t="n">
-        <v>15.05</v>
+        <v>17.42</v>
       </c>
       <c r="E12" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="F12" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="G12" t="n">
-        <v>231</v>
+        <v>125</v>
       </c>
       <c r="H12" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
-        <v>75.25</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>78.77</v>
+        <v>69.8</v>
       </c>
       <c r="L12" t="n">
-        <v>71.11</v>
+        <v>62.77</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6729</v>
+        <v>4749</v>
       </c>
       <c r="O12" t="n">
-        <v>6556</v>
+        <v>6491</v>
       </c>
       <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
       <c r="S12" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.04</v>
+        <v>17.68</v>
       </c>
       <c r="C13" t="n">
-        <v>15.26</v>
+        <v>17.86</v>
       </c>
       <c r="D13" t="n">
-        <v>14.82</v>
+        <v>17.49</v>
       </c>
       <c r="E13" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G13" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="H13" t="n">
-        <v>0.37</v>
+        <v>0.7</v>
       </c>
       <c r="I13" t="n">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J13" t="n">
-        <v>77.86</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>80.23</v>
+        <v>67.11</v>
       </c>
       <c r="L13" t="n">
-        <v>75.81</v>
+        <v>63.11</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5708</v>
+        <v>5962</v>
       </c>
       <c r="O13" t="n">
-        <v>6494</v>
+        <v>6502</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.47</v>
+        <v>17.45</v>
       </c>
       <c r="C14" t="n">
-        <v>14.79</v>
+        <v>17.76</v>
       </c>
       <c r="D14" t="n">
-        <v>14.22</v>
+        <v>17.19</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F14" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G14" t="n">
-        <v>131</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="I14" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="J14" t="n">
-        <v>80.75</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>82.34</v>
+        <v>68.27</v>
       </c>
       <c r="L14" t="n">
-        <v>79.73999999999999</v>
+        <v>62.48</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6254</v>
+        <v>6561</v>
       </c>
       <c r="O14" t="n">
-        <v>6491</v>
+        <v>6539</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.34</v>
+        <v>17.1</v>
       </c>
       <c r="C15" t="n">
-        <v>14.4</v>
+        <v>17.35</v>
       </c>
       <c r="D15" t="n">
-        <v>14.25</v>
+        <v>16.86</v>
       </c>
       <c r="E15" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F15" t="n">
         <v>10.7</v>
       </c>
-      <c r="F15" t="n">
-        <v>10.3</v>
-      </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>246</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="J15" t="n">
-        <v>79.29000000000001</v>
+        <v>67.38</v>
       </c>
       <c r="K15" t="n">
-        <v>80.34999999999999</v>
+        <v>67.78</v>
       </c>
       <c r="L15" t="n">
-        <v>77.13</v>
+        <v>66.55</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3949</v>
+        <v>6671</v>
       </c>
       <c r="O15" t="n">
-        <v>6425</v>
+        <v>6536</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.56</v>
+        <v>16.52</v>
       </c>
       <c r="C16" t="n">
-        <v>14.75</v>
+        <v>17.36</v>
       </c>
       <c r="D16" t="n">
-        <v>14.34</v>
+        <v>16.01</v>
       </c>
       <c r="E16" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F16" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G16" t="n">
+        <v>301</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>69.84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="L16" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6681</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6525</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J16" t="n">
-        <v>78.20999999999999</v>
-      </c>
-      <c r="K16" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="L16" t="n">
-        <v>75.43000000000001</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2449</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6420</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14.79</v>
+        <v>15.55</v>
       </c>
       <c r="C17" t="n">
-        <v>14.98</v>
+        <v>16.32</v>
       </c>
       <c r="D17" t="n">
-        <v>14.63</v>
+        <v>15.05</v>
       </c>
       <c r="E17" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F17" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H17" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="I17" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="J17" t="n">
-        <v>77.20999999999999</v>
+        <v>75.25</v>
       </c>
       <c r="K17" t="n">
-        <v>79.73999999999999</v>
+        <v>78.77</v>
       </c>
       <c r="L17" t="n">
-        <v>74.54000000000001</v>
+        <v>71.11</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6729</v>
       </c>
       <c r="O17" t="n">
-        <v>6411</v>
+        <v>6556</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
@@ -1498,187 +1498,187 @@
         <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.24</v>
+        <v>15.04</v>
       </c>
       <c r="C18" t="n">
-        <v>15.48</v>
+        <v>15.26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14.82</v>
       </c>
       <c r="E18" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="F18" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="H18" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="I18" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="J18" t="n">
-        <v>74.68000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="K18" t="n">
-        <v>75.5</v>
+        <v>80.23</v>
       </c>
       <c r="L18" t="n">
-        <v>73.42</v>
+        <v>75.81</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5708</v>
       </c>
       <c r="O18" t="n">
-        <v>6411</v>
+        <v>6494</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.62</v>
+        <v>14.47</v>
       </c>
       <c r="C19" t="n">
-        <v>15.76</v>
+        <v>14.79</v>
       </c>
       <c r="D19" t="n">
-        <v>15.46</v>
+        <v>14.22</v>
       </c>
       <c r="E19" t="n">
-        <v>12.3</v>
+        <v>11.1</v>
       </c>
       <c r="F19" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="I19" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="J19" t="n">
-        <v>81.47</v>
+        <v>80.75</v>
       </c>
       <c r="K19" t="n">
-        <v>89.01000000000001</v>
+        <v>82.34</v>
       </c>
       <c r="L19" t="n">
-        <v>74.23</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O19" t="n">
-        <v>6402</v>
+        <v>6491</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.86</v>
+        <v>14.34</v>
       </c>
       <c r="C20" t="n">
-        <v>16.08</v>
+        <v>14.4</v>
       </c>
       <c r="D20" t="n">
-        <v>15.66</v>
+        <v>14.25</v>
       </c>
       <c r="E20" t="n">
-        <v>13.8</v>
+        <v>10.7</v>
       </c>
       <c r="F20" t="n">
-        <v>13.7</v>
+        <v>10.3</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H20" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="I20" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="J20" t="n">
-        <v>87.95999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>89.39</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>86.37</v>
+        <v>77.13</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O20" t="n">
-        <v>6411</v>
+        <v>6425</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1687,50 +1687,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.22</v>
+        <v>14.56</v>
       </c>
       <c r="C21" t="n">
-        <v>16.35</v>
+        <v>14.75</v>
       </c>
       <c r="D21" t="n">
-        <v>16.12</v>
+        <v>14.34</v>
       </c>
       <c r="E21" t="n">
-        <v>13.7</v>
+        <v>10.8</v>
       </c>
       <c r="F21" t="n">
-        <v>13.4</v>
+        <v>10.4</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="I21" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="J21" t="n">
-        <v>85.42</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>87.15000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>83.22</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O21" t="n">
-        <v>6405</v>
+        <v>6420</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -1739,7 +1739,7 @@
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1748,41 +1748,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.39</v>
+        <v>14.79</v>
       </c>
       <c r="C22" t="n">
-        <v>16.55</v>
+        <v>14.98</v>
       </c>
       <c r="D22" t="n">
-        <v>16.22</v>
+        <v>14.63</v>
       </c>
       <c r="E22" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
       <c r="F22" t="n">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="J22" t="n">
-        <v>85.56999999999999</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>87.13</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>84.14</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1791,16 +1791,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -1809,41 +1809,41 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.68</v>
+        <v>15.24</v>
       </c>
       <c r="C23" t="n">
-        <v>16.76</v>
+        <v>15.48</v>
       </c>
       <c r="D23" t="n">
-        <v>16.63</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>13.9</v>
+        <v>10.7</v>
       </c>
       <c r="F23" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="I23" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="J23" t="n">
-        <v>84.16</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>86.08</v>
+        <v>75.5</v>
       </c>
       <c r="L23" t="n">
-        <v>81.98</v>
+        <v>73.42</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1855,13 +1855,13 @@
         <v>6411</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -1870,41 +1870,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.64</v>
+        <v>15.62</v>
       </c>
       <c r="C24" t="n">
-        <v>16.72</v>
+        <v>15.76</v>
       </c>
       <c r="D24" t="n">
-        <v>16.62</v>
+        <v>15.46</v>
       </c>
       <c r="E24" t="n">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="F24" t="n">
-        <v>14.3</v>
+        <v>10.8</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.19</v>
       </c>
-      <c r="I24" t="n">
-        <v>0.15</v>
-      </c>
       <c r="J24" t="n">
-        <v>89.45</v>
+        <v>81.47</v>
       </c>
       <c r="K24" t="n">
-        <v>91.73999999999999</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>85.8</v>
+        <v>74.23</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1913,13 +1913,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6411</v>
+        <v>6402</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -1931,41 +1931,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.73</v>
+        <v>15.86</v>
       </c>
       <c r="C25" t="n">
-        <v>16.91</v>
+        <v>16.08</v>
       </c>
       <c r="D25" t="n">
-        <v>16.64</v>
+        <v>15.66</v>
       </c>
       <c r="E25" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="F25" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J25" t="n">
-        <v>91.16</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>91.98999999999999</v>
+        <v>89.39</v>
       </c>
       <c r="L25" t="n">
-        <v>89.92</v>
+        <v>86.37</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -1992,41 +1992,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.79</v>
+        <v>16.22</v>
       </c>
       <c r="C26" t="n">
-        <v>16.87</v>
+        <v>16.35</v>
       </c>
       <c r="D26" t="n">
-        <v>16.65</v>
+        <v>16.12</v>
       </c>
       <c r="E26" t="n">
-        <v>15.5</v>
+        <v>13.7</v>
       </c>
       <c r="F26" t="n">
-        <v>15.3</v>
+        <v>13.4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="I26" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="J26" t="n">
-        <v>92.09999999999999</v>
+        <v>85.42</v>
       </c>
       <c r="K26" t="n">
-        <v>93.45</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>90.81999999999999</v>
+        <v>83.22</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2035,13 +2035,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6420</v>
+        <v>6405</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2053,41 +2053,41 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.6</v>
+        <v>16.39</v>
       </c>
       <c r="C27" t="n">
-        <v>16.66</v>
+        <v>16.55</v>
       </c>
       <c r="D27" t="n">
-        <v>16.52</v>
+        <v>16.22</v>
       </c>
       <c r="E27" t="n">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="F27" t="n">
-        <v>15.6</v>
+        <v>13.8</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="I27" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="J27" t="n">
-        <v>95.29000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>96.45999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="L27" t="n">
-        <v>93.84</v>
+        <v>84.14</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2096,16 +2096,16 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2114,41 +2114,41 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.91</v>
+        <v>16.68</v>
       </c>
       <c r="C28" t="n">
-        <v>17.19</v>
+        <v>16.76</v>
       </c>
       <c r="D28" t="n">
-        <v>16.69</v>
+        <v>16.63</v>
       </c>
       <c r="E28" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="F28" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="I28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="J28" t="n">
-        <v>94.18000000000001</v>
+        <v>84.16</v>
       </c>
       <c r="K28" t="n">
-        <v>96.09</v>
+        <v>86.08</v>
       </c>
       <c r="L28" t="n">
-        <v>90.87</v>
+        <v>81.98</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6442</v>
+        <v>6411</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2175,56 +2175,56 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.68</v>
+        <v>16.64</v>
       </c>
       <c r="C29" t="n">
-        <v>18.12</v>
+        <v>16.72</v>
       </c>
       <c r="D29" t="n">
-        <v>17.08</v>
+        <v>16.62</v>
       </c>
       <c r="E29" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="F29" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="I29" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="J29" t="n">
-        <v>86.59</v>
+        <v>89.45</v>
       </c>
       <c r="K29" t="n">
-        <v>93.40000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>80.54000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6451</v>
+        <v>6411</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -2236,59 +2236,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.95</v>
+        <v>16.73</v>
       </c>
       <c r="C30" t="n">
-        <v>21.08</v>
+        <v>16.91</v>
       </c>
       <c r="D30" t="n">
-        <v>18.04</v>
+        <v>16.64</v>
       </c>
       <c r="E30" t="n">
-        <v>12.9</v>
+        <v>15.2</v>
       </c>
       <c r="F30" t="n">
-        <v>11.6</v>
+        <v>15.1</v>
       </c>
       <c r="G30" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.82</v>
+        <v>0.16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="J30" t="n">
-        <v>64.73999999999999</v>
+        <v>91.16</v>
       </c>
       <c r="K30" t="n">
-        <v>79.75</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>55.98</v>
+        <v>89.92</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6474</v>
+        <v>6417</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2297,59 +2297,59 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.54</v>
+        <v>16.79</v>
       </c>
       <c r="C31" t="n">
-        <v>21.83</v>
+        <v>16.87</v>
       </c>
       <c r="D31" t="n">
-        <v>21.18</v>
+        <v>16.65</v>
       </c>
       <c r="E31" t="n">
-        <v>11.6</v>
+        <v>15.5</v>
       </c>
       <c r="F31" t="n">
-        <v>10.7</v>
+        <v>15.3</v>
       </c>
       <c r="G31" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.19</v>
+        <v>0.14</v>
       </c>
       <c r="I31" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="J31" t="n">
-        <v>53.45</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>58.22</v>
+        <v>93.45</v>
       </c>
       <c r="L31" t="n">
-        <v>49.34</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6485</v>
+        <v>6420</v>
       </c>
       <c r="P31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2358,785 +2358,785 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.02</v>
+        <v>16.6</v>
       </c>
       <c r="C32" t="n">
-        <v>22.16</v>
+        <v>16.66</v>
       </c>
       <c r="D32" t="n">
-        <v>21.88</v>
+        <v>16.52</v>
       </c>
       <c r="E32" t="n">
-        <v>11.1</v>
+        <v>15.8</v>
       </c>
       <c r="F32" t="n">
-        <v>10.4</v>
+        <v>15.6</v>
       </c>
       <c r="G32" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.31</v>
+        <v>0.08</v>
       </c>
       <c r="I32" t="n">
-        <v>1.24</v>
+        <v>0.06</v>
       </c>
       <c r="J32" t="n">
-        <v>50.18</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>52.66</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>47.74</v>
+        <v>93.84</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4352</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6511</v>
+        <v>6425</v>
       </c>
       <c r="P32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.31</v>
+        <v>16.91</v>
       </c>
       <c r="C33" t="n">
-        <v>22.81</v>
+        <v>17.19</v>
       </c>
       <c r="D33" t="n">
-        <v>22.04</v>
+        <v>16.69</v>
       </c>
       <c r="E33" t="n">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
       <c r="F33" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="G33" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.34</v>
+        <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>1.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>50.19</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>51.75</v>
+        <v>96.09</v>
       </c>
       <c r="L33" t="n">
-        <v>47.76</v>
+        <v>90.87</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5406</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6539</v>
+        <v>6442</v>
       </c>
       <c r="P33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.68</v>
+        <v>17.68</v>
       </c>
       <c r="C34" t="n">
-        <v>23.1</v>
+        <v>18.12</v>
       </c>
       <c r="D34" t="n">
-        <v>22.11</v>
+        <v>17.08</v>
       </c>
       <c r="E34" t="n">
-        <v>11.3</v>
+        <v>15.3</v>
       </c>
       <c r="F34" t="n">
-        <v>10.7</v>
+        <v>14.6</v>
       </c>
       <c r="G34" t="n">
-        <v>384</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>1.4</v>
+        <v>0.27</v>
       </c>
       <c r="I34" t="n">
-        <v>1.32</v>
+        <v>0.12</v>
       </c>
       <c r="J34" t="n">
-        <v>48.82</v>
+        <v>86.59</v>
       </c>
       <c r="K34" t="n">
-        <v>51.28</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>47.13</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6743</v>
+        <v>685</v>
       </c>
       <c r="O34" t="n">
-        <v>6573</v>
+        <v>6451</v>
       </c>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.01</v>
+        <v>19.95</v>
       </c>
       <c r="C35" t="n">
-        <v>22.58</v>
+        <v>21.08</v>
       </c>
       <c r="D35" t="n">
-        <v>21.62</v>
+        <v>18.04</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="F35" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="G35" t="n">
-        <v>452</v>
+        <v>18</v>
       </c>
       <c r="H35" t="n">
-        <v>1.33</v>
+        <v>0.82</v>
       </c>
       <c r="I35" t="n">
-        <v>1.27</v>
+        <v>0.41</v>
       </c>
       <c r="J35" t="n">
-        <v>49.71</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>51.65</v>
+        <v>79.75</v>
       </c>
       <c r="L35" t="n">
-        <v>46.69</v>
+        <v>55.98</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6767</v>
+        <v>1926</v>
       </c>
       <c r="O35" t="n">
-        <v>6576</v>
+        <v>6474</v>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.59</v>
+        <v>21.54</v>
       </c>
       <c r="C36" t="n">
-        <v>22.58</v>
+        <v>21.83</v>
       </c>
       <c r="D36" t="n">
-        <v>20.76</v>
+        <v>21.18</v>
       </c>
       <c r="E36" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="F36" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G36" t="n">
-        <v>564</v>
+        <v>44</v>
       </c>
       <c r="H36" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="J36" t="n">
-        <v>51.87</v>
+        <v>53.45</v>
       </c>
       <c r="K36" t="n">
-        <v>56.03</v>
+        <v>58.22</v>
       </c>
       <c r="L36" t="n">
-        <v>45.92</v>
+        <v>49.34</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6796</v>
+        <v>2410</v>
       </c>
       <c r="O36" t="n">
-        <v>6599</v>
+        <v>6485</v>
       </c>
       <c r="P36" t="n">
         <v>6</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R36" t="n">
         <v>5</v>
       </c>
       <c r="S36" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.19</v>
+        <v>22.02</v>
       </c>
       <c r="C37" t="n">
-        <v>20.64</v>
+        <v>22.16</v>
       </c>
       <c r="D37" t="n">
-        <v>19.53</v>
+        <v>21.88</v>
       </c>
       <c r="E37" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="F37" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="G37" t="n">
-        <v>426</v>
+        <v>111</v>
       </c>
       <c r="H37" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>1.24</v>
       </c>
       <c r="J37" t="n">
-        <v>55.29</v>
+        <v>50.18</v>
       </c>
       <c r="K37" t="n">
-        <v>57.87</v>
+        <v>52.66</v>
       </c>
       <c r="L37" t="n">
-        <v>52.99</v>
+        <v>47.74</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6767</v>
+        <v>4352</v>
       </c>
       <c r="O37" t="n">
-        <v>6576</v>
+        <v>6511</v>
       </c>
       <c r="P37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q37" t="n">
+        <v>7</v>
+      </c>
+      <c r="R37" t="n">
         <v>6</v>
       </c>
-      <c r="R37" t="n">
-        <v>5</v>
-      </c>
       <c r="S37" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18.89</v>
+        <v>22.31</v>
       </c>
       <c r="C38" t="n">
-        <v>19.62</v>
+        <v>22.81</v>
       </c>
       <c r="D38" t="n">
-        <v>18.08</v>
+        <v>22.04</v>
       </c>
       <c r="E38" t="n">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="F38" t="n">
         <v>10.9</v>
       </c>
       <c r="G38" t="n">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="H38" t="n">
-        <v>0.66</v>
+        <v>1.34</v>
       </c>
       <c r="I38" t="n">
-        <v>0.35</v>
+        <v>1.28</v>
       </c>
       <c r="J38" t="n">
-        <v>69.7</v>
+        <v>50.19</v>
       </c>
       <c r="K38" t="n">
-        <v>82.87</v>
+        <v>51.75</v>
       </c>
       <c r="L38" t="n">
-        <v>57.89</v>
+        <v>47.76</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6691</v>
+        <v>5406</v>
       </c>
       <c r="O38" t="n">
-        <v>6514</v>
+        <v>6539</v>
       </c>
       <c r="P38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.5</v>
+        <v>22.68</v>
       </c>
       <c r="C39" t="n">
-        <v>17.9</v>
+        <v>23.1</v>
       </c>
       <c r="D39" t="n">
-        <v>17.26</v>
+        <v>22.11</v>
       </c>
       <c r="E39" t="n">
-        <v>14.7</v>
+        <v>11.3</v>
       </c>
       <c r="F39" t="n">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="G39" t="n">
-        <v>43</v>
+        <v>384</v>
       </c>
       <c r="H39" t="n">
-        <v>0.31</v>
+        <v>1.4</v>
       </c>
       <c r="I39" t="n">
-        <v>0.25</v>
+        <v>1.32</v>
       </c>
       <c r="J39" t="n">
-        <v>84.14</v>
+        <v>48.82</v>
       </c>
       <c r="K39" t="n">
-        <v>87.05</v>
+        <v>51.28</v>
       </c>
       <c r="L39" t="n">
-        <v>79.48999999999999</v>
+        <v>47.13</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3786</v>
+        <v>6743</v>
       </c>
       <c r="O39" t="n">
-        <v>6422</v>
+        <v>6573</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.02</v>
+        <v>22.01</v>
       </c>
       <c r="C40" t="n">
-        <v>17.27</v>
+        <v>22.58</v>
       </c>
       <c r="D40" t="n">
-        <v>16.92</v>
+        <v>21.62</v>
       </c>
       <c r="E40" t="n">
-        <v>14.7</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="H40" t="n">
-        <v>0.25</v>
+        <v>1.33</v>
       </c>
       <c r="I40" t="n">
-        <v>0.21</v>
+        <v>1.27</v>
       </c>
       <c r="J40" t="n">
-        <v>86.8</v>
+        <v>49.71</v>
       </c>
       <c r="K40" t="n">
-        <v>88.91</v>
+        <v>51.65</v>
       </c>
       <c r="L40" t="n">
-        <v>81.98999999999999</v>
+        <v>46.69</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1246</v>
+        <v>6767</v>
       </c>
       <c r="O40" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.89</v>
+        <v>21.59</v>
       </c>
       <c r="C41" t="n">
-        <v>17.03</v>
+        <v>22.58</v>
       </c>
       <c r="D41" t="n">
-        <v>16.78</v>
+        <v>20.76</v>
       </c>
       <c r="E41" t="n">
-        <v>14.9</v>
+        <v>11.2</v>
       </c>
       <c r="F41" t="n">
-        <v>14.6</v>
+        <v>10.3</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="H41" t="n">
-        <v>0.21</v>
+        <v>1.24</v>
       </c>
       <c r="I41" t="n">
-        <v>0.18</v>
+        <v>1.07</v>
       </c>
       <c r="J41" t="n">
-        <v>88.48999999999999</v>
+        <v>51.87</v>
       </c>
       <c r="K41" t="n">
-        <v>90.31</v>
+        <v>56.03</v>
       </c>
       <c r="L41" t="n">
-        <v>85.76000000000001</v>
+        <v>45.92</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6796</v>
       </c>
       <c r="O41" t="n">
-        <v>6417</v>
+        <v>6599</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.13</v>
+        <v>20.19</v>
       </c>
       <c r="C42" t="n">
-        <v>17.32</v>
+        <v>20.64</v>
       </c>
       <c r="D42" t="n">
-        <v>16.89</v>
+        <v>19.53</v>
       </c>
       <c r="E42" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="F42" t="n">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H42" t="n">
-        <v>0.27</v>
+        <v>1.05</v>
       </c>
       <c r="I42" t="n">
-        <v>0.22</v>
+        <v>0.95</v>
       </c>
       <c r="J42" t="n">
-        <v>85.90000000000001</v>
+        <v>55.29</v>
       </c>
       <c r="K42" t="n">
-        <v>88.63</v>
+        <v>57.87</v>
       </c>
       <c r="L42" t="n">
-        <v>83.40000000000001</v>
+        <v>52.99</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6767</v>
       </c>
       <c r="O42" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.01</v>
+        <v>18.89</v>
       </c>
       <c r="C43" t="n">
-        <v>17.08</v>
+        <v>19.62</v>
       </c>
       <c r="D43" t="n">
-        <v>16.93</v>
+        <v>18.08</v>
       </c>
       <c r="E43" t="n">
-        <v>15</v>
+        <v>13.1</v>
       </c>
       <c r="F43" t="n">
-        <v>14.8</v>
+        <v>10.9</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H43" t="n">
-        <v>0.22</v>
+        <v>0.66</v>
       </c>
       <c r="I43" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="J43" t="n">
-        <v>88.16</v>
+        <v>69.7</v>
       </c>
       <c r="K43" t="n">
-        <v>88.7</v>
+        <v>82.87</v>
       </c>
       <c r="L43" t="n">
-        <v>87.34999999999999</v>
+        <v>57.89</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="O43" t="n">
-        <v>6414</v>
+        <v>6514</v>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 08:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.07</v>
+        <v>17.5</v>
       </c>
       <c r="C44" t="n">
-        <v>17.29</v>
+        <v>17.9</v>
       </c>
       <c r="D44" t="n">
-        <v>16.93</v>
+        <v>17.26</v>
       </c>
       <c r="E44" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="F44" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="J44" t="n">
-        <v>88.06999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="K44" t="n">
-        <v>89.45999999999999</v>
+        <v>87.05</v>
       </c>
       <c r="L44" t="n">
-        <v>85.97</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3786</v>
       </c>
       <c r="O44" t="n">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -3151,59 +3151,59 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 02:00:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.44</v>
+        <v>17.02</v>
       </c>
       <c r="C45" t="n">
-        <v>17.52</v>
+        <v>17.27</v>
       </c>
       <c r="D45" t="n">
-        <v>17.31</v>
+        <v>16.92</v>
       </c>
       <c r="E45" t="n">
         <v>14.7</v>
       </c>
       <c r="F45" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="I45" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="J45" t="n">
-        <v>84.31999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="K45" t="n">
-        <v>85.27</v>
+        <v>88.91</v>
       </c>
       <c r="L45" t="n">
-        <v>82.56999999999999</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="O45" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3212,41 +3212,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 01:00:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.22</v>
+        <v>16.89</v>
       </c>
       <c r="C46" t="n">
-        <v>17.34</v>
+        <v>17.03</v>
       </c>
       <c r="D46" t="n">
-        <v>17.11</v>
+        <v>16.78</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F46" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="I46" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="J46" t="n">
-        <v>87.37</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>88.34999999999999</v>
+        <v>90.31</v>
       </c>
       <c r="L46" t="n">
-        <v>86.23</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -3273,41 +3273,41 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.38</v>
+        <v>17.13</v>
       </c>
       <c r="C47" t="n">
-        <v>17.5</v>
+        <v>17.32</v>
       </c>
       <c r="D47" t="n">
-        <v>17.22</v>
+        <v>16.89</v>
       </c>
       <c r="E47" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="F47" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I47" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="J47" t="n">
-        <v>87.89</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>89.09</v>
+        <v>88.63</v>
       </c>
       <c r="L47" t="n">
-        <v>87.03</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6408</v>
+        <v>6414</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -3334,23 +3334,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 23:00:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.51</v>
+        <v>17.01</v>
       </c>
       <c r="C48" t="n">
-        <v>17.64</v>
+        <v>17.08</v>
       </c>
       <c r="D48" t="n">
-        <v>17.34</v>
+        <v>16.93</v>
       </c>
       <c r="E48" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3359,16 +3359,16 @@
         <v>0.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J48" t="n">
-        <v>88.95</v>
+        <v>88.16</v>
       </c>
       <c r="K48" t="n">
-        <v>90.3</v>
+        <v>88.7</v>
       </c>
       <c r="L48" t="n">
-        <v>87.78</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6437</v>
+        <v>6414</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3395,20 +3395,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.73</v>
+        <v>17.07</v>
       </c>
       <c r="C49" t="n">
-        <v>18.06</v>
+        <v>17.29</v>
       </c>
       <c r="D49" t="n">
-        <v>17.42</v>
+        <v>16.93</v>
       </c>
       <c r="E49" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
         <v>14.9</v>
@@ -3417,19 +3417,19 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="I49" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
-        <v>85.27</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>88.19</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>81.95</v>
+        <v>85.97</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3438,10 +3438,10 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6457</v>
+        <v>6417</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,59 +528,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.3</v>
+        <v>14.28</v>
       </c>
       <c r="C2" t="n">
-        <v>15.38</v>
+        <v>14.32</v>
       </c>
       <c r="D2" t="n">
-        <v>15.22</v>
+        <v>14.25</v>
       </c>
       <c r="E2" t="n">
-        <v>13.2</v>
+        <v>14.2</v>
       </c>
       <c r="F2" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>88.06999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="K2" t="n">
-        <v>89.27</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>86.81999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3278</v>
       </c>
       <c r="O2" t="n">
-        <v>6408</v>
+        <v>6420</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -589,59 +589,59 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.65</v>
+        <v>14.35</v>
       </c>
       <c r="C3" t="n">
-        <v>15.83</v>
+        <v>14.59</v>
       </c>
       <c r="D3" t="n">
-        <v>15.43</v>
+        <v>14.2</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9</v>
+        <v>14.2</v>
       </c>
       <c r="F3" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.27</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>84.34999999999999</v>
+        <v>99.56</v>
       </c>
       <c r="K3" t="n">
-        <v>86.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>81.81</v>
+        <v>97.86</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="O3" t="n">
         <v>6411</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -650,41 +650,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.77</v>
+        <v>14.73</v>
       </c>
       <c r="C4" t="n">
-        <v>16.04</v>
+        <v>14.93</v>
       </c>
       <c r="D4" t="n">
-        <v>15.59</v>
+        <v>14.58</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
       <c r="J4" t="n">
-        <v>84</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>86.05</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>80.77</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -693,16 +693,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6414</v>
+        <v>6402</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -711,41 +711,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.89</v>
+        <v>14.59</v>
       </c>
       <c r="C5" t="n">
-        <v>16.09</v>
+        <v>14.64</v>
       </c>
       <c r="D5" t="n">
-        <v>15.55</v>
+        <v>14.53</v>
       </c>
       <c r="E5" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5</v>
+        <v>14.2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>81.48999999999999</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>83.06999999999999</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>80.19</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -757,13 +757,13 @@
         <v>6405</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -772,41 +772,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.43</v>
+        <v>14.4</v>
       </c>
       <c r="C6" t="n">
-        <v>15.49</v>
+        <v>14.56</v>
       </c>
       <c r="D6" t="n">
-        <v>15.38</v>
+        <v>14.28</v>
       </c>
       <c r="E6" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="F6" t="n">
-        <v>12.6</v>
+        <v>14.1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.27</v>
+        <v>0.02</v>
       </c>
       <c r="I6" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>83.98999999999999</v>
+        <v>98.81</v>
       </c>
       <c r="K6" t="n">
-        <v>85.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>83.27</v>
+        <v>97.73</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -815,16 +815,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6408</v>
+        <v>6405</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -833,41 +833,41 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.57</v>
+        <v>14.31</v>
       </c>
       <c r="C7" t="n">
-        <v>15.65</v>
+        <v>14.48</v>
       </c>
       <c r="D7" t="n">
-        <v>15.47</v>
+        <v>14.24</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7</v>
+        <v>14.2</v>
       </c>
       <c r="F7" t="n">
-        <v>12.5</v>
+        <v>14.1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>83.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="K7" t="n">
-        <v>84.86</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>82.39</v>
+        <v>98</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -894,41 +894,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.77</v>
+        <v>14.91</v>
       </c>
       <c r="C8" t="n">
-        <v>15.92</v>
+        <v>15.38</v>
       </c>
       <c r="D8" t="n">
-        <v>15.58</v>
+        <v>14.51</v>
       </c>
       <c r="E8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F8" t="n">
         <v>13.1</v>
       </c>
-      <c r="F8" t="n">
-        <v>12.7</v>
-      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="I8" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="J8" t="n">
-        <v>84.48</v>
+        <v>92.72</v>
       </c>
       <c r="K8" t="n">
-        <v>86.84</v>
+        <v>97.28</v>
       </c>
       <c r="L8" t="n">
-        <v>81.94</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6417</v>
+        <v>6408</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -955,41 +955,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.16</v>
+        <v>15.65</v>
       </c>
       <c r="C9" t="n">
-        <v>16.42</v>
+        <v>15.83</v>
       </c>
       <c r="D9" t="n">
-        <v>15.94</v>
+        <v>15.43</v>
       </c>
       <c r="E9" t="n">
         <v>12.9</v>
       </c>
       <c r="F9" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="I9" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="J9" t="n">
-        <v>81.48999999999999</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>84.55</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>78.12</v>
+        <v>81.81</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -1007,7 +1007,7 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1016,59 +1016,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.77</v>
+        <v>15.77</v>
       </c>
       <c r="C10" t="n">
-        <v>17.13</v>
+        <v>16.04</v>
       </c>
       <c r="D10" t="n">
-        <v>16.4</v>
+        <v>15.59</v>
       </c>
       <c r="E10" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
       <c r="I10" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="J10" t="n">
-        <v>75.39</v>
+        <v>84</v>
       </c>
       <c r="K10" t="n">
-        <v>78.58</v>
+        <v>86.05</v>
       </c>
       <c r="L10" t="n">
-        <v>72.19</v>
+        <v>80.77</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6431</v>
+        <v>6414</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1077,59 +1077,59 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17.34</v>
+        <v>15.89</v>
       </c>
       <c r="C11" t="n">
-        <v>17.55</v>
+        <v>16.09</v>
       </c>
       <c r="D11" t="n">
-        <v>17.15</v>
+        <v>15.55</v>
       </c>
       <c r="E11" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F11" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="I11" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
-        <v>70.43000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>72.41</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>68.52</v>
+        <v>80.19</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3144</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6459</v>
+        <v>6405</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1138,355 +1138,355 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.83</v>
+        <v>15.43</v>
       </c>
       <c r="C12" t="n">
-        <v>18.09</v>
+        <v>15.49</v>
       </c>
       <c r="D12" t="n">
-        <v>17.42</v>
+        <v>15.38</v>
       </c>
       <c r="E12" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F12" t="n">
-        <v>10.6</v>
+        <v>12.6</v>
       </c>
       <c r="G12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="J12" t="n">
-        <v>66.04000000000001</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>69.8</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>62.77</v>
+        <v>83.27</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4749</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6491</v>
+        <v>6408</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.68</v>
+        <v>15.57</v>
       </c>
       <c r="C13" t="n">
-        <v>17.86</v>
+        <v>15.65</v>
       </c>
       <c r="D13" t="n">
-        <v>17.49</v>
+        <v>15.47</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="F13" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="G13" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7</v>
+        <v>0.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="J13" t="n">
-        <v>65.15000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>67.11</v>
+        <v>84.86</v>
       </c>
       <c r="L13" t="n">
-        <v>63.11</v>
+        <v>82.39</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5962</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6502</v>
+        <v>6411</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.45</v>
+        <v>15.77</v>
       </c>
       <c r="C14" t="n">
-        <v>17.76</v>
+        <v>15.92</v>
       </c>
       <c r="D14" t="n">
-        <v>17.19</v>
+        <v>15.58</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9</v>
+        <v>13.1</v>
       </c>
       <c r="F14" t="n">
-        <v>10.4</v>
+        <v>12.7</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.68</v>
+        <v>0.27</v>
       </c>
       <c r="I14" t="n">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="J14" t="n">
-        <v>65.79000000000001</v>
+        <v>84.48</v>
       </c>
       <c r="K14" t="n">
-        <v>68.27</v>
+        <v>86.84</v>
       </c>
       <c r="L14" t="n">
-        <v>62.48</v>
+        <v>81.94</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6561</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6539</v>
+        <v>6417</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.1</v>
+        <v>16.16</v>
       </c>
       <c r="C15" t="n">
-        <v>17.35</v>
+        <v>16.42</v>
       </c>
       <c r="D15" t="n">
-        <v>16.86</v>
+        <v>15.94</v>
       </c>
       <c r="E15" t="n">
-        <v>10.9</v>
+        <v>12.9</v>
       </c>
       <c r="F15" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="G15" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="I15" t="n">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
       <c r="J15" t="n">
-        <v>67.38</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>67.78</v>
+        <v>84.55</v>
       </c>
       <c r="L15" t="n">
-        <v>66.55</v>
+        <v>78.12</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6671</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6536</v>
+        <v>6420</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.52</v>
+        <v>16.77</v>
       </c>
       <c r="C16" t="n">
-        <v>17.36</v>
+        <v>17.13</v>
       </c>
       <c r="D16" t="n">
-        <v>16.01</v>
+        <v>16.4</v>
       </c>
       <c r="E16" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="F16" t="n">
-        <v>10.7</v>
+        <v>11.9</v>
       </c>
       <c r="G16" t="n">
-        <v>301</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="J16" t="n">
-        <v>69.84</v>
+        <v>75.39</v>
       </c>
       <c r="K16" t="n">
-        <v>72.16</v>
+        <v>78.58</v>
       </c>
       <c r="L16" t="n">
-        <v>66.34999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6681</v>
+        <v>1164</v>
       </c>
       <c r="O16" t="n">
-        <v>6525</v>
+        <v>6431</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.55</v>
+        <v>17.34</v>
       </c>
       <c r="C17" t="n">
-        <v>16.32</v>
+        <v>17.55</v>
       </c>
       <c r="D17" t="n">
-        <v>15.05</v>
+        <v>17.15</v>
       </c>
       <c r="E17" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="F17" t="n">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="G17" t="n">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="H17" t="n">
-        <v>0.43</v>
+        <v>0.58</v>
       </c>
       <c r="I17" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="J17" t="n">
-        <v>75.25</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>78.77</v>
+        <v>72.41</v>
       </c>
       <c r="L17" t="n">
-        <v>71.11</v>
+        <v>68.52</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6729</v>
+        <v>3144</v>
       </c>
       <c r="O17" t="n">
-        <v>6556</v>
+        <v>6459</v>
       </c>
       <c r="P17" t="n">
         <v>3</v>
@@ -1495,364 +1495,364 @@
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.04</v>
+        <v>17.83</v>
       </c>
       <c r="C18" t="n">
-        <v>15.26</v>
+        <v>18.09</v>
       </c>
       <c r="D18" t="n">
-        <v>14.82</v>
+        <v>17.42</v>
       </c>
       <c r="E18" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="G18" t="n">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H18" t="n">
-        <v>0.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
-        <v>77.86</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>80.23</v>
+        <v>69.8</v>
       </c>
       <c r="L18" t="n">
-        <v>75.81</v>
+        <v>62.77</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5708</v>
+        <v>4749</v>
       </c>
       <c r="O18" t="n">
-        <v>6494</v>
+        <v>6491</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14.47</v>
+        <v>17.68</v>
       </c>
       <c r="C19" t="n">
-        <v>14.79</v>
+        <v>17.86</v>
       </c>
       <c r="D19" t="n">
-        <v>14.22</v>
+        <v>17.49</v>
       </c>
       <c r="E19" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="H19" t="n">
-        <v>0.31</v>
+        <v>0.7</v>
       </c>
       <c r="I19" t="n">
-        <v>0.28</v>
+        <v>0.66</v>
       </c>
       <c r="J19" t="n">
-        <v>80.75</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>82.34</v>
+        <v>67.11</v>
       </c>
       <c r="L19" t="n">
-        <v>79.73999999999999</v>
+        <v>63.11</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6254</v>
+        <v>5962</v>
       </c>
       <c r="O19" t="n">
-        <v>6491</v>
+        <v>6502</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14.34</v>
+        <v>17.45</v>
       </c>
       <c r="C20" t="n">
-        <v>14.4</v>
+        <v>17.76</v>
       </c>
       <c r="D20" t="n">
-        <v>14.25</v>
+        <v>17.19</v>
       </c>
       <c r="E20" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="F20" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="G20" t="n">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="H20" t="n">
-        <v>0.33</v>
+        <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>0.32</v>
+        <v>0.62</v>
       </c>
       <c r="J20" t="n">
-        <v>79.29000000000001</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>80.34999999999999</v>
+        <v>68.27</v>
       </c>
       <c r="L20" t="n">
-        <v>77.13</v>
+        <v>62.48</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3949</v>
+        <v>6561</v>
       </c>
       <c r="O20" t="n">
-        <v>6425</v>
+        <v>6539</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.56</v>
+        <v>17.1</v>
       </c>
       <c r="C21" t="n">
-        <v>14.75</v>
+        <v>17.35</v>
       </c>
       <c r="D21" t="n">
-        <v>14.34</v>
+        <v>16.86</v>
       </c>
       <c r="E21" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F21" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G21" t="n">
+        <v>246</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J21" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="K21" t="n">
+        <v>67.78</v>
+      </c>
+      <c r="L21" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6671</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6536</v>
+      </c>
+      <c r="P21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J21" t="n">
-        <v>78.20999999999999</v>
-      </c>
-      <c r="K21" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="L21" t="n">
-        <v>75.43000000000001</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2449</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6420</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14.79</v>
+        <v>16.52</v>
       </c>
       <c r="C22" t="n">
-        <v>14.98</v>
+        <v>17.36</v>
       </c>
       <c r="D22" t="n">
-        <v>14.63</v>
+        <v>16.01</v>
       </c>
       <c r="E22" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F22" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="H22" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
-        <v>77.20999999999999</v>
+        <v>69.84</v>
       </c>
       <c r="K22" t="n">
-        <v>79.73999999999999</v>
+        <v>72.16</v>
       </c>
       <c r="L22" t="n">
-        <v>74.54000000000001</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6681</v>
       </c>
       <c r="O22" t="n">
-        <v>6411</v>
+        <v>6525</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
         <v>3</v>
       </c>
-      <c r="R22" t="n">
-        <v>2</v>
-      </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.24</v>
+        <v>15.55</v>
       </c>
       <c r="C23" t="n">
-        <v>15.48</v>
+        <v>16.32</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>15.05</v>
       </c>
       <c r="E23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F23" t="n">
         <v>10.7</v>
       </c>
-      <c r="F23" t="n">
-        <v>10.4</v>
-      </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H23" t="n">
         <v>0.43</v>
       </c>
       <c r="I23" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="J23" t="n">
-        <v>74.68000000000001</v>
+        <v>75.25</v>
       </c>
       <c r="K23" t="n">
-        <v>75.5</v>
+        <v>78.77</v>
       </c>
       <c r="L23" t="n">
-        <v>73.42</v>
+        <v>71.11</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>6729</v>
       </c>
       <c r="O23" t="n">
-        <v>6411</v>
+        <v>6556</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -1861,181 +1861,181 @@
         <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.62</v>
+        <v>15.04</v>
       </c>
       <c r="C24" t="n">
-        <v>15.76</v>
+        <v>15.26</v>
       </c>
       <c r="D24" t="n">
-        <v>15.46</v>
+        <v>14.82</v>
       </c>
       <c r="E24" t="n">
-        <v>12.3</v>
+        <v>11.1</v>
       </c>
       <c r="F24" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="H24" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="I24" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J24" t="n">
-        <v>81.47</v>
+        <v>77.86</v>
       </c>
       <c r="K24" t="n">
-        <v>89.01000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="L24" t="n">
-        <v>74.23</v>
+        <v>75.81</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5708</v>
       </c>
       <c r="O24" t="n">
-        <v>6402</v>
+        <v>6494</v>
       </c>
       <c r="P24" t="n">
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.86</v>
+        <v>14.47</v>
       </c>
       <c r="C25" t="n">
-        <v>16.08</v>
+        <v>14.79</v>
       </c>
       <c r="D25" t="n">
-        <v>15.66</v>
+        <v>14.22</v>
       </c>
       <c r="E25" t="n">
-        <v>13.8</v>
+        <v>11.1</v>
       </c>
       <c r="F25" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H25" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="I25" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="J25" t="n">
-        <v>87.95999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="K25" t="n">
-        <v>89.39</v>
+        <v>82.34</v>
       </c>
       <c r="L25" t="n">
-        <v>86.37</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O25" t="n">
-        <v>6411</v>
+        <v>6491</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.22</v>
+        <v>14.34</v>
       </c>
       <c r="C26" t="n">
-        <v>16.35</v>
+        <v>14.4</v>
       </c>
       <c r="D26" t="n">
-        <v>16.12</v>
+        <v>14.25</v>
       </c>
       <c r="E26" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="F26" t="n">
-        <v>13.4</v>
+        <v>10.3</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H26" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="I26" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="J26" t="n">
-        <v>85.42</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>87.15000000000001</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>83.22</v>
+        <v>77.13</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O26" t="n">
-        <v>6405</v>
+        <v>6425</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -2044,7 +2044,7 @@
         <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2053,59 +2053,59 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.39</v>
+        <v>14.56</v>
       </c>
       <c r="C27" t="n">
-        <v>16.55</v>
+        <v>14.75</v>
       </c>
       <c r="D27" t="n">
-        <v>16.22</v>
+        <v>14.34</v>
       </c>
       <c r="E27" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
       <c r="F27" t="n">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="I27" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="J27" t="n">
-        <v>85.56999999999999</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>87.13</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>84.14</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O27" t="n">
-        <v>6417</v>
+        <v>6420</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2114,41 +2114,41 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.68</v>
+        <v>14.79</v>
       </c>
       <c r="C28" t="n">
-        <v>16.76</v>
+        <v>14.98</v>
       </c>
       <c r="D28" t="n">
-        <v>16.63</v>
+        <v>14.63</v>
       </c>
       <c r="E28" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
       <c r="F28" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="J28" t="n">
-        <v>84.16</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>86.08</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>81.98</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2175,41 +2175,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16.64</v>
+        <v>15.24</v>
       </c>
       <c r="C29" t="n">
-        <v>16.72</v>
+        <v>15.48</v>
       </c>
       <c r="D29" t="n">
-        <v>16.62</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="F29" t="n">
-        <v>14.3</v>
+        <v>10.4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.19</v>
+        <v>0.43</v>
       </c>
       <c r="I29" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="J29" t="n">
-        <v>89.45</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>91.73999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="L29" t="n">
-        <v>85.8</v>
+        <v>73.42</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2221,13 +2221,13 @@
         <v>6411</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2236,41 +2236,41 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>16.73</v>
+        <v>15.62</v>
       </c>
       <c r="C30" t="n">
-        <v>16.91</v>
+        <v>15.76</v>
       </c>
       <c r="D30" t="n">
-        <v>16.64</v>
+        <v>15.46</v>
       </c>
       <c r="E30" t="n">
-        <v>15.2</v>
+        <v>12.3</v>
       </c>
       <c r="F30" t="n">
-        <v>15.1</v>
+        <v>10.8</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="I30" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J30" t="n">
-        <v>91.16</v>
+        <v>81.47</v>
       </c>
       <c r="K30" t="n">
-        <v>91.98999999999999</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>89.92</v>
+        <v>74.23</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2279,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6417</v>
+        <v>6402</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -2297,41 +2297,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.79</v>
+        <v>15.86</v>
       </c>
       <c r="C31" t="n">
-        <v>16.87</v>
+        <v>16.08</v>
       </c>
       <c r="D31" t="n">
-        <v>16.65</v>
+        <v>15.66</v>
       </c>
       <c r="E31" t="n">
-        <v>15.5</v>
+        <v>13.8</v>
       </c>
       <c r="F31" t="n">
-        <v>15.3</v>
+        <v>13.7</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="J31" t="n">
-        <v>92.09999999999999</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>93.45</v>
+        <v>89.39</v>
       </c>
       <c r="L31" t="n">
-        <v>90.81999999999999</v>
+        <v>86.37</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2358,41 +2358,41 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.6</v>
+        <v>16.22</v>
       </c>
       <c r="C32" t="n">
-        <v>16.66</v>
+        <v>16.35</v>
       </c>
       <c r="D32" t="n">
-        <v>16.52</v>
+        <v>16.12</v>
       </c>
       <c r="E32" t="n">
-        <v>15.8</v>
+        <v>13.7</v>
       </c>
       <c r="F32" t="n">
-        <v>15.6</v>
+        <v>13.4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="I32" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="J32" t="n">
-        <v>95.29000000000001</v>
+        <v>85.42</v>
       </c>
       <c r="K32" t="n">
-        <v>96.45999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>93.84</v>
+        <v>83.22</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2401,16 +2401,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6425</v>
+        <v>6405</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
         <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2419,41 +2419,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.91</v>
+        <v>16.39</v>
       </c>
       <c r="C33" t="n">
-        <v>17.19</v>
+        <v>16.55</v>
       </c>
       <c r="D33" t="n">
-        <v>16.69</v>
+        <v>16.22</v>
       </c>
       <c r="E33" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="F33" t="n">
-        <v>15.6</v>
+        <v>13.8</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="J33" t="n">
-        <v>94.18000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>96.09</v>
+        <v>87.13</v>
       </c>
       <c r="L33" t="n">
-        <v>90.87</v>
+        <v>84.14</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2462,16 +2462,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6442</v>
+        <v>6417</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="n">
         <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -2480,53 +2480,53 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.68</v>
+        <v>16.68</v>
       </c>
       <c r="C34" t="n">
-        <v>18.12</v>
+        <v>16.76</v>
       </c>
       <c r="D34" t="n">
-        <v>17.08</v>
+        <v>16.63</v>
       </c>
       <c r="E34" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="F34" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="I34" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J34" t="n">
-        <v>86.59</v>
+        <v>84.16</v>
       </c>
       <c r="K34" t="n">
-        <v>93.40000000000001</v>
+        <v>86.08</v>
       </c>
       <c r="L34" t="n">
-        <v>80.54000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6451</v>
+        <v>6411</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
         <v>2</v>
@@ -2541,59 +2541,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.95</v>
+        <v>16.64</v>
       </c>
       <c r="C35" t="n">
-        <v>21.08</v>
+        <v>16.72</v>
       </c>
       <c r="D35" t="n">
-        <v>18.04</v>
+        <v>16.62</v>
       </c>
       <c r="E35" t="n">
-        <v>12.9</v>
+        <v>14.8</v>
       </c>
       <c r="F35" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="G35" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="J35" t="n">
-        <v>64.73999999999999</v>
+        <v>89.45</v>
       </c>
       <c r="K35" t="n">
-        <v>79.75</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>55.98</v>
+        <v>85.8</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6474</v>
+        <v>6411</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -2602,59 +2602,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.54</v>
+        <v>16.73</v>
       </c>
       <c r="C36" t="n">
-        <v>21.83</v>
+        <v>16.91</v>
       </c>
       <c r="D36" t="n">
-        <v>21.18</v>
+        <v>16.64</v>
       </c>
       <c r="E36" t="n">
-        <v>11.6</v>
+        <v>15.2</v>
       </c>
       <c r="F36" t="n">
-        <v>10.7</v>
+        <v>15.1</v>
       </c>
       <c r="G36" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.19</v>
+        <v>0.16</v>
       </c>
       <c r="I36" t="n">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
       <c r="J36" t="n">
-        <v>53.45</v>
+        <v>91.16</v>
       </c>
       <c r="K36" t="n">
-        <v>58.22</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>49.34</v>
+        <v>89.92</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6485</v>
+        <v>6417</v>
       </c>
       <c r="P36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -2663,358 +2663,358 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22.02</v>
+        <v>16.79</v>
       </c>
       <c r="C37" t="n">
-        <v>22.16</v>
+        <v>16.87</v>
       </c>
       <c r="D37" t="n">
-        <v>21.88</v>
+        <v>16.65</v>
       </c>
       <c r="E37" t="n">
-        <v>11.1</v>
+        <v>15.5</v>
       </c>
       <c r="F37" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="G37" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.31</v>
+        <v>0.14</v>
       </c>
       <c r="I37" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="J37" t="n">
-        <v>50.18</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>52.66</v>
+        <v>93.45</v>
       </c>
       <c r="L37" t="n">
-        <v>47.74</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4352</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6511</v>
+        <v>6420</v>
       </c>
       <c r="P37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>22.31</v>
+        <v>16.6</v>
       </c>
       <c r="C38" t="n">
-        <v>22.81</v>
+        <v>16.66</v>
       </c>
       <c r="D38" t="n">
-        <v>22.04</v>
+        <v>16.52</v>
       </c>
       <c r="E38" t="n">
-        <v>11.4</v>
+        <v>15.8</v>
       </c>
       <c r="F38" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="G38" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.34</v>
+        <v>0.08</v>
       </c>
       <c r="I38" t="n">
-        <v>1.28</v>
+        <v>0.06</v>
       </c>
       <c r="J38" t="n">
-        <v>50.19</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>51.75</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>47.76</v>
+        <v>93.84</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>5406</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6539</v>
+        <v>6425</v>
       </c>
       <c r="P38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22.68</v>
+        <v>16.91</v>
       </c>
       <c r="C39" t="n">
-        <v>23.1</v>
+        <v>17.19</v>
       </c>
       <c r="D39" t="n">
-        <v>22.11</v>
+        <v>16.69</v>
       </c>
       <c r="E39" t="n">
-        <v>11.3</v>
+        <v>15.9</v>
       </c>
       <c r="F39" t="n">
-        <v>10.7</v>
+        <v>15.6</v>
       </c>
       <c r="G39" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="I39" t="n">
-        <v>1.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>48.82</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>51.28</v>
+        <v>96.09</v>
       </c>
       <c r="L39" t="n">
-        <v>47.13</v>
+        <v>90.87</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6743</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6573</v>
+        <v>6442</v>
       </c>
       <c r="P39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.01</v>
+        <v>17.68</v>
       </c>
       <c r="C40" t="n">
-        <v>22.58</v>
+        <v>18.12</v>
       </c>
       <c r="D40" t="n">
-        <v>21.62</v>
+        <v>17.08</v>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>15.3</v>
       </c>
       <c r="F40" t="n">
-        <v>10.6</v>
+        <v>14.6</v>
       </c>
       <c r="G40" t="n">
-        <v>452</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>1.33</v>
+        <v>0.27</v>
       </c>
       <c r="I40" t="n">
-        <v>1.27</v>
+        <v>0.12</v>
       </c>
       <c r="J40" t="n">
-        <v>49.71</v>
+        <v>86.59</v>
       </c>
       <c r="K40" t="n">
-        <v>51.65</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>46.69</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6767</v>
+        <v>685</v>
       </c>
       <c r="O40" t="n">
-        <v>6576</v>
+        <v>6451</v>
       </c>
       <c r="P40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>21.59</v>
+        <v>19.95</v>
       </c>
       <c r="C41" t="n">
-        <v>22.58</v>
+        <v>21.08</v>
       </c>
       <c r="D41" t="n">
-        <v>20.76</v>
+        <v>18.04</v>
       </c>
       <c r="E41" t="n">
-        <v>11.2</v>
+        <v>12.9</v>
       </c>
       <c r="F41" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="G41" t="n">
-        <v>564</v>
+        <v>18</v>
       </c>
       <c r="H41" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>1.07</v>
+        <v>0.41</v>
       </c>
       <c r="J41" t="n">
-        <v>51.87</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>56.03</v>
+        <v>79.75</v>
       </c>
       <c r="L41" t="n">
-        <v>45.92</v>
+        <v>55.98</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6796</v>
+        <v>1926</v>
       </c>
       <c r="O41" t="n">
-        <v>6599</v>
+        <v>6474</v>
       </c>
       <c r="P41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>20.19</v>
+        <v>21.54</v>
       </c>
       <c r="C42" t="n">
-        <v>20.64</v>
+        <v>21.83</v>
       </c>
       <c r="D42" t="n">
-        <v>19.53</v>
+        <v>21.18</v>
       </c>
       <c r="E42" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="F42" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="G42" t="n">
-        <v>426</v>
+        <v>44</v>
       </c>
       <c r="H42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I42" t="n">
         <v>1.05</v>
       </c>
-      <c r="I42" t="n">
-        <v>0.95</v>
-      </c>
       <c r="J42" t="n">
-        <v>55.29</v>
+        <v>53.45</v>
       </c>
       <c r="K42" t="n">
-        <v>57.87</v>
+        <v>58.22</v>
       </c>
       <c r="L42" t="n">
-        <v>52.99</v>
+        <v>49.34</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6767</v>
+        <v>2410</v>
       </c>
       <c r="O42" t="n">
-        <v>6576</v>
+        <v>6485</v>
       </c>
       <c r="P42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q42" t="n">
         <v>6</v>
@@ -3023,434 +3023,434 @@
         <v>5</v>
       </c>
       <c r="S42" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.89</v>
+        <v>22.02</v>
       </c>
       <c r="C43" t="n">
-        <v>19.62</v>
+        <v>22.16</v>
       </c>
       <c r="D43" t="n">
-        <v>18.08</v>
+        <v>21.88</v>
       </c>
       <c r="E43" t="n">
-        <v>13.1</v>
+        <v>11.1</v>
       </c>
       <c r="F43" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="G43" t="n">
-        <v>212</v>
+        <v>111</v>
       </c>
       <c r="H43" t="n">
-        <v>0.66</v>
+        <v>1.31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.35</v>
+        <v>1.24</v>
       </c>
       <c r="J43" t="n">
-        <v>69.7</v>
+        <v>50.18</v>
       </c>
       <c r="K43" t="n">
-        <v>82.87</v>
+        <v>52.66</v>
       </c>
       <c r="L43" t="n">
-        <v>57.89</v>
+        <v>47.74</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>6691</v>
+        <v>4352</v>
       </c>
       <c r="O43" t="n">
-        <v>6514</v>
+        <v>6511</v>
       </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-17 14:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17.5</v>
+        <v>22.31</v>
       </c>
       <c r="C44" t="n">
-        <v>17.9</v>
+        <v>22.81</v>
       </c>
       <c r="D44" t="n">
-        <v>17.26</v>
+        <v>22.04</v>
       </c>
       <c r="E44" t="n">
-        <v>14.7</v>
+        <v>11.4</v>
       </c>
       <c r="F44" t="n">
-        <v>14.3</v>
+        <v>10.9</v>
       </c>
       <c r="G44" t="n">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="H44" t="n">
-        <v>0.31</v>
+        <v>1.34</v>
       </c>
       <c r="I44" t="n">
-        <v>0.25</v>
+        <v>1.28</v>
       </c>
       <c r="J44" t="n">
-        <v>84.14</v>
+        <v>50.19</v>
       </c>
       <c r="K44" t="n">
-        <v>87.05</v>
+        <v>51.75</v>
       </c>
       <c r="L44" t="n">
-        <v>79.48999999999999</v>
+        <v>47.76</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3786</v>
+        <v>5406</v>
       </c>
       <c r="O44" t="n">
-        <v>6422</v>
+        <v>6539</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 07:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17.02</v>
+        <v>22.68</v>
       </c>
       <c r="C45" t="n">
-        <v>17.27</v>
+        <v>23.1</v>
       </c>
       <c r="D45" t="n">
-        <v>16.92</v>
+        <v>22.11</v>
       </c>
       <c r="E45" t="n">
-        <v>14.7</v>
+        <v>11.3</v>
       </c>
       <c r="F45" t="n">
-        <v>14.1</v>
+        <v>10.7</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="H45" t="n">
-        <v>0.25</v>
+        <v>1.4</v>
       </c>
       <c r="I45" t="n">
-        <v>0.21</v>
+        <v>1.32</v>
       </c>
       <c r="J45" t="n">
-        <v>86.8</v>
+        <v>48.82</v>
       </c>
       <c r="K45" t="n">
-        <v>88.91</v>
+        <v>51.28</v>
       </c>
       <c r="L45" t="n">
-        <v>81.98999999999999</v>
+        <v>47.13</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1246</v>
+        <v>6743</v>
       </c>
       <c r="O45" t="n">
-        <v>6414</v>
+        <v>6573</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 06:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.89</v>
+        <v>22.01</v>
       </c>
       <c r="C46" t="n">
-        <v>17.03</v>
+        <v>22.58</v>
       </c>
       <c r="D46" t="n">
-        <v>16.78</v>
+        <v>21.62</v>
       </c>
       <c r="E46" t="n">
-        <v>14.9</v>
+        <v>11</v>
       </c>
       <c r="F46" t="n">
-        <v>14.6</v>
+        <v>10.6</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="H46" t="n">
-        <v>0.21</v>
+        <v>1.33</v>
       </c>
       <c r="I46" t="n">
-        <v>0.18</v>
+        <v>1.27</v>
       </c>
       <c r="J46" t="n">
-        <v>88.48999999999999</v>
+        <v>49.71</v>
       </c>
       <c r="K46" t="n">
-        <v>90.31</v>
+        <v>51.65</v>
       </c>
       <c r="L46" t="n">
-        <v>85.76000000000001</v>
+        <v>46.69</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6767</v>
       </c>
       <c r="O46" t="n">
-        <v>6417</v>
+        <v>6576</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 05:00:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.13</v>
+        <v>21.59</v>
       </c>
       <c r="C47" t="n">
-        <v>17.32</v>
+        <v>22.58</v>
       </c>
       <c r="D47" t="n">
-        <v>16.89</v>
+        <v>20.76</v>
       </c>
       <c r="E47" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="F47" t="n">
-        <v>14.4</v>
+        <v>10.3</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="H47" t="n">
-        <v>0.27</v>
+        <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.22</v>
+        <v>1.07</v>
       </c>
       <c r="J47" t="n">
-        <v>85.90000000000001</v>
+        <v>51.87</v>
       </c>
       <c r="K47" t="n">
-        <v>88.63</v>
+        <v>56.03</v>
       </c>
       <c r="L47" t="n">
-        <v>83.40000000000001</v>
+        <v>45.92</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6796</v>
       </c>
       <c r="O47" t="n">
-        <v>6414</v>
+        <v>6599</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17.01</v>
+        <v>20.19</v>
       </c>
       <c r="C48" t="n">
-        <v>17.08</v>
+        <v>20.64</v>
       </c>
       <c r="D48" t="n">
-        <v>16.93</v>
+        <v>19.53</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>10.9</v>
       </c>
       <c r="F48" t="n">
-        <v>14.8</v>
+        <v>10.6</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H48" t="n">
-        <v>0.22</v>
+        <v>1.05</v>
       </c>
       <c r="I48" t="n">
-        <v>0.21</v>
+        <v>0.95</v>
       </c>
       <c r="J48" t="n">
-        <v>88.16</v>
+        <v>55.29</v>
       </c>
       <c r="K48" t="n">
-        <v>88.7</v>
+        <v>57.87</v>
       </c>
       <c r="L48" t="n">
-        <v>87.34999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6767</v>
       </c>
       <c r="O48" t="n">
-        <v>6414</v>
+        <v>6576</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 03:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>17.07</v>
+        <v>18.89</v>
       </c>
       <c r="C49" t="n">
-        <v>17.29</v>
+        <v>19.62</v>
       </c>
       <c r="D49" t="n">
-        <v>16.93</v>
+        <v>18.08</v>
       </c>
       <c r="E49" t="n">
-        <v>15</v>
+        <v>13.1</v>
       </c>
       <c r="F49" t="n">
-        <v>14.9</v>
+        <v>10.9</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H49" t="n">
-        <v>0.22</v>
+        <v>0.66</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J49" t="n">
-        <v>88.06999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K49" t="n">
-        <v>89.45999999999999</v>
+        <v>82.87</v>
       </c>
       <c r="L49" t="n">
-        <v>85.97</v>
+        <v>57.89</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6691</v>
       </c>
       <c r="O49" t="n">
-        <v>6417</v>
+        <v>6514</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,422 +528,422 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.28</v>
+        <v>22.53</v>
       </c>
       <c r="C2" t="n">
-        <v>14.32</v>
+        <v>23.46</v>
       </c>
       <c r="D2" t="n">
-        <v>14.25</v>
+        <v>22.06</v>
       </c>
       <c r="E2" t="n">
-        <v>14.2</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>14.2</v>
+        <v>10.5</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>541</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="J2" t="n">
-        <v>99.98</v>
+        <v>48.35</v>
       </c>
       <c r="K2" t="n">
-        <v>99.98999999999999</v>
+        <v>49.78</v>
       </c>
       <c r="L2" t="n">
-        <v>99.98</v>
+        <v>47.52</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3278</v>
+        <v>6777</v>
       </c>
       <c r="O2" t="n">
-        <v>6420</v>
+        <v>6590</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.35</v>
+        <v>21.55</v>
       </c>
       <c r="C3" t="n">
-        <v>14.59</v>
+        <v>22.58</v>
       </c>
       <c r="D3" t="n">
-        <v>14.2</v>
+        <v>21.03</v>
       </c>
       <c r="E3" t="n">
-        <v>14.2</v>
+        <v>10.6</v>
       </c>
       <c r="F3" t="n">
-        <v>14.1</v>
+        <v>10.3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>532</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01</v>
+        <v>1.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>99.56</v>
+        <v>49.94</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>51.47</v>
       </c>
       <c r="L3" t="n">
-        <v>97.86</v>
+        <v>48.14</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2885</v>
+        <v>6878</v>
       </c>
       <c r="O3" t="n">
-        <v>6411</v>
+        <v>6645</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.73</v>
+        <v>20.76</v>
       </c>
       <c r="C4" t="n">
-        <v>14.93</v>
+        <v>21.18</v>
       </c>
       <c r="D4" t="n">
-        <v>14.58</v>
+        <v>19.55</v>
       </c>
       <c r="E4" t="n">
-        <v>14.2</v>
+        <v>10.9</v>
       </c>
       <c r="F4" t="n">
-        <v>13.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>1.13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01</v>
+        <v>0.87</v>
       </c>
       <c r="J4" t="n">
-        <v>97.15000000000001</v>
+        <v>53.72</v>
       </c>
       <c r="K4" t="n">
-        <v>99.09999999999999</v>
+        <v>61.39</v>
       </c>
       <c r="L4" t="n">
-        <v>92.56999999999999</v>
+        <v>48.89</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6772</v>
       </c>
       <c r="O4" t="n">
-        <v>6402</v>
+        <v>6588</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.59</v>
+        <v>19.19</v>
       </c>
       <c r="C5" t="n">
-        <v>14.64</v>
+        <v>20.1</v>
       </c>
       <c r="D5" t="n">
-        <v>14.53</v>
+        <v>18.13</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>14.2</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>0.72</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="J5" t="n">
-        <v>98.76000000000001</v>
+        <v>67.73</v>
       </c>
       <c r="K5" t="n">
-        <v>99.54000000000001</v>
+        <v>76.56</v>
       </c>
       <c r="L5" t="n">
-        <v>98.01000000000001</v>
+        <v>60.33</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6806</v>
       </c>
       <c r="O5" t="n">
-        <v>6405</v>
+        <v>6608</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.4</v>
+        <v>16.91</v>
       </c>
       <c r="C6" t="n">
-        <v>14.56</v>
+        <v>17.56</v>
       </c>
       <c r="D6" t="n">
-        <v>14.28</v>
+        <v>16.26</v>
       </c>
       <c r="E6" t="n">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="F6" t="n">
-        <v>14.1</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02</v>
+        <v>0.36</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>98.81</v>
+        <v>81.03</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>97.73</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="O6" t="n">
-        <v>6405</v>
+        <v>6528</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.31</v>
+        <v>15.16</v>
       </c>
       <c r="C7" t="n">
-        <v>14.48</v>
+        <v>16.06</v>
       </c>
       <c r="D7" t="n">
-        <v>14.24</v>
+        <v>14.68</v>
       </c>
       <c r="E7" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="F7" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>99.7</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>98</v>
+        <v>88.64</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6585</v>
       </c>
       <c r="O7" t="n">
-        <v>6405</v>
+        <v>6468</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.91</v>
+        <v>14.4</v>
       </c>
       <c r="C8" t="n">
-        <v>15.38</v>
+        <v>14.62</v>
       </c>
       <c r="D8" t="n">
-        <v>14.51</v>
+        <v>14.25</v>
       </c>
       <c r="E8" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="F8" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H8" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>92.72</v>
+        <v>99.98</v>
       </c>
       <c r="K8" t="n">
-        <v>97.28</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>86.81999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3872</v>
       </c>
       <c r="O8" t="n">
-        <v>6408</v>
+        <v>6425</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -955,59 +955,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.65</v>
+        <v>14.35</v>
       </c>
       <c r="C9" t="n">
-        <v>15.83</v>
+        <v>14.59</v>
       </c>
       <c r="D9" t="n">
-        <v>15.43</v>
+        <v>14.2</v>
       </c>
       <c r="E9" t="n">
-        <v>12.9</v>
+        <v>14.2</v>
       </c>
       <c r="F9" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.27</v>
+        <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>84.34999999999999</v>
+        <v>99.56</v>
       </c>
       <c r="K9" t="n">
-        <v>86.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>81.81</v>
+        <v>97.86</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="O9" t="n">
         <v>6411</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1016,41 +1016,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.77</v>
+        <v>14.73</v>
       </c>
       <c r="C10" t="n">
-        <v>16.04</v>
+        <v>14.93</v>
       </c>
       <c r="D10" t="n">
-        <v>15.59</v>
+        <v>14.58</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="F10" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
       <c r="J10" t="n">
-        <v>84</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>86.05</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>80.77</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1059,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6414</v>
+        <v>6402</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1077,41 +1077,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.89</v>
+        <v>14.59</v>
       </c>
       <c r="C11" t="n">
-        <v>16.09</v>
+        <v>14.64</v>
       </c>
       <c r="D11" t="n">
-        <v>15.55</v>
+        <v>14.53</v>
       </c>
       <c r="E11" t="n">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="F11" t="n">
-        <v>12.5</v>
+        <v>14.2</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33</v>
+        <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>81.48999999999999</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>83.06999999999999</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>80.19</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1123,13 +1123,13 @@
         <v>6405</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1138,41 +1138,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.43</v>
+        <v>14.4</v>
       </c>
       <c r="C12" t="n">
-        <v>15.49</v>
+        <v>14.56</v>
       </c>
       <c r="D12" t="n">
-        <v>15.38</v>
+        <v>14.28</v>
       </c>
       <c r="E12" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="F12" t="n">
-        <v>12.6</v>
+        <v>14.1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.27</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>83.98999999999999</v>
+        <v>98.81</v>
       </c>
       <c r="K12" t="n">
-        <v>85.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>83.27</v>
+        <v>97.73</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1181,16 +1181,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6408</v>
+        <v>6405</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1199,41 +1199,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.57</v>
+        <v>14.31</v>
       </c>
       <c r="C13" t="n">
-        <v>15.65</v>
+        <v>14.48</v>
       </c>
       <c r="D13" t="n">
-        <v>15.47</v>
+        <v>14.24</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7</v>
+        <v>14.2</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5</v>
+        <v>14.1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>83.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="K13" t="n">
-        <v>84.86</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>82.39</v>
+        <v>98</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1242,16 +1242,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1260,41 +1260,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.77</v>
+        <v>14.91</v>
       </c>
       <c r="C14" t="n">
-        <v>15.92</v>
+        <v>15.38</v>
       </c>
       <c r="D14" t="n">
-        <v>15.58</v>
+        <v>14.51</v>
       </c>
       <c r="E14" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F14" t="n">
         <v>13.1</v>
       </c>
-      <c r="F14" t="n">
-        <v>12.7</v>
-      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="J14" t="n">
-        <v>84.48</v>
+        <v>92.72</v>
       </c>
       <c r="K14" t="n">
-        <v>86.84</v>
+        <v>97.28</v>
       </c>
       <c r="L14" t="n">
-        <v>81.94</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1303,16 +1303,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6417</v>
+        <v>6408</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1321,41 +1321,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.16</v>
+        <v>15.65</v>
       </c>
       <c r="C15" t="n">
-        <v>16.42</v>
+        <v>15.83</v>
       </c>
       <c r="D15" t="n">
-        <v>15.94</v>
+        <v>15.43</v>
       </c>
       <c r="E15" t="n">
         <v>12.9</v>
       </c>
       <c r="F15" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="I15" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="J15" t="n">
-        <v>81.48999999999999</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>84.55</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>78.12</v>
+        <v>81.81</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -1373,7 +1373,7 @@
         <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1382,59 +1382,59 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.77</v>
+        <v>15.77</v>
       </c>
       <c r="C16" t="n">
-        <v>17.13</v>
+        <v>16.04</v>
       </c>
       <c r="D16" t="n">
-        <v>16.4</v>
+        <v>15.59</v>
       </c>
       <c r="E16" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
       <c r="I16" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="J16" t="n">
-        <v>75.39</v>
+        <v>84</v>
       </c>
       <c r="K16" t="n">
-        <v>78.58</v>
+        <v>86.05</v>
       </c>
       <c r="L16" t="n">
-        <v>72.19</v>
+        <v>80.77</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6431</v>
+        <v>6414</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1443,59 +1443,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.34</v>
+        <v>15.89</v>
       </c>
       <c r="C17" t="n">
-        <v>17.55</v>
+        <v>16.09</v>
       </c>
       <c r="D17" t="n">
-        <v>17.15</v>
+        <v>15.55</v>
       </c>
       <c r="E17" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F17" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
-        <v>70.43000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>72.41</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>68.52</v>
+        <v>80.19</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3144</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6459</v>
+        <v>6405</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1504,355 +1504,355 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.83</v>
+        <v>15.43</v>
       </c>
       <c r="C18" t="n">
-        <v>18.09</v>
+        <v>15.49</v>
       </c>
       <c r="D18" t="n">
-        <v>17.42</v>
+        <v>15.38</v>
       </c>
       <c r="E18" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F18" t="n">
-        <v>10.6</v>
+        <v>12.6</v>
       </c>
       <c r="G18" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="J18" t="n">
-        <v>66.04000000000001</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>69.8</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>62.77</v>
+        <v>83.27</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4749</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6491</v>
+        <v>6408</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.68</v>
+        <v>15.57</v>
       </c>
       <c r="C19" t="n">
-        <v>17.86</v>
+        <v>15.65</v>
       </c>
       <c r="D19" t="n">
-        <v>17.49</v>
+        <v>15.47</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="F19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="G19" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7</v>
+        <v>0.29</v>
       </c>
       <c r="I19" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="J19" t="n">
-        <v>65.15000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>67.11</v>
+        <v>84.86</v>
       </c>
       <c r="L19" t="n">
-        <v>63.11</v>
+        <v>82.39</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5962</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6502</v>
+        <v>6411</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.45</v>
+        <v>15.77</v>
       </c>
       <c r="C20" t="n">
-        <v>17.76</v>
+        <v>15.92</v>
       </c>
       <c r="D20" t="n">
-        <v>17.19</v>
+        <v>15.58</v>
       </c>
       <c r="E20" t="n">
-        <v>10.9</v>
+        <v>13.1</v>
       </c>
       <c r="F20" t="n">
-        <v>10.4</v>
+        <v>12.7</v>
       </c>
       <c r="G20" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.68</v>
+        <v>0.27</v>
       </c>
       <c r="I20" t="n">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="J20" t="n">
-        <v>65.79000000000001</v>
+        <v>84.48</v>
       </c>
       <c r="K20" t="n">
-        <v>68.27</v>
+        <v>86.84</v>
       </c>
       <c r="L20" t="n">
-        <v>62.48</v>
+        <v>81.94</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6561</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6539</v>
+        <v>6417</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.1</v>
+        <v>16.16</v>
       </c>
       <c r="C21" t="n">
-        <v>17.35</v>
+        <v>16.42</v>
       </c>
       <c r="D21" t="n">
-        <v>16.86</v>
+        <v>15.94</v>
       </c>
       <c r="E21" t="n">
-        <v>10.9</v>
+        <v>12.9</v>
       </c>
       <c r="F21" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="G21" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="I21" t="n">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
       <c r="J21" t="n">
-        <v>67.38</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>67.78</v>
+        <v>84.55</v>
       </c>
       <c r="L21" t="n">
-        <v>66.55</v>
+        <v>78.12</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6671</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6536</v>
+        <v>6420</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.52</v>
+        <v>16.77</v>
       </c>
       <c r="C22" t="n">
-        <v>17.36</v>
+        <v>17.13</v>
       </c>
       <c r="D22" t="n">
-        <v>16.01</v>
+        <v>16.4</v>
       </c>
       <c r="E22" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="F22" t="n">
-        <v>10.7</v>
+        <v>11.9</v>
       </c>
       <c r="G22" t="n">
-        <v>301</v>
+        <v>17</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="J22" t="n">
-        <v>69.84</v>
+        <v>75.39</v>
       </c>
       <c r="K22" t="n">
-        <v>72.16</v>
+        <v>78.58</v>
       </c>
       <c r="L22" t="n">
-        <v>66.34999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6681</v>
+        <v>1164</v>
       </c>
       <c r="O22" t="n">
-        <v>6525</v>
+        <v>6431</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.55</v>
+        <v>17.34</v>
       </c>
       <c r="C23" t="n">
-        <v>16.32</v>
+        <v>17.55</v>
       </c>
       <c r="D23" t="n">
-        <v>15.05</v>
+        <v>17.15</v>
       </c>
       <c r="E23" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="F23" t="n">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="G23" t="n">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="H23" t="n">
-        <v>0.43</v>
+        <v>0.58</v>
       </c>
       <c r="I23" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="J23" t="n">
-        <v>75.25</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>78.77</v>
+        <v>72.41</v>
       </c>
       <c r="L23" t="n">
-        <v>71.11</v>
+        <v>68.52</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6729</v>
+        <v>3144</v>
       </c>
       <c r="O23" t="n">
-        <v>6556</v>
+        <v>6459</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -1861,364 +1861,364 @@
         <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.04</v>
+        <v>17.83</v>
       </c>
       <c r="C24" t="n">
-        <v>15.26</v>
+        <v>18.09</v>
       </c>
       <c r="D24" t="n">
-        <v>14.82</v>
+        <v>17.42</v>
       </c>
       <c r="E24" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="G24" t="n">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H24" t="n">
-        <v>0.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
-        <v>77.86</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>80.23</v>
+        <v>69.8</v>
       </c>
       <c r="L24" t="n">
-        <v>75.81</v>
+        <v>62.77</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5708</v>
+        <v>4749</v>
       </c>
       <c r="O24" t="n">
-        <v>6494</v>
+        <v>6491</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.47</v>
+        <v>17.68</v>
       </c>
       <c r="C25" t="n">
-        <v>14.79</v>
+        <v>17.86</v>
       </c>
       <c r="D25" t="n">
-        <v>14.22</v>
+        <v>17.49</v>
       </c>
       <c r="E25" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G25" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="H25" t="n">
-        <v>0.31</v>
+        <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>0.28</v>
+        <v>0.66</v>
       </c>
       <c r="J25" t="n">
-        <v>80.75</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>82.34</v>
+        <v>67.11</v>
       </c>
       <c r="L25" t="n">
-        <v>79.73999999999999</v>
+        <v>63.11</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6254</v>
+        <v>5962</v>
       </c>
       <c r="O25" t="n">
-        <v>6491</v>
+        <v>6502</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S25" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14.34</v>
+        <v>17.45</v>
       </c>
       <c r="C26" t="n">
-        <v>14.4</v>
+        <v>17.76</v>
       </c>
       <c r="D26" t="n">
-        <v>14.25</v>
+        <v>17.19</v>
       </c>
       <c r="E26" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="F26" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="G26" t="n">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="H26" t="n">
-        <v>0.33</v>
+        <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>0.32</v>
+        <v>0.62</v>
       </c>
       <c r="J26" t="n">
-        <v>79.29000000000001</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>80.34999999999999</v>
+        <v>68.27</v>
       </c>
       <c r="L26" t="n">
-        <v>77.13</v>
+        <v>62.48</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3949</v>
+        <v>6561</v>
       </c>
       <c r="O26" t="n">
-        <v>6425</v>
+        <v>6539</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.56</v>
+        <v>17.1</v>
       </c>
       <c r="C27" t="n">
-        <v>14.75</v>
+        <v>17.35</v>
       </c>
       <c r="D27" t="n">
-        <v>14.34</v>
+        <v>16.86</v>
       </c>
       <c r="E27" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F27" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G27" t="n">
+        <v>246</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J27" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="K27" t="n">
+        <v>67.78</v>
+      </c>
+      <c r="L27" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6671</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6536</v>
+      </c>
+      <c r="P27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J27" t="n">
-        <v>78.20999999999999</v>
-      </c>
-      <c r="K27" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="L27" t="n">
-        <v>75.43000000000001</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2449</v>
-      </c>
-      <c r="O27" t="n">
-        <v>6420</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14.79</v>
+        <v>16.52</v>
       </c>
       <c r="C28" t="n">
-        <v>14.98</v>
+        <v>17.36</v>
       </c>
       <c r="D28" t="n">
-        <v>14.63</v>
+        <v>16.01</v>
       </c>
       <c r="E28" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F28" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="H28" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
-        <v>77.20999999999999</v>
+        <v>69.84</v>
       </c>
       <c r="K28" t="n">
-        <v>79.73999999999999</v>
+        <v>72.16</v>
       </c>
       <c r="L28" t="n">
-        <v>74.54000000000001</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6681</v>
       </c>
       <c r="O28" t="n">
-        <v>6411</v>
+        <v>6525</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
         <v>3</v>
       </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15.24</v>
+        <v>15.55</v>
       </c>
       <c r="C29" t="n">
-        <v>15.48</v>
+        <v>16.32</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>15.05</v>
       </c>
       <c r="E29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F29" t="n">
         <v>10.7</v>
       </c>
-      <c r="F29" t="n">
-        <v>10.4</v>
-      </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H29" t="n">
         <v>0.43</v>
       </c>
       <c r="I29" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="J29" t="n">
-        <v>74.68000000000001</v>
+        <v>75.25</v>
       </c>
       <c r="K29" t="n">
-        <v>75.5</v>
+        <v>78.77</v>
       </c>
       <c r="L29" t="n">
-        <v>73.42</v>
+        <v>71.11</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6729</v>
       </c>
       <c r="O29" t="n">
-        <v>6411</v>
+        <v>6556</v>
       </c>
       <c r="P29" t="n">
         <v>3</v>
@@ -2227,181 +2227,181 @@
         <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15.62</v>
+        <v>15.04</v>
       </c>
       <c r="C30" t="n">
-        <v>15.76</v>
+        <v>15.26</v>
       </c>
       <c r="D30" t="n">
-        <v>15.46</v>
+        <v>14.82</v>
       </c>
       <c r="E30" t="n">
-        <v>12.3</v>
+        <v>11.1</v>
       </c>
       <c r="F30" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="H30" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="I30" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J30" t="n">
-        <v>81.47</v>
+        <v>77.86</v>
       </c>
       <c r="K30" t="n">
-        <v>89.01000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="L30" t="n">
-        <v>74.23</v>
+        <v>75.81</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5708</v>
       </c>
       <c r="O30" t="n">
-        <v>6402</v>
+        <v>6494</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>15.86</v>
+        <v>14.47</v>
       </c>
       <c r="C31" t="n">
-        <v>16.08</v>
+        <v>14.79</v>
       </c>
       <c r="D31" t="n">
-        <v>15.66</v>
+        <v>14.22</v>
       </c>
       <c r="E31" t="n">
-        <v>13.8</v>
+        <v>11.1</v>
       </c>
       <c r="F31" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H31" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="I31" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="J31" t="n">
-        <v>87.95999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="K31" t="n">
-        <v>89.39</v>
+        <v>82.34</v>
       </c>
       <c r="L31" t="n">
-        <v>86.37</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O31" t="n">
-        <v>6411</v>
+        <v>6491</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.22</v>
+        <v>14.34</v>
       </c>
       <c r="C32" t="n">
-        <v>16.35</v>
+        <v>14.4</v>
       </c>
       <c r="D32" t="n">
-        <v>16.12</v>
+        <v>14.25</v>
       </c>
       <c r="E32" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="F32" t="n">
-        <v>13.4</v>
+        <v>10.3</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H32" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="I32" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="J32" t="n">
-        <v>85.42</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>87.15000000000001</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>83.22</v>
+        <v>77.13</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O32" t="n">
-        <v>6405</v>
+        <v>6425</v>
       </c>
       <c r="P32" t="n">
         <v>2</v>
@@ -2410,7 +2410,7 @@
         <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2419,59 +2419,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.39</v>
+        <v>14.56</v>
       </c>
       <c r="C33" t="n">
-        <v>16.55</v>
+        <v>14.75</v>
       </c>
       <c r="D33" t="n">
-        <v>16.22</v>
+        <v>14.34</v>
       </c>
       <c r="E33" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
       <c r="F33" t="n">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="I33" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="J33" t="n">
-        <v>85.56999999999999</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>87.13</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>84.14</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O33" t="n">
-        <v>6417</v>
+        <v>6420</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
         <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -2480,41 +2480,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.68</v>
+        <v>14.79</v>
       </c>
       <c r="C34" t="n">
-        <v>16.76</v>
+        <v>14.98</v>
       </c>
       <c r="D34" t="n">
-        <v>16.63</v>
+        <v>14.63</v>
       </c>
       <c r="E34" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
       <c r="F34" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="I34" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="J34" t="n">
-        <v>84.16</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>86.08</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>81.98</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2529,10 +2529,10 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2541,41 +2541,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.64</v>
+        <v>15.24</v>
       </c>
       <c r="C35" t="n">
-        <v>16.72</v>
+        <v>15.48</v>
       </c>
       <c r="D35" t="n">
-        <v>16.62</v>
+        <v>15</v>
       </c>
       <c r="E35" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="F35" t="n">
-        <v>14.3</v>
+        <v>10.4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.19</v>
+        <v>0.43</v>
       </c>
       <c r="I35" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="J35" t="n">
-        <v>89.45</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>91.73999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="L35" t="n">
-        <v>85.8</v>
+        <v>73.42</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2587,13 +2587,13 @@
         <v>6411</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -2602,41 +2602,41 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.73</v>
+        <v>15.62</v>
       </c>
       <c r="C36" t="n">
-        <v>16.91</v>
+        <v>15.76</v>
       </c>
       <c r="D36" t="n">
-        <v>16.64</v>
+        <v>15.46</v>
       </c>
       <c r="E36" t="n">
-        <v>15.2</v>
+        <v>12.3</v>
       </c>
       <c r="F36" t="n">
-        <v>15.1</v>
+        <v>10.8</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="I36" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J36" t="n">
-        <v>91.16</v>
+        <v>81.47</v>
       </c>
       <c r="K36" t="n">
-        <v>91.98999999999999</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>89.92</v>
+        <v>74.23</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2645,13 +2645,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6417</v>
+        <v>6402</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -2663,41 +2663,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16.79</v>
+        <v>15.86</v>
       </c>
       <c r="C37" t="n">
-        <v>16.87</v>
+        <v>16.08</v>
       </c>
       <c r="D37" t="n">
-        <v>16.65</v>
+        <v>15.66</v>
       </c>
       <c r="E37" t="n">
-        <v>15.5</v>
+        <v>13.8</v>
       </c>
       <c r="F37" t="n">
-        <v>15.3</v>
+        <v>13.7</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="J37" t="n">
-        <v>92.09999999999999</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>93.45</v>
+        <v>89.39</v>
       </c>
       <c r="L37" t="n">
-        <v>90.81999999999999</v>
+        <v>86.37</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -2724,41 +2724,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.6</v>
+        <v>16.22</v>
       </c>
       <c r="C38" t="n">
-        <v>16.66</v>
+        <v>16.35</v>
       </c>
       <c r="D38" t="n">
-        <v>16.52</v>
+        <v>16.12</v>
       </c>
       <c r="E38" t="n">
-        <v>15.8</v>
+        <v>13.7</v>
       </c>
       <c r="F38" t="n">
-        <v>15.6</v>
+        <v>13.4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="J38" t="n">
-        <v>95.29000000000001</v>
+        <v>85.42</v>
       </c>
       <c r="K38" t="n">
-        <v>96.45999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>93.84</v>
+        <v>83.22</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2767,16 +2767,16 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6425</v>
+        <v>6405</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
         <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -2785,41 +2785,41 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.91</v>
+        <v>16.39</v>
       </c>
       <c r="C39" t="n">
-        <v>17.19</v>
+        <v>16.55</v>
       </c>
       <c r="D39" t="n">
-        <v>16.69</v>
+        <v>16.22</v>
       </c>
       <c r="E39" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="F39" t="n">
-        <v>15.6</v>
+        <v>13.8</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="J39" t="n">
-        <v>94.18000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>96.09</v>
+        <v>87.13</v>
       </c>
       <c r="L39" t="n">
-        <v>90.87</v>
+        <v>84.14</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6442</v>
+        <v>6417</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
         <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -2846,53 +2846,53 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.68</v>
+        <v>16.68</v>
       </c>
       <c r="C40" t="n">
-        <v>18.12</v>
+        <v>16.76</v>
       </c>
       <c r="D40" t="n">
-        <v>17.08</v>
+        <v>16.63</v>
       </c>
       <c r="E40" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="F40" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="I40" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J40" t="n">
-        <v>86.59</v>
+        <v>84.16</v>
       </c>
       <c r="K40" t="n">
-        <v>93.40000000000001</v>
+        <v>86.08</v>
       </c>
       <c r="L40" t="n">
-        <v>80.54000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6451</v>
+        <v>6411</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
         <v>2</v>
@@ -2907,59 +2907,59 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.95</v>
+        <v>16.64</v>
       </c>
       <c r="C41" t="n">
-        <v>21.08</v>
+        <v>16.72</v>
       </c>
       <c r="D41" t="n">
-        <v>18.04</v>
+        <v>16.62</v>
       </c>
       <c r="E41" t="n">
-        <v>12.9</v>
+        <v>14.8</v>
       </c>
       <c r="F41" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="G41" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="I41" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="J41" t="n">
-        <v>64.73999999999999</v>
+        <v>89.45</v>
       </c>
       <c r="K41" t="n">
-        <v>79.75</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>55.98</v>
+        <v>85.8</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6474</v>
+        <v>6411</v>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -2968,59 +2968,59 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21.54</v>
+        <v>16.73</v>
       </c>
       <c r="C42" t="n">
-        <v>21.83</v>
+        <v>16.91</v>
       </c>
       <c r="D42" t="n">
-        <v>21.18</v>
+        <v>16.64</v>
       </c>
       <c r="E42" t="n">
-        <v>11.6</v>
+        <v>15.2</v>
       </c>
       <c r="F42" t="n">
-        <v>10.7</v>
+        <v>15.1</v>
       </c>
       <c r="G42" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.19</v>
+        <v>0.16</v>
       </c>
       <c r="I42" t="n">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
       <c r="J42" t="n">
-        <v>53.45</v>
+        <v>91.16</v>
       </c>
       <c r="K42" t="n">
-        <v>58.22</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>49.34</v>
+        <v>89.92</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6485</v>
+        <v>6417</v>
       </c>
       <c r="P42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3029,358 +3029,358 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.02</v>
+        <v>16.79</v>
       </c>
       <c r="C43" t="n">
-        <v>22.16</v>
+        <v>16.87</v>
       </c>
       <c r="D43" t="n">
-        <v>21.88</v>
+        <v>16.65</v>
       </c>
       <c r="E43" t="n">
-        <v>11.1</v>
+        <v>15.5</v>
       </c>
       <c r="F43" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="G43" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.31</v>
+        <v>0.14</v>
       </c>
       <c r="I43" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="J43" t="n">
-        <v>50.18</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>52.66</v>
+        <v>93.45</v>
       </c>
       <c r="L43" t="n">
-        <v>47.74</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4352</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6511</v>
+        <v>6420</v>
       </c>
       <c r="P43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22.31</v>
+        <v>16.6</v>
       </c>
       <c r="C44" t="n">
-        <v>22.81</v>
+        <v>16.66</v>
       </c>
       <c r="D44" t="n">
-        <v>22.04</v>
+        <v>16.52</v>
       </c>
       <c r="E44" t="n">
-        <v>11.4</v>
+        <v>15.8</v>
       </c>
       <c r="F44" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="G44" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.34</v>
+        <v>0.08</v>
       </c>
       <c r="I44" t="n">
-        <v>1.28</v>
+        <v>0.06</v>
       </c>
       <c r="J44" t="n">
-        <v>50.19</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>51.75</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>47.76</v>
+        <v>93.84</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5406</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6539</v>
+        <v>6425</v>
       </c>
       <c r="P44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 13:00:00</t>
+          <t>2026-10-17 19:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>22.68</v>
+        <v>16.91</v>
       </c>
       <c r="C45" t="n">
-        <v>23.1</v>
+        <v>17.19</v>
       </c>
       <c r="D45" t="n">
-        <v>22.11</v>
+        <v>16.69</v>
       </c>
       <c r="E45" t="n">
-        <v>11.3</v>
+        <v>15.9</v>
       </c>
       <c r="F45" t="n">
-        <v>10.7</v>
+        <v>15.6</v>
       </c>
       <c r="G45" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="I45" t="n">
-        <v>1.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>48.82</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>51.28</v>
+        <v>96.09</v>
       </c>
       <c r="L45" t="n">
-        <v>47.13</v>
+        <v>90.87</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6743</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6573</v>
+        <v>6442</v>
       </c>
       <c r="P45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22.01</v>
+        <v>17.68</v>
       </c>
       <c r="C46" t="n">
-        <v>22.58</v>
+        <v>18.12</v>
       </c>
       <c r="D46" t="n">
-        <v>21.62</v>
+        <v>17.08</v>
       </c>
       <c r="E46" t="n">
-        <v>11</v>
+        <v>15.3</v>
       </c>
       <c r="F46" t="n">
-        <v>10.6</v>
+        <v>14.6</v>
       </c>
       <c r="G46" t="n">
-        <v>452</v>
+        <v>7</v>
       </c>
       <c r="H46" t="n">
-        <v>1.33</v>
+        <v>0.27</v>
       </c>
       <c r="I46" t="n">
-        <v>1.27</v>
+        <v>0.12</v>
       </c>
       <c r="J46" t="n">
-        <v>49.71</v>
+        <v>86.59</v>
       </c>
       <c r="K46" t="n">
-        <v>51.65</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>46.69</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6767</v>
+        <v>685</v>
       </c>
       <c r="O46" t="n">
-        <v>6576</v>
+        <v>6451</v>
       </c>
       <c r="P46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21.59</v>
+        <v>19.95</v>
       </c>
       <c r="C47" t="n">
-        <v>22.58</v>
+        <v>21.08</v>
       </c>
       <c r="D47" t="n">
-        <v>20.76</v>
+        <v>18.04</v>
       </c>
       <c r="E47" t="n">
-        <v>11.2</v>
+        <v>12.9</v>
       </c>
       <c r="F47" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="G47" t="n">
-        <v>564</v>
+        <v>18</v>
       </c>
       <c r="H47" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="I47" t="n">
-        <v>1.07</v>
+        <v>0.41</v>
       </c>
       <c r="J47" t="n">
-        <v>51.87</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>56.03</v>
+        <v>79.75</v>
       </c>
       <c r="L47" t="n">
-        <v>45.92</v>
+        <v>55.98</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>6796</v>
+        <v>1926</v>
       </c>
       <c r="O47" t="n">
-        <v>6599</v>
+        <v>6474</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 10:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.19</v>
+        <v>21.54</v>
       </c>
       <c r="C48" t="n">
-        <v>20.64</v>
+        <v>21.83</v>
       </c>
       <c r="D48" t="n">
-        <v>19.53</v>
+        <v>21.18</v>
       </c>
       <c r="E48" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="F48" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="G48" t="n">
-        <v>426</v>
+        <v>44</v>
       </c>
       <c r="H48" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I48" t="n">
         <v>1.05</v>
       </c>
-      <c r="I48" t="n">
-        <v>0.95</v>
-      </c>
       <c r="J48" t="n">
-        <v>55.29</v>
+        <v>53.45</v>
       </c>
       <c r="K48" t="n">
-        <v>57.87</v>
+        <v>58.22</v>
       </c>
       <c r="L48" t="n">
-        <v>52.99</v>
+        <v>49.34</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6767</v>
+        <v>2410</v>
       </c>
       <c r="O48" t="n">
-        <v>6576</v>
+        <v>6485</v>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q48" t="n">
         <v>6</v>
@@ -3389,68 +3389,68 @@
         <v>5</v>
       </c>
       <c r="S48" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18.89</v>
+        <v>22.02</v>
       </c>
       <c r="C49" t="n">
-        <v>19.62</v>
+        <v>22.16</v>
       </c>
       <c r="D49" t="n">
-        <v>18.08</v>
+        <v>21.88</v>
       </c>
       <c r="E49" t="n">
-        <v>13.1</v>
+        <v>11.1</v>
       </c>
       <c r="F49" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="G49" t="n">
-        <v>212</v>
+        <v>111</v>
       </c>
       <c r="H49" t="n">
-        <v>0.66</v>
+        <v>1.31</v>
       </c>
       <c r="I49" t="n">
-        <v>0.35</v>
+        <v>1.24</v>
       </c>
       <c r="J49" t="n">
-        <v>69.7</v>
+        <v>50.18</v>
       </c>
       <c r="K49" t="n">
-        <v>82.87</v>
+        <v>52.66</v>
       </c>
       <c r="L49" t="n">
-        <v>57.89</v>
+        <v>47.74</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6691</v>
+        <v>4352</v>
       </c>
       <c r="O49" t="n">
-        <v>6514</v>
+        <v>6511</v>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,697 +528,697 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.53</v>
+        <v>19.69</v>
       </c>
       <c r="C2" t="n">
-        <v>23.46</v>
+        <v>19.74</v>
       </c>
       <c r="D2" t="n">
-        <v>22.06</v>
+        <v>19.55</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="F2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.41</v>
+        <v>0.86</v>
       </c>
       <c r="I2" t="n">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="J2" t="n">
-        <v>48.35</v>
+        <v>62.17</v>
       </c>
       <c r="K2" t="n">
-        <v>49.78</v>
+        <v>63.42</v>
       </c>
       <c r="L2" t="n">
-        <v>47.52</v>
+        <v>61.3</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6777</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6590</v>
+        <v>6485</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.55</v>
+        <v>19.88</v>
       </c>
       <c r="C3" t="n">
-        <v>22.58</v>
+        <v>20.1</v>
       </c>
       <c r="D3" t="n">
-        <v>21.03</v>
+        <v>19.77</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="G3" t="n">
-        <v>532</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>1.28</v>
+        <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>0.88</v>
       </c>
       <c r="J3" t="n">
-        <v>49.94</v>
+        <v>60.69</v>
       </c>
       <c r="K3" t="n">
-        <v>51.47</v>
+        <v>61.7</v>
       </c>
       <c r="L3" t="n">
-        <v>48.14</v>
+        <v>59.35</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6878</v>
+        <v>1116</v>
       </c>
       <c r="O3" t="n">
-        <v>6645</v>
+        <v>6479</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.76</v>
+        <v>20.3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.18</v>
+        <v>20.44</v>
       </c>
       <c r="D4" t="n">
-        <v>19.55</v>
+        <v>20.2</v>
       </c>
       <c r="E4" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="F4" t="n">
-        <v>9.800000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="G4" t="n">
-        <v>562</v>
+        <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="J4" t="n">
-        <v>53.72</v>
+        <v>57.79</v>
       </c>
       <c r="K4" t="n">
-        <v>61.39</v>
+        <v>58.95</v>
       </c>
       <c r="L4" t="n">
-        <v>48.89</v>
+        <v>56.53</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6772</v>
+        <v>3470</v>
       </c>
       <c r="O4" t="n">
-        <v>6588</v>
+        <v>6505</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.19</v>
+        <v>21.04</v>
       </c>
       <c r="C5" t="n">
-        <v>20.1</v>
+        <v>21.75</v>
       </c>
       <c r="D5" t="n">
-        <v>18.13</v>
+        <v>20.48</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11.4</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>650</v>
+        <v>76</v>
       </c>
       <c r="H5" t="n">
-        <v>0.72</v>
+        <v>1.13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.52</v>
+        <v>1.02</v>
       </c>
       <c r="J5" t="n">
-        <v>67.73</v>
+        <v>54.28</v>
       </c>
       <c r="K5" t="n">
-        <v>76.56</v>
+        <v>57.49</v>
       </c>
       <c r="L5" t="n">
-        <v>60.33</v>
+        <v>52.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6806</v>
+        <v>3877</v>
       </c>
       <c r="O5" t="n">
-        <v>6608</v>
+        <v>6519</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
         <v>5</v>
       </c>
-      <c r="R5" t="n">
-        <v>3</v>
-      </c>
       <c r="S5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.91</v>
+        <v>22.64</v>
       </c>
       <c r="C6" t="n">
-        <v>17.56</v>
+        <v>24.1</v>
       </c>
       <c r="D6" t="n">
-        <v>16.26</v>
+        <v>22.02</v>
       </c>
       <c r="E6" t="n">
-        <v>13.6</v>
+        <v>11.3</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="H6" t="n">
-        <v>0.36</v>
+        <v>1.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>1.27</v>
       </c>
       <c r="J6" t="n">
-        <v>81.03</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>88.79000000000001</v>
+        <v>51.75</v>
       </c>
       <c r="L6" t="n">
-        <v>78.15000000000001</v>
+        <v>44.97</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6700</v>
+        <v>5075</v>
       </c>
       <c r="O6" t="n">
-        <v>6528</v>
+        <v>6545</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.16</v>
+        <v>22.62</v>
       </c>
       <c r="C7" t="n">
-        <v>16.06</v>
+        <v>23.46</v>
       </c>
       <c r="D7" t="n">
-        <v>14.68</v>
+        <v>22.06</v>
       </c>
       <c r="E7" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="F7" t="n">
-        <v>13.7</v>
+        <v>10.5</v>
       </c>
       <c r="G7" t="n">
-        <v>111</v>
+        <v>592</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="J7" t="n">
-        <v>96.65000000000001</v>
+        <v>48.33</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>49.78</v>
       </c>
       <c r="L7" t="n">
-        <v>88.64</v>
+        <v>47.52</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6585</v>
+        <v>6863</v>
       </c>
       <c r="O7" t="n">
-        <v>6468</v>
+        <v>6633</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.4</v>
+        <v>21.55</v>
       </c>
       <c r="C8" t="n">
-        <v>14.62</v>
+        <v>22.58</v>
       </c>
       <c r="D8" t="n">
-        <v>14.25</v>
+        <v>21.03</v>
       </c>
       <c r="E8" t="n">
-        <v>14.3</v>
+        <v>10.6</v>
       </c>
       <c r="F8" t="n">
-        <v>14.2</v>
+        <v>10.3</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>532</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>99.98</v>
+        <v>49.94</v>
       </c>
       <c r="K8" t="n">
-        <v>99.98999999999999</v>
+        <v>51.47</v>
       </c>
       <c r="L8" t="n">
-        <v>99.98</v>
+        <v>48.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3872</v>
+        <v>6878</v>
       </c>
       <c r="O8" t="n">
-        <v>6425</v>
+        <v>6645</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.35</v>
+        <v>20.76</v>
       </c>
       <c r="C9" t="n">
-        <v>14.59</v>
+        <v>21.18</v>
       </c>
       <c r="D9" t="n">
-        <v>14.2</v>
+        <v>19.55</v>
       </c>
       <c r="E9" t="n">
-        <v>14.2</v>
+        <v>10.9</v>
       </c>
       <c r="F9" t="n">
-        <v>14.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>562</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01</v>
+        <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="J9" t="n">
-        <v>99.56</v>
+        <v>53.72</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>61.39</v>
       </c>
       <c r="L9" t="n">
-        <v>97.86</v>
+        <v>48.89</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2885</v>
+        <v>6772</v>
       </c>
       <c r="O9" t="n">
-        <v>6411</v>
+        <v>6588</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.73</v>
+        <v>19.19</v>
       </c>
       <c r="C10" t="n">
-        <v>14.93</v>
+        <v>20.1</v>
       </c>
       <c r="D10" t="n">
-        <v>14.58</v>
+        <v>18.13</v>
       </c>
       <c r="E10" t="n">
-        <v>14.2</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>13.7</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04</v>
+        <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="J10" t="n">
-        <v>97.15000000000001</v>
+        <v>67.73</v>
       </c>
       <c r="K10" t="n">
-        <v>99.09999999999999</v>
+        <v>76.56</v>
       </c>
       <c r="L10" t="n">
-        <v>92.56999999999999</v>
+        <v>60.33</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6806</v>
       </c>
       <c r="O10" t="n">
-        <v>6402</v>
+        <v>6608</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.59</v>
+        <v>16.91</v>
       </c>
       <c r="C11" t="n">
-        <v>14.64</v>
+        <v>17.56</v>
       </c>
       <c r="D11" t="n">
-        <v>14.53</v>
+        <v>16.26</v>
       </c>
       <c r="E11" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="F11" t="n">
-        <v>14.2</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
-        <v>98.76000000000001</v>
+        <v>81.03</v>
       </c>
       <c r="K11" t="n">
-        <v>99.54000000000001</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>98.01000000000001</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="O11" t="n">
-        <v>6405</v>
+        <v>6528</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.4</v>
+        <v>15.16</v>
       </c>
       <c r="C12" t="n">
-        <v>14.56</v>
+        <v>16.06</v>
       </c>
       <c r="D12" t="n">
-        <v>14.28</v>
+        <v>14.68</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="F12" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>98.81</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>97.73</v>
+        <v>88.64</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6585</v>
       </c>
       <c r="O12" t="n">
-        <v>6405</v>
+        <v>6468</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.31</v>
+        <v>14.4</v>
       </c>
       <c r="C13" t="n">
-        <v>14.48</v>
+        <v>14.62</v>
       </c>
       <c r="D13" t="n">
-        <v>14.24</v>
+        <v>14.25</v>
       </c>
       <c r="E13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F13" t="n">
         <v>14.2</v>
       </c>
-      <c r="F13" t="n">
-        <v>14.1</v>
-      </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1227,22 +1227,22 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>99.7</v>
+        <v>99.98</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>98</v>
+        <v>99.98</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3872</v>
       </c>
       <c r="O13" t="n">
-        <v>6405</v>
+        <v>6425</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1260,56 +1260,56 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.91</v>
+        <v>14.35</v>
       </c>
       <c r="C14" t="n">
-        <v>15.38</v>
+        <v>14.59</v>
       </c>
       <c r="D14" t="n">
-        <v>14.51</v>
+        <v>14.2</v>
       </c>
       <c r="E14" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="F14" t="n">
-        <v>13.1</v>
+        <v>14.1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>92.72</v>
+        <v>99.56</v>
       </c>
       <c r="K14" t="n">
-        <v>97.28</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>86.81999999999999</v>
+        <v>97.86</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="O14" t="n">
-        <v>6408</v>
+        <v>6411</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1321,41 +1321,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.65</v>
+        <v>14.73</v>
       </c>
       <c r="C15" t="n">
-        <v>15.83</v>
+        <v>14.93</v>
       </c>
       <c r="D15" t="n">
-        <v>15.43</v>
+        <v>14.58</v>
       </c>
       <c r="E15" t="n">
-        <v>12.9</v>
+        <v>14.2</v>
       </c>
       <c r="F15" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.27</v>
+        <v>0.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0.23</v>
+        <v>0.01</v>
       </c>
       <c r="J15" t="n">
-        <v>84.34999999999999</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>86.73999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>81.81</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1364,16 +1364,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>6411</v>
+        <v>6402</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1382,41 +1382,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.77</v>
+        <v>14.59</v>
       </c>
       <c r="C16" t="n">
-        <v>16.04</v>
+        <v>14.64</v>
       </c>
       <c r="D16" t="n">
-        <v>15.59</v>
+        <v>14.53</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="F16" t="n">
-        <v>12.7</v>
+        <v>14.2</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.28</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>84</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>86.05</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>80.77</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1425,16 +1425,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6414</v>
+        <v>6405</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1443,41 +1443,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.89</v>
+        <v>14.4</v>
       </c>
       <c r="C17" t="n">
-        <v>16.09</v>
+        <v>14.56</v>
       </c>
       <c r="D17" t="n">
-        <v>15.55</v>
+        <v>14.28</v>
       </c>
       <c r="E17" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="F17" t="n">
-        <v>12.5</v>
+        <v>14.1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33</v>
+        <v>0.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>81.48999999999999</v>
+        <v>98.81</v>
       </c>
       <c r="K17" t="n">
-        <v>83.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>80.19</v>
+        <v>97.73</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>6405</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1504,41 +1504,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15.43</v>
+        <v>14.31</v>
       </c>
       <c r="C18" t="n">
-        <v>15.49</v>
+        <v>14.48</v>
       </c>
       <c r="D18" t="n">
-        <v>15.38</v>
+        <v>14.24</v>
       </c>
       <c r="E18" t="n">
-        <v>12.7</v>
+        <v>14.2</v>
       </c>
       <c r="F18" t="n">
-        <v>12.6</v>
+        <v>14.1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>83.98999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="K18" t="n">
-        <v>85.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>83.27</v>
+        <v>98</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1547,16 +1547,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6408</v>
+        <v>6405</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1565,41 +1565,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.57</v>
+        <v>14.91</v>
       </c>
       <c r="C19" t="n">
-        <v>15.65</v>
+        <v>15.38</v>
       </c>
       <c r="D19" t="n">
-        <v>15.47</v>
+        <v>14.51</v>
       </c>
       <c r="E19" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="F19" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="J19" t="n">
-        <v>83.40000000000001</v>
+        <v>92.72</v>
       </c>
       <c r="K19" t="n">
-        <v>84.86</v>
+        <v>97.28</v>
       </c>
       <c r="L19" t="n">
-        <v>82.39</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1608,16 +1608,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6411</v>
+        <v>6408</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1626,20 +1626,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.77</v>
+        <v>15.65</v>
       </c>
       <c r="C20" t="n">
-        <v>15.92</v>
+        <v>15.83</v>
       </c>
       <c r="D20" t="n">
-        <v>15.58</v>
+        <v>15.43</v>
       </c>
       <c r="E20" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="F20" t="n">
         <v>12.7</v>
@@ -1654,13 +1654,13 @@
         <v>0.23</v>
       </c>
       <c r="J20" t="n">
-        <v>84.48</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>86.84</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>81.94</v>
+        <v>81.81</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
@@ -1687,41 +1687,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.16</v>
+        <v>15.77</v>
       </c>
       <c r="C21" t="n">
-        <v>16.42</v>
+        <v>16.04</v>
       </c>
       <c r="D21" t="n">
-        <v>15.94</v>
+        <v>15.59</v>
       </c>
       <c r="E21" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="I21" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="J21" t="n">
-        <v>81.48999999999999</v>
+        <v>84</v>
       </c>
       <c r="K21" t="n">
-        <v>84.55</v>
+        <v>86.05</v>
       </c>
       <c r="L21" t="n">
-        <v>78.12</v>
+        <v>80.77</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6420</v>
+        <v>6414</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -1739,7 +1739,7 @@
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1748,56 +1748,56 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.77</v>
+        <v>15.89</v>
       </c>
       <c r="C22" t="n">
-        <v>17.13</v>
+        <v>16.09</v>
       </c>
       <c r="D22" t="n">
-        <v>16.4</v>
+        <v>15.55</v>
       </c>
       <c r="E22" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F22" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="I22" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>75.39</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>78.58</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>72.19</v>
+        <v>80.19</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6431</v>
+        <v>6405</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>2</v>
@@ -1809,59 +1809,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.34</v>
+        <v>15.43</v>
       </c>
       <c r="C23" t="n">
-        <v>17.55</v>
+        <v>15.49</v>
       </c>
       <c r="D23" t="n">
-        <v>17.15</v>
+        <v>15.38</v>
       </c>
       <c r="E23" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="F23" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="G23" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.58</v>
+        <v>0.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="J23" t="n">
-        <v>70.43000000000001</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>72.41</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>68.52</v>
+        <v>83.27</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3144</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6459</v>
+        <v>6408</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -1870,663 +1870,663 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.83</v>
+        <v>15.57</v>
       </c>
       <c r="C24" t="n">
-        <v>18.09</v>
+        <v>15.65</v>
       </c>
       <c r="D24" t="n">
-        <v>17.42</v>
+        <v>15.47</v>
       </c>
       <c r="E24" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F24" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="G24" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="J24" t="n">
-        <v>66.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>69.8</v>
+        <v>84.86</v>
       </c>
       <c r="L24" t="n">
-        <v>62.77</v>
+        <v>82.39</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4749</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6491</v>
+        <v>6411</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.68</v>
+        <v>15.77</v>
       </c>
       <c r="C25" t="n">
-        <v>17.86</v>
+        <v>15.92</v>
       </c>
       <c r="D25" t="n">
-        <v>17.49</v>
+        <v>15.58</v>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>13.1</v>
       </c>
       <c r="F25" t="n">
-        <v>10.5</v>
+        <v>12.7</v>
       </c>
       <c r="G25" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="I25" t="n">
-        <v>0.66</v>
+        <v>0.23</v>
       </c>
       <c r="J25" t="n">
-        <v>65.15000000000001</v>
+        <v>84.48</v>
       </c>
       <c r="K25" t="n">
-        <v>67.11</v>
+        <v>86.84</v>
       </c>
       <c r="L25" t="n">
-        <v>63.11</v>
+        <v>81.94</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5962</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6502</v>
+        <v>6417</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17.45</v>
+        <v>16.16</v>
       </c>
       <c r="C26" t="n">
-        <v>17.76</v>
+        <v>16.42</v>
       </c>
       <c r="D26" t="n">
-        <v>17.19</v>
+        <v>15.94</v>
       </c>
       <c r="E26" t="n">
-        <v>10.9</v>
+        <v>12.9</v>
       </c>
       <c r="F26" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="G26" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.68</v>
+        <v>0.33</v>
       </c>
       <c r="I26" t="n">
-        <v>0.62</v>
+        <v>0.27</v>
       </c>
       <c r="J26" t="n">
-        <v>65.79000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>68.27</v>
+        <v>84.55</v>
       </c>
       <c r="L26" t="n">
-        <v>62.48</v>
+        <v>78.12</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6561</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6539</v>
+        <v>6420</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.1</v>
+        <v>16.77</v>
       </c>
       <c r="C27" t="n">
-        <v>17.35</v>
+        <v>17.13</v>
       </c>
       <c r="D27" t="n">
-        <v>16.86</v>
+        <v>16.4</v>
       </c>
       <c r="E27" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="F27" t="n">
-        <v>10.7</v>
+        <v>11.9</v>
       </c>
       <c r="G27" t="n">
-        <v>246</v>
+        <v>17</v>
       </c>
       <c r="H27" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="I27" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="J27" t="n">
-        <v>67.38</v>
+        <v>75.39</v>
       </c>
       <c r="K27" t="n">
-        <v>67.78</v>
+        <v>78.58</v>
       </c>
       <c r="L27" t="n">
-        <v>66.55</v>
+        <v>72.19</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6671</v>
+        <v>1164</v>
       </c>
       <c r="O27" t="n">
-        <v>6536</v>
+        <v>6431</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.52</v>
+        <v>17.34</v>
       </c>
       <c r="C28" t="n">
-        <v>17.36</v>
+        <v>17.55</v>
       </c>
       <c r="D28" t="n">
-        <v>16.01</v>
+        <v>17.15</v>
       </c>
       <c r="E28" t="n">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="F28" t="n">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="G28" t="n">
-        <v>301</v>
+        <v>58</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="J28" t="n">
-        <v>69.84</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>72.16</v>
+        <v>72.41</v>
       </c>
       <c r="L28" t="n">
-        <v>66.34999999999999</v>
+        <v>68.52</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6681</v>
+        <v>3144</v>
       </c>
       <c r="O28" t="n">
-        <v>6525</v>
+        <v>6459</v>
       </c>
       <c r="P28" t="n">
         <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
         <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15.55</v>
+        <v>17.83</v>
       </c>
       <c r="C29" t="n">
-        <v>16.32</v>
+        <v>18.09</v>
       </c>
       <c r="D29" t="n">
-        <v>15.05</v>
+        <v>17.42</v>
       </c>
       <c r="E29" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="F29" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="G29" t="n">
-        <v>231</v>
+        <v>125</v>
       </c>
       <c r="H29" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
-        <v>75.25</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>78.77</v>
+        <v>69.8</v>
       </c>
       <c r="L29" t="n">
-        <v>71.11</v>
+        <v>62.77</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6729</v>
+        <v>4749</v>
       </c>
       <c r="O29" t="n">
-        <v>6556</v>
+        <v>6491</v>
       </c>
       <c r="P29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
         <v>3</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2</v>
-      </c>
       <c r="S29" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15.04</v>
+        <v>17.68</v>
       </c>
       <c r="C30" t="n">
-        <v>15.26</v>
+        <v>17.86</v>
       </c>
       <c r="D30" t="n">
-        <v>14.82</v>
+        <v>17.49</v>
       </c>
       <c r="E30" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G30" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="H30" t="n">
-        <v>0.37</v>
+        <v>0.7</v>
       </c>
       <c r="I30" t="n">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J30" t="n">
-        <v>77.86</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>80.23</v>
+        <v>67.11</v>
       </c>
       <c r="L30" t="n">
-        <v>75.81</v>
+        <v>63.11</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5708</v>
+        <v>5962</v>
       </c>
       <c r="O30" t="n">
-        <v>6494</v>
+        <v>6502</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>14.47</v>
+        <v>17.45</v>
       </c>
       <c r="C31" t="n">
-        <v>14.79</v>
+        <v>17.76</v>
       </c>
       <c r="D31" t="n">
-        <v>14.22</v>
+        <v>17.19</v>
       </c>
       <c r="E31" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F31" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G31" t="n">
-        <v>131</v>
+        <v>210</v>
       </c>
       <c r="H31" t="n">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="I31" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="J31" t="n">
-        <v>80.75</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>82.34</v>
+        <v>68.27</v>
       </c>
       <c r="L31" t="n">
-        <v>79.73999999999999</v>
+        <v>62.48</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6254</v>
+        <v>6561</v>
       </c>
       <c r="O31" t="n">
-        <v>6491</v>
+        <v>6539</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14.34</v>
+        <v>17.1</v>
       </c>
       <c r="C32" t="n">
-        <v>14.4</v>
+        <v>17.35</v>
       </c>
       <c r="D32" t="n">
-        <v>14.25</v>
+        <v>16.86</v>
       </c>
       <c r="E32" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F32" t="n">
         <v>10.7</v>
       </c>
-      <c r="F32" t="n">
-        <v>10.3</v>
-      </c>
       <c r="G32" t="n">
-        <v>38</v>
+        <v>246</v>
       </c>
       <c r="H32" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="I32" t="n">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="J32" t="n">
-        <v>79.29000000000001</v>
+        <v>67.38</v>
       </c>
       <c r="K32" t="n">
-        <v>80.34999999999999</v>
+        <v>67.78</v>
       </c>
       <c r="L32" t="n">
-        <v>77.13</v>
+        <v>66.55</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3949</v>
+        <v>6671</v>
       </c>
       <c r="O32" t="n">
-        <v>6425</v>
+        <v>6536</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.56</v>
+        <v>16.52</v>
       </c>
       <c r="C33" t="n">
-        <v>14.75</v>
+        <v>17.36</v>
       </c>
       <c r="D33" t="n">
-        <v>14.34</v>
+        <v>16.01</v>
       </c>
       <c r="E33" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F33" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G33" t="n">
+        <v>301</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>69.84</v>
+      </c>
+      <c r="K33" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="L33" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6681</v>
+      </c>
+      <c r="O33" t="n">
+        <v>6525</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="n">
         <v>4</v>
       </c>
-      <c r="H33" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J33" t="n">
-        <v>78.20999999999999</v>
-      </c>
-      <c r="K33" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="L33" t="n">
-        <v>75.43000000000001</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2449</v>
-      </c>
-      <c r="O33" t="n">
-        <v>6420</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2</v>
-      </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>14.79</v>
+        <v>15.55</v>
       </c>
       <c r="C34" t="n">
-        <v>14.98</v>
+        <v>16.32</v>
       </c>
       <c r="D34" t="n">
-        <v>14.63</v>
+        <v>15.05</v>
       </c>
       <c r="E34" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F34" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H34" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="I34" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="J34" t="n">
-        <v>77.20999999999999</v>
+        <v>75.25</v>
       </c>
       <c r="K34" t="n">
-        <v>79.73999999999999</v>
+        <v>78.77</v>
       </c>
       <c r="L34" t="n">
-        <v>74.54000000000001</v>
+        <v>71.11</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6729</v>
       </c>
       <c r="O34" t="n">
-        <v>6411</v>
+        <v>6556</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
         <v>3</v>
@@ -2535,187 +2535,187 @@
         <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.24</v>
+        <v>15.04</v>
       </c>
       <c r="C35" t="n">
-        <v>15.48</v>
+        <v>15.26</v>
       </c>
       <c r="D35" t="n">
-        <v>15</v>
+        <v>14.82</v>
       </c>
       <c r="E35" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="F35" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="H35" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="I35" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="J35" t="n">
-        <v>74.68000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="K35" t="n">
-        <v>75.5</v>
+        <v>80.23</v>
       </c>
       <c r="L35" t="n">
-        <v>73.42</v>
+        <v>75.81</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5708</v>
       </c>
       <c r="O35" t="n">
-        <v>6411</v>
+        <v>6494</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.62</v>
+        <v>14.47</v>
       </c>
       <c r="C36" t="n">
-        <v>15.76</v>
+        <v>14.79</v>
       </c>
       <c r="D36" t="n">
-        <v>15.46</v>
+        <v>14.22</v>
       </c>
       <c r="E36" t="n">
-        <v>12.3</v>
+        <v>11.1</v>
       </c>
       <c r="F36" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H36" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="I36" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="J36" t="n">
-        <v>81.47</v>
+        <v>80.75</v>
       </c>
       <c r="K36" t="n">
-        <v>89.01000000000001</v>
+        <v>82.34</v>
       </c>
       <c r="L36" t="n">
-        <v>74.23</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O36" t="n">
-        <v>6402</v>
+        <v>6491</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.86</v>
+        <v>14.34</v>
       </c>
       <c r="C37" t="n">
-        <v>16.08</v>
+        <v>14.4</v>
       </c>
       <c r="D37" t="n">
-        <v>15.66</v>
+        <v>14.25</v>
       </c>
       <c r="E37" t="n">
-        <v>13.8</v>
+        <v>10.7</v>
       </c>
       <c r="F37" t="n">
-        <v>13.7</v>
+        <v>10.3</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H37" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="I37" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="J37" t="n">
-        <v>87.95999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>89.39</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>86.37</v>
+        <v>77.13</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O37" t="n">
-        <v>6411</v>
+        <v>6425</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -2724,50 +2724,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.22</v>
+        <v>14.56</v>
       </c>
       <c r="C38" t="n">
-        <v>16.35</v>
+        <v>14.75</v>
       </c>
       <c r="D38" t="n">
-        <v>16.12</v>
+        <v>14.34</v>
       </c>
       <c r="E38" t="n">
-        <v>13.7</v>
+        <v>10.8</v>
       </c>
       <c r="F38" t="n">
-        <v>13.4</v>
+        <v>10.4</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="I38" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="J38" t="n">
-        <v>85.42</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>87.15000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>83.22</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O38" t="n">
-        <v>6405</v>
+        <v>6420</v>
       </c>
       <c r="P38" t="n">
         <v>2</v>
@@ -2776,7 +2776,7 @@
         <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -2785,41 +2785,41 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.39</v>
+        <v>14.79</v>
       </c>
       <c r="C39" t="n">
-        <v>16.55</v>
+        <v>14.98</v>
       </c>
       <c r="D39" t="n">
-        <v>16.22</v>
+        <v>14.63</v>
       </c>
       <c r="E39" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
       <c r="F39" t="n">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="I39" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="J39" t="n">
-        <v>85.56999999999999</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>87.13</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>84.14</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -2846,41 +2846,41 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.68</v>
+        <v>15.24</v>
       </c>
       <c r="C40" t="n">
-        <v>16.76</v>
+        <v>15.48</v>
       </c>
       <c r="D40" t="n">
-        <v>16.63</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
-        <v>13.9</v>
+        <v>10.7</v>
       </c>
       <c r="F40" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="I40" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="J40" t="n">
-        <v>84.16</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>86.08</v>
+        <v>75.5</v>
       </c>
       <c r="L40" t="n">
-        <v>81.98</v>
+        <v>73.42</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2892,13 +2892,13 @@
         <v>6411</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -2907,41 +2907,41 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.64</v>
+        <v>15.62</v>
       </c>
       <c r="C41" t="n">
-        <v>16.72</v>
+        <v>15.76</v>
       </c>
       <c r="D41" t="n">
-        <v>16.62</v>
+        <v>15.46</v>
       </c>
       <c r="E41" t="n">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="F41" t="n">
-        <v>14.3</v>
+        <v>10.8</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I41" t="n">
         <v>0.19</v>
       </c>
-      <c r="I41" t="n">
-        <v>0.15</v>
-      </c>
       <c r="J41" t="n">
-        <v>89.45</v>
+        <v>81.47</v>
       </c>
       <c r="K41" t="n">
-        <v>91.73999999999999</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>85.8</v>
+        <v>74.23</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2950,13 +2950,13 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6411</v>
+        <v>6402</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -2968,41 +2968,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16.73</v>
+        <v>15.86</v>
       </c>
       <c r="C42" t="n">
-        <v>16.91</v>
+        <v>16.08</v>
       </c>
       <c r="D42" t="n">
-        <v>16.64</v>
+        <v>15.66</v>
       </c>
       <c r="E42" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="F42" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J42" t="n">
-        <v>91.16</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>91.98999999999999</v>
+        <v>89.39</v>
       </c>
       <c r="L42" t="n">
-        <v>89.92</v>
+        <v>86.37</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6417</v>
+        <v>6411</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3029,41 +3029,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.79</v>
+        <v>16.22</v>
       </c>
       <c r="C43" t="n">
-        <v>16.87</v>
+        <v>16.35</v>
       </c>
       <c r="D43" t="n">
-        <v>16.65</v>
+        <v>16.12</v>
       </c>
       <c r="E43" t="n">
-        <v>15.5</v>
+        <v>13.7</v>
       </c>
       <c r="F43" t="n">
-        <v>15.3</v>
+        <v>13.4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="I43" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="J43" t="n">
-        <v>92.09999999999999</v>
+        <v>85.42</v>
       </c>
       <c r="K43" t="n">
-        <v>93.45</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>90.81999999999999</v>
+        <v>83.22</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3072,13 +3072,13 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6420</v>
+        <v>6405</v>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -3090,41 +3090,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.6</v>
+        <v>16.39</v>
       </c>
       <c r="C44" t="n">
-        <v>16.66</v>
+        <v>16.55</v>
       </c>
       <c r="D44" t="n">
-        <v>16.52</v>
+        <v>16.22</v>
       </c>
       <c r="E44" t="n">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="F44" t="n">
-        <v>15.6</v>
+        <v>13.8</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="I44" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="J44" t="n">
-        <v>95.29000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>96.45999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="L44" t="n">
-        <v>93.84</v>
+        <v>84.14</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3133,16 +3133,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6425</v>
+        <v>6417</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
         <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3151,41 +3151,41 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 19:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.91</v>
+        <v>16.68</v>
       </c>
       <c r="C45" t="n">
-        <v>17.19</v>
+        <v>16.76</v>
       </c>
       <c r="D45" t="n">
-        <v>16.69</v>
+        <v>16.63</v>
       </c>
       <c r="E45" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="F45" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="I45" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="J45" t="n">
-        <v>94.18000000000001</v>
+        <v>84.16</v>
       </c>
       <c r="K45" t="n">
-        <v>96.09</v>
+        <v>86.08</v>
       </c>
       <c r="L45" t="n">
-        <v>90.87</v>
+        <v>81.98</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3194,16 +3194,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>6442</v>
+        <v>6411</v>
       </c>
       <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
         <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3212,56 +3212,56 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.68</v>
+        <v>16.64</v>
       </c>
       <c r="C46" t="n">
-        <v>18.12</v>
+        <v>16.72</v>
       </c>
       <c r="D46" t="n">
-        <v>17.08</v>
+        <v>16.62</v>
       </c>
       <c r="E46" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="F46" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="G46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="I46" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="J46" t="n">
-        <v>86.59</v>
+        <v>89.45</v>
       </c>
       <c r="K46" t="n">
-        <v>93.40000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>80.54000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6451</v>
+        <v>6411</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -3273,59 +3273,59 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 17:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.95</v>
+        <v>16.73</v>
       </c>
       <c r="C47" t="n">
-        <v>21.08</v>
+        <v>16.91</v>
       </c>
       <c r="D47" t="n">
-        <v>18.04</v>
+        <v>16.64</v>
       </c>
       <c r="E47" t="n">
-        <v>12.9</v>
+        <v>15.2</v>
       </c>
       <c r="F47" t="n">
-        <v>11.6</v>
+        <v>15.1</v>
       </c>
       <c r="G47" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.82</v>
+        <v>0.16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="J47" t="n">
-        <v>64.73999999999999</v>
+        <v>91.16</v>
       </c>
       <c r="K47" t="n">
-        <v>79.75</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>55.98</v>
+        <v>89.92</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6474</v>
+        <v>6417</v>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3334,59 +3334,59 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 16:00:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.54</v>
+        <v>16.79</v>
       </c>
       <c r="C48" t="n">
-        <v>21.83</v>
+        <v>16.87</v>
       </c>
       <c r="D48" t="n">
-        <v>21.18</v>
+        <v>16.65</v>
       </c>
       <c r="E48" t="n">
-        <v>11.6</v>
+        <v>15.5</v>
       </c>
       <c r="F48" t="n">
-        <v>10.7</v>
+        <v>15.3</v>
       </c>
       <c r="G48" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.19</v>
+        <v>0.14</v>
       </c>
       <c r="I48" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="J48" t="n">
-        <v>53.45</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>58.22</v>
+        <v>93.45</v>
       </c>
       <c r="L48" t="n">
-        <v>49.34</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6485</v>
+        <v>6420</v>
       </c>
       <c r="P48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -3395,62 +3395,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>22.02</v>
+        <v>16.6</v>
       </c>
       <c r="C49" t="n">
-        <v>22.16</v>
+        <v>16.66</v>
       </c>
       <c r="D49" t="n">
-        <v>21.88</v>
+        <v>16.52</v>
       </c>
       <c r="E49" t="n">
-        <v>11.1</v>
+        <v>15.8</v>
       </c>
       <c r="F49" t="n">
-        <v>10.4</v>
+        <v>15.6</v>
       </c>
       <c r="G49" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.31</v>
+        <v>0.08</v>
       </c>
       <c r="I49" t="n">
-        <v>1.24</v>
+        <v>0.06</v>
       </c>
       <c r="J49" t="n">
-        <v>50.18</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>52.66</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>47.74</v>
+        <v>93.84</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4352</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6511</v>
+        <v>6425</v>
       </c>
       <c r="P49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,41 +528,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.69</v>
+        <v>18.14</v>
       </c>
       <c r="C2" t="n">
-        <v>19.74</v>
+        <v>18.23</v>
       </c>
       <c r="D2" t="n">
-        <v>19.55</v>
+        <v>18.08</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="I2" t="n">
-        <v>0.83</v>
+        <v>0.49</v>
       </c>
       <c r="J2" t="n">
-        <v>62.17</v>
+        <v>73.34</v>
       </c>
       <c r="K2" t="n">
-        <v>63.42</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>61.3</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -571,16 +571,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6485</v>
+        <v>6454</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -589,59 +589,59 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.88</v>
+        <v>18.13</v>
       </c>
       <c r="C3" t="n">
-        <v>20.1</v>
+        <v>18.77</v>
       </c>
       <c r="D3" t="n">
-        <v>19.77</v>
+        <v>13.85</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="F3" t="n">
-        <v>11.8</v>
+        <v>10.6</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91</v>
+        <v>0.59</v>
       </c>
       <c r="I3" t="n">
-        <v>0.88</v>
+        <v>0.29</v>
       </c>
       <c r="J3" t="n">
-        <v>60.69</v>
+        <v>71.88</v>
       </c>
       <c r="K3" t="n">
-        <v>61.7</v>
+        <v>81.11</v>
       </c>
       <c r="L3" t="n">
-        <v>59.35</v>
+        <v>67.7</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6479</v>
+        <v>6454</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -650,59 +650,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.3</v>
+        <v>18.91</v>
       </c>
       <c r="C4" t="n">
-        <v>20.44</v>
+        <v>19.13</v>
       </c>
       <c r="D4" t="n">
-        <v>20.2</v>
+        <v>18.68</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="F4" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>0.97</v>
+        <v>0.63</v>
       </c>
       <c r="J4" t="n">
-        <v>57.79</v>
+        <v>67.64</v>
       </c>
       <c r="K4" t="n">
-        <v>58.95</v>
+        <v>70.67</v>
       </c>
       <c r="L4" t="n">
-        <v>56.53</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3470</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6505</v>
+        <v>6468</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -711,59 +711,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.04</v>
+        <v>19.41</v>
       </c>
       <c r="C5" t="n">
-        <v>21.75</v>
+        <v>19.74</v>
       </c>
       <c r="D5" t="n">
-        <v>20.48</v>
+        <v>18.99</v>
       </c>
       <c r="E5" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.02</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
-        <v>54.28</v>
+        <v>64.3</v>
       </c>
       <c r="K5" t="n">
-        <v>57.49</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>61.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3877</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6519</v>
+        <v>6477</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -772,303 +772,303 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.64</v>
+        <v>19.88</v>
       </c>
       <c r="C6" t="n">
-        <v>24.1</v>
+        <v>20.1</v>
       </c>
       <c r="D6" t="n">
-        <v>22.02</v>
+        <v>19.77</v>
       </c>
       <c r="E6" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="G6" t="n">
-        <v>273</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>1.27</v>
+        <v>0.88</v>
       </c>
       <c r="J6" t="n">
-        <v>49</v>
+        <v>60.69</v>
       </c>
       <c r="K6" t="n">
-        <v>51.75</v>
+        <v>61.7</v>
       </c>
       <c r="L6" t="n">
-        <v>44.97</v>
+        <v>59.35</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5075</v>
+        <v>1116</v>
       </c>
       <c r="O6" t="n">
-        <v>6545</v>
+        <v>6479</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.62</v>
+        <v>20.3</v>
       </c>
       <c r="C7" t="n">
-        <v>23.46</v>
+        <v>20.44</v>
       </c>
       <c r="D7" t="n">
-        <v>22.06</v>
+        <v>20.2</v>
       </c>
       <c r="E7" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="F7" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="G7" t="n">
-        <v>592</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.33</v>
+        <v>0.97</v>
       </c>
       <c r="J7" t="n">
-        <v>48.33</v>
+        <v>57.79</v>
       </c>
       <c r="K7" t="n">
-        <v>49.78</v>
+        <v>58.95</v>
       </c>
       <c r="L7" t="n">
-        <v>47.52</v>
+        <v>56.53</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6863</v>
+        <v>3470</v>
       </c>
       <c r="O7" t="n">
-        <v>6633</v>
+        <v>6505</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 13:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.55</v>
+        <v>21.04</v>
       </c>
       <c r="C8" t="n">
-        <v>22.58</v>
+        <v>21.75</v>
       </c>
       <c r="D8" t="n">
-        <v>21.03</v>
+        <v>20.48</v>
       </c>
       <c r="E8" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="F8" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>532</v>
+        <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="J8" t="n">
-        <v>49.94</v>
+        <v>54.28</v>
       </c>
       <c r="K8" t="n">
-        <v>51.47</v>
+        <v>57.49</v>
       </c>
       <c r="L8" t="n">
-        <v>48.14</v>
+        <v>52.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6878</v>
+        <v>3877</v>
       </c>
       <c r="O8" t="n">
-        <v>6645</v>
+        <v>6519</v>
       </c>
       <c r="P8" t="n">
         <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 12:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.76</v>
+        <v>22.64</v>
       </c>
       <c r="C9" t="n">
-        <v>21.18</v>
+        <v>24.1</v>
       </c>
       <c r="D9" t="n">
-        <v>19.55</v>
+        <v>22.02</v>
       </c>
       <c r="E9" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>562</v>
+        <v>273</v>
       </c>
       <c r="H9" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.87</v>
+        <v>1.27</v>
       </c>
       <c r="J9" t="n">
-        <v>53.72</v>
+        <v>49</v>
       </c>
       <c r="K9" t="n">
-        <v>61.39</v>
+        <v>51.75</v>
       </c>
       <c r="L9" t="n">
-        <v>48.89</v>
+        <v>44.97</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6772</v>
+        <v>5075</v>
       </c>
       <c r="O9" t="n">
-        <v>6588</v>
+        <v>6545</v>
       </c>
       <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>5</v>
-      </c>
       <c r="S9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 11:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.19</v>
+        <v>22.62</v>
       </c>
       <c r="C10" t="n">
-        <v>20.1</v>
+        <v>23.46</v>
       </c>
       <c r="D10" t="n">
-        <v>18.13</v>
+        <v>22.06</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>11.1</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="G10" t="n">
-        <v>650</v>
+        <v>592</v>
       </c>
       <c r="H10" t="n">
-        <v>0.72</v>
+        <v>1.42</v>
       </c>
       <c r="I10" t="n">
-        <v>0.52</v>
+        <v>1.33</v>
       </c>
       <c r="J10" t="n">
-        <v>67.73</v>
+        <v>48.33</v>
       </c>
       <c r="K10" t="n">
-        <v>76.56</v>
+        <v>49.78</v>
       </c>
       <c r="L10" t="n">
-        <v>60.33</v>
+        <v>47.52</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6806</v>
+        <v>6863</v>
       </c>
       <c r="O10" t="n">
-        <v>6608</v>
+        <v>6633</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S10" t="n">
         <v>60</v>
@@ -1077,59 +1077,59 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-19 13:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.91</v>
+        <v>21.55</v>
       </c>
       <c r="C11" t="n">
-        <v>17.56</v>
+        <v>22.58</v>
       </c>
       <c r="D11" t="n">
-        <v>16.26</v>
+        <v>21.03</v>
       </c>
       <c r="E11" t="n">
-        <v>13.6</v>
+        <v>10.6</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>10.3</v>
       </c>
       <c r="G11" t="n">
-        <v>244</v>
+        <v>532</v>
       </c>
       <c r="H11" t="n">
-        <v>0.36</v>
+        <v>1.28</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
-        <v>81.03</v>
+        <v>49.94</v>
       </c>
       <c r="K11" t="n">
-        <v>88.79000000000001</v>
+        <v>51.47</v>
       </c>
       <c r="L11" t="n">
-        <v>78.15000000000001</v>
+        <v>48.14</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6700</v>
+        <v>6878</v>
       </c>
       <c r="O11" t="n">
-        <v>6528</v>
+        <v>6645</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
         <v>60</v>
@@ -1138,233 +1138,233 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:00:00</t>
+          <t>2026-10-19 12:00:00</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.16</v>
+        <v>20.76</v>
       </c>
       <c r="C12" t="n">
-        <v>16.06</v>
+        <v>21.18</v>
       </c>
       <c r="D12" t="n">
-        <v>14.68</v>
+        <v>19.55</v>
       </c>
       <c r="E12" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="F12" t="n">
-        <v>13.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>111</v>
+        <v>562</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="J12" t="n">
-        <v>96.65000000000001</v>
+        <v>53.72</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>61.39</v>
       </c>
       <c r="L12" t="n">
-        <v>88.64</v>
+        <v>48.89</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6585</v>
+        <v>6772</v>
       </c>
       <c r="O12" t="n">
-        <v>6468</v>
+        <v>6588</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19 08:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.4</v>
+        <v>19.19</v>
       </c>
       <c r="C13" t="n">
-        <v>14.62</v>
+        <v>20.1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.25</v>
+        <v>18.13</v>
       </c>
       <c r="E13" t="n">
-        <v>14.3</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>14.2</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>650</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="J13" t="n">
-        <v>99.98</v>
+        <v>67.73</v>
       </c>
       <c r="K13" t="n">
-        <v>99.98999999999999</v>
+        <v>76.56</v>
       </c>
       <c r="L13" t="n">
-        <v>99.98</v>
+        <v>60.33</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3872</v>
+        <v>6806</v>
       </c>
       <c r="O13" t="n">
-        <v>6425</v>
+        <v>6608</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00:00</t>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.35</v>
+        <v>16.91</v>
       </c>
       <c r="C14" t="n">
-        <v>14.59</v>
+        <v>17.56</v>
       </c>
       <c r="D14" t="n">
-        <v>14.2</v>
+        <v>16.26</v>
       </c>
       <c r="E14" t="n">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
       <c r="F14" t="n">
-        <v>14.1</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>244</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
-        <v>99.56</v>
+        <v>81.03</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>97.86</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2885</v>
+        <v>6700</v>
       </c>
       <c r="O14" t="n">
-        <v>6411</v>
+        <v>6528</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.73</v>
+        <v>15.16</v>
       </c>
       <c r="C15" t="n">
-        <v>14.93</v>
+        <v>16.06</v>
       </c>
       <c r="D15" t="n">
-        <v>14.58</v>
+        <v>14.68</v>
       </c>
       <c r="E15" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="F15" t="n">
         <v>13.7</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H15" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>97.15000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>92.56999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6585</v>
       </c>
       <c r="O15" t="n">
-        <v>6402</v>
+        <v>6468</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1376,23 +1376,23 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19 05:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.59</v>
+        <v>14.4</v>
       </c>
       <c r="C16" t="n">
-        <v>14.64</v>
+        <v>14.62</v>
       </c>
       <c r="D16" t="n">
-        <v>14.53</v>
+        <v>14.25</v>
       </c>
       <c r="E16" t="n">
         <v>14.3</v>
@@ -1401,31 +1401,31 @@
         <v>14.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>98.76000000000001</v>
+        <v>99.98</v>
       </c>
       <c r="K16" t="n">
-        <v>99.54000000000001</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>98.01000000000001</v>
+        <v>99.98</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3872</v>
       </c>
       <c r="O16" t="n">
-        <v>6405</v>
+        <v>6425</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1443,50 +1443,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00:00</t>
+          <t>2026-10-19 07:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14.4</v>
+        <v>14.35</v>
       </c>
       <c r="C17" t="n">
-        <v>14.56</v>
+        <v>14.59</v>
       </c>
       <c r="D17" t="n">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="E17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="F17" t="n">
         <v>14.1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>98.81</v>
+        <v>99.56</v>
       </c>
       <c r="K17" t="n">
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>97.73</v>
+        <v>97.86</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="O17" t="n">
-        <v>6405</v>
+        <v>6411</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1504,41 +1504,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19 03:00:00</t>
+          <t>2026-10-19 06:00:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.31</v>
+        <v>14.73</v>
       </c>
       <c r="C18" t="n">
-        <v>14.48</v>
+        <v>14.93</v>
       </c>
       <c r="D18" t="n">
-        <v>14.24</v>
+        <v>14.58</v>
       </c>
       <c r="E18" t="n">
         <v>14.2</v>
       </c>
       <c r="F18" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J18" t="n">
-        <v>99.7</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>98</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1547,13 +1547,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6405</v>
+        <v>6402</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1565,41 +1565,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00:00</t>
+          <t>2026-10-19 05:00:00</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14.91</v>
+        <v>14.59</v>
       </c>
       <c r="C19" t="n">
-        <v>15.38</v>
+        <v>14.64</v>
       </c>
       <c r="D19" t="n">
-        <v>14.51</v>
+        <v>14.53</v>
       </c>
       <c r="E19" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="F19" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>92.72</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>97.28</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>86.81999999999999</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1608,13 +1608,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6408</v>
+        <v>6405</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1626,41 +1626,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00:00</t>
+          <t>2026-10-19 04:00:00</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.65</v>
+        <v>14.4</v>
       </c>
       <c r="C20" t="n">
-        <v>15.83</v>
+        <v>14.56</v>
       </c>
       <c r="D20" t="n">
-        <v>15.43</v>
+        <v>14.28</v>
       </c>
       <c r="E20" t="n">
-        <v>12.9</v>
+        <v>14.1</v>
       </c>
       <c r="F20" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.27</v>
+        <v>0.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>84.34999999999999</v>
+        <v>98.81</v>
       </c>
       <c r="K20" t="n">
-        <v>86.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>81.81</v>
+        <v>97.73</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1669,16 +1669,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1687,41 +1687,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-19 03:00:00</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.77</v>
+        <v>14.31</v>
       </c>
       <c r="C21" t="n">
-        <v>16.04</v>
+        <v>14.48</v>
       </c>
       <c r="D21" t="n">
-        <v>15.59</v>
+        <v>14.24</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="F21" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>84</v>
+        <v>99.7</v>
       </c>
       <c r="K21" t="n">
-        <v>86.05</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>80.77</v>
+        <v>98</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1730,16 +1730,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6414</v>
+        <v>6405</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1748,41 +1748,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-19 02:00:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15.89</v>
+        <v>14.91</v>
       </c>
       <c r="C22" t="n">
-        <v>16.09</v>
+        <v>15.38</v>
       </c>
       <c r="D22" t="n">
-        <v>15.55</v>
+        <v>14.51</v>
       </c>
       <c r="E22" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="F22" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.33</v>
+        <v>0.12</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.04</v>
       </c>
       <c r="J22" t="n">
-        <v>81.48999999999999</v>
+        <v>92.72</v>
       </c>
       <c r="K22" t="n">
-        <v>83.06999999999999</v>
+        <v>97.28</v>
       </c>
       <c r="L22" t="n">
-        <v>80.19</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1791,16 +1791,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6405</v>
+        <v>6408</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -1809,23 +1809,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-18 22:00:00</t>
+          <t>2026-10-19 01:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="C23" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="D23" t="n">
         <v>15.43</v>
       </c>
-      <c r="C23" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="D23" t="n">
-        <v>15.38</v>
-      </c>
       <c r="E23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F23" t="n">
         <v>12.7</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1834,16 +1834,16 @@
         <v>0.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="J23" t="n">
-        <v>83.98999999999999</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>85.06999999999999</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>83.27</v>
+        <v>81.81</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6408</v>
+        <v>6411</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -1861,7 +1861,7 @@
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -1870,41 +1870,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-18 21:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.57</v>
+        <v>15.77</v>
       </c>
       <c r="C24" t="n">
-        <v>15.65</v>
+        <v>16.04</v>
       </c>
       <c r="D24" t="n">
-        <v>15.47</v>
+        <v>15.59</v>
       </c>
       <c r="E24" t="n">
+        <v>13</v>
+      </c>
+      <c r="F24" t="n">
         <v>12.7</v>
       </c>
-      <c r="F24" t="n">
-        <v>12.5</v>
-      </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="J24" t="n">
-        <v>83.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="K24" t="n">
-        <v>84.86</v>
+        <v>86.05</v>
       </c>
       <c r="L24" t="n">
-        <v>82.39</v>
+        <v>80.77</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6411</v>
+        <v>6414</v>
       </c>
       <c r="P24" t="n">
         <v>2</v>
@@ -1922,7 +1922,7 @@
         <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -1931,41 +1931,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-18 23:00:00</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.77</v>
+        <v>15.89</v>
       </c>
       <c r="C25" t="n">
-        <v>15.92</v>
+        <v>16.09</v>
       </c>
       <c r="D25" t="n">
-        <v>15.58</v>
+        <v>15.55</v>
       </c>
       <c r="E25" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="F25" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="I25" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="J25" t="n">
-        <v>84.48</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>86.84</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>81.94</v>
+        <v>80.19</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6417</v>
+        <v>6405</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
@@ -1983,7 +1983,7 @@
         <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -1992,41 +1992,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 19:00:00</t>
+          <t>2026-10-18 22:00:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.16</v>
+        <v>15.43</v>
       </c>
       <c r="C26" t="n">
-        <v>16.42</v>
+        <v>15.49</v>
       </c>
       <c r="D26" t="n">
-        <v>15.94</v>
+        <v>15.38</v>
       </c>
       <c r="E26" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="F26" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="I26" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J26" t="n">
-        <v>81.48999999999999</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>84.55</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>78.12</v>
+        <v>83.27</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6420</v>
+        <v>6408</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -2053,56 +2053,56 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 21:00:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.77</v>
+        <v>15.57</v>
       </c>
       <c r="C27" t="n">
-        <v>17.13</v>
+        <v>15.65</v>
       </c>
       <c r="D27" t="n">
-        <v>16.4</v>
+        <v>15.47</v>
       </c>
       <c r="E27" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="F27" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="G27" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.46</v>
+        <v>0.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="J27" t="n">
-        <v>75.39</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>78.58</v>
+        <v>84.86</v>
       </c>
       <c r="L27" t="n">
-        <v>72.19</v>
+        <v>82.39</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6431</v>
+        <v>6411</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -2114,59 +2114,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 20:00:00</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17.34</v>
+        <v>15.77</v>
       </c>
       <c r="C28" t="n">
-        <v>17.55</v>
+        <v>15.92</v>
       </c>
       <c r="D28" t="n">
-        <v>17.15</v>
+        <v>15.58</v>
       </c>
       <c r="E28" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="F28" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.58</v>
+        <v>0.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="J28" t="n">
-        <v>70.43000000000001</v>
+        <v>84.48</v>
       </c>
       <c r="K28" t="n">
-        <v>72.41</v>
+        <v>86.84</v>
       </c>
       <c r="L28" t="n">
-        <v>68.52</v>
+        <v>81.94</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3144</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6459</v>
+        <v>6417</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2175,233 +2175,233 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 19:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17.83</v>
+        <v>16.16</v>
       </c>
       <c r="C29" t="n">
-        <v>18.09</v>
+        <v>16.42</v>
       </c>
       <c r="D29" t="n">
-        <v>17.42</v>
+        <v>15.94</v>
       </c>
       <c r="E29" t="n">
-        <v>11.3</v>
+        <v>12.9</v>
       </c>
       <c r="F29" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="G29" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="J29" t="n">
-        <v>66.04000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>69.8</v>
+        <v>84.55</v>
       </c>
       <c r="L29" t="n">
-        <v>62.77</v>
+        <v>78.12</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4749</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6491</v>
+        <v>6420</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.68</v>
+        <v>16.77</v>
       </c>
       <c r="C30" t="n">
-        <v>17.86</v>
+        <v>17.13</v>
       </c>
       <c r="D30" t="n">
-        <v>17.49</v>
+        <v>16.4</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="F30" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="G30" t="n">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="I30" t="n">
-        <v>0.66</v>
+        <v>0.39</v>
       </c>
       <c r="J30" t="n">
-        <v>65.15000000000001</v>
+        <v>75.39</v>
       </c>
       <c r="K30" t="n">
-        <v>67.11</v>
+        <v>78.58</v>
       </c>
       <c r="L30" t="n">
-        <v>63.11</v>
+        <v>72.19</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5962</v>
+        <v>1164</v>
       </c>
       <c r="O30" t="n">
-        <v>6502</v>
+        <v>6431</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.45</v>
+        <v>17.34</v>
       </c>
       <c r="C31" t="n">
-        <v>17.76</v>
+        <v>17.55</v>
       </c>
       <c r="D31" t="n">
-        <v>17.19</v>
+        <v>17.15</v>
       </c>
       <c r="E31" t="n">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="F31" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="G31" t="n">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="H31" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="I31" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="J31" t="n">
-        <v>65.79000000000001</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>68.27</v>
+        <v>72.41</v>
       </c>
       <c r="L31" t="n">
-        <v>62.48</v>
+        <v>68.52</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6561</v>
+        <v>3144</v>
       </c>
       <c r="O31" t="n">
-        <v>6539</v>
+        <v>6459</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
         <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.1</v>
+        <v>17.83</v>
       </c>
       <c r="C32" t="n">
-        <v>17.35</v>
+        <v>18.09</v>
       </c>
       <c r="D32" t="n">
-        <v>16.86</v>
+        <v>17.42</v>
       </c>
       <c r="E32" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F32" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="G32" t="n">
-        <v>246</v>
+        <v>125</v>
       </c>
       <c r="H32" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
-        <v>67.38</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>67.78</v>
+        <v>69.8</v>
       </c>
       <c r="L32" t="n">
-        <v>66.55</v>
+        <v>62.77</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6671</v>
+        <v>4749</v>
       </c>
       <c r="O32" t="n">
-        <v>6536</v>
+        <v>6491</v>
       </c>
       <c r="P32" t="n">
         <v>4</v>
@@ -2413,126 +2413,126 @@
         <v>3</v>
       </c>
       <c r="S32" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.52</v>
+        <v>17.68</v>
       </c>
       <c r="C33" t="n">
-        <v>17.36</v>
+        <v>17.86</v>
       </c>
       <c r="D33" t="n">
-        <v>16.01</v>
+        <v>17.49</v>
       </c>
       <c r="E33" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G33" t="n">
-        <v>301</v>
+        <v>148</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="J33" t="n">
-        <v>69.84</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>72.16</v>
+        <v>67.11</v>
       </c>
       <c r="L33" t="n">
-        <v>66.34999999999999</v>
+        <v>63.11</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6681</v>
+        <v>5962</v>
       </c>
       <c r="O33" t="n">
-        <v>6525</v>
+        <v>6502</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
         <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15.55</v>
+        <v>17.45</v>
       </c>
       <c r="C34" t="n">
-        <v>16.32</v>
+        <v>17.76</v>
       </c>
       <c r="D34" t="n">
-        <v>15.05</v>
+        <v>17.19</v>
       </c>
       <c r="E34" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F34" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G34" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="H34" t="n">
-        <v>0.43</v>
+        <v>0.68</v>
       </c>
       <c r="I34" t="n">
-        <v>0.36</v>
+        <v>0.62</v>
       </c>
       <c r="J34" t="n">
-        <v>75.25</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>78.77</v>
+        <v>68.27</v>
       </c>
       <c r="L34" t="n">
-        <v>71.11</v>
+        <v>62.48</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6729</v>
+        <v>6561</v>
       </c>
       <c r="O34" t="n">
-        <v>6556</v>
+        <v>6539</v>
       </c>
       <c r="P34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
         <v>3</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>60</v>
@@ -2541,233 +2541,233 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.04</v>
+        <v>17.1</v>
       </c>
       <c r="C35" t="n">
-        <v>15.26</v>
+        <v>17.35</v>
       </c>
       <c r="D35" t="n">
-        <v>14.82</v>
+        <v>16.86</v>
       </c>
       <c r="E35" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="G35" t="n">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="H35" t="n">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="I35" t="n">
-        <v>0.33</v>
+        <v>0.61</v>
       </c>
       <c r="J35" t="n">
-        <v>77.86</v>
+        <v>67.38</v>
       </c>
       <c r="K35" t="n">
-        <v>80.23</v>
+        <v>67.78</v>
       </c>
       <c r="L35" t="n">
-        <v>75.81</v>
+        <v>66.55</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5708</v>
+        <v>6671</v>
       </c>
       <c r="O35" t="n">
-        <v>6494</v>
+        <v>6536</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 09:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14.47</v>
+        <v>16.52</v>
       </c>
       <c r="C36" t="n">
-        <v>14.79</v>
+        <v>17.36</v>
       </c>
       <c r="D36" t="n">
-        <v>14.22</v>
+        <v>16.01</v>
       </c>
       <c r="E36" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="F36" t="n">
         <v>10.7</v>
       </c>
       <c r="G36" t="n">
-        <v>131</v>
+        <v>301</v>
       </c>
       <c r="H36" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
-        <v>80.75</v>
+        <v>69.84</v>
       </c>
       <c r="K36" t="n">
-        <v>82.34</v>
+        <v>72.16</v>
       </c>
       <c r="L36" t="n">
-        <v>79.73999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6254</v>
+        <v>6681</v>
       </c>
       <c r="O36" t="n">
-        <v>6491</v>
+        <v>6525</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14.34</v>
+        <v>15.55</v>
       </c>
       <c r="C37" t="n">
-        <v>14.4</v>
+        <v>16.32</v>
       </c>
       <c r="D37" t="n">
-        <v>14.25</v>
+        <v>15.05</v>
       </c>
       <c r="E37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F37" t="n">
         <v>10.7</v>
       </c>
-      <c r="F37" t="n">
-        <v>10.3</v>
-      </c>
       <c r="G37" t="n">
-        <v>38</v>
+        <v>231</v>
       </c>
       <c r="H37" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="I37" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="J37" t="n">
-        <v>79.29000000000001</v>
+        <v>75.25</v>
       </c>
       <c r="K37" t="n">
-        <v>80.34999999999999</v>
+        <v>78.77</v>
       </c>
       <c r="L37" t="n">
-        <v>77.13</v>
+        <v>71.11</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3949</v>
+        <v>6729</v>
       </c>
       <c r="O37" t="n">
-        <v>6425</v>
+        <v>6556</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
         <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 07:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.56</v>
+        <v>15.04</v>
       </c>
       <c r="C38" t="n">
-        <v>14.75</v>
+        <v>15.26</v>
       </c>
       <c r="D38" t="n">
-        <v>14.34</v>
+        <v>14.82</v>
       </c>
       <c r="E38" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F38" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="H38" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I38" t="n">
         <v>0.33</v>
       </c>
       <c r="J38" t="n">
-        <v>78.20999999999999</v>
+        <v>77.86</v>
       </c>
       <c r="K38" t="n">
-        <v>80.09999999999999</v>
+        <v>80.23</v>
       </c>
       <c r="L38" t="n">
-        <v>75.43000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2449</v>
+        <v>5708</v>
       </c>
       <c r="O38" t="n">
-        <v>6420</v>
+        <v>6494</v>
       </c>
       <c r="P38" t="n">
         <v>2</v>
@@ -2779,126 +2779,126 @@
         <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 06:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="C39" t="n">
         <v>14.79</v>
       </c>
-      <c r="C39" t="n">
-        <v>14.98</v>
-      </c>
       <c r="D39" t="n">
-        <v>14.63</v>
+        <v>14.22</v>
       </c>
       <c r="E39" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F39" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H39" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I39" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="J39" t="n">
-        <v>77.20999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="K39" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="L39" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="L39" t="n">
-        <v>74.54000000000001</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6254</v>
       </c>
       <c r="O39" t="n">
-        <v>6411</v>
+        <v>6491</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 05:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15.24</v>
+        <v>14.34</v>
       </c>
       <c r="C40" t="n">
-        <v>15.48</v>
+        <v>14.4</v>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="E40" t="n">
         <v>10.7</v>
       </c>
       <c r="F40" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H40" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="I40" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="J40" t="n">
-        <v>74.68000000000001</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>75.5</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>73.42</v>
+        <v>77.13</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O40" t="n">
-        <v>6411</v>
+        <v>6425</v>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -2907,59 +2907,59 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18 04:00:00</t>
+          <t>2026-10-18 07:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.62</v>
+        <v>14.56</v>
       </c>
       <c r="C41" t="n">
-        <v>15.76</v>
+        <v>14.75</v>
       </c>
       <c r="D41" t="n">
-        <v>15.46</v>
+        <v>14.34</v>
       </c>
       <c r="E41" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="F41" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I41" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J41" t="n">
-        <v>81.47</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>89.01000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>74.23</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="O41" t="n">
-        <v>6402</v>
+        <v>6420</v>
       </c>
       <c r="P41" t="n">
         <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -2968,41 +2968,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-18 03:00:00</t>
+          <t>2026-10-18 06:00:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.86</v>
+        <v>14.79</v>
       </c>
       <c r="C42" t="n">
-        <v>16.08</v>
+        <v>14.98</v>
       </c>
       <c r="D42" t="n">
-        <v>15.66</v>
+        <v>14.63</v>
       </c>
       <c r="E42" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="F42" t="n">
-        <v>13.7</v>
+        <v>10.4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="I42" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="J42" t="n">
-        <v>87.95999999999999</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>89.39</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>86.37</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3014,13 +3014,13 @@
         <v>6411</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3029,41 +3029,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18 02:00:00</t>
+          <t>2026-10-18 05:00:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16.22</v>
+        <v>15.24</v>
       </c>
       <c r="C43" t="n">
-        <v>16.35</v>
+        <v>15.48</v>
       </c>
       <c r="D43" t="n">
-        <v>16.12</v>
+        <v>15</v>
       </c>
       <c r="E43" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="F43" t="n">
-        <v>13.4</v>
+        <v>10.4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="I43" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="J43" t="n">
-        <v>85.42</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>87.15000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="L43" t="n">
-        <v>83.22</v>
+        <v>73.42</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3072,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6405</v>
+        <v>6411</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3090,41 +3090,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 01:00:00</t>
+          <t>2026-10-18 04:00:00</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.39</v>
+        <v>15.62</v>
       </c>
       <c r="C44" t="n">
-        <v>16.55</v>
+        <v>15.76</v>
       </c>
       <c r="D44" t="n">
-        <v>16.22</v>
+        <v>15.46</v>
       </c>
       <c r="E44" t="n">
-        <v>13.9</v>
+        <v>12.3</v>
       </c>
       <c r="F44" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I44" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J44" t="n">
-        <v>85.56999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="K44" t="n">
-        <v>87.13</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>84.14</v>
+        <v>74.23</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3133,13 +3133,13 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>6417</v>
+        <v>6402</v>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -3151,41 +3151,41 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-18 03:00:00</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.68</v>
+        <v>15.86</v>
       </c>
       <c r="C45" t="n">
-        <v>16.76</v>
+        <v>16.08</v>
       </c>
       <c r="D45" t="n">
-        <v>16.63</v>
+        <v>15.66</v>
       </c>
       <c r="E45" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F45" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="I45" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="J45" t="n">
-        <v>84.16</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>86.08</v>
+        <v>89.39</v>
       </c>
       <c r="L45" t="n">
-        <v>81.98</v>
+        <v>86.37</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3197,10 +3197,10 @@
         <v>6411</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -3212,41 +3212,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-18 02:00:00</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16.64</v>
+        <v>16.22</v>
       </c>
       <c r="C46" t="n">
-        <v>16.72</v>
+        <v>16.35</v>
       </c>
       <c r="D46" t="n">
-        <v>16.62</v>
+        <v>16.12</v>
       </c>
       <c r="E46" t="n">
-        <v>14.8</v>
+        <v>13.7</v>
       </c>
       <c r="F46" t="n">
-        <v>14.3</v>
+        <v>13.4</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="I46" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J46" t="n">
-        <v>89.45</v>
+        <v>85.42</v>
       </c>
       <c r="K46" t="n">
-        <v>91.73999999999999</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>85.8</v>
+        <v>83.22</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>6411</v>
+        <v>6405</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -3273,41 +3273,41 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-18 01:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.73</v>
+        <v>16.39</v>
       </c>
       <c r="C47" t="n">
-        <v>16.91</v>
+        <v>16.55</v>
       </c>
       <c r="D47" t="n">
-        <v>16.64</v>
+        <v>16.22</v>
       </c>
       <c r="E47" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="F47" t="n">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J47" t="n">
-        <v>91.16</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>91.98999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="L47" t="n">
-        <v>89.92</v>
+        <v>84.14</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -3334,41 +3334,41 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16.79</v>
+        <v>16.68</v>
       </c>
       <c r="C48" t="n">
-        <v>16.87</v>
+        <v>16.76</v>
       </c>
       <c r="D48" t="n">
-        <v>16.65</v>
+        <v>16.63</v>
       </c>
       <c r="E48" t="n">
-        <v>15.5</v>
+        <v>13.9</v>
       </c>
       <c r="F48" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="I48" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J48" t="n">
-        <v>92.09999999999999</v>
+        <v>84.16</v>
       </c>
       <c r="K48" t="n">
-        <v>93.45</v>
+        <v>86.08</v>
       </c>
       <c r="L48" t="n">
-        <v>90.81999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3377,13 +3377,13 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6420</v>
+        <v>6411</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -3395,41 +3395,41 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16.6</v>
+        <v>16.64</v>
       </c>
       <c r="C49" t="n">
-        <v>16.66</v>
+        <v>16.72</v>
       </c>
       <c r="D49" t="n">
-        <v>16.52</v>
+        <v>16.62</v>
       </c>
       <c r="E49" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="F49" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="I49" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J49" t="n">
-        <v>95.29000000000001</v>
+        <v>89.45</v>
       </c>
       <c r="K49" t="n">
-        <v>96.45999999999999</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>93.84</v>
+        <v>85.8</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3438,16 +3438,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6425</v>
+        <v>6411</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>

--- a/00002586_station_data.xlsx
+++ b/00002586_station_data.xlsx
@@ -528,41 +528,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 22:00:00</t>
+          <t>2026-10-20 03:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.14</v>
+        <v>17.27</v>
       </c>
       <c r="C2" t="n">
-        <v>18.23</v>
+        <v>17.33</v>
       </c>
       <c r="D2" t="n">
-        <v>18.08</v>
+        <v>17.21</v>
       </c>
       <c r="E2" t="n">
-        <v>13.2</v>
+        <v>15.1</v>
       </c>
       <c r="F2" t="n">
-        <v>12.8</v>
+        <v>14.8</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.55</v>
+        <v>0.24</v>
       </c>
       <c r="I2" t="n">
-        <v>0.49</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>73.34</v>
+        <v>87.67</v>
       </c>
       <c r="K2" t="n">
-        <v>76.23999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="L2" t="n">
-        <v>71.04000000000001</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -571,16 +571,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6454</v>
+        <v>6402</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -589,41 +589,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 21:00:00</t>
+          <t>2026-10-20 02:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.13</v>
+        <v>17.02</v>
       </c>
       <c r="C3" t="n">
-        <v>18.77</v>
+        <v>17.3</v>
       </c>
       <c r="D3" t="n">
-        <v>13.85</v>
+        <v>16.89</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="F3" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.59</v>
+        <v>0.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.29</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>71.88</v>
+        <v>92.61</v>
       </c>
       <c r="K3" t="n">
-        <v>81.11</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>67.7</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -632,16 +632,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6454</v>
+        <v>6408</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -650,41 +650,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 20:00:00</t>
+          <t>2026-10-20 01:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.91</v>
+        <v>17.3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.13</v>
+        <v>17.52</v>
       </c>
       <c r="D4" t="n">
-        <v>18.68</v>
+        <v>17.1</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7</v>
+        <v>15.7</v>
       </c>
       <c r="F4" t="n">
-        <v>12.3</v>
+        <v>15.3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.63</v>
+        <v>0.12</v>
       </c>
       <c r="J4" t="n">
-        <v>67.64</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>70.67</v>
+        <v>93.67</v>
       </c>
       <c r="L4" t="n">
-        <v>65.40000000000001</v>
+        <v>88.58</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -693,16 +693,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6468</v>
+        <v>6414</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -711,41 +711,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 19:00:00</t>
+          <t>2026-10-20 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.41</v>
+        <v>17.64</v>
       </c>
       <c r="C5" t="n">
-        <v>19.74</v>
+        <v>17.83</v>
       </c>
       <c r="D5" t="n">
-        <v>18.99</v>
+        <v>17.52</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4</v>
+        <v>15.2</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0.27</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>0.22</v>
       </c>
       <c r="J5" t="n">
-        <v>64.3</v>
+        <v>86.12</v>
       </c>
       <c r="K5" t="n">
-        <v>67.73999999999999</v>
+        <v>88.86</v>
       </c>
       <c r="L5" t="n">
-        <v>61.3</v>
+        <v>81.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -754,16 +754,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6477</v>
+        <v>6414</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -772,59 +772,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-19 23:00:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.88</v>
+        <v>17.9</v>
       </c>
       <c r="C6" t="n">
-        <v>20.1</v>
+        <v>18.03</v>
       </c>
       <c r="D6" t="n">
-        <v>19.77</v>
+        <v>17.71</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
       <c r="F6" t="n">
-        <v>11.8</v>
+        <v>13.3</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.91</v>
+        <v>0.41</v>
       </c>
       <c r="I6" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="J6" t="n">
-        <v>60.69</v>
+        <v>79.94</v>
       </c>
       <c r="K6" t="n">
-        <v>61.7</v>
+        <v>84.3</v>
       </c>
       <c r="L6" t="n">
-        <v>59.35</v>
+        <v>74.36</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6479</v>
+        <v>6431</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -833,59 +833,59 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-19 22:00:00</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>20.44</v>
+        <v>18.23</v>
       </c>
       <c r="D7" t="n">
-        <v>20.2</v>
+        <v>17.77</v>
       </c>
       <c r="E7" t="n">
-        <v>11.6</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>11.4</v>
+        <v>12.8</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="I7" t="n">
-        <v>0.97</v>
+        <v>0.36</v>
       </c>
       <c r="J7" t="n">
-        <v>57.79</v>
+        <v>77.84</v>
       </c>
       <c r="K7" t="n">
-        <v>58.95</v>
+        <v>82.38</v>
       </c>
       <c r="L7" t="n">
-        <v>56.53</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3470</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6505</v>
+        <v>6454</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -894,59 +894,59 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-19 21:00:00</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.04</v>
+        <v>18.13</v>
       </c>
       <c r="C8" t="n">
-        <v>21.75</v>
+        <v>18.77</v>
       </c>
       <c r="D8" t="n">
-        <v>20.48</v>
+        <v>13.85</v>
       </c>
       <c r="E8" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="G8" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="I8" t="n">
-        <v>1.02</v>
+        <v>0.29</v>
       </c>
       <c r="J8" t="n">
-        <v>54.28</v>
+        <v>71.88</v>
       </c>
       <c r="K8" t="n">
-        <v>57.49</v>
+        <v>81.11</v>
       </c>
       <c r="L8" t="n">
-        <v>52.2</v>
+        <v>67.7</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3877</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6519</v>
+        <v>6454</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -955,758 +955,758 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00:00</t>
+          <t>2026-10-19 20:00:00</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.64</v>
+        <v>18.91</v>
       </c>
       <c r="C9" t="n">
-        <v>24.1</v>
+        <v>19.13</v>
       </c>
       <c r="D9" t="n">
-        <v>22.02</v>
+        <v>18.68</v>
       </c>
       <c r="E9" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="G9" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.27</v>
+        <v>0.63</v>
       </c>
       <c r="J9" t="n">
-        <v>49</v>
+        <v>67.64</v>
       </c>
       <c r="K9" t="n">
-        <v>51.75</v>
+        <v>70.67</v>
       </c>
       <c r="L9" t="n">
-        <v>44.97</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5075</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6545</v>
+        <v>6468</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-19 19:00:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.62</v>
+        <v>19.41</v>
       </c>
       <c r="C10" t="n">
-        <v>23.46</v>
+        <v>19.74</v>
       </c>
       <c r="D10" t="n">
-        <v>22.06</v>
+        <v>18.99</v>
       </c>
       <c r="E10" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="F10